--- a/s60_signal/position-03328-601328.xlsx
+++ b/s60_signal/position-03328-601328.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="383">
   <si>
     <t>trade_time</t>
   </si>
@@ -454,6 +454,9 @@
     <t>2021-06-25</t>
   </si>
   <si>
+    <t>2021-10-20</t>
+  </si>
+  <si>
     <t>2016-05-31</t>
   </si>
   <si>
@@ -817,6 +820,9 @@
     <t>2021-06-28</t>
   </si>
   <si>
+    <t>2021-10-21</t>
+  </si>
+  <si>
     <t>2016-05-24</t>
   </si>
   <si>
@@ -1151,6 +1157,12 @@
   </si>
   <si>
     <t>2021-04-29</t>
+  </si>
+  <si>
+    <t>2021-10-15</t>
+  </si>
+  <si>
+    <t>2021-10-18</t>
   </si>
 </sst>
 </file>
@@ -1508,7 +1520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P482"/>
+  <dimension ref="A1:P484"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1569,7 +1581,7 @@
         <v>2.636521639996683</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E2">
         <v>2.833647241107702</v>
@@ -1605,7 +1617,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1619,7 +1631,7 @@
         <v>2.808801457176021</v>
       </c>
       <c r="D3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E3">
         <v>2.7135041663212</v>
@@ -1655,7 +1667,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1669,7 +1681,7 @@
         <v>2.746397091058633</v>
       </c>
       <c r="D4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E4">
         <v>2.648930323263125</v>
@@ -1719,7 +1731,7 @@
         <v>2.683209227271539</v>
       </c>
       <c r="D5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E5">
         <v>2.583545744375049</v>
@@ -1755,7 +1767,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1769,7 +1781,7 @@
         <v>2.555958070922727</v>
       </c>
       <c r="D6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E6">
         <v>2.632522016358742</v>
@@ -1805,7 +1817,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1819,7 +1831,7 @@
         <v>2.641252819939413</v>
       </c>
       <c r="D7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E7">
         <v>2.540130729835057</v>
@@ -1855,7 +1867,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1869,7 +1881,7 @@
         <v>2.512285655110759</v>
       </c>
       <c r="D8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E8">
         <v>2.590994611146576</v>
@@ -1905,7 +1917,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1919,7 +1931,7 @@
         <v>2.615441102246784</v>
       </c>
       <c r="D9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E9">
         <v>2.513421672263544</v>
@@ -1955,7 +1967,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1969,7 +1981,7 @@
         <v>2.515418243442972</v>
       </c>
       <c r="D10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E10">
         <v>2.545423958143926</v>
@@ -2005,7 +2017,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2019,7 +2031,7 @@
         <v>2.487273994427867</v>
       </c>
       <c r="D11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E11">
         <v>2.567211421027677</v>
@@ -2055,7 +2067,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2069,7 +2081,7 @@
         <v>2.487984580081365</v>
       </c>
       <c r="D12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E12">
         <v>2.579898802553291</v>
@@ -2105,7 +2117,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2119,7 +2131,7 @@
         <v>2.500805561667341</v>
       </c>
       <c r="D13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E13">
         <v>2.59216563562278</v>
@@ -2155,7 +2167,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2169,7 +2181,7 @@
         <v>2.499441989042522</v>
       </c>
       <c r="D14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E14">
         <v>2.736702547602069</v>
@@ -2219,7 +2231,7 @@
         <v>2.512520850741042</v>
       </c>
       <c r="D15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E15">
         <v>2.749061943431123</v>
@@ -2255,7 +2267,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2269,7 +2281,7 @@
         <v>2.77984350091858</v>
       </c>
       <c r="D16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E16">
         <v>2.889061943431122</v>
@@ -2305,7 +2317,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2319,7 +2331,7 @@
         <v>2.517224153471577</v>
       </c>
       <c r="D17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E17">
         <v>2.753506518310076</v>
@@ -2355,7 +2367,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2369,7 +2381,7 @@
         <v>2.784426680003737</v>
       </c>
       <c r="D18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E18">
         <v>2.924119959439183</v>
@@ -2405,7 +2417,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2419,7 +2431,7 @@
         <v>2.884280694854824</v>
       </c>
       <c r="D19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E19">
         <v>2.961861794886389</v>
@@ -2469,7 +2481,7 @@
         <v>2.920719956495094</v>
       </c>
       <c r="D20" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E20">
         <v>2.907075620138133</v>
@@ -2505,7 +2517,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2519,7 +2531,7 @@
         <v>2.648180125005333</v>
       </c>
       <c r="D21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E21">
         <v>2.848908919700521</v>
@@ -2555,7 +2567,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2605,7 +2617,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2619,7 +2631,7 @@
         <v>2.691620213913162</v>
       </c>
       <c r="D23" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E23">
         <v>2.889959376998489</v>
@@ -2655,7 +2667,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2669,7 +2681,7 @@
         <v>2.984719616116966</v>
       </c>
       <c r="D24" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E24">
         <v>2.755965243802971</v>
@@ -2705,7 +2717,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2719,7 +2731,7 @@
         <v>3.007275184023352</v>
       </c>
       <c r="D25" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E25">
         <v>2.755965243802971</v>
@@ -2755,7 +2767,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2769,7 +2781,7 @@
         <v>2.683495528297218</v>
       </c>
       <c r="D26" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E26">
         <v>2.882281628901694</v>
@@ -2805,7 +2817,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2819,7 +2831,7 @@
         <v>2.976914171586129</v>
       </c>
       <c r="D27" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E27">
         <v>2.747824596132772</v>
@@ -2855,7 +2867,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2869,7 +2881,7 @@
         <v>2.647048085674867</v>
       </c>
       <c r="D28" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E28">
         <v>2.84783915365346</v>
@@ -2905,7 +2917,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2919,7 +2931,7 @@
         <v>2.941898848516719</v>
       </c>
       <c r="D29" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E29">
         <v>2.711305547532774</v>
@@ -2955,7 +2967,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2969,7 +2981,7 @@
         <v>2.962790623816959</v>
       </c>
       <c r="D30" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E30">
         <v>2.711305547532774</v>
@@ -3005,7 +3017,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3019,7 +3031,7 @@
         <v>2.636850318680218</v>
       </c>
       <c r="D31" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E31">
         <v>2.674077933106496</v>
@@ -3055,7 +3067,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3069,7 +3081,7 @@
         <v>2.64386308474694</v>
       </c>
       <c r="D32" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E32">
         <v>2.844829359063415</v>
@@ -3105,7 +3117,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3119,7 +3131,7 @@
         <v>2.938838994972993</v>
       </c>
       <c r="D33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E33">
         <v>2.708114289235636</v>
@@ -3155,7 +3167,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3169,7 +3181,7 @@
         <v>2.959611880258242</v>
       </c>
       <c r="D34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E34">
         <v>2.708114289235636</v>
@@ -3205,7 +3217,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3219,7 +3231,7 @@
         <v>2.63362151616782</v>
       </c>
       <c r="D35" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E35">
         <v>2.706375129633912</v>
@@ -3255,7 +3267,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3269,7 +3281,7 @@
         <v>2.623711665472045</v>
       </c>
       <c r="D36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E36">
         <v>2.825786465799713</v>
@@ -3305,7 +3317,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3319,7 +3331,7 @@
         <v>2.919479379991807</v>
       </c>
       <c r="D37" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E37">
         <v>2.687923279746057</v>
@@ -3355,7 +3367,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3369,7 +3381,7 @@
         <v>2.939500051198033</v>
       </c>
       <c r="D38" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E38">
         <v>2.687923279746057</v>
@@ -3405,7 +3417,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3419,7 +3431,7 @@
         <v>2.613192965390128</v>
       </c>
       <c r="D39" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E39">
         <v>2.65740457966414</v>
@@ -3455,7 +3467,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3469,7 +3481,7 @@
         <v>2.866121269202039</v>
       </c>
       <c r="D40" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E40">
         <v>2.632273716345684</v>
@@ -3519,7 +3531,7 @@
         <v>2.884068721379623</v>
       </c>
       <c r="D41" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E41">
         <v>2.632273716345684</v>
@@ -3569,7 +3581,7 @@
         <v>2.556888701243869</v>
       </c>
       <c r="D42" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E42">
         <v>2.5709911987269</v>
@@ -3619,7 +3631,7 @@
         <v>2.84066903268222</v>
       </c>
       <c r="D43" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E43">
         <v>2.605728438993726</v>
@@ -3655,7 +3667,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3669,7 +3681,7 @@
         <v>2.857627543154535</v>
       </c>
       <c r="D44" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E44">
         <v>2.605728438993726</v>
@@ -3705,7 +3717,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3719,7 +3731,7 @@
         <v>2.530031126511299</v>
       </c>
       <c r="D45" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E45">
         <v>2.536232918189681</v>
@@ -3755,7 +3767,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3769,7 +3781,7 @@
         <v>2.794653597980052</v>
       </c>
       <c r="D46" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E46">
         <v>2.557736881328888</v>
@@ -3805,7 +3817,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3819,7 +3831,7 @@
         <v>2.809824187676618</v>
       </c>
       <c r="D47" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E47">
         <v>2.557736881328888</v>
@@ -3855,7 +3867,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3905,7 +3917,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3919,7 +3931,7 @@
         <v>2.877968395292299</v>
       </c>
       <c r="D49" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E49">
         <v>2.644629614722029</v>
@@ -3955,7 +3967,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3969,7 +3981,7 @@
         <v>2.896376165252531</v>
       </c>
       <c r="D50" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E50">
         <v>2.644629614722029</v>
@@ -4005,7 +4017,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4019,7 +4031,7 @@
         <v>2.521770137334771</v>
       </c>
       <c r="D51" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E51">
         <v>2.535896862069519</v>
@@ -4055,7 +4067,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4069,7 +4081,7 @@
         <v>2.934431839092635</v>
       </c>
       <c r="D52" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E52">
         <v>2.703517868992319</v>
@@ -4105,7 +4117,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4119,7 +4131,7 @@
         <v>2.955033485192349</v>
       </c>
       <c r="D53" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E53">
         <v>2.703517868992319</v>
@@ -4155,7 +4167,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4205,7 +4217,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4219,7 +4231,7 @@
         <v>2.974730272968942</v>
       </c>
       <c r="D55" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E55">
         <v>2.745546910458406</v>
@@ -4255,7 +4267,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4269,7 +4281,7 @@
         <v>2.996897706887981</v>
       </c>
       <c r="D56" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E56">
         <v>2.745546910458406</v>
@@ -4305,7 +4317,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4319,7 +4331,7 @@
         <v>2.624468326525319</v>
       </c>
       <c r="D57" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E57">
         <v>2.660688149733082</v>
@@ -4355,7 +4367,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4369,7 +4381,7 @@
         <v>3.056805462611843</v>
       </c>
       <c r="D58" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E58">
         <v>2.831146801497014</v>
@@ -4405,7 +4417,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4455,7 +4467,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4469,7 +4481,7 @@
         <v>3.075488420323122</v>
       </c>
       <c r="D60" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E60">
         <v>2.850632094815525</v>
@@ -4519,7 +4531,7 @@
         <v>2.73140795531227</v>
       </c>
       <c r="D61" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E61">
         <v>2.75953055997749</v>
@@ -4569,7 +4581,7 @@
         <v>2.72765316464271</v>
       </c>
       <c r="D62" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E62">
         <v>2.75953055997749</v>
@@ -4619,7 +4631,7 @@
         <v>2.72671446697532</v>
       </c>
       <c r="D63" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E63">
         <v>2.75953055997749</v>
@@ -4669,7 +4681,7 @@
         <v>6.293149296554828</v>
       </c>
       <c r="D64" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E64">
         <v>5.963700498102364</v>
@@ -4705,7 +4717,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4719,7 +4731,7 @@
         <v>6.420239880180696</v>
       </c>
       <c r="D65" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E65">
         <v>6.082402264327184</v>
@@ -4755,7 +4767,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4769,7 +4781,7 @@
         <v>6.609514294497387</v>
       </c>
       <c r="D66" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E66">
         <v>6.259183317962906</v>
@@ -4805,7 +4817,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4819,7 +4831,7 @@
         <v>6.515171551263329</v>
       </c>
       <c r="D67" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E67">
         <v>6.612047937164794</v>
@@ -4855,7 +4867,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4869,7 +4881,7 @@
         <v>6.520829737768901</v>
       </c>
       <c r="D68" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E68">
         <v>6.612047937164794</v>
@@ -4905,7 +4917,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4955,7 +4967,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5005,7 +5017,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5055,7 +5067,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5069,7 +5081,7 @@
         <v>6.781478804637512</v>
       </c>
       <c r="D72" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E72">
         <v>6.821616798629249</v>
@@ -5105,7 +5117,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5119,7 +5131,7 @@
         <v>6.927933775178332</v>
       </c>
       <c r="D73" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E73">
         <v>7.025464228815041</v>
@@ -5155,7 +5167,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5169,7 +5181,7 @@
         <v>7.465293617228137</v>
       </c>
       <c r="D74" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E74">
         <v>7.441132824526438</v>
@@ -5205,7 +5217,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5219,7 +5231,7 @@
         <v>2.399740228983164</v>
       </c>
       <c r="D75" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E75">
         <v>2.284756328614283</v>
@@ -5255,7 +5267,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5269,7 +5281,7 @@
         <v>2.181146111927123</v>
       </c>
       <c r="D76" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E76">
         <v>2.105842395854763</v>
@@ -5305,7 +5317,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5319,7 +5331,7 @@
         <v>2.180858495485883</v>
       </c>
       <c r="D77" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E77">
         <v>2.105842395854763</v>
@@ -5355,7 +5367,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5369,7 +5381,7 @@
         <v>2.355267416838251</v>
       </c>
       <c r="D78" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E78">
         <v>2.241615480893012</v>
@@ -5405,7 +5417,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5419,7 +5431,7 @@
         <v>2.138079262229388</v>
       </c>
       <c r="D79" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E79">
         <v>2.115876072829124</v>
@@ -5455,7 +5467,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5469,7 +5481,7 @@
         <v>2.136977667529256</v>
       </c>
       <c r="D80" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E80">
         <v>2.115876072829124</v>
@@ -5505,7 +5517,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5555,7 +5567,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5605,7 +5617,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5655,7 +5667,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5669,7 +5681,7 @@
         <v>1.925553832103902</v>
       </c>
       <c r="D84" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E84">
         <v>1.985821650998686</v>
@@ -5705,7 +5717,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5755,7 +5767,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5769,7 +5781,7 @@
         <v>1.87975631937778</v>
       </c>
       <c r="D86" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E86">
         <v>2.025900250164519</v>
@@ -5805,7 +5817,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5905,7 +5917,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5919,7 +5931,7 @@
         <v>1.789383875507923</v>
       </c>
       <c r="D89" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E89">
         <v>1.940268655809146</v>
@@ -5955,7 +5967,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5969,7 +5981,7 @@
         <v>1.804905667333501</v>
       </c>
       <c r="D90" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E90">
         <v>1.95497618970289</v>
@@ -6005,7 +6017,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6019,7 +6031,7 @@
         <v>1.809491967335235</v>
       </c>
       <c r="D91" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E91">
         <v>1.959321896917648</v>
@@ -6055,7 +6067,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6069,7 +6081,7 @@
         <v>1.822908408572121</v>
       </c>
       <c r="D92" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E92">
         <v>1.972034524843747</v>
@@ -6105,7 +6117,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6119,7 +6131,7 @@
         <v>2.011491451443282</v>
       </c>
       <c r="D93" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E93">
         <v>1.930405304642352</v>
@@ -6155,7 +6167,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6169,7 +6181,7 @@
         <v>1.820166348365971</v>
       </c>
       <c r="D94" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E94">
         <v>1.969436310418903</v>
@@ -6205,7 +6217,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6219,7 +6231,7 @@
         <v>2.008879751476441</v>
       </c>
       <c r="D95" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E95">
         <v>1.927766633591516</v>
@@ -6255,7 +6267,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6269,7 +6281,7 @@
         <v>1.780154910291897</v>
       </c>
       <c r="D96" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E96">
         <v>1.931523833030682</v>
@@ -6305,7 +6317,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6355,7 +6367,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6369,7 +6381,7 @@
         <v>1.781411528733962</v>
       </c>
       <c r="D98" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E98">
         <v>1.932714530505294</v>
@@ -6405,7 +6417,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6455,7 +6467,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6469,7 +6481,7 @@
         <v>1.786869994736246</v>
       </c>
       <c r="D100" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E100">
         <v>1.937886650750082</v>
@@ -6519,7 +6531,7 @@
         <v>1.77389224303264</v>
       </c>
       <c r="D101" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E101">
         <v>1.925589699135846</v>
@@ -6555,7 +6567,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6569,7 +6581,7 @@
         <v>1.764225388294109</v>
       </c>
       <c r="D102" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E102">
         <v>1.916429958088516</v>
@@ -6769,7 +6781,7 @@
         <v>2.039049007419374</v>
       </c>
       <c r="D106" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E106">
         <v>1.958247448115615</v>
@@ -6805,7 +6817,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6819,7 +6831,7 @@
         <v>1.963804213639886</v>
       </c>
       <c r="D107" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E107">
         <v>2.044635472991321</v>
@@ -6855,7 +6867,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6869,7 +6881,7 @@
         <v>2.084469221121035</v>
       </c>
       <c r="D108" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E108">
         <v>2.00413671738046</v>
@@ -6905,7 +6917,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6919,7 +6931,7 @@
         <v>1.970692549466935</v>
       </c>
       <c r="D109" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E109">
         <v>2.103970465510173</v>
@@ -6955,7 +6967,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7005,7 +7017,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7019,7 +7031,7 @@
         <v>1.989826166099606</v>
       </c>
       <c r="D111" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E111">
         <v>2.069999197311251</v>
@@ -7055,7 +7067,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7069,7 +7081,7 @@
         <v>1.996538974422711</v>
       </c>
       <c r="D112" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E112">
         <v>2.129860772341935</v>
@@ -7105,7 +7117,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7155,7 +7167,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7169,7 +7181,7 @@
         <v>1.976959483296697</v>
       </c>
       <c r="D114" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E114">
         <v>2.110248039295503</v>
@@ -7269,7 +7281,7 @@
         <v>1.920546112528168</v>
       </c>
       <c r="D116" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E116">
         <v>2.053738890308352</v>
@@ -7305,7 +7317,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7355,7 +7367,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7369,7 +7381,7 @@
         <v>2.078859445890371</v>
       </c>
       <c r="D118" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E118">
         <v>2.128859445890371</v>
@@ -7405,7 +7417,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7419,7 +7431,7 @@
         <v>1.864471846503076</v>
       </c>
       <c r="D119" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E119">
         <v>1.997569421794252</v>
@@ -7455,7 +7467,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7505,7 +7517,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7555,7 +7567,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7569,7 +7581,7 @@
         <v>1.863420505387863</v>
       </c>
       <c r="D122" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E122">
         <v>1.996516295719591</v>
@@ -7669,7 +7681,7 @@
         <v>2.029857360363785</v>
       </c>
       <c r="D124" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E124">
         <v>2.011995247378231</v>
@@ -7719,7 +7731,7 @@
         <v>1.892165706973767</v>
       </c>
       <c r="D125" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E125">
         <v>2.025310300703773</v>
@@ -7755,7 +7767,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7805,7 +7817,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7855,7 +7867,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7919,7 +7931,7 @@
         <v>2.183293967129219</v>
       </c>
       <c r="D129" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E129">
         <v>2.097698061214447</v>
@@ -7969,7 +7981,7 @@
         <v>2.10409703769314</v>
       </c>
       <c r="D130" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E130">
         <v>2.097698061214447</v>
@@ -8055,7 +8067,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8105,7 +8117,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8155,7 +8167,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8205,7 +8217,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8255,7 +8267,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8305,7 +8317,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8355,7 +8367,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8405,7 +8417,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8419,7 +8431,7 @@
         <v>2.367284598691813</v>
       </c>
       <c r="D139" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E139">
         <v>2.284677125480481</v>
@@ -8469,7 +8481,7 @@
         <v>2.308705785003503</v>
       </c>
       <c r="D140" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E140">
         <v>2.284677125480481</v>
@@ -8605,7 +8617,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8655,7 +8667,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8705,7 +8717,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8755,7 +8767,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8805,7 +8817,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8869,7 +8881,7 @@
         <v>2.673055621612132</v>
       </c>
       <c r="D148" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E148">
         <v>2.649383477311975</v>
@@ -8919,7 +8931,7 @@
         <v>2.694510447967022</v>
       </c>
       <c r="D149" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E149">
         <v>2.66746656530884</v>
@@ -8969,7 +8981,7 @@
         <v>2.61961842602696</v>
       </c>
       <c r="D150" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E150">
         <v>2.674946565009619</v>
@@ -9255,7 +9267,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9269,7 +9281,7 @@
         <v>2.746485076848839</v>
       </c>
       <c r="D156" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E156">
         <v>2.847982602490786</v>
@@ -9305,7 +9317,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9369,7 +9381,7 @@
         <v>2.750734210259811</v>
       </c>
       <c r="D158" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E158">
         <v>2.800734210259812</v>
@@ -9405,7 +9417,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9469,7 +9481,7 @@
         <v>2.717092536535202</v>
       </c>
       <c r="D160" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E160">
         <v>2.791717770085309</v>
@@ -9555,7 +9567,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9569,7 +9581,7 @@
         <v>2.669840281895235</v>
       </c>
       <c r="D162" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E162">
         <v>2.754805459723328</v>
@@ -9605,7 +9617,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9669,7 +9681,7 @@
         <v>2.704152220032186</v>
       </c>
       <c r="D164" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E164">
         <v>2.721608307945189</v>
@@ -9719,7 +9731,7 @@
         <v>0.7516342779874527</v>
       </c>
       <c r="D165" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E165">
         <v>0.6447312303040151</v>
@@ -9755,7 +9767,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9769,7 +9781,7 @@
         <v>0.6347312303040145</v>
       </c>
       <c r="D166" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E166">
         <v>0.7803954970608276</v>
@@ -9805,7 +9817,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9819,7 +9831,7 @@
         <v>0.7872985447442655</v>
       </c>
       <c r="D167" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E167">
         <v>0.6685373256708909</v>
@@ -9855,7 +9867,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9869,7 +9881,7 @@
         <v>0.6141118398407031</v>
       </c>
       <c r="D168" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E168">
         <v>0.7042015924277036</v>
@@ -9905,7 +9917,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9919,7 +9931,7 @@
         <v>0.7076194190074974</v>
       </c>
       <c r="D169" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E169">
         <v>0.8524403513495589</v>
@@ -9969,7 +9981,7 @@
         <v>0.8587410173081755</v>
       </c>
       <c r="D170" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E170">
         <v>0.7402207509247285</v>
@@ -10019,7 +10031,7 @@
         <v>0.6868795521992208</v>
       </c>
       <c r="D171" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E171">
         <v>0.7750416832667906</v>
@@ -10069,7 +10081,7 @@
         <v>0.794311018129779</v>
       </c>
       <c r="D172" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E172">
         <v>0.9381289071762104</v>
@@ -10105,7 +10117,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10119,7 +10131,7 @@
         <v>0.7478436529603893</v>
       </c>
       <c r="D173" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E173">
         <v>0.9381289071762104</v>
@@ -10155,7 +10167,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10169,7 +10181,7 @@
         <v>0.9437131136379486</v>
       </c>
       <c r="D174" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E174">
         <v>0.8254794310532532</v>
@@ -10205,7 +10217,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10219,7 +10231,7 @@
         <v>0.7734278594221262</v>
       </c>
       <c r="D175" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E175">
         <v>0.8592973200996861</v>
@@ -10255,7 +10267,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10269,7 +10281,7 @@
         <v>0.9016190641047892</v>
       </c>
       <c r="D176" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E176">
         <v>1.04419537245399</v>
@@ -10305,7 +10317,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10319,7 +10331,7 @@
         <v>0.8558611736195321</v>
       </c>
       <c r="D177" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E177">
         <v>1.04419537245399</v>
@@ -10355,7 +10367,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10369,7 +10381,7 @@
         <v>1.048892735560562</v>
       </c>
       <c r="D178" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E178">
         <v>0.9310137903179339</v>
@@ -10405,7 +10417,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10419,7 +10431,7 @@
         <v>0.8805585367261042</v>
       </c>
       <c r="D179" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E179">
         <v>0.963590098667134</v>
@@ -10455,7 +10467,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10469,7 +10481,7 @@
         <v>1.076170489586433</v>
       </c>
       <c r="D180" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E180">
         <v>1.260525374010979</v>
@@ -10519,7 +10531,7 @@
         <v>1.26341395784032</v>
       </c>
       <c r="D181" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E181">
         <v>1.146258524308584</v>
@@ -10569,7 +10581,7 @@
         <v>1.099059073415773</v>
       </c>
       <c r="D182" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E182">
         <v>1.176302541669659</v>
@@ -10619,7 +10631,7 @@
         <v>1.931268098407571</v>
       </c>
       <c r="D183" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E183">
         <v>1.946759727730396</v>
@@ -10655,7 +10667,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10705,7 +10717,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10755,7 +10767,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10769,7 +10781,7 @@
         <v>0.5942088493584849</v>
       </c>
       <c r="D186" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E186">
         <v>0.5982130518354056</v>
@@ -10805,7 +10817,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10855,7 +10867,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10905,7 +10917,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10955,7 +10967,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10969,7 +10981,7 @@
         <v>-0.02499489055226256</v>
       </c>
       <c r="D190" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E190">
         <v>-0.07499489055226238</v>
@@ -11005,7 +11017,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11019,7 +11031,7 @@
         <v>-0.04541693580813089</v>
       </c>
       <c r="D191" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E191">
         <v>-0.1350880582477796</v>
@@ -11055,7 +11067,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11105,7 +11117,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11155,7 +11167,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11305,7 +11317,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11319,7 +11331,7 @@
         <v>-0.5154661476950757</v>
       </c>
       <c r="D197" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E197">
         <v>-0.4838284745942198</v>
@@ -11355,7 +11367,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11369,7 +11381,7 @@
         <v>-0.5144835438345625</v>
       </c>
       <c r="D198" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E198">
         <v>-0.4838284745942198</v>
@@ -11405,7 +11417,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11455,7 +11467,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11469,7 +11481,7 @@
         <v>-0.6795603356321358</v>
       </c>
       <c r="D200" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E200">
         <v>-0.6353746161347429</v>
@@ -11505,7 +11517,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11519,7 +11531,7 @@
         <v>-0.6770489039336995</v>
       </c>
       <c r="D201" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E201">
         <v>-0.6353746161347429</v>
@@ -11555,7 +11567,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11605,7 +11617,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11619,7 +11631,7 @@
         <v>-1.275160705635463</v>
       </c>
       <c r="D203" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E203">
         <v>-0.9575450227817477</v>
@@ -11655,7 +11667,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11669,7 +11681,7 @@
         <v>-1.267100202166811</v>
       </c>
       <c r="D204" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E204">
         <v>-0.9575450227817477</v>
@@ -11705,7 +11717,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11769,7 +11781,7 @@
         <v>-1.30354206111917</v>
       </c>
       <c r="D206" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E206">
         <v>-0.9846924062879019</v>
@@ -11819,7 +11831,7 @@
         <v>-1.295217135083899</v>
       </c>
       <c r="D207" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E207">
         <v>-0.9846924062879019</v>
@@ -11869,7 +11881,7 @@
         <v>-1.315601110783377</v>
       </c>
       <c r="D208" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E208">
         <v>-0.9962271494449686</v>
@@ -11919,7 +11931,7 @@
         <v>-1.307163833353718</v>
       </c>
       <c r="D209" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E209">
         <v>-0.9962271494449686</v>
@@ -11969,7 +11981,7 @@
         <v>-1.303470101275702</v>
       </c>
       <c r="D210" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E210">
         <v>-0.9846235751332797</v>
@@ -12005,7 +12017,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12019,7 +12031,7 @@
         <v>-1.295145845673754</v>
       </c>
       <c r="D211" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E211">
         <v>-0.9846235751332797</v>
@@ -12055,7 +12067,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12069,7 +12081,7 @@
         <v>-1.352240812118975</v>
       </c>
       <c r="D212" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E212">
         <v>-1.031273820287715</v>
@@ -12105,7 +12117,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12119,7 +12131,7 @@
         <v>-1.343462171012276</v>
       </c>
       <c r="D213" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E213">
         <v>-1.031273820287715</v>
@@ -12155,7 +12167,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12205,7 +12217,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12219,7 +12231,7 @@
         <v>-1.277973836666044</v>
       </c>
       <c r="D215" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E215">
         <v>-0.9602358437675207</v>
@@ -12269,7 +12281,7 @@
         <v>-1.269887123902075</v>
       </c>
       <c r="D216" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E216">
         <v>-0.9602358437675207</v>
@@ -12319,7 +12331,7 @@
         <v>-1.030235843767521</v>
       </c>
       <c r="D217" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E217">
         <v>-1.080019061857596</v>
@@ -12369,7 +12381,7 @@
         <v>-1.007888992711643</v>
       </c>
       <c r="D218" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E218">
         <v>-1.080019061857596</v>
@@ -12419,7 +12431,7 @@
         <v>-1.154349245698821</v>
       </c>
       <c r="D219" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E219">
         <v>-0.8419862350162637</v>
@@ -12469,7 +12481,7 @@
         <v>-1.147414314838273</v>
       </c>
       <c r="D220" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E220">
         <v>-0.8419862350162637</v>
@@ -12619,7 +12631,7 @@
         <v>-0.9332125637434627</v>
       </c>
       <c r="D223" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E223">
         <v>-0.6304641914067899</v>
@@ -12655,7 +12667,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12669,7 +12681,7 @@
         <v>-0.9283379125284608</v>
       </c>
       <c r="D224" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E224">
         <v>-0.6304641914067899</v>
@@ -12705,7 +12717,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12719,7 +12731,7 @@
         <v>-1.078298911794628</v>
       </c>
       <c r="D225" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E225">
         <v>-0.7337942740491279</v>
@@ -12769,7 +12781,7 @@
         <v>-1.284045732215318</v>
       </c>
       <c r="D226" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E226">
         <v>-0.9315166474955321</v>
@@ -12819,7 +12831,7 @@
         <v>-1.074552792811861</v>
       </c>
       <c r="D227" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E227">
         <v>-0.7301942595508679</v>
@@ -12855,7 +12867,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12869,7 +12881,7 @@
         <v>0.6306184682796347</v>
       </c>
       <c r="D228" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E228">
         <v>0.8825890610024754</v>
@@ -12905,7 +12917,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12919,7 +12931,7 @@
         <v>2.500083924851446</v>
       </c>
       <c r="D229" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E229">
         <v>2.721828222716436</v>
@@ -12955,7 +12967,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12969,7 +12981,7 @@
         <v>2.484743417251086</v>
       </c>
       <c r="D230" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E230">
         <v>2.721828222716436</v>
@@ -13005,7 +13017,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13019,7 +13031,7 @@
         <v>2.959498476516616</v>
       </c>
       <c r="D231" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E231">
         <v>3.019498476516616</v>
@@ -13055,7 +13067,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13105,7 +13117,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13119,7 +13131,7 @@
         <v>3.973072767193392</v>
       </c>
       <c r="D233" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E233">
         <v>3.630196829293595</v>
@@ -13155,7 +13167,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13205,7 +13217,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13255,7 +13267,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13269,7 +13281,7 @@
         <v>4.556254256131551</v>
       </c>
       <c r="D236" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E236">
         <v>4.211276763316661</v>
@@ -13305,7 +13317,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13355,7 +13367,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13405,7 +13417,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13419,7 +13431,7 @@
         <v>4.667791750685101</v>
       </c>
       <c r="D239" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E239">
         <v>4.322412320952902</v>
@@ -13455,7 +13467,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13469,7 +13481,7 @@
         <v>4.273963746622406</v>
       </c>
       <c r="D240" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E240">
         <v>4.266274031756307</v>
@@ -13505,7 +13517,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13555,7 +13567,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13605,7 +13617,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13619,7 +13631,7 @@
         <v>3.655351043939968</v>
       </c>
       <c r="D243" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E243">
         <v>3.313620049187031</v>
@@ -13655,7 +13667,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13669,7 +13681,7 @@
         <v>2.349652973133038</v>
       </c>
       <c r="D244" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E244">
         <v>2.585321458264525</v>
@@ -13719,7 +13731,7 @@
         <v>2.337296219946928</v>
       </c>
       <c r="D245" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E245">
         <v>2.585321458264525</v>
@@ -13769,7 +13781,7 @@
         <v>2.821499834857581</v>
       </c>
       <c r="D246" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E246">
         <v>2.482773709326562</v>
@@ -13819,7 +13831,7 @@
         <v>1.399171925433256</v>
       </c>
       <c r="D247" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E247">
         <v>1.7228188215915</v>
@@ -13855,7 +13867,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13869,7 +13881,7 @@
         <v>1.94957093986026</v>
       </c>
       <c r="D248" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E248">
         <v>1.61398690043734</v>
@@ -13905,7 +13917,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13919,7 +13931,7 @@
         <v>1.388298565840941</v>
       </c>
       <c r="D249" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E249">
         <v>1.05473712956764</v>
@@ -13969,7 +13981,7 @@
         <v>1.206849236469149</v>
       </c>
       <c r="D250" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E250">
         <v>0.8739416716530437</v>
@@ -14019,7 +14031,7 @@
         <v>1.250249534396463</v>
       </c>
       <c r="D251" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E251">
         <v>0.9171855721103492</v>
@@ -14069,7 +14081,7 @@
         <v>1.265784593473219</v>
       </c>
       <c r="D252" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E252">
         <v>0.9326646489922341</v>
@@ -14105,7 +14117,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14119,7 +14131,7 @@
         <v>1.181086185990114</v>
       </c>
       <c r="D253" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E253">
         <v>0.8482714609955542</v>
@@ -14169,7 +14181,7 @@
         <v>3.393868635799184</v>
       </c>
       <c r="D254" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E254">
         <v>3.232668972857903</v>
@@ -14205,7 +14217,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14219,7 +14231,7 @@
         <v>3.344337857016143</v>
       </c>
       <c r="D255" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E255">
         <v>3.232668972857903</v>
@@ -14255,7 +14267,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14269,7 +14281,7 @@
         <v>3.108144846549583</v>
       </c>
       <c r="D256" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E256">
         <v>3.176241351782863</v>
@@ -14305,7 +14317,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14319,7 +14331,7 @@
         <v>3.110765478091183</v>
       </c>
       <c r="D257" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E257">
         <v>3.176241351782863</v>
@@ -14355,7 +14367,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14369,7 +14381,7 @@
         <v>3.484929217459694</v>
       </c>
       <c r="D258" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E258">
         <v>3.328403460479749</v>
@@ -14405,7 +14417,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14419,7 +14431,7 @@
         <v>3.438944160440425</v>
       </c>
       <c r="D259" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E259">
         <v>3.328403460479749</v>
@@ -14455,7 +14467,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14505,7 +14517,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14555,7 +14567,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14569,7 +14581,7 @@
         <v>3.67612531160249</v>
       </c>
       <c r="D262" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E262">
         <v>3.529413159454653</v>
@@ -14605,7 +14617,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14619,7 +14631,7 @@
         <v>3.637585058248958</v>
       </c>
       <c r="D263" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E263">
         <v>3.529413159454653</v>
@@ -14655,7 +14667,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14669,7 +14681,7 @@
         <v>3.405388602484038</v>
       </c>
       <c r="D264" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E264">
         <v>3.509413159454653</v>
@@ -14705,7 +14717,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14719,7 +14731,7 @@
         <v>3.405511387337113</v>
       </c>
       <c r="D265" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E265">
         <v>3.509413159454653</v>
@@ -14755,7 +14767,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14769,7 +14781,7 @@
         <v>3.451364045513422</v>
       </c>
       <c r="D266" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E266">
         <v>3.509413159454653</v>
@@ -14805,7 +14817,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14819,7 +14831,7 @@
         <v>4.004636932335591</v>
       </c>
       <c r="D267" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E267">
         <v>3.867442887120403</v>
@@ -14869,7 +14881,7 @@
         <v>3.774439165379895</v>
       </c>
       <c r="D268" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E268">
         <v>3.837640654076098</v>
@@ -14919,7 +14931,7 @@
         <v>4.220199786446392</v>
       </c>
       <c r="D269" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E269">
         <v>4.085943565478028</v>
@@ -14955,7 +14967,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14969,7 +14981,7 @@
         <v>3.991103703583256</v>
       </c>
       <c r="D270" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E270">
         <v>4.0441357312043</v>
@@ -15005,7 +15017,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15019,7 +15031,7 @@
         <v>4.24807262091024</v>
       </c>
       <c r="D271" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E271">
         <v>4.172298835483293</v>
@@ -15055,7 +15067,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15069,7 +15081,7 @@
         <v>4.076733299050661</v>
       </c>
       <c r="D272" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E272">
         <v>4.185185728196767</v>
@@ -15105,7 +15117,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15169,7 +15181,7 @@
         <v>3.853669569225198</v>
       </c>
       <c r="D274" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E274">
         <v>3.960609701897911</v>
@@ -15305,7 +15317,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15319,7 +15331,7 @@
         <v>3.457860783201086</v>
       </c>
       <c r="D277" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E277">
         <v>3.562117466477025</v>
@@ -15355,7 +15367,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15369,7 +15381,7 @@
         <v>3.461796612382101</v>
       </c>
       <c r="D278" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E278">
         <v>3.45818163729601</v>
@@ -15405,7 +15417,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15469,7 +15481,7 @@
         <v>1.876063224574707</v>
       </c>
       <c r="D280" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E280">
         <v>1.926860456775207</v>
@@ -15519,7 +15531,7 @@
         <v>1.879462993924748</v>
       </c>
       <c r="D281" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E281">
         <v>1.926860456775207</v>
@@ -15569,7 +15581,7 @@
         <v>1.36286186891499</v>
       </c>
       <c r="D282" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E282">
         <v>1.420876924621103</v>
@@ -15605,7 +15617,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15619,7 +15631,7 @@
         <v>1.365396205962064</v>
       </c>
       <c r="D283" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E283">
         <v>1.420876924621103</v>
@@ -15655,7 +15667,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15669,7 +15681,7 @@
         <v>1.492587172538397</v>
       </c>
       <c r="D284" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E284">
         <v>1.422587172538397</v>
@@ -15705,7 +15717,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15719,7 +15731,7 @@
         <v>1.155028253713973</v>
       </c>
       <c r="D285" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E285">
         <v>1.207786135342488</v>
@@ -15769,7 +15781,7 @@
         <v>1.157212112489207</v>
       </c>
       <c r="D286" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E286">
         <v>1.207786135342488</v>
@@ -15819,7 +15831,7 @@
         <v>1.287557383512098</v>
       </c>
       <c r="D287" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E287">
         <v>1.260086513310223</v>
@@ -15869,7 +15881,7 @@
         <v>-0.2566084186298667</v>
       </c>
       <c r="D288" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E288">
         <v>-0.001048450451905936</v>
@@ -15905,7 +15917,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15919,7 +15931,7 @@
         <v>-0.2875710874180024</v>
       </c>
       <c r="D289" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E289">
         <v>-0.001048450451905936</v>
@@ -15955,7 +15967,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16005,7 +16017,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16055,7 +16067,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16069,7 +16081,7 @@
         <v>-0.3429456734762377</v>
       </c>
       <c r="D292" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E292">
         <v>-0.1559309932859021</v>
@@ -16105,7 +16117,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16119,7 +16131,7 @@
         <v>-0.452945673476238</v>
       </c>
       <c r="D293" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E293">
         <v>-0.1559309932859021</v>
@@ -16155,7 +16167,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16169,7 +16181,7 @@
         <v>-0.07614423041516449</v>
       </c>
       <c r="D294" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E294">
         <v>-0.08649962563060054</v>
@@ -16205,7 +16217,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16219,7 +16231,7 @@
         <v>-0.06685502084603723</v>
       </c>
       <c r="D295" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E295">
         <v>-0.08649962563060054</v>
@@ -16255,7 +16267,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16269,7 +16281,7 @@
         <v>-0.6325763258089658</v>
       </c>
       <c r="D296" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E296">
         <v>-0.7397037652284588</v>
@@ -16305,7 +16317,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16319,7 +16331,7 @@
         <v>-0.6888811406779016</v>
       </c>
       <c r="D297" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E297">
         <v>-0.6347573064746772</v>
@@ -16355,7 +16367,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16369,7 +16381,7 @@
         <v>-0.5922830059527424</v>
       </c>
       <c r="D298" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E298">
         <v>-0.6988811406779014</v>
@@ -16405,7 +16417,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16419,7 +16431,7 @@
         <v>-0.7708727781363214</v>
       </c>
       <c r="D299" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E299">
         <v>-0.7160845060282481</v>
@@ -16455,7 +16467,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16469,7 +16481,7 @@
         <v>-0.6732115427634033</v>
       </c>
       <c r="D300" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E300">
         <v>-0.7808727781363212</v>
@@ -16505,7 +16517,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16519,7 +16531,7 @@
         <v>-0.6051723879795468</v>
       </c>
       <c r="D301" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E301">
         <v>-0.5517269067155315</v>
@@ -16555,7 +16567,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16569,7 +16581,7 @@
         <v>-0.509659617957122</v>
       </c>
       <c r="D302" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E302">
         <v>-0.6151723879795465</v>
@@ -16605,7 +16617,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16619,7 +16631,7 @@
         <v>1.374867998585327</v>
       </c>
       <c r="D303" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E303">
         <v>1.61428021608427</v>
@@ -16655,7 +16667,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16669,7 +16681,7 @@
         <v>1.37455579980999</v>
       </c>
       <c r="D304" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E304">
         <v>1.61428021608427</v>
@@ -16705,7 +16717,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16719,7 +16731,7 @@
         <v>1.659046067002767</v>
       </c>
       <c r="D305" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E305">
         <v>1.701663141543517</v>
@@ -16755,7 +16767,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16769,7 +16781,7 @@
         <v>1.400425101402588</v>
       </c>
       <c r="D306" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E306">
         <v>1.63789275673065</v>
@@ -16805,7 +16817,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16819,7 +16831,7 @@
         <v>1.415426421593279</v>
       </c>
       <c r="D307" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E307">
         <v>1.63789275673065</v>
@@ -16855,7 +16867,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16869,7 +16881,7 @@
         <v>1.672891436539961</v>
       </c>
       <c r="D308" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E308">
         <v>1.702888796158578</v>
@@ -16905,7 +16917,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16919,7 +16931,7 @@
         <v>1.682896717302726</v>
       </c>
       <c r="D309" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E309">
         <v>1.702888796158578</v>
@@ -16955,7 +16967,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -16969,7 +16981,7 @@
         <v>1.392287936404873</v>
       </c>
       <c r="D310" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E310">
         <v>1.630374723852328</v>
@@ -17005,7 +17017,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17019,7 +17031,7 @@
         <v>1.392192134372636</v>
       </c>
       <c r="D311" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E311">
         <v>1.630374723852328</v>
@@ -17055,7 +17067,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17069,7 +17081,7 @@
         <v>1.665398674360388</v>
       </c>
       <c r="D312" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E312">
         <v>1.367982501138595</v>
@@ -17105,7 +17117,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17119,7 +17131,7 @@
         <v>1.67530287232815</v>
       </c>
       <c r="D313" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E313">
         <v>1.367982501138595</v>
@@ -17155,7 +17167,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17169,7 +17181,7 @@
         <v>1.683187064752997</v>
       </c>
       <c r="D314" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E314">
         <v>1.385560910531628</v>
@@ -17205,7 +17217,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17219,7 +17231,7 @@
         <v>1.693331241005988</v>
       </c>
       <c r="D315" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E315">
         <v>1.385560910531628</v>
@@ -17255,7 +17267,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17269,7 +17281,7 @@
         <v>1.671335210176903</v>
       </c>
       <c r="D316" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E316">
         <v>1.373848959803819</v>
@@ -17305,7 +17317,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17319,7 +17331,7 @@
         <v>1.68131949631757</v>
       </c>
       <c r="D317" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E317">
         <v>1.373848959803819</v>
@@ -17355,7 +17367,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17369,7 +17381,7 @@
         <v>1.693875753393727</v>
       </c>
       <c r="D318" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E318">
         <v>1.396123425781996</v>
@@ -17405,7 +17417,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17419,7 +17431,7 @@
         <v>1.704164127807133</v>
       </c>
       <c r="D319" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E319">
         <v>1.396123425781996</v>
@@ -17455,7 +17467,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17469,7 +17481,7 @@
         <v>1.366123425781996</v>
       </c>
       <c r="D320" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E320">
         <v>1.403731566187024</v>
@@ -17505,7 +17517,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17519,7 +17531,7 @@
         <v>1.710631890779994</v>
       </c>
       <c r="D321" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E321">
         <v>1.412681767280061</v>
@@ -17555,7 +17567,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17569,7 +17581,7 @@
         <v>1.72114631763706</v>
       </c>
       <c r="D322" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E322">
         <v>1.412681767280061</v>
@@ -17605,7 +17617,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17619,7 +17631,7 @@
         <v>1.382681767280062</v>
       </c>
       <c r="D323" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E323">
         <v>1.420374677351461</v>
@@ -17655,7 +17667,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17669,7 +17681,7 @@
         <v>1.679206240881443</v>
       </c>
       <c r="D324" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E324">
         <v>1.381627077835624</v>
@@ -17719,7 +17731,7 @@
         <v>1.689296712933807</v>
       </c>
       <c r="D325" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E325">
         <v>1.381627077835624</v>
@@ -17769,7 +17781,7 @@
         <v>1.351627077835625</v>
       </c>
       <c r="D326" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E326">
         <v>1.364138386842169</v>
@@ -17819,7 +17831,7 @@
         <v>1.662615013806636</v>
       </c>
       <c r="D327" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E327">
         <v>1.365231699984297</v>
@@ -17855,7 +17867,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17869,7 +17881,7 @@
         <v>1.672481658175022</v>
       </c>
       <c r="D328" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E328">
         <v>1.365231699984297</v>
@@ -17905,7 +17917,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17919,7 +17931,7 @@
         <v>1.335231699984297</v>
       </c>
       <c r="D329" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E329">
         <v>1.330198361076394</v>
@@ -17955,7 +17967,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17969,7 +17981,7 @@
         <v>1.638483426036899</v>
       </c>
       <c r="D330" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E330">
         <v>1.341384970754843</v>
@@ -18019,7 +18031,7 @@
         <v>1.648024517787818</v>
       </c>
       <c r="D331" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E331">
         <v>1.341384970754843</v>
@@ -18119,7 +18131,7 @@
         <v>1.611118158429232</v>
       </c>
       <c r="D333" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E333">
         <v>1.31434273328757</v>
@@ -18169,7 +18181,7 @@
         <v>1.620290072876844</v>
       </c>
       <c r="D334" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E334">
         <v>1.31434273328757</v>
@@ -18219,7 +18231,7 @@
         <v>1.210704115653037</v>
       </c>
       <c r="D335" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E335">
         <v>1.321946243981619</v>
@@ -18269,7 +18281,7 @@
         <v>1.250704115653037</v>
       </c>
       <c r="D336" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E336">
         <v>1.321946243981619</v>
@@ -18319,7 +18331,7 @@
         <v>1.580824889600507</v>
       </c>
       <c r="D337" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E337">
         <v>1.284407057851428</v>
@@ -18355,7 +18367,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18369,7 +18381,7 @@
         <v>1.589588125885168</v>
       </c>
       <c r="D338" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E338">
         <v>1.284407057851428</v>
@@ -18405,7 +18417,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18419,7 +18431,7 @@
         <v>1.180206507742837</v>
       </c>
       <c r="D339" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E339">
         <v>1.27675246238701</v>
@@ -18455,7 +18467,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18469,7 +18481,7 @@
         <v>1.220206507742837</v>
       </c>
       <c r="D340" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E340">
         <v>1.27675246238701</v>
@@ -18505,7 +18517,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18519,7 +18531,7 @@
         <v>1.680056540073359</v>
       </c>
       <c r="D341" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E341">
         <v>1.409353064352823</v>
@@ -18555,7 +18567,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18569,7 +18581,7 @@
         <v>1.717732409003494</v>
       </c>
       <c r="D342" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E342">
         <v>1.409353064352823</v>
@@ -18605,7 +18617,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18619,7 +18631,7 @@
         <v>1.307497917096648</v>
       </c>
       <c r="D343" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E343">
         <v>1.444235818399402</v>
@@ -18655,7 +18667,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18669,7 +18681,7 @@
         <v>1.347497917096648</v>
       </c>
       <c r="D344" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E344">
         <v>1.444235818399402</v>
@@ -18705,7 +18717,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18719,7 +18731,7 @@
         <v>1.842256392262994</v>
       </c>
       <c r="D345" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E345">
         <v>1.530769127897027</v>
@@ -18769,7 +18781,7 @@
         <v>1.431193121765403</v>
       </c>
       <c r="D346" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E346">
         <v>1.572471675023835</v>
@@ -18819,7 +18831,7 @@
         <v>1.471193121765403</v>
       </c>
       <c r="D347" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E347">
         <v>1.572471675023835</v>
@@ -18869,7 +18881,7 @@
         <v>2.306011000659936</v>
       </c>
       <c r="D348" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E348">
         <v>2.348379970519409</v>
@@ -18905,7 +18917,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18919,7 +18931,7 @@
         <v>2.400485390479259</v>
       </c>
       <c r="D349" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E349">
         <v>2.364696230398958</v>
@@ -18955,7 +18967,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19005,7 +19017,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19019,7 +19031,7 @@
         <v>2.315116384839492</v>
       </c>
       <c r="D351" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E351">
         <v>2.323814331699535</v>
@@ -19055,7 +19067,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19069,7 +19081,7 @@
         <v>2.158186337006185</v>
       </c>
       <c r="D352" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E352">
         <v>2.199105803820263</v>
@@ -19105,7 +19117,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19155,7 +19167,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19205,7 +19217,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19219,7 +19231,7 @@
         <v>2.249949180664442</v>
       </c>
       <c r="D355" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E355">
         <v>2.193589002935801</v>
@@ -19255,7 +19267,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19269,7 +19281,7 @@
         <v>3.29910210514231</v>
       </c>
       <c r="D356" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E356">
         <v>3.35230135785332</v>
@@ -19305,7 +19317,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19319,7 +19331,7 @@
         <v>3.804045197377832</v>
       </c>
       <c r="D357" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E357">
         <v>3.415154291605215</v>
@@ -19355,7 +19367,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19369,7 +19381,7 @@
         <v>3.427249571448392</v>
       </c>
       <c r="D358" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E358">
         <v>3.291626526785035</v>
@@ -19405,7 +19417,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19455,7 +19467,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19469,7 +19481,7 @@
         <v>3.442581197445604</v>
       </c>
       <c r="D360" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E360">
         <v>3.306414237004073</v>
@@ -19505,7 +19517,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19519,7 +19531,7 @@
         <v>3.36022431872702</v>
       </c>
       <c r="D361" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E361">
         <v>3.226979110080385</v>
@@ -19555,7 +19567,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19569,7 +19581,7 @@
         <v>3.251003700388559</v>
       </c>
       <c r="D362" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E362">
         <v>3.121633280862579</v>
@@ -19605,7 +19617,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19619,7 +19631,7 @@
         <v>2.99001278638902</v>
       </c>
       <c r="D363" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E363">
         <v>3.032275977245447</v>
@@ -19705,7 +19717,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19719,7 +19731,7 @@
         <v>2.786342722576059</v>
       </c>
       <c r="D365" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E365">
         <v>2.830017022419643</v>
@@ -19755,7 +19767,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19769,7 +19781,7 @@
         <v>2.881784622628198</v>
       </c>
       <c r="D366" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E366">
         <v>2.846342722576059</v>
@@ -19805,7 +19817,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19819,7 +19831,7 @@
         <v>2.713139299753176</v>
       </c>
       <c r="D367" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E367">
         <v>2.672915915531583</v>
@@ -19855,7 +19867,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19869,7 +19881,7 @@
         <v>2.722022378645214</v>
       </c>
       <c r="D368" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E368">
         <v>2.672915915531583</v>
@@ -19905,7 +19917,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19919,7 +19931,7 @@
         <v>2.643362683974768</v>
       </c>
       <c r="D369" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E369">
         <v>2.68802760764238</v>
@@ -19955,7 +19967,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19969,7 +19981,7 @@
         <v>2.738474376085565</v>
       </c>
       <c r="D370" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E370">
         <v>2.678250991863972</v>
@@ -20005,7 +20017,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20019,7 +20031,7 @@
         <v>2.26156876679942</v>
       </c>
       <c r="D371" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E371">
         <v>2.319500204055783</v>
@@ -20055,7 +20067,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20069,7 +20081,7 @@
         <v>2.341086491507057</v>
       </c>
       <c r="D372" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E372">
         <v>2.284741341701965</v>
@@ -20105,7 +20117,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20119,7 +20131,7 @@
         <v>2.25156876679942</v>
       </c>
       <c r="D373" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E373">
         <v>2.298948197976329</v>
@@ -20155,7 +20167,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20169,7 +20181,7 @@
         <v>2.345775623073784</v>
       </c>
       <c r="D374" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E374">
         <v>2.287361910525056</v>
@@ -20205,7 +20217,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20219,7 +20231,7 @@
         <v>1.450725995788351</v>
       </c>
       <c r="D375" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E375">
         <v>1.543612412630503</v>
@@ -20255,7 +20267,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20269,7 +20281,7 @@
         <v>1.378039753255653</v>
       </c>
       <c r="D376" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E376">
         <v>1.473954763536668</v>
@@ -20305,7 +20317,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20319,7 +20331,7 @@
         <v>2.300473418774809</v>
       </c>
       <c r="D377" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E377">
         <v>2.269274816103397</v>
@@ -20369,7 +20381,7 @@
         <v>2.307737312105645</v>
       </c>
       <c r="D378" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E378">
         <v>2.269274816103397</v>
@@ -20419,7 +20431,7 @@
         <v>2.548688372146674</v>
       </c>
       <c r="D379" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E379">
         <v>2.44021981851742</v>
@@ -20455,7 +20467,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20469,7 +20481,7 @@
         <v>4.064626779899114</v>
       </c>
       <c r="D380" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E380">
         <v>3.971827788774664</v>
@@ -20505,7 +20517,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20519,7 +20531,7 @@
         <v>2.704221825320051</v>
       </c>
       <c r="D381" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E381">
         <v>2.757514946748523</v>
@@ -20555,7 +20567,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20569,7 +20581,7 @@
         <v>2.699698304540886</v>
       </c>
       <c r="D382" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E382">
         <v>2.757514946748523</v>
@@ -20605,7 +20617,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20619,7 +20631,7 @@
         <v>2.597723564836138</v>
       </c>
       <c r="D383" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E383">
         <v>2.648687698460786</v>
@@ -20655,7 +20667,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20669,7 +20681,7 @@
         <v>2.594470401040876</v>
       </c>
       <c r="D384" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E384">
         <v>2.648687698460786</v>
@@ -20705,7 +20717,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20719,7 +20731,7 @@
         <v>2.5327482758737</v>
       </c>
       <c r="D385" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E385">
         <v>2.582291478725809</v>
@@ -20755,7 +20767,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20769,7 +20781,7 @@
         <v>2.530270165227095</v>
       </c>
       <c r="D386" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E386">
         <v>2.582291478725809</v>
@@ -20805,7 +20817,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20819,7 +20831,7 @@
         <v>2.615226386520305</v>
       </c>
       <c r="D387" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E387">
         <v>2.605226386520305</v>
@@ -20855,7 +20867,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20869,7 +20881,7 @@
         <v>2.519210324106</v>
       </c>
       <c r="D388" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E388">
         <v>2.474919909368535</v>
@@ -20905,7 +20917,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20919,7 +20931,7 @@
         <v>2.443973795685154</v>
       </c>
       <c r="D389" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E389">
         <v>2.491575608314453</v>
@@ -20955,7 +20967,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20969,7 +20981,7 @@
         <v>2.442554625160083</v>
       </c>
       <c r="D390" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E390">
         <v>2.491575608314453</v>
@@ -21005,7 +21017,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21055,7 +21067,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21069,7 +21081,7 @@
         <v>2.457705873063223</v>
       </c>
       <c r="D392" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E392">
         <v>2.413049360402885</v>
@@ -21105,7 +21117,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21119,7 +21131,7 @@
         <v>2.382591377283335</v>
       </c>
       <c r="D393" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E393">
         <v>2.428850830862097</v>
@@ -21155,7 +21167,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21169,7 +21181,7 @@
         <v>2.381904402604011</v>
       </c>
       <c r="D394" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E394">
         <v>2.428850830862097</v>
@@ -21205,7 +21217,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21219,7 +21231,7 @@
         <v>2.46327835196266</v>
       </c>
       <c r="D395" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E395">
         <v>2.453507343522435</v>
@@ -21255,7 +21267,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21269,7 +21281,7 @@
         <v>2.467705873063223</v>
       </c>
       <c r="D396" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E396">
         <v>2.453507343522435</v>
@@ -21305,7 +21317,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21319,7 +21331,7 @@
         <v>2.447999298642713</v>
       </c>
       <c r="D397" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E397">
         <v>2.403285008753682</v>
@@ -21355,7 +21367,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21369,7 +21381,7 @@
         <v>2.372904061939057</v>
       </c>
       <c r="D398" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E398">
         <v>2.418951665679276</v>
@@ -21405,7 +21417,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21419,7 +21431,7 @@
         <v>2.37233264171712</v>
       </c>
       <c r="D399" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E399">
         <v>2.418951665679276</v>
@@ -21455,7 +21467,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21505,7 +21517,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21555,7 +21567,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21569,7 +21581,7 @@
         <v>2.414261420787727</v>
       </c>
       <c r="D402" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E402">
         <v>2.369346310197177</v>
@@ -21605,7 +21617,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21655,7 +21667,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21705,7 +21717,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21719,7 +21731,7 @@
         <v>2.424261420787727</v>
       </c>
       <c r="D405" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E405">
         <v>2.394544385485897</v>
@@ -21755,7 +21767,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21769,7 +21781,7 @@
         <v>2.414374606666995</v>
       </c>
       <c r="D406" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E406">
         <v>2.394544385485897</v>
@@ -21805,7 +21817,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21819,7 +21831,7 @@
         <v>2.397600622679596</v>
       </c>
       <c r="D407" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E407">
         <v>2.352586340671736</v>
@@ -21855,7 +21867,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21869,7 +21881,7 @@
         <v>2.322605383348882</v>
       </c>
       <c r="D408" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E408">
         <v>2.367553015986731</v>
@@ -21905,7 +21917,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21919,7 +21931,7 @@
         <v>2.322633947364601</v>
       </c>
       <c r="D409" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E409">
         <v>2.367553015986731</v>
@@ -21955,7 +21967,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -21969,7 +21981,7 @@
         <v>2.402576819333163</v>
       </c>
       <c r="D410" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E410">
         <v>2.35256729799459</v>
@@ -22005,7 +22017,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22019,7 +22031,7 @@
         <v>2.407600622679595</v>
       </c>
       <c r="D411" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E411">
         <v>2.35256729799459</v>
@@ -22055,7 +22067,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22069,7 +22081,7 @@
         <v>2.39758158000245</v>
       </c>
       <c r="D412" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E412">
         <v>2.35256729799459</v>
@@ -22105,7 +22117,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22119,7 +22131,7 @@
         <v>2.378737718650321</v>
       </c>
       <c r="D413" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E413">
         <v>2.33361115745181</v>
@@ -22155,7 +22167,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22169,7 +22181,7 @@
         <v>2.30377990571649</v>
       </c>
       <c r="D414" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E414">
         <v>2.348315847988621</v>
@@ -22205,7 +22217,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22219,7 +22231,7 @@
         <v>2.304033028113511</v>
       </c>
       <c r="D415" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E415">
         <v>2.348315847988621</v>
@@ -22255,7 +22267,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22269,7 +22281,7 @@
         <v>2.383526783319471</v>
       </c>
       <c r="D416" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E416">
         <v>2.333442409187131</v>
@@ -22305,7 +22317,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22319,7 +22331,7 @@
         <v>2.38873771865032</v>
       </c>
       <c r="D417" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E417">
         <v>2.333442409187131</v>
@@ -22355,7 +22367,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22369,7 +22381,7 @@
         <v>2.378568970385641</v>
       </c>
       <c r="D418" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E418">
         <v>2.333442409187131</v>
@@ -22405,7 +22417,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22419,7 +22431,7 @@
         <v>2.29477967980894</v>
       </c>
       <c r="D419" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E419">
         <v>2.33911879805526</v>
@@ -22469,7 +22481,7 @@
         <v>2.295140160765494</v>
       </c>
       <c r="D420" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E420">
         <v>2.33911879805526</v>
@@ -22519,7 +22531,7 @@
         <v>2.374419198852388</v>
       </c>
       <c r="D421" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E421">
         <v>2.324299038533536</v>
@@ -22569,7 +22581,7 @@
         <v>2.379719599649515</v>
       </c>
       <c r="D422" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E422">
         <v>2.324299038533536</v>
@@ -22619,7 +22631,7 @@
         <v>2.369479279011813</v>
       </c>
       <c r="D423" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E423">
         <v>2.324299038533536</v>
@@ -22669,7 +22681,7 @@
         <v>2.280590400920047</v>
       </c>
       <c r="D424" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E424">
         <v>2.324619216844741</v>
@@ -22705,7 +22717,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22719,7 +22731,7 @@
         <v>2.281120137688396</v>
       </c>
       <c r="D425" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E425">
         <v>2.324619216844741</v>
@@ -22755,7 +22767,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22769,7 +22781,7 @@
         <v>2.360060664151698</v>
       </c>
       <c r="D426" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E426">
         <v>2.309884085228915</v>
@@ -22805,7 +22817,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22855,7 +22867,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22869,7 +22881,7 @@
         <v>2.281700069738552</v>
       </c>
       <c r="D428" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E428">
         <v>2.325753152774585</v>
@@ -22905,7 +22917,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -22919,7 +22931,7 @@
         <v>2.282216569900716</v>
       </c>
       <c r="D429" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E429">
         <v>2.325753152774585</v>
@@ -22955,7 +22967,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -22969,7 +22981,7 @@
         <v>2.361183569576388</v>
       </c>
       <c r="D430" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E430">
         <v>2.311011402855666</v>
@@ -23005,7 +23017,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23019,7 +23031,7 @@
         <v>2.255753152774584</v>
       </c>
       <c r="D431" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E431">
         <v>2.30032273597278</v>
@@ -23055,7 +23067,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23069,7 +23081,7 @@
         <v>2.248769782041177</v>
       </c>
       <c r="D432" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E432">
         <v>2.297801715354081</v>
@@ -23105,7 +23117,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23119,7 +23131,7 @@
         <v>2.343406757033516</v>
       </c>
       <c r="D433" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E433">
         <v>2.293164740361742</v>
@@ -23155,7 +23167,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23169,7 +23181,7 @@
         <v>2.237801715354081</v>
       </c>
       <c r="D434" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E434">
         <v>2.26243869034642</v>
@@ -23205,7 +23217,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23219,7 +23231,7 @@
         <v>2.228095614122554</v>
       </c>
       <c r="D435" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E435">
         <v>2.276800683120539</v>
@@ -23255,7 +23267,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23269,7 +23281,7 @@
         <v>2.322610014996799</v>
       </c>
       <c r="D436" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E436">
         <v>2.263257480497806</v>
@@ -23305,7 +23317,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23355,7 +23367,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23369,7 +23381,7 @@
         <v>2.224983216186275</v>
       </c>
       <c r="D438" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E438">
         <v>2.273639077311749</v>
@@ -23419,7 +23431,7 @@
         <v>2.319479164108328</v>
       </c>
       <c r="D439" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E439">
         <v>2.26015123354559</v>
@@ -23569,7 +23581,7 @@
         <v>2.3116287572162</v>
       </c>
       <c r="D442" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E442">
         <v>2.252362519438469</v>
@@ -23605,7 +23617,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23655,7 +23667,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23705,7 +23717,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23769,7 +23781,7 @@
         <v>2.185149484739352</v>
       </c>
       <c r="D446" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E446">
         <v>2.165149484739352</v>
@@ -23869,7 +23881,7 @@
         <v>2.20020073233055</v>
       </c>
       <c r="D448" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E448">
         <v>2.205687152603988</v>
@@ -23955,7 +23967,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24005,7 +24017,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24055,7 +24067,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24105,7 +24117,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24155,7 +24167,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24269,7 +24281,7 @@
         <v>2.142114930387524</v>
       </c>
       <c r="D456" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E456">
         <v>2.162114930387524</v>
@@ -24305,7 +24317,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24319,7 +24331,7 @@
         <v>2.115413806995409</v>
       </c>
       <c r="D457" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E457">
         <v>2.141244762127619</v>
@@ -24405,7 +24417,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24419,7 +24431,7 @@
         <v>2.073994682974101</v>
       </c>
       <c r="D459" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E459">
         <v>2.082201671198685</v>
@@ -24469,7 +24481,7 @@
         <v>2.083994682974101</v>
       </c>
       <c r="D460" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E460">
         <v>2.082201671198685</v>
@@ -24555,7 +24567,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24569,7 +24581,7 @@
         <v>2.057461365020192</v>
       </c>
       <c r="D462" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E462">
         <v>2.066125824243982</v>
@@ -24605,7 +24617,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24655,7 +24667,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24705,7 +24717,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24755,7 +24767,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24805,7 +24817,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24819,7 +24831,7 @@
         <v>2.057577737614682</v>
       </c>
       <c r="D467" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E467">
         <v>2.099815205781953</v>
@@ -24855,7 +24867,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24919,7 +24931,7 @@
         <v>2.075267052489131</v>
       </c>
       <c r="D469" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E469">
         <v>2.105974841560053</v>
@@ -24969,7 +24981,7 @@
         <v>2.0673904197019</v>
       </c>
       <c r="D470" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E470">
         <v>2.109513786914668</v>
@@ -25019,7 +25031,7 @@
         <v>2.101281730695467</v>
       </c>
       <c r="D471" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E471">
         <v>2.131889846669813</v>
@@ -25069,7 +25081,7 @@
         <v>2.093106078618507</v>
       </c>
       <c r="D472" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E472">
         <v>2.134930426541548</v>
@@ -25119,7 +25131,7 @@
         <v>2.114232378900782</v>
       </c>
       <c r="D473" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E473">
         <v>2.144790875533345</v>
@@ -25155,7 +25167,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25169,7 +25181,7 @@
         <v>2.164790875533345</v>
       </c>
       <c r="D474" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E474">
         <v>2.134232378900781</v>
@@ -25205,7 +25217,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25219,7 +25231,7 @@
         <v>2.105907868798473</v>
       </c>
       <c r="D475" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E475">
         <v>2.147583358696166</v>
@@ -25255,7 +25267,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25269,7 +25281,7 @@
         <v>2.178667208693582</v>
       </c>
       <c r="D476" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E476">
         <v>2.148162082573172</v>
@@ -25305,7 +25317,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25319,7 +25331,7 @@
         <v>2.119677460934401</v>
       </c>
       <c r="D477" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E477">
         <v>2.161192839295628</v>
@@ -25355,7 +25367,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25369,7 +25381,7 @@
         <v>2.191253934723685</v>
       </c>
       <c r="D478" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E478">
         <v>2.160797219088007</v>
@@ -25419,7 +25431,7 @@
         <v>2.132167365995042</v>
       </c>
       <c r="D479" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E479">
         <v>2.173537512902076</v>
@@ -25519,7 +25531,7 @@
         <v>2.161339958759847</v>
       </c>
       <c r="D481" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E481">
         <v>2.202370889471942</v>
@@ -25569,7 +25581,7 @@
         <v>2.215480849833102</v>
       </c>
       <c r="D482" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E482">
         <v>2.179965384477054</v>
@@ -25606,6 +25618,106 @@
       </c>
       <c r="P482" t="s">
         <v>137</v>
+      </c>
+    </row>
+    <row r="483" spans="1:16">
+      <c r="A483" s="1">
+        <v>0</v>
+      </c>
+      <c r="B483" t="s">
+        <v>146</v>
+      </c>
+      <c r="C483">
+        <v>1.276065947508897</v>
+      </c>
+      <c r="D483" t="s">
+        <v>268</v>
+      </c>
+      <c r="E483">
+        <v>1.302232540035587</v>
+      </c>
+      <c r="F483">
+        <v>1</v>
+      </c>
+      <c r="G483">
+        <v>0.007763934052491102</v>
+      </c>
+      <c r="H483">
+        <v>0.007817767459964412</v>
+      </c>
+      <c r="I483">
+        <v>0.02616659252669074</v>
+      </c>
+      <c r="J483">
+        <v>0.6916703736654803</v>
+      </c>
+      <c r="K483">
+        <v>4.69</v>
+      </c>
+      <c r="L483">
+        <v>4.52</v>
+      </c>
+      <c r="M483">
+        <v>4.71</v>
+      </c>
+      <c r="N483">
+        <v>4.56</v>
+      </c>
+      <c r="O483">
+        <v>1</v>
+      </c>
+      <c r="P483" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="484" spans="1:16">
+      <c r="A484" s="1">
+        <v>0</v>
+      </c>
+      <c r="B484" t="s">
+        <v>146</v>
+      </c>
+      <c r="C484">
+        <v>1.265250934212467</v>
+      </c>
+      <c r="D484" t="s">
+        <v>268</v>
+      </c>
+      <c r="E484">
+        <v>1.291371407279471</v>
+      </c>
+      <c r="F484">
+        <v>1</v>
+      </c>
+      <c r="G484">
+        <v>0.007774749065787532</v>
+      </c>
+      <c r="H484">
+        <v>0.007828628592720528</v>
+      </c>
+      <c r="I484">
+        <v>0.02612047306700438</v>
+      </c>
+      <c r="J484">
+        <v>0.6939763466497937</v>
+      </c>
+      <c r="K484">
+        <v>4.69</v>
+      </c>
+      <c r="L484">
+        <v>4.52</v>
+      </c>
+      <c r="M484">
+        <v>4.71</v>
+      </c>
+      <c r="N484">
+        <v>4.56</v>
+      </c>
+      <c r="O484">
+        <v>1</v>
+      </c>
+      <c r="P484" t="s">
+        <v>382</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-03328-601328.xlsx
+++ b/s60_signal/position-03328-601328.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="385">
   <si>
     <t>trade_time</t>
   </si>
@@ -820,6 +820,9 @@
     <t>2021-06-28</t>
   </si>
   <si>
+    <t>2021-10-25</t>
+  </si>
+  <si>
     <t>2021-10-21</t>
   </si>
   <si>
@@ -1163,6 +1166,9 @@
   </si>
   <si>
     <t>2021-10-18</t>
+  </si>
+  <si>
+    <t>2021-10-19</t>
   </si>
 </sst>
 </file>
@@ -1520,7 +1526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P484"/>
+  <dimension ref="A1:P485"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1617,7 +1623,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1667,7 +1673,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1767,7 +1773,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1817,7 +1823,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1867,7 +1873,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1917,7 +1923,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1967,7 +1973,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2017,7 +2023,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2117,7 +2123,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2167,7 +2173,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2267,7 +2273,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2317,7 +2323,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2667,7 +2673,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2717,7 +2723,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2767,7 +2773,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2817,7 +2823,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2867,7 +2873,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2917,7 +2923,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2967,7 +2973,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3017,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3067,7 +3073,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3117,7 +3123,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3167,7 +3173,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3217,7 +3223,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3267,7 +3273,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3317,7 +3323,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3367,7 +3373,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3417,7 +3423,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3467,7 +3473,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3667,7 +3673,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3717,7 +3723,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3767,7 +3773,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3817,7 +3823,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3867,7 +3873,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3917,7 +3923,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3967,7 +3973,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4017,7 +4023,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4067,7 +4073,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4417,7 +4423,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4467,7 +4473,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4717,7 +4723,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4767,7 +4773,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4817,7 +4823,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4867,7 +4873,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4917,7 +4923,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4967,7 +4973,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5017,7 +5023,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5067,7 +5073,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5117,7 +5123,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5167,7 +5173,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5217,7 +5223,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5267,7 +5273,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5317,7 +5323,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5367,7 +5373,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5417,7 +5423,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5467,7 +5473,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5517,7 +5523,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5567,7 +5573,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5617,7 +5623,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5667,7 +5673,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5717,7 +5723,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5767,7 +5773,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5817,7 +5823,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5917,7 +5923,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5967,7 +5973,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6017,7 +6023,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6067,7 +6073,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6117,7 +6123,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6167,7 +6173,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6217,7 +6223,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6267,7 +6273,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6417,7 +6423,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6467,7 +6473,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6567,7 +6573,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -7067,7 +7073,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7117,7 +7123,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7167,7 +7173,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -8067,7 +8073,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8117,7 +8123,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8317,7 +8323,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8367,7 +8373,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8417,7 +8423,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8617,7 +8623,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8667,7 +8673,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8717,7 +8723,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8767,7 +8773,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8817,7 +8823,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9767,7 +9773,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9817,7 +9823,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9867,7 +9873,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9917,7 +9923,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10117,7 +10123,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10167,7 +10173,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10217,7 +10223,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10267,7 +10273,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10667,7 +10673,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10717,7 +10723,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10767,7 +10773,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10817,7 +10823,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10867,7 +10873,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10917,7 +10923,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10967,7 +10973,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11017,7 +11023,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11067,7 +11073,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11117,7 +11123,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11167,7 +11173,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11467,7 +11473,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11517,7 +11523,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11567,7 +11573,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11617,7 +11623,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11667,7 +11673,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11717,7 +11723,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12017,7 +12023,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12067,7 +12073,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12117,7 +12123,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12167,7 +12173,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12217,7 +12223,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -13117,7 +13123,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13167,7 +13173,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13367,7 +13373,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13417,7 +13423,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13467,7 +13473,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13517,7 +13523,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13567,7 +13573,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13617,7 +13623,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13667,7 +13673,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13867,7 +13873,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13917,7 +13923,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14217,7 +14223,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14267,7 +14273,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14317,7 +14323,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14367,7 +14373,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14417,7 +14423,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14467,7 +14473,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14517,7 +14523,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14567,7 +14573,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14617,7 +14623,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14667,7 +14673,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14717,7 +14723,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14767,7 +14773,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14817,7 +14823,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14967,7 +14973,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15017,7 +15023,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15067,7 +15073,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15117,7 +15123,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15317,7 +15323,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15367,7 +15373,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15417,7 +15423,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15617,7 +15623,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15667,7 +15673,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15717,7 +15723,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15917,7 +15923,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15967,7 +15973,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16017,7 +16023,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16067,7 +16073,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16117,7 +16123,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16167,7 +16173,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16217,7 +16223,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16267,7 +16273,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16367,7 +16373,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16417,7 +16423,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16467,7 +16473,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16517,7 +16523,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16567,7 +16573,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16617,7 +16623,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16667,7 +16673,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16717,7 +16723,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16767,7 +16773,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16817,7 +16823,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16867,7 +16873,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16917,7 +16923,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16967,7 +16973,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17017,7 +17023,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17067,7 +17073,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17117,7 +17123,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17167,7 +17173,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17217,7 +17223,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17267,7 +17273,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17317,7 +17323,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17367,7 +17373,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17417,7 +17423,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17467,7 +17473,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17517,7 +17523,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17567,7 +17573,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17617,7 +17623,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17667,7 +17673,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17867,7 +17873,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17917,7 +17923,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17967,7 +17973,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18567,7 +18573,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18617,7 +18623,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18667,7 +18673,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18717,7 +18723,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18917,7 +18923,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18967,7 +18973,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19017,7 +19023,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19067,7 +19073,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19117,7 +19123,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19167,7 +19173,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19217,7 +19223,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19267,7 +19273,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19317,7 +19323,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19367,7 +19373,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19517,7 +19523,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19567,7 +19573,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19617,7 +19623,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19717,7 +19723,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19767,7 +19773,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19817,7 +19823,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19867,7 +19873,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19917,7 +19923,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19967,7 +19973,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20017,7 +20023,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20067,7 +20073,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20117,7 +20123,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20167,7 +20173,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20217,7 +20223,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20267,7 +20273,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20317,7 +20323,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20467,7 +20473,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20517,7 +20523,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20567,7 +20573,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20617,7 +20623,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20667,7 +20673,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20717,7 +20723,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20767,7 +20773,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20817,7 +20823,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20867,7 +20873,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20917,7 +20923,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20967,7 +20973,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21017,7 +21023,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21067,7 +21073,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21117,7 +21123,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21167,7 +21173,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21217,7 +21223,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21267,7 +21273,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21317,7 +21323,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21367,7 +21373,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21417,7 +21423,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21467,7 +21473,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21517,7 +21523,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21567,7 +21573,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21617,7 +21623,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21667,7 +21673,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21717,7 +21723,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21767,7 +21773,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21817,7 +21823,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21867,7 +21873,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21917,7 +21923,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21967,7 +21973,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22017,7 +22023,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22067,7 +22073,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22117,7 +22123,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22167,7 +22173,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22217,7 +22223,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22267,7 +22273,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22317,7 +22323,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22367,7 +22373,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22417,7 +22423,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22917,7 +22923,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -22967,7 +22973,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23017,7 +23023,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23067,7 +23073,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23117,7 +23123,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23167,7 +23173,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23217,7 +23223,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23267,7 +23273,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23317,7 +23323,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23367,7 +23373,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23617,7 +23623,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23667,7 +23673,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23717,7 +23723,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -25667,7 +25673,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25681,7 +25687,7 @@
         <v>1.265250934212467</v>
       </c>
       <c r="D484" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E484">
         <v>1.291371407279471</v>
@@ -25717,7 +25723,57 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>382</v>
+        <v>383</v>
+      </c>
+    </row>
+    <row r="485" spans="1:16">
+      <c r="A485" s="1">
+        <v>0</v>
+      </c>
+      <c r="B485" t="s">
+        <v>146</v>
+      </c>
+      <c r="C485">
+        <v>1.257848770795328</v>
+      </c>
+      <c r="D485" t="s">
+        <v>269</v>
+      </c>
+      <c r="E485">
+        <v>1.283937678133475</v>
+      </c>
+      <c r="F485">
+        <v>1</v>
+      </c>
+      <c r="G485">
+        <v>0.007782151229204671</v>
+      </c>
+      <c r="H485">
+        <v>0.007836062321866524</v>
+      </c>
+      <c r="I485">
+        <v>0.02608890733814695</v>
+      </c>
+      <c r="J485">
+        <v>0.6955546330926804</v>
+      </c>
+      <c r="K485">
+        <v>4.69</v>
+      </c>
+      <c r="L485">
+        <v>4.52</v>
+      </c>
+      <c r="M485">
+        <v>4.71</v>
+      </c>
+      <c r="N485">
+        <v>4.56</v>
+      </c>
+      <c r="O485">
+        <v>1</v>
+      </c>
+      <c r="P485" t="s">
+        <v>384</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-03328-601328.xlsx
+++ b/s60_signal/position-03328-601328.xlsx
@@ -820,7 +820,7 @@
     <t>2021-06-28</t>
   </si>
   <si>
-    <t>2021-10-25</t>
+    <t>2021-10-26</t>
   </si>
   <si>
     <t>2021-10-21</t>
@@ -25640,7 +25640,7 @@
         <v>268</v>
       </c>
       <c r="E483">
-        <v>1.302232540035587</v>
+        <v>1.302982651245552</v>
       </c>
       <c r="F483">
         <v>1</v>
@@ -25649,10 +25649,10 @@
         <v>0.007763934052491102</v>
       </c>
       <c r="H483">
-        <v>0.007817767459964412</v>
+        <v>0.007777017348754449</v>
       </c>
       <c r="I483">
-        <v>0.02616659252669074</v>
+        <v>0.02691670373665556</v>
       </c>
       <c r="J483">
         <v>0.6916703736654803</v>
@@ -25664,10 +25664,10 @@
         <v>4.52</v>
       </c>
       <c r="M483">
-        <v>4.71</v>
+        <v>4.68</v>
       </c>
       <c r="N483">
-        <v>4.56</v>
+        <v>4.54</v>
       </c>
       <c r="O483">
         <v>1</v>

--- a/s60_signal/position-03328-601328.xlsx
+++ b/s60_signal/position-03328-601328.xlsx
@@ -820,7 +820,7 @@
     <t>2021-06-28</t>
   </si>
   <si>
-    <t>2021-10-26</t>
+    <t>2021-10-28</t>
   </si>
   <si>
     <t>2021-10-21</t>
@@ -25640,7 +25640,7 @@
         <v>268</v>
       </c>
       <c r="E483">
-        <v>1.302982651245552</v>
+        <v>1.307566169928826</v>
       </c>
       <c r="F483">
         <v>1</v>
@@ -25649,10 +25649,10 @@
         <v>0.007763934052491102</v>
       </c>
       <c r="H483">
-        <v>0.007777017348754449</v>
+        <v>0.007712433830071174</v>
       </c>
       <c r="I483">
-        <v>0.02691670373665556</v>
+        <v>0.031500222419929</v>
       </c>
       <c r="J483">
         <v>0.6916703736654803</v>
@@ -25664,10 +25664,10 @@
         <v>4.52</v>
       </c>
       <c r="M483">
-        <v>4.68</v>
+        <v>4.63</v>
       </c>
       <c r="N483">
-        <v>4.54</v>
+        <v>4.51</v>
       </c>
       <c r="O483">
         <v>1</v>

--- a/s60_signal/position-03328-601328.xlsx
+++ b/s60_signal/position-03328-601328.xlsx
@@ -820,10 +820,10 @@
     <t>2021-06-28</t>
   </si>
   <si>
+    <t>2021-10-29</t>
+  </si>
+  <si>
     <t>2021-10-28</t>
-  </si>
-  <si>
-    <t>2021-10-21</t>
   </si>
   <si>
     <t>2016-05-24</t>
@@ -25640,7 +25640,7 @@
         <v>268</v>
       </c>
       <c r="E483">
-        <v>1.307566169928826</v>
+        <v>1.317566169928825</v>
       </c>
       <c r="F483">
         <v>1</v>
@@ -25649,10 +25649,10 @@
         <v>0.007763934052491102</v>
       </c>
       <c r="H483">
-        <v>0.007712433830071174</v>
+        <v>0.007722433830071173</v>
       </c>
       <c r="I483">
-        <v>0.031500222419929</v>
+        <v>0.04150022241992879</v>
       </c>
       <c r="J483">
         <v>0.6916703736654803</v>
@@ -25667,7 +25667,7 @@
         <v>4.63</v>
       </c>
       <c r="N483">
-        <v>4.51</v>
+        <v>4.52</v>
       </c>
       <c r="O483">
         <v>1</v>
@@ -25687,10 +25687,10 @@
         <v>1.265250934212467</v>
       </c>
       <c r="D484" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E484">
-        <v>1.291371407279471</v>
+        <v>1.306889515011455</v>
       </c>
       <c r="F484">
         <v>1</v>
@@ -25699,10 +25699,10 @@
         <v>0.007774749065787532</v>
       </c>
       <c r="H484">
-        <v>0.007828628592720528</v>
+        <v>0.007733110484988545</v>
       </c>
       <c r="I484">
-        <v>0.02612047306700438</v>
+        <v>0.04163858079898786</v>
       </c>
       <c r="J484">
         <v>0.6939763466497937</v>
@@ -25714,10 +25714,10 @@
         <v>4.52</v>
       </c>
       <c r="M484">
-        <v>4.71</v>
+        <v>4.63</v>
       </c>
       <c r="N484">
-        <v>4.56</v>
+        <v>4.52</v>
       </c>
       <c r="O484">
         <v>1</v>
@@ -25740,7 +25740,7 @@
         <v>269</v>
       </c>
       <c r="E485">
-        <v>1.283937678133475</v>
+        <v>1.28958204878089</v>
       </c>
       <c r="F485">
         <v>1</v>
@@ -25749,10 +25749,10 @@
         <v>0.007782151229204671</v>
       </c>
       <c r="H485">
-        <v>0.007836062321866524</v>
+        <v>0.00773041795121911</v>
       </c>
       <c r="I485">
-        <v>0.02608890733814695</v>
+        <v>0.03173327798556169</v>
       </c>
       <c r="J485">
         <v>0.6955546330926804</v>
@@ -25764,10 +25764,10 @@
         <v>4.52</v>
       </c>
       <c r="M485">
-        <v>4.71</v>
+        <v>4.63</v>
       </c>
       <c r="N485">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
       <c r="O485">
         <v>1</v>

--- a/s60_signal/position-03328-601328.xlsx
+++ b/s60_signal/position-03328-601328.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="389">
   <si>
     <t>trade_time</t>
   </si>
@@ -457,6 +457,9 @@
     <t>2021-10-20</t>
   </si>
   <si>
+    <t>2021-11-01</t>
+  </si>
+  <si>
     <t>2016-05-31</t>
   </si>
   <si>
@@ -823,6 +826,9 @@
     <t>2021-10-29</t>
   </si>
   <si>
+    <t>2021-11-02</t>
+  </si>
+  <si>
     <t>2021-10-28</t>
   </si>
   <si>
@@ -1169,6 +1175,12 @@
   </si>
   <si>
     <t>2021-10-19</t>
+  </si>
+  <si>
+    <t>2021-10-26</t>
+  </si>
+  <si>
+    <t>2021-10-27</t>
   </si>
 </sst>
 </file>
@@ -1526,7 +1538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P485"/>
+  <dimension ref="A1:P491"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1587,7 +1599,7 @@
         <v>2.636521639996683</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E2">
         <v>2.833647241107702</v>
@@ -1623,7 +1635,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1637,7 +1649,7 @@
         <v>2.808801457176021</v>
       </c>
       <c r="D3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E3">
         <v>2.7135041663212</v>
@@ -1673,7 +1685,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1687,7 +1699,7 @@
         <v>2.746397091058633</v>
       </c>
       <c r="D4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E4">
         <v>2.648930323263125</v>
@@ -1737,7 +1749,7 @@
         <v>2.683209227271539</v>
       </c>
       <c r="D5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E5">
         <v>2.583545744375049</v>
@@ -1773,7 +1785,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1787,7 +1799,7 @@
         <v>2.555958070922727</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E6">
         <v>2.632522016358742</v>
@@ -1823,7 +1835,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1837,7 +1849,7 @@
         <v>2.641252819939413</v>
       </c>
       <c r="D7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E7">
         <v>2.540130729835057</v>
@@ -1873,7 +1885,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1887,7 +1899,7 @@
         <v>2.512285655110759</v>
       </c>
       <c r="D8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E8">
         <v>2.590994611146576</v>
@@ -1923,7 +1935,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1937,7 +1949,7 @@
         <v>2.615441102246784</v>
       </c>
       <c r="D9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E9">
         <v>2.513421672263544</v>
@@ -1973,7 +1985,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1987,7 +1999,7 @@
         <v>2.515418243442972</v>
       </c>
       <c r="D10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E10">
         <v>2.545423958143926</v>
@@ -2023,7 +2035,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2037,7 +2049,7 @@
         <v>2.487273994427867</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E11">
         <v>2.567211421027677</v>
@@ -2073,7 +2085,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2087,7 +2099,7 @@
         <v>2.487984580081365</v>
       </c>
       <c r="D12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E12">
         <v>2.579898802553291</v>
@@ -2123,7 +2135,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2137,7 +2149,7 @@
         <v>2.500805561667341</v>
       </c>
       <c r="D13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E13">
         <v>2.59216563562278</v>
@@ -2173,7 +2185,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2187,7 +2199,7 @@
         <v>2.499441989042522</v>
       </c>
       <c r="D14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E14">
         <v>2.736702547602069</v>
@@ -2237,7 +2249,7 @@
         <v>2.512520850741042</v>
       </c>
       <c r="D15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E15">
         <v>2.749061943431123</v>
@@ -2273,7 +2285,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2287,7 +2299,7 @@
         <v>2.77984350091858</v>
       </c>
       <c r="D16" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E16">
         <v>2.889061943431122</v>
@@ -2323,7 +2335,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2337,7 +2349,7 @@
         <v>2.517224153471577</v>
       </c>
       <c r="D17" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E17">
         <v>2.753506518310076</v>
@@ -2373,7 +2385,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2387,7 +2399,7 @@
         <v>2.784426680003737</v>
       </c>
       <c r="D18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E18">
         <v>2.924119959439183</v>
@@ -2423,7 +2435,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2437,7 +2449,7 @@
         <v>2.884280694854824</v>
       </c>
       <c r="D19" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E19">
         <v>2.961861794886389</v>
@@ -2487,7 +2499,7 @@
         <v>2.920719956495094</v>
       </c>
       <c r="D20" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E20">
         <v>2.907075620138133</v>
@@ -2523,7 +2535,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2537,7 +2549,7 @@
         <v>2.648180125005333</v>
       </c>
       <c r="D21" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E21">
         <v>2.848908919700521</v>
@@ -2573,7 +2585,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2623,7 +2635,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2637,7 +2649,7 @@
         <v>2.691620213913162</v>
       </c>
       <c r="D23" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E23">
         <v>2.889959376998489</v>
@@ -2673,7 +2685,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2687,7 +2699,7 @@
         <v>2.984719616116966</v>
       </c>
       <c r="D24" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E24">
         <v>2.755965243802971</v>
@@ -2723,7 +2735,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2737,7 +2749,7 @@
         <v>3.007275184023352</v>
       </c>
       <c r="D25" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E25">
         <v>2.755965243802971</v>
@@ -2773,7 +2785,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2787,7 +2799,7 @@
         <v>2.683495528297218</v>
       </c>
       <c r="D26" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E26">
         <v>2.882281628901694</v>
@@ -2823,7 +2835,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2837,7 +2849,7 @@
         <v>2.976914171586129</v>
       </c>
       <c r="D27" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E27">
         <v>2.747824596132772</v>
@@ -2873,7 +2885,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2887,7 +2899,7 @@
         <v>2.647048085674867</v>
       </c>
       <c r="D28" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E28">
         <v>2.84783915365346</v>
@@ -2923,7 +2935,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2937,7 +2949,7 @@
         <v>2.941898848516719</v>
       </c>
       <c r="D29" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E29">
         <v>2.711305547532774</v>
@@ -2973,7 +2985,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2987,7 +2999,7 @@
         <v>2.962790623816959</v>
       </c>
       <c r="D30" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E30">
         <v>2.711305547532774</v>
@@ -3023,7 +3035,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3037,7 +3049,7 @@
         <v>2.636850318680218</v>
       </c>
       <c r="D31" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E31">
         <v>2.674077933106496</v>
@@ -3073,7 +3085,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3087,7 +3099,7 @@
         <v>2.64386308474694</v>
       </c>
       <c r="D32" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E32">
         <v>2.844829359063415</v>
@@ -3123,7 +3135,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3137,7 +3149,7 @@
         <v>2.938838994972993</v>
       </c>
       <c r="D33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E33">
         <v>2.708114289235636</v>
@@ -3173,7 +3185,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3187,7 +3199,7 @@
         <v>2.959611880258242</v>
       </c>
       <c r="D34" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E34">
         <v>2.708114289235636</v>
@@ -3223,7 +3235,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3237,7 +3249,7 @@
         <v>2.63362151616782</v>
       </c>
       <c r="D35" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E35">
         <v>2.706375129633912</v>
@@ -3273,7 +3285,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3287,7 +3299,7 @@
         <v>2.623711665472045</v>
       </c>
       <c r="D36" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E36">
         <v>2.825786465799713</v>
@@ -3323,7 +3335,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3337,7 +3349,7 @@
         <v>2.919479379991807</v>
       </c>
       <c r="D37" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E37">
         <v>2.687923279746057</v>
@@ -3373,7 +3385,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3387,7 +3399,7 @@
         <v>2.939500051198033</v>
       </c>
       <c r="D38" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E38">
         <v>2.687923279746057</v>
@@ -3423,7 +3435,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3437,7 +3449,7 @@
         <v>2.613192965390128</v>
       </c>
       <c r="D39" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E39">
         <v>2.65740457966414</v>
@@ -3473,7 +3485,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3487,7 +3499,7 @@
         <v>2.866121269202039</v>
       </c>
       <c r="D40" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E40">
         <v>2.632273716345684</v>
@@ -3537,7 +3549,7 @@
         <v>2.884068721379623</v>
       </c>
       <c r="D41" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E41">
         <v>2.632273716345684</v>
@@ -3587,7 +3599,7 @@
         <v>2.556888701243869</v>
       </c>
       <c r="D42" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E42">
         <v>2.5709911987269</v>
@@ -3637,7 +3649,7 @@
         <v>2.84066903268222</v>
       </c>
       <c r="D43" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E43">
         <v>2.605728438993726</v>
@@ -3673,7 +3685,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3687,7 +3699,7 @@
         <v>2.857627543154535</v>
       </c>
       <c r="D44" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E44">
         <v>2.605728438993726</v>
@@ -3723,7 +3735,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3737,7 +3749,7 @@
         <v>2.530031126511299</v>
       </c>
       <c r="D45" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E45">
         <v>2.536232918189681</v>
@@ -3773,7 +3785,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3787,7 +3799,7 @@
         <v>2.794653597980052</v>
       </c>
       <c r="D46" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E46">
         <v>2.557736881328888</v>
@@ -3823,7 +3835,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3837,7 +3849,7 @@
         <v>2.809824187676618</v>
       </c>
       <c r="D47" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E47">
         <v>2.557736881328888</v>
@@ -3873,7 +3885,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3923,7 +3935,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3937,7 +3949,7 @@
         <v>2.877968395292299</v>
       </c>
       <c r="D49" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E49">
         <v>2.644629614722029</v>
@@ -3973,7 +3985,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3987,7 +3999,7 @@
         <v>2.896376165252531</v>
       </c>
       <c r="D50" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E50">
         <v>2.644629614722029</v>
@@ -4023,7 +4035,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4037,7 +4049,7 @@
         <v>2.521770137334771</v>
       </c>
       <c r="D51" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E51">
         <v>2.535896862069519</v>
@@ -4073,7 +4085,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4087,7 +4099,7 @@
         <v>2.934431839092635</v>
       </c>
       <c r="D52" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E52">
         <v>2.703517868992319</v>
@@ -4123,7 +4135,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4137,7 +4149,7 @@
         <v>2.955033485192349</v>
       </c>
       <c r="D53" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E53">
         <v>2.703517868992319</v>
@@ -4173,7 +4185,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4223,7 +4235,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4237,7 +4249,7 @@
         <v>2.974730272968942</v>
       </c>
       <c r="D55" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E55">
         <v>2.745546910458406</v>
@@ -4273,7 +4285,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4287,7 +4299,7 @@
         <v>2.996897706887981</v>
       </c>
       <c r="D56" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E56">
         <v>2.745546910458406</v>
@@ -4323,7 +4335,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4337,7 +4349,7 @@
         <v>2.624468326525319</v>
       </c>
       <c r="D57" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E57">
         <v>2.660688149733082</v>
@@ -4373,7 +4385,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4387,7 +4399,7 @@
         <v>3.056805462611843</v>
       </c>
       <c r="D58" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E58">
         <v>2.831146801497014</v>
@@ -4423,7 +4435,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4473,7 +4485,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4487,7 +4499,7 @@
         <v>3.075488420323122</v>
       </c>
       <c r="D60" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E60">
         <v>2.850632094815525</v>
@@ -4537,7 +4549,7 @@
         <v>2.73140795531227</v>
       </c>
       <c r="D61" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E61">
         <v>2.75953055997749</v>
@@ -4587,7 +4599,7 @@
         <v>2.72765316464271</v>
       </c>
       <c r="D62" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E62">
         <v>2.75953055997749</v>
@@ -4637,7 +4649,7 @@
         <v>2.72671446697532</v>
       </c>
       <c r="D63" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E63">
         <v>2.75953055997749</v>
@@ -4687,7 +4699,7 @@
         <v>6.293149296554828</v>
       </c>
       <c r="D64" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E64">
         <v>5.963700498102364</v>
@@ -4723,7 +4735,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4737,7 +4749,7 @@
         <v>6.420239880180696</v>
       </c>
       <c r="D65" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E65">
         <v>6.082402264327184</v>
@@ -4773,7 +4785,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4787,7 +4799,7 @@
         <v>6.609514294497387</v>
       </c>
       <c r="D66" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E66">
         <v>6.259183317962906</v>
@@ -4823,7 +4835,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4837,7 +4849,7 @@
         <v>6.515171551263329</v>
       </c>
       <c r="D67" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E67">
         <v>6.612047937164794</v>
@@ -4873,7 +4885,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4887,7 +4899,7 @@
         <v>6.520829737768901</v>
       </c>
       <c r="D68" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E68">
         <v>6.612047937164794</v>
@@ -4923,7 +4935,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4973,7 +4985,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5023,7 +5035,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5073,7 +5085,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5087,7 +5099,7 @@
         <v>6.781478804637512</v>
       </c>
       <c r="D72" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E72">
         <v>6.821616798629249</v>
@@ -5123,7 +5135,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5137,7 +5149,7 @@
         <v>6.927933775178332</v>
       </c>
       <c r="D73" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E73">
         <v>7.025464228815041</v>
@@ -5173,7 +5185,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5187,7 +5199,7 @@
         <v>7.465293617228137</v>
       </c>
       <c r="D74" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E74">
         <v>7.441132824526438</v>
@@ -5223,7 +5235,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5237,7 +5249,7 @@
         <v>2.399740228983164</v>
       </c>
       <c r="D75" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E75">
         <v>2.284756328614283</v>
@@ -5273,7 +5285,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5287,7 +5299,7 @@
         <v>2.181146111927123</v>
       </c>
       <c r="D76" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E76">
         <v>2.105842395854763</v>
@@ -5323,7 +5335,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5337,7 +5349,7 @@
         <v>2.180858495485883</v>
       </c>
       <c r="D77" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E77">
         <v>2.105842395854763</v>
@@ -5373,7 +5385,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5387,7 +5399,7 @@
         <v>2.355267416838251</v>
       </c>
       <c r="D78" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E78">
         <v>2.241615480893012</v>
@@ -5423,7 +5435,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5437,7 +5449,7 @@
         <v>2.138079262229388</v>
       </c>
       <c r="D79" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E79">
         <v>2.115876072829124</v>
@@ -5473,7 +5485,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5487,7 +5499,7 @@
         <v>2.136977667529256</v>
       </c>
       <c r="D80" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E80">
         <v>2.115876072829124</v>
@@ -5523,7 +5535,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5573,7 +5585,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5623,7 +5635,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5673,7 +5685,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5687,7 +5699,7 @@
         <v>1.925553832103902</v>
       </c>
       <c r="D84" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E84">
         <v>1.985821650998686</v>
@@ -5723,7 +5735,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5773,7 +5785,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5787,7 +5799,7 @@
         <v>1.87975631937778</v>
       </c>
       <c r="D86" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E86">
         <v>2.025900250164519</v>
@@ -5823,7 +5835,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5923,7 +5935,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5937,7 +5949,7 @@
         <v>1.789383875507923</v>
       </c>
       <c r="D89" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E89">
         <v>1.940268655809146</v>
@@ -5973,7 +5985,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5987,7 +5999,7 @@
         <v>1.804905667333501</v>
       </c>
       <c r="D90" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E90">
         <v>1.95497618970289</v>
@@ -6023,7 +6035,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6037,7 +6049,7 @@
         <v>1.809491967335235</v>
       </c>
       <c r="D91" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E91">
         <v>1.959321896917648</v>
@@ -6073,7 +6085,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6087,7 +6099,7 @@
         <v>1.822908408572121</v>
       </c>
       <c r="D92" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E92">
         <v>1.972034524843747</v>
@@ -6123,7 +6135,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6137,7 +6149,7 @@
         <v>2.011491451443282</v>
       </c>
       <c r="D93" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E93">
         <v>1.930405304642352</v>
@@ -6173,7 +6185,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6187,7 +6199,7 @@
         <v>1.820166348365971</v>
       </c>
       <c r="D94" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E94">
         <v>1.969436310418903</v>
@@ -6223,7 +6235,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6237,7 +6249,7 @@
         <v>2.008879751476441</v>
       </c>
       <c r="D95" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E95">
         <v>1.927766633591516</v>
@@ -6273,7 +6285,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6287,7 +6299,7 @@
         <v>1.780154910291897</v>
       </c>
       <c r="D96" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E96">
         <v>1.931523833030682</v>
@@ -6323,7 +6335,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6373,7 +6385,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6387,7 +6399,7 @@
         <v>1.781411528733962</v>
       </c>
       <c r="D98" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E98">
         <v>1.932714530505294</v>
@@ -6423,7 +6435,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6473,7 +6485,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6487,7 +6499,7 @@
         <v>1.786869994736246</v>
       </c>
       <c r="D100" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E100">
         <v>1.937886650750082</v>
@@ -6537,7 +6549,7 @@
         <v>1.77389224303264</v>
       </c>
       <c r="D101" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E101">
         <v>1.925589699135846</v>
@@ -6573,7 +6585,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6587,7 +6599,7 @@
         <v>1.764225388294109</v>
       </c>
       <c r="D102" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E102">
         <v>1.916429958088516</v>
@@ -6787,7 +6799,7 @@
         <v>2.039049007419374</v>
       </c>
       <c r="D106" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E106">
         <v>1.958247448115615</v>
@@ -6823,7 +6835,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6837,7 +6849,7 @@
         <v>1.963804213639886</v>
       </c>
       <c r="D107" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E107">
         <v>2.044635472991321</v>
@@ -6873,7 +6885,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6887,7 +6899,7 @@
         <v>2.084469221121035</v>
       </c>
       <c r="D108" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E108">
         <v>2.00413671738046</v>
@@ -6923,7 +6935,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6937,7 +6949,7 @@
         <v>1.970692549466935</v>
       </c>
       <c r="D109" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E109">
         <v>2.103970465510173</v>
@@ -6973,7 +6985,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7023,7 +7035,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7037,7 +7049,7 @@
         <v>1.989826166099606</v>
       </c>
       <c r="D111" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E111">
         <v>2.069999197311251</v>
@@ -7073,7 +7085,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7087,7 +7099,7 @@
         <v>1.996538974422711</v>
       </c>
       <c r="D112" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E112">
         <v>2.129860772341935</v>
@@ -7123,7 +7135,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7173,7 +7185,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7187,7 +7199,7 @@
         <v>1.976959483296697</v>
       </c>
       <c r="D114" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E114">
         <v>2.110248039295503</v>
@@ -7287,7 +7299,7 @@
         <v>1.920546112528168</v>
       </c>
       <c r="D116" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E116">
         <v>2.053738890308352</v>
@@ -7323,7 +7335,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7373,7 +7385,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7387,7 +7399,7 @@
         <v>2.078859445890371</v>
       </c>
       <c r="D118" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E118">
         <v>2.128859445890371</v>
@@ -7423,7 +7435,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7437,7 +7449,7 @@
         <v>1.864471846503076</v>
       </c>
       <c r="D119" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E119">
         <v>1.997569421794252</v>
@@ -7473,7 +7485,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7523,7 +7535,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7573,7 +7585,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7587,7 +7599,7 @@
         <v>1.863420505387863</v>
       </c>
       <c r="D122" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E122">
         <v>1.996516295719591</v>
@@ -7687,7 +7699,7 @@
         <v>2.029857360363785</v>
       </c>
       <c r="D124" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E124">
         <v>2.011995247378231</v>
@@ -7737,7 +7749,7 @@
         <v>1.892165706973767</v>
       </c>
       <c r="D125" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E125">
         <v>2.025310300703773</v>
@@ -7773,7 +7785,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7823,7 +7835,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7873,7 +7885,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7937,7 +7949,7 @@
         <v>2.183293967129219</v>
       </c>
       <c r="D129" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E129">
         <v>2.097698061214447</v>
@@ -7987,7 +7999,7 @@
         <v>2.10409703769314</v>
       </c>
       <c r="D130" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E130">
         <v>2.097698061214447</v>
@@ -8073,7 +8085,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8123,7 +8135,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8173,7 +8185,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8223,7 +8235,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8273,7 +8285,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8323,7 +8335,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8373,7 +8385,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8423,7 +8435,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8437,7 +8449,7 @@
         <v>2.367284598691813</v>
       </c>
       <c r="D139" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E139">
         <v>2.284677125480481</v>
@@ -8487,7 +8499,7 @@
         <v>2.308705785003503</v>
       </c>
       <c r="D140" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E140">
         <v>2.284677125480481</v>
@@ -8623,7 +8635,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8673,7 +8685,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8723,7 +8735,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8773,7 +8785,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8823,7 +8835,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8887,7 +8899,7 @@
         <v>2.673055621612132</v>
       </c>
       <c r="D148" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E148">
         <v>2.649383477311975</v>
@@ -8937,7 +8949,7 @@
         <v>2.694510447967022</v>
       </c>
       <c r="D149" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E149">
         <v>2.66746656530884</v>
@@ -8987,7 +8999,7 @@
         <v>2.61961842602696</v>
       </c>
       <c r="D150" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E150">
         <v>2.674946565009619</v>
@@ -9273,7 +9285,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9287,7 +9299,7 @@
         <v>2.746485076848839</v>
       </c>
       <c r="D156" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E156">
         <v>2.847982602490786</v>
@@ -9323,7 +9335,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9387,7 +9399,7 @@
         <v>2.750734210259811</v>
       </c>
       <c r="D158" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E158">
         <v>2.800734210259812</v>
@@ -9423,7 +9435,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9487,7 +9499,7 @@
         <v>2.717092536535202</v>
       </c>
       <c r="D160" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E160">
         <v>2.791717770085309</v>
@@ -9573,7 +9585,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9587,7 +9599,7 @@
         <v>2.669840281895235</v>
       </c>
       <c r="D162" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E162">
         <v>2.754805459723328</v>
@@ -9623,7 +9635,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9687,7 +9699,7 @@
         <v>2.704152220032186</v>
       </c>
       <c r="D164" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E164">
         <v>2.721608307945189</v>
@@ -9737,7 +9749,7 @@
         <v>0.7516342779874527</v>
       </c>
       <c r="D165" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E165">
         <v>0.6447312303040151</v>
@@ -9773,7 +9785,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9787,7 +9799,7 @@
         <v>0.6347312303040145</v>
       </c>
       <c r="D166" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E166">
         <v>0.7803954970608276</v>
@@ -9823,7 +9835,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9837,7 +9849,7 @@
         <v>0.7872985447442655</v>
       </c>
       <c r="D167" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E167">
         <v>0.6685373256708909</v>
@@ -9873,7 +9885,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9887,7 +9899,7 @@
         <v>0.6141118398407031</v>
       </c>
       <c r="D168" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E168">
         <v>0.7042015924277036</v>
@@ -9923,7 +9935,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9937,7 +9949,7 @@
         <v>0.7076194190074974</v>
       </c>
       <c r="D169" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E169">
         <v>0.8524403513495589</v>
@@ -9987,7 +9999,7 @@
         <v>0.8587410173081755</v>
       </c>
       <c r="D170" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E170">
         <v>0.7402207509247285</v>
@@ -10037,7 +10049,7 @@
         <v>0.6868795521992208</v>
       </c>
       <c r="D171" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E171">
         <v>0.7750416832667906</v>
@@ -10087,7 +10099,7 @@
         <v>0.794311018129779</v>
       </c>
       <c r="D172" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E172">
         <v>0.9381289071762104</v>
@@ -10123,7 +10135,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10137,7 +10149,7 @@
         <v>0.7478436529603893</v>
       </c>
       <c r="D173" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E173">
         <v>0.9381289071762104</v>
@@ -10173,7 +10185,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10187,7 +10199,7 @@
         <v>0.9437131136379486</v>
       </c>
       <c r="D174" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E174">
         <v>0.8254794310532532</v>
@@ -10223,7 +10235,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10237,7 +10249,7 @@
         <v>0.7734278594221262</v>
       </c>
       <c r="D175" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E175">
         <v>0.8592973200996861</v>
@@ -10273,7 +10285,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10287,7 +10299,7 @@
         <v>0.9016190641047892</v>
       </c>
       <c r="D176" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E176">
         <v>1.04419537245399</v>
@@ -10323,7 +10335,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10337,7 +10349,7 @@
         <v>0.8558611736195321</v>
       </c>
       <c r="D177" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E177">
         <v>1.04419537245399</v>
@@ -10373,7 +10385,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10387,7 +10399,7 @@
         <v>1.048892735560562</v>
       </c>
       <c r="D178" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E178">
         <v>0.9310137903179339</v>
@@ -10423,7 +10435,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10437,7 +10449,7 @@
         <v>0.8805585367261042</v>
       </c>
       <c r="D179" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E179">
         <v>0.963590098667134</v>
@@ -10473,7 +10485,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10487,7 +10499,7 @@
         <v>1.076170489586433</v>
       </c>
       <c r="D180" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E180">
         <v>1.260525374010979</v>
@@ -10537,7 +10549,7 @@
         <v>1.26341395784032</v>
       </c>
       <c r="D181" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E181">
         <v>1.146258524308584</v>
@@ -10587,7 +10599,7 @@
         <v>1.099059073415773</v>
       </c>
       <c r="D182" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E182">
         <v>1.176302541669659</v>
@@ -10637,7 +10649,7 @@
         <v>1.931268098407571</v>
       </c>
       <c r="D183" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E183">
         <v>1.946759727730396</v>
@@ -10673,7 +10685,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10723,7 +10735,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10773,7 +10785,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10787,7 +10799,7 @@
         <v>0.5942088493584849</v>
       </c>
       <c r="D186" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E186">
         <v>0.5982130518354056</v>
@@ -10823,7 +10835,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10873,7 +10885,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10923,7 +10935,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10973,7 +10985,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10987,7 +10999,7 @@
         <v>-0.02499489055226256</v>
       </c>
       <c r="D190" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E190">
         <v>-0.07499489055226238</v>
@@ -11023,7 +11035,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11037,7 +11049,7 @@
         <v>-0.04541693580813089</v>
       </c>
       <c r="D191" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E191">
         <v>-0.1350880582477796</v>
@@ -11073,7 +11085,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11123,7 +11135,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11173,7 +11185,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11323,7 +11335,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11337,7 +11349,7 @@
         <v>-0.5154661476950757</v>
       </c>
       <c r="D197" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E197">
         <v>-0.4838284745942198</v>
@@ -11373,7 +11385,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11387,7 +11399,7 @@
         <v>-0.5144835438345625</v>
       </c>
       <c r="D198" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E198">
         <v>-0.4838284745942198</v>
@@ -11423,7 +11435,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11473,7 +11485,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11487,7 +11499,7 @@
         <v>-0.6795603356321358</v>
       </c>
       <c r="D200" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E200">
         <v>-0.6353746161347429</v>
@@ -11523,7 +11535,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11537,7 +11549,7 @@
         <v>-0.6770489039336995</v>
       </c>
       <c r="D201" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E201">
         <v>-0.6353746161347429</v>
@@ -11573,7 +11585,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11623,7 +11635,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11637,7 +11649,7 @@
         <v>-1.275160705635463</v>
       </c>
       <c r="D203" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E203">
         <v>-0.9575450227817477</v>
@@ -11673,7 +11685,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11687,7 +11699,7 @@
         <v>-1.267100202166811</v>
       </c>
       <c r="D204" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E204">
         <v>-0.9575450227817477</v>
@@ -11723,7 +11735,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11787,7 +11799,7 @@
         <v>-1.30354206111917</v>
       </c>
       <c r="D206" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E206">
         <v>-0.9846924062879019</v>
@@ -11837,7 +11849,7 @@
         <v>-1.295217135083899</v>
       </c>
       <c r="D207" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E207">
         <v>-0.9846924062879019</v>
@@ -11887,7 +11899,7 @@
         <v>-1.315601110783377</v>
       </c>
       <c r="D208" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E208">
         <v>-0.9962271494449686</v>
@@ -11937,7 +11949,7 @@
         <v>-1.307163833353718</v>
       </c>
       <c r="D209" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E209">
         <v>-0.9962271494449686</v>
@@ -11987,7 +11999,7 @@
         <v>-1.303470101275702</v>
       </c>
       <c r="D210" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E210">
         <v>-0.9846235751332797</v>
@@ -12023,7 +12035,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12037,7 +12049,7 @@
         <v>-1.295145845673754</v>
       </c>
       <c r="D211" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E211">
         <v>-0.9846235751332797</v>
@@ -12073,7 +12085,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12087,7 +12099,7 @@
         <v>-1.352240812118975</v>
       </c>
       <c r="D212" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E212">
         <v>-1.031273820287715</v>
@@ -12123,7 +12135,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12137,7 +12149,7 @@
         <v>-1.343462171012276</v>
       </c>
       <c r="D213" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E213">
         <v>-1.031273820287715</v>
@@ -12173,7 +12185,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12223,7 +12235,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12237,7 +12249,7 @@
         <v>-1.277973836666044</v>
       </c>
       <c r="D215" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E215">
         <v>-0.9602358437675207</v>
@@ -12287,7 +12299,7 @@
         <v>-1.269887123902075</v>
       </c>
       <c r="D216" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E216">
         <v>-0.9602358437675207</v>
@@ -12337,7 +12349,7 @@
         <v>-1.030235843767521</v>
       </c>
       <c r="D217" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E217">
         <v>-1.080019061857596</v>
@@ -12387,7 +12399,7 @@
         <v>-1.007888992711643</v>
       </c>
       <c r="D218" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E218">
         <v>-1.080019061857596</v>
@@ -12437,7 +12449,7 @@
         <v>-1.154349245698821</v>
       </c>
       <c r="D219" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E219">
         <v>-0.8419862350162637</v>
@@ -12487,7 +12499,7 @@
         <v>-1.147414314838273</v>
       </c>
       <c r="D220" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E220">
         <v>-0.8419862350162637</v>
@@ -12637,7 +12649,7 @@
         <v>-0.9332125637434627</v>
       </c>
       <c r="D223" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E223">
         <v>-0.6304641914067899</v>
@@ -12673,7 +12685,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12687,7 +12699,7 @@
         <v>-0.9283379125284608</v>
       </c>
       <c r="D224" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E224">
         <v>-0.6304641914067899</v>
@@ -12723,7 +12735,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12737,7 +12749,7 @@
         <v>-1.078298911794628</v>
       </c>
       <c r="D225" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E225">
         <v>-0.7337942740491279</v>
@@ -12787,7 +12799,7 @@
         <v>-1.284045732215318</v>
       </c>
       <c r="D226" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E226">
         <v>-0.9315166474955321</v>
@@ -12837,7 +12849,7 @@
         <v>-1.074552792811861</v>
       </c>
       <c r="D227" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E227">
         <v>-0.7301942595508679</v>
@@ -12873,7 +12885,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12887,7 +12899,7 @@
         <v>0.6306184682796347</v>
       </c>
       <c r="D228" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E228">
         <v>0.8825890610024754</v>
@@ -12923,7 +12935,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12937,7 +12949,7 @@
         <v>2.500083924851446</v>
       </c>
       <c r="D229" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E229">
         <v>2.721828222716436</v>
@@ -12973,7 +12985,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12987,7 +12999,7 @@
         <v>2.484743417251086</v>
       </c>
       <c r="D230" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E230">
         <v>2.721828222716436</v>
@@ -13023,7 +13035,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13037,7 +13049,7 @@
         <v>2.959498476516616</v>
       </c>
       <c r="D231" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E231">
         <v>3.019498476516616</v>
@@ -13073,7 +13085,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13123,7 +13135,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13137,7 +13149,7 @@
         <v>3.973072767193392</v>
       </c>
       <c r="D233" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E233">
         <v>3.630196829293595</v>
@@ -13173,7 +13185,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13223,7 +13235,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13273,7 +13285,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13287,7 +13299,7 @@
         <v>4.556254256131551</v>
       </c>
       <c r="D236" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E236">
         <v>4.211276763316661</v>
@@ -13323,7 +13335,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13373,7 +13385,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13423,7 +13435,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13437,7 +13449,7 @@
         <v>4.667791750685101</v>
       </c>
       <c r="D239" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E239">
         <v>4.322412320952902</v>
@@ -13473,7 +13485,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13487,7 +13499,7 @@
         <v>4.273963746622406</v>
       </c>
       <c r="D240" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E240">
         <v>4.266274031756307</v>
@@ -13523,7 +13535,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13573,7 +13585,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13623,7 +13635,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13637,7 +13649,7 @@
         <v>3.655351043939968</v>
       </c>
       <c r="D243" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E243">
         <v>3.313620049187031</v>
@@ -13673,7 +13685,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13687,7 +13699,7 @@
         <v>2.349652973133038</v>
       </c>
       <c r="D244" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E244">
         <v>2.585321458264525</v>
@@ -13737,7 +13749,7 @@
         <v>2.337296219946928</v>
       </c>
       <c r="D245" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E245">
         <v>2.585321458264525</v>
@@ -13787,7 +13799,7 @@
         <v>2.821499834857581</v>
       </c>
       <c r="D246" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E246">
         <v>2.482773709326562</v>
@@ -13837,7 +13849,7 @@
         <v>1.399171925433256</v>
       </c>
       <c r="D247" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E247">
         <v>1.7228188215915</v>
@@ -13873,7 +13885,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13887,7 +13899,7 @@
         <v>1.94957093986026</v>
       </c>
       <c r="D248" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E248">
         <v>1.61398690043734</v>
@@ -13923,7 +13935,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13937,7 +13949,7 @@
         <v>1.388298565840941</v>
       </c>
       <c r="D249" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E249">
         <v>1.05473712956764</v>
@@ -13987,7 +13999,7 @@
         <v>1.206849236469149</v>
       </c>
       <c r="D250" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E250">
         <v>0.8739416716530437</v>
@@ -14037,7 +14049,7 @@
         <v>1.250249534396463</v>
       </c>
       <c r="D251" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E251">
         <v>0.9171855721103492</v>
@@ -14087,7 +14099,7 @@
         <v>1.265784593473219</v>
       </c>
       <c r="D252" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E252">
         <v>0.9326646489922341</v>
@@ -14123,7 +14135,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14137,7 +14149,7 @@
         <v>1.181086185990114</v>
       </c>
       <c r="D253" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E253">
         <v>0.8482714609955542</v>
@@ -14187,7 +14199,7 @@
         <v>3.393868635799184</v>
       </c>
       <c r="D254" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E254">
         <v>3.232668972857903</v>
@@ -14223,7 +14235,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14237,7 +14249,7 @@
         <v>3.344337857016143</v>
       </c>
       <c r="D255" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E255">
         <v>3.232668972857903</v>
@@ -14273,7 +14285,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14287,7 +14299,7 @@
         <v>3.108144846549583</v>
       </c>
       <c r="D256" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E256">
         <v>3.176241351782863</v>
@@ -14323,7 +14335,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14337,7 +14349,7 @@
         <v>3.110765478091183</v>
       </c>
       <c r="D257" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E257">
         <v>3.176241351782863</v>
@@ -14373,7 +14385,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14387,7 +14399,7 @@
         <v>3.484929217459694</v>
       </c>
       <c r="D258" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E258">
         <v>3.328403460479749</v>
@@ -14423,7 +14435,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14437,7 +14449,7 @@
         <v>3.438944160440425</v>
       </c>
       <c r="D259" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E259">
         <v>3.328403460479749</v>
@@ -14473,7 +14485,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14523,7 +14535,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14573,7 +14585,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14587,7 +14599,7 @@
         <v>3.67612531160249</v>
       </c>
       <c r="D262" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E262">
         <v>3.529413159454653</v>
@@ -14623,7 +14635,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14637,7 +14649,7 @@
         <v>3.637585058248958</v>
       </c>
       <c r="D263" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E263">
         <v>3.529413159454653</v>
@@ -14673,7 +14685,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14687,7 +14699,7 @@
         <v>3.405388602484038</v>
       </c>
       <c r="D264" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E264">
         <v>3.509413159454653</v>
@@ -14723,7 +14735,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14737,7 +14749,7 @@
         <v>3.405511387337113</v>
       </c>
       <c r="D265" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E265">
         <v>3.509413159454653</v>
@@ -14773,7 +14785,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14787,7 +14799,7 @@
         <v>3.451364045513422</v>
       </c>
       <c r="D266" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E266">
         <v>3.509413159454653</v>
@@ -14823,7 +14835,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14837,7 +14849,7 @@
         <v>4.004636932335591</v>
       </c>
       <c r="D267" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E267">
         <v>3.867442887120403</v>
@@ -14887,7 +14899,7 @@
         <v>3.774439165379895</v>
       </c>
       <c r="D268" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E268">
         <v>3.837640654076098</v>
@@ -14937,7 +14949,7 @@
         <v>4.220199786446392</v>
       </c>
       <c r="D269" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E269">
         <v>4.085943565478028</v>
@@ -14973,7 +14985,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14987,7 +14999,7 @@
         <v>3.991103703583256</v>
       </c>
       <c r="D270" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E270">
         <v>4.0441357312043</v>
@@ -15023,7 +15035,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15037,7 +15049,7 @@
         <v>4.24807262091024</v>
       </c>
       <c r="D271" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E271">
         <v>4.172298835483293</v>
@@ -15073,7 +15085,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15087,7 +15099,7 @@
         <v>4.076733299050661</v>
       </c>
       <c r="D272" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E272">
         <v>4.185185728196767</v>
@@ -15123,7 +15135,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15187,7 +15199,7 @@
         <v>3.853669569225198</v>
       </c>
       <c r="D274" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E274">
         <v>3.960609701897911</v>
@@ -15323,7 +15335,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15337,7 +15349,7 @@
         <v>3.457860783201086</v>
       </c>
       <c r="D277" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E277">
         <v>3.562117466477025</v>
@@ -15373,7 +15385,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15387,7 +15399,7 @@
         <v>3.461796612382101</v>
       </c>
       <c r="D278" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E278">
         <v>3.45818163729601</v>
@@ -15423,7 +15435,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15487,7 +15499,7 @@
         <v>1.876063224574707</v>
       </c>
       <c r="D280" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E280">
         <v>1.926860456775207</v>
@@ -15537,7 +15549,7 @@
         <v>1.879462993924748</v>
       </c>
       <c r="D281" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E281">
         <v>1.926860456775207</v>
@@ -15587,7 +15599,7 @@
         <v>1.36286186891499</v>
       </c>
       <c r="D282" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E282">
         <v>1.420876924621103</v>
@@ -15623,7 +15635,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15637,7 +15649,7 @@
         <v>1.365396205962064</v>
       </c>
       <c r="D283" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E283">
         <v>1.420876924621103</v>
@@ -15673,7 +15685,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15687,7 +15699,7 @@
         <v>1.492587172538397</v>
       </c>
       <c r="D284" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E284">
         <v>1.422587172538397</v>
@@ -15723,7 +15735,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15737,7 +15749,7 @@
         <v>1.155028253713973</v>
       </c>
       <c r="D285" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E285">
         <v>1.207786135342488</v>
@@ -15787,7 +15799,7 @@
         <v>1.157212112489207</v>
       </c>
       <c r="D286" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E286">
         <v>1.207786135342488</v>
@@ -15837,7 +15849,7 @@
         <v>1.287557383512098</v>
       </c>
       <c r="D287" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E287">
         <v>1.260086513310223</v>
@@ -15887,7 +15899,7 @@
         <v>-0.2566084186298667</v>
       </c>
       <c r="D288" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E288">
         <v>-0.001048450451905936</v>
@@ -15923,7 +15935,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15937,7 +15949,7 @@
         <v>-0.2875710874180024</v>
       </c>
       <c r="D289" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E289">
         <v>-0.001048450451905936</v>
@@ -15973,7 +15985,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16023,7 +16035,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16073,7 +16085,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16087,7 +16099,7 @@
         <v>-0.3429456734762377</v>
       </c>
       <c r="D292" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E292">
         <v>-0.1559309932859021</v>
@@ -16123,7 +16135,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16137,7 +16149,7 @@
         <v>-0.452945673476238</v>
       </c>
       <c r="D293" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E293">
         <v>-0.1559309932859021</v>
@@ -16173,7 +16185,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16187,7 +16199,7 @@
         <v>-0.07614423041516449</v>
       </c>
       <c r="D294" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E294">
         <v>-0.08649962563060054</v>
@@ -16223,7 +16235,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16237,7 +16249,7 @@
         <v>-0.06685502084603723</v>
       </c>
       <c r="D295" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E295">
         <v>-0.08649962563060054</v>
@@ -16273,7 +16285,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16287,7 +16299,7 @@
         <v>-0.6325763258089658</v>
       </c>
       <c r="D296" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E296">
         <v>-0.7397037652284588</v>
@@ -16323,7 +16335,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16337,7 +16349,7 @@
         <v>-0.6888811406779016</v>
       </c>
       <c r="D297" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E297">
         <v>-0.6347573064746772</v>
@@ -16373,7 +16385,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16387,7 +16399,7 @@
         <v>-0.5922830059527424</v>
       </c>
       <c r="D298" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E298">
         <v>-0.6988811406779014</v>
@@ -16423,7 +16435,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16437,7 +16449,7 @@
         <v>-0.7708727781363214</v>
       </c>
       <c r="D299" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E299">
         <v>-0.7160845060282481</v>
@@ -16473,7 +16485,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16487,7 +16499,7 @@
         <v>-0.6732115427634033</v>
       </c>
       <c r="D300" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E300">
         <v>-0.7808727781363212</v>
@@ -16523,7 +16535,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16537,7 +16549,7 @@
         <v>-0.6051723879795468</v>
       </c>
       <c r="D301" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E301">
         <v>-0.5517269067155315</v>
@@ -16573,7 +16585,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16587,7 +16599,7 @@
         <v>-0.509659617957122</v>
       </c>
       <c r="D302" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E302">
         <v>-0.6151723879795465</v>
@@ -16623,7 +16635,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16637,7 +16649,7 @@
         <v>1.374867998585327</v>
       </c>
       <c r="D303" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E303">
         <v>1.61428021608427</v>
@@ -16673,7 +16685,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16687,7 +16699,7 @@
         <v>1.37455579980999</v>
       </c>
       <c r="D304" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E304">
         <v>1.61428021608427</v>
@@ -16723,7 +16735,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16737,7 +16749,7 @@
         <v>1.659046067002767</v>
       </c>
       <c r="D305" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E305">
         <v>1.701663141543517</v>
@@ -16773,7 +16785,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16787,7 +16799,7 @@
         <v>1.400425101402588</v>
       </c>
       <c r="D306" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E306">
         <v>1.63789275673065</v>
@@ -16823,7 +16835,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16837,7 +16849,7 @@
         <v>1.415426421593279</v>
       </c>
       <c r="D307" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E307">
         <v>1.63789275673065</v>
@@ -16873,7 +16885,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16887,7 +16899,7 @@
         <v>1.672891436539961</v>
       </c>
       <c r="D308" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E308">
         <v>1.702888796158578</v>
@@ -16923,7 +16935,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16937,7 +16949,7 @@
         <v>1.682896717302726</v>
       </c>
       <c r="D309" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E309">
         <v>1.702888796158578</v>
@@ -16973,7 +16985,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -16987,7 +16999,7 @@
         <v>1.392287936404873</v>
       </c>
       <c r="D310" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E310">
         <v>1.630374723852328</v>
@@ -17023,7 +17035,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17037,7 +17049,7 @@
         <v>1.392192134372636</v>
       </c>
       <c r="D311" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E311">
         <v>1.630374723852328</v>
@@ -17073,7 +17085,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17087,7 +17099,7 @@
         <v>1.665398674360388</v>
       </c>
       <c r="D312" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E312">
         <v>1.367982501138595</v>
@@ -17123,7 +17135,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17137,7 +17149,7 @@
         <v>1.67530287232815</v>
       </c>
       <c r="D313" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E313">
         <v>1.367982501138595</v>
@@ -17173,7 +17185,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17187,7 +17199,7 @@
         <v>1.683187064752997</v>
       </c>
       <c r="D314" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E314">
         <v>1.385560910531628</v>
@@ -17223,7 +17235,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17237,7 +17249,7 @@
         <v>1.693331241005988</v>
       </c>
       <c r="D315" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E315">
         <v>1.385560910531628</v>
@@ -17273,7 +17285,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17287,7 +17299,7 @@
         <v>1.671335210176903</v>
       </c>
       <c r="D316" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E316">
         <v>1.373848959803819</v>
@@ -17323,7 +17335,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17337,7 +17349,7 @@
         <v>1.68131949631757</v>
       </c>
       <c r="D317" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E317">
         <v>1.373848959803819</v>
@@ -17373,7 +17385,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17387,7 +17399,7 @@
         <v>1.693875753393727</v>
       </c>
       <c r="D318" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E318">
         <v>1.396123425781996</v>
@@ -17423,7 +17435,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17437,7 +17449,7 @@
         <v>1.704164127807133</v>
       </c>
       <c r="D319" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E319">
         <v>1.396123425781996</v>
@@ -17473,7 +17485,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17487,7 +17499,7 @@
         <v>1.366123425781996</v>
       </c>
       <c r="D320" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E320">
         <v>1.403731566187024</v>
@@ -17523,7 +17535,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17537,7 +17549,7 @@
         <v>1.710631890779994</v>
       </c>
       <c r="D321" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E321">
         <v>1.412681767280061</v>
@@ -17573,7 +17585,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17587,7 +17599,7 @@
         <v>1.72114631763706</v>
       </c>
       <c r="D322" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E322">
         <v>1.412681767280061</v>
@@ -17623,7 +17635,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17637,7 +17649,7 @@
         <v>1.382681767280062</v>
       </c>
       <c r="D323" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E323">
         <v>1.420374677351461</v>
@@ -17673,7 +17685,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17687,7 +17699,7 @@
         <v>1.679206240881443</v>
       </c>
       <c r="D324" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E324">
         <v>1.381627077835624</v>
@@ -17737,7 +17749,7 @@
         <v>1.689296712933807</v>
       </c>
       <c r="D325" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E325">
         <v>1.381627077835624</v>
@@ -17787,7 +17799,7 @@
         <v>1.351627077835625</v>
       </c>
       <c r="D326" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E326">
         <v>1.364138386842169</v>
@@ -17837,7 +17849,7 @@
         <v>1.662615013806636</v>
       </c>
       <c r="D327" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E327">
         <v>1.365231699984297</v>
@@ -17873,7 +17885,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17887,7 +17899,7 @@
         <v>1.672481658175022</v>
       </c>
       <c r="D328" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E328">
         <v>1.365231699984297</v>
@@ -17923,7 +17935,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17937,7 +17949,7 @@
         <v>1.335231699984297</v>
       </c>
       <c r="D329" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E329">
         <v>1.330198361076394</v>
@@ -17973,7 +17985,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17987,7 +17999,7 @@
         <v>1.638483426036899</v>
       </c>
       <c r="D330" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E330">
         <v>1.341384970754843</v>
@@ -18037,7 +18049,7 @@
         <v>1.648024517787818</v>
       </c>
       <c r="D331" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E331">
         <v>1.341384970754843</v>
@@ -18137,7 +18149,7 @@
         <v>1.611118158429232</v>
       </c>
       <c r="D333" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E333">
         <v>1.31434273328757</v>
@@ -18187,7 +18199,7 @@
         <v>1.620290072876844</v>
       </c>
       <c r="D334" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E334">
         <v>1.31434273328757</v>
@@ -18237,7 +18249,7 @@
         <v>1.210704115653037</v>
       </c>
       <c r="D335" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E335">
         <v>1.321946243981619</v>
@@ -18287,7 +18299,7 @@
         <v>1.250704115653037</v>
       </c>
       <c r="D336" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E336">
         <v>1.321946243981619</v>
@@ -18337,7 +18349,7 @@
         <v>1.580824889600507</v>
       </c>
       <c r="D337" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E337">
         <v>1.284407057851428</v>
@@ -18373,7 +18385,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18387,7 +18399,7 @@
         <v>1.589588125885168</v>
       </c>
       <c r="D338" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E338">
         <v>1.284407057851428</v>
@@ -18423,7 +18435,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18437,7 +18449,7 @@
         <v>1.180206507742837</v>
       </c>
       <c r="D339" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E339">
         <v>1.27675246238701</v>
@@ -18473,7 +18485,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18487,7 +18499,7 @@
         <v>1.220206507742837</v>
       </c>
       <c r="D340" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E340">
         <v>1.27675246238701</v>
@@ -18523,7 +18535,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18537,7 +18549,7 @@
         <v>1.680056540073359</v>
       </c>
       <c r="D341" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E341">
         <v>1.409353064352823</v>
@@ -18573,7 +18585,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18587,7 +18599,7 @@
         <v>1.717732409003494</v>
       </c>
       <c r="D342" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E342">
         <v>1.409353064352823</v>
@@ -18623,7 +18635,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18637,7 +18649,7 @@
         <v>1.307497917096648</v>
       </c>
       <c r="D343" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E343">
         <v>1.444235818399402</v>
@@ -18673,7 +18685,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18687,7 +18699,7 @@
         <v>1.347497917096648</v>
       </c>
       <c r="D344" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E344">
         <v>1.444235818399402</v>
@@ -18723,7 +18735,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18737,7 +18749,7 @@
         <v>1.842256392262994</v>
       </c>
       <c r="D345" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E345">
         <v>1.530769127897027</v>
@@ -18787,7 +18799,7 @@
         <v>1.431193121765403</v>
       </c>
       <c r="D346" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E346">
         <v>1.572471675023835</v>
@@ -18837,7 +18849,7 @@
         <v>1.471193121765403</v>
       </c>
       <c r="D347" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E347">
         <v>1.572471675023835</v>
@@ -18887,7 +18899,7 @@
         <v>2.306011000659936</v>
       </c>
       <c r="D348" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E348">
         <v>2.348379970519409</v>
@@ -18923,7 +18935,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18937,7 +18949,7 @@
         <v>2.400485390479259</v>
       </c>
       <c r="D349" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E349">
         <v>2.364696230398958</v>
@@ -18973,7 +18985,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19023,7 +19035,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19037,7 +19049,7 @@
         <v>2.315116384839492</v>
       </c>
       <c r="D351" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E351">
         <v>2.323814331699535</v>
@@ -19073,7 +19085,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19087,7 +19099,7 @@
         <v>2.158186337006185</v>
       </c>
       <c r="D352" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E352">
         <v>2.199105803820263</v>
@@ -19123,7 +19135,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19173,7 +19185,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19223,7 +19235,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19237,7 +19249,7 @@
         <v>2.249949180664442</v>
       </c>
       <c r="D355" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E355">
         <v>2.193589002935801</v>
@@ -19273,7 +19285,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19287,7 +19299,7 @@
         <v>3.29910210514231</v>
       </c>
       <c r="D356" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E356">
         <v>3.35230135785332</v>
@@ -19323,7 +19335,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19337,7 +19349,7 @@
         <v>3.804045197377832</v>
       </c>
       <c r="D357" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E357">
         <v>3.415154291605215</v>
@@ -19373,7 +19385,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19387,7 +19399,7 @@
         <v>3.427249571448392</v>
       </c>
       <c r="D358" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E358">
         <v>3.291626526785035</v>
@@ -19423,7 +19435,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19473,7 +19485,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19487,7 +19499,7 @@
         <v>3.442581197445604</v>
       </c>
       <c r="D360" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E360">
         <v>3.306414237004073</v>
@@ -19523,7 +19535,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19537,7 +19549,7 @@
         <v>3.36022431872702</v>
       </c>
       <c r="D361" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E361">
         <v>3.226979110080385</v>
@@ -19573,7 +19585,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19587,7 +19599,7 @@
         <v>3.251003700388559</v>
       </c>
       <c r="D362" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E362">
         <v>3.121633280862579</v>
@@ -19623,7 +19635,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19637,7 +19649,7 @@
         <v>2.99001278638902</v>
       </c>
       <c r="D363" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E363">
         <v>3.032275977245447</v>
@@ -19723,7 +19735,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19737,7 +19749,7 @@
         <v>2.786342722576059</v>
       </c>
       <c r="D365" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E365">
         <v>2.830017022419643</v>
@@ -19773,7 +19785,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19787,7 +19799,7 @@
         <v>2.881784622628198</v>
       </c>
       <c r="D366" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E366">
         <v>2.846342722576059</v>
@@ -19823,7 +19835,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19837,7 +19849,7 @@
         <v>2.713139299753176</v>
       </c>
       <c r="D367" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E367">
         <v>2.672915915531583</v>
@@ -19873,7 +19885,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19887,7 +19899,7 @@
         <v>2.722022378645214</v>
       </c>
       <c r="D368" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E368">
         <v>2.672915915531583</v>
@@ -19923,7 +19935,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19937,7 +19949,7 @@
         <v>2.643362683974768</v>
       </c>
       <c r="D369" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E369">
         <v>2.68802760764238</v>
@@ -19973,7 +19985,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19987,7 +19999,7 @@
         <v>2.738474376085565</v>
       </c>
       <c r="D370" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E370">
         <v>2.678250991863972</v>
@@ -20023,7 +20035,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20037,7 +20049,7 @@
         <v>2.26156876679942</v>
       </c>
       <c r="D371" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E371">
         <v>2.319500204055783</v>
@@ -20073,7 +20085,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20087,7 +20099,7 @@
         <v>2.341086491507057</v>
       </c>
       <c r="D372" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E372">
         <v>2.284741341701965</v>
@@ -20123,7 +20135,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20137,7 +20149,7 @@
         <v>2.25156876679942</v>
       </c>
       <c r="D373" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E373">
         <v>2.298948197976329</v>
@@ -20173,7 +20185,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20187,7 +20199,7 @@
         <v>2.345775623073784</v>
       </c>
       <c r="D374" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E374">
         <v>2.287361910525056</v>
@@ -20223,7 +20235,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20237,7 +20249,7 @@
         <v>1.450725995788351</v>
       </c>
       <c r="D375" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E375">
         <v>1.543612412630503</v>
@@ -20273,7 +20285,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20287,7 +20299,7 @@
         <v>1.378039753255653</v>
       </c>
       <c r="D376" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E376">
         <v>1.473954763536668</v>
@@ -20323,7 +20335,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20337,7 +20349,7 @@
         <v>2.300473418774809</v>
       </c>
       <c r="D377" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E377">
         <v>2.269274816103397</v>
@@ -20387,7 +20399,7 @@
         <v>2.307737312105645</v>
       </c>
       <c r="D378" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E378">
         <v>2.269274816103397</v>
@@ -20437,7 +20449,7 @@
         <v>2.548688372146674</v>
       </c>
       <c r="D379" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E379">
         <v>2.44021981851742</v>
@@ -20473,7 +20485,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20487,7 +20499,7 @@
         <v>4.064626779899114</v>
       </c>
       <c r="D380" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E380">
         <v>3.971827788774664</v>
@@ -20523,7 +20535,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20537,7 +20549,7 @@
         <v>2.704221825320051</v>
       </c>
       <c r="D381" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E381">
         <v>2.757514946748523</v>
@@ -20573,7 +20585,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20587,7 +20599,7 @@
         <v>2.699698304540886</v>
       </c>
       <c r="D382" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E382">
         <v>2.757514946748523</v>
@@ -20623,7 +20635,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20637,7 +20649,7 @@
         <v>2.597723564836138</v>
       </c>
       <c r="D383" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E383">
         <v>2.648687698460786</v>
@@ -20673,7 +20685,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20687,7 +20699,7 @@
         <v>2.594470401040876</v>
       </c>
       <c r="D384" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E384">
         <v>2.648687698460786</v>
@@ -20723,7 +20735,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20737,7 +20749,7 @@
         <v>2.5327482758737</v>
       </c>
       <c r="D385" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E385">
         <v>2.582291478725809</v>
@@ -20773,7 +20785,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20787,7 +20799,7 @@
         <v>2.530270165227095</v>
       </c>
       <c r="D386" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E386">
         <v>2.582291478725809</v>
@@ -20823,7 +20835,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20837,7 +20849,7 @@
         <v>2.615226386520305</v>
       </c>
       <c r="D387" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E387">
         <v>2.605226386520305</v>
@@ -20873,7 +20885,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20887,7 +20899,7 @@
         <v>2.519210324106</v>
       </c>
       <c r="D388" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E388">
         <v>2.474919909368535</v>
@@ -20923,7 +20935,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20937,7 +20949,7 @@
         <v>2.443973795685154</v>
       </c>
       <c r="D389" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E389">
         <v>2.491575608314453</v>
@@ -20973,7 +20985,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20987,7 +20999,7 @@
         <v>2.442554625160083</v>
       </c>
       <c r="D390" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E390">
         <v>2.491575608314453</v>
@@ -21023,7 +21035,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21073,7 +21085,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21087,7 +21099,7 @@
         <v>2.457705873063223</v>
       </c>
       <c r="D392" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E392">
         <v>2.413049360402885</v>
@@ -21123,7 +21135,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21137,7 +21149,7 @@
         <v>2.382591377283335</v>
       </c>
       <c r="D393" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E393">
         <v>2.428850830862097</v>
@@ -21173,7 +21185,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21187,7 +21199,7 @@
         <v>2.381904402604011</v>
       </c>
       <c r="D394" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E394">
         <v>2.428850830862097</v>
@@ -21223,7 +21235,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21237,7 +21249,7 @@
         <v>2.46327835196266</v>
       </c>
       <c r="D395" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E395">
         <v>2.453507343522435</v>
@@ -21273,7 +21285,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21287,7 +21299,7 @@
         <v>2.467705873063223</v>
       </c>
       <c r="D396" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E396">
         <v>2.453507343522435</v>
@@ -21323,7 +21335,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21337,7 +21349,7 @@
         <v>2.447999298642713</v>
       </c>
       <c r="D397" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E397">
         <v>2.403285008753682</v>
@@ -21373,7 +21385,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21387,7 +21399,7 @@
         <v>2.372904061939057</v>
       </c>
       <c r="D398" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E398">
         <v>2.418951665679276</v>
@@ -21423,7 +21435,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21437,7 +21449,7 @@
         <v>2.37233264171712</v>
       </c>
       <c r="D399" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E399">
         <v>2.418951665679276</v>
@@ -21473,7 +21485,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21523,7 +21535,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21573,7 +21585,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21587,7 +21599,7 @@
         <v>2.414261420787727</v>
       </c>
       <c r="D402" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E402">
         <v>2.369346310197177</v>
@@ -21623,7 +21635,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21673,7 +21685,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21723,7 +21735,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21737,7 +21749,7 @@
         <v>2.424261420787727</v>
       </c>
       <c r="D405" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E405">
         <v>2.394544385485897</v>
@@ -21773,7 +21785,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21787,7 +21799,7 @@
         <v>2.414374606666995</v>
       </c>
       <c r="D406" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E406">
         <v>2.394544385485897</v>
@@ -21823,7 +21835,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21837,7 +21849,7 @@
         <v>2.397600622679596</v>
       </c>
       <c r="D407" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E407">
         <v>2.352586340671736</v>
@@ -21873,7 +21885,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21887,7 +21899,7 @@
         <v>2.322605383348882</v>
       </c>
       <c r="D408" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E408">
         <v>2.367553015986731</v>
@@ -21923,7 +21935,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21937,7 +21949,7 @@
         <v>2.322633947364601</v>
       </c>
       <c r="D409" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E409">
         <v>2.367553015986731</v>
@@ -21973,7 +21985,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -21987,7 +21999,7 @@
         <v>2.402576819333163</v>
       </c>
       <c r="D410" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E410">
         <v>2.35256729799459</v>
@@ -22023,7 +22035,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22037,7 +22049,7 @@
         <v>2.407600622679595</v>
       </c>
       <c r="D411" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E411">
         <v>2.35256729799459</v>
@@ -22073,7 +22085,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22087,7 +22099,7 @@
         <v>2.39758158000245</v>
       </c>
       <c r="D412" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E412">
         <v>2.35256729799459</v>
@@ -22123,7 +22135,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22137,7 +22149,7 @@
         <v>2.378737718650321</v>
       </c>
       <c r="D413" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E413">
         <v>2.33361115745181</v>
@@ -22173,7 +22185,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22187,7 +22199,7 @@
         <v>2.30377990571649</v>
       </c>
       <c r="D414" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E414">
         <v>2.348315847988621</v>
@@ -22223,7 +22235,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22237,7 +22249,7 @@
         <v>2.304033028113511</v>
       </c>
       <c r="D415" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E415">
         <v>2.348315847988621</v>
@@ -22273,7 +22285,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22287,7 +22299,7 @@
         <v>2.383526783319471</v>
       </c>
       <c r="D416" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E416">
         <v>2.333442409187131</v>
@@ -22323,7 +22335,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22337,7 +22349,7 @@
         <v>2.38873771865032</v>
       </c>
       <c r="D417" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E417">
         <v>2.333442409187131</v>
@@ -22373,7 +22385,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22387,7 +22399,7 @@
         <v>2.378568970385641</v>
       </c>
       <c r="D418" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E418">
         <v>2.333442409187131</v>
@@ -22423,7 +22435,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22437,7 +22449,7 @@
         <v>2.29477967980894</v>
       </c>
       <c r="D419" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E419">
         <v>2.33911879805526</v>
@@ -22487,7 +22499,7 @@
         <v>2.295140160765494</v>
       </c>
       <c r="D420" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E420">
         <v>2.33911879805526</v>
@@ -22537,7 +22549,7 @@
         <v>2.374419198852388</v>
       </c>
       <c r="D421" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E421">
         <v>2.324299038533536</v>
@@ -22587,7 +22599,7 @@
         <v>2.379719599649515</v>
       </c>
       <c r="D422" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E422">
         <v>2.324299038533536</v>
@@ -22637,7 +22649,7 @@
         <v>2.369479279011813</v>
       </c>
       <c r="D423" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E423">
         <v>2.324299038533536</v>
@@ -22687,7 +22699,7 @@
         <v>2.280590400920047</v>
       </c>
       <c r="D424" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E424">
         <v>2.324619216844741</v>
@@ -22723,7 +22735,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22737,7 +22749,7 @@
         <v>2.281120137688396</v>
       </c>
       <c r="D425" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E425">
         <v>2.324619216844741</v>
@@ -22773,7 +22785,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22787,7 +22799,7 @@
         <v>2.360060664151698</v>
       </c>
       <c r="D426" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E426">
         <v>2.309884085228915</v>
@@ -22823,7 +22835,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22873,7 +22885,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22887,7 +22899,7 @@
         <v>2.281700069738552</v>
       </c>
       <c r="D428" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E428">
         <v>2.325753152774585</v>
@@ -22923,7 +22935,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -22937,7 +22949,7 @@
         <v>2.282216569900716</v>
       </c>
       <c r="D429" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E429">
         <v>2.325753152774585</v>
@@ -22973,7 +22985,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -22987,7 +22999,7 @@
         <v>2.361183569576388</v>
       </c>
       <c r="D430" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E430">
         <v>2.311011402855666</v>
@@ -23023,7 +23035,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23037,7 +23049,7 @@
         <v>2.255753152774584</v>
       </c>
       <c r="D431" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E431">
         <v>2.30032273597278</v>
@@ -23073,7 +23085,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23087,7 +23099,7 @@
         <v>2.248769782041177</v>
       </c>
       <c r="D432" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E432">
         <v>2.297801715354081</v>
@@ -23123,7 +23135,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23137,7 +23149,7 @@
         <v>2.343406757033516</v>
       </c>
       <c r="D433" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E433">
         <v>2.293164740361742</v>
@@ -23173,7 +23185,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23187,7 +23199,7 @@
         <v>2.237801715354081</v>
       </c>
       <c r="D434" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E434">
         <v>2.26243869034642</v>
@@ -23223,7 +23235,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23237,7 +23249,7 @@
         <v>2.228095614122554</v>
       </c>
       <c r="D435" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E435">
         <v>2.276800683120539</v>
@@ -23273,7 +23285,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23287,7 +23299,7 @@
         <v>2.322610014996799</v>
       </c>
       <c r="D436" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E436">
         <v>2.263257480497806</v>
@@ -23323,7 +23335,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23373,7 +23385,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23387,7 +23399,7 @@
         <v>2.224983216186275</v>
       </c>
       <c r="D438" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E438">
         <v>2.273639077311749</v>
@@ -23437,7 +23449,7 @@
         <v>2.319479164108328</v>
       </c>
       <c r="D439" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E439">
         <v>2.26015123354559</v>
@@ -23587,7 +23599,7 @@
         <v>2.3116287572162</v>
       </c>
       <c r="D442" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E442">
         <v>2.252362519438469</v>
@@ -23623,7 +23635,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23673,7 +23685,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23723,7 +23735,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23787,7 +23799,7 @@
         <v>2.185149484739352</v>
       </c>
       <c r="D446" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E446">
         <v>2.165149484739352</v>
@@ -23887,7 +23899,7 @@
         <v>2.20020073233055</v>
       </c>
       <c r="D448" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E448">
         <v>2.205687152603988</v>
@@ -23973,7 +23985,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24023,7 +24035,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24073,7 +24085,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24123,7 +24135,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24173,7 +24185,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24287,7 +24299,7 @@
         <v>2.142114930387524</v>
       </c>
       <c r="D456" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E456">
         <v>2.162114930387524</v>
@@ -24323,7 +24335,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24337,7 +24349,7 @@
         <v>2.115413806995409</v>
       </c>
       <c r="D457" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E457">
         <v>2.141244762127619</v>
@@ -24423,7 +24435,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24437,7 +24449,7 @@
         <v>2.073994682974101</v>
       </c>
       <c r="D459" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E459">
         <v>2.082201671198685</v>
@@ -24487,7 +24499,7 @@
         <v>2.083994682974101</v>
       </c>
       <c r="D460" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E460">
         <v>2.082201671198685</v>
@@ -24573,7 +24585,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24587,7 +24599,7 @@
         <v>2.057461365020192</v>
       </c>
       <c r="D462" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E462">
         <v>2.066125824243982</v>
@@ -24623,7 +24635,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24673,7 +24685,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24723,7 +24735,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24773,7 +24785,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24823,7 +24835,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24837,7 +24849,7 @@
         <v>2.057577737614682</v>
       </c>
       <c r="D467" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E467">
         <v>2.099815205781953</v>
@@ -24873,7 +24885,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24937,7 +24949,7 @@
         <v>2.075267052489131</v>
       </c>
       <c r="D469" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E469">
         <v>2.105974841560053</v>
@@ -24987,7 +24999,7 @@
         <v>2.0673904197019</v>
       </c>
       <c r="D470" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E470">
         <v>2.109513786914668</v>
@@ -25037,7 +25049,7 @@
         <v>2.101281730695467</v>
       </c>
       <c r="D471" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E471">
         <v>2.131889846669813</v>
@@ -25087,7 +25099,7 @@
         <v>2.093106078618507</v>
       </c>
       <c r="D472" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E472">
         <v>2.134930426541548</v>
@@ -25137,7 +25149,7 @@
         <v>2.114232378900782</v>
       </c>
       <c r="D473" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E473">
         <v>2.144790875533345</v>
@@ -25173,7 +25185,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25187,7 +25199,7 @@
         <v>2.164790875533345</v>
       </c>
       <c r="D474" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E474">
         <v>2.134232378900781</v>
@@ -25223,7 +25235,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25237,7 +25249,7 @@
         <v>2.105907868798473</v>
       </c>
       <c r="D475" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E475">
         <v>2.147583358696166</v>
@@ -25273,7 +25285,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25287,7 +25299,7 @@
         <v>2.178667208693582</v>
       </c>
       <c r="D476" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E476">
         <v>2.148162082573172</v>
@@ -25323,7 +25335,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25337,7 +25349,7 @@
         <v>2.119677460934401</v>
       </c>
       <c r="D477" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E477">
         <v>2.161192839295628</v>
@@ -25373,7 +25385,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25387,7 +25399,7 @@
         <v>2.191253934723685</v>
       </c>
       <c r="D478" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E478">
         <v>2.160797219088007</v>
@@ -25437,7 +25449,7 @@
         <v>2.132167365995042</v>
       </c>
       <c r="D479" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E479">
         <v>2.173537512902076</v>
@@ -25537,7 +25549,7 @@
         <v>2.161339958759847</v>
       </c>
       <c r="D481" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E481">
         <v>2.202370889471942</v>
@@ -25587,7 +25599,7 @@
         <v>2.215480849833102</v>
       </c>
       <c r="D482" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E482">
         <v>2.179965384477054</v>
@@ -25637,7 +25649,7 @@
         <v>1.276065947508897</v>
       </c>
       <c r="D483" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E483">
         <v>1.317566169928825</v>
@@ -25673,57 +25685,57 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="484" spans="1:16">
       <c r="A484" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B484" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C484">
-        <v>1.265250934212467</v>
+        <v>1.37689891014235</v>
       </c>
       <c r="D484" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E484">
-        <v>1.306889515011455</v>
+        <v>1.288399132562277</v>
       </c>
       <c r="F484">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G484">
-        <v>0.007774749065787532</v>
+        <v>0.008003101089857651</v>
       </c>
       <c r="H484">
-        <v>0.007733110484988545</v>
+        <v>0.007831600867437722</v>
       </c>
       <c r="I484">
-        <v>0.04163858079898786</v>
+        <v>0.08849977758007244</v>
       </c>
       <c r="J484">
-        <v>0.6939763466497937</v>
+        <v>0.6916703736654803</v>
       </c>
       <c r="K484">
+        <v>4.79</v>
+      </c>
+      <c r="L484">
         <v>4.69</v>
       </c>
-      <c r="L484">
-        <v>4.52</v>
-      </c>
       <c r="M484">
-        <v>4.63</v>
+        <v>4.73</v>
       </c>
       <c r="N484">
-        <v>4.52</v>
+        <v>4.56</v>
       </c>
       <c r="O484">
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25734,28 +25746,28 @@
         <v>146</v>
       </c>
       <c r="C485">
-        <v>1.257848770795328</v>
+        <v>1.265250934212467</v>
       </c>
       <c r="D485" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E485">
-        <v>1.28958204878089</v>
+        <v>1.296889515011455</v>
       </c>
       <c r="F485">
         <v>1</v>
       </c>
       <c r="G485">
-        <v>0.007782151229204671</v>
+        <v>0.007774749065787532</v>
       </c>
       <c r="H485">
-        <v>0.00773041795121911</v>
+        <v>0.007723110484988545</v>
       </c>
       <c r="I485">
-        <v>0.03173327798556169</v>
+        <v>0.03163858079898807</v>
       </c>
       <c r="J485">
-        <v>0.6955546330926804</v>
+        <v>0.6939763466497937</v>
       </c>
       <c r="K485">
         <v>4.69</v>
@@ -25773,7 +25785,307 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>384</v>
+        <v>385</v>
+      </c>
+    </row>
+    <row r="486" spans="1:16">
+      <c r="A486" s="1">
+        <v>1</v>
+      </c>
+      <c r="B486" t="s">
+        <v>147</v>
+      </c>
+      <c r="C486">
+        <v>1.365853299547489</v>
+      </c>
+      <c r="D486" t="s">
+        <v>270</v>
+      </c>
+      <c r="E486">
+        <v>1.277491880346475</v>
+      </c>
+      <c r="F486">
+        <v>-1</v>
+      </c>
+      <c r="G486">
+        <v>0.008014146700452512</v>
+      </c>
+      <c r="H486">
+        <v>0.007842508119653525</v>
+      </c>
+      <c r="I486">
+        <v>0.08836141920101337</v>
+      </c>
+      <c r="J486">
+        <v>0.6939763466497937</v>
+      </c>
+      <c r="K486">
+        <v>4.79</v>
+      </c>
+      <c r="L486">
+        <v>4.69</v>
+      </c>
+      <c r="M486">
+        <v>4.73</v>
+      </c>
+      <c r="N486">
+        <v>4.56</v>
+      </c>
+      <c r="O486">
+        <v>1</v>
+      </c>
+      <c r="P486" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="487" spans="1:16">
+      <c r="A487" s="1">
+        <v>0</v>
+      </c>
+      <c r="B487" t="s">
+        <v>146</v>
+      </c>
+      <c r="C487">
+        <v>1.257848770795328</v>
+      </c>
+      <c r="D487" t="s">
+        <v>271</v>
+      </c>
+      <c r="E487">
+        <v>1.28958204878089</v>
+      </c>
+      <c r="F487">
+        <v>1</v>
+      </c>
+      <c r="G487">
+        <v>0.007782151229204671</v>
+      </c>
+      <c r="H487">
+        <v>0.00773041795121911</v>
+      </c>
+      <c r="I487">
+        <v>0.03173327798556169</v>
+      </c>
+      <c r="J487">
+        <v>0.6955546330926804</v>
+      </c>
+      <c r="K487">
+        <v>4.69</v>
+      </c>
+      <c r="L487">
+        <v>4.52</v>
+      </c>
+      <c r="M487">
+        <v>4.63</v>
+      </c>
+      <c r="N487">
+        <v>4.51</v>
+      </c>
+      <c r="O487">
+        <v>1</v>
+      </c>
+      <c r="P487" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="488" spans="1:16">
+      <c r="A488" s="1">
+        <v>1</v>
+      </c>
+      <c r="B488" t="s">
+        <v>147</v>
+      </c>
+      <c r="C488">
+        <v>1.358293307486061</v>
+      </c>
+      <c r="D488" t="s">
+        <v>270</v>
+      </c>
+      <c r="E488">
+        <v>1.270026585471621</v>
+      </c>
+      <c r="F488">
+        <v>-1</v>
+      </c>
+      <c r="G488">
+        <v>0.00802170669251394</v>
+      </c>
+      <c r="H488">
+        <v>0.007849973414528378</v>
+      </c>
+      <c r="I488">
+        <v>0.08826672201444019</v>
+      </c>
+      <c r="J488">
+        <v>0.6955546330926804</v>
+      </c>
+      <c r="K488">
+        <v>4.79</v>
+      </c>
+      <c r="L488">
+        <v>4.69</v>
+      </c>
+      <c r="M488">
+        <v>4.73</v>
+      </c>
+      <c r="N488">
+        <v>4.56</v>
+      </c>
+      <c r="O488">
+        <v>1</v>
+      </c>
+      <c r="P488" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="489" spans="1:16">
+      <c r="A489" s="1">
+        <v>0</v>
+      </c>
+      <c r="B489" t="s">
+        <v>147</v>
+      </c>
+      <c r="C489">
+        <v>1.336383675279734</v>
+      </c>
+      <c r="D489" t="s">
+        <v>270</v>
+      </c>
+      <c r="E489">
+        <v>1.248391395422367</v>
+      </c>
+      <c r="F489">
+        <v>-1</v>
+      </c>
+      <c r="G489">
+        <v>0.008043616324720266</v>
+      </c>
+      <c r="H489">
+        <v>0.007871608604577633</v>
+      </c>
+      <c r="I489">
+        <v>0.08799227985736735</v>
+      </c>
+      <c r="J489">
+        <v>0.7001286690438969</v>
+      </c>
+      <c r="K489">
+        <v>4.79</v>
+      </c>
+      <c r="L489">
+        <v>4.69</v>
+      </c>
+      <c r="M489">
+        <v>4.73</v>
+      </c>
+      <c r="N489">
+        <v>4.56</v>
+      </c>
+      <c r="O489">
+        <v>1</v>
+      </c>
+      <c r="P489" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="490" spans="1:16">
+      <c r="A490" s="1">
+        <v>0</v>
+      </c>
+      <c r="B490" t="s">
+        <v>147</v>
+      </c>
+      <c r="C490">
+        <v>1.279467032224208</v>
+      </c>
+      <c r="D490" t="s">
+        <v>270</v>
+      </c>
+      <c r="E490">
+        <v>1.192187695703653</v>
+      </c>
+      <c r="F490">
+        <v>-1</v>
+      </c>
+      <c r="G490">
+        <v>0.008100532967775794</v>
+      </c>
+      <c r="H490">
+        <v>0.007927812304296346</v>
+      </c>
+      <c r="I490">
+        <v>0.08727933652055464</v>
+      </c>
+      <c r="J490">
+        <v>0.7120110579907708</v>
+      </c>
+      <c r="K490">
+        <v>4.79</v>
+      </c>
+      <c r="L490">
+        <v>4.69</v>
+      </c>
+      <c r="M490">
+        <v>4.73</v>
+      </c>
+      <c r="N490">
+        <v>4.56</v>
+      </c>
+      <c r="O490">
+        <v>1</v>
+      </c>
+      <c r="P490" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="491" spans="1:16">
+      <c r="A491" s="1">
+        <v>0</v>
+      </c>
+      <c r="B491" t="s">
+        <v>147</v>
+      </c>
+      <c r="C491">
+        <v>1.24514956586386</v>
+      </c>
+      <c r="D491" t="s">
+        <v>270</v>
+      </c>
+      <c r="E491">
+        <v>1.158300093222558</v>
+      </c>
+      <c r="F491">
+        <v>-1</v>
+      </c>
+      <c r="G491">
+        <v>0.008134850434136141</v>
+      </c>
+      <c r="H491">
+        <v>0.007961699906777442</v>
+      </c>
+      <c r="I491">
+        <v>0.08684947264130205</v>
+      </c>
+      <c r="J491">
+        <v>0.7191754559783174</v>
+      </c>
+      <c r="K491">
+        <v>4.79</v>
+      </c>
+      <c r="L491">
+        <v>4.69</v>
+      </c>
+      <c r="M491">
+        <v>4.73</v>
+      </c>
+      <c r="N491">
+        <v>4.56</v>
+      </c>
+      <c r="O491">
+        <v>1</v>
+      </c>
+      <c r="P491" t="s">
+        <v>388</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-03328-601328.xlsx
+++ b/s60_signal/position-03328-601328.xlsx
@@ -25790,96 +25790,96 @@
     </row>
     <row r="486" spans="1:16">
       <c r="A486" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B486" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C486">
-        <v>1.365853299547489</v>
+        <v>1.257848770795328</v>
       </c>
       <c r="D486" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E486">
-        <v>1.277491880346475</v>
+        <v>1.28958204878089</v>
       </c>
       <c r="F486">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G486">
-        <v>0.008014146700452512</v>
+        <v>0.007782151229204671</v>
       </c>
       <c r="H486">
-        <v>0.007842508119653525</v>
+        <v>0.00773041795121911</v>
       </c>
       <c r="I486">
-        <v>0.08836141920101337</v>
+        <v>0.03173327798556169</v>
       </c>
       <c r="J486">
-        <v>0.6939763466497937</v>
+        <v>0.6955546330926804</v>
       </c>
       <c r="K486">
-        <v>4.79</v>
+        <v>4.69</v>
       </c>
       <c r="L486">
-        <v>4.69</v>
+        <v>4.52</v>
       </c>
       <c r="M486">
-        <v>4.73</v>
+        <v>4.63</v>
       </c>
       <c r="N486">
-        <v>4.56</v>
+        <v>4.51</v>
       </c>
       <c r="O486">
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="487" spans="1:16">
       <c r="A487" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B487" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C487">
-        <v>1.257848770795328</v>
+        <v>1.358293307486061</v>
       </c>
       <c r="D487" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E487">
-        <v>1.28958204878089</v>
+        <v>1.270026585471621</v>
       </c>
       <c r="F487">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G487">
-        <v>0.007782151229204671</v>
+        <v>0.00802170669251394</v>
       </c>
       <c r="H487">
-        <v>0.00773041795121911</v>
+        <v>0.007849973414528378</v>
       </c>
       <c r="I487">
-        <v>0.03173327798556169</v>
+        <v>0.08826672201444019</v>
       </c>
       <c r="J487">
         <v>0.6955546330926804</v>
       </c>
       <c r="K487">
+        <v>4.79</v>
+      </c>
+      <c r="L487">
         <v>4.69</v>
       </c>
-      <c r="L487">
-        <v>4.52</v>
-      </c>
       <c r="M487">
-        <v>4.63</v>
+        <v>4.73</v>
       </c>
       <c r="N487">
-        <v>4.51</v>
+        <v>4.56</v>
       </c>
       <c r="O487">
         <v>1</v>
@@ -25890,34 +25890,34 @@
     </row>
     <row r="488" spans="1:16">
       <c r="A488" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B488" t="s">
         <v>147</v>
       </c>
       <c r="C488">
-        <v>1.358293307486061</v>
+        <v>1.336383675279734</v>
       </c>
       <c r="D488" t="s">
         <v>270</v>
       </c>
       <c r="E488">
-        <v>1.270026585471621</v>
+        <v>1.248391395422367</v>
       </c>
       <c r="F488">
         <v>-1</v>
       </c>
       <c r="G488">
-        <v>0.00802170669251394</v>
+        <v>0.008043616324720266</v>
       </c>
       <c r="H488">
-        <v>0.007849973414528378</v>
+        <v>0.007871608604577633</v>
       </c>
       <c r="I488">
-        <v>0.08826672201444019</v>
+        <v>0.08799227985736735</v>
       </c>
       <c r="J488">
-        <v>0.6955546330926804</v>
+        <v>0.7001286690438969</v>
       </c>
       <c r="K488">
         <v>4.79</v>
@@ -25935,7 +25935,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>386</v>
+        <v>146</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25946,28 +25946,28 @@
         <v>147</v>
       </c>
       <c r="C489">
-        <v>1.336383675279734</v>
+        <v>1.279467032224208</v>
       </c>
       <c r="D489" t="s">
         <v>270</v>
       </c>
       <c r="E489">
-        <v>1.248391395422367</v>
+        <v>1.192187695703653</v>
       </c>
       <c r="F489">
         <v>-1</v>
       </c>
       <c r="G489">
-        <v>0.008043616324720266</v>
+        <v>0.008100532967775794</v>
       </c>
       <c r="H489">
-        <v>0.007871608604577633</v>
+        <v>0.007927812304296346</v>
       </c>
       <c r="I489">
-        <v>0.08799227985736735</v>
+        <v>0.08727933652055464</v>
       </c>
       <c r="J489">
-        <v>0.7001286690438969</v>
+        <v>0.7120110579907708</v>
       </c>
       <c r="K489">
         <v>4.79</v>
@@ -25985,7 +25985,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>146</v>
+        <v>387</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -25996,28 +25996,28 @@
         <v>147</v>
       </c>
       <c r="C490">
-        <v>1.279467032224208</v>
+        <v>1.24514956586386</v>
       </c>
       <c r="D490" t="s">
         <v>270</v>
       </c>
       <c r="E490">
-        <v>1.192187695703653</v>
+        <v>1.158300093222558</v>
       </c>
       <c r="F490">
         <v>-1</v>
       </c>
       <c r="G490">
-        <v>0.008100532967775794</v>
+        <v>0.008134850434136141</v>
       </c>
       <c r="H490">
-        <v>0.007927812304296346</v>
+        <v>0.007961699906777442</v>
       </c>
       <c r="I490">
-        <v>0.08727933652055464</v>
+        <v>0.08684947264130205</v>
       </c>
       <c r="J490">
-        <v>0.7120110579907708</v>
+        <v>0.7191754559783174</v>
       </c>
       <c r="K490">
         <v>4.79</v>
@@ -26035,7 +26035,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26046,28 +26046,28 @@
         <v>147</v>
       </c>
       <c r="C491">
-        <v>1.24514956586386</v>
+        <v>1.226637749198502</v>
       </c>
       <c r="D491" t="s">
         <v>270</v>
       </c>
       <c r="E491">
-        <v>1.158300093222558</v>
+        <v>1.140020157350503</v>
       </c>
       <c r="F491">
         <v>-1</v>
       </c>
       <c r="G491">
-        <v>0.008134850434136141</v>
+        <v>0.008153362250801498</v>
       </c>
       <c r="H491">
-        <v>0.007961699906777442</v>
+        <v>0.007979979842649497</v>
       </c>
       <c r="I491">
-        <v>0.08684947264130205</v>
+        <v>0.086617591847999</v>
       </c>
       <c r="J491">
-        <v>0.7191754559783174</v>
+        <v>0.7230401358667011</v>
       </c>
       <c r="K491">
         <v>4.79</v>
@@ -26085,7 +26085,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>388</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-03328-601328.xlsx
+++ b/s60_signal/position-03328-601328.xlsx
@@ -25840,34 +25840,34 @@
     </row>
     <row r="487" spans="1:16">
       <c r="A487" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B487" t="s">
         <v>147</v>
       </c>
       <c r="C487">
-        <v>1.358293307486061</v>
+        <v>1.336383675279734</v>
       </c>
       <c r="D487" t="s">
         <v>270</v>
       </c>
       <c r="E487">
-        <v>1.270026585471621</v>
+        <v>1.248391395422367</v>
       </c>
       <c r="F487">
         <v>-1</v>
       </c>
       <c r="G487">
-        <v>0.00802170669251394</v>
+        <v>0.008043616324720266</v>
       </c>
       <c r="H487">
-        <v>0.007849973414528378</v>
+        <v>0.007871608604577633</v>
       </c>
       <c r="I487">
-        <v>0.08826672201444019</v>
+        <v>0.08799227985736735</v>
       </c>
       <c r="J487">
-        <v>0.6955546330926804</v>
+        <v>0.7001286690438969</v>
       </c>
       <c r="K487">
         <v>4.79</v>
@@ -25885,7 +25885,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>386</v>
+        <v>146</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25896,28 +25896,28 @@
         <v>147</v>
       </c>
       <c r="C488">
-        <v>1.336383675279734</v>
+        <v>1.279467032224208</v>
       </c>
       <c r="D488" t="s">
         <v>270</v>
       </c>
       <c r="E488">
-        <v>1.248391395422367</v>
+        <v>1.192187695703653</v>
       </c>
       <c r="F488">
         <v>-1</v>
       </c>
       <c r="G488">
-        <v>0.008043616324720266</v>
+        <v>0.008100532967775794</v>
       </c>
       <c r="H488">
-        <v>0.007871608604577633</v>
+        <v>0.007927812304296346</v>
       </c>
       <c r="I488">
-        <v>0.08799227985736735</v>
+        <v>0.08727933652055464</v>
       </c>
       <c r="J488">
-        <v>0.7001286690438969</v>
+        <v>0.7120110579907708</v>
       </c>
       <c r="K488">
         <v>4.79</v>
@@ -25935,7 +25935,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>146</v>
+        <v>387</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25946,28 +25946,28 @@
         <v>147</v>
       </c>
       <c r="C489">
-        <v>1.279467032224208</v>
+        <v>1.24514956586386</v>
       </c>
       <c r="D489" t="s">
         <v>270</v>
       </c>
       <c r="E489">
-        <v>1.192187695703653</v>
+        <v>1.158300093222558</v>
       </c>
       <c r="F489">
         <v>-1</v>
       </c>
       <c r="G489">
-        <v>0.008100532967775794</v>
+        <v>0.008134850434136141</v>
       </c>
       <c r="H489">
-        <v>0.007927812304296346</v>
+        <v>0.007961699906777442</v>
       </c>
       <c r="I489">
-        <v>0.08727933652055464</v>
+        <v>0.08684947264130205</v>
       </c>
       <c r="J489">
-        <v>0.7120110579907708</v>
+        <v>0.7191754559783174</v>
       </c>
       <c r="K489">
         <v>4.79</v>
@@ -25985,7 +25985,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -25996,28 +25996,28 @@
         <v>147</v>
       </c>
       <c r="C490">
-        <v>1.24514956586386</v>
+        <v>1.226637749198502</v>
       </c>
       <c r="D490" t="s">
         <v>270</v>
       </c>
       <c r="E490">
-        <v>1.158300093222558</v>
+        <v>1.140020157350503</v>
       </c>
       <c r="F490">
         <v>-1</v>
       </c>
       <c r="G490">
-        <v>0.008134850434136141</v>
+        <v>0.008153362250801498</v>
       </c>
       <c r="H490">
-        <v>0.007961699906777442</v>
+        <v>0.007979979842649497</v>
       </c>
       <c r="I490">
-        <v>0.08684947264130205</v>
+        <v>0.086617591847999</v>
       </c>
       <c r="J490">
-        <v>0.7191754559783174</v>
+        <v>0.7230401358667011</v>
       </c>
       <c r="K490">
         <v>4.79</v>
@@ -26035,7 +26035,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>388</v>
+        <v>271</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26046,28 +26046,28 @@
         <v>147</v>
       </c>
       <c r="C491">
-        <v>1.226637749198502</v>
+        <v>1.183891513054156</v>
       </c>
       <c r="D491" t="s">
         <v>270</v>
       </c>
       <c r="E491">
-        <v>1.140020157350503</v>
+        <v>1.097809364665167</v>
       </c>
       <c r="F491">
         <v>-1</v>
       </c>
       <c r="G491">
-        <v>0.008153362250801498</v>
+        <v>0.008196108486945847</v>
       </c>
       <c r="H491">
-        <v>0.007979979842649497</v>
+        <v>0.008022190635334832</v>
       </c>
       <c r="I491">
-        <v>0.086617591847999</v>
+        <v>0.08608214838898842</v>
       </c>
       <c r="J491">
-        <v>0.7230401358667011</v>
+        <v>0.7319641935168778</v>
       </c>
       <c r="K491">
         <v>4.79</v>
@@ -26085,7 +26085,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-03328-601328.xlsx
+++ b/s60_signal/position-03328-601328.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="388">
   <si>
     <t>trade_time</t>
   </si>
@@ -460,6 +460,9 @@
     <t>2021-11-01</t>
   </si>
   <si>
+    <t>2021-11-05</t>
+  </si>
+  <si>
     <t>2016-05-31</t>
   </si>
   <si>
@@ -829,7 +832,7 @@
     <t>2021-11-02</t>
   </si>
   <si>
-    <t>2021-10-28</t>
+    <t>2021-11-08</t>
   </si>
   <si>
     <t>2016-05-24</t>
@@ -1175,12 +1178,6 @@
   </si>
   <si>
     <t>2021-10-19</t>
-  </si>
-  <si>
-    <t>2021-10-26</t>
-  </si>
-  <si>
-    <t>2021-10-27</t>
   </si>
 </sst>
 </file>
@@ -1538,7 +1535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P491"/>
+  <dimension ref="A1:P493"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1599,7 +1596,7 @@
         <v>2.636521639996683</v>
       </c>
       <c r="D2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E2">
         <v>2.833647241107702</v>
@@ -1635,7 +1632,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1649,7 +1646,7 @@
         <v>2.808801457176021</v>
       </c>
       <c r="D3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E3">
         <v>2.7135041663212</v>
@@ -1685,7 +1682,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1699,7 +1696,7 @@
         <v>2.746397091058633</v>
       </c>
       <c r="D4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E4">
         <v>2.648930323263125</v>
@@ -1749,7 +1746,7 @@
         <v>2.683209227271539</v>
       </c>
       <c r="D5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E5">
         <v>2.583545744375049</v>
@@ -1785,7 +1782,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1799,7 +1796,7 @@
         <v>2.555958070922727</v>
       </c>
       <c r="D6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E6">
         <v>2.632522016358742</v>
@@ -1835,7 +1832,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1849,7 +1846,7 @@
         <v>2.641252819939413</v>
       </c>
       <c r="D7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E7">
         <v>2.540130729835057</v>
@@ -1885,7 +1882,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1899,7 +1896,7 @@
         <v>2.512285655110759</v>
       </c>
       <c r="D8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E8">
         <v>2.590994611146576</v>
@@ -1935,7 +1932,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1949,7 +1946,7 @@
         <v>2.615441102246784</v>
       </c>
       <c r="D9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E9">
         <v>2.513421672263544</v>
@@ -1985,7 +1982,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1999,7 +1996,7 @@
         <v>2.515418243442972</v>
       </c>
       <c r="D10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E10">
         <v>2.545423958143926</v>
@@ -2035,7 +2032,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2049,7 +2046,7 @@
         <v>2.487273994427867</v>
       </c>
       <c r="D11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E11">
         <v>2.567211421027677</v>
@@ -2085,7 +2082,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2099,7 +2096,7 @@
         <v>2.487984580081365</v>
       </c>
       <c r="D12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E12">
         <v>2.579898802553291</v>
@@ -2135,7 +2132,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2149,7 +2146,7 @@
         <v>2.500805561667341</v>
       </c>
       <c r="D13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E13">
         <v>2.59216563562278</v>
@@ -2185,7 +2182,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2199,7 +2196,7 @@
         <v>2.499441989042522</v>
       </c>
       <c r="D14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E14">
         <v>2.736702547602069</v>
@@ -2249,7 +2246,7 @@
         <v>2.512520850741042</v>
       </c>
       <c r="D15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E15">
         <v>2.749061943431123</v>
@@ -2285,7 +2282,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2299,7 +2296,7 @@
         <v>2.77984350091858</v>
       </c>
       <c r="D16" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E16">
         <v>2.889061943431122</v>
@@ -2335,7 +2332,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2349,7 +2346,7 @@
         <v>2.517224153471577</v>
       </c>
       <c r="D17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E17">
         <v>2.753506518310076</v>
@@ -2385,7 +2382,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2399,7 +2396,7 @@
         <v>2.784426680003737</v>
       </c>
       <c r="D18" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E18">
         <v>2.924119959439183</v>
@@ -2435,7 +2432,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2449,7 +2446,7 @@
         <v>2.884280694854824</v>
       </c>
       <c r="D19" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E19">
         <v>2.961861794886389</v>
@@ -2499,7 +2496,7 @@
         <v>2.920719956495094</v>
       </c>
       <c r="D20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E20">
         <v>2.907075620138133</v>
@@ -2535,7 +2532,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2549,7 +2546,7 @@
         <v>2.648180125005333</v>
       </c>
       <c r="D21" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E21">
         <v>2.848908919700521</v>
@@ -2585,7 +2582,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2635,7 +2632,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2649,7 +2646,7 @@
         <v>2.691620213913162</v>
       </c>
       <c r="D23" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E23">
         <v>2.889959376998489</v>
@@ -2685,7 +2682,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2699,7 +2696,7 @@
         <v>2.984719616116966</v>
       </c>
       <c r="D24" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E24">
         <v>2.755965243802971</v>
@@ -2735,7 +2732,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2749,7 +2746,7 @@
         <v>3.007275184023352</v>
       </c>
       <c r="D25" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E25">
         <v>2.755965243802971</v>
@@ -2785,7 +2782,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2799,7 +2796,7 @@
         <v>2.683495528297218</v>
       </c>
       <c r="D26" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E26">
         <v>2.882281628901694</v>
@@ -2835,7 +2832,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2849,7 +2846,7 @@
         <v>2.976914171586129</v>
       </c>
       <c r="D27" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E27">
         <v>2.747824596132772</v>
@@ -2885,7 +2882,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2899,7 +2896,7 @@
         <v>2.647048085674867</v>
       </c>
       <c r="D28" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E28">
         <v>2.84783915365346</v>
@@ -2935,7 +2932,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2949,7 +2946,7 @@
         <v>2.941898848516719</v>
       </c>
       <c r="D29" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E29">
         <v>2.711305547532774</v>
@@ -2985,7 +2982,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2999,7 +2996,7 @@
         <v>2.962790623816959</v>
       </c>
       <c r="D30" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E30">
         <v>2.711305547532774</v>
@@ -3035,7 +3032,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3049,7 +3046,7 @@
         <v>2.636850318680218</v>
       </c>
       <c r="D31" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E31">
         <v>2.674077933106496</v>
@@ -3085,7 +3082,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3099,7 +3096,7 @@
         <v>2.64386308474694</v>
       </c>
       <c r="D32" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E32">
         <v>2.844829359063415</v>
@@ -3135,7 +3132,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3149,7 +3146,7 @@
         <v>2.938838994972993</v>
       </c>
       <c r="D33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E33">
         <v>2.708114289235636</v>
@@ -3185,7 +3182,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3199,7 +3196,7 @@
         <v>2.959611880258242</v>
       </c>
       <c r="D34" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E34">
         <v>2.708114289235636</v>
@@ -3235,7 +3232,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3249,7 +3246,7 @@
         <v>2.63362151616782</v>
       </c>
       <c r="D35" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E35">
         <v>2.706375129633912</v>
@@ -3285,7 +3282,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3299,7 +3296,7 @@
         <v>2.623711665472045</v>
       </c>
       <c r="D36" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E36">
         <v>2.825786465799713</v>
@@ -3335,7 +3332,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3349,7 +3346,7 @@
         <v>2.919479379991807</v>
       </c>
       <c r="D37" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E37">
         <v>2.687923279746057</v>
@@ -3385,7 +3382,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3399,7 +3396,7 @@
         <v>2.939500051198033</v>
       </c>
       <c r="D38" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E38">
         <v>2.687923279746057</v>
@@ -3435,7 +3432,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3449,7 +3446,7 @@
         <v>2.613192965390128</v>
       </c>
       <c r="D39" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E39">
         <v>2.65740457966414</v>
@@ -3485,7 +3482,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3499,7 +3496,7 @@
         <v>2.866121269202039</v>
       </c>
       <c r="D40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E40">
         <v>2.632273716345684</v>
@@ -3549,7 +3546,7 @@
         <v>2.884068721379623</v>
       </c>
       <c r="D41" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E41">
         <v>2.632273716345684</v>
@@ -3599,7 +3596,7 @@
         <v>2.556888701243869</v>
       </c>
       <c r="D42" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E42">
         <v>2.5709911987269</v>
@@ -3649,7 +3646,7 @@
         <v>2.84066903268222</v>
       </c>
       <c r="D43" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E43">
         <v>2.605728438993726</v>
@@ -3685,7 +3682,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3699,7 +3696,7 @@
         <v>2.857627543154535</v>
       </c>
       <c r="D44" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E44">
         <v>2.605728438993726</v>
@@ -3735,7 +3732,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3749,7 +3746,7 @@
         <v>2.530031126511299</v>
       </c>
       <c r="D45" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E45">
         <v>2.536232918189681</v>
@@ -3785,7 +3782,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3799,7 +3796,7 @@
         <v>2.794653597980052</v>
       </c>
       <c r="D46" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E46">
         <v>2.557736881328888</v>
@@ -3835,7 +3832,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3849,7 +3846,7 @@
         <v>2.809824187676618</v>
       </c>
       <c r="D47" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E47">
         <v>2.557736881328888</v>
@@ -3885,7 +3882,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3935,7 +3932,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3949,7 +3946,7 @@
         <v>2.877968395292299</v>
       </c>
       <c r="D49" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E49">
         <v>2.644629614722029</v>
@@ -3985,7 +3982,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3999,7 +3996,7 @@
         <v>2.896376165252531</v>
       </c>
       <c r="D50" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E50">
         <v>2.644629614722029</v>
@@ -4035,7 +4032,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4049,7 +4046,7 @@
         <v>2.521770137334771</v>
       </c>
       <c r="D51" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E51">
         <v>2.535896862069519</v>
@@ -4085,7 +4082,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4099,7 +4096,7 @@
         <v>2.934431839092635</v>
       </c>
       <c r="D52" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E52">
         <v>2.703517868992319</v>
@@ -4135,7 +4132,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4149,7 +4146,7 @@
         <v>2.955033485192349</v>
       </c>
       <c r="D53" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E53">
         <v>2.703517868992319</v>
@@ -4185,7 +4182,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4235,7 +4232,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4249,7 +4246,7 @@
         <v>2.974730272968942</v>
       </c>
       <c r="D55" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E55">
         <v>2.745546910458406</v>
@@ -4285,7 +4282,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4299,7 +4296,7 @@
         <v>2.996897706887981</v>
       </c>
       <c r="D56" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E56">
         <v>2.745546910458406</v>
@@ -4335,7 +4332,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4349,7 +4346,7 @@
         <v>2.624468326525319</v>
       </c>
       <c r="D57" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E57">
         <v>2.660688149733082</v>
@@ -4385,7 +4382,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4399,7 +4396,7 @@
         <v>3.056805462611843</v>
       </c>
       <c r="D58" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E58">
         <v>2.831146801497014</v>
@@ -4435,7 +4432,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4485,7 +4482,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4499,7 +4496,7 @@
         <v>3.075488420323122</v>
       </c>
       <c r="D60" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E60">
         <v>2.850632094815525</v>
@@ -4549,7 +4546,7 @@
         <v>2.73140795531227</v>
       </c>
       <c r="D61" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E61">
         <v>2.75953055997749</v>
@@ -4599,7 +4596,7 @@
         <v>2.72765316464271</v>
       </c>
       <c r="D62" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E62">
         <v>2.75953055997749</v>
@@ -4649,7 +4646,7 @@
         <v>2.72671446697532</v>
       </c>
       <c r="D63" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E63">
         <v>2.75953055997749</v>
@@ -4699,7 +4696,7 @@
         <v>6.293149296554828</v>
       </c>
       <c r="D64" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E64">
         <v>5.963700498102364</v>
@@ -4735,7 +4732,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4749,7 +4746,7 @@
         <v>6.420239880180696</v>
       </c>
       <c r="D65" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E65">
         <v>6.082402264327184</v>
@@ -4785,7 +4782,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4799,7 +4796,7 @@
         <v>6.609514294497387</v>
       </c>
       <c r="D66" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E66">
         <v>6.259183317962906</v>
@@ -4835,7 +4832,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4849,7 +4846,7 @@
         <v>6.515171551263329</v>
       </c>
       <c r="D67" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E67">
         <v>6.612047937164794</v>
@@ -4885,7 +4882,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4899,7 +4896,7 @@
         <v>6.520829737768901</v>
       </c>
       <c r="D68" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E68">
         <v>6.612047937164794</v>
@@ -4935,7 +4932,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4985,7 +4982,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5035,7 +5032,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5085,7 +5082,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5099,7 +5096,7 @@
         <v>6.781478804637512</v>
       </c>
       <c r="D72" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E72">
         <v>6.821616798629249</v>
@@ -5135,7 +5132,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5149,7 +5146,7 @@
         <v>6.927933775178332</v>
       </c>
       <c r="D73" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E73">
         <v>7.025464228815041</v>
@@ -5185,7 +5182,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5199,7 +5196,7 @@
         <v>7.465293617228137</v>
       </c>
       <c r="D74" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E74">
         <v>7.441132824526438</v>
@@ -5235,7 +5232,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5249,7 +5246,7 @@
         <v>2.399740228983164</v>
       </c>
       <c r="D75" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E75">
         <v>2.284756328614283</v>
@@ -5285,7 +5282,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5299,7 +5296,7 @@
         <v>2.181146111927123</v>
       </c>
       <c r="D76" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E76">
         <v>2.105842395854763</v>
@@ -5335,7 +5332,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5349,7 +5346,7 @@
         <v>2.180858495485883</v>
       </c>
       <c r="D77" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E77">
         <v>2.105842395854763</v>
@@ -5385,7 +5382,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5399,7 +5396,7 @@
         <v>2.355267416838251</v>
       </c>
       <c r="D78" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E78">
         <v>2.241615480893012</v>
@@ -5435,7 +5432,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5449,7 +5446,7 @@
         <v>2.138079262229388</v>
       </c>
       <c r="D79" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E79">
         <v>2.115876072829124</v>
@@ -5485,7 +5482,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5499,7 +5496,7 @@
         <v>2.136977667529256</v>
       </c>
       <c r="D80" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E80">
         <v>2.115876072829124</v>
@@ -5535,7 +5532,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5585,7 +5582,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5635,7 +5632,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5685,7 +5682,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5699,7 +5696,7 @@
         <v>1.925553832103902</v>
       </c>
       <c r="D84" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E84">
         <v>1.985821650998686</v>
@@ -5735,7 +5732,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5785,7 +5782,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5799,7 +5796,7 @@
         <v>1.87975631937778</v>
       </c>
       <c r="D86" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E86">
         <v>2.025900250164519</v>
@@ -5835,7 +5832,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5935,7 +5932,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5949,7 +5946,7 @@
         <v>1.789383875507923</v>
       </c>
       <c r="D89" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E89">
         <v>1.940268655809146</v>
@@ -5985,7 +5982,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5999,7 +5996,7 @@
         <v>1.804905667333501</v>
       </c>
       <c r="D90" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E90">
         <v>1.95497618970289</v>
@@ -6035,7 +6032,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6049,7 +6046,7 @@
         <v>1.809491967335235</v>
       </c>
       <c r="D91" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E91">
         <v>1.959321896917648</v>
@@ -6085,7 +6082,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6099,7 +6096,7 @@
         <v>1.822908408572121</v>
       </c>
       <c r="D92" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E92">
         <v>1.972034524843747</v>
@@ -6135,7 +6132,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6149,7 +6146,7 @@
         <v>2.011491451443282</v>
       </c>
       <c r="D93" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E93">
         <v>1.930405304642352</v>
@@ -6185,7 +6182,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6199,7 +6196,7 @@
         <v>1.820166348365971</v>
       </c>
       <c r="D94" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E94">
         <v>1.969436310418903</v>
@@ -6235,7 +6232,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6249,7 +6246,7 @@
         <v>2.008879751476441</v>
       </c>
       <c r="D95" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E95">
         <v>1.927766633591516</v>
@@ -6285,7 +6282,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6299,7 +6296,7 @@
         <v>1.780154910291897</v>
       </c>
       <c r="D96" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E96">
         <v>1.931523833030682</v>
@@ -6335,7 +6332,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6385,7 +6382,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6399,7 +6396,7 @@
         <v>1.781411528733962</v>
       </c>
       <c r="D98" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E98">
         <v>1.932714530505294</v>
@@ -6435,7 +6432,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6485,7 +6482,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6499,7 +6496,7 @@
         <v>1.786869994736246</v>
       </c>
       <c r="D100" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E100">
         <v>1.937886650750082</v>
@@ -6549,7 +6546,7 @@
         <v>1.77389224303264</v>
       </c>
       <c r="D101" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E101">
         <v>1.925589699135846</v>
@@ -6585,7 +6582,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6599,7 +6596,7 @@
         <v>1.764225388294109</v>
       </c>
       <c r="D102" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E102">
         <v>1.916429958088516</v>
@@ -6799,7 +6796,7 @@
         <v>2.039049007419374</v>
       </c>
       <c r="D106" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E106">
         <v>1.958247448115615</v>
@@ -6835,7 +6832,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6849,7 +6846,7 @@
         <v>1.963804213639886</v>
       </c>
       <c r="D107" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E107">
         <v>2.044635472991321</v>
@@ -6885,7 +6882,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6899,7 +6896,7 @@
         <v>2.084469221121035</v>
       </c>
       <c r="D108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E108">
         <v>2.00413671738046</v>
@@ -6935,7 +6932,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6949,7 +6946,7 @@
         <v>1.970692549466935</v>
       </c>
       <c r="D109" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E109">
         <v>2.103970465510173</v>
@@ -6985,7 +6982,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7035,7 +7032,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7049,7 +7046,7 @@
         <v>1.989826166099606</v>
       </c>
       <c r="D111" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E111">
         <v>2.069999197311251</v>
@@ -7085,7 +7082,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7099,7 +7096,7 @@
         <v>1.996538974422711</v>
       </c>
       <c r="D112" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E112">
         <v>2.129860772341935</v>
@@ -7135,7 +7132,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7185,7 +7182,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7199,7 +7196,7 @@
         <v>1.976959483296697</v>
       </c>
       <c r="D114" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E114">
         <v>2.110248039295503</v>
@@ -7299,7 +7296,7 @@
         <v>1.920546112528168</v>
       </c>
       <c r="D116" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E116">
         <v>2.053738890308352</v>
@@ -7335,7 +7332,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7385,7 +7382,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7399,7 +7396,7 @@
         <v>2.078859445890371</v>
       </c>
       <c r="D118" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E118">
         <v>2.128859445890371</v>
@@ -7435,7 +7432,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7449,7 +7446,7 @@
         <v>1.864471846503076</v>
       </c>
       <c r="D119" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E119">
         <v>1.997569421794252</v>
@@ -7485,7 +7482,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7535,7 +7532,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7585,7 +7582,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7599,7 +7596,7 @@
         <v>1.863420505387863</v>
       </c>
       <c r="D122" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E122">
         <v>1.996516295719591</v>
@@ -7699,7 +7696,7 @@
         <v>2.029857360363785</v>
       </c>
       <c r="D124" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E124">
         <v>2.011995247378231</v>
@@ -7749,7 +7746,7 @@
         <v>1.892165706973767</v>
       </c>
       <c r="D125" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E125">
         <v>2.025310300703773</v>
@@ -7785,7 +7782,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7835,7 +7832,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7885,7 +7882,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7949,7 +7946,7 @@
         <v>2.183293967129219</v>
       </c>
       <c r="D129" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E129">
         <v>2.097698061214447</v>
@@ -7999,7 +7996,7 @@
         <v>2.10409703769314</v>
       </c>
       <c r="D130" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E130">
         <v>2.097698061214447</v>
@@ -8085,7 +8082,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8135,7 +8132,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8185,7 +8182,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8235,7 +8232,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8285,7 +8282,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8335,7 +8332,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8385,7 +8382,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8435,7 +8432,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8449,7 +8446,7 @@
         <v>2.367284598691813</v>
       </c>
       <c r="D139" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E139">
         <v>2.284677125480481</v>
@@ -8499,7 +8496,7 @@
         <v>2.308705785003503</v>
       </c>
       <c r="D140" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E140">
         <v>2.284677125480481</v>
@@ -8635,7 +8632,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8685,7 +8682,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8735,7 +8732,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8785,7 +8782,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8835,7 +8832,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8899,7 +8896,7 @@
         <v>2.673055621612132</v>
       </c>
       <c r="D148" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E148">
         <v>2.649383477311975</v>
@@ -8949,7 +8946,7 @@
         <v>2.694510447967022</v>
       </c>
       <c r="D149" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E149">
         <v>2.66746656530884</v>
@@ -8999,7 +8996,7 @@
         <v>2.61961842602696</v>
       </c>
       <c r="D150" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E150">
         <v>2.674946565009619</v>
@@ -9285,7 +9282,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9299,7 +9296,7 @@
         <v>2.746485076848839</v>
       </c>
       <c r="D156" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E156">
         <v>2.847982602490786</v>
@@ -9335,7 +9332,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9399,7 +9396,7 @@
         <v>2.750734210259811</v>
       </c>
       <c r="D158" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E158">
         <v>2.800734210259812</v>
@@ -9435,7 +9432,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9499,7 +9496,7 @@
         <v>2.717092536535202</v>
       </c>
       <c r="D160" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E160">
         <v>2.791717770085309</v>
@@ -9585,7 +9582,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9599,7 +9596,7 @@
         <v>2.669840281895235</v>
       </c>
       <c r="D162" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E162">
         <v>2.754805459723328</v>
@@ -9635,7 +9632,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9699,7 +9696,7 @@
         <v>2.704152220032186</v>
       </c>
       <c r="D164" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E164">
         <v>2.721608307945189</v>
@@ -9749,7 +9746,7 @@
         <v>0.7516342779874527</v>
       </c>
       <c r="D165" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E165">
         <v>0.6447312303040151</v>
@@ -9785,7 +9782,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9799,7 +9796,7 @@
         <v>0.6347312303040145</v>
       </c>
       <c r="D166" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E166">
         <v>0.7803954970608276</v>
@@ -9835,7 +9832,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9849,7 +9846,7 @@
         <v>0.7872985447442655</v>
       </c>
       <c r="D167" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E167">
         <v>0.6685373256708909</v>
@@ -9885,7 +9882,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9899,7 +9896,7 @@
         <v>0.6141118398407031</v>
       </c>
       <c r="D168" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E168">
         <v>0.7042015924277036</v>
@@ -9935,7 +9932,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9949,7 +9946,7 @@
         <v>0.7076194190074974</v>
       </c>
       <c r="D169" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E169">
         <v>0.8524403513495589</v>
@@ -9999,7 +9996,7 @@
         <v>0.8587410173081755</v>
       </c>
       <c r="D170" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E170">
         <v>0.7402207509247285</v>
@@ -10049,7 +10046,7 @@
         <v>0.6868795521992208</v>
       </c>
       <c r="D171" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E171">
         <v>0.7750416832667906</v>
@@ -10099,7 +10096,7 @@
         <v>0.794311018129779</v>
       </c>
       <c r="D172" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E172">
         <v>0.9381289071762104</v>
@@ -10135,7 +10132,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10149,7 +10146,7 @@
         <v>0.7478436529603893</v>
       </c>
       <c r="D173" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E173">
         <v>0.9381289071762104</v>
@@ -10185,7 +10182,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10199,7 +10196,7 @@
         <v>0.9437131136379486</v>
       </c>
       <c r="D174" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E174">
         <v>0.8254794310532532</v>
@@ -10235,7 +10232,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10249,7 +10246,7 @@
         <v>0.7734278594221262</v>
       </c>
       <c r="D175" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E175">
         <v>0.8592973200996861</v>
@@ -10285,7 +10282,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10299,7 +10296,7 @@
         <v>0.9016190641047892</v>
       </c>
       <c r="D176" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E176">
         <v>1.04419537245399</v>
@@ -10335,7 +10332,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10349,7 +10346,7 @@
         <v>0.8558611736195321</v>
       </c>
       <c r="D177" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E177">
         <v>1.04419537245399</v>
@@ -10385,7 +10382,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10399,7 +10396,7 @@
         <v>1.048892735560562</v>
       </c>
       <c r="D178" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E178">
         <v>0.9310137903179339</v>
@@ -10435,7 +10432,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10449,7 +10446,7 @@
         <v>0.8805585367261042</v>
       </c>
       <c r="D179" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E179">
         <v>0.963590098667134</v>
@@ -10485,7 +10482,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10499,7 +10496,7 @@
         <v>1.076170489586433</v>
       </c>
       <c r="D180" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E180">
         <v>1.260525374010979</v>
@@ -10549,7 +10546,7 @@
         <v>1.26341395784032</v>
       </c>
       <c r="D181" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E181">
         <v>1.146258524308584</v>
@@ -10599,7 +10596,7 @@
         <v>1.099059073415773</v>
       </c>
       <c r="D182" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E182">
         <v>1.176302541669659</v>
@@ -10649,7 +10646,7 @@
         <v>1.931268098407571</v>
       </c>
       <c r="D183" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E183">
         <v>1.946759727730396</v>
@@ -10685,7 +10682,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10735,7 +10732,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10785,7 +10782,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10799,7 +10796,7 @@
         <v>0.5942088493584849</v>
       </c>
       <c r="D186" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E186">
         <v>0.5982130518354056</v>
@@ -10835,7 +10832,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10885,7 +10882,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10935,7 +10932,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10985,7 +10982,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10999,7 +10996,7 @@
         <v>-0.02499489055226256</v>
       </c>
       <c r="D190" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E190">
         <v>-0.07499489055226238</v>
@@ -11035,7 +11032,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11049,7 +11046,7 @@
         <v>-0.04541693580813089</v>
       </c>
       <c r="D191" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E191">
         <v>-0.1350880582477796</v>
@@ -11085,7 +11082,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11135,7 +11132,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11185,7 +11182,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11335,7 +11332,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11349,7 +11346,7 @@
         <v>-0.5154661476950757</v>
       </c>
       <c r="D197" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E197">
         <v>-0.4838284745942198</v>
@@ -11385,7 +11382,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11399,7 +11396,7 @@
         <v>-0.5144835438345625</v>
       </c>
       <c r="D198" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E198">
         <v>-0.4838284745942198</v>
@@ -11435,7 +11432,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11485,7 +11482,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11499,7 +11496,7 @@
         <v>-0.6795603356321358</v>
       </c>
       <c r="D200" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E200">
         <v>-0.6353746161347429</v>
@@ -11535,7 +11532,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11549,7 +11546,7 @@
         <v>-0.6770489039336995</v>
       </c>
       <c r="D201" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E201">
         <v>-0.6353746161347429</v>
@@ -11585,7 +11582,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11635,7 +11632,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11649,7 +11646,7 @@
         <v>-1.275160705635463</v>
       </c>
       <c r="D203" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E203">
         <v>-0.9575450227817477</v>
@@ -11685,7 +11682,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11699,7 +11696,7 @@
         <v>-1.267100202166811</v>
       </c>
       <c r="D204" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E204">
         <v>-0.9575450227817477</v>
@@ -11735,7 +11732,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11799,7 +11796,7 @@
         <v>-1.30354206111917</v>
       </c>
       <c r="D206" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E206">
         <v>-0.9846924062879019</v>
@@ -11849,7 +11846,7 @@
         <v>-1.295217135083899</v>
       </c>
       <c r="D207" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E207">
         <v>-0.9846924062879019</v>
@@ -11899,7 +11896,7 @@
         <v>-1.315601110783377</v>
       </c>
       <c r="D208" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E208">
         <v>-0.9962271494449686</v>
@@ -11949,7 +11946,7 @@
         <v>-1.307163833353718</v>
       </c>
       <c r="D209" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E209">
         <v>-0.9962271494449686</v>
@@ -11999,7 +11996,7 @@
         <v>-1.303470101275702</v>
       </c>
       <c r="D210" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E210">
         <v>-0.9846235751332797</v>
@@ -12035,7 +12032,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12049,7 +12046,7 @@
         <v>-1.295145845673754</v>
       </c>
       <c r="D211" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E211">
         <v>-0.9846235751332797</v>
@@ -12085,7 +12082,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12099,7 +12096,7 @@
         <v>-1.352240812118975</v>
       </c>
       <c r="D212" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E212">
         <v>-1.031273820287715</v>
@@ -12135,7 +12132,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12149,7 +12146,7 @@
         <v>-1.343462171012276</v>
       </c>
       <c r="D213" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E213">
         <v>-1.031273820287715</v>
@@ -12185,7 +12182,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12235,7 +12232,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12249,7 +12246,7 @@
         <v>-1.277973836666044</v>
       </c>
       <c r="D215" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E215">
         <v>-0.9602358437675207</v>
@@ -12299,7 +12296,7 @@
         <v>-1.269887123902075</v>
       </c>
       <c r="D216" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E216">
         <v>-0.9602358437675207</v>
@@ -12349,7 +12346,7 @@
         <v>-1.030235843767521</v>
       </c>
       <c r="D217" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E217">
         <v>-1.080019061857596</v>
@@ -12399,7 +12396,7 @@
         <v>-1.007888992711643</v>
       </c>
       <c r="D218" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E218">
         <v>-1.080019061857596</v>
@@ -12449,7 +12446,7 @@
         <v>-1.154349245698821</v>
       </c>
       <c r="D219" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E219">
         <v>-0.8419862350162637</v>
@@ -12499,7 +12496,7 @@
         <v>-1.147414314838273</v>
       </c>
       <c r="D220" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E220">
         <v>-0.8419862350162637</v>
@@ -12649,7 +12646,7 @@
         <v>-0.9332125637434627</v>
       </c>
       <c r="D223" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E223">
         <v>-0.6304641914067899</v>
@@ -12685,7 +12682,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12699,7 +12696,7 @@
         <v>-0.9283379125284608</v>
       </c>
       <c r="D224" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E224">
         <v>-0.6304641914067899</v>
@@ -12735,7 +12732,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12749,7 +12746,7 @@
         <v>-1.078298911794628</v>
       </c>
       <c r="D225" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E225">
         <v>-0.7337942740491279</v>
@@ -12799,7 +12796,7 @@
         <v>-1.284045732215318</v>
       </c>
       <c r="D226" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E226">
         <v>-0.9315166474955321</v>
@@ -12849,7 +12846,7 @@
         <v>-1.074552792811861</v>
       </c>
       <c r="D227" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E227">
         <v>-0.7301942595508679</v>
@@ -12885,7 +12882,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12899,7 +12896,7 @@
         <v>0.6306184682796347</v>
       </c>
       <c r="D228" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E228">
         <v>0.8825890610024754</v>
@@ -12935,7 +12932,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12949,7 +12946,7 @@
         <v>2.500083924851446</v>
       </c>
       <c r="D229" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E229">
         <v>2.721828222716436</v>
@@ -12985,7 +12982,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12999,7 +12996,7 @@
         <v>2.484743417251086</v>
       </c>
       <c r="D230" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E230">
         <v>2.721828222716436</v>
@@ -13035,7 +13032,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13049,7 +13046,7 @@
         <v>2.959498476516616</v>
       </c>
       <c r="D231" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E231">
         <v>3.019498476516616</v>
@@ -13085,7 +13082,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13135,7 +13132,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13149,7 +13146,7 @@
         <v>3.973072767193392</v>
       </c>
       <c r="D233" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E233">
         <v>3.630196829293595</v>
@@ -13185,7 +13182,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13235,7 +13232,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13285,7 +13282,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13299,7 +13296,7 @@
         <v>4.556254256131551</v>
       </c>
       <c r="D236" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E236">
         <v>4.211276763316661</v>
@@ -13335,7 +13332,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13385,7 +13382,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13435,7 +13432,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13449,7 +13446,7 @@
         <v>4.667791750685101</v>
       </c>
       <c r="D239" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E239">
         <v>4.322412320952902</v>
@@ -13485,7 +13482,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13499,7 +13496,7 @@
         <v>4.273963746622406</v>
       </c>
       <c r="D240" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E240">
         <v>4.266274031756307</v>
@@ -13535,7 +13532,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13585,7 +13582,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13635,7 +13632,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13649,7 +13646,7 @@
         <v>3.655351043939968</v>
       </c>
       <c r="D243" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E243">
         <v>3.313620049187031</v>
@@ -13685,7 +13682,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13699,7 +13696,7 @@
         <v>2.349652973133038</v>
       </c>
       <c r="D244" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E244">
         <v>2.585321458264525</v>
@@ -13749,7 +13746,7 @@
         <v>2.337296219946928</v>
       </c>
       <c r="D245" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E245">
         <v>2.585321458264525</v>
@@ -13799,7 +13796,7 @@
         <v>2.821499834857581</v>
       </c>
       <c r="D246" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E246">
         <v>2.482773709326562</v>
@@ -13849,7 +13846,7 @@
         <v>1.399171925433256</v>
       </c>
       <c r="D247" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E247">
         <v>1.7228188215915</v>
@@ -13885,7 +13882,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13899,7 +13896,7 @@
         <v>1.94957093986026</v>
       </c>
       <c r="D248" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E248">
         <v>1.61398690043734</v>
@@ -13935,7 +13932,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13949,7 +13946,7 @@
         <v>1.388298565840941</v>
       </c>
       <c r="D249" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E249">
         <v>1.05473712956764</v>
@@ -13999,7 +13996,7 @@
         <v>1.206849236469149</v>
       </c>
       <c r="D250" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E250">
         <v>0.8739416716530437</v>
@@ -14049,7 +14046,7 @@
         <v>1.250249534396463</v>
       </c>
       <c r="D251" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E251">
         <v>0.9171855721103492</v>
@@ -14099,7 +14096,7 @@
         <v>1.265784593473219</v>
       </c>
       <c r="D252" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E252">
         <v>0.9326646489922341</v>
@@ -14135,7 +14132,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14149,7 +14146,7 @@
         <v>1.181086185990114</v>
       </c>
       <c r="D253" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E253">
         <v>0.8482714609955542</v>
@@ -14199,7 +14196,7 @@
         <v>3.393868635799184</v>
       </c>
       <c r="D254" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E254">
         <v>3.232668972857903</v>
@@ -14235,7 +14232,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14249,7 +14246,7 @@
         <v>3.344337857016143</v>
       </c>
       <c r="D255" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E255">
         <v>3.232668972857903</v>
@@ -14285,7 +14282,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14299,7 +14296,7 @@
         <v>3.108144846549583</v>
       </c>
       <c r="D256" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E256">
         <v>3.176241351782863</v>
@@ -14335,7 +14332,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14349,7 +14346,7 @@
         <v>3.110765478091183</v>
       </c>
       <c r="D257" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E257">
         <v>3.176241351782863</v>
@@ -14385,7 +14382,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14399,7 +14396,7 @@
         <v>3.484929217459694</v>
       </c>
       <c r="D258" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E258">
         <v>3.328403460479749</v>
@@ -14435,7 +14432,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14449,7 +14446,7 @@
         <v>3.438944160440425</v>
       </c>
       <c r="D259" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E259">
         <v>3.328403460479749</v>
@@ -14485,7 +14482,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14535,7 +14532,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14585,7 +14582,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14599,7 +14596,7 @@
         <v>3.67612531160249</v>
       </c>
       <c r="D262" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E262">
         <v>3.529413159454653</v>
@@ -14635,7 +14632,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14649,7 +14646,7 @@
         <v>3.637585058248958</v>
       </c>
       <c r="D263" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E263">
         <v>3.529413159454653</v>
@@ -14685,7 +14682,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14699,7 +14696,7 @@
         <v>3.405388602484038</v>
       </c>
       <c r="D264" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E264">
         <v>3.509413159454653</v>
@@ -14735,7 +14732,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14749,7 +14746,7 @@
         <v>3.405511387337113</v>
       </c>
       <c r="D265" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E265">
         <v>3.509413159454653</v>
@@ -14785,7 +14782,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14799,7 +14796,7 @@
         <v>3.451364045513422</v>
       </c>
       <c r="D266" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E266">
         <v>3.509413159454653</v>
@@ -14835,7 +14832,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14849,7 +14846,7 @@
         <v>4.004636932335591</v>
       </c>
       <c r="D267" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E267">
         <v>3.867442887120403</v>
@@ -14899,7 +14896,7 @@
         <v>3.774439165379895</v>
       </c>
       <c r="D268" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E268">
         <v>3.837640654076098</v>
@@ -14949,7 +14946,7 @@
         <v>4.220199786446392</v>
       </c>
       <c r="D269" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E269">
         <v>4.085943565478028</v>
@@ -14985,7 +14982,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14999,7 +14996,7 @@
         <v>3.991103703583256</v>
       </c>
       <c r="D270" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E270">
         <v>4.0441357312043</v>
@@ -15035,7 +15032,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15049,7 +15046,7 @@
         <v>4.24807262091024</v>
       </c>
       <c r="D271" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E271">
         <v>4.172298835483293</v>
@@ -15085,7 +15082,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15099,7 +15096,7 @@
         <v>4.076733299050661</v>
       </c>
       <c r="D272" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E272">
         <v>4.185185728196767</v>
@@ -15135,7 +15132,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15199,7 +15196,7 @@
         <v>3.853669569225198</v>
       </c>
       <c r="D274" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E274">
         <v>3.960609701897911</v>
@@ -15335,7 +15332,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15349,7 +15346,7 @@
         <v>3.457860783201086</v>
       </c>
       <c r="D277" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E277">
         <v>3.562117466477025</v>
@@ -15385,7 +15382,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15399,7 +15396,7 @@
         <v>3.461796612382101</v>
       </c>
       <c r="D278" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E278">
         <v>3.45818163729601</v>
@@ -15435,7 +15432,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15499,7 +15496,7 @@
         <v>1.876063224574707</v>
       </c>
       <c r="D280" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E280">
         <v>1.926860456775207</v>
@@ -15549,7 +15546,7 @@
         <v>1.879462993924748</v>
       </c>
       <c r="D281" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E281">
         <v>1.926860456775207</v>
@@ -15599,7 +15596,7 @@
         <v>1.36286186891499</v>
       </c>
       <c r="D282" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E282">
         <v>1.420876924621103</v>
@@ -15635,7 +15632,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15649,7 +15646,7 @@
         <v>1.365396205962064</v>
       </c>
       <c r="D283" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E283">
         <v>1.420876924621103</v>
@@ -15685,7 +15682,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15699,7 +15696,7 @@
         <v>1.492587172538397</v>
       </c>
       <c r="D284" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E284">
         <v>1.422587172538397</v>
@@ -15735,7 +15732,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15749,7 +15746,7 @@
         <v>1.155028253713973</v>
       </c>
       <c r="D285" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E285">
         <v>1.207786135342488</v>
@@ -15799,7 +15796,7 @@
         <v>1.157212112489207</v>
       </c>
       <c r="D286" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E286">
         <v>1.207786135342488</v>
@@ -15849,7 +15846,7 @@
         <v>1.287557383512098</v>
       </c>
       <c r="D287" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E287">
         <v>1.260086513310223</v>
@@ -15899,7 +15896,7 @@
         <v>-0.2566084186298667</v>
       </c>
       <c r="D288" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E288">
         <v>-0.001048450451905936</v>
@@ -15935,7 +15932,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15949,7 +15946,7 @@
         <v>-0.2875710874180024</v>
       </c>
       <c r="D289" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E289">
         <v>-0.001048450451905936</v>
@@ -15985,7 +15982,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16035,7 +16032,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16085,7 +16082,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16099,7 +16096,7 @@
         <v>-0.3429456734762377</v>
       </c>
       <c r="D292" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E292">
         <v>-0.1559309932859021</v>
@@ -16135,7 +16132,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16149,7 +16146,7 @@
         <v>-0.452945673476238</v>
       </c>
       <c r="D293" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E293">
         <v>-0.1559309932859021</v>
@@ -16185,7 +16182,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16199,7 +16196,7 @@
         <v>-0.07614423041516449</v>
       </c>
       <c r="D294" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E294">
         <v>-0.08649962563060054</v>
@@ -16235,7 +16232,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16249,7 +16246,7 @@
         <v>-0.06685502084603723</v>
       </c>
       <c r="D295" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E295">
         <v>-0.08649962563060054</v>
@@ -16285,7 +16282,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16299,7 +16296,7 @@
         <v>-0.6325763258089658</v>
       </c>
       <c r="D296" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E296">
         <v>-0.7397037652284588</v>
@@ -16335,7 +16332,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16349,7 +16346,7 @@
         <v>-0.6888811406779016</v>
       </c>
       <c r="D297" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E297">
         <v>-0.6347573064746772</v>
@@ -16385,7 +16382,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16399,7 +16396,7 @@
         <v>-0.5922830059527424</v>
       </c>
       <c r="D298" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E298">
         <v>-0.6988811406779014</v>
@@ -16435,7 +16432,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16449,7 +16446,7 @@
         <v>-0.7708727781363214</v>
       </c>
       <c r="D299" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E299">
         <v>-0.7160845060282481</v>
@@ -16485,7 +16482,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16499,7 +16496,7 @@
         <v>-0.6732115427634033</v>
       </c>
       <c r="D300" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E300">
         <v>-0.7808727781363212</v>
@@ -16535,7 +16532,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16549,7 +16546,7 @@
         <v>-0.6051723879795468</v>
       </c>
       <c r="D301" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E301">
         <v>-0.5517269067155315</v>
@@ -16585,7 +16582,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16599,7 +16596,7 @@
         <v>-0.509659617957122</v>
       </c>
       <c r="D302" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E302">
         <v>-0.6151723879795465</v>
@@ -16635,7 +16632,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16649,7 +16646,7 @@
         <v>1.374867998585327</v>
       </c>
       <c r="D303" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E303">
         <v>1.61428021608427</v>
@@ -16685,7 +16682,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16699,7 +16696,7 @@
         <v>1.37455579980999</v>
       </c>
       <c r="D304" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E304">
         <v>1.61428021608427</v>
@@ -16735,7 +16732,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16749,7 +16746,7 @@
         <v>1.659046067002767</v>
       </c>
       <c r="D305" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E305">
         <v>1.701663141543517</v>
@@ -16785,7 +16782,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16799,7 +16796,7 @@
         <v>1.400425101402588</v>
       </c>
       <c r="D306" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E306">
         <v>1.63789275673065</v>
@@ -16835,7 +16832,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16849,7 +16846,7 @@
         <v>1.415426421593279</v>
       </c>
       <c r="D307" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E307">
         <v>1.63789275673065</v>
@@ -16885,7 +16882,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16899,7 +16896,7 @@
         <v>1.672891436539961</v>
       </c>
       <c r="D308" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E308">
         <v>1.702888796158578</v>
@@ -16935,7 +16932,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16949,7 +16946,7 @@
         <v>1.682896717302726</v>
       </c>
       <c r="D309" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E309">
         <v>1.702888796158578</v>
@@ -16985,7 +16982,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -16999,7 +16996,7 @@
         <v>1.392287936404873</v>
       </c>
       <c r="D310" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E310">
         <v>1.630374723852328</v>
@@ -17035,7 +17032,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17049,7 +17046,7 @@
         <v>1.392192134372636</v>
       </c>
       <c r="D311" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E311">
         <v>1.630374723852328</v>
@@ -17085,7 +17082,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17099,7 +17096,7 @@
         <v>1.665398674360388</v>
       </c>
       <c r="D312" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E312">
         <v>1.367982501138595</v>
@@ -17135,7 +17132,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17149,7 +17146,7 @@
         <v>1.67530287232815</v>
       </c>
       <c r="D313" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E313">
         <v>1.367982501138595</v>
@@ -17185,7 +17182,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17199,7 +17196,7 @@
         <v>1.683187064752997</v>
       </c>
       <c r="D314" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E314">
         <v>1.385560910531628</v>
@@ -17235,7 +17232,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17249,7 +17246,7 @@
         <v>1.693331241005988</v>
       </c>
       <c r="D315" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E315">
         <v>1.385560910531628</v>
@@ -17285,7 +17282,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17299,7 +17296,7 @@
         <v>1.671335210176903</v>
       </c>
       <c r="D316" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E316">
         <v>1.373848959803819</v>
@@ -17335,7 +17332,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17349,7 +17346,7 @@
         <v>1.68131949631757</v>
       </c>
       <c r="D317" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E317">
         <v>1.373848959803819</v>
@@ -17385,7 +17382,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17399,7 +17396,7 @@
         <v>1.693875753393727</v>
       </c>
       <c r="D318" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E318">
         <v>1.396123425781996</v>
@@ -17435,7 +17432,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17449,7 +17446,7 @@
         <v>1.704164127807133</v>
       </c>
       <c r="D319" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E319">
         <v>1.396123425781996</v>
@@ -17485,7 +17482,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17499,7 +17496,7 @@
         <v>1.366123425781996</v>
       </c>
       <c r="D320" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E320">
         <v>1.403731566187024</v>
@@ -17535,7 +17532,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17549,7 +17546,7 @@
         <v>1.710631890779994</v>
       </c>
       <c r="D321" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E321">
         <v>1.412681767280061</v>
@@ -17585,7 +17582,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17599,7 +17596,7 @@
         <v>1.72114631763706</v>
       </c>
       <c r="D322" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E322">
         <v>1.412681767280061</v>
@@ -17635,7 +17632,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17649,7 +17646,7 @@
         <v>1.382681767280062</v>
       </c>
       <c r="D323" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E323">
         <v>1.420374677351461</v>
@@ -17685,7 +17682,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17699,7 +17696,7 @@
         <v>1.679206240881443</v>
       </c>
       <c r="D324" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E324">
         <v>1.381627077835624</v>
@@ -17749,7 +17746,7 @@
         <v>1.689296712933807</v>
       </c>
       <c r="D325" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E325">
         <v>1.381627077835624</v>
@@ -17799,7 +17796,7 @@
         <v>1.351627077835625</v>
       </c>
       <c r="D326" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E326">
         <v>1.364138386842169</v>
@@ -17849,7 +17846,7 @@
         <v>1.662615013806636</v>
       </c>
       <c r="D327" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E327">
         <v>1.365231699984297</v>
@@ -17885,7 +17882,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17899,7 +17896,7 @@
         <v>1.672481658175022</v>
       </c>
       <c r="D328" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E328">
         <v>1.365231699984297</v>
@@ -17935,7 +17932,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17949,7 +17946,7 @@
         <v>1.335231699984297</v>
       </c>
       <c r="D329" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E329">
         <v>1.330198361076394</v>
@@ -17985,7 +17982,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17999,7 +17996,7 @@
         <v>1.638483426036899</v>
       </c>
       <c r="D330" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E330">
         <v>1.341384970754843</v>
@@ -18049,7 +18046,7 @@
         <v>1.648024517787818</v>
       </c>
       <c r="D331" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E331">
         <v>1.341384970754843</v>
@@ -18149,7 +18146,7 @@
         <v>1.611118158429232</v>
       </c>
       <c r="D333" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E333">
         <v>1.31434273328757</v>
@@ -18199,7 +18196,7 @@
         <v>1.620290072876844</v>
       </c>
       <c r="D334" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E334">
         <v>1.31434273328757</v>
@@ -18249,7 +18246,7 @@
         <v>1.210704115653037</v>
       </c>
       <c r="D335" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E335">
         <v>1.321946243981619</v>
@@ -18299,7 +18296,7 @@
         <v>1.250704115653037</v>
       </c>
       <c r="D336" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E336">
         <v>1.321946243981619</v>
@@ -18349,7 +18346,7 @@
         <v>1.580824889600507</v>
       </c>
       <c r="D337" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E337">
         <v>1.284407057851428</v>
@@ -18385,7 +18382,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18399,7 +18396,7 @@
         <v>1.589588125885168</v>
       </c>
       <c r="D338" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E338">
         <v>1.284407057851428</v>
@@ -18435,7 +18432,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18449,7 +18446,7 @@
         <v>1.180206507742837</v>
       </c>
       <c r="D339" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E339">
         <v>1.27675246238701</v>
@@ -18485,7 +18482,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18499,7 +18496,7 @@
         <v>1.220206507742837</v>
       </c>
       <c r="D340" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E340">
         <v>1.27675246238701</v>
@@ -18535,7 +18532,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18549,7 +18546,7 @@
         <v>1.680056540073359</v>
       </c>
       <c r="D341" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E341">
         <v>1.409353064352823</v>
@@ -18585,7 +18582,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18599,7 +18596,7 @@
         <v>1.717732409003494</v>
       </c>
       <c r="D342" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E342">
         <v>1.409353064352823</v>
@@ -18635,7 +18632,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18649,7 +18646,7 @@
         <v>1.307497917096648</v>
       </c>
       <c r="D343" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E343">
         <v>1.444235818399402</v>
@@ -18685,7 +18682,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18699,7 +18696,7 @@
         <v>1.347497917096648</v>
       </c>
       <c r="D344" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E344">
         <v>1.444235818399402</v>
@@ -18735,7 +18732,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18749,7 +18746,7 @@
         <v>1.842256392262994</v>
       </c>
       <c r="D345" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E345">
         <v>1.530769127897027</v>
@@ -18799,7 +18796,7 @@
         <v>1.431193121765403</v>
       </c>
       <c r="D346" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E346">
         <v>1.572471675023835</v>
@@ -18849,7 +18846,7 @@
         <v>1.471193121765403</v>
       </c>
       <c r="D347" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E347">
         <v>1.572471675023835</v>
@@ -18899,7 +18896,7 @@
         <v>2.306011000659936</v>
       </c>
       <c r="D348" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E348">
         <v>2.348379970519409</v>
@@ -18935,7 +18932,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18949,7 +18946,7 @@
         <v>2.400485390479259</v>
       </c>
       <c r="D349" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E349">
         <v>2.364696230398958</v>
@@ -18985,7 +18982,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19035,7 +19032,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19049,7 +19046,7 @@
         <v>2.315116384839492</v>
       </c>
       <c r="D351" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E351">
         <v>2.323814331699535</v>
@@ -19085,7 +19082,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19099,7 +19096,7 @@
         <v>2.158186337006185</v>
       </c>
       <c r="D352" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E352">
         <v>2.199105803820263</v>
@@ -19135,7 +19132,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19185,7 +19182,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19235,7 +19232,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19249,7 +19246,7 @@
         <v>2.249949180664442</v>
       </c>
       <c r="D355" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E355">
         <v>2.193589002935801</v>
@@ -19285,7 +19282,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19299,7 +19296,7 @@
         <v>3.29910210514231</v>
       </c>
       <c r="D356" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E356">
         <v>3.35230135785332</v>
@@ -19335,7 +19332,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19349,7 +19346,7 @@
         <v>3.804045197377832</v>
       </c>
       <c r="D357" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E357">
         <v>3.415154291605215</v>
@@ -19385,7 +19382,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19399,7 +19396,7 @@
         <v>3.427249571448392</v>
       </c>
       <c r="D358" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E358">
         <v>3.291626526785035</v>
@@ -19435,7 +19432,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19485,7 +19482,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19499,7 +19496,7 @@
         <v>3.442581197445604</v>
       </c>
       <c r="D360" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E360">
         <v>3.306414237004073</v>
@@ -19535,7 +19532,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19549,7 +19546,7 @@
         <v>3.36022431872702</v>
       </c>
       <c r="D361" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E361">
         <v>3.226979110080385</v>
@@ -19585,7 +19582,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19599,7 +19596,7 @@
         <v>3.251003700388559</v>
       </c>
       <c r="D362" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E362">
         <v>3.121633280862579</v>
@@ -19635,7 +19632,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19649,7 +19646,7 @@
         <v>2.99001278638902</v>
       </c>
       <c r="D363" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E363">
         <v>3.032275977245447</v>
@@ -19735,7 +19732,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19749,7 +19746,7 @@
         <v>2.786342722576059</v>
       </c>
       <c r="D365" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E365">
         <v>2.830017022419643</v>
@@ -19785,7 +19782,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19799,7 +19796,7 @@
         <v>2.881784622628198</v>
       </c>
       <c r="D366" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E366">
         <v>2.846342722576059</v>
@@ -19835,7 +19832,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19849,7 +19846,7 @@
         <v>2.713139299753176</v>
       </c>
       <c r="D367" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E367">
         <v>2.672915915531583</v>
@@ -19885,7 +19882,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19899,7 +19896,7 @@
         <v>2.722022378645214</v>
       </c>
       <c r="D368" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E368">
         <v>2.672915915531583</v>
@@ -19935,7 +19932,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19949,7 +19946,7 @@
         <v>2.643362683974768</v>
       </c>
       <c r="D369" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E369">
         <v>2.68802760764238</v>
@@ -19985,7 +19982,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19999,7 +19996,7 @@
         <v>2.738474376085565</v>
       </c>
       <c r="D370" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E370">
         <v>2.678250991863972</v>
@@ -20035,7 +20032,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20049,7 +20046,7 @@
         <v>2.26156876679942</v>
       </c>
       <c r="D371" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E371">
         <v>2.319500204055783</v>
@@ -20085,7 +20082,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20099,7 +20096,7 @@
         <v>2.341086491507057</v>
       </c>
       <c r="D372" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E372">
         <v>2.284741341701965</v>
@@ -20135,7 +20132,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20149,7 +20146,7 @@
         <v>2.25156876679942</v>
       </c>
       <c r="D373" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E373">
         <v>2.298948197976329</v>
@@ -20185,7 +20182,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20199,7 +20196,7 @@
         <v>2.345775623073784</v>
       </c>
       <c r="D374" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E374">
         <v>2.287361910525056</v>
@@ -20235,7 +20232,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20249,7 +20246,7 @@
         <v>1.450725995788351</v>
       </c>
       <c r="D375" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E375">
         <v>1.543612412630503</v>
@@ -20285,7 +20282,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20299,7 +20296,7 @@
         <v>1.378039753255653</v>
       </c>
       <c r="D376" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E376">
         <v>1.473954763536668</v>
@@ -20335,7 +20332,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20349,7 +20346,7 @@
         <v>2.300473418774809</v>
       </c>
       <c r="D377" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E377">
         <v>2.269274816103397</v>
@@ -20399,7 +20396,7 @@
         <v>2.307737312105645</v>
       </c>
       <c r="D378" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E378">
         <v>2.269274816103397</v>
@@ -20449,7 +20446,7 @@
         <v>2.548688372146674</v>
       </c>
       <c r="D379" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E379">
         <v>2.44021981851742</v>
@@ -20485,7 +20482,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20499,7 +20496,7 @@
         <v>4.064626779899114</v>
       </c>
       <c r="D380" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E380">
         <v>3.971827788774664</v>
@@ -20535,7 +20532,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20549,7 +20546,7 @@
         <v>2.704221825320051</v>
       </c>
       <c r="D381" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E381">
         <v>2.757514946748523</v>
@@ -20585,7 +20582,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20599,7 +20596,7 @@
         <v>2.699698304540886</v>
       </c>
       <c r="D382" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E382">
         <v>2.757514946748523</v>
@@ -20635,7 +20632,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20649,7 +20646,7 @@
         <v>2.597723564836138</v>
       </c>
       <c r="D383" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E383">
         <v>2.648687698460786</v>
@@ -20685,7 +20682,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20699,7 +20696,7 @@
         <v>2.594470401040876</v>
       </c>
       <c r="D384" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E384">
         <v>2.648687698460786</v>
@@ -20735,7 +20732,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20749,7 +20746,7 @@
         <v>2.5327482758737</v>
       </c>
       <c r="D385" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E385">
         <v>2.582291478725809</v>
@@ -20785,7 +20782,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20799,7 +20796,7 @@
         <v>2.530270165227095</v>
       </c>
       <c r="D386" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E386">
         <v>2.582291478725809</v>
@@ -20835,7 +20832,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20849,7 +20846,7 @@
         <v>2.615226386520305</v>
       </c>
       <c r="D387" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E387">
         <v>2.605226386520305</v>
@@ -20885,7 +20882,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20899,7 +20896,7 @@
         <v>2.519210324106</v>
       </c>
       <c r="D388" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E388">
         <v>2.474919909368535</v>
@@ -20935,7 +20932,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20949,7 +20946,7 @@
         <v>2.443973795685154</v>
       </c>
       <c r="D389" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E389">
         <v>2.491575608314453</v>
@@ -20985,7 +20982,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20999,7 +20996,7 @@
         <v>2.442554625160083</v>
       </c>
       <c r="D390" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E390">
         <v>2.491575608314453</v>
@@ -21035,7 +21032,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21085,7 +21082,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21099,7 +21096,7 @@
         <v>2.457705873063223</v>
       </c>
       <c r="D392" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E392">
         <v>2.413049360402885</v>
@@ -21135,7 +21132,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21149,7 +21146,7 @@
         <v>2.382591377283335</v>
       </c>
       <c r="D393" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E393">
         <v>2.428850830862097</v>
@@ -21185,7 +21182,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21199,7 +21196,7 @@
         <v>2.381904402604011</v>
       </c>
       <c r="D394" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E394">
         <v>2.428850830862097</v>
@@ -21235,7 +21232,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21249,7 +21246,7 @@
         <v>2.46327835196266</v>
       </c>
       <c r="D395" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E395">
         <v>2.453507343522435</v>
@@ -21285,7 +21282,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21299,7 +21296,7 @@
         <v>2.467705873063223</v>
       </c>
       <c r="D396" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E396">
         <v>2.453507343522435</v>
@@ -21335,7 +21332,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21349,7 +21346,7 @@
         <v>2.447999298642713</v>
       </c>
       <c r="D397" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E397">
         <v>2.403285008753682</v>
@@ -21385,7 +21382,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21399,7 +21396,7 @@
         <v>2.372904061939057</v>
       </c>
       <c r="D398" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E398">
         <v>2.418951665679276</v>
@@ -21435,7 +21432,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21449,7 +21446,7 @@
         <v>2.37233264171712</v>
       </c>
       <c r="D399" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E399">
         <v>2.418951665679276</v>
@@ -21485,7 +21482,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21535,7 +21532,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21585,7 +21582,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21599,7 +21596,7 @@
         <v>2.414261420787727</v>
       </c>
       <c r="D402" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E402">
         <v>2.369346310197177</v>
@@ -21635,7 +21632,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21685,7 +21682,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21735,7 +21732,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21749,7 +21746,7 @@
         <v>2.424261420787727</v>
       </c>
       <c r="D405" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E405">
         <v>2.394544385485897</v>
@@ -21785,7 +21782,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21799,7 +21796,7 @@
         <v>2.414374606666995</v>
       </c>
       <c r="D406" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E406">
         <v>2.394544385485897</v>
@@ -21835,7 +21832,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21849,7 +21846,7 @@
         <v>2.397600622679596</v>
       </c>
       <c r="D407" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E407">
         <v>2.352586340671736</v>
@@ -21885,7 +21882,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21899,7 +21896,7 @@
         <v>2.322605383348882</v>
       </c>
       <c r="D408" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E408">
         <v>2.367553015986731</v>
@@ -21935,7 +21932,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21949,7 +21946,7 @@
         <v>2.322633947364601</v>
       </c>
       <c r="D409" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E409">
         <v>2.367553015986731</v>
@@ -21985,7 +21982,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -21999,7 +21996,7 @@
         <v>2.402576819333163</v>
       </c>
       <c r="D410" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E410">
         <v>2.35256729799459</v>
@@ -22035,7 +22032,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22049,7 +22046,7 @@
         <v>2.407600622679595</v>
       </c>
       <c r="D411" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E411">
         <v>2.35256729799459</v>
@@ -22085,7 +22082,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22099,7 +22096,7 @@
         <v>2.39758158000245</v>
       </c>
       <c r="D412" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E412">
         <v>2.35256729799459</v>
@@ -22135,7 +22132,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22149,7 +22146,7 @@
         <v>2.378737718650321</v>
       </c>
       <c r="D413" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E413">
         <v>2.33361115745181</v>
@@ -22185,7 +22182,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22199,7 +22196,7 @@
         <v>2.30377990571649</v>
       </c>
       <c r="D414" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E414">
         <v>2.348315847988621</v>
@@ -22235,7 +22232,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22249,7 +22246,7 @@
         <v>2.304033028113511</v>
       </c>
       <c r="D415" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E415">
         <v>2.348315847988621</v>
@@ -22285,7 +22282,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22299,7 +22296,7 @@
         <v>2.383526783319471</v>
       </c>
       <c r="D416" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E416">
         <v>2.333442409187131</v>
@@ -22335,7 +22332,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22349,7 +22346,7 @@
         <v>2.38873771865032</v>
       </c>
       <c r="D417" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E417">
         <v>2.333442409187131</v>
@@ -22385,7 +22382,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22399,7 +22396,7 @@
         <v>2.378568970385641</v>
       </c>
       <c r="D418" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E418">
         <v>2.333442409187131</v>
@@ -22435,7 +22432,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22449,7 +22446,7 @@
         <v>2.29477967980894</v>
       </c>
       <c r="D419" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E419">
         <v>2.33911879805526</v>
@@ -22499,7 +22496,7 @@
         <v>2.295140160765494</v>
       </c>
       <c r="D420" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E420">
         <v>2.33911879805526</v>
@@ -22549,7 +22546,7 @@
         <v>2.374419198852388</v>
       </c>
       <c r="D421" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E421">
         <v>2.324299038533536</v>
@@ -22599,7 +22596,7 @@
         <v>2.379719599649515</v>
       </c>
       <c r="D422" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E422">
         <v>2.324299038533536</v>
@@ -22649,7 +22646,7 @@
         <v>2.369479279011813</v>
       </c>
       <c r="D423" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E423">
         <v>2.324299038533536</v>
@@ -22699,7 +22696,7 @@
         <v>2.280590400920047</v>
       </c>
       <c r="D424" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E424">
         <v>2.324619216844741</v>
@@ -22735,7 +22732,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22749,7 +22746,7 @@
         <v>2.281120137688396</v>
       </c>
       <c r="D425" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E425">
         <v>2.324619216844741</v>
@@ -22785,7 +22782,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22799,7 +22796,7 @@
         <v>2.360060664151698</v>
       </c>
       <c r="D426" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E426">
         <v>2.309884085228915</v>
@@ -22835,7 +22832,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22885,7 +22882,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22899,7 +22896,7 @@
         <v>2.281700069738552</v>
       </c>
       <c r="D428" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E428">
         <v>2.325753152774585</v>
@@ -22935,7 +22932,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -22949,7 +22946,7 @@
         <v>2.282216569900716</v>
       </c>
       <c r="D429" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E429">
         <v>2.325753152774585</v>
@@ -22985,7 +22982,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -22999,7 +22996,7 @@
         <v>2.361183569576388</v>
       </c>
       <c r="D430" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E430">
         <v>2.311011402855666</v>
@@ -23035,7 +23032,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23049,7 +23046,7 @@
         <v>2.255753152774584</v>
       </c>
       <c r="D431" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E431">
         <v>2.30032273597278</v>
@@ -23085,7 +23082,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23099,7 +23096,7 @@
         <v>2.248769782041177</v>
       </c>
       <c r="D432" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E432">
         <v>2.297801715354081</v>
@@ -23135,7 +23132,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23149,7 +23146,7 @@
         <v>2.343406757033516</v>
       </c>
       <c r="D433" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E433">
         <v>2.293164740361742</v>
@@ -23185,7 +23182,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23199,7 +23196,7 @@
         <v>2.237801715354081</v>
       </c>
       <c r="D434" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E434">
         <v>2.26243869034642</v>
@@ -23235,7 +23232,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23249,7 +23246,7 @@
         <v>2.228095614122554</v>
       </c>
       <c r="D435" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E435">
         <v>2.276800683120539</v>
@@ -23285,7 +23282,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23299,7 +23296,7 @@
         <v>2.322610014996799</v>
       </c>
       <c r="D436" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E436">
         <v>2.263257480497806</v>
@@ -23335,7 +23332,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23385,7 +23382,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23399,7 +23396,7 @@
         <v>2.224983216186275</v>
       </c>
       <c r="D438" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E438">
         <v>2.273639077311749</v>
@@ -23449,7 +23446,7 @@
         <v>2.319479164108328</v>
       </c>
       <c r="D439" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E439">
         <v>2.26015123354559</v>
@@ -23599,7 +23596,7 @@
         <v>2.3116287572162</v>
       </c>
       <c r="D442" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E442">
         <v>2.252362519438469</v>
@@ -23635,7 +23632,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23685,7 +23682,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23735,7 +23732,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23799,7 +23796,7 @@
         <v>2.185149484739352</v>
       </c>
       <c r="D446" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E446">
         <v>2.165149484739352</v>
@@ -23899,7 +23896,7 @@
         <v>2.20020073233055</v>
       </c>
       <c r="D448" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E448">
         <v>2.205687152603988</v>
@@ -23985,7 +23982,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24035,7 +24032,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24085,7 +24082,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24135,7 +24132,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24185,7 +24182,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24299,7 +24296,7 @@
         <v>2.142114930387524</v>
       </c>
       <c r="D456" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E456">
         <v>2.162114930387524</v>
@@ -24335,7 +24332,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24349,7 +24346,7 @@
         <v>2.115413806995409</v>
       </c>
       <c r="D457" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E457">
         <v>2.141244762127619</v>
@@ -24435,7 +24432,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24449,7 +24446,7 @@
         <v>2.073994682974101</v>
       </c>
       <c r="D459" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E459">
         <v>2.082201671198685</v>
@@ -24499,7 +24496,7 @@
         <v>2.083994682974101</v>
       </c>
       <c r="D460" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E460">
         <v>2.082201671198685</v>
@@ -24585,7 +24582,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24599,7 +24596,7 @@
         <v>2.057461365020192</v>
       </c>
       <c r="D462" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E462">
         <v>2.066125824243982</v>
@@ -24635,7 +24632,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24685,7 +24682,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24735,7 +24732,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24785,7 +24782,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24835,7 +24832,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24849,7 +24846,7 @@
         <v>2.057577737614682</v>
       </c>
       <c r="D467" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E467">
         <v>2.099815205781953</v>
@@ -24885,7 +24882,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24949,7 +24946,7 @@
         <v>2.075267052489131</v>
       </c>
       <c r="D469" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E469">
         <v>2.105974841560053</v>
@@ -24999,7 +24996,7 @@
         <v>2.0673904197019</v>
       </c>
       <c r="D470" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E470">
         <v>2.109513786914668</v>
@@ -25049,7 +25046,7 @@
         <v>2.101281730695467</v>
       </c>
       <c r="D471" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E471">
         <v>2.131889846669813</v>
@@ -25099,7 +25096,7 @@
         <v>2.093106078618507</v>
       </c>
       <c r="D472" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E472">
         <v>2.134930426541548</v>
@@ -25149,7 +25146,7 @@
         <v>2.114232378900782</v>
       </c>
       <c r="D473" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E473">
         <v>2.144790875533345</v>
@@ -25185,7 +25182,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25199,7 +25196,7 @@
         <v>2.164790875533345</v>
       </c>
       <c r="D474" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E474">
         <v>2.134232378900781</v>
@@ -25235,7 +25232,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25249,7 +25246,7 @@
         <v>2.105907868798473</v>
       </c>
       <c r="D475" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E475">
         <v>2.147583358696166</v>
@@ -25285,7 +25282,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25299,7 +25296,7 @@
         <v>2.178667208693582</v>
       </c>
       <c r="D476" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E476">
         <v>2.148162082573172</v>
@@ -25335,7 +25332,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25349,7 +25346,7 @@
         <v>2.119677460934401</v>
       </c>
       <c r="D477" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E477">
         <v>2.161192839295628</v>
@@ -25385,7 +25382,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25399,7 +25396,7 @@
         <v>2.191253934723685</v>
       </c>
       <c r="D478" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E478">
         <v>2.160797219088007</v>
@@ -25449,7 +25446,7 @@
         <v>2.132167365995042</v>
       </c>
       <c r="D479" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E479">
         <v>2.173537512902076</v>
@@ -25549,7 +25546,7 @@
         <v>2.161339958759847</v>
       </c>
       <c r="D481" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E481">
         <v>2.202370889471942</v>
@@ -25599,7 +25596,7 @@
         <v>2.215480849833102</v>
       </c>
       <c r="D482" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E482">
         <v>2.179965384477054</v>
@@ -25649,7 +25646,7 @@
         <v>1.276065947508897</v>
       </c>
       <c r="D483" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E483">
         <v>1.317566169928825</v>
@@ -25685,7 +25682,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25699,7 +25696,7 @@
         <v>1.37689891014235</v>
       </c>
       <c r="D484" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E484">
         <v>1.288399132562277</v>
@@ -25735,51 +25732,51 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="485" spans="1:16">
       <c r="A485" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B485" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C485">
-        <v>1.265250934212467</v>
+        <v>1.376065947508897</v>
       </c>
       <c r="D485" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E485">
-        <v>1.296889515011455</v>
+        <v>1.316898910142349</v>
       </c>
       <c r="F485">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G485">
-        <v>0.007774749065787532</v>
+        <v>0.007863934052491103</v>
       </c>
       <c r="H485">
-        <v>0.007723110484988545</v>
+        <v>0.00794310108985765</v>
       </c>
       <c r="I485">
-        <v>0.03163858079898807</v>
+        <v>0.05916703736654805</v>
       </c>
       <c r="J485">
-        <v>0.6939763466497937</v>
+        <v>0.6916703736654803</v>
       </c>
       <c r="K485">
         <v>4.69</v>
       </c>
       <c r="L485">
-        <v>4.52</v>
+        <v>4.62</v>
       </c>
       <c r="M485">
+        <v>4.79</v>
+      </c>
+      <c r="N485">
         <v>4.63</v>
-      </c>
-      <c r="N485">
-        <v>4.51</v>
       </c>
       <c r="O485">
         <v>1</v>
@@ -25796,28 +25793,28 @@
         <v>146</v>
       </c>
       <c r="C486">
-        <v>1.257848770795328</v>
+        <v>1.265250934212467</v>
       </c>
       <c r="D486" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E486">
-        <v>1.28958204878089</v>
+        <v>1.306889515011455</v>
       </c>
       <c r="F486">
         <v>1</v>
       </c>
       <c r="G486">
-        <v>0.007782151229204671</v>
+        <v>0.007774749065787532</v>
       </c>
       <c r="H486">
-        <v>0.00773041795121911</v>
+        <v>0.007733110484988545</v>
       </c>
       <c r="I486">
-        <v>0.03173327798556169</v>
+        <v>0.04163858079898786</v>
       </c>
       <c r="J486">
-        <v>0.6955546330926804</v>
+        <v>0.6939763466497937</v>
       </c>
       <c r="K486">
         <v>4.69</v>
@@ -25829,7 +25826,7 @@
         <v>4.63</v>
       </c>
       <c r="N486">
-        <v>4.51</v>
+        <v>4.52</v>
       </c>
       <c r="O486">
         <v>1</v>
@@ -25840,34 +25837,34 @@
     </row>
     <row r="487" spans="1:16">
       <c r="A487" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B487" t="s">
         <v>147</v>
       </c>
       <c r="C487">
-        <v>1.336383675279734</v>
+        <v>1.365853299547489</v>
       </c>
       <c r="D487" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E487">
-        <v>1.248391395422367</v>
+        <v>1.277491880346475</v>
       </c>
       <c r="F487">
         <v>-1</v>
       </c>
       <c r="G487">
-        <v>0.008043616324720266</v>
+        <v>0.008014146700452512</v>
       </c>
       <c r="H487">
-        <v>0.007871608604577633</v>
+        <v>0.007842508119653525</v>
       </c>
       <c r="I487">
-        <v>0.08799227985736735</v>
+        <v>0.08836141920101337</v>
       </c>
       <c r="J487">
-        <v>0.7001286690438969</v>
+        <v>0.6939763466497937</v>
       </c>
       <c r="K487">
         <v>4.79</v>
@@ -25885,57 +25882,57 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>146</v>
+        <v>386</v>
       </c>
     </row>
     <row r="488" spans="1:16">
       <c r="A488" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B488" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C488">
-        <v>1.279467032224208</v>
+        <v>1.365250934212467</v>
       </c>
       <c r="D488" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E488">
-        <v>1.192187695703653</v>
+        <v>1.305853299547488</v>
       </c>
       <c r="F488">
         <v>-1</v>
       </c>
       <c r="G488">
-        <v>0.008100532967775794</v>
+        <v>0.007874749065787534</v>
       </c>
       <c r="H488">
-        <v>0.007927812304296346</v>
+        <v>0.007954146700452512</v>
       </c>
       <c r="I488">
-        <v>0.08727933652055464</v>
+        <v>0.05939763466497938</v>
       </c>
       <c r="J488">
-        <v>0.7120110579907708</v>
+        <v>0.6939763466497937</v>
       </c>
       <c r="K488">
+        <v>4.69</v>
+      </c>
+      <c r="L488">
+        <v>4.62</v>
+      </c>
+      <c r="M488">
         <v>4.79</v>
       </c>
-      <c r="L488">
-        <v>4.69</v>
-      </c>
-      <c r="M488">
-        <v>4.73</v>
-      </c>
       <c r="N488">
-        <v>4.56</v>
+        <v>4.63</v>
       </c>
       <c r="O488">
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25943,81 +25940,81 @@
         <v>0</v>
       </c>
       <c r="B489" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C489">
-        <v>1.24514956586386</v>
+        <v>1.257848770795328</v>
       </c>
       <c r="D489" t="s">
         <v>270</v>
       </c>
       <c r="E489">
-        <v>1.158300093222558</v>
+        <v>1.29958204878089</v>
       </c>
       <c r="F489">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G489">
-        <v>0.008134850434136141</v>
+        <v>0.007782151229204671</v>
       </c>
       <c r="H489">
-        <v>0.007961699906777442</v>
+        <v>0.00774041795121911</v>
       </c>
       <c r="I489">
-        <v>0.08684947264130205</v>
+        <v>0.04173327798556148</v>
       </c>
       <c r="J489">
-        <v>0.7191754559783174</v>
+        <v>0.6955546330926804</v>
       </c>
       <c r="K489">
-        <v>4.79</v>
+        <v>4.69</v>
       </c>
       <c r="L489">
-        <v>4.69</v>
+        <v>4.52</v>
       </c>
       <c r="M489">
-        <v>4.73</v>
+        <v>4.63</v>
       </c>
       <c r="N489">
-        <v>4.56</v>
+        <v>4.52</v>
       </c>
       <c r="O489">
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="490" spans="1:16">
       <c r="A490" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B490" t="s">
         <v>147</v>
       </c>
       <c r="C490">
-        <v>1.226637749198502</v>
+        <v>1.358293307486061</v>
       </c>
       <c r="D490" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E490">
-        <v>1.140020157350503</v>
+        <v>1.270026585471621</v>
       </c>
       <c r="F490">
         <v>-1</v>
       </c>
       <c r="G490">
-        <v>0.008153362250801498</v>
+        <v>0.00802170669251394</v>
       </c>
       <c r="H490">
-        <v>0.007979979842649497</v>
+        <v>0.007849973414528378</v>
       </c>
       <c r="I490">
-        <v>0.086617591847999</v>
+        <v>0.08826672201444019</v>
       </c>
       <c r="J490">
-        <v>0.7230401358667011</v>
+        <v>0.6955546330926804</v>
       </c>
       <c r="K490">
         <v>4.79</v>
@@ -26035,57 +26032,157 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>271</v>
+        <v>387</v>
       </c>
     </row>
     <row r="491" spans="1:16">
       <c r="A491" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B491" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C491">
-        <v>1.183891513054156</v>
+        <v>1.357848770795329</v>
       </c>
       <c r="D491" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E491">
-        <v>1.097809364665167</v>
+        <v>1.298293307486061</v>
       </c>
       <c r="F491">
         <v>-1</v>
       </c>
       <c r="G491">
-        <v>0.008196108486945847</v>
+        <v>0.007882151229204671</v>
       </c>
       <c r="H491">
-        <v>0.008022190635334832</v>
+        <v>0.007961706692513939</v>
       </c>
       <c r="I491">
-        <v>0.08608214838898842</v>
+        <v>0.05955546330926786</v>
       </c>
       <c r="J491">
-        <v>0.7319641935168778</v>
+        <v>0.6955546330926804</v>
       </c>
       <c r="K491">
+        <v>4.69</v>
+      </c>
+      <c r="L491">
+        <v>4.62</v>
+      </c>
+      <c r="M491">
         <v>4.79</v>
       </c>
-      <c r="L491">
+      <c r="N491">
+        <v>4.63</v>
+      </c>
+      <c r="O491">
+        <v>1</v>
+      </c>
+      <c r="P491" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="492" spans="1:16">
+      <c r="A492" s="1">
+        <v>0</v>
+      </c>
+      <c r="B492" t="s">
+        <v>147</v>
+      </c>
+      <c r="C492">
+        <v>1.336383675279734</v>
+      </c>
+      <c r="D492" t="s">
+        <v>271</v>
+      </c>
+      <c r="E492">
+        <v>1.248391395422367</v>
+      </c>
+      <c r="F492">
+        <v>-1</v>
+      </c>
+      <c r="G492">
+        <v>0.008043616324720266</v>
+      </c>
+      <c r="H492">
+        <v>0.007871608604577633</v>
+      </c>
+      <c r="I492">
+        <v>0.08799227985736735</v>
+      </c>
+      <c r="J492">
+        <v>0.7001286690438969</v>
+      </c>
+      <c r="K492">
+        <v>4.79</v>
+      </c>
+      <c r="L492">
         <v>4.69</v>
       </c>
-      <c r="M491">
+      <c r="M492">
         <v>4.73</v>
       </c>
-      <c r="N491">
+      <c r="N492">
         <v>4.56</v>
       </c>
-      <c r="O491">
-        <v>1</v>
-      </c>
-      <c r="P491" t="s">
-        <v>269</v>
+      <c r="O492">
+        <v>1</v>
+      </c>
+      <c r="P492" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="493" spans="1:16">
+      <c r="A493" s="1">
+        <v>1</v>
+      </c>
+      <c r="B493" t="s">
+        <v>148</v>
+      </c>
+      <c r="C493">
+        <v>1.336396542184123</v>
+      </c>
+      <c r="D493" t="s">
+        <v>272</v>
+      </c>
+      <c r="E493">
+        <v>1.276383675279734</v>
+      </c>
+      <c r="F493">
+        <v>-1</v>
+      </c>
+      <c r="G493">
+        <v>0.007903603457815878</v>
+      </c>
+      <c r="H493">
+        <v>0.007983616324720267</v>
+      </c>
+      <c r="I493">
+        <v>0.06001286690438956</v>
+      </c>
+      <c r="J493">
+        <v>0.7001286690438969</v>
+      </c>
+      <c r="K493">
+        <v>4.69</v>
+      </c>
+      <c r="L493">
+        <v>4.62</v>
+      </c>
+      <c r="M493">
+        <v>4.79</v>
+      </c>
+      <c r="N493">
+        <v>4.63</v>
+      </c>
+      <c r="O493">
+        <v>1</v>
+      </c>
+      <c r="P493" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-03328-601328.xlsx
+++ b/s60_signal/position-03328-601328.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="390">
   <si>
     <t>trade_time</t>
   </si>
@@ -463,6 +463,9 @@
     <t>2021-11-05</t>
   </si>
   <si>
+    <t>2021-10-27</t>
+  </si>
+  <si>
     <t>2016-05-31</t>
   </si>
   <si>
@@ -832,7 +835,7 @@
     <t>2021-11-02</t>
   </si>
   <si>
-    <t>2021-11-08</t>
+    <t>2021-11-09</t>
   </si>
   <si>
     <t>2016-05-24</t>
@@ -1178,6 +1181,9 @@
   </si>
   <si>
     <t>2021-10-19</t>
+  </si>
+  <si>
+    <t>2021-10-26</t>
   </si>
 </sst>
 </file>
@@ -1535,7 +1541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P493"/>
+  <dimension ref="A1:P494"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1596,7 +1602,7 @@
         <v>2.636521639996683</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E2">
         <v>2.833647241107702</v>
@@ -1632,7 +1638,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1646,7 +1652,7 @@
         <v>2.808801457176021</v>
       </c>
       <c r="D3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E3">
         <v>2.7135041663212</v>
@@ -1682,7 +1688,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1696,7 +1702,7 @@
         <v>2.746397091058633</v>
       </c>
       <c r="D4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E4">
         <v>2.648930323263125</v>
@@ -1746,7 +1752,7 @@
         <v>2.683209227271539</v>
       </c>
       <c r="D5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E5">
         <v>2.583545744375049</v>
@@ -1782,7 +1788,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1796,7 +1802,7 @@
         <v>2.555958070922727</v>
       </c>
       <c r="D6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E6">
         <v>2.632522016358742</v>
@@ -1832,7 +1838,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1846,7 +1852,7 @@
         <v>2.641252819939413</v>
       </c>
       <c r="D7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E7">
         <v>2.540130729835057</v>
@@ -1882,7 +1888,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1896,7 +1902,7 @@
         <v>2.512285655110759</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E8">
         <v>2.590994611146576</v>
@@ -1932,7 +1938,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1946,7 +1952,7 @@
         <v>2.615441102246784</v>
       </c>
       <c r="D9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E9">
         <v>2.513421672263544</v>
@@ -1982,7 +1988,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -1996,7 +2002,7 @@
         <v>2.515418243442972</v>
       </c>
       <c r="D10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E10">
         <v>2.545423958143926</v>
@@ -2032,7 +2038,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2046,7 +2052,7 @@
         <v>2.487273994427867</v>
       </c>
       <c r="D11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E11">
         <v>2.567211421027677</v>
@@ -2082,7 +2088,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2096,7 +2102,7 @@
         <v>2.487984580081365</v>
       </c>
       <c r="D12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E12">
         <v>2.579898802553291</v>
@@ -2132,7 +2138,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2146,7 +2152,7 @@
         <v>2.500805561667341</v>
       </c>
       <c r="D13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E13">
         <v>2.59216563562278</v>
@@ -2182,7 +2188,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2196,7 +2202,7 @@
         <v>2.499441989042522</v>
       </c>
       <c r="D14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E14">
         <v>2.736702547602069</v>
@@ -2246,7 +2252,7 @@
         <v>2.512520850741042</v>
       </c>
       <c r="D15" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E15">
         <v>2.749061943431123</v>
@@ -2282,7 +2288,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2296,7 +2302,7 @@
         <v>2.77984350091858</v>
       </c>
       <c r="D16" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E16">
         <v>2.889061943431122</v>
@@ -2332,7 +2338,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2346,7 +2352,7 @@
         <v>2.517224153471577</v>
       </c>
       <c r="D17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E17">
         <v>2.753506518310076</v>
@@ -2382,7 +2388,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2396,7 +2402,7 @@
         <v>2.784426680003737</v>
       </c>
       <c r="D18" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E18">
         <v>2.924119959439183</v>
@@ -2432,7 +2438,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2446,7 +2452,7 @@
         <v>2.884280694854824</v>
       </c>
       <c r="D19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E19">
         <v>2.961861794886389</v>
@@ -2496,7 +2502,7 @@
         <v>2.920719956495094</v>
       </c>
       <c r="D20" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E20">
         <v>2.907075620138133</v>
@@ -2532,7 +2538,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2546,7 +2552,7 @@
         <v>2.648180125005333</v>
       </c>
       <c r="D21" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E21">
         <v>2.848908919700521</v>
@@ -2582,7 +2588,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2632,7 +2638,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2646,7 +2652,7 @@
         <v>2.691620213913162</v>
       </c>
       <c r="D23" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E23">
         <v>2.889959376998489</v>
@@ -2682,7 +2688,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2696,7 +2702,7 @@
         <v>2.984719616116966</v>
       </c>
       <c r="D24" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E24">
         <v>2.755965243802971</v>
@@ -2732,7 +2738,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2746,7 +2752,7 @@
         <v>3.007275184023352</v>
       </c>
       <c r="D25" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E25">
         <v>2.755965243802971</v>
@@ -2782,7 +2788,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2796,7 +2802,7 @@
         <v>2.683495528297218</v>
       </c>
       <c r="D26" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E26">
         <v>2.882281628901694</v>
@@ -2832,7 +2838,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2846,7 +2852,7 @@
         <v>2.976914171586129</v>
       </c>
       <c r="D27" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E27">
         <v>2.747824596132772</v>
@@ -2882,7 +2888,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2896,7 +2902,7 @@
         <v>2.647048085674867</v>
       </c>
       <c r="D28" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E28">
         <v>2.84783915365346</v>
@@ -2932,7 +2938,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2946,7 +2952,7 @@
         <v>2.941898848516719</v>
       </c>
       <c r="D29" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E29">
         <v>2.711305547532774</v>
@@ -2982,7 +2988,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -2996,7 +3002,7 @@
         <v>2.962790623816959</v>
       </c>
       <c r="D30" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E30">
         <v>2.711305547532774</v>
@@ -3032,7 +3038,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3046,7 +3052,7 @@
         <v>2.636850318680218</v>
       </c>
       <c r="D31" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E31">
         <v>2.674077933106496</v>
@@ -3082,7 +3088,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3096,7 +3102,7 @@
         <v>2.64386308474694</v>
       </c>
       <c r="D32" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E32">
         <v>2.844829359063415</v>
@@ -3132,7 +3138,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3146,7 +3152,7 @@
         <v>2.938838994972993</v>
       </c>
       <c r="D33" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E33">
         <v>2.708114289235636</v>
@@ -3182,7 +3188,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3196,7 +3202,7 @@
         <v>2.959611880258242</v>
       </c>
       <c r="D34" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E34">
         <v>2.708114289235636</v>
@@ -3232,7 +3238,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3246,7 +3252,7 @@
         <v>2.63362151616782</v>
       </c>
       <c r="D35" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E35">
         <v>2.706375129633912</v>
@@ -3282,7 +3288,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3296,7 +3302,7 @@
         <v>2.623711665472045</v>
       </c>
       <c r="D36" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E36">
         <v>2.825786465799713</v>
@@ -3332,7 +3338,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3346,7 +3352,7 @@
         <v>2.919479379991807</v>
       </c>
       <c r="D37" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E37">
         <v>2.687923279746057</v>
@@ -3382,7 +3388,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3396,7 +3402,7 @@
         <v>2.939500051198033</v>
       </c>
       <c r="D38" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E38">
         <v>2.687923279746057</v>
@@ -3432,7 +3438,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3446,7 +3452,7 @@
         <v>2.613192965390128</v>
       </c>
       <c r="D39" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E39">
         <v>2.65740457966414</v>
@@ -3482,7 +3488,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3496,7 +3502,7 @@
         <v>2.866121269202039</v>
       </c>
       <c r="D40" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E40">
         <v>2.632273716345684</v>
@@ -3546,7 +3552,7 @@
         <v>2.884068721379623</v>
       </c>
       <c r="D41" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E41">
         <v>2.632273716345684</v>
@@ -3596,7 +3602,7 @@
         <v>2.556888701243869</v>
       </c>
       <c r="D42" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E42">
         <v>2.5709911987269</v>
@@ -3646,7 +3652,7 @@
         <v>2.84066903268222</v>
       </c>
       <c r="D43" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E43">
         <v>2.605728438993726</v>
@@ -3682,7 +3688,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3696,7 +3702,7 @@
         <v>2.857627543154535</v>
       </c>
       <c r="D44" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E44">
         <v>2.605728438993726</v>
@@ -3732,7 +3738,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3746,7 +3752,7 @@
         <v>2.530031126511299</v>
       </c>
       <c r="D45" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E45">
         <v>2.536232918189681</v>
@@ -3782,7 +3788,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3796,7 +3802,7 @@
         <v>2.794653597980052</v>
       </c>
       <c r="D46" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E46">
         <v>2.557736881328888</v>
@@ -3832,7 +3838,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3846,7 +3852,7 @@
         <v>2.809824187676618</v>
       </c>
       <c r="D47" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E47">
         <v>2.557736881328888</v>
@@ -3882,7 +3888,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3932,7 +3938,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3946,7 +3952,7 @@
         <v>2.877968395292299</v>
       </c>
       <c r="D49" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E49">
         <v>2.644629614722029</v>
@@ -3982,7 +3988,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -3996,7 +4002,7 @@
         <v>2.896376165252531</v>
       </c>
       <c r="D50" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E50">
         <v>2.644629614722029</v>
@@ -4032,7 +4038,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4046,7 +4052,7 @@
         <v>2.521770137334771</v>
       </c>
       <c r="D51" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E51">
         <v>2.535896862069519</v>
@@ -4082,7 +4088,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4096,7 +4102,7 @@
         <v>2.934431839092635</v>
       </c>
       <c r="D52" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E52">
         <v>2.703517868992319</v>
@@ -4132,7 +4138,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4146,7 +4152,7 @@
         <v>2.955033485192349</v>
       </c>
       <c r="D53" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E53">
         <v>2.703517868992319</v>
@@ -4182,7 +4188,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4232,7 +4238,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4246,7 +4252,7 @@
         <v>2.974730272968942</v>
       </c>
       <c r="D55" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E55">
         <v>2.745546910458406</v>
@@ -4282,7 +4288,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4296,7 +4302,7 @@
         <v>2.996897706887981</v>
       </c>
       <c r="D56" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E56">
         <v>2.745546910458406</v>
@@ -4332,7 +4338,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4346,7 +4352,7 @@
         <v>2.624468326525319</v>
       </c>
       <c r="D57" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E57">
         <v>2.660688149733082</v>
@@ -4382,7 +4388,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4396,7 +4402,7 @@
         <v>3.056805462611843</v>
       </c>
       <c r="D58" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E58">
         <v>2.831146801497014</v>
@@ -4432,7 +4438,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4482,7 +4488,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4496,7 +4502,7 @@
         <v>3.075488420323122</v>
       </c>
       <c r="D60" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E60">
         <v>2.850632094815525</v>
@@ -4546,7 +4552,7 @@
         <v>2.73140795531227</v>
       </c>
       <c r="D61" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E61">
         <v>2.75953055997749</v>
@@ -4596,7 +4602,7 @@
         <v>2.72765316464271</v>
       </c>
       <c r="D62" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E62">
         <v>2.75953055997749</v>
@@ -4646,7 +4652,7 @@
         <v>2.72671446697532</v>
       </c>
       <c r="D63" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E63">
         <v>2.75953055997749</v>
@@ -4696,7 +4702,7 @@
         <v>6.293149296554828</v>
       </c>
       <c r="D64" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E64">
         <v>5.963700498102364</v>
@@ -4732,7 +4738,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4746,7 +4752,7 @@
         <v>6.420239880180696</v>
       </c>
       <c r="D65" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E65">
         <v>6.082402264327184</v>
@@ -4782,7 +4788,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4796,7 +4802,7 @@
         <v>6.609514294497387</v>
       </c>
       <c r="D66" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E66">
         <v>6.259183317962906</v>
@@ -4832,7 +4838,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4846,7 +4852,7 @@
         <v>6.515171551263329</v>
       </c>
       <c r="D67" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E67">
         <v>6.612047937164794</v>
@@ -4882,7 +4888,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4896,7 +4902,7 @@
         <v>6.520829737768901</v>
       </c>
       <c r="D68" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E68">
         <v>6.612047937164794</v>
@@ -4932,7 +4938,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4982,7 +4988,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5032,7 +5038,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5082,7 +5088,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5096,7 +5102,7 @@
         <v>6.781478804637512</v>
       </c>
       <c r="D72" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E72">
         <v>6.821616798629249</v>
@@ -5132,7 +5138,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5146,7 +5152,7 @@
         <v>6.927933775178332</v>
       </c>
       <c r="D73" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E73">
         <v>7.025464228815041</v>
@@ -5182,7 +5188,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5196,7 +5202,7 @@
         <v>7.465293617228137</v>
       </c>
       <c r="D74" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E74">
         <v>7.441132824526438</v>
@@ -5232,7 +5238,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5246,7 +5252,7 @@
         <v>2.399740228983164</v>
       </c>
       <c r="D75" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E75">
         <v>2.284756328614283</v>
@@ -5282,7 +5288,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5296,7 +5302,7 @@
         <v>2.181146111927123</v>
       </c>
       <c r="D76" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E76">
         <v>2.105842395854763</v>
@@ -5332,7 +5338,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5346,7 +5352,7 @@
         <v>2.180858495485883</v>
       </c>
       <c r="D77" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E77">
         <v>2.105842395854763</v>
@@ -5382,7 +5388,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5396,7 +5402,7 @@
         <v>2.355267416838251</v>
       </c>
       <c r="D78" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E78">
         <v>2.241615480893012</v>
@@ -5432,7 +5438,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5446,7 +5452,7 @@
         <v>2.138079262229388</v>
       </c>
       <c r="D79" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E79">
         <v>2.115876072829124</v>
@@ -5482,7 +5488,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5496,7 +5502,7 @@
         <v>2.136977667529256</v>
       </c>
       <c r="D80" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E80">
         <v>2.115876072829124</v>
@@ -5532,7 +5538,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5582,7 +5588,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5632,7 +5638,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5682,7 +5688,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5696,7 +5702,7 @@
         <v>1.925553832103902</v>
       </c>
       <c r="D84" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E84">
         <v>1.985821650998686</v>
@@ -5732,7 +5738,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5782,7 +5788,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5796,7 +5802,7 @@
         <v>1.87975631937778</v>
       </c>
       <c r="D86" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E86">
         <v>2.025900250164519</v>
@@ -5832,7 +5838,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5932,7 +5938,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5946,7 +5952,7 @@
         <v>1.789383875507923</v>
       </c>
       <c r="D89" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E89">
         <v>1.940268655809146</v>
@@ -5982,7 +5988,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -5996,7 +6002,7 @@
         <v>1.804905667333501</v>
       </c>
       <c r="D90" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E90">
         <v>1.95497618970289</v>
@@ -6032,7 +6038,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6046,7 +6052,7 @@
         <v>1.809491967335235</v>
       </c>
       <c r="D91" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E91">
         <v>1.959321896917648</v>
@@ -6082,7 +6088,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6096,7 +6102,7 @@
         <v>1.822908408572121</v>
       </c>
       <c r="D92" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E92">
         <v>1.972034524843747</v>
@@ -6132,7 +6138,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6146,7 +6152,7 @@
         <v>2.011491451443282</v>
       </c>
       <c r="D93" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E93">
         <v>1.930405304642352</v>
@@ -6182,7 +6188,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6196,7 +6202,7 @@
         <v>1.820166348365971</v>
       </c>
       <c r="D94" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E94">
         <v>1.969436310418903</v>
@@ -6232,7 +6238,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6246,7 +6252,7 @@
         <v>2.008879751476441</v>
       </c>
       <c r="D95" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E95">
         <v>1.927766633591516</v>
@@ -6282,7 +6288,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6296,7 +6302,7 @@
         <v>1.780154910291897</v>
       </c>
       <c r="D96" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E96">
         <v>1.931523833030682</v>
@@ -6332,7 +6338,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6382,7 +6388,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6396,7 +6402,7 @@
         <v>1.781411528733962</v>
       </c>
       <c r="D98" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E98">
         <v>1.932714530505294</v>
@@ -6432,7 +6438,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6482,7 +6488,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6496,7 +6502,7 @@
         <v>1.786869994736246</v>
       </c>
       <c r="D100" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E100">
         <v>1.937886650750082</v>
@@ -6546,7 +6552,7 @@
         <v>1.77389224303264</v>
       </c>
       <c r="D101" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E101">
         <v>1.925589699135846</v>
@@ -6582,7 +6588,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6596,7 +6602,7 @@
         <v>1.764225388294109</v>
       </c>
       <c r="D102" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E102">
         <v>1.916429958088516</v>
@@ -6796,7 +6802,7 @@
         <v>2.039049007419374</v>
       </c>
       <c r="D106" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E106">
         <v>1.958247448115615</v>
@@ -6832,7 +6838,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6846,7 +6852,7 @@
         <v>1.963804213639886</v>
       </c>
       <c r="D107" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E107">
         <v>2.044635472991321</v>
@@ -6882,7 +6888,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6896,7 +6902,7 @@
         <v>2.084469221121035</v>
       </c>
       <c r="D108" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E108">
         <v>2.00413671738046</v>
@@ -6932,7 +6938,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6946,7 +6952,7 @@
         <v>1.970692549466935</v>
       </c>
       <c r="D109" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E109">
         <v>2.103970465510173</v>
@@ -6982,7 +6988,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7032,7 +7038,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7046,7 +7052,7 @@
         <v>1.989826166099606</v>
       </c>
       <c r="D111" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E111">
         <v>2.069999197311251</v>
@@ -7082,7 +7088,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7096,7 +7102,7 @@
         <v>1.996538974422711</v>
       </c>
       <c r="D112" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E112">
         <v>2.129860772341935</v>
@@ -7132,7 +7138,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7182,7 +7188,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7196,7 +7202,7 @@
         <v>1.976959483296697</v>
       </c>
       <c r="D114" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E114">
         <v>2.110248039295503</v>
@@ -7296,7 +7302,7 @@
         <v>1.920546112528168</v>
       </c>
       <c r="D116" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E116">
         <v>2.053738890308352</v>
@@ -7332,7 +7338,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7382,7 +7388,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7396,7 +7402,7 @@
         <v>2.078859445890371</v>
       </c>
       <c r="D118" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E118">
         <v>2.128859445890371</v>
@@ -7432,7 +7438,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7446,7 +7452,7 @@
         <v>1.864471846503076</v>
       </c>
       <c r="D119" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E119">
         <v>1.997569421794252</v>
@@ -7482,7 +7488,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7532,7 +7538,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7582,7 +7588,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7596,7 +7602,7 @@
         <v>1.863420505387863</v>
       </c>
       <c r="D122" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E122">
         <v>1.996516295719591</v>
@@ -7696,7 +7702,7 @@
         <v>2.029857360363785</v>
       </c>
       <c r="D124" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E124">
         <v>2.011995247378231</v>
@@ -7746,7 +7752,7 @@
         <v>1.892165706973767</v>
       </c>
       <c r="D125" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E125">
         <v>2.025310300703773</v>
@@ -7782,7 +7788,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7832,7 +7838,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7882,7 +7888,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7946,7 +7952,7 @@
         <v>2.183293967129219</v>
       </c>
       <c r="D129" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E129">
         <v>2.097698061214447</v>
@@ -7996,7 +8002,7 @@
         <v>2.10409703769314</v>
       </c>
       <c r="D130" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E130">
         <v>2.097698061214447</v>
@@ -8082,7 +8088,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8132,7 +8138,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8182,7 +8188,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8232,7 +8238,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8282,7 +8288,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8332,7 +8338,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8382,7 +8388,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8432,7 +8438,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8446,7 +8452,7 @@
         <v>2.367284598691813</v>
       </c>
       <c r="D139" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E139">
         <v>2.284677125480481</v>
@@ -8496,7 +8502,7 @@
         <v>2.308705785003503</v>
       </c>
       <c r="D140" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E140">
         <v>2.284677125480481</v>
@@ -8632,7 +8638,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8682,7 +8688,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8732,7 +8738,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8782,7 +8788,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8832,7 +8838,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8896,7 +8902,7 @@
         <v>2.673055621612132</v>
       </c>
       <c r="D148" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E148">
         <v>2.649383477311975</v>
@@ -8946,7 +8952,7 @@
         <v>2.694510447967022</v>
       </c>
       <c r="D149" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E149">
         <v>2.66746656530884</v>
@@ -8996,7 +9002,7 @@
         <v>2.61961842602696</v>
       </c>
       <c r="D150" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E150">
         <v>2.674946565009619</v>
@@ -9282,7 +9288,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9296,7 +9302,7 @@
         <v>2.746485076848839</v>
       </c>
       <c r="D156" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E156">
         <v>2.847982602490786</v>
@@ -9332,7 +9338,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9396,7 +9402,7 @@
         <v>2.750734210259811</v>
       </c>
       <c r="D158" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E158">
         <v>2.800734210259812</v>
@@ -9432,7 +9438,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9496,7 +9502,7 @@
         <v>2.717092536535202</v>
       </c>
       <c r="D160" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E160">
         <v>2.791717770085309</v>
@@ -9582,7 +9588,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9596,7 +9602,7 @@
         <v>2.669840281895235</v>
       </c>
       <c r="D162" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E162">
         <v>2.754805459723328</v>
@@ -9632,7 +9638,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9696,7 +9702,7 @@
         <v>2.704152220032186</v>
       </c>
       <c r="D164" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E164">
         <v>2.721608307945189</v>
@@ -9746,7 +9752,7 @@
         <v>0.7516342779874527</v>
       </c>
       <c r="D165" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E165">
         <v>0.6447312303040151</v>
@@ -9782,7 +9788,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9796,7 +9802,7 @@
         <v>0.6347312303040145</v>
       </c>
       <c r="D166" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E166">
         <v>0.7803954970608276</v>
@@ -9832,7 +9838,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9846,7 +9852,7 @@
         <v>0.7872985447442655</v>
       </c>
       <c r="D167" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E167">
         <v>0.6685373256708909</v>
@@ -9882,7 +9888,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9896,7 +9902,7 @@
         <v>0.6141118398407031</v>
       </c>
       <c r="D168" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E168">
         <v>0.7042015924277036</v>
@@ -9932,7 +9938,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9946,7 +9952,7 @@
         <v>0.7076194190074974</v>
       </c>
       <c r="D169" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E169">
         <v>0.8524403513495589</v>
@@ -9996,7 +10002,7 @@
         <v>0.8587410173081755</v>
       </c>
       <c r="D170" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E170">
         <v>0.7402207509247285</v>
@@ -10046,7 +10052,7 @@
         <v>0.6868795521992208</v>
       </c>
       <c r="D171" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E171">
         <v>0.7750416832667906</v>
@@ -10096,7 +10102,7 @@
         <v>0.794311018129779</v>
       </c>
       <c r="D172" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E172">
         <v>0.9381289071762104</v>
@@ -10132,7 +10138,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10146,7 +10152,7 @@
         <v>0.7478436529603893</v>
       </c>
       <c r="D173" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E173">
         <v>0.9381289071762104</v>
@@ -10182,7 +10188,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10196,7 +10202,7 @@
         <v>0.9437131136379486</v>
       </c>
       <c r="D174" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E174">
         <v>0.8254794310532532</v>
@@ -10232,7 +10238,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10246,7 +10252,7 @@
         <v>0.7734278594221262</v>
       </c>
       <c r="D175" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E175">
         <v>0.8592973200996861</v>
@@ -10282,7 +10288,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10296,7 +10302,7 @@
         <v>0.9016190641047892</v>
       </c>
       <c r="D176" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E176">
         <v>1.04419537245399</v>
@@ -10332,7 +10338,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10346,7 +10352,7 @@
         <v>0.8558611736195321</v>
       </c>
       <c r="D177" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E177">
         <v>1.04419537245399</v>
@@ -10382,7 +10388,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10396,7 +10402,7 @@
         <v>1.048892735560562</v>
       </c>
       <c r="D178" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E178">
         <v>0.9310137903179339</v>
@@ -10432,7 +10438,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10446,7 +10452,7 @@
         <v>0.8805585367261042</v>
       </c>
       <c r="D179" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E179">
         <v>0.963590098667134</v>
@@ -10482,7 +10488,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10496,7 +10502,7 @@
         <v>1.076170489586433</v>
       </c>
       <c r="D180" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E180">
         <v>1.260525374010979</v>
@@ -10546,7 +10552,7 @@
         <v>1.26341395784032</v>
       </c>
       <c r="D181" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E181">
         <v>1.146258524308584</v>
@@ -10596,7 +10602,7 @@
         <v>1.099059073415773</v>
       </c>
       <c r="D182" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E182">
         <v>1.176302541669659</v>
@@ -10646,7 +10652,7 @@
         <v>1.931268098407571</v>
       </c>
       <c r="D183" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E183">
         <v>1.946759727730396</v>
@@ -10682,7 +10688,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10732,7 +10738,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10782,7 +10788,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10796,7 +10802,7 @@
         <v>0.5942088493584849</v>
       </c>
       <c r="D186" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E186">
         <v>0.5982130518354056</v>
@@ -10832,7 +10838,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10882,7 +10888,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10932,7 +10938,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10982,7 +10988,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -10996,7 +11002,7 @@
         <v>-0.02499489055226256</v>
       </c>
       <c r="D190" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E190">
         <v>-0.07499489055226238</v>
@@ -11032,7 +11038,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11046,7 +11052,7 @@
         <v>-0.04541693580813089</v>
       </c>
       <c r="D191" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E191">
         <v>-0.1350880582477796</v>
@@ -11082,7 +11088,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11132,7 +11138,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11182,7 +11188,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11332,7 +11338,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11346,7 +11352,7 @@
         <v>-0.5154661476950757</v>
       </c>
       <c r="D197" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E197">
         <v>-0.4838284745942198</v>
@@ -11382,7 +11388,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11396,7 +11402,7 @@
         <v>-0.5144835438345625</v>
       </c>
       <c r="D198" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E198">
         <v>-0.4838284745942198</v>
@@ -11432,7 +11438,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11482,7 +11488,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11496,7 +11502,7 @@
         <v>-0.6795603356321358</v>
       </c>
       <c r="D200" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E200">
         <v>-0.6353746161347429</v>
@@ -11532,7 +11538,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11546,7 +11552,7 @@
         <v>-0.6770489039336995</v>
       </c>
       <c r="D201" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E201">
         <v>-0.6353746161347429</v>
@@ -11582,7 +11588,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11632,7 +11638,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11646,7 +11652,7 @@
         <v>-1.275160705635463</v>
       </c>
       <c r="D203" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E203">
         <v>-0.9575450227817477</v>
@@ -11682,7 +11688,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11696,7 +11702,7 @@
         <v>-1.267100202166811</v>
       </c>
       <c r="D204" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E204">
         <v>-0.9575450227817477</v>
@@ -11732,7 +11738,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11796,7 +11802,7 @@
         <v>-1.30354206111917</v>
       </c>
       <c r="D206" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E206">
         <v>-0.9846924062879019</v>
@@ -11846,7 +11852,7 @@
         <v>-1.295217135083899</v>
       </c>
       <c r="D207" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E207">
         <v>-0.9846924062879019</v>
@@ -11896,7 +11902,7 @@
         <v>-1.315601110783377</v>
       </c>
       <c r="D208" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E208">
         <v>-0.9962271494449686</v>
@@ -11946,7 +11952,7 @@
         <v>-1.307163833353718</v>
       </c>
       <c r="D209" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E209">
         <v>-0.9962271494449686</v>
@@ -11996,7 +12002,7 @@
         <v>-1.303470101275702</v>
       </c>
       <c r="D210" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E210">
         <v>-0.9846235751332797</v>
@@ -12032,7 +12038,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12046,7 +12052,7 @@
         <v>-1.295145845673754</v>
       </c>
       <c r="D211" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E211">
         <v>-0.9846235751332797</v>
@@ -12082,7 +12088,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12096,7 +12102,7 @@
         <v>-1.352240812118975</v>
       </c>
       <c r="D212" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E212">
         <v>-1.031273820287715</v>
@@ -12132,7 +12138,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12146,7 +12152,7 @@
         <v>-1.343462171012276</v>
       </c>
       <c r="D213" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E213">
         <v>-1.031273820287715</v>
@@ -12182,7 +12188,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12232,7 +12238,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12246,7 +12252,7 @@
         <v>-1.277973836666044</v>
       </c>
       <c r="D215" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E215">
         <v>-0.9602358437675207</v>
@@ -12296,7 +12302,7 @@
         <v>-1.269887123902075</v>
       </c>
       <c r="D216" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E216">
         <v>-0.9602358437675207</v>
@@ -12346,7 +12352,7 @@
         <v>-1.030235843767521</v>
       </c>
       <c r="D217" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E217">
         <v>-1.080019061857596</v>
@@ -12396,7 +12402,7 @@
         <v>-1.007888992711643</v>
       </c>
       <c r="D218" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E218">
         <v>-1.080019061857596</v>
@@ -12446,7 +12452,7 @@
         <v>-1.154349245698821</v>
       </c>
       <c r="D219" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E219">
         <v>-0.8419862350162637</v>
@@ -12496,7 +12502,7 @@
         <v>-1.147414314838273</v>
       </c>
       <c r="D220" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E220">
         <v>-0.8419862350162637</v>
@@ -12646,7 +12652,7 @@
         <v>-0.9332125637434627</v>
       </c>
       <c r="D223" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E223">
         <v>-0.6304641914067899</v>
@@ -12682,7 +12688,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12696,7 +12702,7 @@
         <v>-0.9283379125284608</v>
       </c>
       <c r="D224" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E224">
         <v>-0.6304641914067899</v>
@@ -12732,7 +12738,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12746,7 +12752,7 @@
         <v>-1.078298911794628</v>
       </c>
       <c r="D225" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E225">
         <v>-0.7337942740491279</v>
@@ -12796,7 +12802,7 @@
         <v>-1.284045732215318</v>
       </c>
       <c r="D226" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E226">
         <v>-0.9315166474955321</v>
@@ -12846,7 +12852,7 @@
         <v>-1.074552792811861</v>
       </c>
       <c r="D227" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E227">
         <v>-0.7301942595508679</v>
@@ -12882,7 +12888,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12896,7 +12902,7 @@
         <v>0.6306184682796347</v>
       </c>
       <c r="D228" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E228">
         <v>0.8825890610024754</v>
@@ -12932,7 +12938,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12946,7 +12952,7 @@
         <v>2.500083924851446</v>
       </c>
       <c r="D229" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E229">
         <v>2.721828222716436</v>
@@ -12982,7 +12988,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -12996,7 +13002,7 @@
         <v>2.484743417251086</v>
       </c>
       <c r="D230" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E230">
         <v>2.721828222716436</v>
@@ -13032,7 +13038,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13046,7 +13052,7 @@
         <v>2.959498476516616</v>
       </c>
       <c r="D231" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E231">
         <v>3.019498476516616</v>
@@ -13082,7 +13088,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13132,7 +13138,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13146,7 +13152,7 @@
         <v>3.973072767193392</v>
       </c>
       <c r="D233" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E233">
         <v>3.630196829293595</v>
@@ -13182,7 +13188,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13232,7 +13238,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13282,7 +13288,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13296,7 +13302,7 @@
         <v>4.556254256131551</v>
       </c>
       <c r="D236" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E236">
         <v>4.211276763316661</v>
@@ -13332,7 +13338,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13382,7 +13388,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13432,7 +13438,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13446,7 +13452,7 @@
         <v>4.667791750685101</v>
       </c>
       <c r="D239" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E239">
         <v>4.322412320952902</v>
@@ -13482,7 +13488,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13496,7 +13502,7 @@
         <v>4.273963746622406</v>
       </c>
       <c r="D240" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E240">
         <v>4.266274031756307</v>
@@ -13532,7 +13538,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13582,7 +13588,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13632,7 +13638,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13646,7 +13652,7 @@
         <v>3.655351043939968</v>
       </c>
       <c r="D243" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E243">
         <v>3.313620049187031</v>
@@ -13682,7 +13688,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13696,7 +13702,7 @@
         <v>2.349652973133038</v>
       </c>
       <c r="D244" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E244">
         <v>2.585321458264525</v>
@@ -13746,7 +13752,7 @@
         <v>2.337296219946928</v>
       </c>
       <c r="D245" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E245">
         <v>2.585321458264525</v>
@@ -13796,7 +13802,7 @@
         <v>2.821499834857581</v>
       </c>
       <c r="D246" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E246">
         <v>2.482773709326562</v>
@@ -13846,7 +13852,7 @@
         <v>1.399171925433256</v>
       </c>
       <c r="D247" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E247">
         <v>1.7228188215915</v>
@@ -13882,7 +13888,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13896,7 +13902,7 @@
         <v>1.94957093986026</v>
       </c>
       <c r="D248" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E248">
         <v>1.61398690043734</v>
@@ -13932,7 +13938,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13946,7 +13952,7 @@
         <v>1.388298565840941</v>
       </c>
       <c r="D249" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E249">
         <v>1.05473712956764</v>
@@ -13996,7 +14002,7 @@
         <v>1.206849236469149</v>
       </c>
       <c r="D250" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E250">
         <v>0.8739416716530437</v>
@@ -14046,7 +14052,7 @@
         <v>1.250249534396463</v>
       </c>
       <c r="D251" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E251">
         <v>0.9171855721103492</v>
@@ -14096,7 +14102,7 @@
         <v>1.265784593473219</v>
       </c>
       <c r="D252" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E252">
         <v>0.9326646489922341</v>
@@ -14132,7 +14138,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14146,7 +14152,7 @@
         <v>1.181086185990114</v>
       </c>
       <c r="D253" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E253">
         <v>0.8482714609955542</v>
@@ -14196,7 +14202,7 @@
         <v>3.393868635799184</v>
       </c>
       <c r="D254" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E254">
         <v>3.232668972857903</v>
@@ -14232,7 +14238,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14246,7 +14252,7 @@
         <v>3.344337857016143</v>
       </c>
       <c r="D255" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E255">
         <v>3.232668972857903</v>
@@ -14282,7 +14288,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14296,7 +14302,7 @@
         <v>3.108144846549583</v>
       </c>
       <c r="D256" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E256">
         <v>3.176241351782863</v>
@@ -14332,7 +14338,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14346,7 +14352,7 @@
         <v>3.110765478091183</v>
       </c>
       <c r="D257" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E257">
         <v>3.176241351782863</v>
@@ -14382,7 +14388,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14396,7 +14402,7 @@
         <v>3.484929217459694</v>
       </c>
       <c r="D258" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E258">
         <v>3.328403460479749</v>
@@ -14432,7 +14438,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14446,7 +14452,7 @@
         <v>3.438944160440425</v>
       </c>
       <c r="D259" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E259">
         <v>3.328403460479749</v>
@@ -14482,7 +14488,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14532,7 +14538,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14582,7 +14588,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14596,7 +14602,7 @@
         <v>3.67612531160249</v>
       </c>
       <c r="D262" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E262">
         <v>3.529413159454653</v>
@@ -14632,7 +14638,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14646,7 +14652,7 @@
         <v>3.637585058248958</v>
       </c>
       <c r="D263" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E263">
         <v>3.529413159454653</v>
@@ -14682,7 +14688,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14696,7 +14702,7 @@
         <v>3.405388602484038</v>
       </c>
       <c r="D264" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E264">
         <v>3.509413159454653</v>
@@ -14732,7 +14738,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14746,7 +14752,7 @@
         <v>3.405511387337113</v>
       </c>
       <c r="D265" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E265">
         <v>3.509413159454653</v>
@@ -14782,7 +14788,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14796,7 +14802,7 @@
         <v>3.451364045513422</v>
       </c>
       <c r="D266" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E266">
         <v>3.509413159454653</v>
@@ -14832,7 +14838,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14846,7 +14852,7 @@
         <v>4.004636932335591</v>
       </c>
       <c r="D267" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E267">
         <v>3.867442887120403</v>
@@ -14896,7 +14902,7 @@
         <v>3.774439165379895</v>
       </c>
       <c r="D268" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E268">
         <v>3.837640654076098</v>
@@ -14946,7 +14952,7 @@
         <v>4.220199786446392</v>
       </c>
       <c r="D269" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E269">
         <v>4.085943565478028</v>
@@ -14982,7 +14988,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -14996,7 +15002,7 @@
         <v>3.991103703583256</v>
       </c>
       <c r="D270" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E270">
         <v>4.0441357312043</v>
@@ -15032,7 +15038,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15046,7 +15052,7 @@
         <v>4.24807262091024</v>
       </c>
       <c r="D271" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E271">
         <v>4.172298835483293</v>
@@ -15082,7 +15088,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15096,7 +15102,7 @@
         <v>4.076733299050661</v>
       </c>
       <c r="D272" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E272">
         <v>4.185185728196767</v>
@@ -15132,7 +15138,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15196,7 +15202,7 @@
         <v>3.853669569225198</v>
       </c>
       <c r="D274" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E274">
         <v>3.960609701897911</v>
@@ -15332,7 +15338,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15346,7 +15352,7 @@
         <v>3.457860783201086</v>
       </c>
       <c r="D277" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E277">
         <v>3.562117466477025</v>
@@ -15382,7 +15388,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15396,7 +15402,7 @@
         <v>3.461796612382101</v>
       </c>
       <c r="D278" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E278">
         <v>3.45818163729601</v>
@@ -15432,7 +15438,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15496,7 +15502,7 @@
         <v>1.876063224574707</v>
       </c>
       <c r="D280" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E280">
         <v>1.926860456775207</v>
@@ -15546,7 +15552,7 @@
         <v>1.879462993924748</v>
       </c>
       <c r="D281" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E281">
         <v>1.926860456775207</v>
@@ -15596,7 +15602,7 @@
         <v>1.36286186891499</v>
       </c>
       <c r="D282" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E282">
         <v>1.420876924621103</v>
@@ -15632,7 +15638,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15646,7 +15652,7 @@
         <v>1.365396205962064</v>
       </c>
       <c r="D283" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E283">
         <v>1.420876924621103</v>
@@ -15682,7 +15688,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15696,7 +15702,7 @@
         <v>1.492587172538397</v>
       </c>
       <c r="D284" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E284">
         <v>1.422587172538397</v>
@@ -15732,7 +15738,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15746,7 +15752,7 @@
         <v>1.155028253713973</v>
       </c>
       <c r="D285" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E285">
         <v>1.207786135342488</v>
@@ -15796,7 +15802,7 @@
         <v>1.157212112489207</v>
       </c>
       <c r="D286" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E286">
         <v>1.207786135342488</v>
@@ -15846,7 +15852,7 @@
         <v>1.287557383512098</v>
       </c>
       <c r="D287" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E287">
         <v>1.260086513310223</v>
@@ -15896,7 +15902,7 @@
         <v>-0.2566084186298667</v>
       </c>
       <c r="D288" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E288">
         <v>-0.001048450451905936</v>
@@ -15932,7 +15938,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15946,7 +15952,7 @@
         <v>-0.2875710874180024</v>
       </c>
       <c r="D289" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E289">
         <v>-0.001048450451905936</v>
@@ -15982,7 +15988,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16032,7 +16038,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16082,7 +16088,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16096,7 +16102,7 @@
         <v>-0.3429456734762377</v>
       </c>
       <c r="D292" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E292">
         <v>-0.1559309932859021</v>
@@ -16132,7 +16138,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16146,7 +16152,7 @@
         <v>-0.452945673476238</v>
       </c>
       <c r="D293" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E293">
         <v>-0.1559309932859021</v>
@@ -16182,7 +16188,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16196,7 +16202,7 @@
         <v>-0.07614423041516449</v>
       </c>
       <c r="D294" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E294">
         <v>-0.08649962563060054</v>
@@ -16232,7 +16238,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16246,7 +16252,7 @@
         <v>-0.06685502084603723</v>
       </c>
       <c r="D295" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E295">
         <v>-0.08649962563060054</v>
@@ -16282,7 +16288,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16296,7 +16302,7 @@
         <v>-0.6325763258089658</v>
       </c>
       <c r="D296" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E296">
         <v>-0.7397037652284588</v>
@@ -16332,7 +16338,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16346,7 +16352,7 @@
         <v>-0.6888811406779016</v>
       </c>
       <c r="D297" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E297">
         <v>-0.6347573064746772</v>
@@ -16382,7 +16388,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16396,7 +16402,7 @@
         <v>-0.5922830059527424</v>
       </c>
       <c r="D298" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E298">
         <v>-0.6988811406779014</v>
@@ -16432,7 +16438,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16446,7 +16452,7 @@
         <v>-0.7708727781363214</v>
       </c>
       <c r="D299" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E299">
         <v>-0.7160845060282481</v>
@@ -16482,7 +16488,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16496,7 +16502,7 @@
         <v>-0.6732115427634033</v>
       </c>
       <c r="D300" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E300">
         <v>-0.7808727781363212</v>
@@ -16532,7 +16538,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16546,7 +16552,7 @@
         <v>-0.6051723879795468</v>
       </c>
       <c r="D301" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E301">
         <v>-0.5517269067155315</v>
@@ -16582,7 +16588,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16596,7 +16602,7 @@
         <v>-0.509659617957122</v>
       </c>
       <c r="D302" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E302">
         <v>-0.6151723879795465</v>
@@ -16632,7 +16638,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16646,7 +16652,7 @@
         <v>1.374867998585327</v>
       </c>
       <c r="D303" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E303">
         <v>1.61428021608427</v>
@@ -16682,7 +16688,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16696,7 +16702,7 @@
         <v>1.37455579980999</v>
       </c>
       <c r="D304" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E304">
         <v>1.61428021608427</v>
@@ -16732,7 +16738,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16746,7 +16752,7 @@
         <v>1.659046067002767</v>
       </c>
       <c r="D305" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E305">
         <v>1.701663141543517</v>
@@ -16782,7 +16788,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16796,7 +16802,7 @@
         <v>1.400425101402588</v>
       </c>
       <c r="D306" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E306">
         <v>1.63789275673065</v>
@@ -16832,7 +16838,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16846,7 +16852,7 @@
         <v>1.415426421593279</v>
       </c>
       <c r="D307" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E307">
         <v>1.63789275673065</v>
@@ -16882,7 +16888,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16896,7 +16902,7 @@
         <v>1.672891436539961</v>
       </c>
       <c r="D308" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E308">
         <v>1.702888796158578</v>
@@ -16932,7 +16938,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16946,7 +16952,7 @@
         <v>1.682896717302726</v>
       </c>
       <c r="D309" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E309">
         <v>1.702888796158578</v>
@@ -16982,7 +16988,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -16996,7 +17002,7 @@
         <v>1.392287936404873</v>
       </c>
       <c r="D310" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E310">
         <v>1.630374723852328</v>
@@ -17032,7 +17038,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17046,7 +17052,7 @@
         <v>1.392192134372636</v>
       </c>
       <c r="D311" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E311">
         <v>1.630374723852328</v>
@@ -17082,7 +17088,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17096,7 +17102,7 @@
         <v>1.665398674360388</v>
       </c>
       <c r="D312" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E312">
         <v>1.367982501138595</v>
@@ -17132,7 +17138,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17146,7 +17152,7 @@
         <v>1.67530287232815</v>
       </c>
       <c r="D313" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E313">
         <v>1.367982501138595</v>
@@ -17182,7 +17188,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17196,7 +17202,7 @@
         <v>1.683187064752997</v>
       </c>
       <c r="D314" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E314">
         <v>1.385560910531628</v>
@@ -17232,7 +17238,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17246,7 +17252,7 @@
         <v>1.693331241005988</v>
       </c>
       <c r="D315" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E315">
         <v>1.385560910531628</v>
@@ -17282,7 +17288,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17296,7 +17302,7 @@
         <v>1.671335210176903</v>
       </c>
       <c r="D316" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E316">
         <v>1.373848959803819</v>
@@ -17332,7 +17338,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17346,7 +17352,7 @@
         <v>1.68131949631757</v>
       </c>
       <c r="D317" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E317">
         <v>1.373848959803819</v>
@@ -17382,7 +17388,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17396,7 +17402,7 @@
         <v>1.693875753393727</v>
       </c>
       <c r="D318" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E318">
         <v>1.396123425781996</v>
@@ -17432,7 +17438,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17446,7 +17452,7 @@
         <v>1.704164127807133</v>
       </c>
       <c r="D319" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E319">
         <v>1.396123425781996</v>
@@ -17482,7 +17488,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17496,7 +17502,7 @@
         <v>1.366123425781996</v>
       </c>
       <c r="D320" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E320">
         <v>1.403731566187024</v>
@@ -17532,7 +17538,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17546,7 +17552,7 @@
         <v>1.710631890779994</v>
       </c>
       <c r="D321" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E321">
         <v>1.412681767280061</v>
@@ -17582,7 +17588,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17596,7 +17602,7 @@
         <v>1.72114631763706</v>
       </c>
       <c r="D322" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E322">
         <v>1.412681767280061</v>
@@ -17632,7 +17638,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17646,7 +17652,7 @@
         <v>1.382681767280062</v>
       </c>
       <c r="D323" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E323">
         <v>1.420374677351461</v>
@@ -17682,7 +17688,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17696,7 +17702,7 @@
         <v>1.679206240881443</v>
       </c>
       <c r="D324" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E324">
         <v>1.381627077835624</v>
@@ -17746,7 +17752,7 @@
         <v>1.689296712933807</v>
       </c>
       <c r="D325" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E325">
         <v>1.381627077835624</v>
@@ -17796,7 +17802,7 @@
         <v>1.351627077835625</v>
       </c>
       <c r="D326" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E326">
         <v>1.364138386842169</v>
@@ -17846,7 +17852,7 @@
         <v>1.662615013806636</v>
       </c>
       <c r="D327" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E327">
         <v>1.365231699984297</v>
@@ -17882,7 +17888,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17896,7 +17902,7 @@
         <v>1.672481658175022</v>
       </c>
       <c r="D328" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E328">
         <v>1.365231699984297</v>
@@ -17932,7 +17938,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17946,7 +17952,7 @@
         <v>1.335231699984297</v>
       </c>
       <c r="D329" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E329">
         <v>1.330198361076394</v>
@@ -17982,7 +17988,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -17996,7 +18002,7 @@
         <v>1.638483426036899</v>
       </c>
       <c r="D330" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E330">
         <v>1.341384970754843</v>
@@ -18046,7 +18052,7 @@
         <v>1.648024517787818</v>
       </c>
       <c r="D331" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E331">
         <v>1.341384970754843</v>
@@ -18146,7 +18152,7 @@
         <v>1.611118158429232</v>
       </c>
       <c r="D333" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E333">
         <v>1.31434273328757</v>
@@ -18196,7 +18202,7 @@
         <v>1.620290072876844</v>
       </c>
       <c r="D334" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E334">
         <v>1.31434273328757</v>
@@ -18246,7 +18252,7 @@
         <v>1.210704115653037</v>
       </c>
       <c r="D335" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E335">
         <v>1.321946243981619</v>
@@ -18296,7 +18302,7 @@
         <v>1.250704115653037</v>
       </c>
       <c r="D336" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E336">
         <v>1.321946243981619</v>
@@ -18346,7 +18352,7 @@
         <v>1.580824889600507</v>
       </c>
       <c r="D337" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E337">
         <v>1.284407057851428</v>
@@ -18382,7 +18388,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18396,7 +18402,7 @@
         <v>1.589588125885168</v>
       </c>
       <c r="D338" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E338">
         <v>1.284407057851428</v>
@@ -18432,7 +18438,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18446,7 +18452,7 @@
         <v>1.180206507742837</v>
       </c>
       <c r="D339" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E339">
         <v>1.27675246238701</v>
@@ -18482,7 +18488,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18496,7 +18502,7 @@
         <v>1.220206507742837</v>
       </c>
       <c r="D340" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E340">
         <v>1.27675246238701</v>
@@ -18532,7 +18538,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18546,7 +18552,7 @@
         <v>1.680056540073359</v>
       </c>
       <c r="D341" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E341">
         <v>1.409353064352823</v>
@@ -18582,7 +18588,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18596,7 +18602,7 @@
         <v>1.717732409003494</v>
       </c>
       <c r="D342" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E342">
         <v>1.409353064352823</v>
@@ -18632,7 +18638,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18646,7 +18652,7 @@
         <v>1.307497917096648</v>
       </c>
       <c r="D343" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E343">
         <v>1.444235818399402</v>
@@ -18682,7 +18688,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18696,7 +18702,7 @@
         <v>1.347497917096648</v>
       </c>
       <c r="D344" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E344">
         <v>1.444235818399402</v>
@@ -18732,7 +18738,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18746,7 +18752,7 @@
         <v>1.842256392262994</v>
       </c>
       <c r="D345" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E345">
         <v>1.530769127897027</v>
@@ -18796,7 +18802,7 @@
         <v>1.431193121765403</v>
       </c>
       <c r="D346" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E346">
         <v>1.572471675023835</v>
@@ -18846,7 +18852,7 @@
         <v>1.471193121765403</v>
       </c>
       <c r="D347" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E347">
         <v>1.572471675023835</v>
@@ -18896,7 +18902,7 @@
         <v>2.306011000659936</v>
       </c>
       <c r="D348" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E348">
         <v>2.348379970519409</v>
@@ -18932,7 +18938,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18946,7 +18952,7 @@
         <v>2.400485390479259</v>
       </c>
       <c r="D349" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E349">
         <v>2.364696230398958</v>
@@ -18982,7 +18988,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19032,7 +19038,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19046,7 +19052,7 @@
         <v>2.315116384839492</v>
       </c>
       <c r="D351" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E351">
         <v>2.323814331699535</v>
@@ -19082,7 +19088,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19096,7 +19102,7 @@
         <v>2.158186337006185</v>
       </c>
       <c r="D352" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E352">
         <v>2.199105803820263</v>
@@ -19132,7 +19138,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19182,7 +19188,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19232,7 +19238,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19246,7 +19252,7 @@
         <v>2.249949180664442</v>
       </c>
       <c r="D355" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E355">
         <v>2.193589002935801</v>
@@ -19282,7 +19288,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19296,7 +19302,7 @@
         <v>3.29910210514231</v>
       </c>
       <c r="D356" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E356">
         <v>3.35230135785332</v>
@@ -19332,7 +19338,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19346,7 +19352,7 @@
         <v>3.804045197377832</v>
       </c>
       <c r="D357" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E357">
         <v>3.415154291605215</v>
@@ -19382,7 +19388,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19396,7 +19402,7 @@
         <v>3.427249571448392</v>
       </c>
       <c r="D358" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E358">
         <v>3.291626526785035</v>
@@ -19432,7 +19438,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19482,7 +19488,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19496,7 +19502,7 @@
         <v>3.442581197445604</v>
       </c>
       <c r="D360" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E360">
         <v>3.306414237004073</v>
@@ -19532,7 +19538,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19546,7 +19552,7 @@
         <v>3.36022431872702</v>
       </c>
       <c r="D361" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E361">
         <v>3.226979110080385</v>
@@ -19582,7 +19588,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19596,7 +19602,7 @@
         <v>3.251003700388559</v>
       </c>
       <c r="D362" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E362">
         <v>3.121633280862579</v>
@@ -19632,7 +19638,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19646,7 +19652,7 @@
         <v>2.99001278638902</v>
       </c>
       <c r="D363" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E363">
         <v>3.032275977245447</v>
@@ -19732,7 +19738,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19746,7 +19752,7 @@
         <v>2.786342722576059</v>
       </c>
       <c r="D365" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E365">
         <v>2.830017022419643</v>
@@ -19782,7 +19788,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19796,7 +19802,7 @@
         <v>2.881784622628198</v>
       </c>
       <c r="D366" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E366">
         <v>2.846342722576059</v>
@@ -19832,7 +19838,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19846,7 +19852,7 @@
         <v>2.713139299753176</v>
       </c>
       <c r="D367" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E367">
         <v>2.672915915531583</v>
@@ -19882,7 +19888,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19896,7 +19902,7 @@
         <v>2.722022378645214</v>
       </c>
       <c r="D368" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E368">
         <v>2.672915915531583</v>
@@ -19932,7 +19938,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19946,7 +19952,7 @@
         <v>2.643362683974768</v>
       </c>
       <c r="D369" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E369">
         <v>2.68802760764238</v>
@@ -19982,7 +19988,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -19996,7 +20002,7 @@
         <v>2.738474376085565</v>
       </c>
       <c r="D370" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E370">
         <v>2.678250991863972</v>
@@ -20032,7 +20038,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20046,7 +20052,7 @@
         <v>2.26156876679942</v>
       </c>
       <c r="D371" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E371">
         <v>2.319500204055783</v>
@@ -20082,7 +20088,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20096,7 +20102,7 @@
         <v>2.341086491507057</v>
       </c>
       <c r="D372" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E372">
         <v>2.284741341701965</v>
@@ -20132,7 +20138,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20146,7 +20152,7 @@
         <v>2.25156876679942</v>
       </c>
       <c r="D373" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E373">
         <v>2.298948197976329</v>
@@ -20182,7 +20188,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20196,7 +20202,7 @@
         <v>2.345775623073784</v>
       </c>
       <c r="D374" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E374">
         <v>2.287361910525056</v>
@@ -20232,7 +20238,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20246,7 +20252,7 @@
         <v>1.450725995788351</v>
       </c>
       <c r="D375" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E375">
         <v>1.543612412630503</v>
@@ -20282,7 +20288,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20296,7 +20302,7 @@
         <v>1.378039753255653</v>
       </c>
       <c r="D376" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E376">
         <v>1.473954763536668</v>
@@ -20332,7 +20338,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20346,7 +20352,7 @@
         <v>2.300473418774809</v>
       </c>
       <c r="D377" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E377">
         <v>2.269274816103397</v>
@@ -20396,7 +20402,7 @@
         <v>2.307737312105645</v>
       </c>
       <c r="D378" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E378">
         <v>2.269274816103397</v>
@@ -20446,7 +20452,7 @@
         <v>2.548688372146674</v>
       </c>
       <c r="D379" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E379">
         <v>2.44021981851742</v>
@@ -20482,7 +20488,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20496,7 +20502,7 @@
         <v>4.064626779899114</v>
       </c>
       <c r="D380" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E380">
         <v>3.971827788774664</v>
@@ -20532,7 +20538,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20546,7 +20552,7 @@
         <v>2.704221825320051</v>
       </c>
       <c r="D381" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E381">
         <v>2.757514946748523</v>
@@ -20582,7 +20588,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20596,7 +20602,7 @@
         <v>2.699698304540886</v>
       </c>
       <c r="D382" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E382">
         <v>2.757514946748523</v>
@@ -20632,7 +20638,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20646,7 +20652,7 @@
         <v>2.597723564836138</v>
       </c>
       <c r="D383" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E383">
         <v>2.648687698460786</v>
@@ -20682,7 +20688,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20696,7 +20702,7 @@
         <v>2.594470401040876</v>
       </c>
       <c r="D384" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E384">
         <v>2.648687698460786</v>
@@ -20732,7 +20738,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20746,7 +20752,7 @@
         <v>2.5327482758737</v>
       </c>
       <c r="D385" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E385">
         <v>2.582291478725809</v>
@@ -20782,7 +20788,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20796,7 +20802,7 @@
         <v>2.530270165227095</v>
       </c>
       <c r="D386" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E386">
         <v>2.582291478725809</v>
@@ -20832,7 +20838,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20846,7 +20852,7 @@
         <v>2.615226386520305</v>
       </c>
       <c r="D387" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E387">
         <v>2.605226386520305</v>
@@ -20882,7 +20888,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20896,7 +20902,7 @@
         <v>2.519210324106</v>
       </c>
       <c r="D388" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E388">
         <v>2.474919909368535</v>
@@ -20932,7 +20938,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20946,7 +20952,7 @@
         <v>2.443973795685154</v>
       </c>
       <c r="D389" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E389">
         <v>2.491575608314453</v>
@@ -20982,7 +20988,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -20996,7 +21002,7 @@
         <v>2.442554625160083</v>
       </c>
       <c r="D390" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E390">
         <v>2.491575608314453</v>
@@ -21032,7 +21038,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21082,7 +21088,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21096,7 +21102,7 @@
         <v>2.457705873063223</v>
       </c>
       <c r="D392" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E392">
         <v>2.413049360402885</v>
@@ -21132,7 +21138,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21146,7 +21152,7 @@
         <v>2.382591377283335</v>
       </c>
       <c r="D393" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E393">
         <v>2.428850830862097</v>
@@ -21182,7 +21188,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21196,7 +21202,7 @@
         <v>2.381904402604011</v>
       </c>
       <c r="D394" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E394">
         <v>2.428850830862097</v>
@@ -21232,7 +21238,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21246,7 +21252,7 @@
         <v>2.46327835196266</v>
       </c>
       <c r="D395" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E395">
         <v>2.453507343522435</v>
@@ -21282,7 +21288,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21296,7 +21302,7 @@
         <v>2.467705873063223</v>
       </c>
       <c r="D396" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E396">
         <v>2.453507343522435</v>
@@ -21332,7 +21338,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21346,7 +21352,7 @@
         <v>2.447999298642713</v>
       </c>
       <c r="D397" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E397">
         <v>2.403285008753682</v>
@@ -21382,7 +21388,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21396,7 +21402,7 @@
         <v>2.372904061939057</v>
       </c>
       <c r="D398" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E398">
         <v>2.418951665679276</v>
@@ -21432,7 +21438,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21446,7 +21452,7 @@
         <v>2.37233264171712</v>
       </c>
       <c r="D399" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E399">
         <v>2.418951665679276</v>
@@ -21482,7 +21488,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21532,7 +21538,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21582,7 +21588,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21596,7 +21602,7 @@
         <v>2.414261420787727</v>
       </c>
       <c r="D402" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E402">
         <v>2.369346310197177</v>
@@ -21632,7 +21638,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21682,7 +21688,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21732,7 +21738,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21746,7 +21752,7 @@
         <v>2.424261420787727</v>
       </c>
       <c r="D405" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E405">
         <v>2.394544385485897</v>
@@ -21782,7 +21788,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21796,7 +21802,7 @@
         <v>2.414374606666995</v>
       </c>
       <c r="D406" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E406">
         <v>2.394544385485897</v>
@@ -21832,7 +21838,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21846,7 +21852,7 @@
         <v>2.397600622679596</v>
       </c>
       <c r="D407" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E407">
         <v>2.352586340671736</v>
@@ -21882,7 +21888,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21896,7 +21902,7 @@
         <v>2.322605383348882</v>
       </c>
       <c r="D408" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E408">
         <v>2.367553015986731</v>
@@ -21932,7 +21938,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21946,7 +21952,7 @@
         <v>2.322633947364601</v>
       </c>
       <c r="D409" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E409">
         <v>2.367553015986731</v>
@@ -21982,7 +21988,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -21996,7 +22002,7 @@
         <v>2.402576819333163</v>
       </c>
       <c r="D410" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E410">
         <v>2.35256729799459</v>
@@ -22032,7 +22038,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22046,7 +22052,7 @@
         <v>2.407600622679595</v>
       </c>
       <c r="D411" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E411">
         <v>2.35256729799459</v>
@@ -22082,7 +22088,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22096,7 +22102,7 @@
         <v>2.39758158000245</v>
       </c>
       <c r="D412" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E412">
         <v>2.35256729799459</v>
@@ -22132,7 +22138,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22146,7 +22152,7 @@
         <v>2.378737718650321</v>
       </c>
       <c r="D413" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E413">
         <v>2.33361115745181</v>
@@ -22182,7 +22188,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22196,7 +22202,7 @@
         <v>2.30377990571649</v>
       </c>
       <c r="D414" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E414">
         <v>2.348315847988621</v>
@@ -22232,7 +22238,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22246,7 +22252,7 @@
         <v>2.304033028113511</v>
       </c>
       <c r="D415" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E415">
         <v>2.348315847988621</v>
@@ -22282,7 +22288,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22296,7 +22302,7 @@
         <v>2.383526783319471</v>
       </c>
       <c r="D416" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E416">
         <v>2.333442409187131</v>
@@ -22332,7 +22338,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22346,7 +22352,7 @@
         <v>2.38873771865032</v>
       </c>
       <c r="D417" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E417">
         <v>2.333442409187131</v>
@@ -22382,7 +22388,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22396,7 +22402,7 @@
         <v>2.378568970385641</v>
       </c>
       <c r="D418" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E418">
         <v>2.333442409187131</v>
@@ -22432,7 +22438,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22446,7 +22452,7 @@
         <v>2.29477967980894</v>
       </c>
       <c r="D419" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E419">
         <v>2.33911879805526</v>
@@ -22496,7 +22502,7 @@
         <v>2.295140160765494</v>
       </c>
       <c r="D420" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E420">
         <v>2.33911879805526</v>
@@ -22546,7 +22552,7 @@
         <v>2.374419198852388</v>
       </c>
       <c r="D421" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E421">
         <v>2.324299038533536</v>
@@ -22596,7 +22602,7 @@
         <v>2.379719599649515</v>
       </c>
       <c r="D422" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E422">
         <v>2.324299038533536</v>
@@ -22646,7 +22652,7 @@
         <v>2.369479279011813</v>
       </c>
       <c r="D423" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E423">
         <v>2.324299038533536</v>
@@ -22696,7 +22702,7 @@
         <v>2.280590400920047</v>
       </c>
       <c r="D424" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E424">
         <v>2.324619216844741</v>
@@ -22732,7 +22738,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22746,7 +22752,7 @@
         <v>2.281120137688396</v>
       </c>
       <c r="D425" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E425">
         <v>2.324619216844741</v>
@@ -22782,7 +22788,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22796,7 +22802,7 @@
         <v>2.360060664151698</v>
       </c>
       <c r="D426" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E426">
         <v>2.309884085228915</v>
@@ -22832,7 +22838,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22882,7 +22888,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22896,7 +22902,7 @@
         <v>2.281700069738552</v>
       </c>
       <c r="D428" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E428">
         <v>2.325753152774585</v>
@@ -22932,7 +22938,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -22946,7 +22952,7 @@
         <v>2.282216569900716</v>
       </c>
       <c r="D429" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E429">
         <v>2.325753152774585</v>
@@ -22982,7 +22988,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -22996,7 +23002,7 @@
         <v>2.361183569576388</v>
       </c>
       <c r="D430" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E430">
         <v>2.311011402855666</v>
@@ -23032,7 +23038,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23046,7 +23052,7 @@
         <v>2.255753152774584</v>
       </c>
       <c r="D431" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E431">
         <v>2.30032273597278</v>
@@ -23082,7 +23088,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23096,7 +23102,7 @@
         <v>2.248769782041177</v>
       </c>
       <c r="D432" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E432">
         <v>2.297801715354081</v>
@@ -23132,7 +23138,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23146,7 +23152,7 @@
         <v>2.343406757033516</v>
       </c>
       <c r="D433" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E433">
         <v>2.293164740361742</v>
@@ -23182,7 +23188,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23196,7 +23202,7 @@
         <v>2.237801715354081</v>
       </c>
       <c r="D434" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E434">
         <v>2.26243869034642</v>
@@ -23232,7 +23238,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23246,7 +23252,7 @@
         <v>2.228095614122554</v>
       </c>
       <c r="D435" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E435">
         <v>2.276800683120539</v>
@@ -23282,7 +23288,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23296,7 +23302,7 @@
         <v>2.322610014996799</v>
       </c>
       <c r="D436" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E436">
         <v>2.263257480497806</v>
@@ -23332,7 +23338,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23382,7 +23388,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23396,7 +23402,7 @@
         <v>2.224983216186275</v>
       </c>
       <c r="D438" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E438">
         <v>2.273639077311749</v>
@@ -23446,7 +23452,7 @@
         <v>2.319479164108328</v>
       </c>
       <c r="D439" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E439">
         <v>2.26015123354559</v>
@@ -23596,7 +23602,7 @@
         <v>2.3116287572162</v>
       </c>
       <c r="D442" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E442">
         <v>2.252362519438469</v>
@@ -23632,7 +23638,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23682,7 +23688,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23732,7 +23738,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23796,7 +23802,7 @@
         <v>2.185149484739352</v>
       </c>
       <c r="D446" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E446">
         <v>2.165149484739352</v>
@@ -23896,7 +23902,7 @@
         <v>2.20020073233055</v>
       </c>
       <c r="D448" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E448">
         <v>2.205687152603988</v>
@@ -23982,7 +23988,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24032,7 +24038,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24082,7 +24088,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24132,7 +24138,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24182,7 +24188,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24296,7 +24302,7 @@
         <v>2.142114930387524</v>
       </c>
       <c r="D456" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E456">
         <v>2.162114930387524</v>
@@ -24332,7 +24338,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24346,7 +24352,7 @@
         <v>2.115413806995409</v>
       </c>
       <c r="D457" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E457">
         <v>2.141244762127619</v>
@@ -24432,7 +24438,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24446,7 +24452,7 @@
         <v>2.073994682974101</v>
       </c>
       <c r="D459" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E459">
         <v>2.082201671198685</v>
@@ -24496,7 +24502,7 @@
         <v>2.083994682974101</v>
       </c>
       <c r="D460" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E460">
         <v>2.082201671198685</v>
@@ -24582,7 +24588,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24596,7 +24602,7 @@
         <v>2.057461365020192</v>
       </c>
       <c r="D462" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E462">
         <v>2.066125824243982</v>
@@ -24632,7 +24638,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24682,7 +24688,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24732,7 +24738,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24782,7 +24788,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24832,7 +24838,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24846,7 +24852,7 @@
         <v>2.057577737614682</v>
       </c>
       <c r="D467" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E467">
         <v>2.099815205781953</v>
@@ -24882,7 +24888,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24946,7 +24952,7 @@
         <v>2.075267052489131</v>
       </c>
       <c r="D469" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E469">
         <v>2.105974841560053</v>
@@ -24996,7 +25002,7 @@
         <v>2.0673904197019</v>
       </c>
       <c r="D470" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E470">
         <v>2.109513786914668</v>
@@ -25046,7 +25052,7 @@
         <v>2.101281730695467</v>
       </c>
       <c r="D471" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E471">
         <v>2.131889846669813</v>
@@ -25096,7 +25102,7 @@
         <v>2.093106078618507</v>
       </c>
       <c r="D472" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E472">
         <v>2.134930426541548</v>
@@ -25146,7 +25152,7 @@
         <v>2.114232378900782</v>
       </c>
       <c r="D473" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E473">
         <v>2.144790875533345</v>
@@ -25182,7 +25188,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25196,7 +25202,7 @@
         <v>2.164790875533345</v>
       </c>
       <c r="D474" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E474">
         <v>2.134232378900781</v>
@@ -25232,7 +25238,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25246,7 +25252,7 @@
         <v>2.105907868798473</v>
       </c>
       <c r="D475" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E475">
         <v>2.147583358696166</v>
@@ -25282,7 +25288,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25296,7 +25302,7 @@
         <v>2.178667208693582</v>
       </c>
       <c r="D476" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E476">
         <v>2.148162082573172</v>
@@ -25332,7 +25338,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25346,7 +25352,7 @@
         <v>2.119677460934401</v>
       </c>
       <c r="D477" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E477">
         <v>2.161192839295628</v>
@@ -25382,7 +25388,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25396,7 +25402,7 @@
         <v>2.191253934723685</v>
       </c>
       <c r="D478" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E478">
         <v>2.160797219088007</v>
@@ -25446,7 +25452,7 @@
         <v>2.132167365995042</v>
       </c>
       <c r="D479" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E479">
         <v>2.173537512902076</v>
@@ -25546,7 +25552,7 @@
         <v>2.161339958759847</v>
       </c>
       <c r="D481" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E481">
         <v>2.202370889471942</v>
@@ -25596,7 +25602,7 @@
         <v>2.215480849833102</v>
       </c>
       <c r="D482" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E482">
         <v>2.179965384477054</v>
@@ -25646,7 +25652,7 @@
         <v>1.276065947508897</v>
       </c>
       <c r="D483" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E483">
         <v>1.317566169928825</v>
@@ -25682,7 +25688,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25696,7 +25702,7 @@
         <v>1.37689891014235</v>
       </c>
       <c r="D484" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E484">
         <v>1.288399132562277</v>
@@ -25732,7 +25738,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25746,7 +25752,7 @@
         <v>1.376065947508897</v>
       </c>
       <c r="D485" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E485">
         <v>1.316898910142349</v>
@@ -25782,7 +25788,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25796,7 +25802,7 @@
         <v>1.265250934212467</v>
       </c>
       <c r="D486" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E486">
         <v>1.306889515011455</v>
@@ -25832,7 +25838,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25846,7 +25852,7 @@
         <v>1.365853299547489</v>
       </c>
       <c r="D487" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E487">
         <v>1.277491880346475</v>
@@ -25882,7 +25888,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25896,7 +25902,7 @@
         <v>1.365250934212467</v>
       </c>
       <c r="D488" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E488">
         <v>1.305853299547488</v>
@@ -25932,7 +25938,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25946,7 +25952,7 @@
         <v>1.257848770795328</v>
       </c>
       <c r="D489" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E489">
         <v>1.29958204878089</v>
@@ -25982,7 +25988,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -25996,7 +26002,7 @@
         <v>1.358293307486061</v>
       </c>
       <c r="D490" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E490">
         <v>1.270026585471621</v>
@@ -26032,7 +26038,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26046,7 +26052,7 @@
         <v>1.357848770795329</v>
       </c>
       <c r="D491" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E491">
         <v>1.298293307486061</v>
@@ -26082,7 +26088,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26096,7 +26102,7 @@
         <v>1.336383675279734</v>
       </c>
       <c r="D492" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E492">
         <v>1.248391395422367</v>
@@ -26146,7 +26152,7 @@
         <v>1.336396542184123</v>
       </c>
       <c r="D493" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E493">
         <v>1.276383675279734</v>
@@ -26183,6 +26189,56 @@
       </c>
       <c r="P493" t="s">
         <v>146</v>
+      </c>
+    </row>
+    <row r="494" spans="1:16">
+      <c r="A494" s="1">
+        <v>0</v>
+      </c>
+      <c r="B494" t="s">
+        <v>149</v>
+      </c>
+      <c r="C494">
+        <v>1.1949083591831</v>
+      </c>
+      <c r="D494" t="s">
+        <v>147</v>
+      </c>
+      <c r="E494">
+        <v>1.279467032224208</v>
+      </c>
+      <c r="F494">
+        <v>1</v>
+      </c>
+      <c r="G494">
+        <v>0.0078450916408169</v>
+      </c>
+      <c r="H494">
+        <v>0.008100532967775794</v>
+      </c>
+      <c r="I494">
+        <v>0.08455867304110809</v>
+      </c>
+      <c r="J494">
+        <v>0.7120110579907708</v>
+      </c>
+      <c r="K494">
+        <v>4.67</v>
+      </c>
+      <c r="L494">
+        <v>4.52</v>
+      </c>
+      <c r="M494">
+        <v>4.79</v>
+      </c>
+      <c r="N494">
+        <v>4.69</v>
+      </c>
+      <c r="O494">
+        <v>1</v>
+      </c>
+      <c r="P494" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-03328-601328.xlsx
+++ b/s60_signal/position-03328-601328.xlsx
@@ -835,7 +835,7 @@
     <t>2021-11-02</t>
   </si>
   <si>
-    <t>2021-11-09</t>
+    <t>2021-11-10</t>
   </si>
   <si>
     <t>2016-05-24</t>
@@ -25755,7 +25755,7 @@
         <v>273</v>
       </c>
       <c r="E485">
-        <v>1.316898910142349</v>
+        <v>1.325315836298933</v>
       </c>
       <c r="F485">
         <v>-1</v>
@@ -25764,10 +25764,10 @@
         <v>0.007863934052491103</v>
       </c>
       <c r="H485">
-        <v>0.00794310108985765</v>
+        <v>0.007854684163701067</v>
       </c>
       <c r="I485">
-        <v>0.05916703736654805</v>
+        <v>0.0507501112099642</v>
       </c>
       <c r="J485">
         <v>0.6916703736654803</v>
@@ -25779,10 +25779,10 @@
         <v>4.62</v>
       </c>
       <c r="M485">
-        <v>4.79</v>
+        <v>4.72</v>
       </c>
       <c r="N485">
-        <v>4.63</v>
+        <v>4.59</v>
       </c>
       <c r="O485">
         <v>1</v>
@@ -25905,7 +25905,7 @@
         <v>273</v>
       </c>
       <c r="E488">
-        <v>1.305853299547488</v>
+        <v>1.314431643812974</v>
       </c>
       <c r="F488">
         <v>-1</v>
@@ -25914,10 +25914,10 @@
         <v>0.007874749065787534</v>
       </c>
       <c r="H488">
-        <v>0.007954146700452512</v>
+        <v>0.007865568356187026</v>
       </c>
       <c r="I488">
-        <v>0.05939763466497938</v>
+        <v>0.05081929039949351</v>
       </c>
       <c r="J488">
         <v>0.6939763466497937</v>
@@ -25929,10 +25929,10 @@
         <v>4.62</v>
       </c>
       <c r="M488">
-        <v>4.79</v>
+        <v>4.72</v>
       </c>
       <c r="N488">
-        <v>4.63</v>
+        <v>4.59</v>
       </c>
       <c r="O488">
         <v>1</v>
@@ -26055,7 +26055,7 @@
         <v>273</v>
       </c>
       <c r="E491">
-        <v>1.298293307486061</v>
+        <v>1.306982131802549</v>
       </c>
       <c r="F491">
         <v>-1</v>
@@ -26064,10 +26064,10 @@
         <v>0.007882151229204671</v>
       </c>
       <c r="H491">
-        <v>0.007961706692513939</v>
+        <v>0.007873017868197451</v>
       </c>
       <c r="I491">
-        <v>0.05955546330926786</v>
+        <v>0.0508666389927801</v>
       </c>
       <c r="J491">
         <v>0.6955546330926804</v>
@@ -26079,10 +26079,10 @@
         <v>4.62</v>
       </c>
       <c r="M491">
-        <v>4.79</v>
+        <v>4.72</v>
       </c>
       <c r="N491">
-        <v>4.63</v>
+        <v>4.59</v>
       </c>
       <c r="O491">
         <v>1</v>
@@ -26155,7 +26155,7 @@
         <v>273</v>
       </c>
       <c r="E493">
-        <v>1.276383675279734</v>
+        <v>1.285392682112807</v>
       </c>
       <c r="F493">
         <v>-1</v>
@@ -26164,10 +26164,10 @@
         <v>0.007903603457815878</v>
       </c>
       <c r="H493">
-        <v>0.007983616324720267</v>
+        <v>0.007894607317887194</v>
       </c>
       <c r="I493">
-        <v>0.06001286690438956</v>
+        <v>0.05100386007131652</v>
       </c>
       <c r="J493">
         <v>0.7001286690438969</v>
@@ -26179,10 +26179,10 @@
         <v>4.62</v>
       </c>
       <c r="M493">
-        <v>4.79</v>
+        <v>4.72</v>
       </c>
       <c r="N493">
-        <v>4.63</v>
+        <v>4.59</v>
       </c>
       <c r="O493">
         <v>1</v>

--- a/s60_signal/position-03328-601328.xlsx
+++ b/s60_signal/position-03328-601328.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="390">
   <si>
     <t>trade_time</t>
   </si>
@@ -835,7 +835,7 @@
     <t>2021-11-02</t>
   </si>
   <si>
-    <t>2021-11-10</t>
+    <t>2021-11-11</t>
   </si>
   <si>
     <t>2016-05-24</t>
@@ -1541,7 +1541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P494"/>
+  <dimension ref="A1:P491"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -25743,96 +25743,96 @@
     </row>
     <row r="485" spans="1:16">
       <c r="A485" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B485" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C485">
-        <v>1.376065947508897</v>
+        <v>1.265250934212467</v>
       </c>
       <c r="D485" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E485">
-        <v>1.325315836298933</v>
+        <v>1.306889515011455</v>
       </c>
       <c r="F485">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G485">
-        <v>0.007863934052491103</v>
+        <v>0.007774749065787532</v>
       </c>
       <c r="H485">
-        <v>0.007854684163701067</v>
+        <v>0.007733110484988545</v>
       </c>
       <c r="I485">
-        <v>0.0507501112099642</v>
+        <v>0.04163858079898786</v>
       </c>
       <c r="J485">
-        <v>0.6916703736654803</v>
+        <v>0.6939763466497937</v>
       </c>
       <c r="K485">
         <v>4.69</v>
       </c>
       <c r="L485">
-        <v>4.62</v>
+        <v>4.52</v>
       </c>
       <c r="M485">
-        <v>4.72</v>
+        <v>4.63</v>
       </c>
       <c r="N485">
-        <v>4.59</v>
+        <v>4.52</v>
       </c>
       <c r="O485">
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="486" spans="1:16">
       <c r="A486" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B486" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C486">
-        <v>1.265250934212467</v>
+        <v>1.365853299547489</v>
       </c>
       <c r="D486" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E486">
-        <v>1.306889515011455</v>
+        <v>1.277491880346475</v>
       </c>
       <c r="F486">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G486">
-        <v>0.007774749065787532</v>
+        <v>0.008014146700452512</v>
       </c>
       <c r="H486">
-        <v>0.007733110484988545</v>
+        <v>0.007842508119653525</v>
       </c>
       <c r="I486">
-        <v>0.04163858079898786</v>
+        <v>0.08836141920101337</v>
       </c>
       <c r="J486">
         <v>0.6939763466497937</v>
       </c>
       <c r="K486">
+        <v>4.79</v>
+      </c>
+      <c r="L486">
         <v>4.69</v>
       </c>
-      <c r="L486">
-        <v>4.52</v>
-      </c>
       <c r="M486">
-        <v>4.63</v>
+        <v>4.73</v>
       </c>
       <c r="N486">
-        <v>4.52</v>
+        <v>4.56</v>
       </c>
       <c r="O486">
         <v>1</v>
@@ -25843,131 +25843,131 @@
     </row>
     <row r="487" spans="1:16">
       <c r="A487" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B487" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C487">
-        <v>1.365853299547489</v>
+        <v>1.257848770795328</v>
       </c>
       <c r="D487" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E487">
-        <v>1.277491880346475</v>
+        <v>1.29958204878089</v>
       </c>
       <c r="F487">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G487">
-        <v>0.008014146700452512</v>
+        <v>0.007782151229204671</v>
       </c>
       <c r="H487">
-        <v>0.007842508119653525</v>
+        <v>0.00774041795121911</v>
       </c>
       <c r="I487">
-        <v>0.08836141920101337</v>
+        <v>0.04173327798556148</v>
       </c>
       <c r="J487">
-        <v>0.6939763466497937</v>
+        <v>0.6955546330926804</v>
       </c>
       <c r="K487">
-        <v>4.79</v>
+        <v>4.69</v>
       </c>
       <c r="L487">
-        <v>4.69</v>
+        <v>4.52</v>
       </c>
       <c r="M487">
-        <v>4.73</v>
+        <v>4.63</v>
       </c>
       <c r="N487">
-        <v>4.56</v>
+        <v>4.52</v>
       </c>
       <c r="O487">
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="488" spans="1:16">
       <c r="A488" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B488" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C488">
-        <v>1.365250934212467</v>
+        <v>1.358293307486061</v>
       </c>
       <c r="D488" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E488">
-        <v>1.314431643812974</v>
+        <v>1.270026585471621</v>
       </c>
       <c r="F488">
         <v>-1</v>
       </c>
       <c r="G488">
-        <v>0.007874749065787534</v>
+        <v>0.00802170669251394</v>
       </c>
       <c r="H488">
-        <v>0.007865568356187026</v>
+        <v>0.007849973414528378</v>
       </c>
       <c r="I488">
-        <v>0.05081929039949351</v>
+        <v>0.08826672201444019</v>
       </c>
       <c r="J488">
-        <v>0.6939763466497937</v>
+        <v>0.6955546330926804</v>
       </c>
       <c r="K488">
+        <v>4.79</v>
+      </c>
+      <c r="L488">
         <v>4.69</v>
       </c>
-      <c r="L488">
-        <v>4.62</v>
-      </c>
       <c r="M488">
-        <v>4.72</v>
+        <v>4.73</v>
       </c>
       <c r="N488">
-        <v>4.59</v>
+        <v>4.56</v>
       </c>
       <c r="O488">
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="489" spans="1:16">
       <c r="A489" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B489" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C489">
-        <v>1.257848770795328</v>
+        <v>1.357848770795329</v>
       </c>
       <c r="D489" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E489">
-        <v>1.29958204878089</v>
+        <v>1.328293307486061</v>
       </c>
       <c r="F489">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G489">
-        <v>0.007782151229204671</v>
+        <v>0.007882151229204671</v>
       </c>
       <c r="H489">
-        <v>0.00774041795121911</v>
+        <v>0.00799170669251394</v>
       </c>
       <c r="I489">
-        <v>0.04173327798556148</v>
+        <v>0.02955546330926762</v>
       </c>
       <c r="J489">
         <v>0.6955546330926804</v>
@@ -25976,13 +25976,13 @@
         <v>4.69</v>
       </c>
       <c r="L489">
-        <v>4.52</v>
+        <v>4.62</v>
       </c>
       <c r="M489">
-        <v>4.63</v>
+        <v>4.79</v>
       </c>
       <c r="N489">
-        <v>4.52</v>
+        <v>4.66</v>
       </c>
       <c r="O489">
         <v>1</v>
@@ -25993,34 +25993,34 @@
     </row>
     <row r="490" spans="1:16">
       <c r="A490" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B490" t="s">
         <v>147</v>
       </c>
       <c r="C490">
-        <v>1.358293307486061</v>
+        <v>1.336383675279734</v>
       </c>
       <c r="D490" t="s">
         <v>272</v>
       </c>
       <c r="E490">
-        <v>1.270026585471621</v>
+        <v>1.248391395422367</v>
       </c>
       <c r="F490">
         <v>-1</v>
       </c>
       <c r="G490">
-        <v>0.00802170669251394</v>
+        <v>0.008043616324720266</v>
       </c>
       <c r="H490">
-        <v>0.007849973414528378</v>
+        <v>0.007871608604577633</v>
       </c>
       <c r="I490">
-        <v>0.08826672201444019</v>
+        <v>0.08799227985736735</v>
       </c>
       <c r="J490">
-        <v>0.6955546330926804</v>
+        <v>0.7001286690438969</v>
       </c>
       <c r="K490">
         <v>4.79</v>
@@ -26038,206 +26038,56 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>388</v>
+        <v>146</v>
       </c>
     </row>
     <row r="491" spans="1:16">
       <c r="A491" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B491" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C491">
-        <v>1.357848770795329</v>
+        <v>1.1949083591831</v>
       </c>
       <c r="D491" t="s">
-        <v>273</v>
+        <v>147</v>
       </c>
       <c r="E491">
-        <v>1.306982131802549</v>
+        <v>1.279467032224208</v>
       </c>
       <c r="F491">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G491">
-        <v>0.007882151229204671</v>
+        <v>0.0078450916408169</v>
       </c>
       <c r="H491">
-        <v>0.007873017868197451</v>
+        <v>0.008100532967775794</v>
       </c>
       <c r="I491">
-        <v>0.0508666389927801</v>
+        <v>0.08455867304110809</v>
       </c>
       <c r="J491">
-        <v>0.6955546330926804</v>
+        <v>0.7120110579907708</v>
       </c>
       <c r="K491">
+        <v>4.67</v>
+      </c>
+      <c r="L491">
+        <v>4.52</v>
+      </c>
+      <c r="M491">
+        <v>4.79</v>
+      </c>
+      <c r="N491">
         <v>4.69</v>
       </c>
-      <c r="L491">
-        <v>4.62</v>
-      </c>
-      <c r="M491">
-        <v>4.72</v>
-      </c>
-      <c r="N491">
-        <v>4.59</v>
-      </c>
       <c r="O491">
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="492" spans="1:16">
-      <c r="A492" s="1">
-        <v>0</v>
-      </c>
-      <c r="B492" t="s">
-        <v>147</v>
-      </c>
-      <c r="C492">
-        <v>1.336383675279734</v>
-      </c>
-      <c r="D492" t="s">
-        <v>272</v>
-      </c>
-      <c r="E492">
-        <v>1.248391395422367</v>
-      </c>
-      <c r="F492">
-        <v>-1</v>
-      </c>
-      <c r="G492">
-        <v>0.008043616324720266</v>
-      </c>
-      <c r="H492">
-        <v>0.007871608604577633</v>
-      </c>
-      <c r="I492">
-        <v>0.08799227985736735</v>
-      </c>
-      <c r="J492">
-        <v>0.7001286690438969</v>
-      </c>
-      <c r="K492">
-        <v>4.79</v>
-      </c>
-      <c r="L492">
-        <v>4.69</v>
-      </c>
-      <c r="M492">
-        <v>4.73</v>
-      </c>
-      <c r="N492">
-        <v>4.56</v>
-      </c>
-      <c r="O492">
-        <v>1</v>
-      </c>
-      <c r="P492" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="493" spans="1:16">
-      <c r="A493" s="1">
-        <v>1</v>
-      </c>
-      <c r="B493" t="s">
-        <v>148</v>
-      </c>
-      <c r="C493">
-        <v>1.336396542184123</v>
-      </c>
-      <c r="D493" t="s">
-        <v>273</v>
-      </c>
-      <c r="E493">
-        <v>1.285392682112807</v>
-      </c>
-      <c r="F493">
-        <v>-1</v>
-      </c>
-      <c r="G493">
-        <v>0.007903603457815878</v>
-      </c>
-      <c r="H493">
-        <v>0.007894607317887194</v>
-      </c>
-      <c r="I493">
-        <v>0.05100386007131652</v>
-      </c>
-      <c r="J493">
-        <v>0.7001286690438969</v>
-      </c>
-      <c r="K493">
-        <v>4.69</v>
-      </c>
-      <c r="L493">
-        <v>4.62</v>
-      </c>
-      <c r="M493">
-        <v>4.72</v>
-      </c>
-      <c r="N493">
-        <v>4.59</v>
-      </c>
-      <c r="O493">
-        <v>1</v>
-      </c>
-      <c r="P493" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="494" spans="1:16">
-      <c r="A494" s="1">
-        <v>0</v>
-      </c>
-      <c r="B494" t="s">
-        <v>149</v>
-      </c>
-      <c r="C494">
-        <v>1.1949083591831</v>
-      </c>
-      <c r="D494" t="s">
-        <v>147</v>
-      </c>
-      <c r="E494">
-        <v>1.279467032224208</v>
-      </c>
-      <c r="F494">
-        <v>1</v>
-      </c>
-      <c r="G494">
-        <v>0.0078450916408169</v>
-      </c>
-      <c r="H494">
-        <v>0.008100532967775794</v>
-      </c>
-      <c r="I494">
-        <v>0.08455867304110809</v>
-      </c>
-      <c r="J494">
-        <v>0.7120110579907708</v>
-      </c>
-      <c r="K494">
-        <v>4.67</v>
-      </c>
-      <c r="L494">
-        <v>4.52</v>
-      </c>
-      <c r="M494">
-        <v>4.79</v>
-      </c>
-      <c r="N494">
-        <v>4.69</v>
-      </c>
-      <c r="O494">
-        <v>1</v>
-      </c>
-      <c r="P494" t="s">
         <v>389</v>
       </c>
     </row>

--- a/s60_signal/position-03328-601328.xlsx
+++ b/s60_signal/position-03328-601328.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1485" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="391">
   <si>
     <t>trade_time</t>
   </si>
@@ -463,6 +463,9 @@
     <t>2021-11-05</t>
   </si>
   <si>
+    <t>2021-11-11</t>
+  </si>
+  <si>
     <t>2021-10-27</t>
   </si>
   <si>
@@ -835,7 +838,7 @@
     <t>2021-11-02</t>
   </si>
   <si>
-    <t>2021-11-11</t>
+    <t>2021-11-12</t>
   </si>
   <si>
     <t>2016-05-24</t>
@@ -1541,7 +1544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P491"/>
+  <dimension ref="A1:P494"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1602,7 +1605,7 @@
         <v>2.636521639996683</v>
       </c>
       <c r="D2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E2">
         <v>2.833647241107702</v>
@@ -1638,7 +1641,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1652,7 +1655,7 @@
         <v>2.808801457176021</v>
       </c>
       <c r="D3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E3">
         <v>2.7135041663212</v>
@@ -1688,7 +1691,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1702,7 +1705,7 @@
         <v>2.746397091058633</v>
       </c>
       <c r="D4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E4">
         <v>2.648930323263125</v>
@@ -1752,7 +1755,7 @@
         <v>2.683209227271539</v>
       </c>
       <c r="D5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E5">
         <v>2.583545744375049</v>
@@ -1788,7 +1791,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1802,7 +1805,7 @@
         <v>2.555958070922727</v>
       </c>
       <c r="D6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E6">
         <v>2.632522016358742</v>
@@ -1838,7 +1841,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1852,7 +1855,7 @@
         <v>2.641252819939413</v>
       </c>
       <c r="D7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E7">
         <v>2.540130729835057</v>
@@ -1888,7 +1891,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1902,7 +1905,7 @@
         <v>2.512285655110759</v>
       </c>
       <c r="D8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E8">
         <v>2.590994611146576</v>
@@ -1938,7 +1941,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1952,7 +1955,7 @@
         <v>2.615441102246784</v>
       </c>
       <c r="D9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E9">
         <v>2.513421672263544</v>
@@ -1988,7 +1991,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2002,7 +2005,7 @@
         <v>2.515418243442972</v>
       </c>
       <c r="D10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E10">
         <v>2.545423958143926</v>
@@ -2038,7 +2041,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2052,7 +2055,7 @@
         <v>2.487273994427867</v>
       </c>
       <c r="D11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E11">
         <v>2.567211421027677</v>
@@ -2088,7 +2091,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2102,7 +2105,7 @@
         <v>2.487984580081365</v>
       </c>
       <c r="D12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E12">
         <v>2.579898802553291</v>
@@ -2138,7 +2141,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2152,7 +2155,7 @@
         <v>2.500805561667341</v>
       </c>
       <c r="D13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E13">
         <v>2.59216563562278</v>
@@ -2188,7 +2191,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2202,7 +2205,7 @@
         <v>2.499441989042522</v>
       </c>
       <c r="D14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E14">
         <v>2.736702547602069</v>
@@ -2252,7 +2255,7 @@
         <v>2.512520850741042</v>
       </c>
       <c r="D15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E15">
         <v>2.749061943431123</v>
@@ -2288,7 +2291,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2302,7 +2305,7 @@
         <v>2.77984350091858</v>
       </c>
       <c r="D16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E16">
         <v>2.889061943431122</v>
@@ -2338,7 +2341,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2352,7 +2355,7 @@
         <v>2.517224153471577</v>
       </c>
       <c r="D17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E17">
         <v>2.753506518310076</v>
@@ -2388,7 +2391,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2402,7 +2405,7 @@
         <v>2.784426680003737</v>
       </c>
       <c r="D18" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E18">
         <v>2.924119959439183</v>
@@ -2438,7 +2441,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2452,7 +2455,7 @@
         <v>2.884280694854824</v>
       </c>
       <c r="D19" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E19">
         <v>2.961861794886389</v>
@@ -2502,7 +2505,7 @@
         <v>2.920719956495094</v>
       </c>
       <c r="D20" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E20">
         <v>2.907075620138133</v>
@@ -2538,7 +2541,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2552,7 +2555,7 @@
         <v>2.648180125005333</v>
       </c>
       <c r="D21" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E21">
         <v>2.848908919700521</v>
@@ -2588,7 +2591,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2638,7 +2641,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2652,7 +2655,7 @@
         <v>2.691620213913162</v>
       </c>
       <c r="D23" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E23">
         <v>2.889959376998489</v>
@@ -2688,7 +2691,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2702,7 +2705,7 @@
         <v>2.984719616116966</v>
       </c>
       <c r="D24" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E24">
         <v>2.755965243802971</v>
@@ -2738,7 +2741,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2752,7 +2755,7 @@
         <v>3.007275184023352</v>
       </c>
       <c r="D25" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E25">
         <v>2.755965243802971</v>
@@ -2788,7 +2791,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2802,7 +2805,7 @@
         <v>2.683495528297218</v>
       </c>
       <c r="D26" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E26">
         <v>2.882281628901694</v>
@@ -2838,7 +2841,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2852,7 +2855,7 @@
         <v>2.976914171586129</v>
       </c>
       <c r="D27" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E27">
         <v>2.747824596132772</v>
@@ -2888,7 +2891,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2902,7 +2905,7 @@
         <v>2.647048085674867</v>
       </c>
       <c r="D28" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E28">
         <v>2.84783915365346</v>
@@ -2938,7 +2941,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2952,7 +2955,7 @@
         <v>2.941898848516719</v>
       </c>
       <c r="D29" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E29">
         <v>2.711305547532774</v>
@@ -2988,7 +2991,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3002,7 +3005,7 @@
         <v>2.962790623816959</v>
       </c>
       <c r="D30" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E30">
         <v>2.711305547532774</v>
@@ -3038,7 +3041,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3052,7 +3055,7 @@
         <v>2.636850318680218</v>
       </c>
       <c r="D31" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E31">
         <v>2.674077933106496</v>
@@ -3088,7 +3091,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3102,7 +3105,7 @@
         <v>2.64386308474694</v>
       </c>
       <c r="D32" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E32">
         <v>2.844829359063415</v>
@@ -3138,7 +3141,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3152,7 +3155,7 @@
         <v>2.938838994972993</v>
       </c>
       <c r="D33" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E33">
         <v>2.708114289235636</v>
@@ -3188,7 +3191,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3202,7 +3205,7 @@
         <v>2.959611880258242</v>
       </c>
       <c r="D34" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E34">
         <v>2.708114289235636</v>
@@ -3238,7 +3241,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3252,7 +3255,7 @@
         <v>2.63362151616782</v>
       </c>
       <c r="D35" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E35">
         <v>2.706375129633912</v>
@@ -3288,7 +3291,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3302,7 +3305,7 @@
         <v>2.623711665472045</v>
       </c>
       <c r="D36" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E36">
         <v>2.825786465799713</v>
@@ -3338,7 +3341,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3352,7 +3355,7 @@
         <v>2.919479379991807</v>
       </c>
       <c r="D37" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E37">
         <v>2.687923279746057</v>
@@ -3388,7 +3391,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3402,7 +3405,7 @@
         <v>2.939500051198033</v>
       </c>
       <c r="D38" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E38">
         <v>2.687923279746057</v>
@@ -3438,7 +3441,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3452,7 +3455,7 @@
         <v>2.613192965390128</v>
       </c>
       <c r="D39" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E39">
         <v>2.65740457966414</v>
@@ -3488,7 +3491,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3502,7 +3505,7 @@
         <v>2.866121269202039</v>
       </c>
       <c r="D40" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E40">
         <v>2.632273716345684</v>
@@ -3552,7 +3555,7 @@
         <v>2.884068721379623</v>
       </c>
       <c r="D41" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E41">
         <v>2.632273716345684</v>
@@ -3602,7 +3605,7 @@
         <v>2.556888701243869</v>
       </c>
       <c r="D42" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E42">
         <v>2.5709911987269</v>
@@ -3652,7 +3655,7 @@
         <v>2.84066903268222</v>
       </c>
       <c r="D43" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E43">
         <v>2.605728438993726</v>
@@ -3688,7 +3691,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3702,7 +3705,7 @@
         <v>2.857627543154535</v>
       </c>
       <c r="D44" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E44">
         <v>2.605728438993726</v>
@@ -3738,7 +3741,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3752,7 +3755,7 @@
         <v>2.530031126511299</v>
       </c>
       <c r="D45" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E45">
         <v>2.536232918189681</v>
@@ -3788,7 +3791,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3802,7 +3805,7 @@
         <v>2.794653597980052</v>
       </c>
       <c r="D46" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E46">
         <v>2.557736881328888</v>
@@ -3838,7 +3841,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3852,7 +3855,7 @@
         <v>2.809824187676618</v>
       </c>
       <c r="D47" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E47">
         <v>2.557736881328888</v>
@@ -3888,7 +3891,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3938,7 +3941,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3952,7 +3955,7 @@
         <v>2.877968395292299</v>
       </c>
       <c r="D49" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E49">
         <v>2.644629614722029</v>
@@ -3988,7 +3991,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4002,7 +4005,7 @@
         <v>2.896376165252531</v>
       </c>
       <c r="D50" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E50">
         <v>2.644629614722029</v>
@@ -4038,7 +4041,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4052,7 +4055,7 @@
         <v>2.521770137334771</v>
       </c>
       <c r="D51" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E51">
         <v>2.535896862069519</v>
@@ -4088,7 +4091,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4102,7 +4105,7 @@
         <v>2.934431839092635</v>
       </c>
       <c r="D52" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E52">
         <v>2.703517868992319</v>
@@ -4138,7 +4141,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4152,7 +4155,7 @@
         <v>2.955033485192349</v>
       </c>
       <c r="D53" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E53">
         <v>2.703517868992319</v>
@@ -4188,7 +4191,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4238,7 +4241,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4252,7 +4255,7 @@
         <v>2.974730272968942</v>
       </c>
       <c r="D55" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E55">
         <v>2.745546910458406</v>
@@ -4288,7 +4291,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4302,7 +4305,7 @@
         <v>2.996897706887981</v>
       </c>
       <c r="D56" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E56">
         <v>2.745546910458406</v>
@@ -4338,7 +4341,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4352,7 +4355,7 @@
         <v>2.624468326525319</v>
       </c>
       <c r="D57" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E57">
         <v>2.660688149733082</v>
@@ -4388,7 +4391,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4402,7 +4405,7 @@
         <v>3.056805462611843</v>
       </c>
       <c r="D58" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E58">
         <v>2.831146801497014</v>
@@ -4438,7 +4441,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4488,7 +4491,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4502,7 +4505,7 @@
         <v>3.075488420323122</v>
       </c>
       <c r="D60" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E60">
         <v>2.850632094815525</v>
@@ -4552,7 +4555,7 @@
         <v>2.73140795531227</v>
       </c>
       <c r="D61" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E61">
         <v>2.75953055997749</v>
@@ -4602,7 +4605,7 @@
         <v>2.72765316464271</v>
       </c>
       <c r="D62" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E62">
         <v>2.75953055997749</v>
@@ -4652,7 +4655,7 @@
         <v>2.72671446697532</v>
       </c>
       <c r="D63" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E63">
         <v>2.75953055997749</v>
@@ -4702,7 +4705,7 @@
         <v>6.293149296554828</v>
       </c>
       <c r="D64" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E64">
         <v>5.963700498102364</v>
@@ -4738,7 +4741,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4752,7 +4755,7 @@
         <v>6.420239880180696</v>
       </c>
       <c r="D65" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E65">
         <v>6.082402264327184</v>
@@ -4788,7 +4791,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4802,7 +4805,7 @@
         <v>6.609514294497387</v>
       </c>
       <c r="D66" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E66">
         <v>6.259183317962906</v>
@@ -4838,7 +4841,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4852,7 +4855,7 @@
         <v>6.515171551263329</v>
       </c>
       <c r="D67" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E67">
         <v>6.612047937164794</v>
@@ -4888,7 +4891,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4902,7 +4905,7 @@
         <v>6.520829737768901</v>
       </c>
       <c r="D68" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E68">
         <v>6.612047937164794</v>
@@ -4938,7 +4941,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4988,7 +4991,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5038,7 +5041,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5088,7 +5091,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5102,7 +5105,7 @@
         <v>6.781478804637512</v>
       </c>
       <c r="D72" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E72">
         <v>6.821616798629249</v>
@@ -5138,7 +5141,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5152,7 +5155,7 @@
         <v>6.927933775178332</v>
       </c>
       <c r="D73" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E73">
         <v>7.025464228815041</v>
@@ -5188,7 +5191,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5202,7 +5205,7 @@
         <v>7.465293617228137</v>
       </c>
       <c r="D74" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E74">
         <v>7.441132824526438</v>
@@ -5238,7 +5241,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5252,7 +5255,7 @@
         <v>2.399740228983164</v>
       </c>
       <c r="D75" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E75">
         <v>2.284756328614283</v>
@@ -5288,7 +5291,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5302,7 +5305,7 @@
         <v>2.181146111927123</v>
       </c>
       <c r="D76" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E76">
         <v>2.105842395854763</v>
@@ -5338,7 +5341,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5352,7 +5355,7 @@
         <v>2.180858495485883</v>
       </c>
       <c r="D77" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E77">
         <v>2.105842395854763</v>
@@ -5388,7 +5391,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5402,7 +5405,7 @@
         <v>2.355267416838251</v>
       </c>
       <c r="D78" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E78">
         <v>2.241615480893012</v>
@@ -5438,7 +5441,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5452,7 +5455,7 @@
         <v>2.138079262229388</v>
       </c>
       <c r="D79" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E79">
         <v>2.115876072829124</v>
@@ -5488,7 +5491,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5502,7 +5505,7 @@
         <v>2.136977667529256</v>
       </c>
       <c r="D80" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E80">
         <v>2.115876072829124</v>
@@ -5538,7 +5541,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5588,7 +5591,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5638,7 +5641,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5688,7 +5691,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5702,7 +5705,7 @@
         <v>1.925553832103902</v>
       </c>
       <c r="D84" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E84">
         <v>1.985821650998686</v>
@@ -5738,7 +5741,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5788,7 +5791,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5802,7 +5805,7 @@
         <v>1.87975631937778</v>
       </c>
       <c r="D86" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E86">
         <v>2.025900250164519</v>
@@ -5838,7 +5841,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5938,7 +5941,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5952,7 +5955,7 @@
         <v>1.789383875507923</v>
       </c>
       <c r="D89" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E89">
         <v>1.940268655809146</v>
@@ -5988,7 +5991,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6002,7 +6005,7 @@
         <v>1.804905667333501</v>
       </c>
       <c r="D90" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E90">
         <v>1.95497618970289</v>
@@ -6038,7 +6041,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6052,7 +6055,7 @@
         <v>1.809491967335235</v>
       </c>
       <c r="D91" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E91">
         <v>1.959321896917648</v>
@@ -6088,7 +6091,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6102,7 +6105,7 @@
         <v>1.822908408572121</v>
       </c>
       <c r="D92" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E92">
         <v>1.972034524843747</v>
@@ -6138,7 +6141,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6152,7 +6155,7 @@
         <v>2.011491451443282</v>
       </c>
       <c r="D93" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E93">
         <v>1.930405304642352</v>
@@ -6188,7 +6191,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6202,7 +6205,7 @@
         <v>1.820166348365971</v>
       </c>
       <c r="D94" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E94">
         <v>1.969436310418903</v>
@@ -6238,7 +6241,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6252,7 +6255,7 @@
         <v>2.008879751476441</v>
       </c>
       <c r="D95" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E95">
         <v>1.927766633591516</v>
@@ -6288,7 +6291,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6302,7 +6305,7 @@
         <v>1.780154910291897</v>
       </c>
       <c r="D96" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E96">
         <v>1.931523833030682</v>
@@ -6338,7 +6341,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6388,7 +6391,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6402,7 +6405,7 @@
         <v>1.781411528733962</v>
       </c>
       <c r="D98" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E98">
         <v>1.932714530505294</v>
@@ -6438,7 +6441,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6488,7 +6491,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6502,7 +6505,7 @@
         <v>1.786869994736246</v>
       </c>
       <c r="D100" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E100">
         <v>1.937886650750082</v>
@@ -6552,7 +6555,7 @@
         <v>1.77389224303264</v>
       </c>
       <c r="D101" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E101">
         <v>1.925589699135846</v>
@@ -6588,7 +6591,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6602,7 +6605,7 @@
         <v>1.764225388294109</v>
       </c>
       <c r="D102" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E102">
         <v>1.916429958088516</v>
@@ -6802,7 +6805,7 @@
         <v>2.039049007419374</v>
       </c>
       <c r="D106" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E106">
         <v>1.958247448115615</v>
@@ -6838,7 +6841,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6852,7 +6855,7 @@
         <v>1.963804213639886</v>
       </c>
       <c r="D107" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E107">
         <v>2.044635472991321</v>
@@ -6888,7 +6891,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6902,7 +6905,7 @@
         <v>2.084469221121035</v>
       </c>
       <c r="D108" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E108">
         <v>2.00413671738046</v>
@@ -6938,7 +6941,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6952,7 +6955,7 @@
         <v>1.970692549466935</v>
       </c>
       <c r="D109" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E109">
         <v>2.103970465510173</v>
@@ -6988,7 +6991,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7038,7 +7041,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7052,7 +7055,7 @@
         <v>1.989826166099606</v>
       </c>
       <c r="D111" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E111">
         <v>2.069999197311251</v>
@@ -7088,7 +7091,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7102,7 +7105,7 @@
         <v>1.996538974422711</v>
       </c>
       <c r="D112" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E112">
         <v>2.129860772341935</v>
@@ -7138,7 +7141,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7188,7 +7191,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7202,7 +7205,7 @@
         <v>1.976959483296697</v>
       </c>
       <c r="D114" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E114">
         <v>2.110248039295503</v>
@@ -7302,7 +7305,7 @@
         <v>1.920546112528168</v>
       </c>
       <c r="D116" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E116">
         <v>2.053738890308352</v>
@@ -7338,7 +7341,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7388,7 +7391,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7402,7 +7405,7 @@
         <v>2.078859445890371</v>
       </c>
       <c r="D118" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E118">
         <v>2.128859445890371</v>
@@ -7438,7 +7441,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7452,7 +7455,7 @@
         <v>1.864471846503076</v>
       </c>
       <c r="D119" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E119">
         <v>1.997569421794252</v>
@@ -7488,7 +7491,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7538,7 +7541,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7588,7 +7591,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7602,7 +7605,7 @@
         <v>1.863420505387863</v>
       </c>
       <c r="D122" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E122">
         <v>1.996516295719591</v>
@@ -7702,7 +7705,7 @@
         <v>2.029857360363785</v>
       </c>
       <c r="D124" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E124">
         <v>2.011995247378231</v>
@@ -7752,7 +7755,7 @@
         <v>1.892165706973767</v>
       </c>
       <c r="D125" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E125">
         <v>2.025310300703773</v>
@@ -7788,7 +7791,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7838,7 +7841,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7888,7 +7891,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7952,7 +7955,7 @@
         <v>2.183293967129219</v>
       </c>
       <c r="D129" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E129">
         <v>2.097698061214447</v>
@@ -8002,7 +8005,7 @@
         <v>2.10409703769314</v>
       </c>
       <c r="D130" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E130">
         <v>2.097698061214447</v>
@@ -8088,7 +8091,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8138,7 +8141,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8188,7 +8191,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8238,7 +8241,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8288,7 +8291,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8338,7 +8341,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8388,7 +8391,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8438,7 +8441,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8452,7 +8455,7 @@
         <v>2.367284598691813</v>
       </c>
       <c r="D139" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E139">
         <v>2.284677125480481</v>
@@ -8502,7 +8505,7 @@
         <v>2.308705785003503</v>
       </c>
       <c r="D140" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E140">
         <v>2.284677125480481</v>
@@ -8638,7 +8641,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8688,7 +8691,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8738,7 +8741,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8788,7 +8791,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8838,7 +8841,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8902,7 +8905,7 @@
         <v>2.673055621612132</v>
       </c>
       <c r="D148" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E148">
         <v>2.649383477311975</v>
@@ -8952,7 +8955,7 @@
         <v>2.694510447967022</v>
       </c>
       <c r="D149" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E149">
         <v>2.66746656530884</v>
@@ -9002,7 +9005,7 @@
         <v>2.61961842602696</v>
       </c>
       <c r="D150" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E150">
         <v>2.674946565009619</v>
@@ -9288,7 +9291,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9302,7 +9305,7 @@
         <v>2.746485076848839</v>
       </c>
       <c r="D156" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E156">
         <v>2.847982602490786</v>
@@ -9338,7 +9341,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9402,7 +9405,7 @@
         <v>2.750734210259811</v>
       </c>
       <c r="D158" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E158">
         <v>2.800734210259812</v>
@@ -9438,7 +9441,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9502,7 +9505,7 @@
         <v>2.717092536535202</v>
       </c>
       <c r="D160" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E160">
         <v>2.791717770085309</v>
@@ -9588,7 +9591,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9602,7 +9605,7 @@
         <v>2.669840281895235</v>
       </c>
       <c r="D162" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E162">
         <v>2.754805459723328</v>
@@ -9638,7 +9641,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9702,7 +9705,7 @@
         <v>2.704152220032186</v>
       </c>
       <c r="D164" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E164">
         <v>2.721608307945189</v>
@@ -9752,7 +9755,7 @@
         <v>0.7516342779874527</v>
       </c>
       <c r="D165" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E165">
         <v>0.6447312303040151</v>
@@ -9788,7 +9791,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9802,7 +9805,7 @@
         <v>0.6347312303040145</v>
       </c>
       <c r="D166" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E166">
         <v>0.7803954970608276</v>
@@ -9838,7 +9841,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9852,7 +9855,7 @@
         <v>0.7872985447442655</v>
       </c>
       <c r="D167" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E167">
         <v>0.6685373256708909</v>
@@ -9888,7 +9891,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9902,7 +9905,7 @@
         <v>0.6141118398407031</v>
       </c>
       <c r="D168" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E168">
         <v>0.7042015924277036</v>
@@ -9938,7 +9941,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9952,7 +9955,7 @@
         <v>0.7076194190074974</v>
       </c>
       <c r="D169" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E169">
         <v>0.8524403513495589</v>
@@ -10002,7 +10005,7 @@
         <v>0.8587410173081755</v>
       </c>
       <c r="D170" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E170">
         <v>0.7402207509247285</v>
@@ -10052,7 +10055,7 @@
         <v>0.6868795521992208</v>
       </c>
       <c r="D171" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E171">
         <v>0.7750416832667906</v>
@@ -10102,7 +10105,7 @@
         <v>0.794311018129779</v>
       </c>
       <c r="D172" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E172">
         <v>0.9381289071762104</v>
@@ -10138,7 +10141,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10152,7 +10155,7 @@
         <v>0.7478436529603893</v>
       </c>
       <c r="D173" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E173">
         <v>0.9381289071762104</v>
@@ -10188,7 +10191,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10202,7 +10205,7 @@
         <v>0.9437131136379486</v>
       </c>
       <c r="D174" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E174">
         <v>0.8254794310532532</v>
@@ -10238,7 +10241,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10252,7 +10255,7 @@
         <v>0.7734278594221262</v>
       </c>
       <c r="D175" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E175">
         <v>0.8592973200996861</v>
@@ -10288,7 +10291,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10302,7 +10305,7 @@
         <v>0.9016190641047892</v>
       </c>
       <c r="D176" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E176">
         <v>1.04419537245399</v>
@@ -10338,7 +10341,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10352,7 +10355,7 @@
         <v>0.8558611736195321</v>
       </c>
       <c r="D177" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E177">
         <v>1.04419537245399</v>
@@ -10388,7 +10391,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10402,7 +10405,7 @@
         <v>1.048892735560562</v>
       </c>
       <c r="D178" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E178">
         <v>0.9310137903179339</v>
@@ -10438,7 +10441,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10452,7 +10455,7 @@
         <v>0.8805585367261042</v>
       </c>
       <c r="D179" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E179">
         <v>0.963590098667134</v>
@@ -10488,7 +10491,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10502,7 +10505,7 @@
         <v>1.076170489586433</v>
       </c>
       <c r="D180" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E180">
         <v>1.260525374010979</v>
@@ -10552,7 +10555,7 @@
         <v>1.26341395784032</v>
       </c>
       <c r="D181" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E181">
         <v>1.146258524308584</v>
@@ -10602,7 +10605,7 @@
         <v>1.099059073415773</v>
       </c>
       <c r="D182" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E182">
         <v>1.176302541669659</v>
@@ -10652,7 +10655,7 @@
         <v>1.931268098407571</v>
       </c>
       <c r="D183" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E183">
         <v>1.946759727730396</v>
@@ -10688,7 +10691,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10738,7 +10741,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10788,7 +10791,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10802,7 +10805,7 @@
         <v>0.5942088493584849</v>
       </c>
       <c r="D186" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E186">
         <v>0.5982130518354056</v>
@@ -10838,7 +10841,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10888,7 +10891,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10938,7 +10941,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10988,7 +10991,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11002,7 +11005,7 @@
         <v>-0.02499489055226256</v>
       </c>
       <c r="D190" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E190">
         <v>-0.07499489055226238</v>
@@ -11038,7 +11041,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11052,7 +11055,7 @@
         <v>-0.04541693580813089</v>
       </c>
       <c r="D191" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E191">
         <v>-0.1350880582477796</v>
@@ -11088,7 +11091,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11138,7 +11141,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11188,7 +11191,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11338,7 +11341,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11352,7 +11355,7 @@
         <v>-0.5154661476950757</v>
       </c>
       <c r="D197" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E197">
         <v>-0.4838284745942198</v>
@@ -11388,7 +11391,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11402,7 +11405,7 @@
         <v>-0.5144835438345625</v>
       </c>
       <c r="D198" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E198">
         <v>-0.4838284745942198</v>
@@ -11438,7 +11441,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11488,7 +11491,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11502,7 +11505,7 @@
         <v>-0.6795603356321358</v>
       </c>
       <c r="D200" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E200">
         <v>-0.6353746161347429</v>
@@ -11538,7 +11541,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11552,7 +11555,7 @@
         <v>-0.6770489039336995</v>
       </c>
       <c r="D201" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E201">
         <v>-0.6353746161347429</v>
@@ -11588,7 +11591,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11638,7 +11641,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11652,7 +11655,7 @@
         <v>-1.275160705635463</v>
       </c>
       <c r="D203" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E203">
         <v>-0.9575450227817477</v>
@@ -11688,7 +11691,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11702,7 +11705,7 @@
         <v>-1.267100202166811</v>
       </c>
       <c r="D204" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E204">
         <v>-0.9575450227817477</v>
@@ -11738,7 +11741,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11802,7 +11805,7 @@
         <v>-1.30354206111917</v>
       </c>
       <c r="D206" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E206">
         <v>-0.9846924062879019</v>
@@ -11852,7 +11855,7 @@
         <v>-1.295217135083899</v>
       </c>
       <c r="D207" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E207">
         <v>-0.9846924062879019</v>
@@ -11902,7 +11905,7 @@
         <v>-1.315601110783377</v>
       </c>
       <c r="D208" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E208">
         <v>-0.9962271494449686</v>
@@ -11952,7 +11955,7 @@
         <v>-1.307163833353718</v>
       </c>
       <c r="D209" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E209">
         <v>-0.9962271494449686</v>
@@ -12002,7 +12005,7 @@
         <v>-1.303470101275702</v>
       </c>
       <c r="D210" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E210">
         <v>-0.9846235751332797</v>
@@ -12038,7 +12041,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12052,7 +12055,7 @@
         <v>-1.295145845673754</v>
       </c>
       <c r="D211" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E211">
         <v>-0.9846235751332797</v>
@@ -12088,7 +12091,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12102,7 +12105,7 @@
         <v>-1.352240812118975</v>
       </c>
       <c r="D212" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E212">
         <v>-1.031273820287715</v>
@@ -12138,7 +12141,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12152,7 +12155,7 @@
         <v>-1.343462171012276</v>
       </c>
       <c r="D213" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E213">
         <v>-1.031273820287715</v>
@@ -12188,7 +12191,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12238,7 +12241,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12252,7 +12255,7 @@
         <v>-1.277973836666044</v>
       </c>
       <c r="D215" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E215">
         <v>-0.9602358437675207</v>
@@ -12302,7 +12305,7 @@
         <v>-1.269887123902075</v>
       </c>
       <c r="D216" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E216">
         <v>-0.9602358437675207</v>
@@ -12352,7 +12355,7 @@
         <v>-1.030235843767521</v>
       </c>
       <c r="D217" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E217">
         <v>-1.080019061857596</v>
@@ -12402,7 +12405,7 @@
         <v>-1.007888992711643</v>
       </c>
       <c r="D218" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E218">
         <v>-1.080019061857596</v>
@@ -12452,7 +12455,7 @@
         <v>-1.154349245698821</v>
       </c>
       <c r="D219" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E219">
         <v>-0.8419862350162637</v>
@@ -12502,7 +12505,7 @@
         <v>-1.147414314838273</v>
       </c>
       <c r="D220" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E220">
         <v>-0.8419862350162637</v>
@@ -12652,7 +12655,7 @@
         <v>-0.9332125637434627</v>
       </c>
       <c r="D223" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E223">
         <v>-0.6304641914067899</v>
@@ -12688,7 +12691,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12702,7 +12705,7 @@
         <v>-0.9283379125284608</v>
       </c>
       <c r="D224" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E224">
         <v>-0.6304641914067899</v>
@@ -12738,7 +12741,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12752,7 +12755,7 @@
         <v>-1.078298911794628</v>
       </c>
       <c r="D225" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E225">
         <v>-0.7337942740491279</v>
@@ -12802,7 +12805,7 @@
         <v>-1.284045732215318</v>
       </c>
       <c r="D226" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E226">
         <v>-0.9315166474955321</v>
@@ -12852,7 +12855,7 @@
         <v>-1.074552792811861</v>
       </c>
       <c r="D227" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E227">
         <v>-0.7301942595508679</v>
@@ -12888,7 +12891,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12902,7 +12905,7 @@
         <v>0.6306184682796347</v>
       </c>
       <c r="D228" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E228">
         <v>0.8825890610024754</v>
@@ -12938,7 +12941,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12952,7 +12955,7 @@
         <v>2.500083924851446</v>
       </c>
       <c r="D229" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E229">
         <v>2.721828222716436</v>
@@ -12988,7 +12991,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13002,7 +13005,7 @@
         <v>2.484743417251086</v>
       </c>
       <c r="D230" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E230">
         <v>2.721828222716436</v>
@@ -13038,7 +13041,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13052,7 +13055,7 @@
         <v>2.959498476516616</v>
       </c>
       <c r="D231" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E231">
         <v>3.019498476516616</v>
@@ -13088,7 +13091,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13138,7 +13141,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13152,7 +13155,7 @@
         <v>3.973072767193392</v>
       </c>
       <c r="D233" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E233">
         <v>3.630196829293595</v>
@@ -13188,7 +13191,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13238,7 +13241,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13288,7 +13291,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13302,7 +13305,7 @@
         <v>4.556254256131551</v>
       </c>
       <c r="D236" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E236">
         <v>4.211276763316661</v>
@@ -13338,7 +13341,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13388,7 +13391,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13438,7 +13441,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13452,7 +13455,7 @@
         <v>4.667791750685101</v>
       </c>
       <c r="D239" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E239">
         <v>4.322412320952902</v>
@@ -13488,7 +13491,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13502,7 +13505,7 @@
         <v>4.273963746622406</v>
       </c>
       <c r="D240" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E240">
         <v>4.266274031756307</v>
@@ -13538,7 +13541,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13588,7 +13591,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13638,7 +13641,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13652,7 +13655,7 @@
         <v>3.655351043939968</v>
       </c>
       <c r="D243" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E243">
         <v>3.313620049187031</v>
@@ -13688,7 +13691,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13702,7 +13705,7 @@
         <v>2.349652973133038</v>
       </c>
       <c r="D244" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E244">
         <v>2.585321458264525</v>
@@ -13752,7 +13755,7 @@
         <v>2.337296219946928</v>
       </c>
       <c r="D245" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E245">
         <v>2.585321458264525</v>
@@ -13802,7 +13805,7 @@
         <v>2.821499834857581</v>
       </c>
       <c r="D246" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E246">
         <v>2.482773709326562</v>
@@ -13852,7 +13855,7 @@
         <v>1.399171925433256</v>
       </c>
       <c r="D247" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E247">
         <v>1.7228188215915</v>
@@ -13888,7 +13891,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13902,7 +13905,7 @@
         <v>1.94957093986026</v>
       </c>
       <c r="D248" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E248">
         <v>1.61398690043734</v>
@@ -13938,7 +13941,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13952,7 +13955,7 @@
         <v>1.388298565840941</v>
       </c>
       <c r="D249" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E249">
         <v>1.05473712956764</v>
@@ -14002,7 +14005,7 @@
         <v>1.206849236469149</v>
       </c>
       <c r="D250" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E250">
         <v>0.8739416716530437</v>
@@ -14052,7 +14055,7 @@
         <v>1.250249534396463</v>
       </c>
       <c r="D251" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E251">
         <v>0.9171855721103492</v>
@@ -14102,7 +14105,7 @@
         <v>1.265784593473219</v>
       </c>
       <c r="D252" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E252">
         <v>0.9326646489922341</v>
@@ -14138,7 +14141,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14152,7 +14155,7 @@
         <v>1.181086185990114</v>
       </c>
       <c r="D253" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E253">
         <v>0.8482714609955542</v>
@@ -14202,7 +14205,7 @@
         <v>3.393868635799184</v>
       </c>
       <c r="D254" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E254">
         <v>3.232668972857903</v>
@@ -14238,7 +14241,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14252,7 +14255,7 @@
         <v>3.344337857016143</v>
       </c>
       <c r="D255" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E255">
         <v>3.232668972857903</v>
@@ -14288,7 +14291,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14302,7 +14305,7 @@
         <v>3.108144846549583</v>
       </c>
       <c r="D256" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E256">
         <v>3.176241351782863</v>
@@ -14338,7 +14341,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14352,7 +14355,7 @@
         <v>3.110765478091183</v>
       </c>
       <c r="D257" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E257">
         <v>3.176241351782863</v>
@@ -14388,7 +14391,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14402,7 +14405,7 @@
         <v>3.484929217459694</v>
       </c>
       <c r="D258" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E258">
         <v>3.328403460479749</v>
@@ -14438,7 +14441,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14452,7 +14455,7 @@
         <v>3.438944160440425</v>
       </c>
       <c r="D259" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E259">
         <v>3.328403460479749</v>
@@ -14488,7 +14491,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14538,7 +14541,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14588,7 +14591,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14602,7 +14605,7 @@
         <v>3.67612531160249</v>
       </c>
       <c r="D262" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E262">
         <v>3.529413159454653</v>
@@ -14638,7 +14641,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14652,7 +14655,7 @@
         <v>3.637585058248958</v>
       </c>
       <c r="D263" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E263">
         <v>3.529413159454653</v>
@@ -14688,7 +14691,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14702,7 +14705,7 @@
         <v>3.405388602484038</v>
       </c>
       <c r="D264" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E264">
         <v>3.509413159454653</v>
@@ -14738,7 +14741,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14752,7 +14755,7 @@
         <v>3.405511387337113</v>
       </c>
       <c r="D265" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E265">
         <v>3.509413159454653</v>
@@ -14788,7 +14791,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14802,7 +14805,7 @@
         <v>3.451364045513422</v>
       </c>
       <c r="D266" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E266">
         <v>3.509413159454653</v>
@@ -14838,7 +14841,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14852,7 +14855,7 @@
         <v>4.004636932335591</v>
       </c>
       <c r="D267" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E267">
         <v>3.867442887120403</v>
@@ -14902,7 +14905,7 @@
         <v>3.774439165379895</v>
       </c>
       <c r="D268" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E268">
         <v>3.837640654076098</v>
@@ -14952,7 +14955,7 @@
         <v>4.220199786446392</v>
       </c>
       <c r="D269" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E269">
         <v>4.085943565478028</v>
@@ -14988,7 +14991,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15002,7 +15005,7 @@
         <v>3.991103703583256</v>
       </c>
       <c r="D270" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E270">
         <v>4.0441357312043</v>
@@ -15038,7 +15041,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15052,7 +15055,7 @@
         <v>4.24807262091024</v>
       </c>
       <c r="D271" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E271">
         <v>4.172298835483293</v>
@@ -15088,7 +15091,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15102,7 +15105,7 @@
         <v>4.076733299050661</v>
       </c>
       <c r="D272" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E272">
         <v>4.185185728196767</v>
@@ -15138,7 +15141,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15202,7 +15205,7 @@
         <v>3.853669569225198</v>
       </c>
       <c r="D274" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E274">
         <v>3.960609701897911</v>
@@ -15338,7 +15341,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15352,7 +15355,7 @@
         <v>3.457860783201086</v>
       </c>
       <c r="D277" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E277">
         <v>3.562117466477025</v>
@@ -15388,7 +15391,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15402,7 +15405,7 @@
         <v>3.461796612382101</v>
       </c>
       <c r="D278" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E278">
         <v>3.45818163729601</v>
@@ -15438,7 +15441,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15502,7 +15505,7 @@
         <v>1.876063224574707</v>
       </c>
       <c r="D280" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E280">
         <v>1.926860456775207</v>
@@ -15552,7 +15555,7 @@
         <v>1.879462993924748</v>
       </c>
       <c r="D281" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E281">
         <v>1.926860456775207</v>
@@ -15602,7 +15605,7 @@
         <v>1.36286186891499</v>
       </c>
       <c r="D282" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E282">
         <v>1.420876924621103</v>
@@ -15638,7 +15641,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15652,7 +15655,7 @@
         <v>1.365396205962064</v>
       </c>
       <c r="D283" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E283">
         <v>1.420876924621103</v>
@@ -15688,7 +15691,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15702,7 +15705,7 @@
         <v>1.492587172538397</v>
       </c>
       <c r="D284" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E284">
         <v>1.422587172538397</v>
@@ -15738,7 +15741,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15752,7 +15755,7 @@
         <v>1.155028253713973</v>
       </c>
       <c r="D285" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E285">
         <v>1.207786135342488</v>
@@ -15802,7 +15805,7 @@
         <v>1.157212112489207</v>
       </c>
       <c r="D286" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E286">
         <v>1.207786135342488</v>
@@ -15852,7 +15855,7 @@
         <v>1.287557383512098</v>
       </c>
       <c r="D287" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E287">
         <v>1.260086513310223</v>
@@ -15902,7 +15905,7 @@
         <v>-0.2566084186298667</v>
       </c>
       <c r="D288" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E288">
         <v>-0.001048450451905936</v>
@@ -15938,7 +15941,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15952,7 +15955,7 @@
         <v>-0.2875710874180024</v>
       </c>
       <c r="D289" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E289">
         <v>-0.001048450451905936</v>
@@ -15988,7 +15991,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16038,7 +16041,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16088,7 +16091,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16102,7 +16105,7 @@
         <v>-0.3429456734762377</v>
       </c>
       <c r="D292" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E292">
         <v>-0.1559309932859021</v>
@@ -16138,7 +16141,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16152,7 +16155,7 @@
         <v>-0.452945673476238</v>
       </c>
       <c r="D293" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E293">
         <v>-0.1559309932859021</v>
@@ -16188,7 +16191,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16202,7 +16205,7 @@
         <v>-0.07614423041516449</v>
       </c>
       <c r="D294" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E294">
         <v>-0.08649962563060054</v>
@@ -16238,7 +16241,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16252,7 +16255,7 @@
         <v>-0.06685502084603723</v>
       </c>
       <c r="D295" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E295">
         <v>-0.08649962563060054</v>
@@ -16288,7 +16291,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16302,7 +16305,7 @@
         <v>-0.6325763258089658</v>
       </c>
       <c r="D296" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E296">
         <v>-0.7397037652284588</v>
@@ -16338,7 +16341,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16352,7 +16355,7 @@
         <v>-0.6888811406779016</v>
       </c>
       <c r="D297" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E297">
         <v>-0.6347573064746772</v>
@@ -16388,7 +16391,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16402,7 +16405,7 @@
         <v>-0.5922830059527424</v>
       </c>
       <c r="D298" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E298">
         <v>-0.6988811406779014</v>
@@ -16438,7 +16441,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16452,7 +16455,7 @@
         <v>-0.7708727781363214</v>
       </c>
       <c r="D299" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E299">
         <v>-0.7160845060282481</v>
@@ -16488,7 +16491,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16502,7 +16505,7 @@
         <v>-0.6732115427634033</v>
       </c>
       <c r="D300" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E300">
         <v>-0.7808727781363212</v>
@@ -16538,7 +16541,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16552,7 +16555,7 @@
         <v>-0.6051723879795468</v>
       </c>
       <c r="D301" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E301">
         <v>-0.5517269067155315</v>
@@ -16588,7 +16591,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16602,7 +16605,7 @@
         <v>-0.509659617957122</v>
       </c>
       <c r="D302" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E302">
         <v>-0.6151723879795465</v>
@@ -16638,7 +16641,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16652,7 +16655,7 @@
         <v>1.374867998585327</v>
       </c>
       <c r="D303" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E303">
         <v>1.61428021608427</v>
@@ -16688,7 +16691,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16702,7 +16705,7 @@
         <v>1.37455579980999</v>
       </c>
       <c r="D304" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E304">
         <v>1.61428021608427</v>
@@ -16738,7 +16741,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16752,7 +16755,7 @@
         <v>1.659046067002767</v>
       </c>
       <c r="D305" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E305">
         <v>1.701663141543517</v>
@@ -16788,7 +16791,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16802,7 +16805,7 @@
         <v>1.400425101402588</v>
       </c>
       <c r="D306" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E306">
         <v>1.63789275673065</v>
@@ -16838,7 +16841,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16852,7 +16855,7 @@
         <v>1.415426421593279</v>
       </c>
       <c r="D307" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E307">
         <v>1.63789275673065</v>
@@ -16888,7 +16891,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16902,7 +16905,7 @@
         <v>1.672891436539961</v>
       </c>
       <c r="D308" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E308">
         <v>1.702888796158578</v>
@@ -16938,7 +16941,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16952,7 +16955,7 @@
         <v>1.682896717302726</v>
       </c>
       <c r="D309" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E309">
         <v>1.702888796158578</v>
@@ -16988,7 +16991,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17002,7 +17005,7 @@
         <v>1.392287936404873</v>
       </c>
       <c r="D310" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E310">
         <v>1.630374723852328</v>
@@ -17038,7 +17041,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17052,7 +17055,7 @@
         <v>1.392192134372636</v>
       </c>
       <c r="D311" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E311">
         <v>1.630374723852328</v>
@@ -17088,7 +17091,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17102,7 +17105,7 @@
         <v>1.665398674360388</v>
       </c>
       <c r="D312" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E312">
         <v>1.367982501138595</v>
@@ -17138,7 +17141,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17152,7 +17155,7 @@
         <v>1.67530287232815</v>
       </c>
       <c r="D313" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E313">
         <v>1.367982501138595</v>
@@ -17188,7 +17191,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17202,7 +17205,7 @@
         <v>1.683187064752997</v>
       </c>
       <c r="D314" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E314">
         <v>1.385560910531628</v>
@@ -17238,7 +17241,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17252,7 +17255,7 @@
         <v>1.693331241005988</v>
       </c>
       <c r="D315" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E315">
         <v>1.385560910531628</v>
@@ -17288,7 +17291,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17302,7 +17305,7 @@
         <v>1.671335210176903</v>
       </c>
       <c r="D316" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E316">
         <v>1.373848959803819</v>
@@ -17338,7 +17341,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17352,7 +17355,7 @@
         <v>1.68131949631757</v>
       </c>
       <c r="D317" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E317">
         <v>1.373848959803819</v>
@@ -17388,7 +17391,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17402,7 +17405,7 @@
         <v>1.693875753393727</v>
       </c>
       <c r="D318" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E318">
         <v>1.396123425781996</v>
@@ -17438,7 +17441,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17452,7 +17455,7 @@
         <v>1.704164127807133</v>
       </c>
       <c r="D319" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E319">
         <v>1.396123425781996</v>
@@ -17488,7 +17491,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17502,7 +17505,7 @@
         <v>1.366123425781996</v>
       </c>
       <c r="D320" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E320">
         <v>1.403731566187024</v>
@@ -17538,7 +17541,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17552,7 +17555,7 @@
         <v>1.710631890779994</v>
       </c>
       <c r="D321" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E321">
         <v>1.412681767280061</v>
@@ -17588,7 +17591,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17602,7 +17605,7 @@
         <v>1.72114631763706</v>
       </c>
       <c r="D322" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E322">
         <v>1.412681767280061</v>
@@ -17638,7 +17641,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17652,7 +17655,7 @@
         <v>1.382681767280062</v>
       </c>
       <c r="D323" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E323">
         <v>1.420374677351461</v>
@@ -17688,7 +17691,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17702,7 +17705,7 @@
         <v>1.679206240881443</v>
       </c>
       <c r="D324" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E324">
         <v>1.381627077835624</v>
@@ -17752,7 +17755,7 @@
         <v>1.689296712933807</v>
       </c>
       <c r="D325" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E325">
         <v>1.381627077835624</v>
@@ -17802,7 +17805,7 @@
         <v>1.351627077835625</v>
       </c>
       <c r="D326" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E326">
         <v>1.364138386842169</v>
@@ -17852,7 +17855,7 @@
         <v>1.662615013806636</v>
       </c>
       <c r="D327" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E327">
         <v>1.365231699984297</v>
@@ -17888,7 +17891,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17902,7 +17905,7 @@
         <v>1.672481658175022</v>
       </c>
       <c r="D328" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E328">
         <v>1.365231699984297</v>
@@ -17938,7 +17941,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17952,7 +17955,7 @@
         <v>1.335231699984297</v>
       </c>
       <c r="D329" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E329">
         <v>1.330198361076394</v>
@@ -17988,7 +17991,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18002,7 +18005,7 @@
         <v>1.638483426036899</v>
       </c>
       <c r="D330" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E330">
         <v>1.341384970754843</v>
@@ -18052,7 +18055,7 @@
         <v>1.648024517787818</v>
       </c>
       <c r="D331" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E331">
         <v>1.341384970754843</v>
@@ -18152,7 +18155,7 @@
         <v>1.611118158429232</v>
       </c>
       <c r="D333" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E333">
         <v>1.31434273328757</v>
@@ -18202,7 +18205,7 @@
         <v>1.620290072876844</v>
       </c>
       <c r="D334" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E334">
         <v>1.31434273328757</v>
@@ -18252,7 +18255,7 @@
         <v>1.210704115653037</v>
       </c>
       <c r="D335" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E335">
         <v>1.321946243981619</v>
@@ -18302,7 +18305,7 @@
         <v>1.250704115653037</v>
       </c>
       <c r="D336" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E336">
         <v>1.321946243981619</v>
@@ -18352,7 +18355,7 @@
         <v>1.580824889600507</v>
       </c>
       <c r="D337" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E337">
         <v>1.284407057851428</v>
@@ -18388,7 +18391,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18402,7 +18405,7 @@
         <v>1.589588125885168</v>
       </c>
       <c r="D338" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E338">
         <v>1.284407057851428</v>
@@ -18438,7 +18441,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18452,7 +18455,7 @@
         <v>1.180206507742837</v>
       </c>
       <c r="D339" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E339">
         <v>1.27675246238701</v>
@@ -18488,7 +18491,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18502,7 +18505,7 @@
         <v>1.220206507742837</v>
       </c>
       <c r="D340" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E340">
         <v>1.27675246238701</v>
@@ -18538,7 +18541,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18552,7 +18555,7 @@
         <v>1.680056540073359</v>
       </c>
       <c r="D341" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E341">
         <v>1.409353064352823</v>
@@ -18588,7 +18591,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18602,7 +18605,7 @@
         <v>1.717732409003494</v>
       </c>
       <c r="D342" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E342">
         <v>1.409353064352823</v>
@@ -18638,7 +18641,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18652,7 +18655,7 @@
         <v>1.307497917096648</v>
       </c>
       <c r="D343" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E343">
         <v>1.444235818399402</v>
@@ -18688,7 +18691,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18702,7 +18705,7 @@
         <v>1.347497917096648</v>
       </c>
       <c r="D344" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E344">
         <v>1.444235818399402</v>
@@ -18738,7 +18741,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18752,7 +18755,7 @@
         <v>1.842256392262994</v>
       </c>
       <c r="D345" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E345">
         <v>1.530769127897027</v>
@@ -18802,7 +18805,7 @@
         <v>1.431193121765403</v>
       </c>
       <c r="D346" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E346">
         <v>1.572471675023835</v>
@@ -18852,7 +18855,7 @@
         <v>1.471193121765403</v>
       </c>
       <c r="D347" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E347">
         <v>1.572471675023835</v>
@@ -18902,7 +18905,7 @@
         <v>2.306011000659936</v>
       </c>
       <c r="D348" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E348">
         <v>2.348379970519409</v>
@@ -18938,7 +18941,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18952,7 +18955,7 @@
         <v>2.400485390479259</v>
       </c>
       <c r="D349" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E349">
         <v>2.364696230398958</v>
@@ -18988,7 +18991,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19038,7 +19041,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19052,7 +19055,7 @@
         <v>2.315116384839492</v>
       </c>
       <c r="D351" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E351">
         <v>2.323814331699535</v>
@@ -19088,7 +19091,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19102,7 +19105,7 @@
         <v>2.158186337006185</v>
       </c>
       <c r="D352" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E352">
         <v>2.199105803820263</v>
@@ -19138,7 +19141,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19188,7 +19191,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19238,7 +19241,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19252,7 +19255,7 @@
         <v>2.249949180664442</v>
       </c>
       <c r="D355" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E355">
         <v>2.193589002935801</v>
@@ -19288,7 +19291,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19302,7 +19305,7 @@
         <v>3.29910210514231</v>
       </c>
       <c r="D356" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E356">
         <v>3.35230135785332</v>
@@ -19338,7 +19341,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19352,7 +19355,7 @@
         <v>3.804045197377832</v>
       </c>
       <c r="D357" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E357">
         <v>3.415154291605215</v>
@@ -19388,7 +19391,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19402,7 +19405,7 @@
         <v>3.427249571448392</v>
       </c>
       <c r="D358" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E358">
         <v>3.291626526785035</v>
@@ -19438,7 +19441,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19488,7 +19491,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19502,7 +19505,7 @@
         <v>3.442581197445604</v>
       </c>
       <c r="D360" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E360">
         <v>3.306414237004073</v>
@@ -19538,7 +19541,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19552,7 +19555,7 @@
         <v>3.36022431872702</v>
       </c>
       <c r="D361" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E361">
         <v>3.226979110080385</v>
@@ -19588,7 +19591,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19602,7 +19605,7 @@
         <v>3.251003700388559</v>
       </c>
       <c r="D362" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E362">
         <v>3.121633280862579</v>
@@ -19638,7 +19641,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19652,7 +19655,7 @@
         <v>2.99001278638902</v>
       </c>
       <c r="D363" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E363">
         <v>3.032275977245447</v>
@@ -19738,7 +19741,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19752,7 +19755,7 @@
         <v>2.786342722576059</v>
       </c>
       <c r="D365" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E365">
         <v>2.830017022419643</v>
@@ -19788,7 +19791,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19802,7 +19805,7 @@
         <v>2.881784622628198</v>
       </c>
       <c r="D366" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E366">
         <v>2.846342722576059</v>
@@ -19838,7 +19841,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19852,7 +19855,7 @@
         <v>2.713139299753176</v>
       </c>
       <c r="D367" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E367">
         <v>2.672915915531583</v>
@@ -19888,7 +19891,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19902,7 +19905,7 @@
         <v>2.722022378645214</v>
       </c>
       <c r="D368" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E368">
         <v>2.672915915531583</v>
@@ -19938,7 +19941,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19952,7 +19955,7 @@
         <v>2.643362683974768</v>
       </c>
       <c r="D369" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E369">
         <v>2.68802760764238</v>
@@ -19988,7 +19991,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20002,7 +20005,7 @@
         <v>2.738474376085565</v>
       </c>
       <c r="D370" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E370">
         <v>2.678250991863972</v>
@@ -20038,7 +20041,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20052,7 +20055,7 @@
         <v>2.26156876679942</v>
       </c>
       <c r="D371" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E371">
         <v>2.319500204055783</v>
@@ -20088,7 +20091,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20102,7 +20105,7 @@
         <v>2.341086491507057</v>
       </c>
       <c r="D372" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E372">
         <v>2.284741341701965</v>
@@ -20138,7 +20141,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20152,7 +20155,7 @@
         <v>2.25156876679942</v>
       </c>
       <c r="D373" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E373">
         <v>2.298948197976329</v>
@@ -20188,7 +20191,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20202,7 +20205,7 @@
         <v>2.345775623073784</v>
       </c>
       <c r="D374" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E374">
         <v>2.287361910525056</v>
@@ -20238,7 +20241,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20252,7 +20255,7 @@
         <v>1.450725995788351</v>
       </c>
       <c r="D375" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E375">
         <v>1.543612412630503</v>
@@ -20288,7 +20291,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20302,7 +20305,7 @@
         <v>1.378039753255653</v>
       </c>
       <c r="D376" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E376">
         <v>1.473954763536668</v>
@@ -20338,7 +20341,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20352,7 +20355,7 @@
         <v>2.300473418774809</v>
       </c>
       <c r="D377" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E377">
         <v>2.269274816103397</v>
@@ -20402,7 +20405,7 @@
         <v>2.307737312105645</v>
       </c>
       <c r="D378" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E378">
         <v>2.269274816103397</v>
@@ -20452,7 +20455,7 @@
         <v>2.548688372146674</v>
       </c>
       <c r="D379" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E379">
         <v>2.44021981851742</v>
@@ -20488,7 +20491,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20502,7 +20505,7 @@
         <v>4.064626779899114</v>
       </c>
       <c r="D380" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E380">
         <v>3.971827788774664</v>
@@ -20538,7 +20541,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20552,7 +20555,7 @@
         <v>2.704221825320051</v>
       </c>
       <c r="D381" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E381">
         <v>2.757514946748523</v>
@@ -20588,7 +20591,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20602,7 +20605,7 @@
         <v>2.699698304540886</v>
       </c>
       <c r="D382" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E382">
         <v>2.757514946748523</v>
@@ -20638,7 +20641,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20652,7 +20655,7 @@
         <v>2.597723564836138</v>
       </c>
       <c r="D383" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E383">
         <v>2.648687698460786</v>
@@ -20688,7 +20691,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20702,7 +20705,7 @@
         <v>2.594470401040876</v>
       </c>
       <c r="D384" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E384">
         <v>2.648687698460786</v>
@@ -20738,7 +20741,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20752,7 +20755,7 @@
         <v>2.5327482758737</v>
       </c>
       <c r="D385" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E385">
         <v>2.582291478725809</v>
@@ -20788,7 +20791,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20802,7 +20805,7 @@
         <v>2.530270165227095</v>
       </c>
       <c r="D386" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E386">
         <v>2.582291478725809</v>
@@ -20838,7 +20841,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20852,7 +20855,7 @@
         <v>2.615226386520305</v>
       </c>
       <c r="D387" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E387">
         <v>2.605226386520305</v>
@@ -20888,7 +20891,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20902,7 +20905,7 @@
         <v>2.519210324106</v>
       </c>
       <c r="D388" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E388">
         <v>2.474919909368535</v>
@@ -20938,7 +20941,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20952,7 +20955,7 @@
         <v>2.443973795685154</v>
       </c>
       <c r="D389" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E389">
         <v>2.491575608314453</v>
@@ -20988,7 +20991,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21002,7 +21005,7 @@
         <v>2.442554625160083</v>
       </c>
       <c r="D390" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E390">
         <v>2.491575608314453</v>
@@ -21038,7 +21041,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21088,7 +21091,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21102,7 +21105,7 @@
         <v>2.457705873063223</v>
       </c>
       <c r="D392" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E392">
         <v>2.413049360402885</v>
@@ -21138,7 +21141,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21152,7 +21155,7 @@
         <v>2.382591377283335</v>
       </c>
       <c r="D393" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E393">
         <v>2.428850830862097</v>
@@ -21188,7 +21191,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21202,7 +21205,7 @@
         <v>2.381904402604011</v>
       </c>
       <c r="D394" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E394">
         <v>2.428850830862097</v>
@@ -21238,7 +21241,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21252,7 +21255,7 @@
         <v>2.46327835196266</v>
       </c>
       <c r="D395" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E395">
         <v>2.453507343522435</v>
@@ -21288,7 +21291,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21302,7 +21305,7 @@
         <v>2.467705873063223</v>
       </c>
       <c r="D396" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E396">
         <v>2.453507343522435</v>
@@ -21338,7 +21341,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21352,7 +21355,7 @@
         <v>2.447999298642713</v>
       </c>
       <c r="D397" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E397">
         <v>2.403285008753682</v>
@@ -21388,7 +21391,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21402,7 +21405,7 @@
         <v>2.372904061939057</v>
       </c>
       <c r="D398" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E398">
         <v>2.418951665679276</v>
@@ -21438,7 +21441,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21452,7 +21455,7 @@
         <v>2.37233264171712</v>
       </c>
       <c r="D399" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E399">
         <v>2.418951665679276</v>
@@ -21488,7 +21491,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21538,7 +21541,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21588,7 +21591,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21602,7 +21605,7 @@
         <v>2.414261420787727</v>
       </c>
       <c r="D402" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E402">
         <v>2.369346310197177</v>
@@ -21638,7 +21641,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21688,7 +21691,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21738,7 +21741,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21752,7 +21755,7 @@
         <v>2.424261420787727</v>
       </c>
       <c r="D405" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E405">
         <v>2.394544385485897</v>
@@ -21788,7 +21791,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21802,7 +21805,7 @@
         <v>2.414374606666995</v>
       </c>
       <c r="D406" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E406">
         <v>2.394544385485897</v>
@@ -21838,7 +21841,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21852,7 +21855,7 @@
         <v>2.397600622679596</v>
       </c>
       <c r="D407" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E407">
         <v>2.352586340671736</v>
@@ -21888,7 +21891,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21902,7 +21905,7 @@
         <v>2.322605383348882</v>
       </c>
       <c r="D408" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E408">
         <v>2.367553015986731</v>
@@ -21938,7 +21941,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21952,7 +21955,7 @@
         <v>2.322633947364601</v>
       </c>
       <c r="D409" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E409">
         <v>2.367553015986731</v>
@@ -21988,7 +21991,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22002,7 +22005,7 @@
         <v>2.402576819333163</v>
       </c>
       <c r="D410" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E410">
         <v>2.35256729799459</v>
@@ -22038,7 +22041,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22052,7 +22055,7 @@
         <v>2.407600622679595</v>
       </c>
       <c r="D411" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E411">
         <v>2.35256729799459</v>
@@ -22088,7 +22091,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22102,7 +22105,7 @@
         <v>2.39758158000245</v>
       </c>
       <c r="D412" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E412">
         <v>2.35256729799459</v>
@@ -22138,7 +22141,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22152,7 +22155,7 @@
         <v>2.378737718650321</v>
       </c>
       <c r="D413" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E413">
         <v>2.33361115745181</v>
@@ -22188,7 +22191,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22202,7 +22205,7 @@
         <v>2.30377990571649</v>
       </c>
       <c r="D414" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E414">
         <v>2.348315847988621</v>
@@ -22238,7 +22241,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22252,7 +22255,7 @@
         <v>2.304033028113511</v>
       </c>
       <c r="D415" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E415">
         <v>2.348315847988621</v>
@@ -22288,7 +22291,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22302,7 +22305,7 @@
         <v>2.383526783319471</v>
       </c>
       <c r="D416" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E416">
         <v>2.333442409187131</v>
@@ -22338,7 +22341,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22352,7 +22355,7 @@
         <v>2.38873771865032</v>
       </c>
       <c r="D417" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E417">
         <v>2.333442409187131</v>
@@ -22388,7 +22391,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22402,7 +22405,7 @@
         <v>2.378568970385641</v>
       </c>
       <c r="D418" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E418">
         <v>2.333442409187131</v>
@@ -22438,7 +22441,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22452,7 +22455,7 @@
         <v>2.29477967980894</v>
       </c>
       <c r="D419" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E419">
         <v>2.33911879805526</v>
@@ -22502,7 +22505,7 @@
         <v>2.295140160765494</v>
       </c>
       <c r="D420" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E420">
         <v>2.33911879805526</v>
@@ -22552,7 +22555,7 @@
         <v>2.374419198852388</v>
       </c>
       <c r="D421" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E421">
         <v>2.324299038533536</v>
@@ -22602,7 +22605,7 @@
         <v>2.379719599649515</v>
       </c>
       <c r="D422" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E422">
         <v>2.324299038533536</v>
@@ -22652,7 +22655,7 @@
         <v>2.369479279011813</v>
       </c>
       <c r="D423" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E423">
         <v>2.324299038533536</v>
@@ -22702,7 +22705,7 @@
         <v>2.280590400920047</v>
       </c>
       <c r="D424" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E424">
         <v>2.324619216844741</v>
@@ -22738,7 +22741,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22752,7 +22755,7 @@
         <v>2.281120137688396</v>
       </c>
       <c r="D425" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E425">
         <v>2.324619216844741</v>
@@ -22788,7 +22791,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22802,7 +22805,7 @@
         <v>2.360060664151698</v>
       </c>
       <c r="D426" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E426">
         <v>2.309884085228915</v>
@@ -22838,7 +22841,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22888,7 +22891,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22902,7 +22905,7 @@
         <v>2.281700069738552</v>
       </c>
       <c r="D428" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E428">
         <v>2.325753152774585</v>
@@ -22938,7 +22941,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -22952,7 +22955,7 @@
         <v>2.282216569900716</v>
       </c>
       <c r="D429" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E429">
         <v>2.325753152774585</v>
@@ -22988,7 +22991,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23002,7 +23005,7 @@
         <v>2.361183569576388</v>
       </c>
       <c r="D430" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E430">
         <v>2.311011402855666</v>
@@ -23038,7 +23041,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23052,7 +23055,7 @@
         <v>2.255753152774584</v>
       </c>
       <c r="D431" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E431">
         <v>2.30032273597278</v>
@@ -23088,7 +23091,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23102,7 +23105,7 @@
         <v>2.248769782041177</v>
       </c>
       <c r="D432" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E432">
         <v>2.297801715354081</v>
@@ -23138,7 +23141,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23152,7 +23155,7 @@
         <v>2.343406757033516</v>
       </c>
       <c r="D433" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E433">
         <v>2.293164740361742</v>
@@ -23188,7 +23191,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23202,7 +23205,7 @@
         <v>2.237801715354081</v>
       </c>
       <c r="D434" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E434">
         <v>2.26243869034642</v>
@@ -23238,7 +23241,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23252,7 +23255,7 @@
         <v>2.228095614122554</v>
       </c>
       <c r="D435" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E435">
         <v>2.276800683120539</v>
@@ -23288,7 +23291,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23302,7 +23305,7 @@
         <v>2.322610014996799</v>
       </c>
       <c r="D436" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E436">
         <v>2.263257480497806</v>
@@ -23338,7 +23341,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23388,7 +23391,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23402,7 +23405,7 @@
         <v>2.224983216186275</v>
       </c>
       <c r="D438" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E438">
         <v>2.273639077311749</v>
@@ -23452,7 +23455,7 @@
         <v>2.319479164108328</v>
       </c>
       <c r="D439" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E439">
         <v>2.26015123354559</v>
@@ -23602,7 +23605,7 @@
         <v>2.3116287572162</v>
       </c>
       <c r="D442" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E442">
         <v>2.252362519438469</v>
@@ -23638,7 +23641,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23688,7 +23691,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23738,7 +23741,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23802,7 +23805,7 @@
         <v>2.185149484739352</v>
       </c>
       <c r="D446" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E446">
         <v>2.165149484739352</v>
@@ -23902,7 +23905,7 @@
         <v>2.20020073233055</v>
       </c>
       <c r="D448" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E448">
         <v>2.205687152603988</v>
@@ -23988,7 +23991,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24038,7 +24041,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24088,7 +24091,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24138,7 +24141,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24188,7 +24191,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24302,7 +24305,7 @@
         <v>2.142114930387524</v>
       </c>
       <c r="D456" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E456">
         <v>2.162114930387524</v>
@@ -24338,7 +24341,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24352,7 +24355,7 @@
         <v>2.115413806995409</v>
       </c>
       <c r="D457" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E457">
         <v>2.141244762127619</v>
@@ -24438,7 +24441,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24452,7 +24455,7 @@
         <v>2.073994682974101</v>
       </c>
       <c r="D459" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E459">
         <v>2.082201671198685</v>
@@ -24502,7 +24505,7 @@
         <v>2.083994682974101</v>
       </c>
       <c r="D460" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E460">
         <v>2.082201671198685</v>
@@ -24588,7 +24591,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24602,7 +24605,7 @@
         <v>2.057461365020192</v>
       </c>
       <c r="D462" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E462">
         <v>2.066125824243982</v>
@@ -24638,7 +24641,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24688,7 +24691,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24738,7 +24741,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24788,7 +24791,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24838,7 +24841,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24852,7 +24855,7 @@
         <v>2.057577737614682</v>
       </c>
       <c r="D467" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E467">
         <v>2.099815205781953</v>
@@ -24888,7 +24891,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24952,7 +24955,7 @@
         <v>2.075267052489131</v>
       </c>
       <c r="D469" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E469">
         <v>2.105974841560053</v>
@@ -25002,7 +25005,7 @@
         <v>2.0673904197019</v>
       </c>
       <c r="D470" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E470">
         <v>2.109513786914668</v>
@@ -25052,7 +25055,7 @@
         <v>2.101281730695467</v>
       </c>
       <c r="D471" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E471">
         <v>2.131889846669813</v>
@@ -25102,7 +25105,7 @@
         <v>2.093106078618507</v>
       </c>
       <c r="D472" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E472">
         <v>2.134930426541548</v>
@@ -25152,7 +25155,7 @@
         <v>2.114232378900782</v>
       </c>
       <c r="D473" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E473">
         <v>2.144790875533345</v>
@@ -25188,7 +25191,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25202,7 +25205,7 @@
         <v>2.164790875533345</v>
       </c>
       <c r="D474" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E474">
         <v>2.134232378900781</v>
@@ -25238,7 +25241,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25252,7 +25255,7 @@
         <v>2.105907868798473</v>
       </c>
       <c r="D475" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E475">
         <v>2.147583358696166</v>
@@ -25288,7 +25291,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25302,7 +25305,7 @@
         <v>2.178667208693582</v>
       </c>
       <c r="D476" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E476">
         <v>2.148162082573172</v>
@@ -25338,7 +25341,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25352,7 +25355,7 @@
         <v>2.119677460934401</v>
       </c>
       <c r="D477" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E477">
         <v>2.161192839295628</v>
@@ -25388,7 +25391,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25402,7 +25405,7 @@
         <v>2.191253934723685</v>
       </c>
       <c r="D478" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E478">
         <v>2.160797219088007</v>
@@ -25452,7 +25455,7 @@
         <v>2.132167365995042</v>
       </c>
       <c r="D479" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E479">
         <v>2.173537512902076</v>
@@ -25552,7 +25555,7 @@
         <v>2.161339958759847</v>
       </c>
       <c r="D481" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E481">
         <v>2.202370889471942</v>
@@ -25602,7 +25605,7 @@
         <v>2.215480849833102</v>
       </c>
       <c r="D482" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E482">
         <v>2.179965384477054</v>
@@ -25652,7 +25655,7 @@
         <v>1.276065947508897</v>
       </c>
       <c r="D483" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E483">
         <v>1.317566169928825</v>
@@ -25688,7 +25691,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25702,7 +25705,7 @@
         <v>1.37689891014235</v>
       </c>
       <c r="D484" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E484">
         <v>1.288399132562277</v>
@@ -25738,7 +25741,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25752,7 +25755,7 @@
         <v>1.265250934212467</v>
       </c>
       <c r="D485" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E485">
         <v>1.306889515011455</v>
@@ -25788,7 +25791,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25802,7 +25805,7 @@
         <v>1.365853299547489</v>
       </c>
       <c r="D486" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E486">
         <v>1.277491880346475</v>
@@ -25838,51 +25841,51 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="487" spans="1:16">
       <c r="A487" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B487" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C487">
-        <v>1.257848770795328</v>
+        <v>1.365250934212467</v>
       </c>
       <c r="D487" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E487">
-        <v>1.29958204878089</v>
+        <v>1.29891353608099</v>
       </c>
       <c r="F487">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G487">
-        <v>0.007782151229204671</v>
+        <v>0.007874749065787534</v>
       </c>
       <c r="H487">
-        <v>0.00774041795121911</v>
+        <v>0.00796108646391901</v>
       </c>
       <c r="I487">
-        <v>0.04173327798556148</v>
+        <v>0.06633739813147699</v>
       </c>
       <c r="J487">
-        <v>0.6955546330926804</v>
+        <v>0.6939763466497937</v>
       </c>
       <c r="K487">
         <v>4.69</v>
       </c>
       <c r="L487">
-        <v>4.52</v>
+        <v>4.62</v>
       </c>
       <c r="M487">
+        <v>4.8</v>
+      </c>
+      <c r="N487">
         <v>4.63</v>
-      </c>
-      <c r="N487">
-        <v>4.52</v>
       </c>
       <c r="O487">
         <v>1</v>
@@ -25893,46 +25896,46 @@
     </row>
     <row r="488" spans="1:16">
       <c r="A488" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B488" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C488">
-        <v>1.358293307486061</v>
+        <v>1.335853299547488</v>
       </c>
       <c r="D488" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E488">
-        <v>1.270026585471621</v>
+        <v>1.29891353608099</v>
       </c>
       <c r="F488">
         <v>-1</v>
       </c>
       <c r="G488">
-        <v>0.00802170669251394</v>
+        <v>0.007984146700452513</v>
       </c>
       <c r="H488">
-        <v>0.007849973414528378</v>
+        <v>0.00796108646391901</v>
       </c>
       <c r="I488">
-        <v>0.08826672201444019</v>
+        <v>0.03693976346649785</v>
       </c>
       <c r="J488">
-        <v>0.6955546330926804</v>
+        <v>0.6939763466497937</v>
       </c>
       <c r="K488">
         <v>4.79</v>
       </c>
       <c r="L488">
-        <v>4.69</v>
+        <v>4.66</v>
       </c>
       <c r="M488">
-        <v>4.73</v>
+        <v>4.8</v>
       </c>
       <c r="N488">
-        <v>4.56</v>
+        <v>4.63</v>
       </c>
       <c r="O488">
         <v>1</v>
@@ -25943,31 +25946,31 @@
     </row>
     <row r="489" spans="1:16">
       <c r="A489" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B489" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C489">
-        <v>1.357848770795329</v>
+        <v>1.257848770795328</v>
       </c>
       <c r="D489" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E489">
-        <v>1.328293307486061</v>
+        <v>1.29958204878089</v>
       </c>
       <c r="F489">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G489">
-        <v>0.007882151229204671</v>
+        <v>0.007782151229204671</v>
       </c>
       <c r="H489">
-        <v>0.00799170669251394</v>
+        <v>0.00774041795121911</v>
       </c>
       <c r="I489">
-        <v>0.02955546330926762</v>
+        <v>0.04173327798556148</v>
       </c>
       <c r="J489">
         <v>0.6955546330926804</v>
@@ -25976,51 +25979,51 @@
         <v>4.69</v>
       </c>
       <c r="L489">
-        <v>4.62</v>
+        <v>4.52</v>
       </c>
       <c r="M489">
-        <v>4.79</v>
+        <v>4.63</v>
       </c>
       <c r="N489">
-        <v>4.66</v>
+        <v>4.52</v>
       </c>
       <c r="O489">
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="490" spans="1:16">
       <c r="A490" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B490" t="s">
         <v>147</v>
       </c>
       <c r="C490">
-        <v>1.336383675279734</v>
+        <v>1.358293307486061</v>
       </c>
       <c r="D490" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E490">
-        <v>1.248391395422367</v>
+        <v>1.270026585471621</v>
       </c>
       <c r="F490">
         <v>-1</v>
       </c>
       <c r="G490">
-        <v>0.008043616324720266</v>
+        <v>0.00802170669251394</v>
       </c>
       <c r="H490">
-        <v>0.007871608604577633</v>
+        <v>0.007849973414528378</v>
       </c>
       <c r="I490">
-        <v>0.08799227985736735</v>
+        <v>0.08826672201444019</v>
       </c>
       <c r="J490">
-        <v>0.7001286690438969</v>
+        <v>0.6955546330926804</v>
       </c>
       <c r="K490">
         <v>4.79</v>
@@ -26038,57 +26041,207 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>146</v>
+        <v>389</v>
       </c>
     </row>
     <row r="491" spans="1:16">
       <c r="A491" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B491" t="s">
         <v>149</v>
       </c>
       <c r="C491">
-        <v>1.1949083591831</v>
+        <v>1.328293307486061</v>
       </c>
       <c r="D491" t="s">
-        <v>147</v>
+        <v>274</v>
       </c>
       <c r="E491">
-        <v>1.279467032224208</v>
+        <v>1.291337761155134</v>
       </c>
       <c r="F491">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G491">
-        <v>0.0078450916408169</v>
+        <v>0.00799170669251394</v>
       </c>
       <c r="H491">
-        <v>0.008100532967775794</v>
+        <v>0.007968662238844865</v>
       </c>
       <c r="I491">
-        <v>0.08455867304110809</v>
+        <v>0.03695554633092701</v>
       </c>
       <c r="J491">
-        <v>0.7120110579907708</v>
+        <v>0.6955546330926804</v>
       </c>
       <c r="K491">
-        <v>4.67</v>
+        <v>4.79</v>
       </c>
       <c r="L491">
-        <v>4.52</v>
+        <v>4.66</v>
       </c>
       <c r="M491">
-        <v>4.79</v>
+        <v>4.8</v>
       </c>
       <c r="N491">
-        <v>4.69</v>
+        <v>4.63</v>
       </c>
       <c r="O491">
         <v>1</v>
       </c>
       <c r="P491" t="s">
         <v>389</v>
+      </c>
+    </row>
+    <row r="492" spans="1:16">
+      <c r="A492" s="1">
+        <v>0</v>
+      </c>
+      <c r="B492" t="s">
+        <v>147</v>
+      </c>
+      <c r="C492">
+        <v>1.336383675279734</v>
+      </c>
+      <c r="D492" t="s">
+        <v>273</v>
+      </c>
+      <c r="E492">
+        <v>1.248391395422367</v>
+      </c>
+      <c r="F492">
+        <v>-1</v>
+      </c>
+      <c r="G492">
+        <v>0.008043616324720266</v>
+      </c>
+      <c r="H492">
+        <v>0.007871608604577633</v>
+      </c>
+      <c r="I492">
+        <v>0.08799227985736735</v>
+      </c>
+      <c r="J492">
+        <v>0.7001286690438969</v>
+      </c>
+      <c r="K492">
+        <v>4.79</v>
+      </c>
+      <c r="L492">
+        <v>4.69</v>
+      </c>
+      <c r="M492">
+        <v>4.73</v>
+      </c>
+      <c r="N492">
+        <v>4.56</v>
+      </c>
+      <c r="O492">
+        <v>1</v>
+      </c>
+      <c r="P492" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="493" spans="1:16">
+      <c r="A493" s="1">
+        <v>1</v>
+      </c>
+      <c r="B493" t="s">
+        <v>149</v>
+      </c>
+      <c r="C493">
+        <v>1.306383675279734</v>
+      </c>
+      <c r="D493" t="s">
+        <v>274</v>
+      </c>
+      <c r="E493">
+        <v>1.269382388589295</v>
+      </c>
+      <c r="F493">
+        <v>-1</v>
+      </c>
+      <c r="G493">
+        <v>0.008013616324720267</v>
+      </c>
+      <c r="H493">
+        <v>0.007990617611410705</v>
+      </c>
+      <c r="I493">
+        <v>0.03700128669043901</v>
+      </c>
+      <c r="J493">
+        <v>0.7001286690438969</v>
+      </c>
+      <c r="K493">
+        <v>4.79</v>
+      </c>
+      <c r="L493">
+        <v>4.66</v>
+      </c>
+      <c r="M493">
+        <v>4.8</v>
+      </c>
+      <c r="N493">
+        <v>4.63</v>
+      </c>
+      <c r="O493">
+        <v>1</v>
+      </c>
+      <c r="P493" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="494" spans="1:16">
+      <c r="A494" s="1">
+        <v>0</v>
+      </c>
+      <c r="B494" t="s">
+        <v>150</v>
+      </c>
+      <c r="C494">
+        <v>1.1949083591831</v>
+      </c>
+      <c r="D494" t="s">
+        <v>147</v>
+      </c>
+      <c r="E494">
+        <v>1.279467032224208</v>
+      </c>
+      <c r="F494">
+        <v>1</v>
+      </c>
+      <c r="G494">
+        <v>0.0078450916408169</v>
+      </c>
+      <c r="H494">
+        <v>0.008100532967775794</v>
+      </c>
+      <c r="I494">
+        <v>0.08455867304110809</v>
+      </c>
+      <c r="J494">
+        <v>0.7120110579907708</v>
+      </c>
+      <c r="K494">
+        <v>4.67</v>
+      </c>
+      <c r="L494">
+        <v>4.52</v>
+      </c>
+      <c r="M494">
+        <v>4.79</v>
+      </c>
+      <c r="N494">
+        <v>4.69</v>
+      </c>
+      <c r="O494">
+        <v>1</v>
+      </c>
+      <c r="P494" t="s">
+        <v>390</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-03328-601328.xlsx
+++ b/s60_signal/position-03328-601328.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="393">
   <si>
     <t>trade_time</t>
   </si>
@@ -469,6 +469,9 @@
     <t>2021-10-27</t>
   </si>
   <si>
+    <t>2021-11-15</t>
+  </si>
+  <si>
     <t>2016-05-31</t>
   </si>
   <si>
@@ -839,6 +842,9 @@
   </si>
   <si>
     <t>2021-11-12</t>
+  </si>
+  <si>
+    <t>2021-11-16</t>
   </si>
   <si>
     <t>2016-05-24</t>
@@ -1544,7 +1550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P494"/>
+  <dimension ref="A1:P498"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1605,7 +1611,7 @@
         <v>2.636521639996683</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E2">
         <v>2.833647241107702</v>
@@ -1641,7 +1647,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1655,7 +1661,7 @@
         <v>2.808801457176021</v>
       </c>
       <c r="D3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E3">
         <v>2.7135041663212</v>
@@ -1691,7 +1697,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1705,7 +1711,7 @@
         <v>2.746397091058633</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E4">
         <v>2.648930323263125</v>
@@ -1755,7 +1761,7 @@
         <v>2.683209227271539</v>
       </c>
       <c r="D5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E5">
         <v>2.583545744375049</v>
@@ -1791,7 +1797,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1805,7 +1811,7 @@
         <v>2.555958070922727</v>
       </c>
       <c r="D6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E6">
         <v>2.632522016358742</v>
@@ -1841,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1855,7 +1861,7 @@
         <v>2.641252819939413</v>
       </c>
       <c r="D7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E7">
         <v>2.540130729835057</v>
@@ -1891,7 +1897,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1905,7 +1911,7 @@
         <v>2.512285655110759</v>
       </c>
       <c r="D8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E8">
         <v>2.590994611146576</v>
@@ -1941,7 +1947,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1955,7 +1961,7 @@
         <v>2.615441102246784</v>
       </c>
       <c r="D9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E9">
         <v>2.513421672263544</v>
@@ -1991,7 +1997,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2005,7 +2011,7 @@
         <v>2.515418243442972</v>
       </c>
       <c r="D10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E10">
         <v>2.545423958143926</v>
@@ -2041,7 +2047,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2055,7 +2061,7 @@
         <v>2.487273994427867</v>
       </c>
       <c r="D11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E11">
         <v>2.567211421027677</v>
@@ -2091,7 +2097,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2105,7 +2111,7 @@
         <v>2.487984580081365</v>
       </c>
       <c r="D12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E12">
         <v>2.579898802553291</v>
@@ -2141,7 +2147,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2155,7 +2161,7 @@
         <v>2.500805561667341</v>
       </c>
       <c r="D13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E13">
         <v>2.59216563562278</v>
@@ -2191,7 +2197,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2205,7 +2211,7 @@
         <v>2.499441989042522</v>
       </c>
       <c r="D14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E14">
         <v>2.736702547602069</v>
@@ -2255,7 +2261,7 @@
         <v>2.512520850741042</v>
       </c>
       <c r="D15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E15">
         <v>2.749061943431123</v>
@@ -2291,7 +2297,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2305,7 +2311,7 @@
         <v>2.77984350091858</v>
       </c>
       <c r="D16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E16">
         <v>2.889061943431122</v>
@@ -2341,7 +2347,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2355,7 +2361,7 @@
         <v>2.517224153471577</v>
       </c>
       <c r="D17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E17">
         <v>2.753506518310076</v>
@@ -2391,7 +2397,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2405,7 +2411,7 @@
         <v>2.784426680003737</v>
       </c>
       <c r="D18" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E18">
         <v>2.924119959439183</v>
@@ -2441,7 +2447,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2455,7 +2461,7 @@
         <v>2.884280694854824</v>
       </c>
       <c r="D19" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E19">
         <v>2.961861794886389</v>
@@ -2505,7 +2511,7 @@
         <v>2.920719956495094</v>
       </c>
       <c r="D20" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E20">
         <v>2.907075620138133</v>
@@ -2541,7 +2547,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2555,7 +2561,7 @@
         <v>2.648180125005333</v>
       </c>
       <c r="D21" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E21">
         <v>2.848908919700521</v>
@@ -2591,7 +2597,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2641,7 +2647,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2655,7 +2661,7 @@
         <v>2.691620213913162</v>
       </c>
       <c r="D23" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E23">
         <v>2.889959376998489</v>
@@ -2691,7 +2697,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2705,7 +2711,7 @@
         <v>2.984719616116966</v>
       </c>
       <c r="D24" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E24">
         <v>2.755965243802971</v>
@@ -2741,7 +2747,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2755,7 +2761,7 @@
         <v>3.007275184023352</v>
       </c>
       <c r="D25" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E25">
         <v>2.755965243802971</v>
@@ -2791,7 +2797,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2805,7 +2811,7 @@
         <v>2.683495528297218</v>
       </c>
       <c r="D26" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E26">
         <v>2.882281628901694</v>
@@ -2841,7 +2847,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2855,7 +2861,7 @@
         <v>2.976914171586129</v>
       </c>
       <c r="D27" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E27">
         <v>2.747824596132772</v>
@@ -2891,7 +2897,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2905,7 +2911,7 @@
         <v>2.647048085674867</v>
       </c>
       <c r="D28" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E28">
         <v>2.84783915365346</v>
@@ -2941,7 +2947,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2955,7 +2961,7 @@
         <v>2.941898848516719</v>
       </c>
       <c r="D29" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E29">
         <v>2.711305547532774</v>
@@ -2991,7 +2997,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3005,7 +3011,7 @@
         <v>2.962790623816959</v>
       </c>
       <c r="D30" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E30">
         <v>2.711305547532774</v>
@@ -3041,7 +3047,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3055,7 +3061,7 @@
         <v>2.636850318680218</v>
       </c>
       <c r="D31" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E31">
         <v>2.674077933106496</v>
@@ -3091,7 +3097,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3105,7 +3111,7 @@
         <v>2.64386308474694</v>
       </c>
       <c r="D32" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E32">
         <v>2.844829359063415</v>
@@ -3141,7 +3147,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3155,7 +3161,7 @@
         <v>2.938838994972993</v>
       </c>
       <c r="D33" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E33">
         <v>2.708114289235636</v>
@@ -3191,7 +3197,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3205,7 +3211,7 @@
         <v>2.959611880258242</v>
       </c>
       <c r="D34" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E34">
         <v>2.708114289235636</v>
@@ -3241,7 +3247,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3255,7 +3261,7 @@
         <v>2.63362151616782</v>
       </c>
       <c r="D35" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E35">
         <v>2.706375129633912</v>
@@ -3291,7 +3297,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3305,7 +3311,7 @@
         <v>2.623711665472045</v>
       </c>
       <c r="D36" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E36">
         <v>2.825786465799713</v>
@@ -3341,7 +3347,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3355,7 +3361,7 @@
         <v>2.919479379991807</v>
       </c>
       <c r="D37" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E37">
         <v>2.687923279746057</v>
@@ -3391,7 +3397,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3405,7 +3411,7 @@
         <v>2.939500051198033</v>
       </c>
       <c r="D38" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E38">
         <v>2.687923279746057</v>
@@ -3441,7 +3447,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3455,7 +3461,7 @@
         <v>2.613192965390128</v>
       </c>
       <c r="D39" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E39">
         <v>2.65740457966414</v>
@@ -3491,7 +3497,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3505,7 +3511,7 @@
         <v>2.866121269202039</v>
       </c>
       <c r="D40" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E40">
         <v>2.632273716345684</v>
@@ -3555,7 +3561,7 @@
         <v>2.884068721379623</v>
       </c>
       <c r="D41" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E41">
         <v>2.632273716345684</v>
@@ -3605,7 +3611,7 @@
         <v>2.556888701243869</v>
       </c>
       <c r="D42" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E42">
         <v>2.5709911987269</v>
@@ -3655,7 +3661,7 @@
         <v>2.84066903268222</v>
       </c>
       <c r="D43" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E43">
         <v>2.605728438993726</v>
@@ -3691,7 +3697,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3705,7 +3711,7 @@
         <v>2.857627543154535</v>
       </c>
       <c r="D44" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E44">
         <v>2.605728438993726</v>
@@ -3741,7 +3747,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3755,7 +3761,7 @@
         <v>2.530031126511299</v>
       </c>
       <c r="D45" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E45">
         <v>2.536232918189681</v>
@@ -3791,7 +3797,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3805,7 +3811,7 @@
         <v>2.794653597980052</v>
       </c>
       <c r="D46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E46">
         <v>2.557736881328888</v>
@@ -3841,7 +3847,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3855,7 +3861,7 @@
         <v>2.809824187676618</v>
       </c>
       <c r="D47" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E47">
         <v>2.557736881328888</v>
@@ -3891,7 +3897,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3941,7 +3947,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3955,7 +3961,7 @@
         <v>2.877968395292299</v>
       </c>
       <c r="D49" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E49">
         <v>2.644629614722029</v>
@@ -3991,7 +3997,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4005,7 +4011,7 @@
         <v>2.896376165252531</v>
       </c>
       <c r="D50" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E50">
         <v>2.644629614722029</v>
@@ -4041,7 +4047,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4055,7 +4061,7 @@
         <v>2.521770137334771</v>
       </c>
       <c r="D51" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E51">
         <v>2.535896862069519</v>
@@ -4091,7 +4097,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4105,7 +4111,7 @@
         <v>2.934431839092635</v>
       </c>
       <c r="D52" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E52">
         <v>2.703517868992319</v>
@@ -4141,7 +4147,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4155,7 +4161,7 @@
         <v>2.955033485192349</v>
       </c>
       <c r="D53" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E53">
         <v>2.703517868992319</v>
@@ -4191,7 +4197,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4241,7 +4247,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4255,7 +4261,7 @@
         <v>2.974730272968942</v>
       </c>
       <c r="D55" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E55">
         <v>2.745546910458406</v>
@@ -4291,7 +4297,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4305,7 +4311,7 @@
         <v>2.996897706887981</v>
       </c>
       <c r="D56" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E56">
         <v>2.745546910458406</v>
@@ -4341,7 +4347,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4355,7 +4361,7 @@
         <v>2.624468326525319</v>
       </c>
       <c r="D57" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E57">
         <v>2.660688149733082</v>
@@ -4391,7 +4397,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4405,7 +4411,7 @@
         <v>3.056805462611843</v>
       </c>
       <c r="D58" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E58">
         <v>2.831146801497014</v>
@@ -4441,7 +4447,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4491,7 +4497,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4505,7 +4511,7 @@
         <v>3.075488420323122</v>
       </c>
       <c r="D60" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E60">
         <v>2.850632094815525</v>
@@ -4555,7 +4561,7 @@
         <v>2.73140795531227</v>
       </c>
       <c r="D61" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E61">
         <v>2.75953055997749</v>
@@ -4605,7 +4611,7 @@
         <v>2.72765316464271</v>
       </c>
       <c r="D62" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E62">
         <v>2.75953055997749</v>
@@ -4655,7 +4661,7 @@
         <v>2.72671446697532</v>
       </c>
       <c r="D63" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E63">
         <v>2.75953055997749</v>
@@ -4705,7 +4711,7 @@
         <v>6.293149296554828</v>
       </c>
       <c r="D64" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E64">
         <v>5.963700498102364</v>
@@ -4741,7 +4747,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4755,7 +4761,7 @@
         <v>6.420239880180696</v>
       </c>
       <c r="D65" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E65">
         <v>6.082402264327184</v>
@@ -4791,7 +4797,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4805,7 +4811,7 @@
         <v>6.609514294497387</v>
       </c>
       <c r="D66" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E66">
         <v>6.259183317962906</v>
@@ -4841,7 +4847,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4855,7 +4861,7 @@
         <v>6.515171551263329</v>
       </c>
       <c r="D67" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E67">
         <v>6.612047937164794</v>
@@ -4891,7 +4897,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4905,7 +4911,7 @@
         <v>6.520829737768901</v>
       </c>
       <c r="D68" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E68">
         <v>6.612047937164794</v>
@@ -4941,7 +4947,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4991,7 +4997,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5041,7 +5047,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5091,7 +5097,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5105,7 +5111,7 @@
         <v>6.781478804637512</v>
       </c>
       <c r="D72" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E72">
         <v>6.821616798629249</v>
@@ -5141,7 +5147,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5155,7 +5161,7 @@
         <v>6.927933775178332</v>
       </c>
       <c r="D73" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E73">
         <v>7.025464228815041</v>
@@ -5191,7 +5197,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5205,7 +5211,7 @@
         <v>7.465293617228137</v>
       </c>
       <c r="D74" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E74">
         <v>7.441132824526438</v>
@@ -5241,7 +5247,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5255,7 +5261,7 @@
         <v>2.399740228983164</v>
       </c>
       <c r="D75" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E75">
         <v>2.284756328614283</v>
@@ -5291,7 +5297,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5305,7 +5311,7 @@
         <v>2.181146111927123</v>
       </c>
       <c r="D76" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E76">
         <v>2.105842395854763</v>
@@ -5341,7 +5347,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5355,7 +5361,7 @@
         <v>2.180858495485883</v>
       </c>
       <c r="D77" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E77">
         <v>2.105842395854763</v>
@@ -5391,7 +5397,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5405,7 +5411,7 @@
         <v>2.355267416838251</v>
       </c>
       <c r="D78" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E78">
         <v>2.241615480893012</v>
@@ -5441,7 +5447,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5455,7 +5461,7 @@
         <v>2.138079262229388</v>
       </c>
       <c r="D79" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E79">
         <v>2.115876072829124</v>
@@ -5491,7 +5497,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5505,7 +5511,7 @@
         <v>2.136977667529256</v>
       </c>
       <c r="D80" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E80">
         <v>2.115876072829124</v>
@@ -5541,7 +5547,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5591,7 +5597,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5641,7 +5647,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5691,7 +5697,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5705,7 +5711,7 @@
         <v>1.925553832103902</v>
       </c>
       <c r="D84" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E84">
         <v>1.985821650998686</v>
@@ -5741,7 +5747,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5791,7 +5797,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5805,7 +5811,7 @@
         <v>1.87975631937778</v>
       </c>
       <c r="D86" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E86">
         <v>2.025900250164519</v>
@@ -5841,7 +5847,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5941,7 +5947,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5955,7 +5961,7 @@
         <v>1.789383875507923</v>
       </c>
       <c r="D89" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E89">
         <v>1.940268655809146</v>
@@ -5991,7 +5997,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6005,7 +6011,7 @@
         <v>1.804905667333501</v>
       </c>
       <c r="D90" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E90">
         <v>1.95497618970289</v>
@@ -6041,7 +6047,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6055,7 +6061,7 @@
         <v>1.809491967335235</v>
       </c>
       <c r="D91" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E91">
         <v>1.959321896917648</v>
@@ -6091,7 +6097,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6105,7 +6111,7 @@
         <v>1.822908408572121</v>
       </c>
       <c r="D92" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E92">
         <v>1.972034524843747</v>
@@ -6141,7 +6147,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6155,7 +6161,7 @@
         <v>2.011491451443282</v>
       </c>
       <c r="D93" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E93">
         <v>1.930405304642352</v>
@@ -6191,7 +6197,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6205,7 +6211,7 @@
         <v>1.820166348365971</v>
       </c>
       <c r="D94" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E94">
         <v>1.969436310418903</v>
@@ -6241,7 +6247,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6255,7 +6261,7 @@
         <v>2.008879751476441</v>
       </c>
       <c r="D95" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E95">
         <v>1.927766633591516</v>
@@ -6291,7 +6297,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6305,7 +6311,7 @@
         <v>1.780154910291897</v>
       </c>
       <c r="D96" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E96">
         <v>1.931523833030682</v>
@@ -6341,7 +6347,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6391,7 +6397,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6405,7 +6411,7 @@
         <v>1.781411528733962</v>
       </c>
       <c r="D98" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E98">
         <v>1.932714530505294</v>
@@ -6441,7 +6447,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6491,7 +6497,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6505,7 +6511,7 @@
         <v>1.786869994736246</v>
       </c>
       <c r="D100" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E100">
         <v>1.937886650750082</v>
@@ -6555,7 +6561,7 @@
         <v>1.77389224303264</v>
       </c>
       <c r="D101" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E101">
         <v>1.925589699135846</v>
@@ -6591,7 +6597,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6605,7 +6611,7 @@
         <v>1.764225388294109</v>
       </c>
       <c r="D102" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E102">
         <v>1.916429958088516</v>
@@ -6805,7 +6811,7 @@
         <v>2.039049007419374</v>
       </c>
       <c r="D106" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E106">
         <v>1.958247448115615</v>
@@ -6841,7 +6847,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6855,7 +6861,7 @@
         <v>1.963804213639886</v>
       </c>
       <c r="D107" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E107">
         <v>2.044635472991321</v>
@@ -6891,7 +6897,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6905,7 +6911,7 @@
         <v>2.084469221121035</v>
       </c>
       <c r="D108" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E108">
         <v>2.00413671738046</v>
@@ -6941,7 +6947,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6955,7 +6961,7 @@
         <v>1.970692549466935</v>
       </c>
       <c r="D109" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E109">
         <v>2.103970465510173</v>
@@ -6991,7 +6997,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7041,7 +7047,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7055,7 +7061,7 @@
         <v>1.989826166099606</v>
       </c>
       <c r="D111" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E111">
         <v>2.069999197311251</v>
@@ -7091,7 +7097,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7105,7 +7111,7 @@
         <v>1.996538974422711</v>
       </c>
       <c r="D112" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E112">
         <v>2.129860772341935</v>
@@ -7141,7 +7147,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7191,7 +7197,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7205,7 +7211,7 @@
         <v>1.976959483296697</v>
       </c>
       <c r="D114" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E114">
         <v>2.110248039295503</v>
@@ -7305,7 +7311,7 @@
         <v>1.920546112528168</v>
       </c>
       <c r="D116" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E116">
         <v>2.053738890308352</v>
@@ -7341,7 +7347,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7391,7 +7397,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7405,7 +7411,7 @@
         <v>2.078859445890371</v>
       </c>
       <c r="D118" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E118">
         <v>2.128859445890371</v>
@@ -7441,7 +7447,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7455,7 +7461,7 @@
         <v>1.864471846503076</v>
       </c>
       <c r="D119" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E119">
         <v>1.997569421794252</v>
@@ -7491,7 +7497,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7541,7 +7547,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7591,7 +7597,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7605,7 +7611,7 @@
         <v>1.863420505387863</v>
       </c>
       <c r="D122" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E122">
         <v>1.996516295719591</v>
@@ -7705,7 +7711,7 @@
         <v>2.029857360363785</v>
       </c>
       <c r="D124" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E124">
         <v>2.011995247378231</v>
@@ -7755,7 +7761,7 @@
         <v>1.892165706973767</v>
       </c>
       <c r="D125" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E125">
         <v>2.025310300703773</v>
@@ -7791,7 +7797,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7841,7 +7847,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7891,7 +7897,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7955,7 +7961,7 @@
         <v>2.183293967129219</v>
       </c>
       <c r="D129" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E129">
         <v>2.097698061214447</v>
@@ -8005,7 +8011,7 @@
         <v>2.10409703769314</v>
       </c>
       <c r="D130" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E130">
         <v>2.097698061214447</v>
@@ -8091,7 +8097,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8141,7 +8147,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8191,7 +8197,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8241,7 +8247,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8291,7 +8297,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8341,7 +8347,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8391,7 +8397,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8441,7 +8447,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8455,7 +8461,7 @@
         <v>2.367284598691813</v>
       </c>
       <c r="D139" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E139">
         <v>2.284677125480481</v>
@@ -8505,7 +8511,7 @@
         <v>2.308705785003503</v>
       </c>
       <c r="D140" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E140">
         <v>2.284677125480481</v>
@@ -8641,7 +8647,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8691,7 +8697,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8741,7 +8747,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8791,7 +8797,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8841,7 +8847,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8905,7 +8911,7 @@
         <v>2.673055621612132</v>
       </c>
       <c r="D148" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E148">
         <v>2.649383477311975</v>
@@ -8955,7 +8961,7 @@
         <v>2.694510447967022</v>
       </c>
       <c r="D149" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E149">
         <v>2.66746656530884</v>
@@ -9005,7 +9011,7 @@
         <v>2.61961842602696</v>
       </c>
       <c r="D150" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E150">
         <v>2.674946565009619</v>
@@ -9291,7 +9297,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9305,7 +9311,7 @@
         <v>2.746485076848839</v>
       </c>
       <c r="D156" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E156">
         <v>2.847982602490786</v>
@@ -9341,7 +9347,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9405,7 +9411,7 @@
         <v>2.750734210259811</v>
       </c>
       <c r="D158" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E158">
         <v>2.800734210259812</v>
@@ -9441,7 +9447,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9505,7 +9511,7 @@
         <v>2.717092536535202</v>
       </c>
       <c r="D160" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E160">
         <v>2.791717770085309</v>
@@ -9591,7 +9597,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9605,7 +9611,7 @@
         <v>2.669840281895235</v>
       </c>
       <c r="D162" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E162">
         <v>2.754805459723328</v>
@@ -9641,7 +9647,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9705,7 +9711,7 @@
         <v>2.704152220032186</v>
       </c>
       <c r="D164" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E164">
         <v>2.721608307945189</v>
@@ -9755,7 +9761,7 @@
         <v>0.7516342779874527</v>
       </c>
       <c r="D165" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E165">
         <v>0.6447312303040151</v>
@@ -9791,7 +9797,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9805,7 +9811,7 @@
         <v>0.6347312303040145</v>
       </c>
       <c r="D166" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E166">
         <v>0.7803954970608276</v>
@@ -9841,7 +9847,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9855,7 +9861,7 @@
         <v>0.7872985447442655</v>
       </c>
       <c r="D167" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E167">
         <v>0.6685373256708909</v>
@@ -9891,7 +9897,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9905,7 +9911,7 @@
         <v>0.6141118398407031</v>
       </c>
       <c r="D168" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E168">
         <v>0.7042015924277036</v>
@@ -9941,7 +9947,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9955,7 +9961,7 @@
         <v>0.7076194190074974</v>
       </c>
       <c r="D169" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E169">
         <v>0.8524403513495589</v>
@@ -10005,7 +10011,7 @@
         <v>0.8587410173081755</v>
       </c>
       <c r="D170" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E170">
         <v>0.7402207509247285</v>
@@ -10055,7 +10061,7 @@
         <v>0.6868795521992208</v>
       </c>
       <c r="D171" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E171">
         <v>0.7750416832667906</v>
@@ -10105,7 +10111,7 @@
         <v>0.794311018129779</v>
       </c>
       <c r="D172" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E172">
         <v>0.9381289071762104</v>
@@ -10141,7 +10147,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10155,7 +10161,7 @@
         <v>0.7478436529603893</v>
       </c>
       <c r="D173" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E173">
         <v>0.9381289071762104</v>
@@ -10191,7 +10197,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10205,7 +10211,7 @@
         <v>0.9437131136379486</v>
       </c>
       <c r="D174" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E174">
         <v>0.8254794310532532</v>
@@ -10241,7 +10247,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10255,7 +10261,7 @@
         <v>0.7734278594221262</v>
       </c>
       <c r="D175" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E175">
         <v>0.8592973200996861</v>
@@ -10291,7 +10297,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10305,7 +10311,7 @@
         <v>0.9016190641047892</v>
       </c>
       <c r="D176" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E176">
         <v>1.04419537245399</v>
@@ -10341,7 +10347,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10355,7 +10361,7 @@
         <v>0.8558611736195321</v>
       </c>
       <c r="D177" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E177">
         <v>1.04419537245399</v>
@@ -10391,7 +10397,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10405,7 +10411,7 @@
         <v>1.048892735560562</v>
       </c>
       <c r="D178" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E178">
         <v>0.9310137903179339</v>
@@ -10441,7 +10447,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10455,7 +10461,7 @@
         <v>0.8805585367261042</v>
       </c>
       <c r="D179" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E179">
         <v>0.963590098667134</v>
@@ -10491,7 +10497,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10505,7 +10511,7 @@
         <v>1.076170489586433</v>
       </c>
       <c r="D180" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E180">
         <v>1.260525374010979</v>
@@ -10555,7 +10561,7 @@
         <v>1.26341395784032</v>
       </c>
       <c r="D181" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E181">
         <v>1.146258524308584</v>
@@ -10605,7 +10611,7 @@
         <v>1.099059073415773</v>
       </c>
       <c r="D182" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E182">
         <v>1.176302541669659</v>
@@ -10655,7 +10661,7 @@
         <v>1.931268098407571</v>
       </c>
       <c r="D183" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E183">
         <v>1.946759727730396</v>
@@ -10691,7 +10697,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10741,7 +10747,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10791,7 +10797,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10805,7 +10811,7 @@
         <v>0.5942088493584849</v>
       </c>
       <c r="D186" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E186">
         <v>0.5982130518354056</v>
@@ -10841,7 +10847,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10891,7 +10897,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10941,7 +10947,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10991,7 +10997,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11005,7 +11011,7 @@
         <v>-0.02499489055226256</v>
       </c>
       <c r="D190" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E190">
         <v>-0.07499489055226238</v>
@@ -11041,7 +11047,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11055,7 +11061,7 @@
         <v>-0.04541693580813089</v>
       </c>
       <c r="D191" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E191">
         <v>-0.1350880582477796</v>
@@ -11091,7 +11097,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11141,7 +11147,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11191,7 +11197,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11341,7 +11347,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11355,7 +11361,7 @@
         <v>-0.5154661476950757</v>
       </c>
       <c r="D197" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E197">
         <v>-0.4838284745942198</v>
@@ -11391,7 +11397,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11405,7 +11411,7 @@
         <v>-0.5144835438345625</v>
       </c>
       <c r="D198" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E198">
         <v>-0.4838284745942198</v>
@@ -11441,7 +11447,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11491,7 +11497,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11505,7 +11511,7 @@
         <v>-0.6795603356321358</v>
       </c>
       <c r="D200" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E200">
         <v>-0.6353746161347429</v>
@@ -11541,7 +11547,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11555,7 +11561,7 @@
         <v>-0.6770489039336995</v>
       </c>
       <c r="D201" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E201">
         <v>-0.6353746161347429</v>
@@ -11591,7 +11597,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11641,7 +11647,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11655,7 +11661,7 @@
         <v>-1.275160705635463</v>
       </c>
       <c r="D203" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E203">
         <v>-0.9575450227817477</v>
@@ -11691,7 +11697,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11705,7 +11711,7 @@
         <v>-1.267100202166811</v>
       </c>
       <c r="D204" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E204">
         <v>-0.9575450227817477</v>
@@ -11741,7 +11747,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11805,7 +11811,7 @@
         <v>-1.30354206111917</v>
       </c>
       <c r="D206" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E206">
         <v>-0.9846924062879019</v>
@@ -11855,7 +11861,7 @@
         <v>-1.295217135083899</v>
       </c>
       <c r="D207" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E207">
         <v>-0.9846924062879019</v>
@@ -11905,7 +11911,7 @@
         <v>-1.315601110783377</v>
       </c>
       <c r="D208" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E208">
         <v>-0.9962271494449686</v>
@@ -11955,7 +11961,7 @@
         <v>-1.307163833353718</v>
       </c>
       <c r="D209" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E209">
         <v>-0.9962271494449686</v>
@@ -12005,7 +12011,7 @@
         <v>-1.303470101275702</v>
       </c>
       <c r="D210" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E210">
         <v>-0.9846235751332797</v>
@@ -12041,7 +12047,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12055,7 +12061,7 @@
         <v>-1.295145845673754</v>
       </c>
       <c r="D211" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E211">
         <v>-0.9846235751332797</v>
@@ -12091,7 +12097,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12105,7 +12111,7 @@
         <v>-1.352240812118975</v>
       </c>
       <c r="D212" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E212">
         <v>-1.031273820287715</v>
@@ -12141,7 +12147,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12155,7 +12161,7 @@
         <v>-1.343462171012276</v>
       </c>
       <c r="D213" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E213">
         <v>-1.031273820287715</v>
@@ -12191,7 +12197,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12241,7 +12247,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12255,7 +12261,7 @@
         <v>-1.277973836666044</v>
       </c>
       <c r="D215" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E215">
         <v>-0.9602358437675207</v>
@@ -12305,7 +12311,7 @@
         <v>-1.269887123902075</v>
       </c>
       <c r="D216" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E216">
         <v>-0.9602358437675207</v>
@@ -12355,7 +12361,7 @@
         <v>-1.030235843767521</v>
       </c>
       <c r="D217" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E217">
         <v>-1.080019061857596</v>
@@ -12405,7 +12411,7 @@
         <v>-1.007888992711643</v>
       </c>
       <c r="D218" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E218">
         <v>-1.080019061857596</v>
@@ -12455,7 +12461,7 @@
         <v>-1.154349245698821</v>
       </c>
       <c r="D219" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E219">
         <v>-0.8419862350162637</v>
@@ -12505,7 +12511,7 @@
         <v>-1.147414314838273</v>
       </c>
       <c r="D220" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E220">
         <v>-0.8419862350162637</v>
@@ -12655,7 +12661,7 @@
         <v>-0.9332125637434627</v>
       </c>
       <c r="D223" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E223">
         <v>-0.6304641914067899</v>
@@ -12691,7 +12697,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12705,7 +12711,7 @@
         <v>-0.9283379125284608</v>
       </c>
       <c r="D224" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E224">
         <v>-0.6304641914067899</v>
@@ -12741,7 +12747,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12755,7 +12761,7 @@
         <v>-1.078298911794628</v>
       </c>
       <c r="D225" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E225">
         <v>-0.7337942740491279</v>
@@ -12805,7 +12811,7 @@
         <v>-1.284045732215318</v>
       </c>
       <c r="D226" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E226">
         <v>-0.9315166474955321</v>
@@ -12855,7 +12861,7 @@
         <v>-1.074552792811861</v>
       </c>
       <c r="D227" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E227">
         <v>-0.7301942595508679</v>
@@ -12891,7 +12897,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12905,7 +12911,7 @@
         <v>0.6306184682796347</v>
       </c>
       <c r="D228" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E228">
         <v>0.8825890610024754</v>
@@ -12941,7 +12947,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12955,7 +12961,7 @@
         <v>2.500083924851446</v>
       </c>
       <c r="D229" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E229">
         <v>2.721828222716436</v>
@@ -12991,7 +12997,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13005,7 +13011,7 @@
         <v>2.484743417251086</v>
       </c>
       <c r="D230" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E230">
         <v>2.721828222716436</v>
@@ -13041,7 +13047,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13055,7 +13061,7 @@
         <v>2.959498476516616</v>
       </c>
       <c r="D231" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E231">
         <v>3.019498476516616</v>
@@ -13091,7 +13097,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13141,7 +13147,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13155,7 +13161,7 @@
         <v>3.973072767193392</v>
       </c>
       <c r="D233" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E233">
         <v>3.630196829293595</v>
@@ -13191,7 +13197,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13241,7 +13247,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13291,7 +13297,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13305,7 +13311,7 @@
         <v>4.556254256131551</v>
       </c>
       <c r="D236" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E236">
         <v>4.211276763316661</v>
@@ -13341,7 +13347,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13391,7 +13397,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13441,7 +13447,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13455,7 +13461,7 @@
         <v>4.667791750685101</v>
       </c>
       <c r="D239" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E239">
         <v>4.322412320952902</v>
@@ -13491,7 +13497,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13505,7 +13511,7 @@
         <v>4.273963746622406</v>
       </c>
       <c r="D240" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E240">
         <v>4.266274031756307</v>
@@ -13541,7 +13547,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13591,7 +13597,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13641,7 +13647,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13655,7 +13661,7 @@
         <v>3.655351043939968</v>
       </c>
       <c r="D243" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E243">
         <v>3.313620049187031</v>
@@ -13691,7 +13697,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13705,7 +13711,7 @@
         <v>2.349652973133038</v>
       </c>
       <c r="D244" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E244">
         <v>2.585321458264525</v>
@@ -13755,7 +13761,7 @@
         <v>2.337296219946928</v>
       </c>
       <c r="D245" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E245">
         <v>2.585321458264525</v>
@@ -13805,7 +13811,7 @@
         <v>2.821499834857581</v>
       </c>
       <c r="D246" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E246">
         <v>2.482773709326562</v>
@@ -13855,7 +13861,7 @@
         <v>1.399171925433256</v>
       </c>
       <c r="D247" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E247">
         <v>1.7228188215915</v>
@@ -13891,7 +13897,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13905,7 +13911,7 @@
         <v>1.94957093986026</v>
       </c>
       <c r="D248" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E248">
         <v>1.61398690043734</v>
@@ -13941,7 +13947,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13955,7 +13961,7 @@
         <v>1.388298565840941</v>
       </c>
       <c r="D249" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E249">
         <v>1.05473712956764</v>
@@ -14005,7 +14011,7 @@
         <v>1.206849236469149</v>
       </c>
       <c r="D250" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E250">
         <v>0.8739416716530437</v>
@@ -14055,7 +14061,7 @@
         <v>1.250249534396463</v>
       </c>
       <c r="D251" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E251">
         <v>0.9171855721103492</v>
@@ -14105,7 +14111,7 @@
         <v>1.265784593473219</v>
       </c>
       <c r="D252" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E252">
         <v>0.9326646489922341</v>
@@ -14141,7 +14147,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14155,7 +14161,7 @@
         <v>1.181086185990114</v>
       </c>
       <c r="D253" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E253">
         <v>0.8482714609955542</v>
@@ -14205,7 +14211,7 @@
         <v>3.393868635799184</v>
       </c>
       <c r="D254" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E254">
         <v>3.232668972857903</v>
@@ -14241,7 +14247,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14255,7 +14261,7 @@
         <v>3.344337857016143</v>
       </c>
       <c r="D255" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E255">
         <v>3.232668972857903</v>
@@ -14291,7 +14297,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14305,7 +14311,7 @@
         <v>3.108144846549583</v>
       </c>
       <c r="D256" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E256">
         <v>3.176241351782863</v>
@@ -14341,7 +14347,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14355,7 +14361,7 @@
         <v>3.110765478091183</v>
       </c>
       <c r="D257" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E257">
         <v>3.176241351782863</v>
@@ -14391,7 +14397,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14405,7 +14411,7 @@
         <v>3.484929217459694</v>
       </c>
       <c r="D258" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E258">
         <v>3.328403460479749</v>
@@ -14441,7 +14447,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14455,7 +14461,7 @@
         <v>3.438944160440425</v>
       </c>
       <c r="D259" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E259">
         <v>3.328403460479749</v>
@@ -14491,7 +14497,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14541,7 +14547,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14591,7 +14597,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14605,7 +14611,7 @@
         <v>3.67612531160249</v>
       </c>
       <c r="D262" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E262">
         <v>3.529413159454653</v>
@@ -14641,7 +14647,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14655,7 +14661,7 @@
         <v>3.637585058248958</v>
       </c>
       <c r="D263" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E263">
         <v>3.529413159454653</v>
@@ -14691,7 +14697,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14705,7 +14711,7 @@
         <v>3.405388602484038</v>
       </c>
       <c r="D264" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E264">
         <v>3.509413159454653</v>
@@ -14741,7 +14747,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14755,7 +14761,7 @@
         <v>3.405511387337113</v>
       </c>
       <c r="D265" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E265">
         <v>3.509413159454653</v>
@@ -14791,7 +14797,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14805,7 +14811,7 @@
         <v>3.451364045513422</v>
       </c>
       <c r="D266" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E266">
         <v>3.509413159454653</v>
@@ -14841,7 +14847,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14855,7 +14861,7 @@
         <v>4.004636932335591</v>
       </c>
       <c r="D267" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E267">
         <v>3.867442887120403</v>
@@ -14905,7 +14911,7 @@
         <v>3.774439165379895</v>
       </c>
       <c r="D268" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E268">
         <v>3.837640654076098</v>
@@ -14955,7 +14961,7 @@
         <v>4.220199786446392</v>
       </c>
       <c r="D269" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E269">
         <v>4.085943565478028</v>
@@ -14991,7 +14997,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15005,7 +15011,7 @@
         <v>3.991103703583256</v>
       </c>
       <c r="D270" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E270">
         <v>4.0441357312043</v>
@@ -15041,7 +15047,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15055,7 +15061,7 @@
         <v>4.24807262091024</v>
       </c>
       <c r="D271" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E271">
         <v>4.172298835483293</v>
@@ -15091,7 +15097,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15105,7 +15111,7 @@
         <v>4.076733299050661</v>
       </c>
       <c r="D272" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E272">
         <v>4.185185728196767</v>
@@ -15141,7 +15147,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15205,7 +15211,7 @@
         <v>3.853669569225198</v>
       </c>
       <c r="D274" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E274">
         <v>3.960609701897911</v>
@@ -15341,7 +15347,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15355,7 +15361,7 @@
         <v>3.457860783201086</v>
       </c>
       <c r="D277" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E277">
         <v>3.562117466477025</v>
@@ -15391,7 +15397,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15405,7 +15411,7 @@
         <v>3.461796612382101</v>
       </c>
       <c r="D278" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E278">
         <v>3.45818163729601</v>
@@ -15441,7 +15447,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15505,7 +15511,7 @@
         <v>1.876063224574707</v>
       </c>
       <c r="D280" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E280">
         <v>1.926860456775207</v>
@@ -15555,7 +15561,7 @@
         <v>1.879462993924748</v>
       </c>
       <c r="D281" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E281">
         <v>1.926860456775207</v>
@@ -15605,7 +15611,7 @@
         <v>1.36286186891499</v>
       </c>
       <c r="D282" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E282">
         <v>1.420876924621103</v>
@@ -15641,7 +15647,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15655,7 +15661,7 @@
         <v>1.365396205962064</v>
       </c>
       <c r="D283" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E283">
         <v>1.420876924621103</v>
@@ -15691,7 +15697,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15705,7 +15711,7 @@
         <v>1.492587172538397</v>
       </c>
       <c r="D284" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E284">
         <v>1.422587172538397</v>
@@ -15741,7 +15747,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15755,7 +15761,7 @@
         <v>1.155028253713973</v>
       </c>
       <c r="D285" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E285">
         <v>1.207786135342488</v>
@@ -15805,7 +15811,7 @@
         <v>1.157212112489207</v>
       </c>
       <c r="D286" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E286">
         <v>1.207786135342488</v>
@@ -15855,7 +15861,7 @@
         <v>1.287557383512098</v>
       </c>
       <c r="D287" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E287">
         <v>1.260086513310223</v>
@@ -15905,7 +15911,7 @@
         <v>-0.2566084186298667</v>
       </c>
       <c r="D288" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E288">
         <v>-0.001048450451905936</v>
@@ -15941,7 +15947,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15955,7 +15961,7 @@
         <v>-0.2875710874180024</v>
       </c>
       <c r="D289" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E289">
         <v>-0.001048450451905936</v>
@@ -15991,7 +15997,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16041,7 +16047,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16091,7 +16097,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16105,7 +16111,7 @@
         <v>-0.3429456734762377</v>
       </c>
       <c r="D292" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E292">
         <v>-0.1559309932859021</v>
@@ -16141,7 +16147,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16155,7 +16161,7 @@
         <v>-0.452945673476238</v>
       </c>
       <c r="D293" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E293">
         <v>-0.1559309932859021</v>
@@ -16191,7 +16197,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16205,7 +16211,7 @@
         <v>-0.07614423041516449</v>
       </c>
       <c r="D294" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E294">
         <v>-0.08649962563060054</v>
@@ -16241,7 +16247,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16255,7 +16261,7 @@
         <v>-0.06685502084603723</v>
       </c>
       <c r="D295" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E295">
         <v>-0.08649962563060054</v>
@@ -16291,7 +16297,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16305,7 +16311,7 @@
         <v>-0.6325763258089658</v>
       </c>
       <c r="D296" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E296">
         <v>-0.7397037652284588</v>
@@ -16341,7 +16347,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16355,7 +16361,7 @@
         <v>-0.6888811406779016</v>
       </c>
       <c r="D297" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E297">
         <v>-0.6347573064746772</v>
@@ -16391,7 +16397,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16405,7 +16411,7 @@
         <v>-0.5922830059527424</v>
       </c>
       <c r="D298" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E298">
         <v>-0.6988811406779014</v>
@@ -16441,7 +16447,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16455,7 +16461,7 @@
         <v>-0.7708727781363214</v>
       </c>
       <c r="D299" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E299">
         <v>-0.7160845060282481</v>
@@ -16491,7 +16497,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16505,7 +16511,7 @@
         <v>-0.6732115427634033</v>
       </c>
       <c r="D300" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E300">
         <v>-0.7808727781363212</v>
@@ -16541,7 +16547,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16555,7 +16561,7 @@
         <v>-0.6051723879795468</v>
       </c>
       <c r="D301" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E301">
         <v>-0.5517269067155315</v>
@@ -16591,7 +16597,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16605,7 +16611,7 @@
         <v>-0.509659617957122</v>
       </c>
       <c r="D302" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E302">
         <v>-0.6151723879795465</v>
@@ -16641,7 +16647,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16655,7 +16661,7 @@
         <v>1.374867998585327</v>
       </c>
       <c r="D303" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E303">
         <v>1.61428021608427</v>
@@ -16691,7 +16697,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16705,7 +16711,7 @@
         <v>1.37455579980999</v>
       </c>
       <c r="D304" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E304">
         <v>1.61428021608427</v>
@@ -16741,7 +16747,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16755,7 +16761,7 @@
         <v>1.659046067002767</v>
       </c>
       <c r="D305" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E305">
         <v>1.701663141543517</v>
@@ -16791,7 +16797,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16805,7 +16811,7 @@
         <v>1.400425101402588</v>
       </c>
       <c r="D306" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E306">
         <v>1.63789275673065</v>
@@ -16841,7 +16847,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16855,7 +16861,7 @@
         <v>1.415426421593279</v>
       </c>
       <c r="D307" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E307">
         <v>1.63789275673065</v>
@@ -16891,7 +16897,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16905,7 +16911,7 @@
         <v>1.672891436539961</v>
       </c>
       <c r="D308" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E308">
         <v>1.702888796158578</v>
@@ -16941,7 +16947,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16955,7 +16961,7 @@
         <v>1.682896717302726</v>
       </c>
       <c r="D309" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E309">
         <v>1.702888796158578</v>
@@ -16991,7 +16997,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17005,7 +17011,7 @@
         <v>1.392287936404873</v>
       </c>
       <c r="D310" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E310">
         <v>1.630374723852328</v>
@@ -17041,7 +17047,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17055,7 +17061,7 @@
         <v>1.392192134372636</v>
       </c>
       <c r="D311" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E311">
         <v>1.630374723852328</v>
@@ -17091,7 +17097,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17105,7 +17111,7 @@
         <v>1.665398674360388</v>
       </c>
       <c r="D312" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E312">
         <v>1.367982501138595</v>
@@ -17141,7 +17147,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17155,7 +17161,7 @@
         <v>1.67530287232815</v>
       </c>
       <c r="D313" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E313">
         <v>1.367982501138595</v>
@@ -17191,7 +17197,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17205,7 +17211,7 @@
         <v>1.683187064752997</v>
       </c>
       <c r="D314" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E314">
         <v>1.385560910531628</v>
@@ -17241,7 +17247,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17255,7 +17261,7 @@
         <v>1.693331241005988</v>
       </c>
       <c r="D315" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E315">
         <v>1.385560910531628</v>
@@ -17291,7 +17297,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17305,7 +17311,7 @@
         <v>1.671335210176903</v>
       </c>
       <c r="D316" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E316">
         <v>1.373848959803819</v>
@@ -17341,7 +17347,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17355,7 +17361,7 @@
         <v>1.68131949631757</v>
       </c>
       <c r="D317" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E317">
         <v>1.373848959803819</v>
@@ -17391,7 +17397,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17405,7 +17411,7 @@
         <v>1.693875753393727</v>
       </c>
       <c r="D318" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E318">
         <v>1.396123425781996</v>
@@ -17441,7 +17447,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17455,7 +17461,7 @@
         <v>1.704164127807133</v>
       </c>
       <c r="D319" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E319">
         <v>1.396123425781996</v>
@@ -17491,7 +17497,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17505,7 +17511,7 @@
         <v>1.366123425781996</v>
       </c>
       <c r="D320" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E320">
         <v>1.403731566187024</v>
@@ -17541,7 +17547,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17555,7 +17561,7 @@
         <v>1.710631890779994</v>
       </c>
       <c r="D321" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E321">
         <v>1.412681767280061</v>
@@ -17591,7 +17597,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17605,7 +17611,7 @@
         <v>1.72114631763706</v>
       </c>
       <c r="D322" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E322">
         <v>1.412681767280061</v>
@@ -17641,7 +17647,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17655,7 +17661,7 @@
         <v>1.382681767280062</v>
       </c>
       <c r="D323" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E323">
         <v>1.420374677351461</v>
@@ -17691,7 +17697,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17705,7 +17711,7 @@
         <v>1.679206240881443</v>
       </c>
       <c r="D324" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E324">
         <v>1.381627077835624</v>
@@ -17755,7 +17761,7 @@
         <v>1.689296712933807</v>
       </c>
       <c r="D325" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E325">
         <v>1.381627077835624</v>
@@ -17805,7 +17811,7 @@
         <v>1.351627077835625</v>
       </c>
       <c r="D326" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E326">
         <v>1.364138386842169</v>
@@ -17855,7 +17861,7 @@
         <v>1.662615013806636</v>
       </c>
       <c r="D327" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E327">
         <v>1.365231699984297</v>
@@ -17891,7 +17897,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17905,7 +17911,7 @@
         <v>1.672481658175022</v>
       </c>
       <c r="D328" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E328">
         <v>1.365231699984297</v>
@@ -17941,7 +17947,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17955,7 +17961,7 @@
         <v>1.335231699984297</v>
       </c>
       <c r="D329" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E329">
         <v>1.330198361076394</v>
@@ -17991,7 +17997,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18005,7 +18011,7 @@
         <v>1.638483426036899</v>
       </c>
       <c r="D330" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E330">
         <v>1.341384970754843</v>
@@ -18055,7 +18061,7 @@
         <v>1.648024517787818</v>
       </c>
       <c r="D331" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E331">
         <v>1.341384970754843</v>
@@ -18155,7 +18161,7 @@
         <v>1.611118158429232</v>
       </c>
       <c r="D333" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E333">
         <v>1.31434273328757</v>
@@ -18205,7 +18211,7 @@
         <v>1.620290072876844</v>
       </c>
       <c r="D334" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E334">
         <v>1.31434273328757</v>
@@ -18255,7 +18261,7 @@
         <v>1.210704115653037</v>
       </c>
       <c r="D335" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E335">
         <v>1.321946243981619</v>
@@ -18305,7 +18311,7 @@
         <v>1.250704115653037</v>
       </c>
       <c r="D336" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E336">
         <v>1.321946243981619</v>
@@ -18355,7 +18361,7 @@
         <v>1.580824889600507</v>
       </c>
       <c r="D337" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E337">
         <v>1.284407057851428</v>
@@ -18391,7 +18397,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18405,7 +18411,7 @@
         <v>1.589588125885168</v>
       </c>
       <c r="D338" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E338">
         <v>1.284407057851428</v>
@@ -18441,7 +18447,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18455,7 +18461,7 @@
         <v>1.180206507742837</v>
       </c>
       <c r="D339" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E339">
         <v>1.27675246238701</v>
@@ -18491,7 +18497,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18505,7 +18511,7 @@
         <v>1.220206507742837</v>
       </c>
       <c r="D340" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E340">
         <v>1.27675246238701</v>
@@ -18541,7 +18547,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18555,7 +18561,7 @@
         <v>1.680056540073359</v>
       </c>
       <c r="D341" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E341">
         <v>1.409353064352823</v>
@@ -18591,7 +18597,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18605,7 +18611,7 @@
         <v>1.717732409003494</v>
       </c>
       <c r="D342" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E342">
         <v>1.409353064352823</v>
@@ -18641,7 +18647,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18655,7 +18661,7 @@
         <v>1.307497917096648</v>
       </c>
       <c r="D343" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E343">
         <v>1.444235818399402</v>
@@ -18691,7 +18697,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18705,7 +18711,7 @@
         <v>1.347497917096648</v>
       </c>
       <c r="D344" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E344">
         <v>1.444235818399402</v>
@@ -18741,7 +18747,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18755,7 +18761,7 @@
         <v>1.842256392262994</v>
       </c>
       <c r="D345" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E345">
         <v>1.530769127897027</v>
@@ -18805,7 +18811,7 @@
         <v>1.431193121765403</v>
       </c>
       <c r="D346" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E346">
         <v>1.572471675023835</v>
@@ -18855,7 +18861,7 @@
         <v>1.471193121765403</v>
       </c>
       <c r="D347" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E347">
         <v>1.572471675023835</v>
@@ -18905,7 +18911,7 @@
         <v>2.306011000659936</v>
       </c>
       <c r="D348" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E348">
         <v>2.348379970519409</v>
@@ -18941,7 +18947,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18955,7 +18961,7 @@
         <v>2.400485390479259</v>
       </c>
       <c r="D349" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E349">
         <v>2.364696230398958</v>
@@ -18991,7 +18997,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19041,7 +19047,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19055,7 +19061,7 @@
         <v>2.315116384839492</v>
       </c>
       <c r="D351" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E351">
         <v>2.323814331699535</v>
@@ -19091,7 +19097,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19105,7 +19111,7 @@
         <v>2.158186337006185</v>
       </c>
       <c r="D352" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E352">
         <v>2.199105803820263</v>
@@ -19141,7 +19147,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19191,7 +19197,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19241,7 +19247,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19255,7 +19261,7 @@
         <v>2.249949180664442</v>
       </c>
       <c r="D355" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E355">
         <v>2.193589002935801</v>
@@ -19291,7 +19297,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19305,7 +19311,7 @@
         <v>3.29910210514231</v>
       </c>
       <c r="D356" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E356">
         <v>3.35230135785332</v>
@@ -19341,7 +19347,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19355,7 +19361,7 @@
         <v>3.804045197377832</v>
       </c>
       <c r="D357" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E357">
         <v>3.415154291605215</v>
@@ -19391,7 +19397,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19405,7 +19411,7 @@
         <v>3.427249571448392</v>
       </c>
       <c r="D358" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E358">
         <v>3.291626526785035</v>
@@ -19441,7 +19447,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19491,7 +19497,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19505,7 +19511,7 @@
         <v>3.442581197445604</v>
       </c>
       <c r="D360" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E360">
         <v>3.306414237004073</v>
@@ -19541,7 +19547,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19555,7 +19561,7 @@
         <v>3.36022431872702</v>
       </c>
       <c r="D361" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E361">
         <v>3.226979110080385</v>
@@ -19591,7 +19597,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19605,7 +19611,7 @@
         <v>3.251003700388559</v>
       </c>
       <c r="D362" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E362">
         <v>3.121633280862579</v>
@@ -19641,7 +19647,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19655,7 +19661,7 @@
         <v>2.99001278638902</v>
       </c>
       <c r="D363" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E363">
         <v>3.032275977245447</v>
@@ -19741,7 +19747,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19755,7 +19761,7 @@
         <v>2.786342722576059</v>
       </c>
       <c r="D365" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E365">
         <v>2.830017022419643</v>
@@ -19791,7 +19797,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19805,7 +19811,7 @@
         <v>2.881784622628198</v>
       </c>
       <c r="D366" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E366">
         <v>2.846342722576059</v>
@@ -19841,7 +19847,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19855,7 +19861,7 @@
         <v>2.713139299753176</v>
       </c>
       <c r="D367" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E367">
         <v>2.672915915531583</v>
@@ -19891,7 +19897,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19905,7 +19911,7 @@
         <v>2.722022378645214</v>
       </c>
       <c r="D368" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E368">
         <v>2.672915915531583</v>
@@ -19941,7 +19947,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19955,7 +19961,7 @@
         <v>2.643362683974768</v>
       </c>
       <c r="D369" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E369">
         <v>2.68802760764238</v>
@@ -19991,7 +19997,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20005,7 +20011,7 @@
         <v>2.738474376085565</v>
       </c>
       <c r="D370" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E370">
         <v>2.678250991863972</v>
@@ -20041,7 +20047,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20055,7 +20061,7 @@
         <v>2.26156876679942</v>
       </c>
       <c r="D371" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E371">
         <v>2.319500204055783</v>
@@ -20091,7 +20097,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20105,7 +20111,7 @@
         <v>2.341086491507057</v>
       </c>
       <c r="D372" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E372">
         <v>2.284741341701965</v>
@@ -20141,7 +20147,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20155,7 +20161,7 @@
         <v>2.25156876679942</v>
       </c>
       <c r="D373" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E373">
         <v>2.298948197976329</v>
@@ -20191,7 +20197,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20205,7 +20211,7 @@
         <v>2.345775623073784</v>
       </c>
       <c r="D374" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E374">
         <v>2.287361910525056</v>
@@ -20241,7 +20247,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20255,7 +20261,7 @@
         <v>1.450725995788351</v>
       </c>
       <c r="D375" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E375">
         <v>1.543612412630503</v>
@@ -20291,7 +20297,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20305,7 +20311,7 @@
         <v>1.378039753255653</v>
       </c>
       <c r="D376" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E376">
         <v>1.473954763536668</v>
@@ -20341,7 +20347,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20355,7 +20361,7 @@
         <v>2.300473418774809</v>
       </c>
       <c r="D377" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E377">
         <v>2.269274816103397</v>
@@ -20405,7 +20411,7 @@
         <v>2.307737312105645</v>
       </c>
       <c r="D378" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E378">
         <v>2.269274816103397</v>
@@ -20455,7 +20461,7 @@
         <v>2.548688372146674</v>
       </c>
       <c r="D379" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E379">
         <v>2.44021981851742</v>
@@ -20491,7 +20497,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20505,7 +20511,7 @@
         <v>4.064626779899114</v>
       </c>
       <c r="D380" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E380">
         <v>3.971827788774664</v>
@@ -20541,7 +20547,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20555,7 +20561,7 @@
         <v>2.704221825320051</v>
       </c>
       <c r="D381" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E381">
         <v>2.757514946748523</v>
@@ -20591,7 +20597,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20605,7 +20611,7 @@
         <v>2.699698304540886</v>
       </c>
       <c r="D382" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E382">
         <v>2.757514946748523</v>
@@ -20641,7 +20647,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20655,7 +20661,7 @@
         <v>2.597723564836138</v>
       </c>
       <c r="D383" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E383">
         <v>2.648687698460786</v>
@@ -20691,7 +20697,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20705,7 +20711,7 @@
         <v>2.594470401040876</v>
       </c>
       <c r="D384" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E384">
         <v>2.648687698460786</v>
@@ -20741,7 +20747,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20755,7 +20761,7 @@
         <v>2.5327482758737</v>
       </c>
       <c r="D385" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E385">
         <v>2.582291478725809</v>
@@ -20791,7 +20797,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20805,7 +20811,7 @@
         <v>2.530270165227095</v>
       </c>
       <c r="D386" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E386">
         <v>2.582291478725809</v>
@@ -20841,7 +20847,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20855,7 +20861,7 @@
         <v>2.615226386520305</v>
       </c>
       <c r="D387" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E387">
         <v>2.605226386520305</v>
@@ -20891,7 +20897,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20905,7 +20911,7 @@
         <v>2.519210324106</v>
       </c>
       <c r="D388" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E388">
         <v>2.474919909368535</v>
@@ -20941,7 +20947,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20955,7 +20961,7 @@
         <v>2.443973795685154</v>
       </c>
       <c r="D389" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E389">
         <v>2.491575608314453</v>
@@ -20991,7 +20997,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21005,7 +21011,7 @@
         <v>2.442554625160083</v>
       </c>
       <c r="D390" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E390">
         <v>2.491575608314453</v>
@@ -21041,7 +21047,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21091,7 +21097,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21105,7 +21111,7 @@
         <v>2.457705873063223</v>
       </c>
       <c r="D392" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E392">
         <v>2.413049360402885</v>
@@ -21141,7 +21147,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21155,7 +21161,7 @@
         <v>2.382591377283335</v>
       </c>
       <c r="D393" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E393">
         <v>2.428850830862097</v>
@@ -21191,7 +21197,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21205,7 +21211,7 @@
         <v>2.381904402604011</v>
       </c>
       <c r="D394" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E394">
         <v>2.428850830862097</v>
@@ -21241,7 +21247,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21255,7 +21261,7 @@
         <v>2.46327835196266</v>
       </c>
       <c r="D395" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E395">
         <v>2.453507343522435</v>
@@ -21291,7 +21297,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21305,7 +21311,7 @@
         <v>2.467705873063223</v>
       </c>
       <c r="D396" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E396">
         <v>2.453507343522435</v>
@@ -21341,7 +21347,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21355,7 +21361,7 @@
         <v>2.447999298642713</v>
       </c>
       <c r="D397" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E397">
         <v>2.403285008753682</v>
@@ -21391,7 +21397,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21405,7 +21411,7 @@
         <v>2.372904061939057</v>
       </c>
       <c r="D398" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E398">
         <v>2.418951665679276</v>
@@ -21441,7 +21447,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21455,7 +21461,7 @@
         <v>2.37233264171712</v>
       </c>
       <c r="D399" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E399">
         <v>2.418951665679276</v>
@@ -21491,7 +21497,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21541,7 +21547,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21591,7 +21597,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21605,7 +21611,7 @@
         <v>2.414261420787727</v>
       </c>
       <c r="D402" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E402">
         <v>2.369346310197177</v>
@@ -21641,7 +21647,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21691,7 +21697,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21741,7 +21747,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21755,7 +21761,7 @@
         <v>2.424261420787727</v>
       </c>
       <c r="D405" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E405">
         <v>2.394544385485897</v>
@@ -21791,7 +21797,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21805,7 +21811,7 @@
         <v>2.414374606666995</v>
       </c>
       <c r="D406" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E406">
         <v>2.394544385485897</v>
@@ -21841,7 +21847,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21855,7 +21861,7 @@
         <v>2.397600622679596</v>
       </c>
       <c r="D407" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E407">
         <v>2.352586340671736</v>
@@ -21891,7 +21897,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21905,7 +21911,7 @@
         <v>2.322605383348882</v>
       </c>
       <c r="D408" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E408">
         <v>2.367553015986731</v>
@@ -21941,7 +21947,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21955,7 +21961,7 @@
         <v>2.322633947364601</v>
       </c>
       <c r="D409" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E409">
         <v>2.367553015986731</v>
@@ -21991,7 +21997,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22005,7 +22011,7 @@
         <v>2.402576819333163</v>
       </c>
       <c r="D410" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E410">
         <v>2.35256729799459</v>
@@ -22041,7 +22047,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22055,7 +22061,7 @@
         <v>2.407600622679595</v>
       </c>
       <c r="D411" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E411">
         <v>2.35256729799459</v>
@@ -22091,7 +22097,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22105,7 +22111,7 @@
         <v>2.39758158000245</v>
       </c>
       <c r="D412" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E412">
         <v>2.35256729799459</v>
@@ -22141,7 +22147,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22155,7 +22161,7 @@
         <v>2.378737718650321</v>
       </c>
       <c r="D413" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E413">
         <v>2.33361115745181</v>
@@ -22191,7 +22197,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22205,7 +22211,7 @@
         <v>2.30377990571649</v>
       </c>
       <c r="D414" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E414">
         <v>2.348315847988621</v>
@@ -22241,7 +22247,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22255,7 +22261,7 @@
         <v>2.304033028113511</v>
       </c>
       <c r="D415" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E415">
         <v>2.348315847988621</v>
@@ -22291,7 +22297,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22305,7 +22311,7 @@
         <v>2.383526783319471</v>
       </c>
       <c r="D416" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E416">
         <v>2.333442409187131</v>
@@ -22341,7 +22347,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22355,7 +22361,7 @@
         <v>2.38873771865032</v>
       </c>
       <c r="D417" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E417">
         <v>2.333442409187131</v>
@@ -22391,7 +22397,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22405,7 +22411,7 @@
         <v>2.378568970385641</v>
       </c>
       <c r="D418" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E418">
         <v>2.333442409187131</v>
@@ -22441,7 +22447,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22455,7 +22461,7 @@
         <v>2.29477967980894</v>
       </c>
       <c r="D419" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E419">
         <v>2.33911879805526</v>
@@ -22505,7 +22511,7 @@
         <v>2.295140160765494</v>
       </c>
       <c r="D420" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E420">
         <v>2.33911879805526</v>
@@ -22555,7 +22561,7 @@
         <v>2.374419198852388</v>
       </c>
       <c r="D421" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E421">
         <v>2.324299038533536</v>
@@ -22605,7 +22611,7 @@
         <v>2.379719599649515</v>
       </c>
       <c r="D422" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E422">
         <v>2.324299038533536</v>
@@ -22655,7 +22661,7 @@
         <v>2.369479279011813</v>
       </c>
       <c r="D423" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E423">
         <v>2.324299038533536</v>
@@ -22705,7 +22711,7 @@
         <v>2.280590400920047</v>
       </c>
       <c r="D424" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E424">
         <v>2.324619216844741</v>
@@ -22741,7 +22747,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22755,7 +22761,7 @@
         <v>2.281120137688396</v>
       </c>
       <c r="D425" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E425">
         <v>2.324619216844741</v>
@@ -22791,7 +22797,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22805,7 +22811,7 @@
         <v>2.360060664151698</v>
       </c>
       <c r="D426" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E426">
         <v>2.309884085228915</v>
@@ -22841,7 +22847,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22891,7 +22897,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22905,7 +22911,7 @@
         <v>2.281700069738552</v>
       </c>
       <c r="D428" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E428">
         <v>2.325753152774585</v>
@@ -22941,7 +22947,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -22955,7 +22961,7 @@
         <v>2.282216569900716</v>
       </c>
       <c r="D429" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E429">
         <v>2.325753152774585</v>
@@ -22991,7 +22997,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23005,7 +23011,7 @@
         <v>2.361183569576388</v>
       </c>
       <c r="D430" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E430">
         <v>2.311011402855666</v>
@@ -23041,7 +23047,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23055,7 +23061,7 @@
         <v>2.255753152774584</v>
       </c>
       <c r="D431" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E431">
         <v>2.30032273597278</v>
@@ -23091,7 +23097,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23105,7 +23111,7 @@
         <v>2.248769782041177</v>
       </c>
       <c r="D432" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E432">
         <v>2.297801715354081</v>
@@ -23141,7 +23147,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23155,7 +23161,7 @@
         <v>2.343406757033516</v>
       </c>
       <c r="D433" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E433">
         <v>2.293164740361742</v>
@@ -23191,7 +23197,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23205,7 +23211,7 @@
         <v>2.237801715354081</v>
       </c>
       <c r="D434" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E434">
         <v>2.26243869034642</v>
@@ -23241,7 +23247,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23255,7 +23261,7 @@
         <v>2.228095614122554</v>
       </c>
       <c r="D435" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E435">
         <v>2.276800683120539</v>
@@ -23291,7 +23297,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23305,7 +23311,7 @@
         <v>2.322610014996799</v>
       </c>
       <c r="D436" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E436">
         <v>2.263257480497806</v>
@@ -23341,7 +23347,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23391,7 +23397,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23405,7 +23411,7 @@
         <v>2.224983216186275</v>
       </c>
       <c r="D438" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E438">
         <v>2.273639077311749</v>
@@ -23455,7 +23461,7 @@
         <v>2.319479164108328</v>
       </c>
       <c r="D439" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E439">
         <v>2.26015123354559</v>
@@ -23605,7 +23611,7 @@
         <v>2.3116287572162</v>
       </c>
       <c r="D442" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E442">
         <v>2.252362519438469</v>
@@ -23641,7 +23647,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23691,7 +23697,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23741,7 +23747,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23805,7 +23811,7 @@
         <v>2.185149484739352</v>
       </c>
       <c r="D446" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E446">
         <v>2.165149484739352</v>
@@ -23905,7 +23911,7 @@
         <v>2.20020073233055</v>
       </c>
       <c r="D448" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E448">
         <v>2.205687152603988</v>
@@ -23991,7 +23997,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24041,7 +24047,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24091,7 +24097,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24141,7 +24147,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24191,7 +24197,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24305,7 +24311,7 @@
         <v>2.142114930387524</v>
       </c>
       <c r="D456" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E456">
         <v>2.162114930387524</v>
@@ -24341,7 +24347,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24355,7 +24361,7 @@
         <v>2.115413806995409</v>
       </c>
       <c r="D457" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E457">
         <v>2.141244762127619</v>
@@ -24441,7 +24447,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24455,7 +24461,7 @@
         <v>2.073994682974101</v>
       </c>
       <c r="D459" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E459">
         <v>2.082201671198685</v>
@@ -24505,7 +24511,7 @@
         <v>2.083994682974101</v>
       </c>
       <c r="D460" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E460">
         <v>2.082201671198685</v>
@@ -24591,7 +24597,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24605,7 +24611,7 @@
         <v>2.057461365020192</v>
       </c>
       <c r="D462" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E462">
         <v>2.066125824243982</v>
@@ -24641,7 +24647,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24691,7 +24697,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24741,7 +24747,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24791,7 +24797,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24841,7 +24847,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24855,7 +24861,7 @@
         <v>2.057577737614682</v>
       </c>
       <c r="D467" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E467">
         <v>2.099815205781953</v>
@@ -24891,7 +24897,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24955,7 +24961,7 @@
         <v>2.075267052489131</v>
       </c>
       <c r="D469" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E469">
         <v>2.105974841560053</v>
@@ -25005,7 +25011,7 @@
         <v>2.0673904197019</v>
       </c>
       <c r="D470" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E470">
         <v>2.109513786914668</v>
@@ -25055,7 +25061,7 @@
         <v>2.101281730695467</v>
       </c>
       <c r="D471" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E471">
         <v>2.131889846669813</v>
@@ -25105,7 +25111,7 @@
         <v>2.093106078618507</v>
       </c>
       <c r="D472" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E472">
         <v>2.134930426541548</v>
@@ -25155,7 +25161,7 @@
         <v>2.114232378900782</v>
       </c>
       <c r="D473" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E473">
         <v>2.144790875533345</v>
@@ -25191,7 +25197,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25205,7 +25211,7 @@
         <v>2.164790875533345</v>
       </c>
       <c r="D474" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E474">
         <v>2.134232378900781</v>
@@ -25241,7 +25247,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25255,7 +25261,7 @@
         <v>2.105907868798473</v>
       </c>
       <c r="D475" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E475">
         <v>2.147583358696166</v>
@@ -25291,7 +25297,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25305,7 +25311,7 @@
         <v>2.178667208693582</v>
       </c>
       <c r="D476" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E476">
         <v>2.148162082573172</v>
@@ -25341,7 +25347,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25355,7 +25361,7 @@
         <v>2.119677460934401</v>
       </c>
       <c r="D477" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E477">
         <v>2.161192839295628</v>
@@ -25391,7 +25397,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25405,7 +25411,7 @@
         <v>2.191253934723685</v>
       </c>
       <c r="D478" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E478">
         <v>2.160797219088007</v>
@@ -25455,7 +25461,7 @@
         <v>2.132167365995042</v>
       </c>
       <c r="D479" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E479">
         <v>2.173537512902076</v>
@@ -25555,7 +25561,7 @@
         <v>2.161339958759847</v>
       </c>
       <c r="D481" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E481">
         <v>2.202370889471942</v>
@@ -25605,7 +25611,7 @@
         <v>2.215480849833102</v>
       </c>
       <c r="D482" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E482">
         <v>2.179965384477054</v>
@@ -25655,7 +25661,7 @@
         <v>1.276065947508897</v>
       </c>
       <c r="D483" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E483">
         <v>1.317566169928825</v>
@@ -25691,7 +25697,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25705,7 +25711,7 @@
         <v>1.37689891014235</v>
       </c>
       <c r="D484" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E484">
         <v>1.288399132562277</v>
@@ -25741,7 +25747,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25755,7 +25761,7 @@
         <v>1.265250934212467</v>
       </c>
       <c r="D485" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E485">
         <v>1.306889515011455</v>
@@ -25791,7 +25797,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25805,7 +25811,7 @@
         <v>1.365853299547489</v>
       </c>
       <c r="D486" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E486">
         <v>1.277491880346475</v>
@@ -25841,7 +25847,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25855,7 +25861,7 @@
         <v>1.365250934212467</v>
       </c>
       <c r="D487" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E487">
         <v>1.29891353608099</v>
@@ -25891,7 +25897,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25905,7 +25911,7 @@
         <v>1.335853299547488</v>
       </c>
       <c r="D488" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E488">
         <v>1.29891353608099</v>
@@ -25941,7 +25947,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25955,7 +25961,7 @@
         <v>1.257848770795328</v>
       </c>
       <c r="D489" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E489">
         <v>1.29958204878089</v>
@@ -25991,7 +25997,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26005,7 +26011,7 @@
         <v>1.358293307486061</v>
       </c>
       <c r="D490" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E490">
         <v>1.270026585471621</v>
@@ -26041,7 +26047,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26055,7 +26061,7 @@
         <v>1.328293307486061</v>
       </c>
       <c r="D491" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E491">
         <v>1.291337761155134</v>
@@ -26091,7 +26097,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26105,7 +26111,7 @@
         <v>1.336383675279734</v>
       </c>
       <c r="D492" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E492">
         <v>1.248391395422367</v>
@@ -26155,7 +26161,7 @@
         <v>1.306383675279734</v>
       </c>
       <c r="D493" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E493">
         <v>1.269382388589295</v>
@@ -26205,10 +26211,10 @@
         <v>1.1949083591831</v>
       </c>
       <c r="D494" t="s">
-        <v>147</v>
+        <v>273</v>
       </c>
       <c r="E494">
-        <v>1.279467032224208</v>
+        <v>1.223388801502731</v>
       </c>
       <c r="F494">
         <v>1</v>
@@ -26217,10 +26223,10 @@
         <v>0.0078450916408169</v>
       </c>
       <c r="H494">
-        <v>0.008100532967775794</v>
+        <v>0.007816611198497268</v>
       </c>
       <c r="I494">
-        <v>0.08455867304110809</v>
+        <v>0.02848044231963076</v>
       </c>
       <c r="J494">
         <v>0.7120110579907708</v>
@@ -26232,16 +26238,216 @@
         <v>4.52</v>
       </c>
       <c r="M494">
+        <v>4.63</v>
+      </c>
+      <c r="N494">
+        <v>4.52</v>
+      </c>
+      <c r="O494">
+        <v>1</v>
+      </c>
+      <c r="P494" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="495" spans="1:16">
+      <c r="A495" s="1">
+        <v>1</v>
+      </c>
+      <c r="B495" t="s">
+        <v>147</v>
+      </c>
+      <c r="C495">
+        <v>1.279467032224208</v>
+      </c>
+      <c r="D495" t="s">
+        <v>274</v>
+      </c>
+      <c r="E495">
+        <v>1.192187695703653</v>
+      </c>
+      <c r="F495">
+        <v>-1</v>
+      </c>
+      <c r="G495">
+        <v>0.008100532967775794</v>
+      </c>
+      <c r="H495">
+        <v>0.007927812304296346</v>
+      </c>
+      <c r="I495">
+        <v>0.08727933652055464</v>
+      </c>
+      <c r="J495">
+        <v>0.7120110579907708</v>
+      </c>
+      <c r="K495">
         <v>4.79</v>
       </c>
-      <c r="N494">
+      <c r="L495">
         <v>4.69</v>
       </c>
-      <c r="O494">
-        <v>1</v>
-      </c>
-      <c r="P494" t="s">
-        <v>390</v>
+      <c r="M495">
+        <v>4.73</v>
+      </c>
+      <c r="N495">
+        <v>4.56</v>
+      </c>
+      <c r="O495">
+        <v>1</v>
+      </c>
+      <c r="P495" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="496" spans="1:16">
+      <c r="A496" s="1">
+        <v>2</v>
+      </c>
+      <c r="B496" t="s">
+        <v>149</v>
+      </c>
+      <c r="C496">
+        <v>1.249467032224208</v>
+      </c>
+      <c r="D496" t="s">
+        <v>275</v>
+      </c>
+      <c r="E496">
+        <v>1.2123469216443</v>
+      </c>
+      <c r="F496">
+        <v>-1</v>
+      </c>
+      <c r="G496">
+        <v>0.008070532967775792</v>
+      </c>
+      <c r="H496">
+        <v>0.008047653078355699</v>
+      </c>
+      <c r="I496">
+        <v>0.03712011057990772</v>
+      </c>
+      <c r="J496">
+        <v>0.7120110579907708</v>
+      </c>
+      <c r="K496">
+        <v>4.79</v>
+      </c>
+      <c r="L496">
+        <v>4.66</v>
+      </c>
+      <c r="M496">
+        <v>4.8</v>
+      </c>
+      <c r="N496">
+        <v>4.63</v>
+      </c>
+      <c r="O496">
+        <v>1</v>
+      </c>
+      <c r="P496" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="497" spans="1:16">
+      <c r="A497" s="1">
+        <v>0</v>
+      </c>
+      <c r="B497" t="s">
+        <v>149</v>
+      </c>
+      <c r="C497">
+        <v>1.061287302238483</v>
+      </c>
+      <c r="D497" t="s">
+        <v>275</v>
+      </c>
+      <c r="E497">
+        <v>1.023774332097018</v>
+      </c>
+      <c r="F497">
+        <v>-1</v>
+      </c>
+      <c r="G497">
+        <v>0.008258712697761517</v>
+      </c>
+      <c r="H497">
+        <v>0.008236225667902983</v>
+      </c>
+      <c r="I497">
+        <v>0.03751297014146449</v>
+      </c>
+      <c r="J497">
+        <v>0.7512970141464546</v>
+      </c>
+      <c r="K497">
+        <v>4.79</v>
+      </c>
+      <c r="L497">
+        <v>4.66</v>
+      </c>
+      <c r="M497">
+        <v>4.8</v>
+      </c>
+      <c r="N497">
+        <v>4.63</v>
+      </c>
+      <c r="O497">
+        <v>1</v>
+      </c>
+      <c r="P497" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="498" spans="1:16">
+      <c r="A498" s="1">
+        <v>0</v>
+      </c>
+      <c r="B498" t="s">
+        <v>151</v>
+      </c>
+      <c r="C498">
+        <v>1.049221706841676</v>
+      </c>
+      <c r="D498" t="s">
+        <v>276</v>
+      </c>
+      <c r="E498">
+        <v>1.016747983025339</v>
+      </c>
+      <c r="F498">
+        <v>-1</v>
+      </c>
+      <c r="G498">
+        <v>0.008270778293158325</v>
+      </c>
+      <c r="H498">
+        <v>0.008283252016974661</v>
+      </c>
+      <c r="I498">
+        <v>0.03247372381633751</v>
+      </c>
+      <c r="J498">
+        <v>0.7491241272112704</v>
+      </c>
+      <c r="K498">
+        <v>4.82</v>
+      </c>
+      <c r="L498">
+        <v>4.66</v>
+      </c>
+      <c r="M498">
+        <v>4.85</v>
+      </c>
+      <c r="N498">
+        <v>4.65</v>
+      </c>
+      <c r="O498">
+        <v>1</v>
+      </c>
+      <c r="P498" t="s">
+        <v>275</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-03328-601328.xlsx
+++ b/s60_signal/position-03328-601328.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1527" uniqueCount="397">
   <si>
     <t>trade_time</t>
   </si>
@@ -469,6 +469,9 @@
     <t>2021-10-27</t>
   </si>
   <si>
+    <t>2021-11-16</t>
+  </si>
+  <si>
     <t>2021-11-15</t>
   </si>
   <si>
@@ -844,7 +847,7 @@
     <t>2021-11-12</t>
   </si>
   <si>
-    <t>2021-11-16</t>
+    <t>2021-11-17</t>
   </si>
   <si>
     <t>2016-05-24</t>
@@ -1193,6 +1196,15 @@
   </si>
   <si>
     <t>2021-10-26</t>
+  </si>
+  <si>
+    <t>2021-10-28</t>
+  </si>
+  <si>
+    <t>2021-11-03</t>
+  </si>
+  <si>
+    <t>2021-11-04</t>
   </si>
 </sst>
 </file>
@@ -1550,7 +1562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P498"/>
+  <dimension ref="A1:P505"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1611,7 +1623,7 @@
         <v>2.636521639996683</v>
       </c>
       <c r="D2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E2">
         <v>2.833647241107702</v>
@@ -1647,7 +1659,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1661,7 +1673,7 @@
         <v>2.808801457176021</v>
       </c>
       <c r="D3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E3">
         <v>2.7135041663212</v>
@@ -1697,7 +1709,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1711,7 +1723,7 @@
         <v>2.746397091058633</v>
       </c>
       <c r="D4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E4">
         <v>2.648930323263125</v>
@@ -1761,7 +1773,7 @@
         <v>2.683209227271539</v>
       </c>
       <c r="D5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E5">
         <v>2.583545744375049</v>
@@ -1797,7 +1809,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1811,7 +1823,7 @@
         <v>2.555958070922727</v>
       </c>
       <c r="D6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E6">
         <v>2.632522016358742</v>
@@ -1847,7 +1859,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1861,7 +1873,7 @@
         <v>2.641252819939413</v>
       </c>
       <c r="D7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E7">
         <v>2.540130729835057</v>
@@ -1897,7 +1909,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1911,7 +1923,7 @@
         <v>2.512285655110759</v>
       </c>
       <c r="D8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E8">
         <v>2.590994611146576</v>
@@ -1947,7 +1959,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1961,7 +1973,7 @@
         <v>2.615441102246784</v>
       </c>
       <c r="D9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E9">
         <v>2.513421672263544</v>
@@ -1997,7 +2009,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2011,7 +2023,7 @@
         <v>2.515418243442972</v>
       </c>
       <c r="D10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E10">
         <v>2.545423958143926</v>
@@ -2047,7 +2059,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2061,7 +2073,7 @@
         <v>2.487273994427867</v>
       </c>
       <c r="D11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E11">
         <v>2.567211421027677</v>
@@ -2097,7 +2109,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2111,7 +2123,7 @@
         <v>2.487984580081365</v>
       </c>
       <c r="D12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E12">
         <v>2.579898802553291</v>
@@ -2147,7 +2159,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2161,7 +2173,7 @@
         <v>2.500805561667341</v>
       </c>
       <c r="D13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E13">
         <v>2.59216563562278</v>
@@ -2197,7 +2209,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2211,7 +2223,7 @@
         <v>2.499441989042522</v>
       </c>
       <c r="D14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E14">
         <v>2.736702547602069</v>
@@ -2261,7 +2273,7 @@
         <v>2.512520850741042</v>
       </c>
       <c r="D15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E15">
         <v>2.749061943431123</v>
@@ -2297,7 +2309,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2311,7 +2323,7 @@
         <v>2.77984350091858</v>
       </c>
       <c r="D16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E16">
         <v>2.889061943431122</v>
@@ -2347,7 +2359,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2361,7 +2373,7 @@
         <v>2.517224153471577</v>
       </c>
       <c r="D17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E17">
         <v>2.753506518310076</v>
@@ -2397,7 +2409,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2411,7 +2423,7 @@
         <v>2.784426680003737</v>
       </c>
       <c r="D18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E18">
         <v>2.924119959439183</v>
@@ -2447,7 +2459,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2461,7 +2473,7 @@
         <v>2.884280694854824</v>
       </c>
       <c r="D19" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E19">
         <v>2.961861794886389</v>
@@ -2511,7 +2523,7 @@
         <v>2.920719956495094</v>
       </c>
       <c r="D20" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E20">
         <v>2.907075620138133</v>
@@ -2547,7 +2559,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2561,7 +2573,7 @@
         <v>2.648180125005333</v>
       </c>
       <c r="D21" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E21">
         <v>2.848908919700521</v>
@@ -2597,7 +2609,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2647,7 +2659,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2661,7 +2673,7 @@
         <v>2.691620213913162</v>
       </c>
       <c r="D23" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E23">
         <v>2.889959376998489</v>
@@ -2697,7 +2709,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2711,7 +2723,7 @@
         <v>2.984719616116966</v>
       </c>
       <c r="D24" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E24">
         <v>2.755965243802971</v>
@@ -2747,7 +2759,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2761,7 +2773,7 @@
         <v>3.007275184023352</v>
       </c>
       <c r="D25" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E25">
         <v>2.755965243802971</v>
@@ -2797,7 +2809,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2811,7 +2823,7 @@
         <v>2.683495528297218</v>
       </c>
       <c r="D26" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E26">
         <v>2.882281628901694</v>
@@ -2847,7 +2859,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2861,7 +2873,7 @@
         <v>2.976914171586129</v>
       </c>
       <c r="D27" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E27">
         <v>2.747824596132772</v>
@@ -2897,7 +2909,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2911,7 +2923,7 @@
         <v>2.647048085674867</v>
       </c>
       <c r="D28" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E28">
         <v>2.84783915365346</v>
@@ -2947,7 +2959,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2961,7 +2973,7 @@
         <v>2.941898848516719</v>
       </c>
       <c r="D29" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E29">
         <v>2.711305547532774</v>
@@ -2997,7 +3009,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3011,7 +3023,7 @@
         <v>2.962790623816959</v>
       </c>
       <c r="D30" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E30">
         <v>2.711305547532774</v>
@@ -3047,7 +3059,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3061,7 +3073,7 @@
         <v>2.636850318680218</v>
       </c>
       <c r="D31" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E31">
         <v>2.674077933106496</v>
@@ -3097,7 +3109,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3111,7 +3123,7 @@
         <v>2.64386308474694</v>
       </c>
       <c r="D32" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E32">
         <v>2.844829359063415</v>
@@ -3147,7 +3159,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3161,7 +3173,7 @@
         <v>2.938838994972993</v>
       </c>
       <c r="D33" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E33">
         <v>2.708114289235636</v>
@@ -3197,7 +3209,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3211,7 +3223,7 @@
         <v>2.959611880258242</v>
       </c>
       <c r="D34" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E34">
         <v>2.708114289235636</v>
@@ -3247,7 +3259,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3261,7 +3273,7 @@
         <v>2.63362151616782</v>
       </c>
       <c r="D35" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E35">
         <v>2.706375129633912</v>
@@ -3297,7 +3309,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3311,7 +3323,7 @@
         <v>2.623711665472045</v>
       </c>
       <c r="D36" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E36">
         <v>2.825786465799713</v>
@@ -3347,7 +3359,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3361,7 +3373,7 @@
         <v>2.919479379991807</v>
       </c>
       <c r="D37" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E37">
         <v>2.687923279746057</v>
@@ -3397,7 +3409,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3411,7 +3423,7 @@
         <v>2.939500051198033</v>
       </c>
       <c r="D38" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E38">
         <v>2.687923279746057</v>
@@ -3447,7 +3459,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3461,7 +3473,7 @@
         <v>2.613192965390128</v>
       </c>
       <c r="D39" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E39">
         <v>2.65740457966414</v>
@@ -3497,7 +3509,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3511,7 +3523,7 @@
         <v>2.866121269202039</v>
       </c>
       <c r="D40" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E40">
         <v>2.632273716345684</v>
@@ -3561,7 +3573,7 @@
         <v>2.884068721379623</v>
       </c>
       <c r="D41" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E41">
         <v>2.632273716345684</v>
@@ -3611,7 +3623,7 @@
         <v>2.556888701243869</v>
       </c>
       <c r="D42" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E42">
         <v>2.5709911987269</v>
@@ -3661,7 +3673,7 @@
         <v>2.84066903268222</v>
       </c>
       <c r="D43" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E43">
         <v>2.605728438993726</v>
@@ -3697,7 +3709,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3711,7 +3723,7 @@
         <v>2.857627543154535</v>
       </c>
       <c r="D44" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E44">
         <v>2.605728438993726</v>
@@ -3747,7 +3759,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3761,7 +3773,7 @@
         <v>2.530031126511299</v>
       </c>
       <c r="D45" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E45">
         <v>2.536232918189681</v>
@@ -3797,7 +3809,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3811,7 +3823,7 @@
         <v>2.794653597980052</v>
       </c>
       <c r="D46" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E46">
         <v>2.557736881328888</v>
@@ -3847,7 +3859,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3861,7 +3873,7 @@
         <v>2.809824187676618</v>
       </c>
       <c r="D47" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E47">
         <v>2.557736881328888</v>
@@ -3897,7 +3909,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3947,7 +3959,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3961,7 +3973,7 @@
         <v>2.877968395292299</v>
       </c>
       <c r="D49" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E49">
         <v>2.644629614722029</v>
@@ -3997,7 +4009,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4011,7 +4023,7 @@
         <v>2.896376165252531</v>
       </c>
       <c r="D50" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E50">
         <v>2.644629614722029</v>
@@ -4047,7 +4059,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4061,7 +4073,7 @@
         <v>2.521770137334771</v>
       </c>
       <c r="D51" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E51">
         <v>2.535896862069519</v>
@@ -4097,7 +4109,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4111,7 +4123,7 @@
         <v>2.934431839092635</v>
       </c>
       <c r="D52" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E52">
         <v>2.703517868992319</v>
@@ -4147,7 +4159,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4161,7 +4173,7 @@
         <v>2.955033485192349</v>
       </c>
       <c r="D53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E53">
         <v>2.703517868992319</v>
@@ -4197,7 +4209,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4247,7 +4259,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4261,7 +4273,7 @@
         <v>2.974730272968942</v>
       </c>
       <c r="D55" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E55">
         <v>2.745546910458406</v>
@@ -4297,7 +4309,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4311,7 +4323,7 @@
         <v>2.996897706887981</v>
       </c>
       <c r="D56" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E56">
         <v>2.745546910458406</v>
@@ -4347,7 +4359,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4361,7 +4373,7 @@
         <v>2.624468326525319</v>
       </c>
       <c r="D57" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E57">
         <v>2.660688149733082</v>
@@ -4397,7 +4409,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4411,7 +4423,7 @@
         <v>3.056805462611843</v>
       </c>
       <c r="D58" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E58">
         <v>2.831146801497014</v>
@@ -4447,7 +4459,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4497,7 +4509,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4511,7 +4523,7 @@
         <v>3.075488420323122</v>
       </c>
       <c r="D60" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E60">
         <v>2.850632094815525</v>
@@ -4561,7 +4573,7 @@
         <v>2.73140795531227</v>
       </c>
       <c r="D61" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E61">
         <v>2.75953055997749</v>
@@ -4611,7 +4623,7 @@
         <v>2.72765316464271</v>
       </c>
       <c r="D62" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E62">
         <v>2.75953055997749</v>
@@ -4661,7 +4673,7 @@
         <v>2.72671446697532</v>
       </c>
       <c r="D63" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E63">
         <v>2.75953055997749</v>
@@ -4711,7 +4723,7 @@
         <v>6.293149296554828</v>
       </c>
       <c r="D64" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E64">
         <v>5.963700498102364</v>
@@ -4747,7 +4759,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4761,7 +4773,7 @@
         <v>6.420239880180696</v>
       </c>
       <c r="D65" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E65">
         <v>6.082402264327184</v>
@@ -4797,7 +4809,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4811,7 +4823,7 @@
         <v>6.609514294497387</v>
       </c>
       <c r="D66" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E66">
         <v>6.259183317962906</v>
@@ -4847,7 +4859,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4861,7 +4873,7 @@
         <v>6.515171551263329</v>
       </c>
       <c r="D67" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E67">
         <v>6.612047937164794</v>
@@ -4897,7 +4909,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4911,7 +4923,7 @@
         <v>6.520829737768901</v>
       </c>
       <c r="D68" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E68">
         <v>6.612047937164794</v>
@@ -4947,7 +4959,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -4997,7 +5009,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5047,7 +5059,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5097,7 +5109,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5111,7 +5123,7 @@
         <v>6.781478804637512</v>
       </c>
       <c r="D72" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E72">
         <v>6.821616798629249</v>
@@ -5147,7 +5159,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5161,7 +5173,7 @@
         <v>6.927933775178332</v>
       </c>
       <c r="D73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E73">
         <v>7.025464228815041</v>
@@ -5197,7 +5209,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5211,7 +5223,7 @@
         <v>7.465293617228137</v>
       </c>
       <c r="D74" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E74">
         <v>7.441132824526438</v>
@@ -5247,7 +5259,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5261,7 +5273,7 @@
         <v>2.399740228983164</v>
       </c>
       <c r="D75" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E75">
         <v>2.284756328614283</v>
@@ -5297,7 +5309,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5311,7 +5323,7 @@
         <v>2.181146111927123</v>
       </c>
       <c r="D76" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E76">
         <v>2.105842395854763</v>
@@ -5347,7 +5359,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5361,7 +5373,7 @@
         <v>2.180858495485883</v>
       </c>
       <c r="D77" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E77">
         <v>2.105842395854763</v>
@@ -5397,7 +5409,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5411,7 +5423,7 @@
         <v>2.355267416838251</v>
       </c>
       <c r="D78" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E78">
         <v>2.241615480893012</v>
@@ -5447,7 +5459,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5461,7 +5473,7 @@
         <v>2.138079262229388</v>
       </c>
       <c r="D79" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E79">
         <v>2.115876072829124</v>
@@ -5497,7 +5509,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5511,7 +5523,7 @@
         <v>2.136977667529256</v>
       </c>
       <c r="D80" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E80">
         <v>2.115876072829124</v>
@@ -5547,7 +5559,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5597,7 +5609,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5647,7 +5659,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5697,7 +5709,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5711,7 +5723,7 @@
         <v>1.925553832103902</v>
       </c>
       <c r="D84" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E84">
         <v>1.985821650998686</v>
@@ -5747,7 +5759,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5797,7 +5809,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5811,7 +5823,7 @@
         <v>1.87975631937778</v>
       </c>
       <c r="D86" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E86">
         <v>2.025900250164519</v>
@@ -5847,7 +5859,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5947,7 +5959,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5961,7 +5973,7 @@
         <v>1.789383875507923</v>
       </c>
       <c r="D89" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E89">
         <v>1.940268655809146</v>
@@ -5997,7 +6009,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6011,7 +6023,7 @@
         <v>1.804905667333501</v>
       </c>
       <c r="D90" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E90">
         <v>1.95497618970289</v>
@@ -6047,7 +6059,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6061,7 +6073,7 @@
         <v>1.809491967335235</v>
       </c>
       <c r="D91" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E91">
         <v>1.959321896917648</v>
@@ -6097,7 +6109,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6111,7 +6123,7 @@
         <v>1.822908408572121</v>
       </c>
       <c r="D92" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E92">
         <v>1.972034524843747</v>
@@ -6147,7 +6159,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6161,7 +6173,7 @@
         <v>2.011491451443282</v>
       </c>
       <c r="D93" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E93">
         <v>1.930405304642352</v>
@@ -6197,7 +6209,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6211,7 +6223,7 @@
         <v>1.820166348365971</v>
       </c>
       <c r="D94" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E94">
         <v>1.969436310418903</v>
@@ -6247,7 +6259,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6261,7 +6273,7 @@
         <v>2.008879751476441</v>
       </c>
       <c r="D95" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E95">
         <v>1.927766633591516</v>
@@ -6297,7 +6309,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6311,7 +6323,7 @@
         <v>1.780154910291897</v>
       </c>
       <c r="D96" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E96">
         <v>1.931523833030682</v>
@@ -6347,7 +6359,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6397,7 +6409,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6411,7 +6423,7 @@
         <v>1.781411528733962</v>
       </c>
       <c r="D98" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E98">
         <v>1.932714530505294</v>
@@ -6447,7 +6459,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6497,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6511,7 +6523,7 @@
         <v>1.786869994736246</v>
       </c>
       <c r="D100" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E100">
         <v>1.937886650750082</v>
@@ -6561,7 +6573,7 @@
         <v>1.77389224303264</v>
       </c>
       <c r="D101" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E101">
         <v>1.925589699135846</v>
@@ -6597,7 +6609,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6611,7 +6623,7 @@
         <v>1.764225388294109</v>
       </c>
       <c r="D102" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E102">
         <v>1.916429958088516</v>
@@ -6811,7 +6823,7 @@
         <v>2.039049007419374</v>
       </c>
       <c r="D106" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E106">
         <v>1.958247448115615</v>
@@ -6847,7 +6859,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6861,7 +6873,7 @@
         <v>1.963804213639886</v>
       </c>
       <c r="D107" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E107">
         <v>2.044635472991321</v>
@@ -6897,7 +6909,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6911,7 +6923,7 @@
         <v>2.084469221121035</v>
       </c>
       <c r="D108" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E108">
         <v>2.00413671738046</v>
@@ -6947,7 +6959,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6961,7 +6973,7 @@
         <v>1.970692549466935</v>
       </c>
       <c r="D109" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E109">
         <v>2.103970465510173</v>
@@ -6997,7 +7009,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7047,7 +7059,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7061,7 +7073,7 @@
         <v>1.989826166099606</v>
       </c>
       <c r="D111" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E111">
         <v>2.069999197311251</v>
@@ -7097,7 +7109,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7111,7 +7123,7 @@
         <v>1.996538974422711</v>
       </c>
       <c r="D112" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E112">
         <v>2.129860772341935</v>
@@ -7147,7 +7159,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7197,7 +7209,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7211,7 +7223,7 @@
         <v>1.976959483296697</v>
       </c>
       <c r="D114" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E114">
         <v>2.110248039295503</v>
@@ -7311,7 +7323,7 @@
         <v>1.920546112528168</v>
       </c>
       <c r="D116" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E116">
         <v>2.053738890308352</v>
@@ -7347,7 +7359,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7397,7 +7409,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7411,7 +7423,7 @@
         <v>2.078859445890371</v>
       </c>
       <c r="D118" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E118">
         <v>2.128859445890371</v>
@@ -7447,7 +7459,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7461,7 +7473,7 @@
         <v>1.864471846503076</v>
       </c>
       <c r="D119" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E119">
         <v>1.997569421794252</v>
@@ -7497,7 +7509,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7547,7 +7559,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7597,7 +7609,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7611,7 +7623,7 @@
         <v>1.863420505387863</v>
       </c>
       <c r="D122" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E122">
         <v>1.996516295719591</v>
@@ -7711,7 +7723,7 @@
         <v>2.029857360363785</v>
       </c>
       <c r="D124" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E124">
         <v>2.011995247378231</v>
@@ -7761,7 +7773,7 @@
         <v>1.892165706973767</v>
       </c>
       <c r="D125" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E125">
         <v>2.025310300703773</v>
@@ -7797,7 +7809,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7847,7 +7859,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7897,7 +7909,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7961,7 +7973,7 @@
         <v>2.183293967129219</v>
       </c>
       <c r="D129" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E129">
         <v>2.097698061214447</v>
@@ -8011,7 +8023,7 @@
         <v>2.10409703769314</v>
       </c>
       <c r="D130" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E130">
         <v>2.097698061214447</v>
@@ -8097,7 +8109,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8147,7 +8159,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8197,7 +8209,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8247,7 +8259,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8297,7 +8309,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8347,7 +8359,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8397,7 +8409,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8447,7 +8459,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8461,7 +8473,7 @@
         <v>2.367284598691813</v>
       </c>
       <c r="D139" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E139">
         <v>2.284677125480481</v>
@@ -8511,7 +8523,7 @@
         <v>2.308705785003503</v>
       </c>
       <c r="D140" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E140">
         <v>2.284677125480481</v>
@@ -8647,7 +8659,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8697,7 +8709,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8747,7 +8759,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8797,7 +8809,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8847,7 +8859,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8911,7 +8923,7 @@
         <v>2.673055621612132</v>
       </c>
       <c r="D148" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E148">
         <v>2.649383477311975</v>
@@ -8961,7 +8973,7 @@
         <v>2.694510447967022</v>
       </c>
       <c r="D149" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E149">
         <v>2.66746656530884</v>
@@ -9011,7 +9023,7 @@
         <v>2.61961842602696</v>
       </c>
       <c r="D150" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E150">
         <v>2.674946565009619</v>
@@ -9297,7 +9309,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9311,7 +9323,7 @@
         <v>2.746485076848839</v>
       </c>
       <c r="D156" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E156">
         <v>2.847982602490786</v>
@@ -9347,7 +9359,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9411,7 +9423,7 @@
         <v>2.750734210259811</v>
       </c>
       <c r="D158" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E158">
         <v>2.800734210259812</v>
@@ -9447,7 +9459,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9511,7 +9523,7 @@
         <v>2.717092536535202</v>
       </c>
       <c r="D160" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E160">
         <v>2.791717770085309</v>
@@ -9597,7 +9609,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9611,7 +9623,7 @@
         <v>2.669840281895235</v>
       </c>
       <c r="D162" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E162">
         <v>2.754805459723328</v>
@@ -9647,7 +9659,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9711,7 +9723,7 @@
         <v>2.704152220032186</v>
       </c>
       <c r="D164" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E164">
         <v>2.721608307945189</v>
@@ -9761,7 +9773,7 @@
         <v>0.7516342779874527</v>
       </c>
       <c r="D165" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E165">
         <v>0.6447312303040151</v>
@@ -9797,7 +9809,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9811,7 +9823,7 @@
         <v>0.6347312303040145</v>
       </c>
       <c r="D166" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E166">
         <v>0.7803954970608276</v>
@@ -9847,7 +9859,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9861,7 +9873,7 @@
         <v>0.7872985447442655</v>
       </c>
       <c r="D167" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E167">
         <v>0.6685373256708909</v>
@@ -9897,7 +9909,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9911,7 +9923,7 @@
         <v>0.6141118398407031</v>
       </c>
       <c r="D168" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E168">
         <v>0.7042015924277036</v>
@@ -9947,7 +9959,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9961,7 +9973,7 @@
         <v>0.7076194190074974</v>
       </c>
       <c r="D169" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E169">
         <v>0.8524403513495589</v>
@@ -10011,7 +10023,7 @@
         <v>0.8587410173081755</v>
       </c>
       <c r="D170" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E170">
         <v>0.7402207509247285</v>
@@ -10061,7 +10073,7 @@
         <v>0.6868795521992208</v>
       </c>
       <c r="D171" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E171">
         <v>0.7750416832667906</v>
@@ -10111,7 +10123,7 @@
         <v>0.794311018129779</v>
       </c>
       <c r="D172" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E172">
         <v>0.9381289071762104</v>
@@ -10147,7 +10159,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10161,7 +10173,7 @@
         <v>0.7478436529603893</v>
       </c>
       <c r="D173" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E173">
         <v>0.9381289071762104</v>
@@ -10197,7 +10209,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10211,7 +10223,7 @@
         <v>0.9437131136379486</v>
       </c>
       <c r="D174" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E174">
         <v>0.8254794310532532</v>
@@ -10247,7 +10259,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10261,7 +10273,7 @@
         <v>0.7734278594221262</v>
       </c>
       <c r="D175" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E175">
         <v>0.8592973200996861</v>
@@ -10297,7 +10309,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10311,7 +10323,7 @@
         <v>0.9016190641047892</v>
       </c>
       <c r="D176" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E176">
         <v>1.04419537245399</v>
@@ -10347,7 +10359,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10361,7 +10373,7 @@
         <v>0.8558611736195321</v>
       </c>
       <c r="D177" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E177">
         <v>1.04419537245399</v>
@@ -10397,7 +10409,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10411,7 +10423,7 @@
         <v>1.048892735560562</v>
       </c>
       <c r="D178" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E178">
         <v>0.9310137903179339</v>
@@ -10447,7 +10459,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10461,7 +10473,7 @@
         <v>0.8805585367261042</v>
       </c>
       <c r="D179" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E179">
         <v>0.963590098667134</v>
@@ -10497,7 +10509,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10511,7 +10523,7 @@
         <v>1.076170489586433</v>
       </c>
       <c r="D180" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E180">
         <v>1.260525374010979</v>
@@ -10561,7 +10573,7 @@
         <v>1.26341395784032</v>
       </c>
       <c r="D181" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E181">
         <v>1.146258524308584</v>
@@ -10611,7 +10623,7 @@
         <v>1.099059073415773</v>
       </c>
       <c r="D182" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E182">
         <v>1.176302541669659</v>
@@ -10661,7 +10673,7 @@
         <v>1.931268098407571</v>
       </c>
       <c r="D183" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E183">
         <v>1.946759727730396</v>
@@ -10697,7 +10709,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10747,7 +10759,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10797,7 +10809,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10811,7 +10823,7 @@
         <v>0.5942088493584849</v>
       </c>
       <c r="D186" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E186">
         <v>0.5982130518354056</v>
@@ -10847,7 +10859,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10897,7 +10909,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10947,7 +10959,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -10997,7 +11009,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11011,7 +11023,7 @@
         <v>-0.02499489055226256</v>
       </c>
       <c r="D190" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E190">
         <v>-0.07499489055226238</v>
@@ -11047,7 +11059,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11061,7 +11073,7 @@
         <v>-0.04541693580813089</v>
       </c>
       <c r="D191" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E191">
         <v>-0.1350880582477796</v>
@@ -11097,7 +11109,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11147,7 +11159,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11197,7 +11209,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11347,7 +11359,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11361,7 +11373,7 @@
         <v>-0.5154661476950757</v>
       </c>
       <c r="D197" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E197">
         <v>-0.4838284745942198</v>
@@ -11397,7 +11409,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11411,7 +11423,7 @@
         <v>-0.5144835438345625</v>
       </c>
       <c r="D198" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E198">
         <v>-0.4838284745942198</v>
@@ -11447,7 +11459,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11497,7 +11509,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11511,7 +11523,7 @@
         <v>-0.6795603356321358</v>
       </c>
       <c r="D200" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E200">
         <v>-0.6353746161347429</v>
@@ -11547,7 +11559,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11561,7 +11573,7 @@
         <v>-0.6770489039336995</v>
       </c>
       <c r="D201" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E201">
         <v>-0.6353746161347429</v>
@@ -11597,7 +11609,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11647,7 +11659,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11661,7 +11673,7 @@
         <v>-1.275160705635463</v>
       </c>
       <c r="D203" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E203">
         <v>-0.9575450227817477</v>
@@ -11697,7 +11709,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11711,7 +11723,7 @@
         <v>-1.267100202166811</v>
       </c>
       <c r="D204" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E204">
         <v>-0.9575450227817477</v>
@@ -11747,7 +11759,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11811,7 +11823,7 @@
         <v>-1.30354206111917</v>
       </c>
       <c r="D206" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E206">
         <v>-0.9846924062879019</v>
@@ -11861,7 +11873,7 @@
         <v>-1.295217135083899</v>
       </c>
       <c r="D207" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E207">
         <v>-0.9846924062879019</v>
@@ -11911,7 +11923,7 @@
         <v>-1.315601110783377</v>
       </c>
       <c r="D208" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E208">
         <v>-0.9962271494449686</v>
@@ -11961,7 +11973,7 @@
         <v>-1.307163833353718</v>
       </c>
       <c r="D209" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E209">
         <v>-0.9962271494449686</v>
@@ -12011,7 +12023,7 @@
         <v>-1.303470101275702</v>
       </c>
       <c r="D210" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E210">
         <v>-0.9846235751332797</v>
@@ -12047,7 +12059,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12061,7 +12073,7 @@
         <v>-1.295145845673754</v>
       </c>
       <c r="D211" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E211">
         <v>-0.9846235751332797</v>
@@ -12097,7 +12109,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12111,7 +12123,7 @@
         <v>-1.352240812118975</v>
       </c>
       <c r="D212" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E212">
         <v>-1.031273820287715</v>
@@ -12147,7 +12159,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12161,7 +12173,7 @@
         <v>-1.343462171012276</v>
       </c>
       <c r="D213" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E213">
         <v>-1.031273820287715</v>
@@ -12197,7 +12209,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12247,7 +12259,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12261,7 +12273,7 @@
         <v>-1.277973836666044</v>
       </c>
       <c r="D215" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E215">
         <v>-0.9602358437675207</v>
@@ -12311,7 +12323,7 @@
         <v>-1.269887123902075</v>
       </c>
       <c r="D216" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E216">
         <v>-0.9602358437675207</v>
@@ -12361,7 +12373,7 @@
         <v>-1.030235843767521</v>
       </c>
       <c r="D217" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E217">
         <v>-1.080019061857596</v>
@@ -12411,7 +12423,7 @@
         <v>-1.007888992711643</v>
       </c>
       <c r="D218" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E218">
         <v>-1.080019061857596</v>
@@ -12461,7 +12473,7 @@
         <v>-1.154349245698821</v>
       </c>
       <c r="D219" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E219">
         <v>-0.8419862350162637</v>
@@ -12511,7 +12523,7 @@
         <v>-1.147414314838273</v>
       </c>
       <c r="D220" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E220">
         <v>-0.8419862350162637</v>
@@ -12661,7 +12673,7 @@
         <v>-0.9332125637434627</v>
       </c>
       <c r="D223" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E223">
         <v>-0.6304641914067899</v>
@@ -12697,7 +12709,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12711,7 +12723,7 @@
         <v>-0.9283379125284608</v>
       </c>
       <c r="D224" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E224">
         <v>-0.6304641914067899</v>
@@ -12747,7 +12759,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12761,7 +12773,7 @@
         <v>-1.078298911794628</v>
       </c>
       <c r="D225" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E225">
         <v>-0.7337942740491279</v>
@@ -12811,7 +12823,7 @@
         <v>-1.284045732215318</v>
       </c>
       <c r="D226" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E226">
         <v>-0.9315166474955321</v>
@@ -12861,7 +12873,7 @@
         <v>-1.074552792811861</v>
       </c>
       <c r="D227" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E227">
         <v>-0.7301942595508679</v>
@@ -12897,7 +12909,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12911,7 +12923,7 @@
         <v>0.6306184682796347</v>
       </c>
       <c r="D228" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E228">
         <v>0.8825890610024754</v>
@@ -12947,7 +12959,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12961,7 +12973,7 @@
         <v>2.500083924851446</v>
       </c>
       <c r="D229" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E229">
         <v>2.721828222716436</v>
@@ -12997,7 +13009,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13011,7 +13023,7 @@
         <v>2.484743417251086</v>
       </c>
       <c r="D230" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E230">
         <v>2.721828222716436</v>
@@ -13047,7 +13059,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13061,7 +13073,7 @@
         <v>2.959498476516616</v>
       </c>
       <c r="D231" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E231">
         <v>3.019498476516616</v>
@@ -13097,7 +13109,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13147,7 +13159,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13161,7 +13173,7 @@
         <v>3.973072767193392</v>
       </c>
       <c r="D233" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E233">
         <v>3.630196829293595</v>
@@ -13197,7 +13209,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13247,7 +13259,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13297,7 +13309,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13311,7 +13323,7 @@
         <v>4.556254256131551</v>
       </c>
       <c r="D236" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E236">
         <v>4.211276763316661</v>
@@ -13347,7 +13359,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13397,7 +13409,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13447,7 +13459,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13461,7 +13473,7 @@
         <v>4.667791750685101</v>
       </c>
       <c r="D239" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E239">
         <v>4.322412320952902</v>
@@ -13497,7 +13509,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13511,7 +13523,7 @@
         <v>4.273963746622406</v>
       </c>
       <c r="D240" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E240">
         <v>4.266274031756307</v>
@@ -13547,7 +13559,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13597,7 +13609,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13647,7 +13659,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13661,7 +13673,7 @@
         <v>3.655351043939968</v>
       </c>
       <c r="D243" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E243">
         <v>3.313620049187031</v>
@@ -13697,7 +13709,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13711,7 +13723,7 @@
         <v>2.349652973133038</v>
       </c>
       <c r="D244" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E244">
         <v>2.585321458264525</v>
@@ -13761,7 +13773,7 @@
         <v>2.337296219946928</v>
       </c>
       <c r="D245" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E245">
         <v>2.585321458264525</v>
@@ -13811,7 +13823,7 @@
         <v>2.821499834857581</v>
       </c>
       <c r="D246" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E246">
         <v>2.482773709326562</v>
@@ -13861,7 +13873,7 @@
         <v>1.399171925433256</v>
       </c>
       <c r="D247" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E247">
         <v>1.7228188215915</v>
@@ -13897,7 +13909,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13911,7 +13923,7 @@
         <v>1.94957093986026</v>
       </c>
       <c r="D248" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E248">
         <v>1.61398690043734</v>
@@ -13947,7 +13959,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13961,7 +13973,7 @@
         <v>1.388298565840941</v>
       </c>
       <c r="D249" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E249">
         <v>1.05473712956764</v>
@@ -14011,7 +14023,7 @@
         <v>1.206849236469149</v>
       </c>
       <c r="D250" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E250">
         <v>0.8739416716530437</v>
@@ -14061,7 +14073,7 @@
         <v>1.250249534396463</v>
       </c>
       <c r="D251" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E251">
         <v>0.9171855721103492</v>
@@ -14111,7 +14123,7 @@
         <v>1.265784593473219</v>
       </c>
       <c r="D252" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E252">
         <v>0.9326646489922341</v>
@@ -14147,7 +14159,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14161,7 +14173,7 @@
         <v>1.181086185990114</v>
       </c>
       <c r="D253" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E253">
         <v>0.8482714609955542</v>
@@ -14211,7 +14223,7 @@
         <v>3.393868635799184</v>
       </c>
       <c r="D254" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E254">
         <v>3.232668972857903</v>
@@ -14247,7 +14259,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14261,7 +14273,7 @@
         <v>3.344337857016143</v>
       </c>
       <c r="D255" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E255">
         <v>3.232668972857903</v>
@@ -14297,7 +14309,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14311,7 +14323,7 @@
         <v>3.108144846549583</v>
       </c>
       <c r="D256" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E256">
         <v>3.176241351782863</v>
@@ -14347,7 +14359,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14361,7 +14373,7 @@
         <v>3.110765478091183</v>
       </c>
       <c r="D257" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E257">
         <v>3.176241351782863</v>
@@ -14397,7 +14409,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14411,7 +14423,7 @@
         <v>3.484929217459694</v>
       </c>
       <c r="D258" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E258">
         <v>3.328403460479749</v>
@@ -14447,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14461,7 +14473,7 @@
         <v>3.438944160440425</v>
       </c>
       <c r="D259" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E259">
         <v>3.328403460479749</v>
@@ -14497,7 +14509,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14547,7 +14559,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14597,7 +14609,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14611,7 +14623,7 @@
         <v>3.67612531160249</v>
       </c>
       <c r="D262" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E262">
         <v>3.529413159454653</v>
@@ -14647,7 +14659,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14661,7 +14673,7 @@
         <v>3.637585058248958</v>
       </c>
       <c r="D263" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E263">
         <v>3.529413159454653</v>
@@ -14697,7 +14709,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14711,7 +14723,7 @@
         <v>3.405388602484038</v>
       </c>
       <c r="D264" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E264">
         <v>3.509413159454653</v>
@@ -14747,7 +14759,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14761,7 +14773,7 @@
         <v>3.405511387337113</v>
       </c>
       <c r="D265" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E265">
         <v>3.509413159454653</v>
@@ -14797,7 +14809,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14811,7 +14823,7 @@
         <v>3.451364045513422</v>
       </c>
       <c r="D266" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E266">
         <v>3.509413159454653</v>
@@ -14847,7 +14859,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14861,7 +14873,7 @@
         <v>4.004636932335591</v>
       </c>
       <c r="D267" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E267">
         <v>3.867442887120403</v>
@@ -14911,7 +14923,7 @@
         <v>3.774439165379895</v>
       </c>
       <c r="D268" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E268">
         <v>3.837640654076098</v>
@@ -14961,7 +14973,7 @@
         <v>4.220199786446392</v>
       </c>
       <c r="D269" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E269">
         <v>4.085943565478028</v>
@@ -14997,7 +15009,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15011,7 +15023,7 @@
         <v>3.991103703583256</v>
       </c>
       <c r="D270" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E270">
         <v>4.0441357312043</v>
@@ -15047,7 +15059,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15061,7 +15073,7 @@
         <v>4.24807262091024</v>
       </c>
       <c r="D271" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E271">
         <v>4.172298835483293</v>
@@ -15097,7 +15109,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15111,7 +15123,7 @@
         <v>4.076733299050661</v>
       </c>
       <c r="D272" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E272">
         <v>4.185185728196767</v>
@@ -15147,7 +15159,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15211,7 +15223,7 @@
         <v>3.853669569225198</v>
       </c>
       <c r="D274" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E274">
         <v>3.960609701897911</v>
@@ -15347,7 +15359,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15361,7 +15373,7 @@
         <v>3.457860783201086</v>
       </c>
       <c r="D277" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E277">
         <v>3.562117466477025</v>
@@ -15397,7 +15409,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15411,7 +15423,7 @@
         <v>3.461796612382101</v>
       </c>
       <c r="D278" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E278">
         <v>3.45818163729601</v>
@@ -15447,7 +15459,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15511,7 +15523,7 @@
         <v>1.876063224574707</v>
       </c>
       <c r="D280" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E280">
         <v>1.926860456775207</v>
@@ -15561,7 +15573,7 @@
         <v>1.879462993924748</v>
       </c>
       <c r="D281" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E281">
         <v>1.926860456775207</v>
@@ -15611,7 +15623,7 @@
         <v>1.36286186891499</v>
       </c>
       <c r="D282" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E282">
         <v>1.420876924621103</v>
@@ -15647,7 +15659,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15661,7 +15673,7 @@
         <v>1.365396205962064</v>
       </c>
       <c r="D283" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E283">
         <v>1.420876924621103</v>
@@ -15697,7 +15709,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15711,7 +15723,7 @@
         <v>1.492587172538397</v>
       </c>
       <c r="D284" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E284">
         <v>1.422587172538397</v>
@@ -15747,7 +15759,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15761,7 +15773,7 @@
         <v>1.155028253713973</v>
       </c>
       <c r="D285" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E285">
         <v>1.207786135342488</v>
@@ -15811,7 +15823,7 @@
         <v>1.157212112489207</v>
       </c>
       <c r="D286" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E286">
         <v>1.207786135342488</v>
@@ -15861,7 +15873,7 @@
         <v>1.287557383512098</v>
       </c>
       <c r="D287" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E287">
         <v>1.260086513310223</v>
@@ -15911,7 +15923,7 @@
         <v>-0.2566084186298667</v>
       </c>
       <c r="D288" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E288">
         <v>-0.001048450451905936</v>
@@ -15947,7 +15959,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15961,7 +15973,7 @@
         <v>-0.2875710874180024</v>
       </c>
       <c r="D289" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E289">
         <v>-0.001048450451905936</v>
@@ -15997,7 +16009,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16047,7 +16059,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16097,7 +16109,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16111,7 +16123,7 @@
         <v>-0.3429456734762377</v>
       </c>
       <c r="D292" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E292">
         <v>-0.1559309932859021</v>
@@ -16147,7 +16159,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16161,7 +16173,7 @@
         <v>-0.452945673476238</v>
       </c>
       <c r="D293" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E293">
         <v>-0.1559309932859021</v>
@@ -16197,7 +16209,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16211,7 +16223,7 @@
         <v>-0.07614423041516449</v>
       </c>
       <c r="D294" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E294">
         <v>-0.08649962563060054</v>
@@ -16247,7 +16259,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16261,7 +16273,7 @@
         <v>-0.06685502084603723</v>
       </c>
       <c r="D295" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E295">
         <v>-0.08649962563060054</v>
@@ -16297,7 +16309,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16311,7 +16323,7 @@
         <v>-0.6325763258089658</v>
       </c>
       <c r="D296" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E296">
         <v>-0.7397037652284588</v>
@@ -16347,7 +16359,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16361,7 +16373,7 @@
         <v>-0.6888811406779016</v>
       </c>
       <c r="D297" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E297">
         <v>-0.6347573064746772</v>
@@ -16397,7 +16409,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16411,7 +16423,7 @@
         <v>-0.5922830059527424</v>
       </c>
       <c r="D298" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E298">
         <v>-0.6988811406779014</v>
@@ -16447,7 +16459,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16461,7 +16473,7 @@
         <v>-0.7708727781363214</v>
       </c>
       <c r="D299" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E299">
         <v>-0.7160845060282481</v>
@@ -16497,7 +16509,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16511,7 +16523,7 @@
         <v>-0.6732115427634033</v>
       </c>
       <c r="D300" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E300">
         <v>-0.7808727781363212</v>
@@ -16547,7 +16559,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16561,7 +16573,7 @@
         <v>-0.6051723879795468</v>
       </c>
       <c r="D301" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E301">
         <v>-0.5517269067155315</v>
@@ -16597,7 +16609,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16611,7 +16623,7 @@
         <v>-0.509659617957122</v>
       </c>
       <c r="D302" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E302">
         <v>-0.6151723879795465</v>
@@ -16647,7 +16659,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16661,7 +16673,7 @@
         <v>1.374867998585327</v>
       </c>
       <c r="D303" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E303">
         <v>1.61428021608427</v>
@@ -16697,7 +16709,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16711,7 +16723,7 @@
         <v>1.37455579980999</v>
       </c>
       <c r="D304" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E304">
         <v>1.61428021608427</v>
@@ -16747,7 +16759,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16761,7 +16773,7 @@
         <v>1.659046067002767</v>
       </c>
       <c r="D305" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E305">
         <v>1.701663141543517</v>
@@ -16797,7 +16809,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16811,7 +16823,7 @@
         <v>1.400425101402588</v>
       </c>
       <c r="D306" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E306">
         <v>1.63789275673065</v>
@@ -16847,7 +16859,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16861,7 +16873,7 @@
         <v>1.415426421593279</v>
       </c>
       <c r="D307" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E307">
         <v>1.63789275673065</v>
@@ -16897,7 +16909,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16911,7 +16923,7 @@
         <v>1.672891436539961</v>
       </c>
       <c r="D308" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E308">
         <v>1.702888796158578</v>
@@ -16947,7 +16959,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16961,7 +16973,7 @@
         <v>1.682896717302726</v>
       </c>
       <c r="D309" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E309">
         <v>1.702888796158578</v>
@@ -16997,7 +17009,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17011,7 +17023,7 @@
         <v>1.392287936404873</v>
       </c>
       <c r="D310" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E310">
         <v>1.630374723852328</v>
@@ -17047,7 +17059,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17061,7 +17073,7 @@
         <v>1.392192134372636</v>
       </c>
       <c r="D311" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E311">
         <v>1.630374723852328</v>
@@ -17097,7 +17109,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17111,7 +17123,7 @@
         <v>1.665398674360388</v>
       </c>
       <c r="D312" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E312">
         <v>1.367982501138595</v>
@@ -17147,7 +17159,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17161,7 +17173,7 @@
         <v>1.67530287232815</v>
       </c>
       <c r="D313" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E313">
         <v>1.367982501138595</v>
@@ -17197,7 +17209,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17211,7 +17223,7 @@
         <v>1.683187064752997</v>
       </c>
       <c r="D314" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E314">
         <v>1.385560910531628</v>
@@ -17247,7 +17259,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17261,7 +17273,7 @@
         <v>1.693331241005988</v>
       </c>
       <c r="D315" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E315">
         <v>1.385560910531628</v>
@@ -17297,7 +17309,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17311,7 +17323,7 @@
         <v>1.671335210176903</v>
       </c>
       <c r="D316" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E316">
         <v>1.373848959803819</v>
@@ -17347,7 +17359,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17361,7 +17373,7 @@
         <v>1.68131949631757</v>
       </c>
       <c r="D317" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E317">
         <v>1.373848959803819</v>
@@ -17397,7 +17409,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17411,7 +17423,7 @@
         <v>1.693875753393727</v>
       </c>
       <c r="D318" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E318">
         <v>1.396123425781996</v>
@@ -17447,7 +17459,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17461,7 +17473,7 @@
         <v>1.704164127807133</v>
       </c>
       <c r="D319" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E319">
         <v>1.396123425781996</v>
@@ -17497,7 +17509,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17511,7 +17523,7 @@
         <v>1.366123425781996</v>
       </c>
       <c r="D320" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E320">
         <v>1.403731566187024</v>
@@ -17547,7 +17559,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17561,7 +17573,7 @@
         <v>1.710631890779994</v>
       </c>
       <c r="D321" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E321">
         <v>1.412681767280061</v>
@@ -17597,7 +17609,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17611,7 +17623,7 @@
         <v>1.72114631763706</v>
       </c>
       <c r="D322" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E322">
         <v>1.412681767280061</v>
@@ -17647,7 +17659,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17661,7 +17673,7 @@
         <v>1.382681767280062</v>
       </c>
       <c r="D323" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E323">
         <v>1.420374677351461</v>
@@ -17697,7 +17709,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17711,7 +17723,7 @@
         <v>1.679206240881443</v>
       </c>
       <c r="D324" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E324">
         <v>1.381627077835624</v>
@@ -17761,7 +17773,7 @@
         <v>1.689296712933807</v>
       </c>
       <c r="D325" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E325">
         <v>1.381627077835624</v>
@@ -17811,7 +17823,7 @@
         <v>1.351627077835625</v>
       </c>
       <c r="D326" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E326">
         <v>1.364138386842169</v>
@@ -17861,7 +17873,7 @@
         <v>1.662615013806636</v>
       </c>
       <c r="D327" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E327">
         <v>1.365231699984297</v>
@@ -17897,7 +17909,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17911,7 +17923,7 @@
         <v>1.672481658175022</v>
       </c>
       <c r="D328" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E328">
         <v>1.365231699984297</v>
@@ -17947,7 +17959,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17961,7 +17973,7 @@
         <v>1.335231699984297</v>
       </c>
       <c r="D329" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E329">
         <v>1.330198361076394</v>
@@ -17997,7 +18009,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18011,7 +18023,7 @@
         <v>1.638483426036899</v>
       </c>
       <c r="D330" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E330">
         <v>1.341384970754843</v>
@@ -18061,7 +18073,7 @@
         <v>1.648024517787818</v>
       </c>
       <c r="D331" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E331">
         <v>1.341384970754843</v>
@@ -18161,7 +18173,7 @@
         <v>1.611118158429232</v>
       </c>
       <c r="D333" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E333">
         <v>1.31434273328757</v>
@@ -18211,7 +18223,7 @@
         <v>1.620290072876844</v>
       </c>
       <c r="D334" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E334">
         <v>1.31434273328757</v>
@@ -18261,7 +18273,7 @@
         <v>1.210704115653037</v>
       </c>
       <c r="D335" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E335">
         <v>1.321946243981619</v>
@@ -18311,7 +18323,7 @@
         <v>1.250704115653037</v>
       </c>
       <c r="D336" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E336">
         <v>1.321946243981619</v>
@@ -18361,7 +18373,7 @@
         <v>1.580824889600507</v>
       </c>
       <c r="D337" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E337">
         <v>1.284407057851428</v>
@@ -18397,7 +18409,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18411,7 +18423,7 @@
         <v>1.589588125885168</v>
       </c>
       <c r="D338" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E338">
         <v>1.284407057851428</v>
@@ -18447,7 +18459,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18461,7 +18473,7 @@
         <v>1.180206507742837</v>
       </c>
       <c r="D339" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E339">
         <v>1.27675246238701</v>
@@ -18497,7 +18509,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18511,7 +18523,7 @@
         <v>1.220206507742837</v>
       </c>
       <c r="D340" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E340">
         <v>1.27675246238701</v>
@@ -18547,7 +18559,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18561,7 +18573,7 @@
         <v>1.680056540073359</v>
       </c>
       <c r="D341" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E341">
         <v>1.409353064352823</v>
@@ -18597,7 +18609,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18611,7 +18623,7 @@
         <v>1.717732409003494</v>
       </c>
       <c r="D342" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E342">
         <v>1.409353064352823</v>
@@ -18647,7 +18659,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18661,7 +18673,7 @@
         <v>1.307497917096648</v>
       </c>
       <c r="D343" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E343">
         <v>1.444235818399402</v>
@@ -18697,7 +18709,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18711,7 +18723,7 @@
         <v>1.347497917096648</v>
       </c>
       <c r="D344" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E344">
         <v>1.444235818399402</v>
@@ -18747,7 +18759,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18761,7 +18773,7 @@
         <v>1.842256392262994</v>
       </c>
       <c r="D345" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E345">
         <v>1.530769127897027</v>
@@ -18811,7 +18823,7 @@
         <v>1.431193121765403</v>
       </c>
       <c r="D346" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E346">
         <v>1.572471675023835</v>
@@ -18861,7 +18873,7 @@
         <v>1.471193121765403</v>
       </c>
       <c r="D347" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E347">
         <v>1.572471675023835</v>
@@ -18911,7 +18923,7 @@
         <v>2.306011000659936</v>
       </c>
       <c r="D348" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E348">
         <v>2.348379970519409</v>
@@ -18947,7 +18959,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18961,7 +18973,7 @@
         <v>2.400485390479259</v>
       </c>
       <c r="D349" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E349">
         <v>2.364696230398958</v>
@@ -18997,7 +19009,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19047,7 +19059,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19061,7 +19073,7 @@
         <v>2.315116384839492</v>
       </c>
       <c r="D351" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E351">
         <v>2.323814331699535</v>
@@ -19097,7 +19109,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19111,7 +19123,7 @@
         <v>2.158186337006185</v>
       </c>
       <c r="D352" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E352">
         <v>2.199105803820263</v>
@@ -19147,7 +19159,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19197,7 +19209,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19247,7 +19259,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19261,7 +19273,7 @@
         <v>2.249949180664442</v>
       </c>
       <c r="D355" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E355">
         <v>2.193589002935801</v>
@@ -19297,7 +19309,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19311,7 +19323,7 @@
         <v>3.29910210514231</v>
       </c>
       <c r="D356" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E356">
         <v>3.35230135785332</v>
@@ -19347,7 +19359,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19361,7 +19373,7 @@
         <v>3.804045197377832</v>
       </c>
       <c r="D357" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E357">
         <v>3.415154291605215</v>
@@ -19397,7 +19409,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19411,7 +19423,7 @@
         <v>3.427249571448392</v>
       </c>
       <c r="D358" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E358">
         <v>3.291626526785035</v>
@@ -19447,7 +19459,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19497,7 +19509,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19511,7 +19523,7 @@
         <v>3.442581197445604</v>
       </c>
       <c r="D360" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E360">
         <v>3.306414237004073</v>
@@ -19547,7 +19559,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19561,7 +19573,7 @@
         <v>3.36022431872702</v>
       </c>
       <c r="D361" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E361">
         <v>3.226979110080385</v>
@@ -19597,7 +19609,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19611,7 +19623,7 @@
         <v>3.251003700388559</v>
       </c>
       <c r="D362" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E362">
         <v>3.121633280862579</v>
@@ -19647,7 +19659,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19661,7 +19673,7 @@
         <v>2.99001278638902</v>
       </c>
       <c r="D363" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E363">
         <v>3.032275977245447</v>
@@ -19747,7 +19759,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19761,7 +19773,7 @@
         <v>2.786342722576059</v>
       </c>
       <c r="D365" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E365">
         <v>2.830017022419643</v>
@@ -19797,7 +19809,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19811,7 +19823,7 @@
         <v>2.881784622628198</v>
       </c>
       <c r="D366" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E366">
         <v>2.846342722576059</v>
@@ -19847,7 +19859,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19861,7 +19873,7 @@
         <v>2.713139299753176</v>
       </c>
       <c r="D367" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E367">
         <v>2.672915915531583</v>
@@ -19897,7 +19909,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19911,7 +19923,7 @@
         <v>2.722022378645214</v>
       </c>
       <c r="D368" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E368">
         <v>2.672915915531583</v>
@@ -19947,7 +19959,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19961,7 +19973,7 @@
         <v>2.643362683974768</v>
       </c>
       <c r="D369" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E369">
         <v>2.68802760764238</v>
@@ -19997,7 +20009,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20011,7 +20023,7 @@
         <v>2.738474376085565</v>
       </c>
       <c r="D370" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E370">
         <v>2.678250991863972</v>
@@ -20047,7 +20059,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20061,7 +20073,7 @@
         <v>2.26156876679942</v>
       </c>
       <c r="D371" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E371">
         <v>2.319500204055783</v>
@@ -20097,7 +20109,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20111,7 +20123,7 @@
         <v>2.341086491507057</v>
       </c>
       <c r="D372" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E372">
         <v>2.284741341701965</v>
@@ -20147,7 +20159,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20161,7 +20173,7 @@
         <v>2.25156876679942</v>
       </c>
       <c r="D373" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E373">
         <v>2.298948197976329</v>
@@ -20197,7 +20209,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20211,7 +20223,7 @@
         <v>2.345775623073784</v>
       </c>
       <c r="D374" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E374">
         <v>2.287361910525056</v>
@@ -20247,7 +20259,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20261,7 +20273,7 @@
         <v>1.450725995788351</v>
       </c>
       <c r="D375" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E375">
         <v>1.543612412630503</v>
@@ -20297,7 +20309,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20311,7 +20323,7 @@
         <v>1.378039753255653</v>
       </c>
       <c r="D376" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E376">
         <v>1.473954763536668</v>
@@ -20347,7 +20359,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20361,7 +20373,7 @@
         <v>2.300473418774809</v>
       </c>
       <c r="D377" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E377">
         <v>2.269274816103397</v>
@@ -20411,7 +20423,7 @@
         <v>2.307737312105645</v>
       </c>
       <c r="D378" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E378">
         <v>2.269274816103397</v>
@@ -20461,7 +20473,7 @@
         <v>2.548688372146674</v>
       </c>
       <c r="D379" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E379">
         <v>2.44021981851742</v>
@@ -20497,7 +20509,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20511,7 +20523,7 @@
         <v>4.064626779899114</v>
       </c>
       <c r="D380" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E380">
         <v>3.971827788774664</v>
@@ -20547,7 +20559,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20561,7 +20573,7 @@
         <v>2.704221825320051</v>
       </c>
       <c r="D381" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E381">
         <v>2.757514946748523</v>
@@ -20597,7 +20609,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20611,7 +20623,7 @@
         <v>2.699698304540886</v>
       </c>
       <c r="D382" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E382">
         <v>2.757514946748523</v>
@@ -20647,7 +20659,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20661,7 +20673,7 @@
         <v>2.597723564836138</v>
       </c>
       <c r="D383" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E383">
         <v>2.648687698460786</v>
@@ -20697,7 +20709,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20711,7 +20723,7 @@
         <v>2.594470401040876</v>
       </c>
       <c r="D384" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E384">
         <v>2.648687698460786</v>
@@ -20747,7 +20759,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20761,7 +20773,7 @@
         <v>2.5327482758737</v>
       </c>
       <c r="D385" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E385">
         <v>2.582291478725809</v>
@@ -20797,7 +20809,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20811,7 +20823,7 @@
         <v>2.530270165227095</v>
       </c>
       <c r="D386" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E386">
         <v>2.582291478725809</v>
@@ -20847,7 +20859,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20861,7 +20873,7 @@
         <v>2.615226386520305</v>
       </c>
       <c r="D387" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E387">
         <v>2.605226386520305</v>
@@ -20897,7 +20909,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20911,7 +20923,7 @@
         <v>2.519210324106</v>
       </c>
       <c r="D388" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E388">
         <v>2.474919909368535</v>
@@ -20947,7 +20959,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20961,7 +20973,7 @@
         <v>2.443973795685154</v>
       </c>
       <c r="D389" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E389">
         <v>2.491575608314453</v>
@@ -20997,7 +21009,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21011,7 +21023,7 @@
         <v>2.442554625160083</v>
       </c>
       <c r="D390" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E390">
         <v>2.491575608314453</v>
@@ -21047,7 +21059,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21097,7 +21109,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21111,7 +21123,7 @@
         <v>2.457705873063223</v>
       </c>
       <c r="D392" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E392">
         <v>2.413049360402885</v>
@@ -21147,7 +21159,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21161,7 +21173,7 @@
         <v>2.382591377283335</v>
       </c>
       <c r="D393" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E393">
         <v>2.428850830862097</v>
@@ -21197,7 +21209,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21211,7 +21223,7 @@
         <v>2.381904402604011</v>
       </c>
       <c r="D394" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E394">
         <v>2.428850830862097</v>
@@ -21247,7 +21259,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21261,7 +21273,7 @@
         <v>2.46327835196266</v>
       </c>
       <c r="D395" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E395">
         <v>2.453507343522435</v>
@@ -21297,7 +21309,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21311,7 +21323,7 @@
         <v>2.467705873063223</v>
       </c>
       <c r="D396" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E396">
         <v>2.453507343522435</v>
@@ -21347,7 +21359,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21361,7 +21373,7 @@
         <v>2.447999298642713</v>
       </c>
       <c r="D397" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E397">
         <v>2.403285008753682</v>
@@ -21397,7 +21409,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21411,7 +21423,7 @@
         <v>2.372904061939057</v>
       </c>
       <c r="D398" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E398">
         <v>2.418951665679276</v>
@@ -21447,7 +21459,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21461,7 +21473,7 @@
         <v>2.37233264171712</v>
       </c>
       <c r="D399" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E399">
         <v>2.418951665679276</v>
@@ -21497,7 +21509,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21547,7 +21559,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21597,7 +21609,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21611,7 +21623,7 @@
         <v>2.414261420787727</v>
       </c>
       <c r="D402" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E402">
         <v>2.369346310197177</v>
@@ -21647,7 +21659,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21697,7 +21709,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21747,7 +21759,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21761,7 +21773,7 @@
         <v>2.424261420787727</v>
       </c>
       <c r="D405" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E405">
         <v>2.394544385485897</v>
@@ -21797,7 +21809,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21811,7 +21823,7 @@
         <v>2.414374606666995</v>
       </c>
       <c r="D406" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E406">
         <v>2.394544385485897</v>
@@ -21847,7 +21859,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21861,7 +21873,7 @@
         <v>2.397600622679596</v>
       </c>
       <c r="D407" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E407">
         <v>2.352586340671736</v>
@@ -21897,7 +21909,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21911,7 +21923,7 @@
         <v>2.322605383348882</v>
       </c>
       <c r="D408" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E408">
         <v>2.367553015986731</v>
@@ -21947,7 +21959,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21961,7 +21973,7 @@
         <v>2.322633947364601</v>
       </c>
       <c r="D409" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E409">
         <v>2.367553015986731</v>
@@ -21997,7 +22009,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22011,7 +22023,7 @@
         <v>2.402576819333163</v>
       </c>
       <c r="D410" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E410">
         <v>2.35256729799459</v>
@@ -22047,7 +22059,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22061,7 +22073,7 @@
         <v>2.407600622679595</v>
       </c>
       <c r="D411" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E411">
         <v>2.35256729799459</v>
@@ -22097,7 +22109,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22111,7 +22123,7 @@
         <v>2.39758158000245</v>
       </c>
       <c r="D412" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E412">
         <v>2.35256729799459</v>
@@ -22147,7 +22159,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22161,7 +22173,7 @@
         <v>2.378737718650321</v>
       </c>
       <c r="D413" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E413">
         <v>2.33361115745181</v>
@@ -22197,7 +22209,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22211,7 +22223,7 @@
         <v>2.30377990571649</v>
       </c>
       <c r="D414" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E414">
         <v>2.348315847988621</v>
@@ -22247,7 +22259,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22261,7 +22273,7 @@
         <v>2.304033028113511</v>
       </c>
       <c r="D415" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E415">
         <v>2.348315847988621</v>
@@ -22297,7 +22309,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22311,7 +22323,7 @@
         <v>2.383526783319471</v>
       </c>
       <c r="D416" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E416">
         <v>2.333442409187131</v>
@@ -22347,7 +22359,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22361,7 +22373,7 @@
         <v>2.38873771865032</v>
       </c>
       <c r="D417" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E417">
         <v>2.333442409187131</v>
@@ -22397,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22411,7 +22423,7 @@
         <v>2.378568970385641</v>
       </c>
       <c r="D418" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E418">
         <v>2.333442409187131</v>
@@ -22447,7 +22459,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22461,7 +22473,7 @@
         <v>2.29477967980894</v>
       </c>
       <c r="D419" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E419">
         <v>2.33911879805526</v>
@@ -22511,7 +22523,7 @@
         <v>2.295140160765494</v>
       </c>
       <c r="D420" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E420">
         <v>2.33911879805526</v>
@@ -22561,7 +22573,7 @@
         <v>2.374419198852388</v>
       </c>
       <c r="D421" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E421">
         <v>2.324299038533536</v>
@@ -22611,7 +22623,7 @@
         <v>2.379719599649515</v>
       </c>
       <c r="D422" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E422">
         <v>2.324299038533536</v>
@@ -22661,7 +22673,7 @@
         <v>2.369479279011813</v>
       </c>
       <c r="D423" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E423">
         <v>2.324299038533536</v>
@@ -22711,7 +22723,7 @@
         <v>2.280590400920047</v>
       </c>
       <c r="D424" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E424">
         <v>2.324619216844741</v>
@@ -22747,7 +22759,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22761,7 +22773,7 @@
         <v>2.281120137688396</v>
       </c>
       <c r="D425" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E425">
         <v>2.324619216844741</v>
@@ -22797,7 +22809,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22811,7 +22823,7 @@
         <v>2.360060664151698</v>
       </c>
       <c r="D426" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E426">
         <v>2.309884085228915</v>
@@ -22847,7 +22859,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22897,7 +22909,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22911,7 +22923,7 @@
         <v>2.281700069738552</v>
       </c>
       <c r="D428" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E428">
         <v>2.325753152774585</v>
@@ -22947,7 +22959,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -22961,7 +22973,7 @@
         <v>2.282216569900716</v>
       </c>
       <c r="D429" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E429">
         <v>2.325753152774585</v>
@@ -22997,7 +23009,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23011,7 +23023,7 @@
         <v>2.361183569576388</v>
       </c>
       <c r="D430" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E430">
         <v>2.311011402855666</v>
@@ -23047,7 +23059,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23061,7 +23073,7 @@
         <v>2.255753152774584</v>
       </c>
       <c r="D431" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E431">
         <v>2.30032273597278</v>
@@ -23097,7 +23109,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23111,7 +23123,7 @@
         <v>2.248769782041177</v>
       </c>
       <c r="D432" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E432">
         <v>2.297801715354081</v>
@@ -23147,7 +23159,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23161,7 +23173,7 @@
         <v>2.343406757033516</v>
       </c>
       <c r="D433" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E433">
         <v>2.293164740361742</v>
@@ -23197,7 +23209,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23211,7 +23223,7 @@
         <v>2.237801715354081</v>
       </c>
       <c r="D434" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E434">
         <v>2.26243869034642</v>
@@ -23247,7 +23259,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23261,7 +23273,7 @@
         <v>2.228095614122554</v>
       </c>
       <c r="D435" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E435">
         <v>2.276800683120539</v>
@@ -23297,7 +23309,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23311,7 +23323,7 @@
         <v>2.322610014996799</v>
       </c>
       <c r="D436" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E436">
         <v>2.263257480497806</v>
@@ -23347,7 +23359,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23397,7 +23409,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23411,7 +23423,7 @@
         <v>2.224983216186275</v>
       </c>
       <c r="D438" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E438">
         <v>2.273639077311749</v>
@@ -23461,7 +23473,7 @@
         <v>2.319479164108328</v>
       </c>
       <c r="D439" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E439">
         <v>2.26015123354559</v>
@@ -23611,7 +23623,7 @@
         <v>2.3116287572162</v>
       </c>
       <c r="D442" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E442">
         <v>2.252362519438469</v>
@@ -23647,7 +23659,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23697,7 +23709,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23747,7 +23759,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23811,7 +23823,7 @@
         <v>2.185149484739352</v>
       </c>
       <c r="D446" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E446">
         <v>2.165149484739352</v>
@@ -23911,7 +23923,7 @@
         <v>2.20020073233055</v>
       </c>
       <c r="D448" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E448">
         <v>2.205687152603988</v>
@@ -23997,7 +24009,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24047,7 +24059,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24097,7 +24109,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24147,7 +24159,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24197,7 +24209,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24311,7 +24323,7 @@
         <v>2.142114930387524</v>
       </c>
       <c r="D456" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E456">
         <v>2.162114930387524</v>
@@ -24347,7 +24359,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24361,7 +24373,7 @@
         <v>2.115413806995409</v>
       </c>
       <c r="D457" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E457">
         <v>2.141244762127619</v>
@@ -24447,7 +24459,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24461,7 +24473,7 @@
         <v>2.073994682974101</v>
       </c>
       <c r="D459" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E459">
         <v>2.082201671198685</v>
@@ -24511,7 +24523,7 @@
         <v>2.083994682974101</v>
       </c>
       <c r="D460" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E460">
         <v>2.082201671198685</v>
@@ -24597,7 +24609,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24611,7 +24623,7 @@
         <v>2.057461365020192</v>
       </c>
       <c r="D462" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E462">
         <v>2.066125824243982</v>
@@ -24647,7 +24659,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24697,7 +24709,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24747,7 +24759,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24797,7 +24809,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24847,7 +24859,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24861,7 +24873,7 @@
         <v>2.057577737614682</v>
       </c>
       <c r="D467" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E467">
         <v>2.099815205781953</v>
@@ -24897,7 +24909,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24961,7 +24973,7 @@
         <v>2.075267052489131</v>
       </c>
       <c r="D469" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E469">
         <v>2.105974841560053</v>
@@ -25011,7 +25023,7 @@
         <v>2.0673904197019</v>
       </c>
       <c r="D470" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E470">
         <v>2.109513786914668</v>
@@ -25061,7 +25073,7 @@
         <v>2.101281730695467</v>
       </c>
       <c r="D471" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E471">
         <v>2.131889846669813</v>
@@ -25111,7 +25123,7 @@
         <v>2.093106078618507</v>
       </c>
       <c r="D472" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E472">
         <v>2.134930426541548</v>
@@ -25161,7 +25173,7 @@
         <v>2.114232378900782</v>
       </c>
       <c r="D473" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="E473">
         <v>2.144790875533345</v>
@@ -25197,7 +25209,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25211,7 +25223,7 @@
         <v>2.164790875533345</v>
       </c>
       <c r="D474" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E474">
         <v>2.134232378900781</v>
@@ -25247,7 +25259,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25261,7 +25273,7 @@
         <v>2.105907868798473</v>
       </c>
       <c r="D475" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E475">
         <v>2.147583358696166</v>
@@ -25297,7 +25309,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25311,7 +25323,7 @@
         <v>2.178667208693582</v>
       </c>
       <c r="D476" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E476">
         <v>2.148162082573172</v>
@@ -25347,7 +25359,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25361,7 +25373,7 @@
         <v>2.119677460934401</v>
       </c>
       <c r="D477" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E477">
         <v>2.161192839295628</v>
@@ -25397,7 +25409,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25411,7 +25423,7 @@
         <v>2.191253934723685</v>
       </c>
       <c r="D478" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E478">
         <v>2.160797219088007</v>
@@ -25461,7 +25473,7 @@
         <v>2.132167365995042</v>
       </c>
       <c r="D479" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E479">
         <v>2.173537512902076</v>
@@ -25561,7 +25573,7 @@
         <v>2.161339958759847</v>
       </c>
       <c r="D481" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E481">
         <v>2.202370889471942</v>
@@ -25611,7 +25623,7 @@
         <v>2.215480849833102</v>
       </c>
       <c r="D482" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E482">
         <v>2.179965384477054</v>
@@ -25661,7 +25673,7 @@
         <v>1.276065947508897</v>
       </c>
       <c r="D483" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E483">
         <v>1.317566169928825</v>
@@ -25697,7 +25709,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25711,7 +25723,7 @@
         <v>1.37689891014235</v>
       </c>
       <c r="D484" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E484">
         <v>1.288399132562277</v>
@@ -25747,7 +25759,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25761,7 +25773,7 @@
         <v>1.265250934212467</v>
       </c>
       <c r="D485" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E485">
         <v>1.306889515011455</v>
@@ -25797,7 +25809,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25811,7 +25823,7 @@
         <v>1.365853299547489</v>
       </c>
       <c r="D486" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E486">
         <v>1.277491880346475</v>
@@ -25847,7 +25859,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25861,7 +25873,7 @@
         <v>1.365250934212467</v>
       </c>
       <c r="D487" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E487">
         <v>1.29891353608099</v>
@@ -25897,7 +25909,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25911,7 +25923,7 @@
         <v>1.335853299547488</v>
       </c>
       <c r="D488" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E488">
         <v>1.29891353608099</v>
@@ -25947,7 +25959,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25961,7 +25973,7 @@
         <v>1.257848770795328</v>
       </c>
       <c r="D489" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E489">
         <v>1.29958204878089</v>
@@ -25997,7 +26009,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26011,7 +26023,7 @@
         <v>1.358293307486061</v>
       </c>
       <c r="D490" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E490">
         <v>1.270026585471621</v>
@@ -26047,7 +26059,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26061,7 +26073,7 @@
         <v>1.328293307486061</v>
       </c>
       <c r="D491" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E491">
         <v>1.291337761155134</v>
@@ -26097,7 +26109,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26111,7 +26123,7 @@
         <v>1.336383675279734</v>
       </c>
       <c r="D492" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E492">
         <v>1.248391395422367</v>
@@ -26161,7 +26173,7 @@
         <v>1.306383675279734</v>
       </c>
       <c r="D493" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E493">
         <v>1.269382388589295</v>
@@ -26211,7 +26223,7 @@
         <v>1.1949083591831</v>
       </c>
       <c r="D494" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E494">
         <v>1.223388801502731</v>
@@ -26247,7 +26259,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26261,7 +26273,7 @@
         <v>1.279467032224208</v>
       </c>
       <c r="D495" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E495">
         <v>1.192187695703653</v>
@@ -26297,7 +26309,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26311,7 +26323,7 @@
         <v>1.249467032224208</v>
       </c>
       <c r="D496" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E496">
         <v>1.2123469216443</v>
@@ -26347,7 +26359,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26355,99 +26367,449 @@
         <v>0</v>
       </c>
       <c r="B497" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C497">
-        <v>1.061287302238483</v>
+        <v>1.24514956586386</v>
       </c>
       <c r="D497" t="s">
         <v>275</v>
       </c>
       <c r="E497">
-        <v>1.023774332097018</v>
+        <v>1.158300093222558</v>
       </c>
       <c r="F497">
         <v>-1</v>
       </c>
       <c r="G497">
-        <v>0.008258712697761517</v>
+        <v>0.008134850434136141</v>
       </c>
       <c r="H497">
-        <v>0.008236225667902983</v>
+        <v>0.007961699906777442</v>
       </c>
       <c r="I497">
-        <v>0.03751297014146449</v>
+        <v>0.08684947264130205</v>
       </c>
       <c r="J497">
-        <v>0.7512970141464546</v>
+        <v>0.7191754559783174</v>
       </c>
       <c r="K497">
         <v>4.79</v>
       </c>
       <c r="L497">
-        <v>4.66</v>
+        <v>4.69</v>
       </c>
       <c r="M497">
-        <v>4.8</v>
+        <v>4.73</v>
       </c>
       <c r="N497">
-        <v>4.63</v>
+        <v>4.56</v>
       </c>
       <c r="O497">
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>274</v>
+        <v>150</v>
       </c>
     </row>
     <row r="498" spans="1:16">
       <c r="A498" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B498" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C498">
-        <v>1.049221706841676</v>
+        <v>1.21514956586386</v>
       </c>
       <c r="D498" t="s">
         <v>276</v>
       </c>
       <c r="E498">
-        <v>1.016747983025339</v>
+        <v>1.177957811304076</v>
       </c>
       <c r="F498">
         <v>-1</v>
       </c>
       <c r="G498">
-        <v>0.008270778293158325</v>
+        <v>0.00810485043413614</v>
       </c>
       <c r="H498">
-        <v>0.008283252016974661</v>
+        <v>0.008082042188695925</v>
       </c>
       <c r="I498">
-        <v>0.03247372381633751</v>
+        <v>0.03719175455978352</v>
       </c>
       <c r="J498">
-        <v>0.7491241272112704</v>
+        <v>0.7191754559783174</v>
       </c>
       <c r="K498">
-        <v>4.82</v>
+        <v>4.79</v>
       </c>
       <c r="L498">
         <v>4.66</v>
       </c>
       <c r="M498">
+        <v>4.8</v>
+      </c>
+      <c r="N498">
+        <v>4.63</v>
+      </c>
+      <c r="O498">
+        <v>1</v>
+      </c>
+      <c r="P498" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="499" spans="1:16">
+      <c r="A499" s="1">
+        <v>0</v>
+      </c>
+      <c r="B499" t="s">
+        <v>147</v>
+      </c>
+      <c r="C499">
+        <v>1.226637749198502</v>
+      </c>
+      <c r="D499" t="s">
+        <v>275</v>
+      </c>
+      <c r="E499">
+        <v>1.140020157350503</v>
+      </c>
+      <c r="F499">
+        <v>-1</v>
+      </c>
+      <c r="G499">
+        <v>0.008153362250801498</v>
+      </c>
+      <c r="H499">
+        <v>0.007979979842649497</v>
+      </c>
+      <c r="I499">
+        <v>0.086617591847999</v>
+      </c>
+      <c r="J499">
+        <v>0.7230401358667011</v>
+      </c>
+      <c r="K499">
+        <v>4.79</v>
+      </c>
+      <c r="L499">
+        <v>4.69</v>
+      </c>
+      <c r="M499">
+        <v>4.73</v>
+      </c>
+      <c r="N499">
+        <v>4.56</v>
+      </c>
+      <c r="O499">
+        <v>1</v>
+      </c>
+      <c r="P499" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="500" spans="1:16">
+      <c r="A500" s="1">
+        <v>0</v>
+      </c>
+      <c r="B500" t="s">
+        <v>147</v>
+      </c>
+      <c r="C500">
+        <v>1.183891513054156</v>
+      </c>
+      <c r="D500" t="s">
+        <v>275</v>
+      </c>
+      <c r="E500">
+        <v>1.097809364665167</v>
+      </c>
+      <c r="F500">
+        <v>-1</v>
+      </c>
+      <c r="G500">
+        <v>0.008196108486945847</v>
+      </c>
+      <c r="H500">
+        <v>0.008022190635334832</v>
+      </c>
+      <c r="I500">
+        <v>0.08608214838898842</v>
+      </c>
+      <c r="J500">
+        <v>0.7319641935168778</v>
+      </c>
+      <c r="K500">
+        <v>4.79</v>
+      </c>
+      <c r="L500">
+        <v>4.69</v>
+      </c>
+      <c r="M500">
+        <v>4.73</v>
+      </c>
+      <c r="N500">
+        <v>4.56</v>
+      </c>
+      <c r="O500">
+        <v>1</v>
+      </c>
+      <c r="P500" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="501" spans="1:16">
+      <c r="A501" s="1">
+        <v>0</v>
+      </c>
+      <c r="B501" t="s">
+        <v>149</v>
+      </c>
+      <c r="C501">
+        <v>1.061287302238483</v>
+      </c>
+      <c r="D501" t="s">
+        <v>276</v>
+      </c>
+      <c r="E501">
+        <v>1.023774332097018</v>
+      </c>
+      <c r="F501">
+        <v>-1</v>
+      </c>
+      <c r="G501">
+        <v>0.008258712697761517</v>
+      </c>
+      <c r="H501">
+        <v>0.008236225667902983</v>
+      </c>
+      <c r="I501">
+        <v>0.03751297014146449</v>
+      </c>
+      <c r="J501">
+        <v>0.7512970141464546</v>
+      </c>
+      <c r="K501">
+        <v>4.79</v>
+      </c>
+      <c r="L501">
+        <v>4.66</v>
+      </c>
+      <c r="M501">
+        <v>4.8</v>
+      </c>
+      <c r="N501">
+        <v>4.63</v>
+      </c>
+      <c r="O501">
+        <v>1</v>
+      </c>
+      <c r="P501" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="502" spans="1:16">
+      <c r="A502" s="1">
+        <v>0</v>
+      </c>
+      <c r="B502" t="s">
+        <v>149</v>
+      </c>
+      <c r="C502">
+        <v>0.9405281118670676</v>
+      </c>
+      <c r="D502" t="s">
+        <v>276</v>
+      </c>
+      <c r="E502">
+        <v>0.9027630348563518</v>
+      </c>
+      <c r="F502">
+        <v>-1</v>
+      </c>
+      <c r="G502">
+        <v>0.008379471888132933</v>
+      </c>
+      <c r="H502">
+        <v>0.00835723696514365</v>
+      </c>
+      <c r="I502">
+        <v>0.03776507701071585</v>
+      </c>
+      <c r="J502">
+        <v>0.7765077010715934</v>
+      </c>
+      <c r="K502">
+        <v>4.79</v>
+      </c>
+      <c r="L502">
+        <v>4.66</v>
+      </c>
+      <c r="M502">
+        <v>4.8</v>
+      </c>
+      <c r="N502">
+        <v>4.63</v>
+      </c>
+      <c r="O502">
+        <v>1</v>
+      </c>
+      <c r="P502" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="503" spans="1:16">
+      <c r="A503" s="1">
+        <v>0</v>
+      </c>
+      <c r="B503" t="s">
+        <v>151</v>
+      </c>
+      <c r="C503">
+        <v>0.746167021374426</v>
+      </c>
+      <c r="D503" t="s">
+        <v>277</v>
+      </c>
+      <c r="E503">
+        <v>0.7503144418607692</v>
+      </c>
+      <c r="F503">
+        <v>1</v>
+      </c>
+      <c r="G503">
+        <v>0.008553832978625575</v>
+      </c>
+      <c r="H503">
+        <v>0.00850968555813923</v>
+      </c>
+      <c r="I503">
+        <v>0.004147420486343201</v>
+      </c>
+      <c r="J503">
+        <v>0.8049140162114586</v>
+      </c>
+      <c r="K503">
         <v>4.85</v>
       </c>
-      <c r="N498">
+      <c r="L503">
         <v>4.65</v>
       </c>
-      <c r="O498">
-        <v>1</v>
-      </c>
-      <c r="P498" t="s">
-        <v>275</v>
+      <c r="M503">
+        <v>4.82</v>
+      </c>
+      <c r="N503">
+        <v>4.63</v>
+      </c>
+      <c r="O503">
+        <v>1</v>
+      </c>
+      <c r="P503" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="504" spans="1:16">
+      <c r="A504" s="1">
+        <v>0</v>
+      </c>
+      <c r="B504" t="s">
+        <v>151</v>
+      </c>
+      <c r="C504">
+        <v>0.5224815208071796</v>
+      </c>
+      <c r="D504" t="s">
+        <v>277</v>
+      </c>
+      <c r="E504">
+        <v>0.5280125629465156</v>
+      </c>
+      <c r="F504">
+        <v>1</v>
+      </c>
+      <c r="G504">
+        <v>0.008777518479192821</v>
+      </c>
+      <c r="H504">
+        <v>0.008731987437053484</v>
+      </c>
+      <c r="I504">
+        <v>0.005531042139335973</v>
+      </c>
+      <c r="J504">
+        <v>0.8510347379779013</v>
+      </c>
+      <c r="K504">
+        <v>4.85</v>
+      </c>
+      <c r="L504">
+        <v>4.65</v>
+      </c>
+      <c r="M504">
+        <v>4.82</v>
+      </c>
+      <c r="N504">
+        <v>4.63</v>
+      </c>
+      <c r="O504">
+        <v>1</v>
+      </c>
+      <c r="P504" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="505" spans="1:16">
+      <c r="A505" s="1">
+        <v>0</v>
+      </c>
+      <c r="B505" t="s">
+        <v>152</v>
+      </c>
+      <c r="C505">
+        <v>1.049221706841676</v>
+      </c>
+      <c r="D505" t="s">
+        <v>151</v>
+      </c>
+      <c r="E505">
+        <v>1.016747983025339</v>
+      </c>
+      <c r="F505">
+        <v>-1</v>
+      </c>
+      <c r="G505">
+        <v>0.008270778293158325</v>
+      </c>
+      <c r="H505">
+        <v>0.008283252016974661</v>
+      </c>
+      <c r="I505">
+        <v>0.03247372381633751</v>
+      </c>
+      <c r="J505">
+        <v>0.7491241272112704</v>
+      </c>
+      <c r="K505">
+        <v>4.82</v>
+      </c>
+      <c r="L505">
+        <v>4.66</v>
+      </c>
+      <c r="M505">
+        <v>4.85</v>
+      </c>
+      <c r="N505">
+        <v>4.65</v>
+      </c>
+      <c r="O505">
+        <v>1</v>
+      </c>
+      <c r="P505" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-03328-601328.xlsx
+++ b/s60_signal/position-03328-601328.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1527" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="399">
   <si>
     <t>trade_time</t>
   </si>
@@ -466,736 +466,742 @@
     <t>2021-11-11</t>
   </si>
   <si>
+    <t>2021-11-19</t>
+  </si>
+  <si>
+    <t>2021-11-15</t>
+  </si>
+  <si>
+    <t>2016-05-31</t>
+  </si>
+  <si>
+    <t>2016-06-07</t>
+  </si>
+  <si>
+    <t>2016-06-13</t>
+  </si>
+  <si>
+    <t>2016-06-28</t>
+  </si>
+  <si>
+    <t>2016-06-14</t>
+  </si>
+  <si>
+    <t>2016-06-29</t>
+  </si>
+  <si>
+    <t>2016-07-06</t>
+  </si>
+  <si>
+    <t>2016-07-07</t>
+  </si>
+  <si>
+    <t>2016-07-08</t>
+  </si>
+  <si>
+    <t>2016-07-11</t>
+  </si>
+  <si>
+    <t>2016-07-13</t>
+  </si>
+  <si>
+    <t>2016-07-15</t>
+  </si>
+  <si>
+    <t>2016-07-18</t>
+  </si>
+  <si>
+    <t>2016-07-19</t>
+  </si>
+  <si>
+    <t>2016-07-20</t>
+  </si>
+  <si>
+    <t>2016-07-21</t>
+  </si>
+  <si>
+    <t>2016-07-25</t>
+  </si>
+  <si>
+    <t>2016-07-27</t>
+  </si>
+  <si>
+    <t>2016-07-29</t>
+  </si>
+  <si>
+    <t>2016-12-15</t>
+  </si>
+  <si>
+    <t>2017-01-03</t>
+  </si>
+  <si>
+    <t>2017-02-14</t>
+  </si>
+  <si>
+    <t>2017-02-15</t>
+  </si>
+  <si>
+    <t>2017-03-02</t>
+  </si>
+  <si>
+    <t>2017-04-18</t>
+  </si>
+  <si>
+    <t>2017-04-26</t>
+  </si>
+  <si>
+    <t>2017-04-27</t>
+  </si>
+  <si>
+    <t>2017-05-04</t>
+  </si>
+  <si>
+    <t>2017-05-05</t>
+  </si>
+  <si>
+    <t>2017-05-09</t>
+  </si>
+  <si>
+    <t>2017-05-12</t>
+  </si>
+  <si>
+    <t>2017-06-02</t>
+  </si>
+  <si>
+    <t>2017-06-06</t>
+  </si>
+  <si>
+    <t>2017-06-08</t>
+  </si>
+  <si>
+    <t>2017-06-14</t>
+  </si>
+  <si>
+    <t>2017-06-22</t>
+  </si>
+  <si>
+    <t>2017-06-23</t>
+  </si>
+  <si>
+    <t>2017-06-20</t>
+  </si>
+  <si>
+    <t>2017-06-29</t>
+  </si>
+  <si>
+    <t>2017-07-03</t>
+  </si>
+  <si>
+    <t>2017-07-04</t>
+  </si>
+  <si>
+    <t>2017-07-05</t>
+  </si>
+  <si>
+    <t>2017-07-06</t>
+  </si>
+  <si>
+    <t>2017-10-12</t>
+  </si>
+  <si>
+    <t>2017-10-19</t>
+  </si>
+  <si>
+    <t>2017-10-26</t>
+  </si>
+  <si>
+    <t>2017-10-31</t>
+  </si>
+  <si>
+    <t>2018-03-15</t>
+  </si>
+  <si>
+    <t>2018-06-05</t>
+  </si>
+  <si>
+    <t>2018-06-08</t>
+  </si>
+  <si>
+    <t>2018-05-16</t>
+  </si>
+  <si>
+    <t>2018-06-13</t>
+  </si>
+  <si>
+    <t>2018-06-14</t>
+  </si>
+  <si>
+    <t>2018-06-19</t>
+  </si>
+  <si>
+    <t>2018-06-29</t>
+  </si>
+  <si>
+    <t>2018-07-12</t>
+  </si>
+  <si>
+    <t>2018-07-04</t>
+  </si>
+  <si>
+    <t>2018-07-13</t>
+  </si>
+  <si>
+    <t>2018-07-16</t>
+  </si>
+  <si>
+    <t>2018-07-18</t>
+  </si>
+  <si>
+    <t>2018-11-05</t>
+  </si>
+  <si>
+    <t>2018-11-15</t>
+  </si>
+  <si>
+    <t>2018-11-19</t>
+  </si>
+  <si>
+    <t>2018-11-07</t>
+  </si>
+  <si>
+    <t>2018-11-21</t>
+  </si>
+  <si>
+    <t>2018-11-22</t>
+  </si>
+  <si>
+    <t>2018-11-27</t>
+  </si>
+  <si>
+    <t>2018-12-03</t>
+  </si>
+  <si>
+    <t>2018-12-04</t>
+  </si>
+  <si>
+    <t>2018-12-10</t>
+  </si>
+  <si>
+    <t>2018-12-11</t>
+  </si>
+  <si>
+    <t>2019-05-09</t>
+  </si>
+  <si>
+    <t>2019-05-27</t>
+  </si>
+  <si>
+    <t>2019-05-30</t>
+  </si>
+  <si>
+    <t>2019-06-25</t>
+  </si>
+  <si>
+    <t>2019-07-04</t>
+  </si>
+  <si>
+    <t>2019-07-08</t>
+  </si>
+  <si>
+    <t>2019-07-09</t>
+  </si>
+  <si>
+    <t>2019-07-15</t>
+  </si>
+  <si>
+    <t>2019-07-16</t>
+  </si>
+  <si>
+    <t>2019-07-17</t>
+  </si>
+  <si>
+    <t>2019-07-18</t>
+  </si>
+  <si>
+    <t>2019-07-22</t>
+  </si>
+  <si>
+    <t>2019-07-23</t>
+  </si>
+  <si>
+    <t>2019-07-24</t>
+  </si>
+  <si>
+    <t>2019-07-25</t>
+  </si>
+  <si>
+    <t>2019-09-19</t>
+  </si>
+  <si>
+    <t>2019-09-23</t>
+  </si>
+  <si>
+    <t>2019-09-27</t>
+  </si>
+  <si>
+    <t>2019-09-06</t>
+  </si>
+  <si>
+    <t>2019-09-30</t>
+  </si>
+  <si>
+    <t>2019-11-25</t>
+  </si>
+  <si>
+    <t>2020-07-14</t>
+  </si>
+  <si>
+    <t>2020-07-24</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>2020-08-18</t>
+  </si>
+  <si>
+    <t>2020-08-12</t>
+  </si>
+  <si>
+    <t>2020-08-19</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>2020-12-08</t>
+  </si>
+  <si>
+    <t>2020-12-09</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>2021-05-10</t>
+  </si>
+  <si>
+    <t>2021-05-12</t>
+  </si>
+  <si>
+    <t>2021-04-22</t>
+  </si>
+  <si>
+    <t>2021-05-14</t>
+  </si>
+  <si>
+    <t>2021-05-18</t>
+  </si>
+  <si>
+    <t>2021-05-20</t>
+  </si>
+  <si>
+    <t>2021-05-26</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>2021-05-27</t>
+  </si>
+  <si>
+    <t>2021-05-21</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>2021-06-10</t>
+  </si>
+  <si>
+    <t>2021-06-15</t>
+  </si>
+  <si>
+    <t>2021-06-16</t>
+  </si>
+  <si>
+    <t>2021-06-18</t>
+  </si>
+  <si>
+    <t>2021-06-28</t>
+  </si>
+  <si>
+    <t>2021-10-29</t>
+  </si>
+  <si>
+    <t>2021-11-02</t>
+  </si>
+  <si>
+    <t>2021-11-12</t>
+  </si>
+  <si>
+    <t>2021-11-22</t>
+  </si>
+  <si>
+    <t>2021-11-23</t>
+  </si>
+  <si>
+    <t>2021-11-16</t>
+  </si>
+  <si>
+    <t>2016-05-24</t>
+  </si>
+  <si>
+    <t>2016-05-26</t>
+  </si>
+  <si>
+    <t>2016-05-27</t>
+  </si>
+  <si>
+    <t>2016-05-30</t>
+  </si>
+  <si>
+    <t>2016-06-01</t>
+  </si>
+  <si>
+    <t>2016-06-02</t>
+  </si>
+  <si>
+    <t>2016-06-06</t>
+  </si>
+  <si>
+    <t>2016-06-15</t>
+  </si>
+  <si>
+    <t>2016-06-16</t>
+  </si>
+  <si>
+    <t>2016-06-17</t>
+  </si>
+  <si>
+    <t>2016-06-20</t>
+  </si>
+  <si>
+    <t>2016-06-21</t>
+  </si>
+  <si>
+    <t>2016-06-23</t>
+  </si>
+  <si>
+    <t>2016-06-24</t>
+  </si>
+  <si>
+    <t>2016-06-27</t>
+  </si>
+  <si>
+    <t>2016-06-30</t>
+  </si>
+  <si>
+    <t>2016-12-06</t>
+  </si>
+  <si>
+    <t>2016-12-07</t>
+  </si>
+  <si>
+    <t>2016-12-08</t>
+  </si>
+  <si>
+    <t>2016-12-14</t>
+  </si>
+  <si>
+    <t>2017-01-06</t>
+  </si>
+  <si>
+    <t>2017-01-09</t>
+  </si>
+  <si>
+    <t>2017-01-11</t>
+  </si>
+  <si>
+    <t>2017-01-12</t>
+  </si>
+  <si>
+    <t>2017-02-03</t>
+  </si>
+  <si>
+    <t>2017-03-24</t>
+  </si>
+  <si>
+    <t>2017-03-27</t>
+  </si>
+  <si>
+    <t>2017-03-29</t>
+  </si>
+  <si>
+    <t>2017-03-30</t>
+  </si>
+  <si>
+    <t>2017-03-31</t>
+  </si>
+  <si>
+    <t>2017-04-06</t>
+  </si>
+  <si>
+    <t>2017-04-07</t>
+  </si>
+  <si>
+    <t>2017-04-10</t>
+  </si>
+  <si>
+    <t>2017-04-11</t>
+  </si>
+  <si>
+    <t>2017-04-12</t>
+  </si>
+  <si>
+    <t>2017-04-13</t>
+  </si>
+  <si>
+    <t>2017-04-19</t>
+  </si>
+  <si>
+    <t>2017-04-21</t>
+  </si>
+  <si>
+    <t>2017-04-28</t>
+  </si>
+  <si>
+    <t>2017-05-11</t>
+  </si>
+  <si>
+    <t>2017-05-15</t>
+  </si>
+  <si>
+    <t>2017-05-18</t>
+  </si>
+  <si>
+    <t>2017-05-19</t>
+  </si>
+  <si>
+    <t>2017-05-22</t>
+  </si>
+  <si>
+    <t>2017-10-09</t>
+  </si>
+  <si>
+    <t>2017-10-11</t>
+  </si>
+  <si>
+    <t>2018-02-09</t>
+  </si>
+  <si>
+    <t>2018-05-07</t>
+  </si>
+  <si>
+    <t>2018-05-08</t>
+  </si>
+  <si>
+    <t>2018-05-09</t>
+  </si>
+  <si>
+    <t>2018-05-10</t>
+  </si>
+  <si>
+    <t>2018-05-11</t>
+  </si>
+  <si>
+    <t>2018-05-14</t>
+  </si>
+  <si>
+    <t>2018-05-17</t>
+  </si>
+  <si>
+    <t>2018-05-25</t>
+  </si>
+  <si>
+    <t>2018-05-30</t>
+  </si>
+  <si>
+    <t>2018-05-31</t>
+  </si>
+  <si>
+    <t>2018-06-15</t>
+  </si>
+  <si>
+    <t>2018-06-20</t>
+  </si>
+  <si>
+    <t>2018-06-21</t>
+  </si>
+  <si>
+    <t>2018-06-25</t>
+  </si>
+  <si>
+    <t>2018-10-19</t>
+  </si>
+  <si>
+    <t>2018-10-22</t>
+  </si>
+  <si>
+    <t>2018-10-23</t>
+  </si>
+  <si>
+    <t>2018-10-26</t>
+  </si>
+  <si>
+    <t>2018-10-29</t>
+  </si>
+  <si>
+    <t>2018-10-31</t>
+  </si>
+  <si>
+    <t>2018-11-13</t>
+  </si>
+  <si>
+    <t>2019-04-23</t>
+  </si>
+  <si>
+    <t>2019-04-24</t>
+  </si>
+  <si>
+    <t>2019-05-14</t>
+  </si>
+  <si>
+    <t>2019-05-15</t>
+  </si>
+  <si>
+    <t>2019-05-16</t>
+  </si>
+  <si>
+    <t>2019-06-05</t>
+  </si>
+  <si>
+    <t>2019-06-10</t>
+  </si>
+  <si>
+    <t>2019-06-12</t>
+  </si>
+  <si>
+    <t>2019-06-13</t>
+  </si>
+  <si>
+    <t>2019-06-14</t>
+  </si>
+  <si>
+    <t>2019-06-17</t>
+  </si>
+  <si>
+    <t>2019-06-18</t>
+  </si>
+  <si>
+    <t>2019-06-20</t>
+  </si>
+  <si>
+    <t>2019-06-26</t>
+  </si>
+  <si>
+    <t>2019-08-26</t>
+  </si>
+  <si>
+    <t>2019-08-27</t>
+  </si>
+  <si>
+    <t>2019-08-30</t>
+  </si>
+  <si>
+    <t>2019-09-02</t>
+  </si>
+  <si>
+    <t>2019-11-05</t>
+  </si>
+  <si>
+    <t>2020-06-15</t>
+  </si>
+  <si>
+    <t>2020-07-15</t>
+  </si>
+  <si>
+    <t>2020-07-16</t>
+  </si>
+  <si>
+    <t>2020-07-17</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>2020-07-22</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>2020-11-03</t>
+  </si>
+  <si>
+    <t>2020-11-04</t>
+  </si>
+  <si>
+    <t>2020-11-12</t>
+  </si>
+  <si>
+    <t>2021-03-02</t>
+  </si>
+  <si>
+    <t>2021-04-08</t>
+  </si>
+  <si>
+    <t>2021-04-09</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>2021-04-13</t>
+  </si>
+  <si>
+    <t>2021-04-14</t>
+  </si>
+  <si>
+    <t>2021-04-15</t>
+  </si>
+  <si>
+    <t>2021-04-16</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>2021-04-20</t>
+  </si>
+  <si>
+    <t>2021-04-23</t>
+  </si>
+  <si>
+    <t>2021-04-26</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>2021-04-29</t>
+  </si>
+  <si>
+    <t>2021-10-15</t>
+  </si>
+  <si>
+    <t>2021-10-18</t>
+  </si>
+  <si>
+    <t>2021-10-19</t>
+  </si>
+  <si>
+    <t>2021-10-26</t>
+  </si>
+  <si>
     <t>2021-10-27</t>
-  </si>
-  <si>
-    <t>2021-11-16</t>
-  </si>
-  <si>
-    <t>2021-11-15</t>
-  </si>
-  <si>
-    <t>2016-05-31</t>
-  </si>
-  <si>
-    <t>2016-06-07</t>
-  </si>
-  <si>
-    <t>2016-06-13</t>
-  </si>
-  <si>
-    <t>2016-06-28</t>
-  </si>
-  <si>
-    <t>2016-06-14</t>
-  </si>
-  <si>
-    <t>2016-06-29</t>
-  </si>
-  <si>
-    <t>2016-07-06</t>
-  </si>
-  <si>
-    <t>2016-07-07</t>
-  </si>
-  <si>
-    <t>2016-07-08</t>
-  </si>
-  <si>
-    <t>2016-07-11</t>
-  </si>
-  <si>
-    <t>2016-07-13</t>
-  </si>
-  <si>
-    <t>2016-07-15</t>
-  </si>
-  <si>
-    <t>2016-07-18</t>
-  </si>
-  <si>
-    <t>2016-07-19</t>
-  </si>
-  <si>
-    <t>2016-07-20</t>
-  </si>
-  <si>
-    <t>2016-07-21</t>
-  </si>
-  <si>
-    <t>2016-07-25</t>
-  </si>
-  <si>
-    <t>2016-07-27</t>
-  </si>
-  <si>
-    <t>2016-07-29</t>
-  </si>
-  <si>
-    <t>2016-12-15</t>
-  </si>
-  <si>
-    <t>2017-01-03</t>
-  </si>
-  <si>
-    <t>2017-02-14</t>
-  </si>
-  <si>
-    <t>2017-02-15</t>
-  </si>
-  <si>
-    <t>2017-03-02</t>
-  </si>
-  <si>
-    <t>2017-04-18</t>
-  </si>
-  <si>
-    <t>2017-04-26</t>
-  </si>
-  <si>
-    <t>2017-04-27</t>
-  </si>
-  <si>
-    <t>2017-05-04</t>
-  </si>
-  <si>
-    <t>2017-05-05</t>
-  </si>
-  <si>
-    <t>2017-05-09</t>
-  </si>
-  <si>
-    <t>2017-05-12</t>
-  </si>
-  <si>
-    <t>2017-06-02</t>
-  </si>
-  <si>
-    <t>2017-06-06</t>
-  </si>
-  <si>
-    <t>2017-06-08</t>
-  </si>
-  <si>
-    <t>2017-06-14</t>
-  </si>
-  <si>
-    <t>2017-06-22</t>
-  </si>
-  <si>
-    <t>2017-06-23</t>
-  </si>
-  <si>
-    <t>2017-06-20</t>
-  </si>
-  <si>
-    <t>2017-06-29</t>
-  </si>
-  <si>
-    <t>2017-07-03</t>
-  </si>
-  <si>
-    <t>2017-07-04</t>
-  </si>
-  <si>
-    <t>2017-07-05</t>
-  </si>
-  <si>
-    <t>2017-07-06</t>
-  </si>
-  <si>
-    <t>2017-10-12</t>
-  </si>
-  <si>
-    <t>2017-10-19</t>
-  </si>
-  <si>
-    <t>2017-10-26</t>
-  </si>
-  <si>
-    <t>2017-10-31</t>
-  </si>
-  <si>
-    <t>2018-03-15</t>
-  </si>
-  <si>
-    <t>2018-06-05</t>
-  </si>
-  <si>
-    <t>2018-06-08</t>
-  </si>
-  <si>
-    <t>2018-05-16</t>
-  </si>
-  <si>
-    <t>2018-06-13</t>
-  </si>
-  <si>
-    <t>2018-06-14</t>
-  </si>
-  <si>
-    <t>2018-06-19</t>
-  </si>
-  <si>
-    <t>2018-06-29</t>
-  </si>
-  <si>
-    <t>2018-07-12</t>
-  </si>
-  <si>
-    <t>2018-07-04</t>
-  </si>
-  <si>
-    <t>2018-07-13</t>
-  </si>
-  <si>
-    <t>2018-07-16</t>
-  </si>
-  <si>
-    <t>2018-07-18</t>
-  </si>
-  <si>
-    <t>2018-11-05</t>
-  </si>
-  <si>
-    <t>2018-11-15</t>
-  </si>
-  <si>
-    <t>2018-11-19</t>
-  </si>
-  <si>
-    <t>2018-11-07</t>
-  </si>
-  <si>
-    <t>2018-11-21</t>
-  </si>
-  <si>
-    <t>2018-11-22</t>
-  </si>
-  <si>
-    <t>2018-11-27</t>
-  </si>
-  <si>
-    <t>2018-12-03</t>
-  </si>
-  <si>
-    <t>2018-12-04</t>
-  </si>
-  <si>
-    <t>2018-12-10</t>
-  </si>
-  <si>
-    <t>2018-12-11</t>
-  </si>
-  <si>
-    <t>2019-05-09</t>
-  </si>
-  <si>
-    <t>2019-05-27</t>
-  </si>
-  <si>
-    <t>2019-05-30</t>
-  </si>
-  <si>
-    <t>2019-06-25</t>
-  </si>
-  <si>
-    <t>2019-07-04</t>
-  </si>
-  <si>
-    <t>2019-07-08</t>
-  </si>
-  <si>
-    <t>2019-07-09</t>
-  </si>
-  <si>
-    <t>2019-07-15</t>
-  </si>
-  <si>
-    <t>2019-07-16</t>
-  </si>
-  <si>
-    <t>2019-07-17</t>
-  </si>
-  <si>
-    <t>2019-07-18</t>
-  </si>
-  <si>
-    <t>2019-07-22</t>
-  </si>
-  <si>
-    <t>2019-07-23</t>
-  </si>
-  <si>
-    <t>2019-07-24</t>
-  </si>
-  <si>
-    <t>2019-07-25</t>
-  </si>
-  <si>
-    <t>2019-09-19</t>
-  </si>
-  <si>
-    <t>2019-09-23</t>
-  </si>
-  <si>
-    <t>2019-09-27</t>
-  </si>
-  <si>
-    <t>2019-09-06</t>
-  </si>
-  <si>
-    <t>2019-09-30</t>
-  </si>
-  <si>
-    <t>2019-11-25</t>
-  </si>
-  <si>
-    <t>2020-07-14</t>
-  </si>
-  <si>
-    <t>2020-07-24</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>2020-08-18</t>
-  </si>
-  <si>
-    <t>2020-08-12</t>
-  </si>
-  <si>
-    <t>2020-08-19</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>2020-12-08</t>
-  </si>
-  <si>
-    <t>2020-12-09</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>2021-05-10</t>
-  </si>
-  <si>
-    <t>2021-05-12</t>
-  </si>
-  <si>
-    <t>2021-04-22</t>
-  </si>
-  <si>
-    <t>2021-05-14</t>
-  </si>
-  <si>
-    <t>2021-05-18</t>
-  </si>
-  <si>
-    <t>2021-05-20</t>
-  </si>
-  <si>
-    <t>2021-05-26</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>2021-05-27</t>
-  </si>
-  <si>
-    <t>2021-05-21</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>2021-06-10</t>
-  </si>
-  <si>
-    <t>2021-06-15</t>
-  </si>
-  <si>
-    <t>2021-06-16</t>
-  </si>
-  <si>
-    <t>2021-06-18</t>
-  </si>
-  <si>
-    <t>2021-06-28</t>
-  </si>
-  <si>
-    <t>2021-10-29</t>
-  </si>
-  <si>
-    <t>2021-11-02</t>
-  </si>
-  <si>
-    <t>2021-11-12</t>
-  </si>
-  <si>
-    <t>2021-11-17</t>
-  </si>
-  <si>
-    <t>2016-05-24</t>
-  </si>
-  <si>
-    <t>2016-05-26</t>
-  </si>
-  <si>
-    <t>2016-05-27</t>
-  </si>
-  <si>
-    <t>2016-05-30</t>
-  </si>
-  <si>
-    <t>2016-06-01</t>
-  </si>
-  <si>
-    <t>2016-06-02</t>
-  </si>
-  <si>
-    <t>2016-06-06</t>
-  </si>
-  <si>
-    <t>2016-06-15</t>
-  </si>
-  <si>
-    <t>2016-06-16</t>
-  </si>
-  <si>
-    <t>2016-06-17</t>
-  </si>
-  <si>
-    <t>2016-06-20</t>
-  </si>
-  <si>
-    <t>2016-06-21</t>
-  </si>
-  <si>
-    <t>2016-06-23</t>
-  </si>
-  <si>
-    <t>2016-06-24</t>
-  </si>
-  <si>
-    <t>2016-06-27</t>
-  </si>
-  <si>
-    <t>2016-06-30</t>
-  </si>
-  <si>
-    <t>2016-12-06</t>
-  </si>
-  <si>
-    <t>2016-12-07</t>
-  </si>
-  <si>
-    <t>2016-12-08</t>
-  </si>
-  <si>
-    <t>2016-12-14</t>
-  </si>
-  <si>
-    <t>2017-01-06</t>
-  </si>
-  <si>
-    <t>2017-01-09</t>
-  </si>
-  <si>
-    <t>2017-01-11</t>
-  </si>
-  <si>
-    <t>2017-01-12</t>
-  </si>
-  <si>
-    <t>2017-02-03</t>
-  </si>
-  <si>
-    <t>2017-03-24</t>
-  </si>
-  <si>
-    <t>2017-03-27</t>
-  </si>
-  <si>
-    <t>2017-03-29</t>
-  </si>
-  <si>
-    <t>2017-03-30</t>
-  </si>
-  <si>
-    <t>2017-03-31</t>
-  </si>
-  <si>
-    <t>2017-04-06</t>
-  </si>
-  <si>
-    <t>2017-04-07</t>
-  </si>
-  <si>
-    <t>2017-04-10</t>
-  </si>
-  <si>
-    <t>2017-04-11</t>
-  </si>
-  <si>
-    <t>2017-04-12</t>
-  </si>
-  <si>
-    <t>2017-04-13</t>
-  </si>
-  <si>
-    <t>2017-04-19</t>
-  </si>
-  <si>
-    <t>2017-04-21</t>
-  </si>
-  <si>
-    <t>2017-04-28</t>
-  </si>
-  <si>
-    <t>2017-05-11</t>
-  </si>
-  <si>
-    <t>2017-05-15</t>
-  </si>
-  <si>
-    <t>2017-05-18</t>
-  </si>
-  <si>
-    <t>2017-05-19</t>
-  </si>
-  <si>
-    <t>2017-05-22</t>
-  </si>
-  <si>
-    <t>2017-10-09</t>
-  </si>
-  <si>
-    <t>2017-10-11</t>
-  </si>
-  <si>
-    <t>2018-02-09</t>
-  </si>
-  <si>
-    <t>2018-05-07</t>
-  </si>
-  <si>
-    <t>2018-05-08</t>
-  </si>
-  <si>
-    <t>2018-05-09</t>
-  </si>
-  <si>
-    <t>2018-05-10</t>
-  </si>
-  <si>
-    <t>2018-05-11</t>
-  </si>
-  <si>
-    <t>2018-05-14</t>
-  </si>
-  <si>
-    <t>2018-05-17</t>
-  </si>
-  <si>
-    <t>2018-05-25</t>
-  </si>
-  <si>
-    <t>2018-05-30</t>
-  </si>
-  <si>
-    <t>2018-05-31</t>
-  </si>
-  <si>
-    <t>2018-06-15</t>
-  </si>
-  <si>
-    <t>2018-06-20</t>
-  </si>
-  <si>
-    <t>2018-06-21</t>
-  </si>
-  <si>
-    <t>2018-06-25</t>
-  </si>
-  <si>
-    <t>2018-10-19</t>
-  </si>
-  <si>
-    <t>2018-10-22</t>
-  </si>
-  <si>
-    <t>2018-10-23</t>
-  </si>
-  <si>
-    <t>2018-10-26</t>
-  </si>
-  <si>
-    <t>2018-10-29</t>
-  </si>
-  <si>
-    <t>2018-10-31</t>
-  </si>
-  <si>
-    <t>2018-11-13</t>
-  </si>
-  <si>
-    <t>2019-04-23</t>
-  </si>
-  <si>
-    <t>2019-04-24</t>
-  </si>
-  <si>
-    <t>2019-05-14</t>
-  </si>
-  <si>
-    <t>2019-05-15</t>
-  </si>
-  <si>
-    <t>2019-05-16</t>
-  </si>
-  <si>
-    <t>2019-06-05</t>
-  </si>
-  <si>
-    <t>2019-06-10</t>
-  </si>
-  <si>
-    <t>2019-06-12</t>
-  </si>
-  <si>
-    <t>2019-06-13</t>
-  </si>
-  <si>
-    <t>2019-06-14</t>
-  </si>
-  <si>
-    <t>2019-06-17</t>
-  </si>
-  <si>
-    <t>2019-06-18</t>
-  </si>
-  <si>
-    <t>2019-06-20</t>
-  </si>
-  <si>
-    <t>2019-06-26</t>
-  </si>
-  <si>
-    <t>2019-08-26</t>
-  </si>
-  <si>
-    <t>2019-08-27</t>
-  </si>
-  <si>
-    <t>2019-08-30</t>
-  </si>
-  <si>
-    <t>2019-09-02</t>
-  </si>
-  <si>
-    <t>2019-11-05</t>
-  </si>
-  <si>
-    <t>2020-06-15</t>
-  </si>
-  <si>
-    <t>2020-07-15</t>
-  </si>
-  <si>
-    <t>2020-07-16</t>
-  </si>
-  <si>
-    <t>2020-07-17</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>2020-07-22</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>2020-11-03</t>
-  </si>
-  <si>
-    <t>2020-11-04</t>
-  </si>
-  <si>
-    <t>2020-11-12</t>
-  </si>
-  <si>
-    <t>2021-03-02</t>
-  </si>
-  <si>
-    <t>2021-04-08</t>
-  </si>
-  <si>
-    <t>2021-04-09</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>2021-04-13</t>
-  </si>
-  <si>
-    <t>2021-04-14</t>
-  </si>
-  <si>
-    <t>2021-04-15</t>
-  </si>
-  <si>
-    <t>2021-04-16</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>2021-04-20</t>
-  </si>
-  <si>
-    <t>2021-04-23</t>
-  </si>
-  <si>
-    <t>2021-04-26</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>2021-04-29</t>
-  </si>
-  <si>
-    <t>2021-10-15</t>
-  </si>
-  <si>
-    <t>2021-10-18</t>
-  </si>
-  <si>
-    <t>2021-10-19</t>
-  </si>
-  <si>
-    <t>2021-10-26</t>
   </si>
   <si>
     <t>2021-10-28</t>
@@ -1562,7 +1568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P505"/>
+  <dimension ref="A1:P522"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1623,7 +1629,7 @@
         <v>2.636521639996683</v>
       </c>
       <c r="D2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E2">
         <v>2.833647241107702</v>
@@ -1659,7 +1665,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1673,7 +1679,7 @@
         <v>2.808801457176021</v>
       </c>
       <c r="D3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E3">
         <v>2.7135041663212</v>
@@ -1709,7 +1715,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1723,7 +1729,7 @@
         <v>2.746397091058633</v>
       </c>
       <c r="D4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E4">
         <v>2.648930323263125</v>
@@ -1773,7 +1779,7 @@
         <v>2.683209227271539</v>
       </c>
       <c r="D5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E5">
         <v>2.583545744375049</v>
@@ -1809,7 +1815,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1823,7 +1829,7 @@
         <v>2.555958070922727</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E6">
         <v>2.632522016358742</v>
@@ -1859,7 +1865,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1873,7 +1879,7 @@
         <v>2.641252819939413</v>
       </c>
       <c r="D7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E7">
         <v>2.540130729835057</v>
@@ -1909,7 +1915,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1923,7 +1929,7 @@
         <v>2.512285655110759</v>
       </c>
       <c r="D8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E8">
         <v>2.590994611146576</v>
@@ -1959,7 +1965,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1973,7 +1979,7 @@
         <v>2.615441102246784</v>
       </c>
       <c r="D9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E9">
         <v>2.513421672263544</v>
@@ -2009,7 +2015,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2023,7 +2029,7 @@
         <v>2.515418243442972</v>
       </c>
       <c r="D10" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E10">
         <v>2.545423958143926</v>
@@ -2059,7 +2065,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2073,7 +2079,7 @@
         <v>2.487273994427867</v>
       </c>
       <c r="D11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E11">
         <v>2.567211421027677</v>
@@ -2109,7 +2115,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2123,7 +2129,7 @@
         <v>2.487984580081365</v>
       </c>
       <c r="D12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E12">
         <v>2.579898802553291</v>
@@ -2159,7 +2165,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2173,7 +2179,7 @@
         <v>2.500805561667341</v>
       </c>
       <c r="D13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E13">
         <v>2.59216563562278</v>
@@ -2209,7 +2215,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2223,7 +2229,7 @@
         <v>2.499441989042522</v>
       </c>
       <c r="D14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E14">
         <v>2.736702547602069</v>
@@ -2273,7 +2279,7 @@
         <v>2.512520850741042</v>
       </c>
       <c r="D15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E15">
         <v>2.749061943431123</v>
@@ -2309,7 +2315,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2323,7 +2329,7 @@
         <v>2.77984350091858</v>
       </c>
       <c r="D16" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E16">
         <v>2.889061943431122</v>
@@ -2359,7 +2365,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2373,7 +2379,7 @@
         <v>2.517224153471577</v>
       </c>
       <c r="D17" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E17">
         <v>2.753506518310076</v>
@@ -2409,7 +2415,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2423,7 +2429,7 @@
         <v>2.784426680003737</v>
       </c>
       <c r="D18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E18">
         <v>2.924119959439183</v>
@@ -2459,7 +2465,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2473,7 +2479,7 @@
         <v>2.884280694854824</v>
       </c>
       <c r="D19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E19">
         <v>2.961861794886389</v>
@@ -2523,7 +2529,7 @@
         <v>2.920719956495094</v>
       </c>
       <c r="D20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E20">
         <v>2.907075620138133</v>
@@ -2559,7 +2565,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2573,7 +2579,7 @@
         <v>2.648180125005333</v>
       </c>
       <c r="D21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E21">
         <v>2.848908919700521</v>
@@ -2609,7 +2615,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2659,7 +2665,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2673,7 +2679,7 @@
         <v>2.691620213913162</v>
       </c>
       <c r="D23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E23">
         <v>2.889959376998489</v>
@@ -2709,7 +2715,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2723,7 +2729,7 @@
         <v>2.984719616116966</v>
       </c>
       <c r="D24" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E24">
         <v>2.755965243802971</v>
@@ -2759,7 +2765,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2773,7 +2779,7 @@
         <v>3.007275184023352</v>
       </c>
       <c r="D25" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E25">
         <v>2.755965243802971</v>
@@ -2809,7 +2815,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2823,7 +2829,7 @@
         <v>2.683495528297218</v>
       </c>
       <c r="D26" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E26">
         <v>2.882281628901694</v>
@@ -2859,7 +2865,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2873,7 +2879,7 @@
         <v>2.976914171586129</v>
       </c>
       <c r="D27" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E27">
         <v>2.747824596132772</v>
@@ -2909,7 +2915,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2923,7 +2929,7 @@
         <v>2.647048085674867</v>
       </c>
       <c r="D28" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E28">
         <v>2.84783915365346</v>
@@ -2959,7 +2965,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2973,7 +2979,7 @@
         <v>2.941898848516719</v>
       </c>
       <c r="D29" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E29">
         <v>2.711305547532774</v>
@@ -3009,7 +3015,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3023,7 +3029,7 @@
         <v>2.962790623816959</v>
       </c>
       <c r="D30" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E30">
         <v>2.711305547532774</v>
@@ -3059,7 +3065,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3073,7 +3079,7 @@
         <v>2.636850318680218</v>
       </c>
       <c r="D31" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E31">
         <v>2.674077933106496</v>
@@ -3109,7 +3115,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3123,7 +3129,7 @@
         <v>2.64386308474694</v>
       </c>
       <c r="D32" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E32">
         <v>2.844829359063415</v>
@@ -3159,7 +3165,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3173,7 +3179,7 @@
         <v>2.938838994972993</v>
       </c>
       <c r="D33" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E33">
         <v>2.708114289235636</v>
@@ -3209,7 +3215,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3223,7 +3229,7 @@
         <v>2.959611880258242</v>
       </c>
       <c r="D34" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E34">
         <v>2.708114289235636</v>
@@ -3259,7 +3265,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3273,7 +3279,7 @@
         <v>2.63362151616782</v>
       </c>
       <c r="D35" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E35">
         <v>2.706375129633912</v>
@@ -3309,7 +3315,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3323,7 +3329,7 @@
         <v>2.623711665472045</v>
       </c>
       <c r="D36" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E36">
         <v>2.825786465799713</v>
@@ -3359,7 +3365,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3373,7 +3379,7 @@
         <v>2.919479379991807</v>
       </c>
       <c r="D37" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E37">
         <v>2.687923279746057</v>
@@ -3409,7 +3415,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3423,7 +3429,7 @@
         <v>2.939500051198033</v>
       </c>
       <c r="D38" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E38">
         <v>2.687923279746057</v>
@@ -3459,7 +3465,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3473,7 +3479,7 @@
         <v>2.613192965390128</v>
       </c>
       <c r="D39" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E39">
         <v>2.65740457966414</v>
@@ -3509,7 +3515,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3523,7 +3529,7 @@
         <v>2.866121269202039</v>
       </c>
       <c r="D40" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E40">
         <v>2.632273716345684</v>
@@ -3573,7 +3579,7 @@
         <v>2.884068721379623</v>
       </c>
       <c r="D41" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E41">
         <v>2.632273716345684</v>
@@ -3623,7 +3629,7 @@
         <v>2.556888701243869</v>
       </c>
       <c r="D42" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E42">
         <v>2.5709911987269</v>
@@ -3673,7 +3679,7 @@
         <v>2.84066903268222</v>
       </c>
       <c r="D43" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E43">
         <v>2.605728438993726</v>
@@ -3709,7 +3715,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3723,7 +3729,7 @@
         <v>2.857627543154535</v>
       </c>
       <c r="D44" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E44">
         <v>2.605728438993726</v>
@@ -3759,7 +3765,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3773,7 +3779,7 @@
         <v>2.530031126511299</v>
       </c>
       <c r="D45" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E45">
         <v>2.536232918189681</v>
@@ -3809,7 +3815,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3823,7 +3829,7 @@
         <v>2.794653597980052</v>
       </c>
       <c r="D46" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E46">
         <v>2.557736881328888</v>
@@ -3859,7 +3865,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3873,7 +3879,7 @@
         <v>2.809824187676618</v>
       </c>
       <c r="D47" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E47">
         <v>2.557736881328888</v>
@@ -3909,7 +3915,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3959,7 +3965,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3973,7 +3979,7 @@
         <v>2.877968395292299</v>
       </c>
       <c r="D49" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E49">
         <v>2.644629614722029</v>
@@ -4009,7 +4015,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4023,7 +4029,7 @@
         <v>2.896376165252531</v>
       </c>
       <c r="D50" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E50">
         <v>2.644629614722029</v>
@@ -4059,7 +4065,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4073,7 +4079,7 @@
         <v>2.521770137334771</v>
       </c>
       <c r="D51" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E51">
         <v>2.535896862069519</v>
@@ -4109,7 +4115,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4123,7 +4129,7 @@
         <v>2.934431839092635</v>
       </c>
       <c r="D52" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E52">
         <v>2.703517868992319</v>
@@ -4159,7 +4165,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4173,7 +4179,7 @@
         <v>2.955033485192349</v>
       </c>
       <c r="D53" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E53">
         <v>2.703517868992319</v>
@@ -4209,7 +4215,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4259,7 +4265,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4273,7 +4279,7 @@
         <v>2.974730272968942</v>
       </c>
       <c r="D55" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E55">
         <v>2.745546910458406</v>
@@ -4309,7 +4315,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4323,7 +4329,7 @@
         <v>2.996897706887981</v>
       </c>
       <c r="D56" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E56">
         <v>2.745546910458406</v>
@@ -4359,7 +4365,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4373,7 +4379,7 @@
         <v>2.624468326525319</v>
       </c>
       <c r="D57" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E57">
         <v>2.660688149733082</v>
@@ -4409,7 +4415,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4423,7 +4429,7 @@
         <v>3.056805462611843</v>
       </c>
       <c r="D58" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E58">
         <v>2.831146801497014</v>
@@ -4459,7 +4465,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4509,7 +4515,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4523,7 +4529,7 @@
         <v>3.075488420323122</v>
       </c>
       <c r="D60" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E60">
         <v>2.850632094815525</v>
@@ -4573,7 +4579,7 @@
         <v>2.73140795531227</v>
       </c>
       <c r="D61" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E61">
         <v>2.75953055997749</v>
@@ -4623,7 +4629,7 @@
         <v>2.72765316464271</v>
       </c>
       <c r="D62" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E62">
         <v>2.75953055997749</v>
@@ -4673,7 +4679,7 @@
         <v>2.72671446697532</v>
       </c>
       <c r="D63" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E63">
         <v>2.75953055997749</v>
@@ -4723,7 +4729,7 @@
         <v>6.293149296554828</v>
       </c>
       <c r="D64" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E64">
         <v>5.963700498102364</v>
@@ -4759,7 +4765,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4773,7 +4779,7 @@
         <v>6.420239880180696</v>
       </c>
       <c r="D65" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E65">
         <v>6.082402264327184</v>
@@ -4809,7 +4815,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4823,7 +4829,7 @@
         <v>6.609514294497387</v>
       </c>
       <c r="D66" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E66">
         <v>6.259183317962906</v>
@@ -4859,7 +4865,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4873,7 +4879,7 @@
         <v>6.515171551263329</v>
       </c>
       <c r="D67" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E67">
         <v>6.612047937164794</v>
@@ -4909,7 +4915,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4923,7 +4929,7 @@
         <v>6.520829737768901</v>
       </c>
       <c r="D68" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E68">
         <v>6.612047937164794</v>
@@ -4959,7 +4965,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5009,7 +5015,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5059,7 +5065,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5109,7 +5115,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5123,7 +5129,7 @@
         <v>6.781478804637512</v>
       </c>
       <c r="D72" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E72">
         <v>6.821616798629249</v>
@@ -5159,7 +5165,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5173,7 +5179,7 @@
         <v>6.927933775178332</v>
       </c>
       <c r="D73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E73">
         <v>7.025464228815041</v>
@@ -5209,7 +5215,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5223,7 +5229,7 @@
         <v>7.465293617228137</v>
       </c>
       <c r="D74" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E74">
         <v>7.441132824526438</v>
@@ -5259,7 +5265,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5273,7 +5279,7 @@
         <v>2.399740228983164</v>
       </c>
       <c r="D75" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E75">
         <v>2.284756328614283</v>
@@ -5309,7 +5315,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5323,7 +5329,7 @@
         <v>2.181146111927123</v>
       </c>
       <c r="D76" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E76">
         <v>2.105842395854763</v>
@@ -5359,7 +5365,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5373,7 +5379,7 @@
         <v>2.180858495485883</v>
       </c>
       <c r="D77" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E77">
         <v>2.105842395854763</v>
@@ -5409,7 +5415,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5423,7 +5429,7 @@
         <v>2.355267416838251</v>
       </c>
       <c r="D78" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E78">
         <v>2.241615480893012</v>
@@ -5459,7 +5465,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5473,7 +5479,7 @@
         <v>2.138079262229388</v>
       </c>
       <c r="D79" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E79">
         <v>2.115876072829124</v>
@@ -5509,7 +5515,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5523,7 +5529,7 @@
         <v>2.136977667529256</v>
       </c>
       <c r="D80" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E80">
         <v>2.115876072829124</v>
@@ -5559,7 +5565,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5609,7 +5615,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5659,7 +5665,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5709,7 +5715,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5723,7 +5729,7 @@
         <v>1.925553832103902</v>
       </c>
       <c r="D84" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E84">
         <v>1.985821650998686</v>
@@ -5759,7 +5765,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5809,7 +5815,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5823,7 +5829,7 @@
         <v>1.87975631937778</v>
       </c>
       <c r="D86" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E86">
         <v>2.025900250164519</v>
@@ -5859,7 +5865,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5959,7 +5965,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5973,7 +5979,7 @@
         <v>1.789383875507923</v>
       </c>
       <c r="D89" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E89">
         <v>1.940268655809146</v>
@@ -6009,7 +6015,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6023,7 +6029,7 @@
         <v>1.804905667333501</v>
       </c>
       <c r="D90" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E90">
         <v>1.95497618970289</v>
@@ -6059,7 +6065,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6073,7 +6079,7 @@
         <v>1.809491967335235</v>
       </c>
       <c r="D91" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E91">
         <v>1.959321896917648</v>
@@ -6109,7 +6115,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6123,7 +6129,7 @@
         <v>1.822908408572121</v>
       </c>
       <c r="D92" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E92">
         <v>1.972034524843747</v>
@@ -6159,7 +6165,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6173,7 +6179,7 @@
         <v>2.011491451443282</v>
       </c>
       <c r="D93" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E93">
         <v>1.930405304642352</v>
@@ -6209,7 +6215,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6223,7 +6229,7 @@
         <v>1.820166348365971</v>
       </c>
       <c r="D94" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E94">
         <v>1.969436310418903</v>
@@ -6259,7 +6265,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6273,7 +6279,7 @@
         <v>2.008879751476441</v>
       </c>
       <c r="D95" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E95">
         <v>1.927766633591516</v>
@@ -6309,7 +6315,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6323,7 +6329,7 @@
         <v>1.780154910291897</v>
       </c>
       <c r="D96" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E96">
         <v>1.931523833030682</v>
@@ -6359,7 +6365,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6409,7 +6415,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6423,7 +6429,7 @@
         <v>1.781411528733962</v>
       </c>
       <c r="D98" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E98">
         <v>1.932714530505294</v>
@@ -6459,7 +6465,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6509,7 +6515,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6523,7 +6529,7 @@
         <v>1.786869994736246</v>
       </c>
       <c r="D100" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E100">
         <v>1.937886650750082</v>
@@ -6573,7 +6579,7 @@
         <v>1.77389224303264</v>
       </c>
       <c r="D101" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E101">
         <v>1.925589699135846</v>
@@ -6609,7 +6615,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6623,7 +6629,7 @@
         <v>1.764225388294109</v>
       </c>
       <c r="D102" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E102">
         <v>1.916429958088516</v>
@@ -6823,7 +6829,7 @@
         <v>2.039049007419374</v>
       </c>
       <c r="D106" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E106">
         <v>1.958247448115615</v>
@@ -6859,7 +6865,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6873,7 +6879,7 @@
         <v>1.963804213639886</v>
       </c>
       <c r="D107" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E107">
         <v>2.044635472991321</v>
@@ -6909,7 +6915,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6923,7 +6929,7 @@
         <v>2.084469221121035</v>
       </c>
       <c r="D108" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E108">
         <v>2.00413671738046</v>
@@ -6959,7 +6965,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6973,7 +6979,7 @@
         <v>1.970692549466935</v>
       </c>
       <c r="D109" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E109">
         <v>2.103970465510173</v>
@@ -7009,7 +7015,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7059,7 +7065,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7073,7 +7079,7 @@
         <v>1.989826166099606</v>
       </c>
       <c r="D111" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E111">
         <v>2.069999197311251</v>
@@ -7109,7 +7115,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7123,7 +7129,7 @@
         <v>1.996538974422711</v>
       </c>
       <c r="D112" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E112">
         <v>2.129860772341935</v>
@@ -7159,7 +7165,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7209,7 +7215,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7223,7 +7229,7 @@
         <v>1.976959483296697</v>
       </c>
       <c r="D114" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E114">
         <v>2.110248039295503</v>
@@ -7323,7 +7329,7 @@
         <v>1.920546112528168</v>
       </c>
       <c r="D116" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E116">
         <v>2.053738890308352</v>
@@ -7359,7 +7365,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7409,7 +7415,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7423,7 +7429,7 @@
         <v>2.078859445890371</v>
       </c>
       <c r="D118" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E118">
         <v>2.128859445890371</v>
@@ -7459,7 +7465,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7473,7 +7479,7 @@
         <v>1.864471846503076</v>
       </c>
       <c r="D119" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E119">
         <v>1.997569421794252</v>
@@ -7509,7 +7515,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7559,7 +7565,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7609,7 +7615,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7623,7 +7629,7 @@
         <v>1.863420505387863</v>
       </c>
       <c r="D122" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E122">
         <v>1.996516295719591</v>
@@ -7723,7 +7729,7 @@
         <v>2.029857360363785</v>
       </c>
       <c r="D124" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E124">
         <v>2.011995247378231</v>
@@ -7773,7 +7779,7 @@
         <v>1.892165706973767</v>
       </c>
       <c r="D125" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E125">
         <v>2.025310300703773</v>
@@ -7809,7 +7815,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7859,7 +7865,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7909,7 +7915,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7973,7 +7979,7 @@
         <v>2.183293967129219</v>
       </c>
       <c r="D129" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E129">
         <v>2.097698061214447</v>
@@ -8023,7 +8029,7 @@
         <v>2.10409703769314</v>
       </c>
       <c r="D130" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E130">
         <v>2.097698061214447</v>
@@ -8109,7 +8115,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8159,7 +8165,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8209,7 +8215,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8259,7 +8265,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8309,7 +8315,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8359,7 +8365,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8409,7 +8415,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8459,7 +8465,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8473,7 +8479,7 @@
         <v>2.367284598691813</v>
       </c>
       <c r="D139" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E139">
         <v>2.284677125480481</v>
@@ -8523,7 +8529,7 @@
         <v>2.308705785003503</v>
       </c>
       <c r="D140" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E140">
         <v>2.284677125480481</v>
@@ -8659,7 +8665,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8709,7 +8715,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8759,7 +8765,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8809,7 +8815,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8859,7 +8865,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8923,7 +8929,7 @@
         <v>2.673055621612132</v>
       </c>
       <c r="D148" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E148">
         <v>2.649383477311975</v>
@@ -8973,7 +8979,7 @@
         <v>2.694510447967022</v>
       </c>
       <c r="D149" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E149">
         <v>2.66746656530884</v>
@@ -9023,7 +9029,7 @@
         <v>2.61961842602696</v>
       </c>
       <c r="D150" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E150">
         <v>2.674946565009619</v>
@@ -9309,7 +9315,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9323,7 +9329,7 @@
         <v>2.746485076848839</v>
       </c>
       <c r="D156" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E156">
         <v>2.847982602490786</v>
@@ -9359,7 +9365,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9423,7 +9429,7 @@
         <v>2.750734210259811</v>
       </c>
       <c r="D158" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E158">
         <v>2.800734210259812</v>
@@ -9459,7 +9465,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9523,7 +9529,7 @@
         <v>2.717092536535202</v>
       </c>
       <c r="D160" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E160">
         <v>2.791717770085309</v>
@@ -9609,7 +9615,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9623,7 +9629,7 @@
         <v>2.669840281895235</v>
       </c>
       <c r="D162" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E162">
         <v>2.754805459723328</v>
@@ -9659,7 +9665,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9723,7 +9729,7 @@
         <v>2.704152220032186</v>
       </c>
       <c r="D164" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E164">
         <v>2.721608307945189</v>
@@ -9773,7 +9779,7 @@
         <v>0.7516342779874527</v>
       </c>
       <c r="D165" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E165">
         <v>0.6447312303040151</v>
@@ -9809,7 +9815,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9823,7 +9829,7 @@
         <v>0.6347312303040145</v>
       </c>
       <c r="D166" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E166">
         <v>0.7803954970608276</v>
@@ -9859,7 +9865,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9873,7 +9879,7 @@
         <v>0.7872985447442655</v>
       </c>
       <c r="D167" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E167">
         <v>0.6685373256708909</v>
@@ -9909,7 +9915,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9923,7 +9929,7 @@
         <v>0.6141118398407031</v>
       </c>
       <c r="D168" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E168">
         <v>0.7042015924277036</v>
@@ -9959,7 +9965,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9973,7 +9979,7 @@
         <v>0.7076194190074974</v>
       </c>
       <c r="D169" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E169">
         <v>0.8524403513495589</v>
@@ -10023,7 +10029,7 @@
         <v>0.8587410173081755</v>
       </c>
       <c r="D170" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E170">
         <v>0.7402207509247285</v>
@@ -10073,7 +10079,7 @@
         <v>0.6868795521992208</v>
       </c>
       <c r="D171" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E171">
         <v>0.7750416832667906</v>
@@ -10123,7 +10129,7 @@
         <v>0.794311018129779</v>
       </c>
       <c r="D172" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E172">
         <v>0.9381289071762104</v>
@@ -10159,7 +10165,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10173,7 +10179,7 @@
         <v>0.7478436529603893</v>
       </c>
       <c r="D173" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E173">
         <v>0.9381289071762104</v>
@@ -10209,7 +10215,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10223,7 +10229,7 @@
         <v>0.9437131136379486</v>
       </c>
       <c r="D174" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E174">
         <v>0.8254794310532532</v>
@@ -10259,7 +10265,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10273,7 +10279,7 @@
         <v>0.7734278594221262</v>
       </c>
       <c r="D175" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E175">
         <v>0.8592973200996861</v>
@@ -10309,7 +10315,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10323,7 +10329,7 @@
         <v>0.9016190641047892</v>
       </c>
       <c r="D176" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E176">
         <v>1.04419537245399</v>
@@ -10359,7 +10365,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10373,7 +10379,7 @@
         <v>0.8558611736195321</v>
       </c>
       <c r="D177" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E177">
         <v>1.04419537245399</v>
@@ -10409,7 +10415,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10423,7 +10429,7 @@
         <v>1.048892735560562</v>
       </c>
       <c r="D178" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E178">
         <v>0.9310137903179339</v>
@@ -10459,7 +10465,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10473,7 +10479,7 @@
         <v>0.8805585367261042</v>
       </c>
       <c r="D179" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E179">
         <v>0.963590098667134</v>
@@ -10509,7 +10515,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10523,7 +10529,7 @@
         <v>1.076170489586433</v>
       </c>
       <c r="D180" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E180">
         <v>1.260525374010979</v>
@@ -10573,7 +10579,7 @@
         <v>1.26341395784032</v>
       </c>
       <c r="D181" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E181">
         <v>1.146258524308584</v>
@@ -10623,7 +10629,7 @@
         <v>1.099059073415773</v>
       </c>
       <c r="D182" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E182">
         <v>1.176302541669659</v>
@@ -10673,7 +10679,7 @@
         <v>1.931268098407571</v>
       </c>
       <c r="D183" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E183">
         <v>1.946759727730396</v>
@@ -10709,7 +10715,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10759,7 +10765,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10809,7 +10815,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10823,7 +10829,7 @@
         <v>0.5942088493584849</v>
       </c>
       <c r="D186" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E186">
         <v>0.5982130518354056</v>
@@ -10859,7 +10865,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10909,7 +10915,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10959,7 +10965,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11009,7 +11015,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11023,7 +11029,7 @@
         <v>-0.02499489055226256</v>
       </c>
       <c r="D190" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E190">
         <v>-0.07499489055226238</v>
@@ -11059,7 +11065,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11073,7 +11079,7 @@
         <v>-0.04541693580813089</v>
       </c>
       <c r="D191" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E191">
         <v>-0.1350880582477796</v>
@@ -11109,7 +11115,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11159,7 +11165,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11209,7 +11215,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11359,7 +11365,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11373,7 +11379,7 @@
         <v>-0.5154661476950757</v>
       </c>
       <c r="D197" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E197">
         <v>-0.4838284745942198</v>
@@ -11409,7 +11415,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11423,7 +11429,7 @@
         <v>-0.5144835438345625</v>
       </c>
       <c r="D198" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E198">
         <v>-0.4838284745942198</v>
@@ -11459,7 +11465,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11509,7 +11515,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11523,7 +11529,7 @@
         <v>-0.6795603356321358</v>
       </c>
       <c r="D200" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E200">
         <v>-0.6353746161347429</v>
@@ -11559,7 +11565,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11573,7 +11579,7 @@
         <v>-0.6770489039336995</v>
       </c>
       <c r="D201" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E201">
         <v>-0.6353746161347429</v>
@@ -11609,7 +11615,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11659,7 +11665,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11673,7 +11679,7 @@
         <v>-1.275160705635463</v>
       </c>
       <c r="D203" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E203">
         <v>-0.9575450227817477</v>
@@ -11709,7 +11715,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11723,7 +11729,7 @@
         <v>-1.267100202166811</v>
       </c>
       <c r="D204" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E204">
         <v>-0.9575450227817477</v>
@@ -11759,7 +11765,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11823,7 +11829,7 @@
         <v>-1.30354206111917</v>
       </c>
       <c r="D206" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E206">
         <v>-0.9846924062879019</v>
@@ -11873,7 +11879,7 @@
         <v>-1.295217135083899</v>
       </c>
       <c r="D207" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E207">
         <v>-0.9846924062879019</v>
@@ -11923,7 +11929,7 @@
         <v>-1.315601110783377</v>
       </c>
       <c r="D208" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E208">
         <v>-0.9962271494449686</v>
@@ -11973,7 +11979,7 @@
         <v>-1.307163833353718</v>
       </c>
       <c r="D209" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E209">
         <v>-0.9962271494449686</v>
@@ -12023,7 +12029,7 @@
         <v>-1.303470101275702</v>
       </c>
       <c r="D210" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E210">
         <v>-0.9846235751332797</v>
@@ -12059,7 +12065,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12073,7 +12079,7 @@
         <v>-1.295145845673754</v>
       </c>
       <c r="D211" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E211">
         <v>-0.9846235751332797</v>
@@ -12109,7 +12115,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12123,7 +12129,7 @@
         <v>-1.352240812118975</v>
       </c>
       <c r="D212" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E212">
         <v>-1.031273820287715</v>
@@ -12159,7 +12165,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12173,7 +12179,7 @@
         <v>-1.343462171012276</v>
       </c>
       <c r="D213" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E213">
         <v>-1.031273820287715</v>
@@ -12209,7 +12215,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12259,7 +12265,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12273,7 +12279,7 @@
         <v>-1.277973836666044</v>
       </c>
       <c r="D215" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E215">
         <v>-0.9602358437675207</v>
@@ -12323,7 +12329,7 @@
         <v>-1.269887123902075</v>
       </c>
       <c r="D216" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E216">
         <v>-0.9602358437675207</v>
@@ -12373,7 +12379,7 @@
         <v>-1.030235843767521</v>
       </c>
       <c r="D217" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E217">
         <v>-1.080019061857596</v>
@@ -12423,7 +12429,7 @@
         <v>-1.007888992711643</v>
       </c>
       <c r="D218" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E218">
         <v>-1.080019061857596</v>
@@ -12473,7 +12479,7 @@
         <v>-1.154349245698821</v>
       </c>
       <c r="D219" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E219">
         <v>-0.8419862350162637</v>
@@ -12523,7 +12529,7 @@
         <v>-1.147414314838273</v>
       </c>
       <c r="D220" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E220">
         <v>-0.8419862350162637</v>
@@ -12673,7 +12679,7 @@
         <v>-0.9332125637434627</v>
       </c>
       <c r="D223" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E223">
         <v>-0.6304641914067899</v>
@@ -12709,7 +12715,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12723,7 +12729,7 @@
         <v>-0.9283379125284608</v>
       </c>
       <c r="D224" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E224">
         <v>-0.6304641914067899</v>
@@ -12759,7 +12765,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12773,7 +12779,7 @@
         <v>-1.078298911794628</v>
       </c>
       <c r="D225" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E225">
         <v>-0.7337942740491279</v>
@@ -12823,7 +12829,7 @@
         <v>-1.284045732215318</v>
       </c>
       <c r="D226" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E226">
         <v>-0.9315166474955321</v>
@@ -12873,7 +12879,7 @@
         <v>-1.074552792811861</v>
       </c>
       <c r="D227" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E227">
         <v>-0.7301942595508679</v>
@@ -12909,7 +12915,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12923,7 +12929,7 @@
         <v>0.6306184682796347</v>
       </c>
       <c r="D228" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E228">
         <v>0.8825890610024754</v>
@@ -12959,7 +12965,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12973,7 +12979,7 @@
         <v>2.500083924851446</v>
       </c>
       <c r="D229" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E229">
         <v>2.721828222716436</v>
@@ -13009,7 +13015,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13023,7 +13029,7 @@
         <v>2.484743417251086</v>
       </c>
       <c r="D230" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E230">
         <v>2.721828222716436</v>
@@ -13059,7 +13065,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13073,7 +13079,7 @@
         <v>2.959498476516616</v>
       </c>
       <c r="D231" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E231">
         <v>3.019498476516616</v>
@@ -13109,7 +13115,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13159,7 +13165,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13173,7 +13179,7 @@
         <v>3.973072767193392</v>
       </c>
       <c r="D233" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E233">
         <v>3.630196829293595</v>
@@ -13209,7 +13215,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13259,7 +13265,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13309,7 +13315,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13323,7 +13329,7 @@
         <v>4.556254256131551</v>
       </c>
       <c r="D236" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E236">
         <v>4.211276763316661</v>
@@ -13359,7 +13365,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13409,7 +13415,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13459,7 +13465,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13473,7 +13479,7 @@
         <v>4.667791750685101</v>
       </c>
       <c r="D239" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E239">
         <v>4.322412320952902</v>
@@ -13509,7 +13515,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13523,7 +13529,7 @@
         <v>4.273963746622406</v>
       </c>
       <c r="D240" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E240">
         <v>4.266274031756307</v>
@@ -13559,7 +13565,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13609,7 +13615,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13659,7 +13665,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13673,7 +13679,7 @@
         <v>3.655351043939968</v>
       </c>
       <c r="D243" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E243">
         <v>3.313620049187031</v>
@@ -13709,7 +13715,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13723,7 +13729,7 @@
         <v>2.349652973133038</v>
       </c>
       <c r="D244" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E244">
         <v>2.585321458264525</v>
@@ -13773,7 +13779,7 @@
         <v>2.337296219946928</v>
       </c>
       <c r="D245" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E245">
         <v>2.585321458264525</v>
@@ -13823,7 +13829,7 @@
         <v>2.821499834857581</v>
       </c>
       <c r="D246" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E246">
         <v>2.482773709326562</v>
@@ -13873,7 +13879,7 @@
         <v>1.399171925433256</v>
       </c>
       <c r="D247" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E247">
         <v>1.7228188215915</v>
@@ -13909,7 +13915,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13923,7 +13929,7 @@
         <v>1.94957093986026</v>
       </c>
       <c r="D248" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E248">
         <v>1.61398690043734</v>
@@ -13959,7 +13965,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13973,7 +13979,7 @@
         <v>1.388298565840941</v>
       </c>
       <c r="D249" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E249">
         <v>1.05473712956764</v>
@@ -14023,7 +14029,7 @@
         <v>1.206849236469149</v>
       </c>
       <c r="D250" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E250">
         <v>0.8739416716530437</v>
@@ -14073,7 +14079,7 @@
         <v>1.250249534396463</v>
       </c>
       <c r="D251" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E251">
         <v>0.9171855721103492</v>
@@ -14123,7 +14129,7 @@
         <v>1.265784593473219</v>
       </c>
       <c r="D252" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E252">
         <v>0.9326646489922341</v>
@@ -14159,7 +14165,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14173,7 +14179,7 @@
         <v>1.181086185990114</v>
       </c>
       <c r="D253" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E253">
         <v>0.8482714609955542</v>
@@ -14223,7 +14229,7 @@
         <v>3.393868635799184</v>
       </c>
       <c r="D254" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E254">
         <v>3.232668972857903</v>
@@ -14259,7 +14265,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14273,7 +14279,7 @@
         <v>3.344337857016143</v>
       </c>
       <c r="D255" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E255">
         <v>3.232668972857903</v>
@@ -14309,7 +14315,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14323,7 +14329,7 @@
         <v>3.108144846549583</v>
       </c>
       <c r="D256" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E256">
         <v>3.176241351782863</v>
@@ -14359,7 +14365,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14373,7 +14379,7 @@
         <v>3.110765478091183</v>
       </c>
       <c r="D257" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E257">
         <v>3.176241351782863</v>
@@ -14409,7 +14415,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14423,7 +14429,7 @@
         <v>3.484929217459694</v>
       </c>
       <c r="D258" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E258">
         <v>3.328403460479749</v>
@@ -14459,7 +14465,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14473,7 +14479,7 @@
         <v>3.438944160440425</v>
       </c>
       <c r="D259" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E259">
         <v>3.328403460479749</v>
@@ -14509,7 +14515,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14559,7 +14565,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14609,7 +14615,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14623,7 +14629,7 @@
         <v>3.67612531160249</v>
       </c>
       <c r="D262" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E262">
         <v>3.529413159454653</v>
@@ -14659,7 +14665,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14673,7 +14679,7 @@
         <v>3.637585058248958</v>
       </c>
       <c r="D263" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E263">
         <v>3.529413159454653</v>
@@ -14709,7 +14715,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14723,7 +14729,7 @@
         <v>3.405388602484038</v>
       </c>
       <c r="D264" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E264">
         <v>3.509413159454653</v>
@@ -14759,7 +14765,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14773,7 +14779,7 @@
         <v>3.405511387337113</v>
       </c>
       <c r="D265" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E265">
         <v>3.509413159454653</v>
@@ -14809,7 +14815,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14823,7 +14829,7 @@
         <v>3.451364045513422</v>
       </c>
       <c r="D266" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E266">
         <v>3.509413159454653</v>
@@ -14859,7 +14865,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14873,7 +14879,7 @@
         <v>4.004636932335591</v>
       </c>
       <c r="D267" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E267">
         <v>3.867442887120403</v>
@@ -14923,7 +14929,7 @@
         <v>3.774439165379895</v>
       </c>
       <c r="D268" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E268">
         <v>3.837640654076098</v>
@@ -14973,7 +14979,7 @@
         <v>4.220199786446392</v>
       </c>
       <c r="D269" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E269">
         <v>4.085943565478028</v>
@@ -15009,7 +15015,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15023,7 +15029,7 @@
         <v>3.991103703583256</v>
       </c>
       <c r="D270" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E270">
         <v>4.0441357312043</v>
@@ -15059,7 +15065,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15073,7 +15079,7 @@
         <v>4.24807262091024</v>
       </c>
       <c r="D271" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E271">
         <v>4.172298835483293</v>
@@ -15109,7 +15115,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15123,7 +15129,7 @@
         <v>4.076733299050661</v>
       </c>
       <c r="D272" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E272">
         <v>4.185185728196767</v>
@@ -15159,7 +15165,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15223,7 +15229,7 @@
         <v>3.853669569225198</v>
       </c>
       <c r="D274" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E274">
         <v>3.960609701897911</v>
@@ -15359,7 +15365,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15373,7 +15379,7 @@
         <v>3.457860783201086</v>
       </c>
       <c r="D277" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E277">
         <v>3.562117466477025</v>
@@ -15409,7 +15415,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15423,7 +15429,7 @@
         <v>3.461796612382101</v>
       </c>
       <c r="D278" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E278">
         <v>3.45818163729601</v>
@@ -15459,7 +15465,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15523,7 +15529,7 @@
         <v>1.876063224574707</v>
       </c>
       <c r="D280" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E280">
         <v>1.926860456775207</v>
@@ -15573,7 +15579,7 @@
         <v>1.879462993924748</v>
       </c>
       <c r="D281" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E281">
         <v>1.926860456775207</v>
@@ -15623,7 +15629,7 @@
         <v>1.36286186891499</v>
       </c>
       <c r="D282" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E282">
         <v>1.420876924621103</v>
@@ -15659,7 +15665,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15673,7 +15679,7 @@
         <v>1.365396205962064</v>
       </c>
       <c r="D283" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E283">
         <v>1.420876924621103</v>
@@ -15709,7 +15715,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15723,7 +15729,7 @@
         <v>1.492587172538397</v>
       </c>
       <c r="D284" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E284">
         <v>1.422587172538397</v>
@@ -15759,7 +15765,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15773,7 +15779,7 @@
         <v>1.155028253713973</v>
       </c>
       <c r="D285" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E285">
         <v>1.207786135342488</v>
@@ -15823,7 +15829,7 @@
         <v>1.157212112489207</v>
       </c>
       <c r="D286" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E286">
         <v>1.207786135342488</v>
@@ -15873,7 +15879,7 @@
         <v>1.287557383512098</v>
       </c>
       <c r="D287" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E287">
         <v>1.260086513310223</v>
@@ -15923,7 +15929,7 @@
         <v>-0.2566084186298667</v>
       </c>
       <c r="D288" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E288">
         <v>-0.001048450451905936</v>
@@ -15959,7 +15965,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15973,7 +15979,7 @@
         <v>-0.2875710874180024</v>
       </c>
       <c r="D289" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E289">
         <v>-0.001048450451905936</v>
@@ -16009,7 +16015,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16059,7 +16065,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16109,7 +16115,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16123,7 +16129,7 @@
         <v>-0.3429456734762377</v>
       </c>
       <c r="D292" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E292">
         <v>-0.1559309932859021</v>
@@ -16159,7 +16165,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16173,7 +16179,7 @@
         <v>-0.452945673476238</v>
       </c>
       <c r="D293" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E293">
         <v>-0.1559309932859021</v>
@@ -16209,7 +16215,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16223,7 +16229,7 @@
         <v>-0.07614423041516449</v>
       </c>
       <c r="D294" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E294">
         <v>-0.08649962563060054</v>
@@ -16259,7 +16265,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16273,7 +16279,7 @@
         <v>-0.06685502084603723</v>
       </c>
       <c r="D295" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E295">
         <v>-0.08649962563060054</v>
@@ -16309,7 +16315,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16323,7 +16329,7 @@
         <v>-0.6325763258089658</v>
       </c>
       <c r="D296" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E296">
         <v>-0.7397037652284588</v>
@@ -16359,7 +16365,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16373,7 +16379,7 @@
         <v>-0.6888811406779016</v>
       </c>
       <c r="D297" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E297">
         <v>-0.6347573064746772</v>
@@ -16409,7 +16415,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16423,7 +16429,7 @@
         <v>-0.5922830059527424</v>
       </c>
       <c r="D298" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E298">
         <v>-0.6988811406779014</v>
@@ -16459,7 +16465,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16473,7 +16479,7 @@
         <v>-0.7708727781363214</v>
       </c>
       <c r="D299" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E299">
         <v>-0.7160845060282481</v>
@@ -16509,7 +16515,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16523,7 +16529,7 @@
         <v>-0.6732115427634033</v>
       </c>
       <c r="D300" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E300">
         <v>-0.7808727781363212</v>
@@ -16559,7 +16565,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16573,7 +16579,7 @@
         <v>-0.6051723879795468</v>
       </c>
       <c r="D301" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E301">
         <v>-0.5517269067155315</v>
@@ -16609,7 +16615,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16623,7 +16629,7 @@
         <v>-0.509659617957122</v>
       </c>
       <c r="D302" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E302">
         <v>-0.6151723879795465</v>
@@ -16659,7 +16665,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16673,7 +16679,7 @@
         <v>1.374867998585327</v>
       </c>
       <c r="D303" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E303">
         <v>1.61428021608427</v>
@@ -16709,7 +16715,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16723,7 +16729,7 @@
         <v>1.37455579980999</v>
       </c>
       <c r="D304" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E304">
         <v>1.61428021608427</v>
@@ -16759,7 +16765,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16773,7 +16779,7 @@
         <v>1.659046067002767</v>
       </c>
       <c r="D305" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E305">
         <v>1.701663141543517</v>
@@ -16809,7 +16815,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16823,7 +16829,7 @@
         <v>1.400425101402588</v>
       </c>
       <c r="D306" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E306">
         <v>1.63789275673065</v>
@@ -16859,7 +16865,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16873,7 +16879,7 @@
         <v>1.415426421593279</v>
       </c>
       <c r="D307" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E307">
         <v>1.63789275673065</v>
@@ -16909,7 +16915,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16923,7 +16929,7 @@
         <v>1.672891436539961</v>
       </c>
       <c r="D308" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E308">
         <v>1.702888796158578</v>
@@ -16959,7 +16965,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16973,7 +16979,7 @@
         <v>1.682896717302726</v>
       </c>
       <c r="D309" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E309">
         <v>1.702888796158578</v>
@@ -17009,7 +17015,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17023,7 +17029,7 @@
         <v>1.392287936404873</v>
       </c>
       <c r="D310" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E310">
         <v>1.630374723852328</v>
@@ -17059,7 +17065,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17073,7 +17079,7 @@
         <v>1.392192134372636</v>
       </c>
       <c r="D311" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E311">
         <v>1.630374723852328</v>
@@ -17109,7 +17115,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17123,7 +17129,7 @@
         <v>1.665398674360388</v>
       </c>
       <c r="D312" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E312">
         <v>1.367982501138595</v>
@@ -17159,7 +17165,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17173,7 +17179,7 @@
         <v>1.67530287232815</v>
       </c>
       <c r="D313" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E313">
         <v>1.367982501138595</v>
@@ -17209,7 +17215,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17223,7 +17229,7 @@
         <v>1.683187064752997</v>
       </c>
       <c r="D314" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E314">
         <v>1.385560910531628</v>
@@ -17259,7 +17265,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17273,7 +17279,7 @@
         <v>1.693331241005988</v>
       </c>
       <c r="D315" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E315">
         <v>1.385560910531628</v>
@@ -17309,7 +17315,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17323,7 +17329,7 @@
         <v>1.671335210176903</v>
       </c>
       <c r="D316" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E316">
         <v>1.373848959803819</v>
@@ -17359,7 +17365,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17373,7 +17379,7 @@
         <v>1.68131949631757</v>
       </c>
       <c r="D317" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E317">
         <v>1.373848959803819</v>
@@ -17409,7 +17415,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17423,7 +17429,7 @@
         <v>1.693875753393727</v>
       </c>
       <c r="D318" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E318">
         <v>1.396123425781996</v>
@@ -17459,7 +17465,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17473,7 +17479,7 @@
         <v>1.704164127807133</v>
       </c>
       <c r="D319" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E319">
         <v>1.396123425781996</v>
@@ -17509,7 +17515,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17523,7 +17529,7 @@
         <v>1.366123425781996</v>
       </c>
       <c r="D320" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E320">
         <v>1.403731566187024</v>
@@ -17559,7 +17565,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17573,7 +17579,7 @@
         <v>1.710631890779994</v>
       </c>
       <c r="D321" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E321">
         <v>1.412681767280061</v>
@@ -17609,7 +17615,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17623,7 +17629,7 @@
         <v>1.72114631763706</v>
       </c>
       <c r="D322" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E322">
         <v>1.412681767280061</v>
@@ -17659,7 +17665,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17673,7 +17679,7 @@
         <v>1.382681767280062</v>
       </c>
       <c r="D323" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E323">
         <v>1.420374677351461</v>
@@ -17709,7 +17715,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17723,7 +17729,7 @@
         <v>1.679206240881443</v>
       </c>
       <c r="D324" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E324">
         <v>1.381627077835624</v>
@@ -17773,7 +17779,7 @@
         <v>1.689296712933807</v>
       </c>
       <c r="D325" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E325">
         <v>1.381627077835624</v>
@@ -17823,7 +17829,7 @@
         <v>1.351627077835625</v>
       </c>
       <c r="D326" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E326">
         <v>1.364138386842169</v>
@@ -17873,7 +17879,7 @@
         <v>1.662615013806636</v>
       </c>
       <c r="D327" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E327">
         <v>1.365231699984297</v>
@@ -17909,7 +17915,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17923,7 +17929,7 @@
         <v>1.672481658175022</v>
       </c>
       <c r="D328" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E328">
         <v>1.365231699984297</v>
@@ -17959,7 +17965,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17973,7 +17979,7 @@
         <v>1.335231699984297</v>
       </c>
       <c r="D329" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E329">
         <v>1.330198361076394</v>
@@ -18009,7 +18015,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18023,7 +18029,7 @@
         <v>1.638483426036899</v>
       </c>
       <c r="D330" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E330">
         <v>1.341384970754843</v>
@@ -18073,7 +18079,7 @@
         <v>1.648024517787818</v>
       </c>
       <c r="D331" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E331">
         <v>1.341384970754843</v>
@@ -18173,7 +18179,7 @@
         <v>1.611118158429232</v>
       </c>
       <c r="D333" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E333">
         <v>1.31434273328757</v>
@@ -18223,7 +18229,7 @@
         <v>1.620290072876844</v>
       </c>
       <c r="D334" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E334">
         <v>1.31434273328757</v>
@@ -18273,7 +18279,7 @@
         <v>1.210704115653037</v>
       </c>
       <c r="D335" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E335">
         <v>1.321946243981619</v>
@@ -18323,7 +18329,7 @@
         <v>1.250704115653037</v>
       </c>
       <c r="D336" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E336">
         <v>1.321946243981619</v>
@@ -18373,7 +18379,7 @@
         <v>1.580824889600507</v>
       </c>
       <c r="D337" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E337">
         <v>1.284407057851428</v>
@@ -18409,7 +18415,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18423,7 +18429,7 @@
         <v>1.589588125885168</v>
       </c>
       <c r="D338" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E338">
         <v>1.284407057851428</v>
@@ -18459,7 +18465,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18473,7 +18479,7 @@
         <v>1.180206507742837</v>
       </c>
       <c r="D339" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E339">
         <v>1.27675246238701</v>
@@ -18509,7 +18515,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18523,7 +18529,7 @@
         <v>1.220206507742837</v>
       </c>
       <c r="D340" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E340">
         <v>1.27675246238701</v>
@@ -18559,7 +18565,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18573,7 +18579,7 @@
         <v>1.680056540073359</v>
       </c>
       <c r="D341" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E341">
         <v>1.409353064352823</v>
@@ -18609,7 +18615,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18623,7 +18629,7 @@
         <v>1.717732409003494</v>
       </c>
       <c r="D342" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E342">
         <v>1.409353064352823</v>
@@ -18659,7 +18665,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18673,7 +18679,7 @@
         <v>1.307497917096648</v>
       </c>
       <c r="D343" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E343">
         <v>1.444235818399402</v>
@@ -18709,7 +18715,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18723,7 +18729,7 @@
         <v>1.347497917096648</v>
       </c>
       <c r="D344" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E344">
         <v>1.444235818399402</v>
@@ -18759,7 +18765,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18773,7 +18779,7 @@
         <v>1.842256392262994</v>
       </c>
       <c r="D345" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E345">
         <v>1.530769127897027</v>
@@ -18823,7 +18829,7 @@
         <v>1.431193121765403</v>
       </c>
       <c r="D346" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E346">
         <v>1.572471675023835</v>
@@ -18873,7 +18879,7 @@
         <v>1.471193121765403</v>
       </c>
       <c r="D347" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E347">
         <v>1.572471675023835</v>
@@ -18923,7 +18929,7 @@
         <v>2.306011000659936</v>
       </c>
       <c r="D348" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E348">
         <v>2.348379970519409</v>
@@ -18959,7 +18965,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18973,7 +18979,7 @@
         <v>2.400485390479259</v>
       </c>
       <c r="D349" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E349">
         <v>2.364696230398958</v>
@@ -19009,7 +19015,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19059,7 +19065,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19073,7 +19079,7 @@
         <v>2.315116384839492</v>
       </c>
       <c r="D351" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E351">
         <v>2.323814331699535</v>
@@ -19109,7 +19115,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19123,7 +19129,7 @@
         <v>2.158186337006185</v>
       </c>
       <c r="D352" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E352">
         <v>2.199105803820263</v>
@@ -19159,7 +19165,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19209,7 +19215,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19259,7 +19265,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19273,7 +19279,7 @@
         <v>2.249949180664442</v>
       </c>
       <c r="D355" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E355">
         <v>2.193589002935801</v>
@@ -19309,7 +19315,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19323,7 +19329,7 @@
         <v>3.29910210514231</v>
       </c>
       <c r="D356" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E356">
         <v>3.35230135785332</v>
@@ -19359,7 +19365,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19373,7 +19379,7 @@
         <v>3.804045197377832</v>
       </c>
       <c r="D357" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E357">
         <v>3.415154291605215</v>
@@ -19409,7 +19415,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19423,7 +19429,7 @@
         <v>3.427249571448392</v>
       </c>
       <c r="D358" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E358">
         <v>3.291626526785035</v>
@@ -19459,7 +19465,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19509,7 +19515,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19523,7 +19529,7 @@
         <v>3.442581197445604</v>
       </c>
       <c r="D360" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E360">
         <v>3.306414237004073</v>
@@ -19559,7 +19565,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19573,7 +19579,7 @@
         <v>3.36022431872702</v>
       </c>
       <c r="D361" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E361">
         <v>3.226979110080385</v>
@@ -19609,7 +19615,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19623,7 +19629,7 @@
         <v>3.251003700388559</v>
       </c>
       <c r="D362" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E362">
         <v>3.121633280862579</v>
@@ -19659,7 +19665,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19673,7 +19679,7 @@
         <v>2.99001278638902</v>
       </c>
       <c r="D363" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E363">
         <v>3.032275977245447</v>
@@ -19759,7 +19765,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19773,7 +19779,7 @@
         <v>2.786342722576059</v>
       </c>
       <c r="D365" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E365">
         <v>2.830017022419643</v>
@@ -19809,7 +19815,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19823,7 +19829,7 @@
         <v>2.881784622628198</v>
       </c>
       <c r="D366" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E366">
         <v>2.846342722576059</v>
@@ -19859,7 +19865,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19873,7 +19879,7 @@
         <v>2.713139299753176</v>
       </c>
       <c r="D367" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E367">
         <v>2.672915915531583</v>
@@ -19909,7 +19915,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19923,7 +19929,7 @@
         <v>2.722022378645214</v>
       </c>
       <c r="D368" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E368">
         <v>2.672915915531583</v>
@@ -19959,7 +19965,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19973,7 +19979,7 @@
         <v>2.643362683974768</v>
       </c>
       <c r="D369" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E369">
         <v>2.68802760764238</v>
@@ -20009,7 +20015,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20023,7 +20029,7 @@
         <v>2.738474376085565</v>
       </c>
       <c r="D370" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E370">
         <v>2.678250991863972</v>
@@ -20059,7 +20065,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20073,7 +20079,7 @@
         <v>2.26156876679942</v>
       </c>
       <c r="D371" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E371">
         <v>2.319500204055783</v>
@@ -20109,7 +20115,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20123,7 +20129,7 @@
         <v>2.341086491507057</v>
       </c>
       <c r="D372" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E372">
         <v>2.284741341701965</v>
@@ -20159,7 +20165,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20173,7 +20179,7 @@
         <v>2.25156876679942</v>
       </c>
       <c r="D373" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E373">
         <v>2.298948197976329</v>
@@ -20209,7 +20215,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20223,7 +20229,7 @@
         <v>2.345775623073784</v>
       </c>
       <c r="D374" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E374">
         <v>2.287361910525056</v>
@@ -20259,7 +20265,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20273,7 +20279,7 @@
         <v>1.450725995788351</v>
       </c>
       <c r="D375" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E375">
         <v>1.543612412630503</v>
@@ -20309,7 +20315,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20323,7 +20329,7 @@
         <v>1.378039753255653</v>
       </c>
       <c r="D376" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E376">
         <v>1.473954763536668</v>
@@ -20359,7 +20365,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20373,7 +20379,7 @@
         <v>2.300473418774809</v>
       </c>
       <c r="D377" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E377">
         <v>2.269274816103397</v>
@@ -20423,7 +20429,7 @@
         <v>2.307737312105645</v>
       </c>
       <c r="D378" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E378">
         <v>2.269274816103397</v>
@@ -20473,7 +20479,7 @@
         <v>2.548688372146674</v>
       </c>
       <c r="D379" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E379">
         <v>2.44021981851742</v>
@@ -20509,7 +20515,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20523,7 +20529,7 @@
         <v>4.064626779899114</v>
       </c>
       <c r="D380" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E380">
         <v>3.971827788774664</v>
@@ -20559,7 +20565,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20573,7 +20579,7 @@
         <v>2.704221825320051</v>
       </c>
       <c r="D381" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E381">
         <v>2.757514946748523</v>
@@ -20609,7 +20615,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20623,7 +20629,7 @@
         <v>2.699698304540886</v>
       </c>
       <c r="D382" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E382">
         <v>2.757514946748523</v>
@@ -20659,7 +20665,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20673,7 +20679,7 @@
         <v>2.597723564836138</v>
       </c>
       <c r="D383" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E383">
         <v>2.648687698460786</v>
@@ -20709,7 +20715,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20723,7 +20729,7 @@
         <v>2.594470401040876</v>
       </c>
       <c r="D384" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E384">
         <v>2.648687698460786</v>
@@ -20759,7 +20765,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20773,7 +20779,7 @@
         <v>2.5327482758737</v>
       </c>
       <c r="D385" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E385">
         <v>2.582291478725809</v>
@@ -20809,7 +20815,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20823,7 +20829,7 @@
         <v>2.530270165227095</v>
       </c>
       <c r="D386" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E386">
         <v>2.582291478725809</v>
@@ -20859,7 +20865,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20873,7 +20879,7 @@
         <v>2.615226386520305</v>
       </c>
       <c r="D387" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E387">
         <v>2.605226386520305</v>
@@ -20909,7 +20915,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20923,7 +20929,7 @@
         <v>2.519210324106</v>
       </c>
       <c r="D388" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E388">
         <v>2.474919909368535</v>
@@ -20959,7 +20965,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20973,7 +20979,7 @@
         <v>2.443973795685154</v>
       </c>
       <c r="D389" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E389">
         <v>2.491575608314453</v>
@@ -21009,7 +21015,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21023,7 +21029,7 @@
         <v>2.442554625160083</v>
       </c>
       <c r="D390" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E390">
         <v>2.491575608314453</v>
@@ -21059,7 +21065,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21109,7 +21115,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21123,7 +21129,7 @@
         <v>2.457705873063223</v>
       </c>
       <c r="D392" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E392">
         <v>2.413049360402885</v>
@@ -21159,7 +21165,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21173,7 +21179,7 @@
         <v>2.382591377283335</v>
       </c>
       <c r="D393" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E393">
         <v>2.428850830862097</v>
@@ -21209,7 +21215,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21223,7 +21229,7 @@
         <v>2.381904402604011</v>
       </c>
       <c r="D394" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E394">
         <v>2.428850830862097</v>
@@ -21259,7 +21265,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21273,7 +21279,7 @@
         <v>2.46327835196266</v>
       </c>
       <c r="D395" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E395">
         <v>2.453507343522435</v>
@@ -21309,7 +21315,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21323,7 +21329,7 @@
         <v>2.467705873063223</v>
       </c>
       <c r="D396" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E396">
         <v>2.453507343522435</v>
@@ -21359,7 +21365,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21373,7 +21379,7 @@
         <v>2.447999298642713</v>
       </c>
       <c r="D397" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E397">
         <v>2.403285008753682</v>
@@ -21409,7 +21415,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21423,7 +21429,7 @@
         <v>2.372904061939057</v>
       </c>
       <c r="D398" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E398">
         <v>2.418951665679276</v>
@@ -21459,7 +21465,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21473,7 +21479,7 @@
         <v>2.37233264171712</v>
       </c>
       <c r="D399" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E399">
         <v>2.418951665679276</v>
@@ -21509,7 +21515,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21559,7 +21565,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21609,7 +21615,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21623,7 +21629,7 @@
         <v>2.414261420787727</v>
       </c>
       <c r="D402" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E402">
         <v>2.369346310197177</v>
@@ -21659,7 +21665,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21709,7 +21715,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21759,7 +21765,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21773,7 +21779,7 @@
         <v>2.424261420787727</v>
       </c>
       <c r="D405" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E405">
         <v>2.394544385485897</v>
@@ -21809,7 +21815,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21823,7 +21829,7 @@
         <v>2.414374606666995</v>
       </c>
       <c r="D406" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E406">
         <v>2.394544385485897</v>
@@ -21859,7 +21865,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21873,7 +21879,7 @@
         <v>2.397600622679596</v>
       </c>
       <c r="D407" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E407">
         <v>2.352586340671736</v>
@@ -21909,7 +21915,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21923,7 +21929,7 @@
         <v>2.322605383348882</v>
       </c>
       <c r="D408" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E408">
         <v>2.367553015986731</v>
@@ -21959,7 +21965,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21973,7 +21979,7 @@
         <v>2.322633947364601</v>
       </c>
       <c r="D409" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E409">
         <v>2.367553015986731</v>
@@ -22009,7 +22015,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22023,7 +22029,7 @@
         <v>2.402576819333163</v>
       </c>
       <c r="D410" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E410">
         <v>2.35256729799459</v>
@@ -22059,7 +22065,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22073,7 +22079,7 @@
         <v>2.407600622679595</v>
       </c>
       <c r="D411" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E411">
         <v>2.35256729799459</v>
@@ -22109,7 +22115,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22123,7 +22129,7 @@
         <v>2.39758158000245</v>
       </c>
       <c r="D412" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E412">
         <v>2.35256729799459</v>
@@ -22159,7 +22165,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22173,7 +22179,7 @@
         <v>2.378737718650321</v>
       </c>
       <c r="D413" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E413">
         <v>2.33361115745181</v>
@@ -22209,7 +22215,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22223,7 +22229,7 @@
         <v>2.30377990571649</v>
       </c>
       <c r="D414" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E414">
         <v>2.348315847988621</v>
@@ -22259,7 +22265,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22273,7 +22279,7 @@
         <v>2.304033028113511</v>
       </c>
       <c r="D415" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E415">
         <v>2.348315847988621</v>
@@ -22309,7 +22315,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22323,7 +22329,7 @@
         <v>2.383526783319471</v>
       </c>
       <c r="D416" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E416">
         <v>2.333442409187131</v>
@@ -22359,7 +22365,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22373,7 +22379,7 @@
         <v>2.38873771865032</v>
       </c>
       <c r="D417" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E417">
         <v>2.333442409187131</v>
@@ -22409,7 +22415,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22423,7 +22429,7 @@
         <v>2.378568970385641</v>
       </c>
       <c r="D418" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E418">
         <v>2.333442409187131</v>
@@ -22459,7 +22465,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22473,7 +22479,7 @@
         <v>2.29477967980894</v>
       </c>
       <c r="D419" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E419">
         <v>2.33911879805526</v>
@@ -22523,7 +22529,7 @@
         <v>2.295140160765494</v>
       </c>
       <c r="D420" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E420">
         <v>2.33911879805526</v>
@@ -22573,7 +22579,7 @@
         <v>2.374419198852388</v>
       </c>
       <c r="D421" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E421">
         <v>2.324299038533536</v>
@@ -22623,7 +22629,7 @@
         <v>2.379719599649515</v>
       </c>
       <c r="D422" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E422">
         <v>2.324299038533536</v>
@@ -22673,7 +22679,7 @@
         <v>2.369479279011813</v>
       </c>
       <c r="D423" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E423">
         <v>2.324299038533536</v>
@@ -22723,7 +22729,7 @@
         <v>2.280590400920047</v>
       </c>
       <c r="D424" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E424">
         <v>2.324619216844741</v>
@@ -22759,7 +22765,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22773,7 +22779,7 @@
         <v>2.281120137688396</v>
       </c>
       <c r="D425" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E425">
         <v>2.324619216844741</v>
@@ -22809,7 +22815,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22823,7 +22829,7 @@
         <v>2.360060664151698</v>
       </c>
       <c r="D426" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E426">
         <v>2.309884085228915</v>
@@ -22859,7 +22865,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22909,7 +22915,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22923,7 +22929,7 @@
         <v>2.281700069738552</v>
       </c>
       <c r="D428" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E428">
         <v>2.325753152774585</v>
@@ -22959,7 +22965,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -22973,7 +22979,7 @@
         <v>2.282216569900716</v>
       </c>
       <c r="D429" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E429">
         <v>2.325753152774585</v>
@@ -23009,7 +23015,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23023,7 +23029,7 @@
         <v>2.361183569576388</v>
       </c>
       <c r="D430" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E430">
         <v>2.311011402855666</v>
@@ -23059,7 +23065,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23073,7 +23079,7 @@
         <v>2.255753152774584</v>
       </c>
       <c r="D431" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E431">
         <v>2.30032273597278</v>
@@ -23109,7 +23115,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23123,7 +23129,7 @@
         <v>2.248769782041177</v>
       </c>
       <c r="D432" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E432">
         <v>2.297801715354081</v>
@@ -23159,7 +23165,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23173,7 +23179,7 @@
         <v>2.343406757033516</v>
       </c>
       <c r="D433" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E433">
         <v>2.293164740361742</v>
@@ -23209,7 +23215,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23223,7 +23229,7 @@
         <v>2.237801715354081</v>
       </c>
       <c r="D434" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E434">
         <v>2.26243869034642</v>
@@ -23259,7 +23265,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23273,7 +23279,7 @@
         <v>2.228095614122554</v>
       </c>
       <c r="D435" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E435">
         <v>2.276800683120539</v>
@@ -23309,7 +23315,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23323,7 +23329,7 @@
         <v>2.322610014996799</v>
       </c>
       <c r="D436" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E436">
         <v>2.263257480497806</v>
@@ -23359,7 +23365,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23409,7 +23415,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23423,7 +23429,7 @@
         <v>2.224983216186275</v>
       </c>
       <c r="D438" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E438">
         <v>2.273639077311749</v>
@@ -23473,7 +23479,7 @@
         <v>2.319479164108328</v>
       </c>
       <c r="D439" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E439">
         <v>2.26015123354559</v>
@@ -23623,7 +23629,7 @@
         <v>2.3116287572162</v>
       </c>
       <c r="D442" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E442">
         <v>2.252362519438469</v>
@@ -23659,7 +23665,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23709,7 +23715,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23759,7 +23765,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23823,7 +23829,7 @@
         <v>2.185149484739352</v>
       </c>
       <c r="D446" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E446">
         <v>2.165149484739352</v>
@@ -23923,7 +23929,7 @@
         <v>2.20020073233055</v>
       </c>
       <c r="D448" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E448">
         <v>2.205687152603988</v>
@@ -24009,7 +24015,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24059,7 +24065,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24109,7 +24115,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24159,7 +24165,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24209,7 +24215,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24323,7 +24329,7 @@
         <v>2.142114930387524</v>
       </c>
       <c r="D456" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E456">
         <v>2.162114930387524</v>
@@ -24359,7 +24365,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24373,7 +24379,7 @@
         <v>2.115413806995409</v>
       </c>
       <c r="D457" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E457">
         <v>2.141244762127619</v>
@@ -24459,7 +24465,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24473,7 +24479,7 @@
         <v>2.073994682974101</v>
       </c>
       <c r="D459" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E459">
         <v>2.082201671198685</v>
@@ -24523,7 +24529,7 @@
         <v>2.083994682974101</v>
       </c>
       <c r="D460" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E460">
         <v>2.082201671198685</v>
@@ -24609,7 +24615,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24623,7 +24629,7 @@
         <v>2.057461365020192</v>
       </c>
       <c r="D462" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E462">
         <v>2.066125824243982</v>
@@ -24659,7 +24665,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24709,7 +24715,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24759,7 +24765,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24809,7 +24815,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24859,7 +24865,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24873,7 +24879,7 @@
         <v>2.057577737614682</v>
       </c>
       <c r="D467" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E467">
         <v>2.099815205781953</v>
@@ -24909,7 +24915,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24973,7 +24979,7 @@
         <v>2.075267052489131</v>
       </c>
       <c r="D469" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E469">
         <v>2.105974841560053</v>
@@ -25023,7 +25029,7 @@
         <v>2.0673904197019</v>
       </c>
       <c r="D470" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E470">
         <v>2.109513786914668</v>
@@ -25073,7 +25079,7 @@
         <v>2.101281730695467</v>
       </c>
       <c r="D471" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E471">
         <v>2.131889846669813</v>
@@ -25123,7 +25129,7 @@
         <v>2.093106078618507</v>
       </c>
       <c r="D472" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E472">
         <v>2.134930426541548</v>
@@ -25173,7 +25179,7 @@
         <v>2.114232378900782</v>
       </c>
       <c r="D473" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E473">
         <v>2.144790875533345</v>
@@ -25209,7 +25215,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25223,7 +25229,7 @@
         <v>2.164790875533345</v>
       </c>
       <c r="D474" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E474">
         <v>2.134232378900781</v>
@@ -25259,7 +25265,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25273,7 +25279,7 @@
         <v>2.105907868798473</v>
       </c>
       <c r="D475" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E475">
         <v>2.147583358696166</v>
@@ -25309,7 +25315,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25323,7 +25329,7 @@
         <v>2.178667208693582</v>
       </c>
       <c r="D476" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E476">
         <v>2.148162082573172</v>
@@ -25359,7 +25365,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25373,7 +25379,7 @@
         <v>2.119677460934401</v>
       </c>
       <c r="D477" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E477">
         <v>2.161192839295628</v>
@@ -25409,7 +25415,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25423,7 +25429,7 @@
         <v>2.191253934723685</v>
       </c>
       <c r="D478" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E478">
         <v>2.160797219088007</v>
@@ -25473,7 +25479,7 @@
         <v>2.132167365995042</v>
       </c>
       <c r="D479" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E479">
         <v>2.173537512902076</v>
@@ -25573,7 +25579,7 @@
         <v>2.161339958759847</v>
       </c>
       <c r="D481" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E481">
         <v>2.202370889471942</v>
@@ -25623,7 +25629,7 @@
         <v>2.215480849833102</v>
       </c>
       <c r="D482" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E482">
         <v>2.179965384477054</v>
@@ -25673,7 +25679,7 @@
         <v>1.276065947508897</v>
       </c>
       <c r="D483" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E483">
         <v>1.317566169928825</v>
@@ -25709,7 +25715,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25723,7 +25729,7 @@
         <v>1.37689891014235</v>
       </c>
       <c r="D484" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E484">
         <v>1.288399132562277</v>
@@ -25759,7 +25765,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25773,7 +25779,7 @@
         <v>1.265250934212467</v>
       </c>
       <c r="D485" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E485">
         <v>1.306889515011455</v>
@@ -25809,7 +25815,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25823,7 +25829,7 @@
         <v>1.365853299547489</v>
       </c>
       <c r="D486" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E486">
         <v>1.277491880346475</v>
@@ -25859,7 +25865,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25873,7 +25879,7 @@
         <v>1.365250934212467</v>
       </c>
       <c r="D487" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E487">
         <v>1.29891353608099</v>
@@ -25909,7 +25915,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25923,7 +25929,7 @@
         <v>1.335853299547488</v>
       </c>
       <c r="D488" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E488">
         <v>1.29891353608099</v>
@@ -25959,7 +25965,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25973,7 +25979,7 @@
         <v>1.257848770795328</v>
       </c>
       <c r="D489" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E489">
         <v>1.29958204878089</v>
@@ -26009,7 +26015,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26023,7 +26029,7 @@
         <v>1.358293307486061</v>
       </c>
       <c r="D490" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E490">
         <v>1.270026585471621</v>
@@ -26059,7 +26065,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26073,7 +26079,7 @@
         <v>1.328293307486061</v>
       </c>
       <c r="D491" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E491">
         <v>1.291337761155134</v>
@@ -26109,7 +26115,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26123,7 +26129,7 @@
         <v>1.336383675279734</v>
       </c>
       <c r="D492" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E492">
         <v>1.248391395422367</v>
@@ -26173,7 +26179,7 @@
         <v>1.306383675279734</v>
       </c>
       <c r="D493" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E493">
         <v>1.269382388589295</v>
@@ -26217,49 +26223,49 @@
         <v>0</v>
       </c>
       <c r="B494" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C494">
-        <v>1.1949083591831</v>
+        <v>1.279467032224208</v>
       </c>
       <c r="D494" t="s">
         <v>274</v>
       </c>
       <c r="E494">
-        <v>1.223388801502731</v>
+        <v>1.192187695703653</v>
       </c>
       <c r="F494">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G494">
-        <v>0.0078450916408169</v>
+        <v>0.008100532967775794</v>
       </c>
       <c r="H494">
-        <v>0.007816611198497268</v>
+        <v>0.007927812304296346</v>
       </c>
       <c r="I494">
-        <v>0.02848044231963076</v>
+        <v>0.08727933652055464</v>
       </c>
       <c r="J494">
         <v>0.7120110579907708</v>
       </c>
       <c r="K494">
-        <v>4.67</v>
+        <v>4.79</v>
       </c>
       <c r="L494">
-        <v>4.52</v>
+        <v>4.69</v>
       </c>
       <c r="M494">
-        <v>4.63</v>
+        <v>4.73</v>
       </c>
       <c r="N494">
-        <v>4.52</v>
+        <v>4.56</v>
       </c>
       <c r="O494">
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26267,49 +26273,49 @@
         <v>1</v>
       </c>
       <c r="B495" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C495">
-        <v>1.279467032224208</v>
+        <v>1.280668138023285</v>
       </c>
       <c r="D495" t="s">
         <v>275</v>
       </c>
       <c r="E495">
-        <v>1.192187695703653</v>
+        <v>1.2123469216443</v>
       </c>
       <c r="F495">
         <v>-1</v>
       </c>
       <c r="G495">
-        <v>0.008100532967775794</v>
+        <v>0.007959331861976716</v>
       </c>
       <c r="H495">
-        <v>0.007927812304296346</v>
+        <v>0.008047653078355699</v>
       </c>
       <c r="I495">
-        <v>0.08727933652055464</v>
+        <v>0.06832121637898458</v>
       </c>
       <c r="J495">
         <v>0.7120110579907708</v>
       </c>
       <c r="K495">
-        <v>4.79</v>
+        <v>4.69</v>
       </c>
       <c r="L495">
-        <v>4.69</v>
+        <v>4.62</v>
       </c>
       <c r="M495">
-        <v>4.73</v>
+        <v>4.8</v>
       </c>
       <c r="N495">
-        <v>4.56</v>
+        <v>4.63</v>
       </c>
       <c r="O495">
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26323,7 +26329,7 @@
         <v>1.249467032224208</v>
       </c>
       <c r="D496" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E496">
         <v>1.2123469216443</v>
@@ -26359,86 +26365,86 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="497" spans="1:16">
       <c r="A497" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B497" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C497">
-        <v>1.24514956586386</v>
+        <v>1.175386037005039</v>
       </c>
       <c r="D497" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E497">
-        <v>1.158300093222558</v>
+        <v>1.183866479324669</v>
       </c>
       <c r="F497">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G497">
-        <v>0.008134850434136141</v>
+        <v>0.008124613962994963</v>
       </c>
       <c r="H497">
-        <v>0.007961699906777442</v>
+        <v>0.00807613352067533</v>
       </c>
       <c r="I497">
-        <v>0.08684947264130205</v>
+        <v>0.008480442319630299</v>
       </c>
       <c r="J497">
-        <v>0.7191754559783174</v>
+        <v>0.7120110579907708</v>
       </c>
       <c r="K497">
-        <v>4.79</v>
+        <v>4.88</v>
       </c>
       <c r="L497">
-        <v>4.69</v>
+        <v>4.65</v>
       </c>
       <c r="M497">
-        <v>4.73</v>
+        <v>4.84</v>
       </c>
       <c r="N497">
-        <v>4.56</v>
+        <v>4.63</v>
       </c>
       <c r="O497">
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>150</v>
+        <v>394</v>
       </c>
     </row>
     <row r="498" spans="1:16">
       <c r="A498" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B498" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C498">
-        <v>1.21514956586386</v>
+        <v>1.24514956586386</v>
       </c>
       <c r="D498" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E498">
-        <v>1.177957811304076</v>
+        <v>1.158300093222558</v>
       </c>
       <c r="F498">
         <v>-1</v>
       </c>
       <c r="G498">
-        <v>0.00810485043413614</v>
+        <v>0.008134850434136141</v>
       </c>
       <c r="H498">
-        <v>0.008082042188695925</v>
+        <v>0.007961699906777442</v>
       </c>
       <c r="I498">
-        <v>0.03719175455978352</v>
+        <v>0.08684947264130205</v>
       </c>
       <c r="J498">
         <v>0.7191754559783174</v>
@@ -26447,169 +26453,169 @@
         <v>4.79</v>
       </c>
       <c r="L498">
-        <v>4.66</v>
+        <v>4.69</v>
       </c>
       <c r="M498">
-        <v>4.8</v>
+        <v>4.73</v>
       </c>
       <c r="N498">
-        <v>4.63</v>
+        <v>4.56</v>
       </c>
       <c r="O498">
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>150</v>
+        <v>395</v>
       </c>
     </row>
     <row r="499" spans="1:16">
       <c r="A499" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B499" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C499">
-        <v>1.226637749198502</v>
+        <v>1.247067111461691</v>
       </c>
       <c r="D499" t="s">
         <v>275</v>
       </c>
       <c r="E499">
-        <v>1.140020157350503</v>
+        <v>1.177957811304076</v>
       </c>
       <c r="F499">
         <v>-1</v>
       </c>
       <c r="G499">
-        <v>0.008153362250801498</v>
+        <v>0.00799293288853831</v>
       </c>
       <c r="H499">
-        <v>0.007979979842649497</v>
+        <v>0.008082042188695925</v>
       </c>
       <c r="I499">
-        <v>0.086617591847999</v>
+        <v>0.06910930015761485</v>
       </c>
       <c r="J499">
-        <v>0.7230401358667011</v>
+        <v>0.7191754559783174</v>
       </c>
       <c r="K499">
-        <v>4.79</v>
+        <v>4.69</v>
       </c>
       <c r="L499">
-        <v>4.69</v>
+        <v>4.62</v>
       </c>
       <c r="M499">
-        <v>4.73</v>
+        <v>4.8</v>
       </c>
       <c r="N499">
-        <v>4.56</v>
+        <v>4.63</v>
       </c>
       <c r="O499">
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="500" spans="1:16">
       <c r="A500" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B500" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C500">
-        <v>1.183891513054156</v>
+        <v>1.21514956586386</v>
       </c>
       <c r="D500" t="s">
         <v>275</v>
       </c>
       <c r="E500">
-        <v>1.097809364665167</v>
+        <v>1.177957811304076</v>
       </c>
       <c r="F500">
         <v>-1</v>
       </c>
       <c r="G500">
-        <v>0.008196108486945847</v>
+        <v>0.00810485043413614</v>
       </c>
       <c r="H500">
-        <v>0.008022190635334832</v>
+        <v>0.008082042188695925</v>
       </c>
       <c r="I500">
-        <v>0.08608214838898842</v>
+        <v>0.03719175455978352</v>
       </c>
       <c r="J500">
-        <v>0.7319641935168778</v>
+        <v>0.7191754559783174</v>
       </c>
       <c r="K500">
         <v>4.79</v>
       </c>
       <c r="L500">
-        <v>4.69</v>
+        <v>4.66</v>
       </c>
       <c r="M500">
-        <v>4.73</v>
+        <v>4.8</v>
       </c>
       <c r="N500">
-        <v>4.56</v>
+        <v>4.63</v>
       </c>
       <c r="O500">
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>274</v>
+        <v>395</v>
       </c>
     </row>
     <row r="501" spans="1:16">
       <c r="A501" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B501" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C501">
-        <v>1.061287302238483</v>
+        <v>1.140423774825811</v>
       </c>
       <c r="D501" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E501">
-        <v>1.023774332097018</v>
+        <v>1.202341320423642</v>
       </c>
       <c r="F501">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G501">
-        <v>0.008258712697761517</v>
+        <v>0.00815957622517419</v>
       </c>
       <c r="H501">
-        <v>0.008236225667902983</v>
+        <v>0.008077658679576358</v>
       </c>
       <c r="I501">
-        <v>0.03751297014146449</v>
+        <v>0.06191754559783069</v>
       </c>
       <c r="J501">
-        <v>0.7512970141464546</v>
+        <v>0.7191754559783174</v>
       </c>
       <c r="K501">
-        <v>4.79</v>
+        <v>4.88</v>
       </c>
       <c r="L501">
-        <v>4.66</v>
+        <v>4.65</v>
       </c>
       <c r="M501">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="N501">
-        <v>4.63</v>
+        <v>4.64</v>
       </c>
       <c r="O501">
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>275</v>
+        <v>395</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26617,90 +26623,90 @@
         <v>0</v>
       </c>
       <c r="B502" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C502">
-        <v>0.9405281118670676</v>
+        <v>1.226637749198502</v>
       </c>
       <c r="D502" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E502">
-        <v>0.9027630348563518</v>
+        <v>1.140020157350503</v>
       </c>
       <c r="F502">
         <v>-1</v>
       </c>
       <c r="G502">
-        <v>0.008379471888132933</v>
+        <v>0.008153362250801498</v>
       </c>
       <c r="H502">
-        <v>0.00835723696514365</v>
+        <v>0.007979979842649497</v>
       </c>
       <c r="I502">
-        <v>0.03776507701071585</v>
+        <v>0.086617591847999</v>
       </c>
       <c r="J502">
-        <v>0.7765077010715934</v>
+        <v>0.7230401358667011</v>
       </c>
       <c r="K502">
         <v>4.79</v>
       </c>
       <c r="L502">
-        <v>4.66</v>
+        <v>4.69</v>
       </c>
       <c r="M502">
-        <v>4.8</v>
+        <v>4.73</v>
       </c>
       <c r="N502">
-        <v>4.63</v>
+        <v>4.56</v>
       </c>
       <c r="O502">
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="503" spans="1:16">
       <c r="A503" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B503" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C503">
-        <v>0.746167021374426</v>
+        <v>1.196637749198502</v>
       </c>
       <c r="D503" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E503">
-        <v>0.7503144418607692</v>
+        <v>1.159407347839835</v>
       </c>
       <c r="F503">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G503">
-        <v>0.008553832978625575</v>
+        <v>0.0081233622508015</v>
       </c>
       <c r="H503">
-        <v>0.00850968555813923</v>
+        <v>0.008100592652160165</v>
       </c>
       <c r="I503">
-        <v>0.004147420486343201</v>
+        <v>0.03723040135866729</v>
       </c>
       <c r="J503">
-        <v>0.8049140162114586</v>
+        <v>0.7230401358667011</v>
       </c>
       <c r="K503">
-        <v>4.85</v>
+        <v>4.79</v>
       </c>
       <c r="L503">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="M503">
-        <v>4.82</v>
+        <v>4.8</v>
       </c>
       <c r="N503">
         <v>4.63</v>
@@ -26714,52 +26720,52 @@
     </row>
     <row r="504" spans="1:16">
       <c r="A504" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B504" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C504">
-        <v>0.5224815208071796</v>
+        <v>1.121564136970499</v>
       </c>
       <c r="D504" t="s">
         <v>277</v>
       </c>
       <c r="E504">
-        <v>0.5280125629465156</v>
+        <v>1.183868150557168</v>
       </c>
       <c r="F504">
         <v>1</v>
       </c>
       <c r="G504">
-        <v>0.008777518479192821</v>
+        <v>0.008178435863029503</v>
       </c>
       <c r="H504">
-        <v>0.008731987437053484</v>
+        <v>0.008096131849442832</v>
       </c>
       <c r="I504">
-        <v>0.005531042139335973</v>
+        <v>0.06230401358666926</v>
       </c>
       <c r="J504">
-        <v>0.8510347379779013</v>
+        <v>0.7230401358667011</v>
       </c>
       <c r="K504">
-        <v>4.85</v>
+        <v>4.88</v>
       </c>
       <c r="L504">
         <v>4.65</v>
       </c>
       <c r="M504">
-        <v>4.82</v>
+        <v>4.78</v>
       </c>
       <c r="N504">
-        <v>4.63</v>
+        <v>4.64</v>
       </c>
       <c r="O504">
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>148</v>
+        <v>396</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26767,49 +26773,899 @@
         <v>0</v>
       </c>
       <c r="B505" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C505">
-        <v>1.049221706841676</v>
+        <v>1.183891513054156</v>
       </c>
       <c r="D505" t="s">
-        <v>151</v>
+        <v>274</v>
       </c>
       <c r="E505">
-        <v>1.016747983025339</v>
+        <v>1.097809364665167</v>
       </c>
       <c r="F505">
         <v>-1</v>
       </c>
       <c r="G505">
+        <v>0.008196108486945847</v>
+      </c>
+      <c r="H505">
+        <v>0.008022190635334832</v>
+      </c>
+      <c r="I505">
+        <v>0.08608214838898842</v>
+      </c>
+      <c r="J505">
+        <v>0.7319641935168778</v>
+      </c>
+      <c r="K505">
+        <v>4.79</v>
+      </c>
+      <c r="L505">
+        <v>4.69</v>
+      </c>
+      <c r="M505">
+        <v>4.73</v>
+      </c>
+      <c r="N505">
+        <v>4.56</v>
+      </c>
+      <c r="O505">
+        <v>1</v>
+      </c>
+      <c r="P505" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="506" spans="1:16">
+      <c r="A506" s="1">
+        <v>1</v>
+      </c>
+      <c r="B506" t="s">
+        <v>149</v>
+      </c>
+      <c r="C506">
+        <v>1.153891513054155</v>
+      </c>
+      <c r="D506" t="s">
+        <v>275</v>
+      </c>
+      <c r="E506">
+        <v>1.116571871118987</v>
+      </c>
+      <c r="F506">
+        <v>-1</v>
+      </c>
+      <c r="G506">
+        <v>0.008166108486945845</v>
+      </c>
+      <c r="H506">
+        <v>0.008143428128881013</v>
+      </c>
+      <c r="I506">
+        <v>0.03731964193516868</v>
+      </c>
+      <c r="J506">
+        <v>0.7319641935168778</v>
+      </c>
+      <c r="K506">
+        <v>4.79</v>
+      </c>
+      <c r="L506">
+        <v>4.66</v>
+      </c>
+      <c r="M506">
+        <v>4.8</v>
+      </c>
+      <c r="N506">
+        <v>4.63</v>
+      </c>
+      <c r="O506">
+        <v>1</v>
+      </c>
+      <c r="P506" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="507" spans="1:16">
+      <c r="A507" s="1">
+        <v>2</v>
+      </c>
+      <c r="B507" t="s">
+        <v>150</v>
+      </c>
+      <c r="C507">
+        <v>1.078014735637637</v>
+      </c>
+      <c r="D507" t="s">
+        <v>277</v>
+      </c>
+      <c r="E507">
+        <v>1.141211154989324</v>
+      </c>
+      <c r="F507">
+        <v>1</v>
+      </c>
+      <c r="G507">
+        <v>0.008221985264362363</v>
+      </c>
+      <c r="H507">
+        <v>0.008138788845010677</v>
+      </c>
+      <c r="I507">
+        <v>0.06319641935168718</v>
+      </c>
+      <c r="J507">
+        <v>0.7319641935168778</v>
+      </c>
+      <c r="K507">
+        <v>4.88</v>
+      </c>
+      <c r="L507">
+        <v>4.65</v>
+      </c>
+      <c r="M507">
+        <v>4.78</v>
+      </c>
+      <c r="N507">
+        <v>4.64</v>
+      </c>
+      <c r="O507">
+        <v>1</v>
+      </c>
+      <c r="P507" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="508" spans="1:16">
+      <c r="A508" s="1">
+        <v>0</v>
+      </c>
+      <c r="B508" t="s">
+        <v>149</v>
+      </c>
+      <c r="C508">
+        <v>1.120386130880944</v>
+      </c>
+      <c r="D508" t="s">
+        <v>275</v>
+      </c>
+      <c r="E508">
+        <v>1.082996540339985</v>
+      </c>
+      <c r="F508">
+        <v>-1</v>
+      </c>
+      <c r="G508">
+        <v>0.008199613869119058</v>
+      </c>
+      <c r="H508">
+        <v>0.008177003459660014</v>
+      </c>
+      <c r="I508">
+        <v>0.03738959054095847</v>
+      </c>
+      <c r="J508">
+        <v>0.7389590540958364</v>
+      </c>
+      <c r="K508">
+        <v>4.79</v>
+      </c>
+      <c r="L508">
+        <v>4.66</v>
+      </c>
+      <c r="M508">
+        <v>4.8</v>
+      </c>
+      <c r="N508">
+        <v>4.63</v>
+      </c>
+      <c r="O508">
+        <v>1</v>
+      </c>
+      <c r="P508" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="509" spans="1:16">
+      <c r="A509" s="1">
+        <v>1</v>
+      </c>
+      <c r="B509" t="s">
+        <v>150</v>
+      </c>
+      <c r="C509">
+        <v>1.043879816012319</v>
+      </c>
+      <c r="D509" t="s">
+        <v>277</v>
+      </c>
+      <c r="E509">
+        <v>1.107775721421902</v>
+      </c>
+      <c r="F509">
+        <v>1</v>
+      </c>
+      <c r="G509">
+        <v>0.008256120183987683</v>
+      </c>
+      <c r="H509">
+        <v>0.008172224278578097</v>
+      </c>
+      <c r="I509">
+        <v>0.0638959054095829</v>
+      </c>
+      <c r="J509">
+        <v>0.7389590540958364</v>
+      </c>
+      <c r="K509">
+        <v>4.88</v>
+      </c>
+      <c r="L509">
+        <v>4.65</v>
+      </c>
+      <c r="M509">
+        <v>4.78</v>
+      </c>
+      <c r="N509">
+        <v>4.64</v>
+      </c>
+      <c r="O509">
+        <v>1</v>
+      </c>
+      <c r="P509" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="510" spans="1:16">
+      <c r="A510" s="1">
+        <v>0</v>
+      </c>
+      <c r="B510" t="s">
+        <v>148</v>
+      </c>
+      <c r="C510">
+        <v>1.096417003653128</v>
+      </c>
+      <c r="D510" t="s">
+        <v>275</v>
+      </c>
+      <c r="E510">
+        <v>1.023774332097018</v>
+      </c>
+      <c r="F510">
+        <v>-1</v>
+      </c>
+      <c r="G510">
+        <v>0.008143582996346873</v>
+      </c>
+      <c r="H510">
+        <v>0.008236225667902983</v>
+      </c>
+      <c r="I510">
+        <v>0.07264267155610948</v>
+      </c>
+      <c r="J510">
+        <v>0.7512970141464546</v>
+      </c>
+      <c r="K510">
+        <v>4.69</v>
+      </c>
+      <c r="L510">
+        <v>4.62</v>
+      </c>
+      <c r="M510">
+        <v>4.8</v>
+      </c>
+      <c r="N510">
+        <v>4.63</v>
+      </c>
+      <c r="O510">
+        <v>1</v>
+      </c>
+      <c r="P510" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="511" spans="1:16">
+      <c r="A511" s="1">
+        <v>1</v>
+      </c>
+      <c r="B511" t="s">
+        <v>149</v>
+      </c>
+      <c r="C511">
+        <v>1.061287302238483</v>
+      </c>
+      <c r="D511" t="s">
+        <v>275</v>
+      </c>
+      <c r="E511">
+        <v>1.023774332097018</v>
+      </c>
+      <c r="F511">
+        <v>-1</v>
+      </c>
+      <c r="G511">
+        <v>0.008258712697761517</v>
+      </c>
+      <c r="H511">
+        <v>0.008236225667902983</v>
+      </c>
+      <c r="I511">
+        <v>0.03751297014146449</v>
+      </c>
+      <c r="J511">
+        <v>0.7512970141464546</v>
+      </c>
+      <c r="K511">
+        <v>4.79</v>
+      </c>
+      <c r="L511">
+        <v>4.66</v>
+      </c>
+      <c r="M511">
+        <v>4.8</v>
+      </c>
+      <c r="N511">
+        <v>4.63</v>
+      </c>
+      <c r="O511">
+        <v>1</v>
+      </c>
+      <c r="P511" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="512" spans="1:16">
+      <c r="A512" s="1">
+        <v>2</v>
+      </c>
+      <c r="B512" t="s">
+        <v>150</v>
+      </c>
+      <c r="C512">
+        <v>0.9836705709653022</v>
+      </c>
+      <c r="D512" t="s">
+        <v>277</v>
+      </c>
+      <c r="E512">
+        <v>1.048800272379947</v>
+      </c>
+      <c r="F512">
+        <v>1</v>
+      </c>
+      <c r="G512">
+        <v>0.008316329429034699</v>
+      </c>
+      <c r="H512">
+        <v>0.008231199727620053</v>
+      </c>
+      <c r="I512">
+        <v>0.06512970141464436</v>
+      </c>
+      <c r="J512">
+        <v>0.7512970141464546</v>
+      </c>
+      <c r="K512">
+        <v>4.88</v>
+      </c>
+      <c r="L512">
+        <v>4.65</v>
+      </c>
+      <c r="M512">
+        <v>4.78</v>
+      </c>
+      <c r="N512">
+        <v>4.64</v>
+      </c>
+      <c r="O512">
+        <v>1</v>
+      </c>
+      <c r="P512" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="513" spans="1:16">
+      <c r="A513" s="1">
+        <v>0</v>
+      </c>
+      <c r="B513" t="s">
+        <v>148</v>
+      </c>
+      <c r="C513">
+        <v>0.9781788819742268</v>
+      </c>
+      <c r="D513" t="s">
+        <v>275</v>
+      </c>
+      <c r="E513">
+        <v>0.9027630348563518</v>
+      </c>
+      <c r="F513">
+        <v>-1</v>
+      </c>
+      <c r="G513">
+        <v>0.008261821118025774</v>
+      </c>
+      <c r="H513">
+        <v>0.00835723696514365</v>
+      </c>
+      <c r="I513">
+        <v>0.07541584711787497</v>
+      </c>
+      <c r="J513">
+        <v>0.7765077010715934</v>
+      </c>
+      <c r="K513">
+        <v>4.69</v>
+      </c>
+      <c r="L513">
+        <v>4.62</v>
+      </c>
+      <c r="M513">
+        <v>4.8</v>
+      </c>
+      <c r="N513">
+        <v>4.63</v>
+      </c>
+      <c r="O513">
+        <v>1</v>
+      </c>
+      <c r="P513" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="514" spans="1:16">
+      <c r="A514" s="1">
+        <v>1</v>
+      </c>
+      <c r="B514" t="s">
+        <v>149</v>
+      </c>
+      <c r="C514">
+        <v>0.9405281118670676</v>
+      </c>
+      <c r="D514" t="s">
+        <v>275</v>
+      </c>
+      <c r="E514">
+        <v>0.9027630348563518</v>
+      </c>
+      <c r="F514">
+        <v>-1</v>
+      </c>
+      <c r="G514">
+        <v>0.008379471888132933</v>
+      </c>
+      <c r="H514">
+        <v>0.00835723696514365</v>
+      </c>
+      <c r="I514">
+        <v>0.03776507701071585</v>
+      </c>
+      <c r="J514">
+        <v>0.7765077010715934</v>
+      </c>
+      <c r="K514">
+        <v>4.79</v>
+      </c>
+      <c r="L514">
+        <v>4.66</v>
+      </c>
+      <c r="M514">
+        <v>4.8</v>
+      </c>
+      <c r="N514">
+        <v>4.63</v>
+      </c>
+      <c r="O514">
+        <v>1</v>
+      </c>
+      <c r="P514" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="515" spans="1:16">
+      <c r="A515" s="1">
+        <v>2</v>
+      </c>
+      <c r="B515" t="s">
+        <v>150</v>
+      </c>
+      <c r="C515">
+        <v>0.8606424187706248</v>
+      </c>
+      <c r="D515" t="s">
+        <v>277</v>
+      </c>
+      <c r="E515">
+        <v>0.9282931888777832</v>
+      </c>
+      <c r="F515">
+        <v>1</v>
+      </c>
+      <c r="G515">
+        <v>0.008439357581229377</v>
+      </c>
+      <c r="H515">
+        <v>0.008351706811122217</v>
+      </c>
+      <c r="I515">
+        <v>0.06765077010715848</v>
+      </c>
+      <c r="J515">
+        <v>0.7765077010715934</v>
+      </c>
+      <c r="K515">
+        <v>4.88</v>
+      </c>
+      <c r="L515">
+        <v>4.65</v>
+      </c>
+      <c r="M515">
+        <v>4.78</v>
+      </c>
+      <c r="N515">
+        <v>4.64</v>
+      </c>
+      <c r="O515">
+        <v>1</v>
+      </c>
+      <c r="P515" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="516" spans="1:16">
+      <c r="A516" s="1">
+        <v>0</v>
+      </c>
+      <c r="B516" t="s">
+        <v>148</v>
+      </c>
+      <c r="C516">
+        <v>0.8449532639682586</v>
+      </c>
+      <c r="D516" t="s">
+        <v>275</v>
+      </c>
+      <c r="E516">
+        <v>0.7664127221849988</v>
+      </c>
+      <c r="F516">
+        <v>-1</v>
+      </c>
+      <c r="G516">
+        <v>0.008395046736031741</v>
+      </c>
+      <c r="H516">
+        <v>0.008493587277815001</v>
+      </c>
+      <c r="I516">
+        <v>0.07854054178325987</v>
+      </c>
+      <c r="J516">
+        <v>0.8049140162114586</v>
+      </c>
+      <c r="K516">
+        <v>4.69</v>
+      </c>
+      <c r="L516">
+        <v>4.62</v>
+      </c>
+      <c r="M516">
+        <v>4.8</v>
+      </c>
+      <c r="N516">
+        <v>4.63</v>
+      </c>
+      <c r="O516">
+        <v>1</v>
+      </c>
+      <c r="P516" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="517" spans="1:16">
+      <c r="A517" s="1">
+        <v>1</v>
+      </c>
+      <c r="B517" t="s">
+        <v>149</v>
+      </c>
+      <c r="C517">
+        <v>0.8044618623471131</v>
+      </c>
+      <c r="D517" t="s">
+        <v>275</v>
+      </c>
+      <c r="E517">
+        <v>0.7664127221849988</v>
+      </c>
+      <c r="F517">
+        <v>-1</v>
+      </c>
+      <c r="G517">
+        <v>0.008515538137652887</v>
+      </c>
+      <c r="H517">
+        <v>0.008493587277815001</v>
+      </c>
+      <c r="I517">
+        <v>0.03804914016211436</v>
+      </c>
+      <c r="J517">
+        <v>0.8049140162114586</v>
+      </c>
+      <c r="K517">
+        <v>4.79</v>
+      </c>
+      <c r="L517">
+        <v>4.66</v>
+      </c>
+      <c r="M517">
+        <v>4.8</v>
+      </c>
+      <c r="N517">
+        <v>4.63</v>
+      </c>
+      <c r="O517">
+        <v>1</v>
+      </c>
+      <c r="P517" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="518" spans="1:16">
+      <c r="A518" s="1">
+        <v>2</v>
+      </c>
+      <c r="B518" t="s">
+        <v>150</v>
+      </c>
+      <c r="C518">
+        <v>0.7220196008880824</v>
+      </c>
+      <c r="D518" t="s">
+        <v>277</v>
+      </c>
+      <c r="E518">
+        <v>0.7925110025092272</v>
+      </c>
+      <c r="F518">
+        <v>1</v>
+      </c>
+      <c r="G518">
+        <v>0.00857798039911192</v>
+      </c>
+      <c r="H518">
+        <v>0.008487488997490772</v>
+      </c>
+      <c r="I518">
+        <v>0.07049140162114487</v>
+      </c>
+      <c r="J518">
+        <v>0.8049140162114586</v>
+      </c>
+      <c r="K518">
+        <v>4.88</v>
+      </c>
+      <c r="L518">
+        <v>4.65</v>
+      </c>
+      <c r="M518">
+        <v>4.78</v>
+      </c>
+      <c r="N518">
+        <v>4.64</v>
+      </c>
+      <c r="O518">
+        <v>1</v>
+      </c>
+      <c r="P518" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="519" spans="1:16">
+      <c r="A519" s="1">
+        <v>0</v>
+      </c>
+      <c r="B519" t="s">
+        <v>150</v>
+      </c>
+      <c r="C519">
+        <v>0.4969504786678423</v>
+      </c>
+      <c r="D519" t="s">
+        <v>277</v>
+      </c>
+      <c r="E519">
+        <v>0.5720539524656312</v>
+      </c>
+      <c r="F519">
+        <v>1</v>
+      </c>
+      <c r="G519">
+        <v>0.00880304952133216</v>
+      </c>
+      <c r="H519">
+        <v>0.008707946047534368</v>
+      </c>
+      <c r="I519">
+        <v>0.07510347379778892</v>
+      </c>
+      <c r="J519">
+        <v>0.8510347379779013</v>
+      </c>
+      <c r="K519">
+        <v>4.88</v>
+      </c>
+      <c r="L519">
+        <v>4.65</v>
+      </c>
+      <c r="M519">
+        <v>4.78</v>
+      </c>
+      <c r="N519">
+        <v>4.64</v>
+      </c>
+      <c r="O519">
+        <v>1</v>
+      </c>
+      <c r="P519" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="520" spans="1:16">
+      <c r="A520" s="1">
+        <v>0</v>
+      </c>
+      <c r="B520" t="s">
+        <v>151</v>
+      </c>
+      <c r="C520">
+        <v>1.049221706841676</v>
+      </c>
+      <c r="D520" t="s">
+        <v>278</v>
+      </c>
+      <c r="E520">
+        <v>1.016747983025339</v>
+      </c>
+      <c r="F520">
+        <v>-1</v>
+      </c>
+      <c r="G520">
         <v>0.008270778293158325</v>
       </c>
-      <c r="H505">
+      <c r="H520">
         <v>0.008283252016974661</v>
       </c>
-      <c r="I505">
+      <c r="I520">
         <v>0.03247372381633751</v>
       </c>
-      <c r="J505">
+      <c r="J520">
         <v>0.7491241272112704</v>
       </c>
-      <c r="K505">
+      <c r="K520">
         <v>4.82</v>
       </c>
-      <c r="L505">
+      <c r="L520">
         <v>4.66</v>
       </c>
-      <c r="M505">
+      <c r="M520">
         <v>4.85</v>
       </c>
-      <c r="N505">
+      <c r="N520">
         <v>4.65</v>
       </c>
-      <c r="O505">
-        <v>1</v>
-      </c>
-      <c r="P505" t="s">
-        <v>276</v>
+      <c r="O520">
+        <v>1</v>
+      </c>
+      <c r="P520" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="521" spans="1:16">
+      <c r="A521" s="1">
+        <v>1</v>
+      </c>
+      <c r="B521" t="s">
+        <v>150</v>
+      </c>
+      <c r="C521">
+        <v>0.9942742592090008</v>
+      </c>
+      <c r="D521" t="s">
+        <v>277</v>
+      </c>
+      <c r="E521">
+        <v>1.059186671930127</v>
+      </c>
+      <c r="F521">
+        <v>1</v>
+      </c>
+      <c r="G521">
+        <v>0.008305725740791001</v>
+      </c>
+      <c r="H521">
+        <v>0.008220813328069874</v>
+      </c>
+      <c r="I521">
+        <v>0.06491241272112624</v>
+      </c>
+      <c r="J521">
+        <v>0.7491241272112704</v>
+      </c>
+      <c r="K521">
+        <v>4.88</v>
+      </c>
+      <c r="L521">
+        <v>4.65</v>
+      </c>
+      <c r="M521">
+        <v>4.78</v>
+      </c>
+      <c r="N521">
+        <v>4.64</v>
+      </c>
+      <c r="O521">
+        <v>1</v>
+      </c>
+      <c r="P521" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="522" spans="1:16">
+      <c r="A522" s="1">
+        <v>0</v>
+      </c>
+      <c r="B522" t="s">
+        <v>150</v>
+      </c>
+      <c r="C522">
+        <v>1.041561394347275</v>
+      </c>
+      <c r="D522" t="s">
+        <v>277</v>
+      </c>
+      <c r="E522">
+        <v>1.105504808397535</v>
+      </c>
+      <c r="F522">
+        <v>1</v>
+      </c>
+      <c r="G522">
+        <v>0.008258438605652724</v>
+      </c>
+      <c r="H522">
+        <v>0.008174495191602463</v>
+      </c>
+      <c r="I522">
+        <v>0.06394341405025994</v>
+      </c>
+      <c r="J522">
+        <v>0.7394341405026076</v>
+      </c>
+      <c r="K522">
+        <v>4.88</v>
+      </c>
+      <c r="L522">
+        <v>4.65</v>
+      </c>
+      <c r="M522">
+        <v>4.78</v>
+      </c>
+      <c r="N522">
+        <v>4.64</v>
+      </c>
+      <c r="O522">
+        <v>1</v>
+      </c>
+      <c r="P522" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-03328-601328.xlsx
+++ b/s60_signal/position-03328-601328.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="398">
   <si>
     <t>trade_time</t>
   </si>
@@ -469,748 +469,745 @@
     <t>2021-11-19</t>
   </si>
   <si>
+    <t>2016-05-31</t>
+  </si>
+  <si>
+    <t>2016-06-07</t>
+  </si>
+  <si>
+    <t>2016-06-13</t>
+  </si>
+  <si>
+    <t>2016-06-28</t>
+  </si>
+  <si>
+    <t>2016-06-14</t>
+  </si>
+  <si>
+    <t>2016-06-29</t>
+  </si>
+  <si>
+    <t>2016-07-06</t>
+  </si>
+  <si>
+    <t>2016-07-07</t>
+  </si>
+  <si>
+    <t>2016-07-08</t>
+  </si>
+  <si>
+    <t>2016-07-11</t>
+  </si>
+  <si>
+    <t>2016-07-13</t>
+  </si>
+  <si>
+    <t>2016-07-15</t>
+  </si>
+  <si>
+    <t>2016-07-18</t>
+  </si>
+  <si>
+    <t>2016-07-19</t>
+  </si>
+  <si>
+    <t>2016-07-20</t>
+  </si>
+  <si>
+    <t>2016-07-21</t>
+  </si>
+  <si>
+    <t>2016-07-25</t>
+  </si>
+  <si>
+    <t>2016-07-27</t>
+  </si>
+  <si>
+    <t>2016-07-29</t>
+  </si>
+  <si>
+    <t>2016-12-15</t>
+  </si>
+  <si>
+    <t>2017-01-03</t>
+  </si>
+  <si>
+    <t>2017-02-14</t>
+  </si>
+  <si>
+    <t>2017-02-15</t>
+  </si>
+  <si>
+    <t>2017-03-02</t>
+  </si>
+  <si>
+    <t>2017-04-18</t>
+  </si>
+  <si>
+    <t>2017-04-26</t>
+  </si>
+  <si>
+    <t>2017-04-27</t>
+  </si>
+  <si>
+    <t>2017-05-04</t>
+  </si>
+  <si>
+    <t>2017-05-05</t>
+  </si>
+  <si>
+    <t>2017-05-09</t>
+  </si>
+  <si>
+    <t>2017-05-12</t>
+  </si>
+  <si>
+    <t>2017-06-02</t>
+  </si>
+  <si>
+    <t>2017-06-06</t>
+  </si>
+  <si>
+    <t>2017-06-08</t>
+  </si>
+  <si>
+    <t>2017-06-14</t>
+  </si>
+  <si>
+    <t>2017-06-22</t>
+  </si>
+  <si>
+    <t>2017-06-23</t>
+  </si>
+  <si>
+    <t>2017-06-20</t>
+  </si>
+  <si>
+    <t>2017-06-29</t>
+  </si>
+  <si>
+    <t>2017-07-03</t>
+  </si>
+  <si>
+    <t>2017-07-04</t>
+  </si>
+  <si>
+    <t>2017-07-05</t>
+  </si>
+  <si>
+    <t>2017-07-06</t>
+  </si>
+  <si>
+    <t>2017-10-12</t>
+  </si>
+  <si>
+    <t>2017-10-19</t>
+  </si>
+  <si>
+    <t>2017-10-26</t>
+  </si>
+  <si>
+    <t>2017-10-31</t>
+  </si>
+  <si>
+    <t>2018-03-15</t>
+  </si>
+  <si>
+    <t>2018-06-05</t>
+  </si>
+  <si>
+    <t>2018-06-08</t>
+  </si>
+  <si>
+    <t>2018-05-16</t>
+  </si>
+  <si>
+    <t>2018-06-13</t>
+  </si>
+  <si>
+    <t>2018-06-14</t>
+  </si>
+  <si>
+    <t>2018-06-19</t>
+  </si>
+  <si>
+    <t>2018-06-29</t>
+  </si>
+  <si>
+    <t>2018-07-12</t>
+  </si>
+  <si>
+    <t>2018-07-04</t>
+  </si>
+  <si>
+    <t>2018-07-13</t>
+  </si>
+  <si>
+    <t>2018-07-16</t>
+  </si>
+  <si>
+    <t>2018-07-18</t>
+  </si>
+  <si>
+    <t>2018-11-05</t>
+  </si>
+  <si>
+    <t>2018-11-15</t>
+  </si>
+  <si>
+    <t>2018-11-19</t>
+  </si>
+  <si>
+    <t>2018-11-07</t>
+  </si>
+  <si>
+    <t>2018-11-21</t>
+  </si>
+  <si>
+    <t>2018-11-22</t>
+  </si>
+  <si>
+    <t>2018-11-27</t>
+  </si>
+  <si>
+    <t>2018-12-03</t>
+  </si>
+  <si>
+    <t>2018-12-04</t>
+  </si>
+  <si>
+    <t>2018-12-10</t>
+  </si>
+  <si>
+    <t>2018-12-11</t>
+  </si>
+  <si>
+    <t>2019-05-09</t>
+  </si>
+  <si>
+    <t>2019-05-27</t>
+  </si>
+  <si>
+    <t>2019-05-30</t>
+  </si>
+  <si>
+    <t>2019-06-25</t>
+  </si>
+  <si>
+    <t>2019-07-04</t>
+  </si>
+  <si>
+    <t>2019-07-08</t>
+  </si>
+  <si>
+    <t>2019-07-09</t>
+  </si>
+  <si>
+    <t>2019-07-15</t>
+  </si>
+  <si>
+    <t>2019-07-16</t>
+  </si>
+  <si>
+    <t>2019-07-17</t>
+  </si>
+  <si>
+    <t>2019-07-18</t>
+  </si>
+  <si>
+    <t>2019-07-22</t>
+  </si>
+  <si>
+    <t>2019-07-23</t>
+  </si>
+  <si>
+    <t>2019-07-24</t>
+  </si>
+  <si>
+    <t>2019-07-25</t>
+  </si>
+  <si>
+    <t>2019-09-19</t>
+  </si>
+  <si>
+    <t>2019-09-23</t>
+  </si>
+  <si>
+    <t>2019-09-27</t>
+  </si>
+  <si>
+    <t>2019-09-06</t>
+  </si>
+  <si>
+    <t>2019-09-30</t>
+  </si>
+  <si>
+    <t>2019-11-25</t>
+  </si>
+  <si>
+    <t>2020-07-14</t>
+  </si>
+  <si>
+    <t>2020-07-24</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>2020-08-18</t>
+  </si>
+  <si>
+    <t>2020-08-12</t>
+  </si>
+  <si>
+    <t>2020-08-19</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>2020-12-08</t>
+  </si>
+  <si>
+    <t>2020-12-09</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>2021-05-10</t>
+  </si>
+  <si>
+    <t>2021-05-12</t>
+  </si>
+  <si>
+    <t>2021-04-22</t>
+  </si>
+  <si>
+    <t>2021-05-14</t>
+  </si>
+  <si>
+    <t>2021-05-18</t>
+  </si>
+  <si>
+    <t>2021-05-20</t>
+  </si>
+  <si>
+    <t>2021-05-26</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>2021-05-27</t>
+  </si>
+  <si>
+    <t>2021-05-21</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>2021-06-10</t>
+  </si>
+  <si>
+    <t>2021-06-15</t>
+  </si>
+  <si>
+    <t>2021-06-16</t>
+  </si>
+  <si>
+    <t>2021-06-18</t>
+  </si>
+  <si>
+    <t>2021-06-28</t>
+  </si>
+  <si>
+    <t>2021-10-29</t>
+  </si>
+  <si>
+    <t>2021-11-02</t>
+  </si>
+  <si>
+    <t>2021-11-12</t>
+  </si>
+  <si>
+    <t>2021-11-22</t>
+  </si>
+  <si>
+    <t>2021-11-23</t>
+  </si>
+  <si>
+    <t>2016-05-24</t>
+  </si>
+  <si>
+    <t>2016-05-26</t>
+  </si>
+  <si>
+    <t>2016-05-27</t>
+  </si>
+  <si>
+    <t>2016-05-30</t>
+  </si>
+  <si>
+    <t>2016-06-01</t>
+  </si>
+  <si>
+    <t>2016-06-02</t>
+  </si>
+  <si>
+    <t>2016-06-06</t>
+  </si>
+  <si>
+    <t>2016-06-15</t>
+  </si>
+  <si>
+    <t>2016-06-16</t>
+  </si>
+  <si>
+    <t>2016-06-17</t>
+  </si>
+  <si>
+    <t>2016-06-20</t>
+  </si>
+  <si>
+    <t>2016-06-21</t>
+  </si>
+  <si>
+    <t>2016-06-23</t>
+  </si>
+  <si>
+    <t>2016-06-24</t>
+  </si>
+  <si>
+    <t>2016-06-27</t>
+  </si>
+  <si>
+    <t>2016-06-30</t>
+  </si>
+  <si>
+    <t>2016-12-06</t>
+  </si>
+  <si>
+    <t>2016-12-07</t>
+  </si>
+  <si>
+    <t>2016-12-08</t>
+  </si>
+  <si>
+    <t>2016-12-14</t>
+  </si>
+  <si>
+    <t>2017-01-06</t>
+  </si>
+  <si>
+    <t>2017-01-09</t>
+  </si>
+  <si>
+    <t>2017-01-11</t>
+  </si>
+  <si>
+    <t>2017-01-12</t>
+  </si>
+  <si>
+    <t>2017-02-03</t>
+  </si>
+  <si>
+    <t>2017-03-24</t>
+  </si>
+  <si>
+    <t>2017-03-27</t>
+  </si>
+  <si>
+    <t>2017-03-29</t>
+  </si>
+  <si>
+    <t>2017-03-30</t>
+  </si>
+  <si>
+    <t>2017-03-31</t>
+  </si>
+  <si>
+    <t>2017-04-06</t>
+  </si>
+  <si>
+    <t>2017-04-07</t>
+  </si>
+  <si>
+    <t>2017-04-10</t>
+  </si>
+  <si>
+    <t>2017-04-11</t>
+  </si>
+  <si>
+    <t>2017-04-12</t>
+  </si>
+  <si>
+    <t>2017-04-13</t>
+  </si>
+  <si>
+    <t>2017-04-19</t>
+  </si>
+  <si>
+    <t>2017-04-21</t>
+  </si>
+  <si>
+    <t>2017-04-28</t>
+  </si>
+  <si>
+    <t>2017-05-11</t>
+  </si>
+  <si>
+    <t>2017-05-15</t>
+  </si>
+  <si>
+    <t>2017-05-18</t>
+  </si>
+  <si>
+    <t>2017-05-19</t>
+  </si>
+  <si>
+    <t>2017-05-22</t>
+  </si>
+  <si>
+    <t>2017-10-09</t>
+  </si>
+  <si>
+    <t>2017-10-11</t>
+  </si>
+  <si>
+    <t>2018-02-09</t>
+  </si>
+  <si>
+    <t>2018-05-07</t>
+  </si>
+  <si>
+    <t>2018-05-08</t>
+  </si>
+  <si>
+    <t>2018-05-09</t>
+  </si>
+  <si>
+    <t>2018-05-10</t>
+  </si>
+  <si>
+    <t>2018-05-11</t>
+  </si>
+  <si>
+    <t>2018-05-14</t>
+  </si>
+  <si>
+    <t>2018-05-17</t>
+  </si>
+  <si>
+    <t>2018-05-25</t>
+  </si>
+  <si>
+    <t>2018-05-30</t>
+  </si>
+  <si>
+    <t>2018-05-31</t>
+  </si>
+  <si>
+    <t>2018-06-15</t>
+  </si>
+  <si>
+    <t>2018-06-20</t>
+  </si>
+  <si>
+    <t>2018-06-21</t>
+  </si>
+  <si>
+    <t>2018-06-25</t>
+  </si>
+  <si>
+    <t>2018-10-19</t>
+  </si>
+  <si>
+    <t>2018-10-22</t>
+  </si>
+  <si>
+    <t>2018-10-23</t>
+  </si>
+  <si>
+    <t>2018-10-26</t>
+  </si>
+  <si>
+    <t>2018-10-29</t>
+  </si>
+  <si>
+    <t>2018-10-31</t>
+  </si>
+  <si>
+    <t>2018-11-13</t>
+  </si>
+  <si>
+    <t>2019-04-23</t>
+  </si>
+  <si>
+    <t>2019-04-24</t>
+  </si>
+  <si>
+    <t>2019-05-14</t>
+  </si>
+  <si>
+    <t>2019-05-15</t>
+  </si>
+  <si>
+    <t>2019-05-16</t>
+  </si>
+  <si>
+    <t>2019-06-05</t>
+  </si>
+  <si>
+    <t>2019-06-10</t>
+  </si>
+  <si>
+    <t>2019-06-12</t>
+  </si>
+  <si>
+    <t>2019-06-13</t>
+  </si>
+  <si>
+    <t>2019-06-14</t>
+  </si>
+  <si>
+    <t>2019-06-17</t>
+  </si>
+  <si>
+    <t>2019-06-18</t>
+  </si>
+  <si>
+    <t>2019-06-20</t>
+  </si>
+  <si>
+    <t>2019-06-26</t>
+  </si>
+  <si>
+    <t>2019-08-26</t>
+  </si>
+  <si>
+    <t>2019-08-27</t>
+  </si>
+  <si>
+    <t>2019-08-30</t>
+  </si>
+  <si>
+    <t>2019-09-02</t>
+  </si>
+  <si>
+    <t>2019-11-05</t>
+  </si>
+  <si>
+    <t>2020-06-15</t>
+  </si>
+  <si>
+    <t>2020-07-15</t>
+  </si>
+  <si>
+    <t>2020-07-16</t>
+  </si>
+  <si>
+    <t>2020-07-17</t>
+  </si>
+  <si>
+    <t>2020-07-21</t>
+  </si>
+  <si>
+    <t>2020-07-22</t>
+  </si>
+  <si>
+    <t>2020-07-23</t>
+  </si>
+  <si>
+    <t>2020-07-27</t>
+  </si>
+  <si>
+    <t>2020-11-03</t>
+  </si>
+  <si>
+    <t>2020-11-04</t>
+  </si>
+  <si>
+    <t>2020-11-12</t>
+  </si>
+  <si>
+    <t>2021-03-02</t>
+  </si>
+  <si>
+    <t>2021-04-08</t>
+  </si>
+  <si>
+    <t>2021-04-09</t>
+  </si>
+  <si>
+    <t>2021-04-12</t>
+  </si>
+  <si>
+    <t>2021-04-13</t>
+  </si>
+  <si>
+    <t>2021-04-14</t>
+  </si>
+  <si>
+    <t>2021-04-15</t>
+  </si>
+  <si>
+    <t>2021-04-16</t>
+  </si>
+  <si>
+    <t>2021-04-19</t>
+  </si>
+  <si>
+    <t>2021-04-20</t>
+  </si>
+  <si>
+    <t>2021-04-23</t>
+  </si>
+  <si>
+    <t>2021-04-26</t>
+  </si>
+  <si>
+    <t>2021-04-27</t>
+  </si>
+  <si>
+    <t>2021-04-29</t>
+  </si>
+  <si>
+    <t>2021-10-15</t>
+  </si>
+  <si>
+    <t>2021-10-18</t>
+  </si>
+  <si>
+    <t>2021-10-19</t>
+  </si>
+  <si>
+    <t>2021-10-26</t>
+  </si>
+  <si>
+    <t>2021-10-27</t>
+  </si>
+  <si>
+    <t>2021-10-28</t>
+  </si>
+  <si>
+    <t>2021-11-03</t>
+  </si>
+  <si>
+    <t>2021-11-04</t>
+  </si>
+  <si>
     <t>2021-11-15</t>
-  </si>
-  <si>
-    <t>2016-05-31</t>
-  </si>
-  <si>
-    <t>2016-06-07</t>
-  </si>
-  <si>
-    <t>2016-06-13</t>
-  </si>
-  <si>
-    <t>2016-06-28</t>
-  </si>
-  <si>
-    <t>2016-06-14</t>
-  </si>
-  <si>
-    <t>2016-06-29</t>
-  </si>
-  <si>
-    <t>2016-07-06</t>
-  </si>
-  <si>
-    <t>2016-07-07</t>
-  </si>
-  <si>
-    <t>2016-07-08</t>
-  </si>
-  <si>
-    <t>2016-07-11</t>
-  </si>
-  <si>
-    <t>2016-07-13</t>
-  </si>
-  <si>
-    <t>2016-07-15</t>
-  </si>
-  <si>
-    <t>2016-07-18</t>
-  </si>
-  <si>
-    <t>2016-07-19</t>
-  </si>
-  <si>
-    <t>2016-07-20</t>
-  </si>
-  <si>
-    <t>2016-07-21</t>
-  </si>
-  <si>
-    <t>2016-07-25</t>
-  </si>
-  <si>
-    <t>2016-07-27</t>
-  </si>
-  <si>
-    <t>2016-07-29</t>
-  </si>
-  <si>
-    <t>2016-12-15</t>
-  </si>
-  <si>
-    <t>2017-01-03</t>
-  </si>
-  <si>
-    <t>2017-02-14</t>
-  </si>
-  <si>
-    <t>2017-02-15</t>
-  </si>
-  <si>
-    <t>2017-03-02</t>
-  </si>
-  <si>
-    <t>2017-04-18</t>
-  </si>
-  <si>
-    <t>2017-04-26</t>
-  </si>
-  <si>
-    <t>2017-04-27</t>
-  </si>
-  <si>
-    <t>2017-05-04</t>
-  </si>
-  <si>
-    <t>2017-05-05</t>
-  </si>
-  <si>
-    <t>2017-05-09</t>
-  </si>
-  <si>
-    <t>2017-05-12</t>
-  </si>
-  <si>
-    <t>2017-06-02</t>
-  </si>
-  <si>
-    <t>2017-06-06</t>
-  </si>
-  <si>
-    <t>2017-06-08</t>
-  </si>
-  <si>
-    <t>2017-06-14</t>
-  </si>
-  <si>
-    <t>2017-06-22</t>
-  </si>
-  <si>
-    <t>2017-06-23</t>
-  </si>
-  <si>
-    <t>2017-06-20</t>
-  </si>
-  <si>
-    <t>2017-06-29</t>
-  </si>
-  <si>
-    <t>2017-07-03</t>
-  </si>
-  <si>
-    <t>2017-07-04</t>
-  </si>
-  <si>
-    <t>2017-07-05</t>
-  </si>
-  <si>
-    <t>2017-07-06</t>
-  </si>
-  <si>
-    <t>2017-10-12</t>
-  </si>
-  <si>
-    <t>2017-10-19</t>
-  </si>
-  <si>
-    <t>2017-10-26</t>
-  </si>
-  <si>
-    <t>2017-10-31</t>
-  </si>
-  <si>
-    <t>2018-03-15</t>
-  </si>
-  <si>
-    <t>2018-06-05</t>
-  </si>
-  <si>
-    <t>2018-06-08</t>
-  </si>
-  <si>
-    <t>2018-05-16</t>
-  </si>
-  <si>
-    <t>2018-06-13</t>
-  </si>
-  <si>
-    <t>2018-06-14</t>
-  </si>
-  <si>
-    <t>2018-06-19</t>
-  </si>
-  <si>
-    <t>2018-06-29</t>
-  </si>
-  <si>
-    <t>2018-07-12</t>
-  </si>
-  <si>
-    <t>2018-07-04</t>
-  </si>
-  <si>
-    <t>2018-07-13</t>
-  </si>
-  <si>
-    <t>2018-07-16</t>
-  </si>
-  <si>
-    <t>2018-07-18</t>
-  </si>
-  <si>
-    <t>2018-11-05</t>
-  </si>
-  <si>
-    <t>2018-11-15</t>
-  </si>
-  <si>
-    <t>2018-11-19</t>
-  </si>
-  <si>
-    <t>2018-11-07</t>
-  </si>
-  <si>
-    <t>2018-11-21</t>
-  </si>
-  <si>
-    <t>2018-11-22</t>
-  </si>
-  <si>
-    <t>2018-11-27</t>
-  </si>
-  <si>
-    <t>2018-12-03</t>
-  </si>
-  <si>
-    <t>2018-12-04</t>
-  </si>
-  <si>
-    <t>2018-12-10</t>
-  </si>
-  <si>
-    <t>2018-12-11</t>
-  </si>
-  <si>
-    <t>2019-05-09</t>
-  </si>
-  <si>
-    <t>2019-05-27</t>
-  </si>
-  <si>
-    <t>2019-05-30</t>
-  </si>
-  <si>
-    <t>2019-06-25</t>
-  </si>
-  <si>
-    <t>2019-07-04</t>
-  </si>
-  <si>
-    <t>2019-07-08</t>
-  </si>
-  <si>
-    <t>2019-07-09</t>
-  </si>
-  <si>
-    <t>2019-07-15</t>
-  </si>
-  <si>
-    <t>2019-07-16</t>
-  </si>
-  <si>
-    <t>2019-07-17</t>
-  </si>
-  <si>
-    <t>2019-07-18</t>
-  </si>
-  <si>
-    <t>2019-07-22</t>
-  </si>
-  <si>
-    <t>2019-07-23</t>
-  </si>
-  <si>
-    <t>2019-07-24</t>
-  </si>
-  <si>
-    <t>2019-07-25</t>
-  </si>
-  <si>
-    <t>2019-09-19</t>
-  </si>
-  <si>
-    <t>2019-09-23</t>
-  </si>
-  <si>
-    <t>2019-09-27</t>
-  </si>
-  <si>
-    <t>2019-09-06</t>
-  </si>
-  <si>
-    <t>2019-09-30</t>
-  </si>
-  <si>
-    <t>2019-11-25</t>
-  </si>
-  <si>
-    <t>2020-07-14</t>
-  </si>
-  <si>
-    <t>2020-07-24</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>2020-08-18</t>
-  </si>
-  <si>
-    <t>2020-08-12</t>
-  </si>
-  <si>
-    <t>2020-08-19</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>2020-12-08</t>
-  </si>
-  <si>
-    <t>2020-12-09</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>2021-05-10</t>
-  </si>
-  <si>
-    <t>2021-05-12</t>
-  </si>
-  <si>
-    <t>2021-04-22</t>
-  </si>
-  <si>
-    <t>2021-05-14</t>
-  </si>
-  <si>
-    <t>2021-05-18</t>
-  </si>
-  <si>
-    <t>2021-05-20</t>
-  </si>
-  <si>
-    <t>2021-05-26</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>2021-05-27</t>
-  </si>
-  <si>
-    <t>2021-05-21</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>2021-06-10</t>
-  </si>
-  <si>
-    <t>2021-06-15</t>
-  </si>
-  <si>
-    <t>2021-06-16</t>
-  </si>
-  <si>
-    <t>2021-06-18</t>
-  </si>
-  <si>
-    <t>2021-06-28</t>
-  </si>
-  <si>
-    <t>2021-10-29</t>
-  </si>
-  <si>
-    <t>2021-11-02</t>
-  </si>
-  <si>
-    <t>2021-11-12</t>
-  </si>
-  <si>
-    <t>2021-11-22</t>
-  </si>
-  <si>
-    <t>2021-11-23</t>
-  </si>
-  <si>
-    <t>2021-11-16</t>
-  </si>
-  <si>
-    <t>2016-05-24</t>
-  </si>
-  <si>
-    <t>2016-05-26</t>
-  </si>
-  <si>
-    <t>2016-05-27</t>
-  </si>
-  <si>
-    <t>2016-05-30</t>
-  </si>
-  <si>
-    <t>2016-06-01</t>
-  </si>
-  <si>
-    <t>2016-06-02</t>
-  </si>
-  <si>
-    <t>2016-06-06</t>
-  </si>
-  <si>
-    <t>2016-06-15</t>
-  </si>
-  <si>
-    <t>2016-06-16</t>
-  </si>
-  <si>
-    <t>2016-06-17</t>
-  </si>
-  <si>
-    <t>2016-06-20</t>
-  </si>
-  <si>
-    <t>2016-06-21</t>
-  </si>
-  <si>
-    <t>2016-06-23</t>
-  </si>
-  <si>
-    <t>2016-06-24</t>
-  </si>
-  <si>
-    <t>2016-06-27</t>
-  </si>
-  <si>
-    <t>2016-06-30</t>
-  </si>
-  <si>
-    <t>2016-12-06</t>
-  </si>
-  <si>
-    <t>2016-12-07</t>
-  </si>
-  <si>
-    <t>2016-12-08</t>
-  </si>
-  <si>
-    <t>2016-12-14</t>
-  </si>
-  <si>
-    <t>2017-01-06</t>
-  </si>
-  <si>
-    <t>2017-01-09</t>
-  </si>
-  <si>
-    <t>2017-01-11</t>
-  </si>
-  <si>
-    <t>2017-01-12</t>
-  </si>
-  <si>
-    <t>2017-02-03</t>
-  </si>
-  <si>
-    <t>2017-03-24</t>
-  </si>
-  <si>
-    <t>2017-03-27</t>
-  </si>
-  <si>
-    <t>2017-03-29</t>
-  </si>
-  <si>
-    <t>2017-03-30</t>
-  </si>
-  <si>
-    <t>2017-03-31</t>
-  </si>
-  <si>
-    <t>2017-04-06</t>
-  </si>
-  <si>
-    <t>2017-04-07</t>
-  </si>
-  <si>
-    <t>2017-04-10</t>
-  </si>
-  <si>
-    <t>2017-04-11</t>
-  </si>
-  <si>
-    <t>2017-04-12</t>
-  </si>
-  <si>
-    <t>2017-04-13</t>
-  </si>
-  <si>
-    <t>2017-04-19</t>
-  </si>
-  <si>
-    <t>2017-04-21</t>
-  </si>
-  <si>
-    <t>2017-04-28</t>
-  </si>
-  <si>
-    <t>2017-05-11</t>
-  </si>
-  <si>
-    <t>2017-05-15</t>
-  </si>
-  <si>
-    <t>2017-05-18</t>
-  </si>
-  <si>
-    <t>2017-05-19</t>
-  </si>
-  <si>
-    <t>2017-05-22</t>
-  </si>
-  <si>
-    <t>2017-10-09</t>
-  </si>
-  <si>
-    <t>2017-10-11</t>
-  </si>
-  <si>
-    <t>2018-02-09</t>
-  </si>
-  <si>
-    <t>2018-05-07</t>
-  </si>
-  <si>
-    <t>2018-05-08</t>
-  </si>
-  <si>
-    <t>2018-05-09</t>
-  </si>
-  <si>
-    <t>2018-05-10</t>
-  </si>
-  <si>
-    <t>2018-05-11</t>
-  </si>
-  <si>
-    <t>2018-05-14</t>
-  </si>
-  <si>
-    <t>2018-05-17</t>
-  </si>
-  <si>
-    <t>2018-05-25</t>
-  </si>
-  <si>
-    <t>2018-05-30</t>
-  </si>
-  <si>
-    <t>2018-05-31</t>
-  </si>
-  <si>
-    <t>2018-06-15</t>
-  </si>
-  <si>
-    <t>2018-06-20</t>
-  </si>
-  <si>
-    <t>2018-06-21</t>
-  </si>
-  <si>
-    <t>2018-06-25</t>
-  </si>
-  <si>
-    <t>2018-10-19</t>
-  </si>
-  <si>
-    <t>2018-10-22</t>
-  </si>
-  <si>
-    <t>2018-10-23</t>
-  </si>
-  <si>
-    <t>2018-10-26</t>
-  </si>
-  <si>
-    <t>2018-10-29</t>
-  </si>
-  <si>
-    <t>2018-10-31</t>
-  </si>
-  <si>
-    <t>2018-11-13</t>
-  </si>
-  <si>
-    <t>2019-04-23</t>
-  </si>
-  <si>
-    <t>2019-04-24</t>
-  </si>
-  <si>
-    <t>2019-05-14</t>
-  </si>
-  <si>
-    <t>2019-05-15</t>
-  </si>
-  <si>
-    <t>2019-05-16</t>
-  </si>
-  <si>
-    <t>2019-06-05</t>
-  </si>
-  <si>
-    <t>2019-06-10</t>
-  </si>
-  <si>
-    <t>2019-06-12</t>
-  </si>
-  <si>
-    <t>2019-06-13</t>
-  </si>
-  <si>
-    <t>2019-06-14</t>
-  </si>
-  <si>
-    <t>2019-06-17</t>
-  </si>
-  <si>
-    <t>2019-06-18</t>
-  </si>
-  <si>
-    <t>2019-06-20</t>
-  </si>
-  <si>
-    <t>2019-06-26</t>
-  </si>
-  <si>
-    <t>2019-08-26</t>
-  </si>
-  <si>
-    <t>2019-08-27</t>
-  </si>
-  <si>
-    <t>2019-08-30</t>
-  </si>
-  <si>
-    <t>2019-09-02</t>
-  </si>
-  <si>
-    <t>2019-11-05</t>
-  </si>
-  <si>
-    <t>2020-06-15</t>
-  </si>
-  <si>
-    <t>2020-07-15</t>
-  </si>
-  <si>
-    <t>2020-07-16</t>
-  </si>
-  <si>
-    <t>2020-07-17</t>
-  </si>
-  <si>
-    <t>2020-07-21</t>
-  </si>
-  <si>
-    <t>2020-07-22</t>
-  </si>
-  <si>
-    <t>2020-07-23</t>
-  </si>
-  <si>
-    <t>2020-07-27</t>
-  </si>
-  <si>
-    <t>2020-11-03</t>
-  </si>
-  <si>
-    <t>2020-11-04</t>
-  </si>
-  <si>
-    <t>2020-11-12</t>
-  </si>
-  <si>
-    <t>2021-03-02</t>
-  </si>
-  <si>
-    <t>2021-04-08</t>
-  </si>
-  <si>
-    <t>2021-04-09</t>
-  </si>
-  <si>
-    <t>2021-04-12</t>
-  </si>
-  <si>
-    <t>2021-04-13</t>
-  </si>
-  <si>
-    <t>2021-04-14</t>
-  </si>
-  <si>
-    <t>2021-04-15</t>
-  </si>
-  <si>
-    <t>2021-04-16</t>
-  </si>
-  <si>
-    <t>2021-04-19</t>
-  </si>
-  <si>
-    <t>2021-04-20</t>
-  </si>
-  <si>
-    <t>2021-04-23</t>
-  </si>
-  <si>
-    <t>2021-04-26</t>
-  </si>
-  <si>
-    <t>2021-04-27</t>
-  </si>
-  <si>
-    <t>2021-04-29</t>
-  </si>
-  <si>
-    <t>2021-10-15</t>
-  </si>
-  <si>
-    <t>2021-10-18</t>
-  </si>
-  <si>
-    <t>2021-10-19</t>
-  </si>
-  <si>
-    <t>2021-10-26</t>
-  </si>
-  <si>
-    <t>2021-10-27</t>
-  </si>
-  <si>
-    <t>2021-10-28</t>
-  </si>
-  <si>
-    <t>2021-11-03</t>
-  </si>
-  <si>
-    <t>2021-11-04</t>
   </si>
 </sst>
 </file>
@@ -1568,7 +1565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P522"/>
+  <dimension ref="A1:P521"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1629,7 +1626,7 @@
         <v>2.636521639996683</v>
       </c>
       <c r="D2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E2">
         <v>2.833647241107702</v>
@@ -1665,7 +1662,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1679,7 +1676,7 @@
         <v>2.808801457176021</v>
       </c>
       <c r="D3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E3">
         <v>2.7135041663212</v>
@@ -1715,7 +1712,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1729,7 +1726,7 @@
         <v>2.746397091058633</v>
       </c>
       <c r="D4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E4">
         <v>2.648930323263125</v>
@@ -1779,7 +1776,7 @@
         <v>2.683209227271539</v>
       </c>
       <c r="D5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E5">
         <v>2.583545744375049</v>
@@ -1815,7 +1812,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1829,7 +1826,7 @@
         <v>2.555958070922727</v>
       </c>
       <c r="D6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E6">
         <v>2.632522016358742</v>
@@ -1865,7 +1862,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1879,7 +1876,7 @@
         <v>2.641252819939413</v>
       </c>
       <c r="D7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E7">
         <v>2.540130729835057</v>
@@ -1915,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1929,7 +1926,7 @@
         <v>2.512285655110759</v>
       </c>
       <c r="D8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E8">
         <v>2.590994611146576</v>
@@ -1965,7 +1962,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1979,7 +1976,7 @@
         <v>2.615441102246784</v>
       </c>
       <c r="D9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E9">
         <v>2.513421672263544</v>
@@ -2015,7 +2012,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2029,7 +2026,7 @@
         <v>2.515418243442972</v>
       </c>
       <c r="D10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E10">
         <v>2.545423958143926</v>
@@ -2065,7 +2062,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2079,7 +2076,7 @@
         <v>2.487273994427867</v>
       </c>
       <c r="D11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E11">
         <v>2.567211421027677</v>
@@ -2115,7 +2112,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2129,7 +2126,7 @@
         <v>2.487984580081365</v>
       </c>
       <c r="D12" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E12">
         <v>2.579898802553291</v>
@@ -2165,7 +2162,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2179,7 +2176,7 @@
         <v>2.500805561667341</v>
       </c>
       <c r="D13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E13">
         <v>2.59216563562278</v>
@@ -2215,7 +2212,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2229,7 +2226,7 @@
         <v>2.499441989042522</v>
       </c>
       <c r="D14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E14">
         <v>2.736702547602069</v>
@@ -2279,7 +2276,7 @@
         <v>2.512520850741042</v>
       </c>
       <c r="D15" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E15">
         <v>2.749061943431123</v>
@@ -2315,7 +2312,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2329,7 +2326,7 @@
         <v>2.77984350091858</v>
       </c>
       <c r="D16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E16">
         <v>2.889061943431122</v>
@@ -2365,7 +2362,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2379,7 +2376,7 @@
         <v>2.517224153471577</v>
       </c>
       <c r="D17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E17">
         <v>2.753506518310076</v>
@@ -2415,7 +2412,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2429,7 +2426,7 @@
         <v>2.784426680003737</v>
       </c>
       <c r="D18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E18">
         <v>2.924119959439183</v>
@@ -2465,7 +2462,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2479,7 +2476,7 @@
         <v>2.884280694854824</v>
       </c>
       <c r="D19" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E19">
         <v>2.961861794886389</v>
@@ -2529,7 +2526,7 @@
         <v>2.920719956495094</v>
       </c>
       <c r="D20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E20">
         <v>2.907075620138133</v>
@@ -2565,7 +2562,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2579,7 +2576,7 @@
         <v>2.648180125005333</v>
       </c>
       <c r="D21" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E21">
         <v>2.848908919700521</v>
@@ -2615,7 +2612,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2665,7 +2662,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2679,7 +2676,7 @@
         <v>2.691620213913162</v>
       </c>
       <c r="D23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E23">
         <v>2.889959376998489</v>
@@ -2715,7 +2712,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2729,7 +2726,7 @@
         <v>2.984719616116966</v>
       </c>
       <c r="D24" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E24">
         <v>2.755965243802971</v>
@@ -2765,7 +2762,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2779,7 +2776,7 @@
         <v>3.007275184023352</v>
       </c>
       <c r="D25" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E25">
         <v>2.755965243802971</v>
@@ -2815,7 +2812,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2829,7 +2826,7 @@
         <v>2.683495528297218</v>
       </c>
       <c r="D26" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E26">
         <v>2.882281628901694</v>
@@ -2865,7 +2862,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2879,7 +2876,7 @@
         <v>2.976914171586129</v>
       </c>
       <c r="D27" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E27">
         <v>2.747824596132772</v>
@@ -2915,7 +2912,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2929,7 +2926,7 @@
         <v>2.647048085674867</v>
       </c>
       <c r="D28" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E28">
         <v>2.84783915365346</v>
@@ -2965,7 +2962,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2979,7 +2976,7 @@
         <v>2.941898848516719</v>
       </c>
       <c r="D29" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E29">
         <v>2.711305547532774</v>
@@ -3015,7 +3012,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3029,7 +3026,7 @@
         <v>2.962790623816959</v>
       </c>
       <c r="D30" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E30">
         <v>2.711305547532774</v>
@@ -3065,7 +3062,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3079,7 +3076,7 @@
         <v>2.636850318680218</v>
       </c>
       <c r="D31" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E31">
         <v>2.674077933106496</v>
@@ -3115,7 +3112,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3129,7 +3126,7 @@
         <v>2.64386308474694</v>
       </c>
       <c r="D32" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E32">
         <v>2.844829359063415</v>
@@ -3165,7 +3162,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3179,7 +3176,7 @@
         <v>2.938838994972993</v>
       </c>
       <c r="D33" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E33">
         <v>2.708114289235636</v>
@@ -3215,7 +3212,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3229,7 +3226,7 @@
         <v>2.959611880258242</v>
       </c>
       <c r="D34" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E34">
         <v>2.708114289235636</v>
@@ -3265,7 +3262,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3279,7 +3276,7 @@
         <v>2.63362151616782</v>
       </c>
       <c r="D35" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E35">
         <v>2.706375129633912</v>
@@ -3315,7 +3312,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3329,7 +3326,7 @@
         <v>2.623711665472045</v>
       </c>
       <c r="D36" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E36">
         <v>2.825786465799713</v>
@@ -3365,7 +3362,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3379,7 +3376,7 @@
         <v>2.919479379991807</v>
       </c>
       <c r="D37" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E37">
         <v>2.687923279746057</v>
@@ -3415,7 +3412,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3429,7 +3426,7 @@
         <v>2.939500051198033</v>
       </c>
       <c r="D38" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E38">
         <v>2.687923279746057</v>
@@ -3465,7 +3462,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3479,7 +3476,7 @@
         <v>2.613192965390128</v>
       </c>
       <c r="D39" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E39">
         <v>2.65740457966414</v>
@@ -3515,7 +3512,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3529,7 +3526,7 @@
         <v>2.866121269202039</v>
       </c>
       <c r="D40" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E40">
         <v>2.632273716345684</v>
@@ -3579,7 +3576,7 @@
         <v>2.884068721379623</v>
       </c>
       <c r="D41" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E41">
         <v>2.632273716345684</v>
@@ -3629,7 +3626,7 @@
         <v>2.556888701243869</v>
       </c>
       <c r="D42" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E42">
         <v>2.5709911987269</v>
@@ -3679,7 +3676,7 @@
         <v>2.84066903268222</v>
       </c>
       <c r="D43" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E43">
         <v>2.605728438993726</v>
@@ -3715,7 +3712,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3729,7 +3726,7 @@
         <v>2.857627543154535</v>
       </c>
       <c r="D44" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E44">
         <v>2.605728438993726</v>
@@ -3765,7 +3762,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3779,7 +3776,7 @@
         <v>2.530031126511299</v>
       </c>
       <c r="D45" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E45">
         <v>2.536232918189681</v>
@@ -3815,7 +3812,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3829,7 +3826,7 @@
         <v>2.794653597980052</v>
       </c>
       <c r="D46" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E46">
         <v>2.557736881328888</v>
@@ -3865,7 +3862,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3879,7 +3876,7 @@
         <v>2.809824187676618</v>
       </c>
       <c r="D47" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E47">
         <v>2.557736881328888</v>
@@ -3915,7 +3912,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3965,7 +3962,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3979,7 +3976,7 @@
         <v>2.877968395292299</v>
       </c>
       <c r="D49" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E49">
         <v>2.644629614722029</v>
@@ -4015,7 +4012,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4029,7 +4026,7 @@
         <v>2.896376165252531</v>
       </c>
       <c r="D50" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E50">
         <v>2.644629614722029</v>
@@ -4065,7 +4062,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4079,7 +4076,7 @@
         <v>2.521770137334771</v>
       </c>
       <c r="D51" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E51">
         <v>2.535896862069519</v>
@@ -4115,7 +4112,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4129,7 +4126,7 @@
         <v>2.934431839092635</v>
       </c>
       <c r="D52" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E52">
         <v>2.703517868992319</v>
@@ -4165,7 +4162,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4179,7 +4176,7 @@
         <v>2.955033485192349</v>
       </c>
       <c r="D53" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E53">
         <v>2.703517868992319</v>
@@ -4215,7 +4212,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4265,7 +4262,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4279,7 +4276,7 @@
         <v>2.974730272968942</v>
       </c>
       <c r="D55" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E55">
         <v>2.745546910458406</v>
@@ -4315,7 +4312,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4329,7 +4326,7 @@
         <v>2.996897706887981</v>
       </c>
       <c r="D56" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E56">
         <v>2.745546910458406</v>
@@ -4365,7 +4362,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4379,7 +4376,7 @@
         <v>2.624468326525319</v>
       </c>
       <c r="D57" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E57">
         <v>2.660688149733082</v>
@@ -4415,7 +4412,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4429,7 +4426,7 @@
         <v>3.056805462611843</v>
       </c>
       <c r="D58" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E58">
         <v>2.831146801497014</v>
@@ -4465,7 +4462,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4515,7 +4512,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4529,7 +4526,7 @@
         <v>3.075488420323122</v>
       </c>
       <c r="D60" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E60">
         <v>2.850632094815525</v>
@@ -4579,7 +4576,7 @@
         <v>2.73140795531227</v>
       </c>
       <c r="D61" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E61">
         <v>2.75953055997749</v>
@@ -4629,7 +4626,7 @@
         <v>2.72765316464271</v>
       </c>
       <c r="D62" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E62">
         <v>2.75953055997749</v>
@@ -4679,7 +4676,7 @@
         <v>2.72671446697532</v>
       </c>
       <c r="D63" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E63">
         <v>2.75953055997749</v>
@@ -4729,7 +4726,7 @@
         <v>6.293149296554828</v>
       </c>
       <c r="D64" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E64">
         <v>5.963700498102364</v>
@@ -4765,7 +4762,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4779,7 +4776,7 @@
         <v>6.420239880180696</v>
       </c>
       <c r="D65" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E65">
         <v>6.082402264327184</v>
@@ -4815,7 +4812,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4829,7 +4826,7 @@
         <v>6.609514294497387</v>
       </c>
       <c r="D66" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E66">
         <v>6.259183317962906</v>
@@ -4865,7 +4862,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4879,7 +4876,7 @@
         <v>6.515171551263329</v>
       </c>
       <c r="D67" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E67">
         <v>6.612047937164794</v>
@@ -4915,7 +4912,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4929,7 +4926,7 @@
         <v>6.520829737768901</v>
       </c>
       <c r="D68" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E68">
         <v>6.612047937164794</v>
@@ -4965,7 +4962,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5015,7 +5012,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5065,7 +5062,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5115,7 +5112,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5129,7 +5126,7 @@
         <v>6.781478804637512</v>
       </c>
       <c r="D72" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E72">
         <v>6.821616798629249</v>
@@ -5165,7 +5162,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5179,7 +5176,7 @@
         <v>6.927933775178332</v>
       </c>
       <c r="D73" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E73">
         <v>7.025464228815041</v>
@@ -5215,7 +5212,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5229,7 +5226,7 @@
         <v>7.465293617228137</v>
       </c>
       <c r="D74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E74">
         <v>7.441132824526438</v>
@@ -5265,7 +5262,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5279,7 +5276,7 @@
         <v>2.399740228983164</v>
       </c>
       <c r="D75" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E75">
         <v>2.284756328614283</v>
@@ -5315,7 +5312,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5329,7 +5326,7 @@
         <v>2.181146111927123</v>
       </c>
       <c r="D76" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E76">
         <v>2.105842395854763</v>
@@ -5365,7 +5362,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5379,7 +5376,7 @@
         <v>2.180858495485883</v>
       </c>
       <c r="D77" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E77">
         <v>2.105842395854763</v>
@@ -5415,7 +5412,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5429,7 +5426,7 @@
         <v>2.355267416838251</v>
       </c>
       <c r="D78" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E78">
         <v>2.241615480893012</v>
@@ -5465,7 +5462,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5479,7 +5476,7 @@
         <v>2.138079262229388</v>
       </c>
       <c r="D79" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E79">
         <v>2.115876072829124</v>
@@ -5515,7 +5512,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5529,7 +5526,7 @@
         <v>2.136977667529256</v>
       </c>
       <c r="D80" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E80">
         <v>2.115876072829124</v>
@@ -5565,7 +5562,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5615,7 +5612,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5665,7 +5662,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5715,7 +5712,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5729,7 +5726,7 @@
         <v>1.925553832103902</v>
       </c>
       <c r="D84" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E84">
         <v>1.985821650998686</v>
@@ -5765,7 +5762,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5815,7 +5812,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5829,7 +5826,7 @@
         <v>1.87975631937778</v>
       </c>
       <c r="D86" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E86">
         <v>2.025900250164519</v>
@@ -5865,7 +5862,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5965,7 +5962,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5979,7 +5976,7 @@
         <v>1.789383875507923</v>
       </c>
       <c r="D89" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E89">
         <v>1.940268655809146</v>
@@ -6015,7 +6012,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6029,7 +6026,7 @@
         <v>1.804905667333501</v>
       </c>
       <c r="D90" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E90">
         <v>1.95497618970289</v>
@@ -6065,7 +6062,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6079,7 +6076,7 @@
         <v>1.809491967335235</v>
       </c>
       <c r="D91" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E91">
         <v>1.959321896917648</v>
@@ -6115,7 +6112,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6129,7 +6126,7 @@
         <v>1.822908408572121</v>
       </c>
       <c r="D92" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E92">
         <v>1.972034524843747</v>
@@ -6165,7 +6162,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6179,7 +6176,7 @@
         <v>2.011491451443282</v>
       </c>
       <c r="D93" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E93">
         <v>1.930405304642352</v>
@@ -6215,7 +6212,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6229,7 +6226,7 @@
         <v>1.820166348365971</v>
       </c>
       <c r="D94" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E94">
         <v>1.969436310418903</v>
@@ -6265,7 +6262,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6279,7 +6276,7 @@
         <v>2.008879751476441</v>
       </c>
       <c r="D95" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E95">
         <v>1.927766633591516</v>
@@ -6315,7 +6312,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6329,7 +6326,7 @@
         <v>1.780154910291897</v>
       </c>
       <c r="D96" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E96">
         <v>1.931523833030682</v>
@@ -6365,7 +6362,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6415,7 +6412,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6429,7 +6426,7 @@
         <v>1.781411528733962</v>
       </c>
       <c r="D98" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E98">
         <v>1.932714530505294</v>
@@ -6465,7 +6462,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6515,7 +6512,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6529,7 +6526,7 @@
         <v>1.786869994736246</v>
       </c>
       <c r="D100" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E100">
         <v>1.937886650750082</v>
@@ -6579,7 +6576,7 @@
         <v>1.77389224303264</v>
       </c>
       <c r="D101" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E101">
         <v>1.925589699135846</v>
@@ -6615,7 +6612,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6629,7 +6626,7 @@
         <v>1.764225388294109</v>
       </c>
       <c r="D102" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E102">
         <v>1.916429958088516</v>
@@ -6829,7 +6826,7 @@
         <v>2.039049007419374</v>
       </c>
       <c r="D106" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E106">
         <v>1.958247448115615</v>
@@ -6865,7 +6862,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6879,7 +6876,7 @@
         <v>1.963804213639886</v>
       </c>
       <c r="D107" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E107">
         <v>2.044635472991321</v>
@@ -6915,7 +6912,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6929,7 +6926,7 @@
         <v>2.084469221121035</v>
       </c>
       <c r="D108" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E108">
         <v>2.00413671738046</v>
@@ -6965,7 +6962,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6979,7 +6976,7 @@
         <v>1.970692549466935</v>
       </c>
       <c r="D109" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E109">
         <v>2.103970465510173</v>
@@ -7015,7 +7012,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7065,7 +7062,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7079,7 +7076,7 @@
         <v>1.989826166099606</v>
       </c>
       <c r="D111" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E111">
         <v>2.069999197311251</v>
@@ -7115,7 +7112,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7129,7 +7126,7 @@
         <v>1.996538974422711</v>
       </c>
       <c r="D112" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E112">
         <v>2.129860772341935</v>
@@ -7165,7 +7162,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7215,7 +7212,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7229,7 +7226,7 @@
         <v>1.976959483296697</v>
       </c>
       <c r="D114" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E114">
         <v>2.110248039295503</v>
@@ -7329,7 +7326,7 @@
         <v>1.920546112528168</v>
       </c>
       <c r="D116" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E116">
         <v>2.053738890308352</v>
@@ -7365,7 +7362,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7415,7 +7412,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7429,7 +7426,7 @@
         <v>2.078859445890371</v>
       </c>
       <c r="D118" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E118">
         <v>2.128859445890371</v>
@@ -7465,7 +7462,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7479,7 +7476,7 @@
         <v>1.864471846503076</v>
       </c>
       <c r="D119" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E119">
         <v>1.997569421794252</v>
@@ -7515,7 +7512,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7565,7 +7562,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7615,7 +7612,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7629,7 +7626,7 @@
         <v>1.863420505387863</v>
       </c>
       <c r="D122" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E122">
         <v>1.996516295719591</v>
@@ -7729,7 +7726,7 @@
         <v>2.029857360363785</v>
       </c>
       <c r="D124" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E124">
         <v>2.011995247378231</v>
@@ -7779,7 +7776,7 @@
         <v>1.892165706973767</v>
       </c>
       <c r="D125" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E125">
         <v>2.025310300703773</v>
@@ -7815,7 +7812,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7865,7 +7862,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7915,7 +7912,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7979,7 +7976,7 @@
         <v>2.183293967129219</v>
       </c>
       <c r="D129" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E129">
         <v>2.097698061214447</v>
@@ -8029,7 +8026,7 @@
         <v>2.10409703769314</v>
       </c>
       <c r="D130" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E130">
         <v>2.097698061214447</v>
@@ -8115,7 +8112,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8165,7 +8162,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8215,7 +8212,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8265,7 +8262,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8315,7 +8312,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8365,7 +8362,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8415,7 +8412,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8465,7 +8462,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8479,7 +8476,7 @@
         <v>2.367284598691813</v>
       </c>
       <c r="D139" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E139">
         <v>2.284677125480481</v>
@@ -8529,7 +8526,7 @@
         <v>2.308705785003503</v>
       </c>
       <c r="D140" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E140">
         <v>2.284677125480481</v>
@@ -8665,7 +8662,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8715,7 +8712,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8765,7 +8762,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8815,7 +8812,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8865,7 +8862,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8929,7 +8926,7 @@
         <v>2.673055621612132</v>
       </c>
       <c r="D148" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E148">
         <v>2.649383477311975</v>
@@ -8979,7 +8976,7 @@
         <v>2.694510447967022</v>
       </c>
       <c r="D149" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E149">
         <v>2.66746656530884</v>
@@ -9029,7 +9026,7 @@
         <v>2.61961842602696</v>
       </c>
       <c r="D150" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E150">
         <v>2.674946565009619</v>
@@ -9315,7 +9312,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9329,7 +9326,7 @@
         <v>2.746485076848839</v>
       </c>
       <c r="D156" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E156">
         <v>2.847982602490786</v>
@@ -9365,7 +9362,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9429,7 +9426,7 @@
         <v>2.750734210259811</v>
       </c>
       <c r="D158" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E158">
         <v>2.800734210259812</v>
@@ -9465,7 +9462,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9529,7 +9526,7 @@
         <v>2.717092536535202</v>
       </c>
       <c r="D160" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E160">
         <v>2.791717770085309</v>
@@ -9615,7 +9612,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9629,7 +9626,7 @@
         <v>2.669840281895235</v>
       </c>
       <c r="D162" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E162">
         <v>2.754805459723328</v>
@@ -9665,7 +9662,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9729,7 +9726,7 @@
         <v>2.704152220032186</v>
       </c>
       <c r="D164" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E164">
         <v>2.721608307945189</v>
@@ -9779,7 +9776,7 @@
         <v>0.7516342779874527</v>
       </c>
       <c r="D165" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E165">
         <v>0.6447312303040151</v>
@@ -9815,7 +9812,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9829,7 +9826,7 @@
         <v>0.6347312303040145</v>
       </c>
       <c r="D166" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E166">
         <v>0.7803954970608276</v>
@@ -9865,7 +9862,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9879,7 +9876,7 @@
         <v>0.7872985447442655</v>
       </c>
       <c r="D167" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E167">
         <v>0.6685373256708909</v>
@@ -9915,7 +9912,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9929,7 +9926,7 @@
         <v>0.6141118398407031</v>
       </c>
       <c r="D168" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E168">
         <v>0.7042015924277036</v>
@@ -9965,7 +9962,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9979,7 +9976,7 @@
         <v>0.7076194190074974</v>
       </c>
       <c r="D169" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E169">
         <v>0.8524403513495589</v>
@@ -10029,7 +10026,7 @@
         <v>0.8587410173081755</v>
       </c>
       <c r="D170" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E170">
         <v>0.7402207509247285</v>
@@ -10079,7 +10076,7 @@
         <v>0.6868795521992208</v>
       </c>
       <c r="D171" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E171">
         <v>0.7750416832667906</v>
@@ -10129,7 +10126,7 @@
         <v>0.794311018129779</v>
       </c>
       <c r="D172" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E172">
         <v>0.9381289071762104</v>
@@ -10165,7 +10162,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10179,7 +10176,7 @@
         <v>0.7478436529603893</v>
       </c>
       <c r="D173" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E173">
         <v>0.9381289071762104</v>
@@ -10215,7 +10212,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10229,7 +10226,7 @@
         <v>0.9437131136379486</v>
       </c>
       <c r="D174" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E174">
         <v>0.8254794310532532</v>
@@ -10265,7 +10262,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10279,7 +10276,7 @@
         <v>0.7734278594221262</v>
       </c>
       <c r="D175" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E175">
         <v>0.8592973200996861</v>
@@ -10315,7 +10312,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10329,7 +10326,7 @@
         <v>0.9016190641047892</v>
       </c>
       <c r="D176" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E176">
         <v>1.04419537245399</v>
@@ -10365,7 +10362,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10379,7 +10376,7 @@
         <v>0.8558611736195321</v>
       </c>
       <c r="D177" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E177">
         <v>1.04419537245399</v>
@@ -10415,7 +10412,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10429,7 +10426,7 @@
         <v>1.048892735560562</v>
       </c>
       <c r="D178" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E178">
         <v>0.9310137903179339</v>
@@ -10465,7 +10462,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10479,7 +10476,7 @@
         <v>0.8805585367261042</v>
       </c>
       <c r="D179" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E179">
         <v>0.963590098667134</v>
@@ -10515,7 +10512,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10529,7 +10526,7 @@
         <v>1.076170489586433</v>
       </c>
       <c r="D180" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E180">
         <v>1.260525374010979</v>
@@ -10579,7 +10576,7 @@
         <v>1.26341395784032</v>
       </c>
       <c r="D181" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E181">
         <v>1.146258524308584</v>
@@ -10629,7 +10626,7 @@
         <v>1.099059073415773</v>
       </c>
       <c r="D182" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E182">
         <v>1.176302541669659</v>
@@ -10679,7 +10676,7 @@
         <v>1.931268098407571</v>
       </c>
       <c r="D183" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E183">
         <v>1.946759727730396</v>
@@ -10715,7 +10712,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10765,7 +10762,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10815,7 +10812,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10829,7 +10826,7 @@
         <v>0.5942088493584849</v>
       </c>
       <c r="D186" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E186">
         <v>0.5982130518354056</v>
@@ -10865,7 +10862,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10915,7 +10912,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10965,7 +10962,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11015,7 +11012,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11029,7 +11026,7 @@
         <v>-0.02499489055226256</v>
       </c>
       <c r="D190" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E190">
         <v>-0.07499489055226238</v>
@@ -11065,7 +11062,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11079,7 +11076,7 @@
         <v>-0.04541693580813089</v>
       </c>
       <c r="D191" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E191">
         <v>-0.1350880582477796</v>
@@ -11115,7 +11112,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11165,7 +11162,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11215,7 +11212,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11365,7 +11362,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11379,7 +11376,7 @@
         <v>-0.5154661476950757</v>
       </c>
       <c r="D197" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E197">
         <v>-0.4838284745942198</v>
@@ -11415,7 +11412,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11429,7 +11426,7 @@
         <v>-0.5144835438345625</v>
       </c>
       <c r="D198" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E198">
         <v>-0.4838284745942198</v>
@@ -11465,7 +11462,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11515,7 +11512,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11529,7 +11526,7 @@
         <v>-0.6795603356321358</v>
       </c>
       <c r="D200" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E200">
         <v>-0.6353746161347429</v>
@@ -11565,7 +11562,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11579,7 +11576,7 @@
         <v>-0.6770489039336995</v>
       </c>
       <c r="D201" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E201">
         <v>-0.6353746161347429</v>
@@ -11615,7 +11612,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11665,7 +11662,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11679,7 +11676,7 @@
         <v>-1.275160705635463</v>
       </c>
       <c r="D203" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E203">
         <v>-0.9575450227817477</v>
@@ -11715,7 +11712,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11729,7 +11726,7 @@
         <v>-1.267100202166811</v>
       </c>
       <c r="D204" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E204">
         <v>-0.9575450227817477</v>
@@ -11765,7 +11762,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11829,7 +11826,7 @@
         <v>-1.30354206111917</v>
       </c>
       <c r="D206" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E206">
         <v>-0.9846924062879019</v>
@@ -11879,7 +11876,7 @@
         <v>-1.295217135083899</v>
       </c>
       <c r="D207" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E207">
         <v>-0.9846924062879019</v>
@@ -11929,7 +11926,7 @@
         <v>-1.315601110783377</v>
       </c>
       <c r="D208" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E208">
         <v>-0.9962271494449686</v>
@@ -11979,7 +11976,7 @@
         <v>-1.307163833353718</v>
       </c>
       <c r="D209" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E209">
         <v>-0.9962271494449686</v>
@@ -12029,7 +12026,7 @@
         <v>-1.303470101275702</v>
       </c>
       <c r="D210" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E210">
         <v>-0.9846235751332797</v>
@@ -12065,7 +12062,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12079,7 +12076,7 @@
         <v>-1.295145845673754</v>
       </c>
       <c r="D211" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E211">
         <v>-0.9846235751332797</v>
@@ -12115,7 +12112,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12129,7 +12126,7 @@
         <v>-1.352240812118975</v>
       </c>
       <c r="D212" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E212">
         <v>-1.031273820287715</v>
@@ -12165,7 +12162,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12179,7 +12176,7 @@
         <v>-1.343462171012276</v>
       </c>
       <c r="D213" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E213">
         <v>-1.031273820287715</v>
@@ -12215,7 +12212,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12265,7 +12262,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12279,7 +12276,7 @@
         <v>-1.277973836666044</v>
       </c>
       <c r="D215" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E215">
         <v>-0.9602358437675207</v>
@@ -12329,7 +12326,7 @@
         <v>-1.269887123902075</v>
       </c>
       <c r="D216" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E216">
         <v>-0.9602358437675207</v>
@@ -12379,7 +12376,7 @@
         <v>-1.030235843767521</v>
       </c>
       <c r="D217" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E217">
         <v>-1.080019061857596</v>
@@ -12429,7 +12426,7 @@
         <v>-1.007888992711643</v>
       </c>
       <c r="D218" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E218">
         <v>-1.080019061857596</v>
@@ -12479,7 +12476,7 @@
         <v>-1.154349245698821</v>
       </c>
       <c r="D219" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E219">
         <v>-0.8419862350162637</v>
@@ -12529,7 +12526,7 @@
         <v>-1.147414314838273</v>
       </c>
       <c r="D220" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E220">
         <v>-0.8419862350162637</v>
@@ -12679,7 +12676,7 @@
         <v>-0.9332125637434627</v>
       </c>
       <c r="D223" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E223">
         <v>-0.6304641914067899</v>
@@ -12715,7 +12712,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12729,7 +12726,7 @@
         <v>-0.9283379125284608</v>
       </c>
       <c r="D224" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E224">
         <v>-0.6304641914067899</v>
@@ -12765,7 +12762,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12779,7 +12776,7 @@
         <v>-1.078298911794628</v>
       </c>
       <c r="D225" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E225">
         <v>-0.7337942740491279</v>
@@ -12829,7 +12826,7 @@
         <v>-1.284045732215318</v>
       </c>
       <c r="D226" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E226">
         <v>-0.9315166474955321</v>
@@ -12879,7 +12876,7 @@
         <v>-1.074552792811861</v>
       </c>
       <c r="D227" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E227">
         <v>-0.7301942595508679</v>
@@ -12915,7 +12912,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12929,7 +12926,7 @@
         <v>0.6306184682796347</v>
       </c>
       <c r="D228" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E228">
         <v>0.8825890610024754</v>
@@ -12965,7 +12962,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12979,7 +12976,7 @@
         <v>2.500083924851446</v>
       </c>
       <c r="D229" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E229">
         <v>2.721828222716436</v>
@@ -13015,7 +13012,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13029,7 +13026,7 @@
         <v>2.484743417251086</v>
       </c>
       <c r="D230" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E230">
         <v>2.721828222716436</v>
@@ -13065,7 +13062,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13079,7 +13076,7 @@
         <v>2.959498476516616</v>
       </c>
       <c r="D231" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E231">
         <v>3.019498476516616</v>
@@ -13115,7 +13112,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13165,7 +13162,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13179,7 +13176,7 @@
         <v>3.973072767193392</v>
       </c>
       <c r="D233" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E233">
         <v>3.630196829293595</v>
@@ -13215,7 +13212,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13265,7 +13262,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13315,7 +13312,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13329,7 +13326,7 @@
         <v>4.556254256131551</v>
       </c>
       <c r="D236" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E236">
         <v>4.211276763316661</v>
@@ -13365,7 +13362,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13415,7 +13412,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13465,7 +13462,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13479,7 +13476,7 @@
         <v>4.667791750685101</v>
       </c>
       <c r="D239" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E239">
         <v>4.322412320952902</v>
@@ -13515,7 +13512,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13529,7 +13526,7 @@
         <v>4.273963746622406</v>
       </c>
       <c r="D240" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E240">
         <v>4.266274031756307</v>
@@ -13565,7 +13562,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13615,7 +13612,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13665,7 +13662,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13679,7 +13676,7 @@
         <v>3.655351043939968</v>
       </c>
       <c r="D243" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E243">
         <v>3.313620049187031</v>
@@ -13715,7 +13712,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13729,7 +13726,7 @@
         <v>2.349652973133038</v>
       </c>
       <c r="D244" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E244">
         <v>2.585321458264525</v>
@@ -13779,7 +13776,7 @@
         <v>2.337296219946928</v>
       </c>
       <c r="D245" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E245">
         <v>2.585321458264525</v>
@@ -13829,7 +13826,7 @@
         <v>2.821499834857581</v>
       </c>
       <c r="D246" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E246">
         <v>2.482773709326562</v>
@@ -13879,7 +13876,7 @@
         <v>1.399171925433256</v>
       </c>
       <c r="D247" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E247">
         <v>1.7228188215915</v>
@@ -13915,7 +13912,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13929,7 +13926,7 @@
         <v>1.94957093986026</v>
       </c>
       <c r="D248" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E248">
         <v>1.61398690043734</v>
@@ -13965,7 +13962,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13979,7 +13976,7 @@
         <v>1.388298565840941</v>
       </c>
       <c r="D249" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E249">
         <v>1.05473712956764</v>
@@ -14029,7 +14026,7 @@
         <v>1.206849236469149</v>
       </c>
       <c r="D250" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E250">
         <v>0.8739416716530437</v>
@@ -14079,7 +14076,7 @@
         <v>1.250249534396463</v>
       </c>
       <c r="D251" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E251">
         <v>0.9171855721103492</v>
@@ -14129,7 +14126,7 @@
         <v>1.265784593473219</v>
       </c>
       <c r="D252" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E252">
         <v>0.9326646489922341</v>
@@ -14165,7 +14162,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14179,7 +14176,7 @@
         <v>1.181086185990114</v>
       </c>
       <c r="D253" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E253">
         <v>0.8482714609955542</v>
@@ -14229,7 +14226,7 @@
         <v>3.393868635799184</v>
       </c>
       <c r="D254" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E254">
         <v>3.232668972857903</v>
@@ -14265,7 +14262,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14279,7 +14276,7 @@
         <v>3.344337857016143</v>
       </c>
       <c r="D255" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E255">
         <v>3.232668972857903</v>
@@ -14315,7 +14312,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14329,7 +14326,7 @@
         <v>3.108144846549583</v>
       </c>
       <c r="D256" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E256">
         <v>3.176241351782863</v>
@@ -14365,7 +14362,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14379,7 +14376,7 @@
         <v>3.110765478091183</v>
       </c>
       <c r="D257" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E257">
         <v>3.176241351782863</v>
@@ -14415,7 +14412,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14429,7 +14426,7 @@
         <v>3.484929217459694</v>
       </c>
       <c r="D258" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E258">
         <v>3.328403460479749</v>
@@ -14465,7 +14462,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14479,7 +14476,7 @@
         <v>3.438944160440425</v>
       </c>
       <c r="D259" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E259">
         <v>3.328403460479749</v>
@@ -14515,7 +14512,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14565,7 +14562,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14615,7 +14612,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14629,7 +14626,7 @@
         <v>3.67612531160249</v>
       </c>
       <c r="D262" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E262">
         <v>3.529413159454653</v>
@@ -14665,7 +14662,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14679,7 +14676,7 @@
         <v>3.637585058248958</v>
       </c>
       <c r="D263" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E263">
         <v>3.529413159454653</v>
@@ -14715,7 +14712,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14729,7 +14726,7 @@
         <v>3.405388602484038</v>
       </c>
       <c r="D264" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E264">
         <v>3.509413159454653</v>
@@ -14765,7 +14762,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14779,7 +14776,7 @@
         <v>3.405511387337113</v>
       </c>
       <c r="D265" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E265">
         <v>3.509413159454653</v>
@@ -14815,7 +14812,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14829,7 +14826,7 @@
         <v>3.451364045513422</v>
       </c>
       <c r="D266" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E266">
         <v>3.509413159454653</v>
@@ -14865,7 +14862,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14879,7 +14876,7 @@
         <v>4.004636932335591</v>
       </c>
       <c r="D267" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E267">
         <v>3.867442887120403</v>
@@ -14929,7 +14926,7 @@
         <v>3.774439165379895</v>
       </c>
       <c r="D268" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E268">
         <v>3.837640654076098</v>
@@ -14979,7 +14976,7 @@
         <v>4.220199786446392</v>
       </c>
       <c r="D269" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E269">
         <v>4.085943565478028</v>
@@ -15015,7 +15012,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15029,7 +15026,7 @@
         <v>3.991103703583256</v>
       </c>
       <c r="D270" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E270">
         <v>4.0441357312043</v>
@@ -15065,7 +15062,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15079,7 +15076,7 @@
         <v>4.24807262091024</v>
       </c>
       <c r="D271" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E271">
         <v>4.172298835483293</v>
@@ -15115,7 +15112,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15129,7 +15126,7 @@
         <v>4.076733299050661</v>
       </c>
       <c r="D272" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E272">
         <v>4.185185728196767</v>
@@ -15165,7 +15162,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15229,7 +15226,7 @@
         <v>3.853669569225198</v>
       </c>
       <c r="D274" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E274">
         <v>3.960609701897911</v>
@@ -15365,7 +15362,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15379,7 +15376,7 @@
         <v>3.457860783201086</v>
       </c>
       <c r="D277" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E277">
         <v>3.562117466477025</v>
@@ -15415,7 +15412,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15429,7 +15426,7 @@
         <v>3.461796612382101</v>
       </c>
       <c r="D278" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E278">
         <v>3.45818163729601</v>
@@ -15465,7 +15462,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15529,7 +15526,7 @@
         <v>1.876063224574707</v>
       </c>
       <c r="D280" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E280">
         <v>1.926860456775207</v>
@@ -15579,7 +15576,7 @@
         <v>1.879462993924748</v>
       </c>
       <c r="D281" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E281">
         <v>1.926860456775207</v>
@@ -15629,7 +15626,7 @@
         <v>1.36286186891499</v>
       </c>
       <c r="D282" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E282">
         <v>1.420876924621103</v>
@@ -15665,7 +15662,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15679,7 +15676,7 @@
         <v>1.365396205962064</v>
       </c>
       <c r="D283" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E283">
         <v>1.420876924621103</v>
@@ -15715,7 +15712,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15729,7 +15726,7 @@
         <v>1.492587172538397</v>
       </c>
       <c r="D284" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E284">
         <v>1.422587172538397</v>
@@ -15765,7 +15762,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15779,7 +15776,7 @@
         <v>1.155028253713973</v>
       </c>
       <c r="D285" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E285">
         <v>1.207786135342488</v>
@@ -15829,7 +15826,7 @@
         <v>1.157212112489207</v>
       </c>
       <c r="D286" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E286">
         <v>1.207786135342488</v>
@@ -15879,7 +15876,7 @@
         <v>1.287557383512098</v>
       </c>
       <c r="D287" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E287">
         <v>1.260086513310223</v>
@@ -15929,7 +15926,7 @@
         <v>-0.2566084186298667</v>
       </c>
       <c r="D288" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E288">
         <v>-0.001048450451905936</v>
@@ -15965,7 +15962,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15979,7 +15976,7 @@
         <v>-0.2875710874180024</v>
       </c>
       <c r="D289" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E289">
         <v>-0.001048450451905936</v>
@@ -16015,7 +16012,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16065,7 +16062,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16115,7 +16112,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16129,7 +16126,7 @@
         <v>-0.3429456734762377</v>
       </c>
       <c r="D292" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E292">
         <v>-0.1559309932859021</v>
@@ -16165,7 +16162,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16179,7 +16176,7 @@
         <v>-0.452945673476238</v>
       </c>
       <c r="D293" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E293">
         <v>-0.1559309932859021</v>
@@ -16215,7 +16212,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16229,7 +16226,7 @@
         <v>-0.07614423041516449</v>
       </c>
       <c r="D294" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E294">
         <v>-0.08649962563060054</v>
@@ -16265,7 +16262,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16279,7 +16276,7 @@
         <v>-0.06685502084603723</v>
       </c>
       <c r="D295" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E295">
         <v>-0.08649962563060054</v>
@@ -16315,7 +16312,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16329,7 +16326,7 @@
         <v>-0.6325763258089658</v>
       </c>
       <c r="D296" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E296">
         <v>-0.7397037652284588</v>
@@ -16365,7 +16362,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16379,7 +16376,7 @@
         <v>-0.6888811406779016</v>
       </c>
       <c r="D297" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E297">
         <v>-0.6347573064746772</v>
@@ -16415,7 +16412,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16429,7 +16426,7 @@
         <v>-0.5922830059527424</v>
       </c>
       <c r="D298" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E298">
         <v>-0.6988811406779014</v>
@@ -16465,7 +16462,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16479,7 +16476,7 @@
         <v>-0.7708727781363214</v>
       </c>
       <c r="D299" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E299">
         <v>-0.7160845060282481</v>
@@ -16515,7 +16512,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16529,7 +16526,7 @@
         <v>-0.6732115427634033</v>
       </c>
       <c r="D300" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E300">
         <v>-0.7808727781363212</v>
@@ -16565,7 +16562,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16579,7 +16576,7 @@
         <v>-0.6051723879795468</v>
       </c>
       <c r="D301" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E301">
         <v>-0.5517269067155315</v>
@@ -16615,7 +16612,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16629,7 +16626,7 @@
         <v>-0.509659617957122</v>
       </c>
       <c r="D302" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E302">
         <v>-0.6151723879795465</v>
@@ -16665,7 +16662,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16679,7 +16676,7 @@
         <v>1.374867998585327</v>
       </c>
       <c r="D303" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E303">
         <v>1.61428021608427</v>
@@ -16715,7 +16712,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16729,7 +16726,7 @@
         <v>1.37455579980999</v>
       </c>
       <c r="D304" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E304">
         <v>1.61428021608427</v>
@@ -16765,7 +16762,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16779,7 +16776,7 @@
         <v>1.659046067002767</v>
       </c>
       <c r="D305" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E305">
         <v>1.701663141543517</v>
@@ -16815,7 +16812,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16829,7 +16826,7 @@
         <v>1.400425101402588</v>
       </c>
       <c r="D306" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E306">
         <v>1.63789275673065</v>
@@ -16865,7 +16862,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16879,7 +16876,7 @@
         <v>1.415426421593279</v>
       </c>
       <c r="D307" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E307">
         <v>1.63789275673065</v>
@@ -16915,7 +16912,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16929,7 +16926,7 @@
         <v>1.672891436539961</v>
       </c>
       <c r="D308" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E308">
         <v>1.702888796158578</v>
@@ -16965,7 +16962,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16979,7 +16976,7 @@
         <v>1.682896717302726</v>
       </c>
       <c r="D309" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E309">
         <v>1.702888796158578</v>
@@ -17015,7 +17012,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17029,7 +17026,7 @@
         <v>1.392287936404873</v>
       </c>
       <c r="D310" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E310">
         <v>1.630374723852328</v>
@@ -17065,7 +17062,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17079,7 +17076,7 @@
         <v>1.392192134372636</v>
       </c>
       <c r="D311" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E311">
         <v>1.630374723852328</v>
@@ -17115,7 +17112,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17129,7 +17126,7 @@
         <v>1.665398674360388</v>
       </c>
       <c r="D312" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E312">
         <v>1.367982501138595</v>
@@ -17165,7 +17162,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17179,7 +17176,7 @@
         <v>1.67530287232815</v>
       </c>
       <c r="D313" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E313">
         <v>1.367982501138595</v>
@@ -17215,7 +17212,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17229,7 +17226,7 @@
         <v>1.683187064752997</v>
       </c>
       <c r="D314" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E314">
         <v>1.385560910531628</v>
@@ -17265,7 +17262,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17279,7 +17276,7 @@
         <v>1.693331241005988</v>
       </c>
       <c r="D315" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E315">
         <v>1.385560910531628</v>
@@ -17315,7 +17312,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17329,7 +17326,7 @@
         <v>1.671335210176903</v>
       </c>
       <c r="D316" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E316">
         <v>1.373848959803819</v>
@@ -17365,7 +17362,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17379,7 +17376,7 @@
         <v>1.68131949631757</v>
       </c>
       <c r="D317" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E317">
         <v>1.373848959803819</v>
@@ -17415,7 +17412,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17429,7 +17426,7 @@
         <v>1.693875753393727</v>
       </c>
       <c r="D318" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E318">
         <v>1.396123425781996</v>
@@ -17465,7 +17462,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17479,7 +17476,7 @@
         <v>1.704164127807133</v>
       </c>
       <c r="D319" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E319">
         <v>1.396123425781996</v>
@@ -17515,7 +17512,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17529,7 +17526,7 @@
         <v>1.366123425781996</v>
       </c>
       <c r="D320" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E320">
         <v>1.403731566187024</v>
@@ -17565,7 +17562,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17579,7 +17576,7 @@
         <v>1.710631890779994</v>
       </c>
       <c r="D321" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E321">
         <v>1.412681767280061</v>
@@ -17615,7 +17612,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17629,7 +17626,7 @@
         <v>1.72114631763706</v>
       </c>
       <c r="D322" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E322">
         <v>1.412681767280061</v>
@@ -17665,7 +17662,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17679,7 +17676,7 @@
         <v>1.382681767280062</v>
       </c>
       <c r="D323" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E323">
         <v>1.420374677351461</v>
@@ -17715,7 +17712,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17729,7 +17726,7 @@
         <v>1.679206240881443</v>
       </c>
       <c r="D324" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E324">
         <v>1.381627077835624</v>
@@ -17779,7 +17776,7 @@
         <v>1.689296712933807</v>
       </c>
       <c r="D325" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E325">
         <v>1.381627077835624</v>
@@ -17829,7 +17826,7 @@
         <v>1.351627077835625</v>
       </c>
       <c r="D326" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E326">
         <v>1.364138386842169</v>
@@ -17879,7 +17876,7 @@
         <v>1.662615013806636</v>
       </c>
       <c r="D327" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E327">
         <v>1.365231699984297</v>
@@ -17915,7 +17912,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17929,7 +17926,7 @@
         <v>1.672481658175022</v>
       </c>
       <c r="D328" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E328">
         <v>1.365231699984297</v>
@@ -17965,7 +17962,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17979,7 +17976,7 @@
         <v>1.335231699984297</v>
       </c>
       <c r="D329" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E329">
         <v>1.330198361076394</v>
@@ -18015,7 +18012,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18029,7 +18026,7 @@
         <v>1.638483426036899</v>
       </c>
       <c r="D330" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E330">
         <v>1.341384970754843</v>
@@ -18079,7 +18076,7 @@
         <v>1.648024517787818</v>
       </c>
       <c r="D331" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E331">
         <v>1.341384970754843</v>
@@ -18179,7 +18176,7 @@
         <v>1.611118158429232</v>
       </c>
       <c r="D333" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E333">
         <v>1.31434273328757</v>
@@ -18229,7 +18226,7 @@
         <v>1.620290072876844</v>
       </c>
       <c r="D334" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E334">
         <v>1.31434273328757</v>
@@ -18279,7 +18276,7 @@
         <v>1.210704115653037</v>
       </c>
       <c r="D335" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E335">
         <v>1.321946243981619</v>
@@ -18329,7 +18326,7 @@
         <v>1.250704115653037</v>
       </c>
       <c r="D336" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E336">
         <v>1.321946243981619</v>
@@ -18379,7 +18376,7 @@
         <v>1.580824889600507</v>
       </c>
       <c r="D337" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E337">
         <v>1.284407057851428</v>
@@ -18415,7 +18412,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18429,7 +18426,7 @@
         <v>1.589588125885168</v>
       </c>
       <c r="D338" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E338">
         <v>1.284407057851428</v>
@@ -18465,7 +18462,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18479,7 +18476,7 @@
         <v>1.180206507742837</v>
       </c>
       <c r="D339" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E339">
         <v>1.27675246238701</v>
@@ -18515,7 +18512,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18529,7 +18526,7 @@
         <v>1.220206507742837</v>
       </c>
       <c r="D340" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E340">
         <v>1.27675246238701</v>
@@ -18565,7 +18562,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18579,7 +18576,7 @@
         <v>1.680056540073359</v>
       </c>
       <c r="D341" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E341">
         <v>1.409353064352823</v>
@@ -18615,7 +18612,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18629,7 +18626,7 @@
         <v>1.717732409003494</v>
       </c>
       <c r="D342" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E342">
         <v>1.409353064352823</v>
@@ -18665,7 +18662,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18679,7 +18676,7 @@
         <v>1.307497917096648</v>
       </c>
       <c r="D343" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E343">
         <v>1.444235818399402</v>
@@ -18715,7 +18712,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18729,7 +18726,7 @@
         <v>1.347497917096648</v>
       </c>
       <c r="D344" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E344">
         <v>1.444235818399402</v>
@@ -18765,7 +18762,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18779,7 +18776,7 @@
         <v>1.842256392262994</v>
       </c>
       <c r="D345" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E345">
         <v>1.530769127897027</v>
@@ -18829,7 +18826,7 @@
         <v>1.431193121765403</v>
       </c>
       <c r="D346" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E346">
         <v>1.572471675023835</v>
@@ -18879,7 +18876,7 @@
         <v>1.471193121765403</v>
       </c>
       <c r="D347" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E347">
         <v>1.572471675023835</v>
@@ -18929,7 +18926,7 @@
         <v>2.306011000659936</v>
       </c>
       <c r="D348" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E348">
         <v>2.348379970519409</v>
@@ -18965,7 +18962,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18979,7 +18976,7 @@
         <v>2.400485390479259</v>
       </c>
       <c r="D349" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E349">
         <v>2.364696230398958</v>
@@ -19015,7 +19012,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19065,7 +19062,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19079,7 +19076,7 @@
         <v>2.315116384839492</v>
       </c>
       <c r="D351" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E351">
         <v>2.323814331699535</v>
@@ -19115,7 +19112,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19129,7 +19126,7 @@
         <v>2.158186337006185</v>
       </c>
       <c r="D352" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E352">
         <v>2.199105803820263</v>
@@ -19165,7 +19162,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19215,7 +19212,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19265,7 +19262,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19279,7 +19276,7 @@
         <v>2.249949180664442</v>
       </c>
       <c r="D355" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E355">
         <v>2.193589002935801</v>
@@ -19315,7 +19312,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19329,7 +19326,7 @@
         <v>3.29910210514231</v>
       </c>
       <c r="D356" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E356">
         <v>3.35230135785332</v>
@@ -19365,7 +19362,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19379,7 +19376,7 @@
         <v>3.804045197377832</v>
       </c>
       <c r="D357" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E357">
         <v>3.415154291605215</v>
@@ -19415,7 +19412,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19429,7 +19426,7 @@
         <v>3.427249571448392</v>
       </c>
       <c r="D358" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E358">
         <v>3.291626526785035</v>
@@ -19465,7 +19462,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19515,7 +19512,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19529,7 +19526,7 @@
         <v>3.442581197445604</v>
       </c>
       <c r="D360" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E360">
         <v>3.306414237004073</v>
@@ -19565,7 +19562,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19579,7 +19576,7 @@
         <v>3.36022431872702</v>
       </c>
       <c r="D361" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E361">
         <v>3.226979110080385</v>
@@ -19615,7 +19612,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19629,7 +19626,7 @@
         <v>3.251003700388559</v>
       </c>
       <c r="D362" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E362">
         <v>3.121633280862579</v>
@@ -19665,7 +19662,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19679,7 +19676,7 @@
         <v>2.99001278638902</v>
       </c>
       <c r="D363" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E363">
         <v>3.032275977245447</v>
@@ -19765,7 +19762,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19779,7 +19776,7 @@
         <v>2.786342722576059</v>
       </c>
       <c r="D365" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E365">
         <v>2.830017022419643</v>
@@ -19815,7 +19812,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19829,7 +19826,7 @@
         <v>2.881784622628198</v>
       </c>
       <c r="D366" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E366">
         <v>2.846342722576059</v>
@@ -19865,7 +19862,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19879,7 +19876,7 @@
         <v>2.713139299753176</v>
       </c>
       <c r="D367" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E367">
         <v>2.672915915531583</v>
@@ -19915,7 +19912,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19929,7 +19926,7 @@
         <v>2.722022378645214</v>
       </c>
       <c r="D368" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E368">
         <v>2.672915915531583</v>
@@ -19965,7 +19962,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19979,7 +19976,7 @@
         <v>2.643362683974768</v>
       </c>
       <c r="D369" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E369">
         <v>2.68802760764238</v>
@@ -20015,7 +20012,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20029,7 +20026,7 @@
         <v>2.738474376085565</v>
       </c>
       <c r="D370" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E370">
         <v>2.678250991863972</v>
@@ -20065,7 +20062,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20079,7 +20076,7 @@
         <v>2.26156876679942</v>
       </c>
       <c r="D371" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E371">
         <v>2.319500204055783</v>
@@ -20115,7 +20112,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20129,7 +20126,7 @@
         <v>2.341086491507057</v>
       </c>
       <c r="D372" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E372">
         <v>2.284741341701965</v>
@@ -20165,7 +20162,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20179,7 +20176,7 @@
         <v>2.25156876679942</v>
       </c>
       <c r="D373" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E373">
         <v>2.298948197976329</v>
@@ -20215,7 +20212,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20229,7 +20226,7 @@
         <v>2.345775623073784</v>
       </c>
       <c r="D374" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E374">
         <v>2.287361910525056</v>
@@ -20265,7 +20262,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20279,7 +20276,7 @@
         <v>1.450725995788351</v>
       </c>
       <c r="D375" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E375">
         <v>1.543612412630503</v>
@@ -20315,7 +20312,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20329,7 +20326,7 @@
         <v>1.378039753255653</v>
       </c>
       <c r="D376" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E376">
         <v>1.473954763536668</v>
@@ -20365,7 +20362,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20379,7 +20376,7 @@
         <v>2.300473418774809</v>
       </c>
       <c r="D377" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E377">
         <v>2.269274816103397</v>
@@ -20429,7 +20426,7 @@
         <v>2.307737312105645</v>
       </c>
       <c r="D378" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E378">
         <v>2.269274816103397</v>
@@ -20479,7 +20476,7 @@
         <v>2.548688372146674</v>
       </c>
       <c r="D379" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E379">
         <v>2.44021981851742</v>
@@ -20515,7 +20512,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20529,7 +20526,7 @@
         <v>4.064626779899114</v>
       </c>
       <c r="D380" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E380">
         <v>3.971827788774664</v>
@@ -20565,7 +20562,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20579,7 +20576,7 @@
         <v>2.704221825320051</v>
       </c>
       <c r="D381" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E381">
         <v>2.757514946748523</v>
@@ -20615,7 +20612,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20629,7 +20626,7 @@
         <v>2.699698304540886</v>
       </c>
       <c r="D382" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E382">
         <v>2.757514946748523</v>
@@ -20665,7 +20662,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20679,7 +20676,7 @@
         <v>2.597723564836138</v>
       </c>
       <c r="D383" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E383">
         <v>2.648687698460786</v>
@@ -20715,7 +20712,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20729,7 +20726,7 @@
         <v>2.594470401040876</v>
       </c>
       <c r="D384" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E384">
         <v>2.648687698460786</v>
@@ -20765,7 +20762,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20779,7 +20776,7 @@
         <v>2.5327482758737</v>
       </c>
       <c r="D385" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E385">
         <v>2.582291478725809</v>
@@ -20815,7 +20812,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20829,7 +20826,7 @@
         <v>2.530270165227095</v>
       </c>
       <c r="D386" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E386">
         <v>2.582291478725809</v>
@@ -20865,7 +20862,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20879,7 +20876,7 @@
         <v>2.615226386520305</v>
       </c>
       <c r="D387" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E387">
         <v>2.605226386520305</v>
@@ -20915,7 +20912,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20929,7 +20926,7 @@
         <v>2.519210324106</v>
       </c>
       <c r="D388" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E388">
         <v>2.474919909368535</v>
@@ -20965,7 +20962,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20979,7 +20976,7 @@
         <v>2.443973795685154</v>
       </c>
       <c r="D389" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E389">
         <v>2.491575608314453</v>
@@ -21015,7 +21012,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21029,7 +21026,7 @@
         <v>2.442554625160083</v>
       </c>
       <c r="D390" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E390">
         <v>2.491575608314453</v>
@@ -21065,7 +21062,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21115,7 +21112,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21129,7 +21126,7 @@
         <v>2.457705873063223</v>
       </c>
       <c r="D392" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E392">
         <v>2.413049360402885</v>
@@ -21165,7 +21162,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21179,7 +21176,7 @@
         <v>2.382591377283335</v>
       </c>
       <c r="D393" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E393">
         <v>2.428850830862097</v>
@@ -21215,7 +21212,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21229,7 +21226,7 @@
         <v>2.381904402604011</v>
       </c>
       <c r="D394" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E394">
         <v>2.428850830862097</v>
@@ -21265,7 +21262,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21279,7 +21276,7 @@
         <v>2.46327835196266</v>
       </c>
       <c r="D395" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E395">
         <v>2.453507343522435</v>
@@ -21315,7 +21312,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21329,7 +21326,7 @@
         <v>2.467705873063223</v>
       </c>
       <c r="D396" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E396">
         <v>2.453507343522435</v>
@@ -21365,7 +21362,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21379,7 +21376,7 @@
         <v>2.447999298642713</v>
       </c>
       <c r="D397" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E397">
         <v>2.403285008753682</v>
@@ -21415,7 +21412,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21429,7 +21426,7 @@
         <v>2.372904061939057</v>
       </c>
       <c r="D398" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E398">
         <v>2.418951665679276</v>
@@ -21465,7 +21462,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21479,7 +21476,7 @@
         <v>2.37233264171712</v>
       </c>
       <c r="D399" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E399">
         <v>2.418951665679276</v>
@@ -21515,7 +21512,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21565,7 +21562,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21615,7 +21612,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21629,7 +21626,7 @@
         <v>2.414261420787727</v>
       </c>
       <c r="D402" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E402">
         <v>2.369346310197177</v>
@@ -21665,7 +21662,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21715,7 +21712,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21765,7 +21762,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21779,7 +21776,7 @@
         <v>2.424261420787727</v>
       </c>
       <c r="D405" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E405">
         <v>2.394544385485897</v>
@@ -21815,7 +21812,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21829,7 +21826,7 @@
         <v>2.414374606666995</v>
       </c>
       <c r="D406" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E406">
         <v>2.394544385485897</v>
@@ -21865,7 +21862,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21879,7 +21876,7 @@
         <v>2.397600622679596</v>
       </c>
       <c r="D407" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E407">
         <v>2.352586340671736</v>
@@ -21915,7 +21912,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21929,7 +21926,7 @@
         <v>2.322605383348882</v>
       </c>
       <c r="D408" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E408">
         <v>2.367553015986731</v>
@@ -21965,7 +21962,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21979,7 +21976,7 @@
         <v>2.322633947364601</v>
       </c>
       <c r="D409" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E409">
         <v>2.367553015986731</v>
@@ -22015,7 +22012,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22029,7 +22026,7 @@
         <v>2.402576819333163</v>
       </c>
       <c r="D410" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E410">
         <v>2.35256729799459</v>
@@ -22065,7 +22062,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22079,7 +22076,7 @@
         <v>2.407600622679595</v>
       </c>
       <c r="D411" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E411">
         <v>2.35256729799459</v>
@@ -22115,7 +22112,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22129,7 +22126,7 @@
         <v>2.39758158000245</v>
       </c>
       <c r="D412" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E412">
         <v>2.35256729799459</v>
@@ -22165,7 +22162,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22179,7 +22176,7 @@
         <v>2.378737718650321</v>
       </c>
       <c r="D413" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E413">
         <v>2.33361115745181</v>
@@ -22215,7 +22212,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22229,7 +22226,7 @@
         <v>2.30377990571649</v>
       </c>
       <c r="D414" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E414">
         <v>2.348315847988621</v>
@@ -22265,7 +22262,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22279,7 +22276,7 @@
         <v>2.304033028113511</v>
       </c>
       <c r="D415" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E415">
         <v>2.348315847988621</v>
@@ -22315,7 +22312,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22329,7 +22326,7 @@
         <v>2.383526783319471</v>
       </c>
       <c r="D416" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E416">
         <v>2.333442409187131</v>
@@ -22365,7 +22362,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22379,7 +22376,7 @@
         <v>2.38873771865032</v>
       </c>
       <c r="D417" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E417">
         <v>2.333442409187131</v>
@@ -22415,7 +22412,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22429,7 +22426,7 @@
         <v>2.378568970385641</v>
       </c>
       <c r="D418" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E418">
         <v>2.333442409187131</v>
@@ -22465,7 +22462,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22479,7 +22476,7 @@
         <v>2.29477967980894</v>
       </c>
       <c r="D419" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E419">
         <v>2.33911879805526</v>
@@ -22529,7 +22526,7 @@
         <v>2.295140160765494</v>
       </c>
       <c r="D420" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E420">
         <v>2.33911879805526</v>
@@ -22579,7 +22576,7 @@
         <v>2.374419198852388</v>
       </c>
       <c r="D421" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E421">
         <v>2.324299038533536</v>
@@ -22629,7 +22626,7 @@
         <v>2.379719599649515</v>
       </c>
       <c r="D422" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E422">
         <v>2.324299038533536</v>
@@ -22679,7 +22676,7 @@
         <v>2.369479279011813</v>
       </c>
       <c r="D423" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E423">
         <v>2.324299038533536</v>
@@ -22729,7 +22726,7 @@
         <v>2.280590400920047</v>
       </c>
       <c r="D424" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E424">
         <v>2.324619216844741</v>
@@ -22765,7 +22762,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22779,7 +22776,7 @@
         <v>2.281120137688396</v>
       </c>
       <c r="D425" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E425">
         <v>2.324619216844741</v>
@@ -22815,7 +22812,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22829,7 +22826,7 @@
         <v>2.360060664151698</v>
       </c>
       <c r="D426" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E426">
         <v>2.309884085228915</v>
@@ -22865,7 +22862,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22915,7 +22912,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22929,7 +22926,7 @@
         <v>2.281700069738552</v>
       </c>
       <c r="D428" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E428">
         <v>2.325753152774585</v>
@@ -22965,7 +22962,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -22979,7 +22976,7 @@
         <v>2.282216569900716</v>
       </c>
       <c r="D429" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E429">
         <v>2.325753152774585</v>
@@ -23015,7 +23012,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23029,7 +23026,7 @@
         <v>2.361183569576388</v>
       </c>
       <c r="D430" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E430">
         <v>2.311011402855666</v>
@@ -23065,7 +23062,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23079,7 +23076,7 @@
         <v>2.255753152774584</v>
       </c>
       <c r="D431" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E431">
         <v>2.30032273597278</v>
@@ -23115,7 +23112,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23129,7 +23126,7 @@
         <v>2.248769782041177</v>
       </c>
       <c r="D432" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E432">
         <v>2.297801715354081</v>
@@ -23165,7 +23162,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23179,7 +23176,7 @@
         <v>2.343406757033516</v>
       </c>
       <c r="D433" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E433">
         <v>2.293164740361742</v>
@@ -23215,7 +23212,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23229,7 +23226,7 @@
         <v>2.237801715354081</v>
       </c>
       <c r="D434" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E434">
         <v>2.26243869034642</v>
@@ -23265,7 +23262,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23279,7 +23276,7 @@
         <v>2.228095614122554</v>
       </c>
       <c r="D435" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E435">
         <v>2.276800683120539</v>
@@ -23315,7 +23312,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23329,7 +23326,7 @@
         <v>2.322610014996799</v>
       </c>
       <c r="D436" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E436">
         <v>2.263257480497806</v>
@@ -23365,7 +23362,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23415,7 +23412,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23429,7 +23426,7 @@
         <v>2.224983216186275</v>
       </c>
       <c r="D438" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E438">
         <v>2.273639077311749</v>
@@ -23479,7 +23476,7 @@
         <v>2.319479164108328</v>
       </c>
       <c r="D439" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E439">
         <v>2.26015123354559</v>
@@ -23629,7 +23626,7 @@
         <v>2.3116287572162</v>
       </c>
       <c r="D442" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E442">
         <v>2.252362519438469</v>
@@ -23665,7 +23662,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23715,7 +23712,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23765,7 +23762,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23829,7 +23826,7 @@
         <v>2.185149484739352</v>
       </c>
       <c r="D446" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E446">
         <v>2.165149484739352</v>
@@ -23929,7 +23926,7 @@
         <v>2.20020073233055</v>
       </c>
       <c r="D448" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E448">
         <v>2.205687152603988</v>
@@ -24015,7 +24012,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24065,7 +24062,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24115,7 +24112,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24165,7 +24162,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24215,7 +24212,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24329,7 +24326,7 @@
         <v>2.142114930387524</v>
       </c>
       <c r="D456" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E456">
         <v>2.162114930387524</v>
@@ -24365,7 +24362,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24379,7 +24376,7 @@
         <v>2.115413806995409</v>
       </c>
       <c r="D457" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E457">
         <v>2.141244762127619</v>
@@ -24465,7 +24462,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24479,7 +24476,7 @@
         <v>2.073994682974101</v>
       </c>
       <c r="D459" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E459">
         <v>2.082201671198685</v>
@@ -24529,7 +24526,7 @@
         <v>2.083994682974101</v>
       </c>
       <c r="D460" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E460">
         <v>2.082201671198685</v>
@@ -24615,7 +24612,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24629,7 +24626,7 @@
         <v>2.057461365020192</v>
       </c>
       <c r="D462" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E462">
         <v>2.066125824243982</v>
@@ -24665,7 +24662,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24715,7 +24712,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24765,7 +24762,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24815,7 +24812,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24865,7 +24862,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24879,7 +24876,7 @@
         <v>2.057577737614682</v>
       </c>
       <c r="D467" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E467">
         <v>2.099815205781953</v>
@@ -24915,7 +24912,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24979,7 +24976,7 @@
         <v>2.075267052489131</v>
       </c>
       <c r="D469" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E469">
         <v>2.105974841560053</v>
@@ -25029,7 +25026,7 @@
         <v>2.0673904197019</v>
       </c>
       <c r="D470" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E470">
         <v>2.109513786914668</v>
@@ -25079,7 +25076,7 @@
         <v>2.101281730695467</v>
       </c>
       <c r="D471" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E471">
         <v>2.131889846669813</v>
@@ -25129,7 +25126,7 @@
         <v>2.093106078618507</v>
       </c>
       <c r="D472" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E472">
         <v>2.134930426541548</v>
@@ -25179,7 +25176,7 @@
         <v>2.114232378900782</v>
       </c>
       <c r="D473" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E473">
         <v>2.144790875533345</v>
@@ -25215,7 +25212,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25229,7 +25226,7 @@
         <v>2.164790875533345</v>
       </c>
       <c r="D474" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E474">
         <v>2.134232378900781</v>
@@ -25265,7 +25262,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25279,7 +25276,7 @@
         <v>2.105907868798473</v>
       </c>
       <c r="D475" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E475">
         <v>2.147583358696166</v>
@@ -25315,7 +25312,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25329,7 +25326,7 @@
         <v>2.178667208693582</v>
       </c>
       <c r="D476" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E476">
         <v>2.148162082573172</v>
@@ -25365,7 +25362,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25379,7 +25376,7 @@
         <v>2.119677460934401</v>
       </c>
       <c r="D477" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E477">
         <v>2.161192839295628</v>
@@ -25415,7 +25412,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25429,7 +25426,7 @@
         <v>2.191253934723685</v>
       </c>
       <c r="D478" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E478">
         <v>2.160797219088007</v>
@@ -25479,7 +25476,7 @@
         <v>2.132167365995042</v>
       </c>
       <c r="D479" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E479">
         <v>2.173537512902076</v>
@@ -25579,7 +25576,7 @@
         <v>2.161339958759847</v>
       </c>
       <c r="D481" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E481">
         <v>2.202370889471942</v>
@@ -25629,7 +25626,7 @@
         <v>2.215480849833102</v>
       </c>
       <c r="D482" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E482">
         <v>2.179965384477054</v>
@@ -25679,7 +25676,7 @@
         <v>1.276065947508897</v>
       </c>
       <c r="D483" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E483">
         <v>1.317566169928825</v>
@@ -25715,7 +25712,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25729,7 +25726,7 @@
         <v>1.37689891014235</v>
       </c>
       <c r="D484" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E484">
         <v>1.288399132562277</v>
@@ -25765,7 +25762,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25779,7 +25776,7 @@
         <v>1.265250934212467</v>
       </c>
       <c r="D485" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E485">
         <v>1.306889515011455</v>
@@ -25815,7 +25812,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25829,7 +25826,7 @@
         <v>1.365853299547489</v>
       </c>
       <c r="D486" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E486">
         <v>1.277491880346475</v>
@@ -25865,7 +25862,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25879,7 +25876,7 @@
         <v>1.365250934212467</v>
       </c>
       <c r="D487" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E487">
         <v>1.29891353608099</v>
@@ -25915,7 +25912,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25929,7 +25926,7 @@
         <v>1.335853299547488</v>
       </c>
       <c r="D488" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E488">
         <v>1.29891353608099</v>
@@ -25965,7 +25962,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25979,7 +25976,7 @@
         <v>1.257848770795328</v>
       </c>
       <c r="D489" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E489">
         <v>1.29958204878089</v>
@@ -26015,7 +26012,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26029,7 +26026,7 @@
         <v>1.358293307486061</v>
       </c>
       <c r="D490" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E490">
         <v>1.270026585471621</v>
@@ -26065,7 +26062,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26079,7 +26076,7 @@
         <v>1.328293307486061</v>
       </c>
       <c r="D491" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E491">
         <v>1.291337761155134</v>
@@ -26115,7 +26112,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26129,7 +26126,7 @@
         <v>1.336383675279734</v>
       </c>
       <c r="D492" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E492">
         <v>1.248391395422367</v>
@@ -26179,7 +26176,7 @@
         <v>1.306383675279734</v>
       </c>
       <c r="D493" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E493">
         <v>1.269382388589295</v>
@@ -26229,7 +26226,7 @@
         <v>1.279467032224208</v>
       </c>
       <c r="D494" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E494">
         <v>1.192187695703653</v>
@@ -26265,7 +26262,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26279,7 +26276,7 @@
         <v>1.280668138023285</v>
       </c>
       <c r="D495" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E495">
         <v>1.2123469216443</v>
@@ -26315,7 +26312,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26329,7 +26326,7 @@
         <v>1.249467032224208</v>
       </c>
       <c r="D496" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E496">
         <v>1.2123469216443</v>
@@ -26365,7 +26362,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26379,7 +26376,7 @@
         <v>1.175386037005039</v>
       </c>
       <c r="D497" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E497">
         <v>1.183866479324669</v>
@@ -26415,7 +26412,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26429,7 +26426,7 @@
         <v>1.24514956586386</v>
       </c>
       <c r="D498" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E498">
         <v>1.158300093222558</v>
@@ -26465,7 +26462,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26479,7 +26476,7 @@
         <v>1.247067111461691</v>
       </c>
       <c r="D499" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E499">
         <v>1.177957811304076</v>
@@ -26515,7 +26512,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26529,7 +26526,7 @@
         <v>1.21514956586386</v>
       </c>
       <c r="D500" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E500">
         <v>1.177957811304076</v>
@@ -26565,7 +26562,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26579,7 +26576,7 @@
         <v>1.140423774825811</v>
       </c>
       <c r="D501" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E501">
         <v>1.202341320423642</v>
@@ -26615,7 +26612,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26629,7 +26626,7 @@
         <v>1.226637749198502</v>
       </c>
       <c r="D502" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E502">
         <v>1.140020157350503</v>
@@ -26665,7 +26662,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26679,7 +26676,7 @@
         <v>1.196637749198502</v>
       </c>
       <c r="D503" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E503">
         <v>1.159407347839835</v>
@@ -26715,7 +26712,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26729,7 +26726,7 @@
         <v>1.121564136970499</v>
       </c>
       <c r="D504" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E504">
         <v>1.183868150557168</v>
@@ -26765,7 +26762,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26779,7 +26776,7 @@
         <v>1.183891513054156</v>
       </c>
       <c r="D505" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E505">
         <v>1.097809364665167</v>
@@ -26815,7 +26812,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26829,7 +26826,7 @@
         <v>1.153891513054155</v>
       </c>
       <c r="D506" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E506">
         <v>1.116571871118987</v>
@@ -26865,7 +26862,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26879,7 +26876,7 @@
         <v>1.078014735637637</v>
       </c>
       <c r="D507" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E507">
         <v>1.141211154989324</v>
@@ -26915,7 +26912,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26929,7 +26926,7 @@
         <v>1.120386130880944</v>
       </c>
       <c r="D508" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E508">
         <v>1.082996540339985</v>
@@ -26979,7 +26976,7 @@
         <v>1.043879816012319</v>
       </c>
       <c r="D509" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E509">
         <v>1.107775721421902</v>
@@ -27029,7 +27026,7 @@
         <v>1.096417003653128</v>
       </c>
       <c r="D510" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E510">
         <v>1.023774332097018</v>
@@ -27065,7 +27062,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27079,7 +27076,7 @@
         <v>1.061287302238483</v>
       </c>
       <c r="D511" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E511">
         <v>1.023774332097018</v>
@@ -27115,7 +27112,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27129,7 +27126,7 @@
         <v>0.9836705709653022</v>
       </c>
       <c r="D512" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E512">
         <v>1.048800272379947</v>
@@ -27165,7 +27162,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27179,7 +27176,7 @@
         <v>0.9781788819742268</v>
       </c>
       <c r="D513" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E513">
         <v>0.9027630348563518</v>
@@ -27215,7 +27212,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27229,7 +27226,7 @@
         <v>0.9405281118670676</v>
       </c>
       <c r="D514" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E514">
         <v>0.9027630348563518</v>
@@ -27265,7 +27262,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27279,7 +27276,7 @@
         <v>0.8606424187706248</v>
       </c>
       <c r="D515" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E515">
         <v>0.9282931888777832</v>
@@ -27315,7 +27312,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27329,7 +27326,7 @@
         <v>0.8449532639682586</v>
       </c>
       <c r="D516" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E516">
         <v>0.7664127221849988</v>
@@ -27365,7 +27362,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27379,7 +27376,7 @@
         <v>0.8044618623471131</v>
       </c>
       <c r="D517" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E517">
         <v>0.7664127221849988</v>
@@ -27415,7 +27412,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27429,7 +27426,7 @@
         <v>0.7220196008880824</v>
       </c>
       <c r="D518" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E518">
         <v>0.7925110025092272</v>
@@ -27465,7 +27462,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27479,7 +27476,7 @@
         <v>0.4969504786678423</v>
       </c>
       <c r="D519" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E519">
         <v>0.5720539524656312</v>
@@ -27523,81 +27520,81 @@
         <v>0</v>
       </c>
       <c r="B520" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C520">
-        <v>1.049221706841676</v>
+        <v>0.9942742592090008</v>
       </c>
       <c r="D520" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E520">
-        <v>1.016747983025339</v>
+        <v>1.059186671930127</v>
       </c>
       <c r="F520">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G520">
-        <v>0.008270778293158325</v>
+        <v>0.008305725740791001</v>
       </c>
       <c r="H520">
-        <v>0.008283252016974661</v>
+        <v>0.008220813328069874</v>
       </c>
       <c r="I520">
-        <v>0.03247372381633751</v>
+        <v>0.06491241272112624</v>
       </c>
       <c r="J520">
         <v>0.7491241272112704</v>
       </c>
       <c r="K520">
-        <v>4.82</v>
+        <v>4.88</v>
       </c>
       <c r="L520">
-        <v>4.66</v>
+        <v>4.65</v>
       </c>
       <c r="M520">
-        <v>4.85</v>
+        <v>4.78</v>
       </c>
       <c r="N520">
-        <v>4.65</v>
+        <v>4.64</v>
       </c>
       <c r="O520">
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="521" spans="1:16">
       <c r="A521" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B521" t="s">
         <v>150</v>
       </c>
       <c r="C521">
-        <v>0.9942742592090008</v>
+        <v>1.041561394347275</v>
       </c>
       <c r="D521" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E521">
-        <v>1.059186671930127</v>
+        <v>1.105504808397535</v>
       </c>
       <c r="F521">
         <v>1</v>
       </c>
       <c r="G521">
-        <v>0.008305725740791001</v>
+        <v>0.008258438605652724</v>
       </c>
       <c r="H521">
-        <v>0.008220813328069874</v>
+        <v>0.008174495191602463</v>
       </c>
       <c r="I521">
-        <v>0.06491241272112624</v>
+        <v>0.06394341405025994</v>
       </c>
       <c r="J521">
-        <v>0.7491241272112704</v>
+        <v>0.7394341405026076</v>
       </c>
       <c r="K521">
         <v>4.88</v>
@@ -27615,57 +27612,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="522" spans="1:16">
-      <c r="A522" s="1">
-        <v>0</v>
-      </c>
-      <c r="B522" t="s">
-        <v>150</v>
-      </c>
-      <c r="C522">
-        <v>1.041561394347275</v>
-      </c>
-      <c r="D522" t="s">
-        <v>277</v>
-      </c>
-      <c r="E522">
-        <v>1.105504808397535</v>
-      </c>
-      <c r="F522">
-        <v>1</v>
-      </c>
-      <c r="G522">
-        <v>0.008258438605652724</v>
-      </c>
-      <c r="H522">
-        <v>0.008174495191602463</v>
-      </c>
-      <c r="I522">
-        <v>0.06394341405025994</v>
-      </c>
-      <c r="J522">
-        <v>0.7394341405026076</v>
-      </c>
-      <c r="K522">
-        <v>4.88</v>
-      </c>
-      <c r="L522">
-        <v>4.65</v>
-      </c>
-      <c r="M522">
-        <v>4.78</v>
-      </c>
-      <c r="N522">
-        <v>4.64</v>
-      </c>
-      <c r="O522">
-        <v>1</v>
-      </c>
-      <c r="P522" t="s">
-        <v>151</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-03328-601328.xlsx
+++ b/s60_signal/position-03328-601328.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="399">
   <si>
     <t>trade_time</t>
   </si>
@@ -845,6 +845,9 @@
   </si>
   <si>
     <t>2021-11-23</t>
+  </si>
+  <si>
+    <t>2021-11-08</t>
   </si>
   <si>
     <t>2016-05-24</t>
@@ -1662,7 +1665,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1712,7 +1715,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1812,7 +1815,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1862,7 +1865,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1912,7 +1915,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1962,7 +1965,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -2012,7 +2015,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2062,7 +2065,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2162,7 +2165,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2212,7 +2215,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2312,7 +2315,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2362,7 +2365,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2712,7 +2715,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2762,7 +2765,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2812,7 +2815,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2862,7 +2865,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2912,7 +2915,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2962,7 +2965,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -3012,7 +3015,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3062,7 +3065,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3112,7 +3115,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3162,7 +3165,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3212,7 +3215,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3262,7 +3265,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3312,7 +3315,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3362,7 +3365,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3412,7 +3415,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3462,7 +3465,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3512,7 +3515,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3712,7 +3715,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3762,7 +3765,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3812,7 +3815,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3862,7 +3865,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3912,7 +3915,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3962,7 +3965,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -4012,7 +4015,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4062,7 +4065,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4112,7 +4115,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4462,7 +4465,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4512,7 +4515,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4762,7 +4765,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4812,7 +4815,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4862,7 +4865,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4912,7 +4915,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4962,7 +4965,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5012,7 +5015,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5062,7 +5065,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5112,7 +5115,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5162,7 +5165,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5212,7 +5215,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5262,7 +5265,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5312,7 +5315,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5362,7 +5365,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5412,7 +5415,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5462,7 +5465,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5512,7 +5515,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5562,7 +5565,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5612,7 +5615,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5662,7 +5665,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5712,7 +5715,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5762,7 +5765,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5812,7 +5815,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5862,7 +5865,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5962,7 +5965,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -6012,7 +6015,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6062,7 +6065,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6112,7 +6115,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6162,7 +6165,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6212,7 +6215,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6262,7 +6265,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6312,7 +6315,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6462,7 +6465,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6512,7 +6515,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6612,7 +6615,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -7112,7 +7115,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7162,7 +7165,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7212,7 +7215,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -8112,7 +8115,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8162,7 +8165,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8362,7 +8365,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8412,7 +8415,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8462,7 +8465,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8662,7 +8665,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8712,7 +8715,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8762,7 +8765,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8812,7 +8815,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8862,7 +8865,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -9812,7 +9815,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9862,7 +9865,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9912,7 +9915,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9962,7 +9965,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -10162,7 +10165,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10212,7 +10215,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10262,7 +10265,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10312,7 +10315,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10712,7 +10715,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10762,7 +10765,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10812,7 +10815,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10862,7 +10865,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10912,7 +10915,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10962,7 +10965,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11012,7 +11015,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11062,7 +11065,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11112,7 +11115,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11162,7 +11165,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11212,7 +11215,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11512,7 +11515,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11562,7 +11565,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11612,7 +11615,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11662,7 +11665,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11712,7 +11715,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11762,7 +11765,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12062,7 +12065,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12112,7 +12115,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12162,7 +12165,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12212,7 +12215,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12262,7 +12265,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -13162,7 +13165,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13212,7 +13215,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13412,7 +13415,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13462,7 +13465,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13512,7 +13515,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13562,7 +13565,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13612,7 +13615,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13662,7 +13665,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13712,7 +13715,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13912,7 +13915,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13962,7 +13965,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14262,7 +14265,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14312,7 +14315,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14362,7 +14365,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14412,7 +14415,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14462,7 +14465,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14512,7 +14515,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14562,7 +14565,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14612,7 +14615,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14662,7 +14665,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14712,7 +14715,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14762,7 +14765,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14812,7 +14815,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14862,7 +14865,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15012,7 +15015,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15062,7 +15065,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15112,7 +15115,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15162,7 +15165,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15362,7 +15365,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15412,7 +15415,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15462,7 +15465,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15662,7 +15665,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15712,7 +15715,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15762,7 +15765,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15962,7 +15965,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16012,7 +16015,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16062,7 +16065,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16112,7 +16115,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16162,7 +16165,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16212,7 +16215,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16262,7 +16265,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16312,7 +16315,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16412,7 +16415,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16462,7 +16465,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16512,7 +16515,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16562,7 +16565,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16612,7 +16615,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16662,7 +16665,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16712,7 +16715,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16762,7 +16765,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16812,7 +16815,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16862,7 +16865,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16912,7 +16915,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16962,7 +16965,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17012,7 +17015,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17062,7 +17065,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17112,7 +17115,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17162,7 +17165,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17212,7 +17215,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17262,7 +17265,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17312,7 +17315,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17362,7 +17365,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17412,7 +17415,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17462,7 +17465,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17512,7 +17515,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17562,7 +17565,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17612,7 +17615,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17662,7 +17665,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17712,7 +17715,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17912,7 +17915,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17962,7 +17965,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -18012,7 +18015,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18612,7 +18615,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18662,7 +18665,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18712,7 +18715,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18762,7 +18765,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18962,7 +18965,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19012,7 +19015,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19062,7 +19065,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19112,7 +19115,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19162,7 +19165,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19212,7 +19215,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19262,7 +19265,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19312,7 +19315,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19362,7 +19365,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19412,7 +19415,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19562,7 +19565,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19612,7 +19615,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19662,7 +19665,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19762,7 +19765,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19812,7 +19815,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19862,7 +19865,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19912,7 +19915,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19962,7 +19965,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20012,7 +20015,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20062,7 +20065,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20112,7 +20115,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20162,7 +20165,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20212,7 +20215,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20262,7 +20265,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20312,7 +20315,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20362,7 +20365,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20512,7 +20515,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20562,7 +20565,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20612,7 +20615,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20662,7 +20665,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20712,7 +20715,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20762,7 +20765,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20812,7 +20815,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20862,7 +20865,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20912,7 +20915,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20962,7 +20965,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21012,7 +21015,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21062,7 +21065,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21112,7 +21115,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21162,7 +21165,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21212,7 +21215,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21262,7 +21265,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21312,7 +21315,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21362,7 +21365,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21412,7 +21415,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21462,7 +21465,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21512,7 +21515,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21562,7 +21565,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21612,7 +21615,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21662,7 +21665,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21712,7 +21715,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21762,7 +21765,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21812,7 +21815,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21862,7 +21865,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21912,7 +21915,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21962,7 +21965,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22012,7 +22015,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22062,7 +22065,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22112,7 +22115,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22162,7 +22165,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22212,7 +22215,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22262,7 +22265,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22312,7 +22315,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22362,7 +22365,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22412,7 +22415,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22462,7 +22465,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22962,7 +22965,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23012,7 +23015,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23062,7 +23065,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23112,7 +23115,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23162,7 +23165,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23212,7 +23215,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23262,7 +23265,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23312,7 +23315,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23362,7 +23365,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23412,7 +23415,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23662,7 +23665,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23712,7 +23715,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23762,7 +23765,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -25712,7 +25715,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25762,7 +25765,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25812,7 +25815,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25862,7 +25865,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25912,7 +25915,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25962,7 +25965,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26012,7 +26015,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26062,7 +26065,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26112,7 +26115,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26262,7 +26265,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26312,7 +26315,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26362,7 +26365,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26412,7 +26415,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26462,7 +26465,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26512,7 +26515,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26562,7 +26565,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26612,7 +26615,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26662,7 +26665,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26712,7 +26715,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26762,7 +26765,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27212,7 +27215,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27262,7 +27265,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27312,7 +27315,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27326,10 +27329,10 @@
         <v>0.8449532639682586</v>
       </c>
       <c r="D516" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E516">
-        <v>0.7664127221849988</v>
+        <v>0.7744618623471129</v>
       </c>
       <c r="F516">
         <v>-1</v>
@@ -27338,10 +27341,10 @@
         <v>0.008395046736031741</v>
       </c>
       <c r="H516">
-        <v>0.008493587277815001</v>
+        <v>0.008485538137652886</v>
       </c>
       <c r="I516">
-        <v>0.07854054178325987</v>
+        <v>0.07049140162114576</v>
       </c>
       <c r="J516">
         <v>0.8049140162114586</v>
@@ -27353,7 +27356,7 @@
         <v>4.62</v>
       </c>
       <c r="M516">
-        <v>4.8</v>
+        <v>4.79</v>
       </c>
       <c r="N516">
         <v>4.63</v>
@@ -27362,7 +27365,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27412,7 +27415,7 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27462,7 +27465,7 @@
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27612,7 +27615,7 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-03328-601328.xlsx
+++ b/s60_signal/position-03328-601328.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="401">
   <si>
     <t>trade_time</t>
   </si>
@@ -469,6 +469,12 @@
     <t>2021-11-19</t>
   </si>
   <si>
+    <t>2021-11-26</t>
+  </si>
+  <si>
+    <t>2021-11-16</t>
+  </si>
+  <si>
     <t>2016-05-31</t>
   </si>
   <si>
@@ -847,7 +853,7 @@
     <t>2021-11-23</t>
   </si>
   <si>
-    <t>2021-11-08</t>
+    <t>2021-11-29</t>
   </si>
   <si>
     <t>2016-05-24</t>
@@ -1568,7 +1574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P521"/>
+  <dimension ref="A1:P522"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1629,7 +1635,7 @@
         <v>2.636521639996683</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E2">
         <v>2.833647241107702</v>
@@ -1665,7 +1671,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1679,7 +1685,7 @@
         <v>2.808801457176021</v>
       </c>
       <c r="D3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E3">
         <v>2.7135041663212</v>
@@ -1715,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1729,7 +1735,7 @@
         <v>2.746397091058633</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E4">
         <v>2.648930323263125</v>
@@ -1779,7 +1785,7 @@
         <v>2.683209227271539</v>
       </c>
       <c r="D5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E5">
         <v>2.583545744375049</v>
@@ -1815,7 +1821,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1829,7 +1835,7 @@
         <v>2.555958070922727</v>
       </c>
       <c r="D6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E6">
         <v>2.632522016358742</v>
@@ -1865,7 +1871,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1879,7 +1885,7 @@
         <v>2.641252819939413</v>
       </c>
       <c r="D7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E7">
         <v>2.540130729835057</v>
@@ -1915,7 +1921,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1929,7 +1935,7 @@
         <v>2.512285655110759</v>
       </c>
       <c r="D8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E8">
         <v>2.590994611146576</v>
@@ -1965,7 +1971,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1979,7 +1985,7 @@
         <v>2.615441102246784</v>
       </c>
       <c r="D9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E9">
         <v>2.513421672263544</v>
@@ -2015,7 +2021,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2029,7 +2035,7 @@
         <v>2.515418243442972</v>
       </c>
       <c r="D10" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E10">
         <v>2.545423958143926</v>
@@ -2065,7 +2071,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2079,7 +2085,7 @@
         <v>2.487273994427867</v>
       </c>
       <c r="D11" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E11">
         <v>2.567211421027677</v>
@@ -2115,7 +2121,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2129,7 +2135,7 @@
         <v>2.487984580081365</v>
       </c>
       <c r="D12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E12">
         <v>2.579898802553291</v>
@@ -2165,7 +2171,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2179,7 +2185,7 @@
         <v>2.500805561667341</v>
       </c>
       <c r="D13" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E13">
         <v>2.59216563562278</v>
@@ -2215,7 +2221,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2229,7 +2235,7 @@
         <v>2.499441989042522</v>
       </c>
       <c r="D14" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E14">
         <v>2.736702547602069</v>
@@ -2279,7 +2285,7 @@
         <v>2.512520850741042</v>
       </c>
       <c r="D15" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E15">
         <v>2.749061943431123</v>
@@ -2315,7 +2321,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2329,7 +2335,7 @@
         <v>2.77984350091858</v>
       </c>
       <c r="D16" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E16">
         <v>2.889061943431122</v>
@@ -2365,7 +2371,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2379,7 +2385,7 @@
         <v>2.517224153471577</v>
       </c>
       <c r="D17" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E17">
         <v>2.753506518310076</v>
@@ -2415,7 +2421,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2429,7 +2435,7 @@
         <v>2.784426680003737</v>
       </c>
       <c r="D18" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E18">
         <v>2.924119959439183</v>
@@ -2465,7 +2471,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2479,7 +2485,7 @@
         <v>2.884280694854824</v>
       </c>
       <c r="D19" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E19">
         <v>2.961861794886389</v>
@@ -2529,7 +2535,7 @@
         <v>2.920719956495094</v>
       </c>
       <c r="D20" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E20">
         <v>2.907075620138133</v>
@@ -2565,7 +2571,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2579,7 +2585,7 @@
         <v>2.648180125005333</v>
       </c>
       <c r="D21" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E21">
         <v>2.848908919700521</v>
@@ -2615,7 +2621,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2665,7 +2671,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2679,7 +2685,7 @@
         <v>2.691620213913162</v>
       </c>
       <c r="D23" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E23">
         <v>2.889959376998489</v>
@@ -2715,7 +2721,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2729,7 +2735,7 @@
         <v>2.984719616116966</v>
       </c>
       <c r="D24" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E24">
         <v>2.755965243802971</v>
@@ -2765,7 +2771,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2779,7 +2785,7 @@
         <v>3.007275184023352</v>
       </c>
       <c r="D25" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E25">
         <v>2.755965243802971</v>
@@ -2815,7 +2821,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2829,7 +2835,7 @@
         <v>2.683495528297218</v>
       </c>
       <c r="D26" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E26">
         <v>2.882281628901694</v>
@@ -2865,7 +2871,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2879,7 +2885,7 @@
         <v>2.976914171586129</v>
       </c>
       <c r="D27" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E27">
         <v>2.747824596132772</v>
@@ -2915,7 +2921,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2929,7 +2935,7 @@
         <v>2.647048085674867</v>
       </c>
       <c r="D28" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E28">
         <v>2.84783915365346</v>
@@ -2965,7 +2971,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2979,7 +2985,7 @@
         <v>2.941898848516719</v>
       </c>
       <c r="D29" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E29">
         <v>2.711305547532774</v>
@@ -3015,7 +3021,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3029,7 +3035,7 @@
         <v>2.962790623816959</v>
       </c>
       <c r="D30" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E30">
         <v>2.711305547532774</v>
@@ -3065,7 +3071,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3079,7 +3085,7 @@
         <v>2.636850318680218</v>
       </c>
       <c r="D31" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E31">
         <v>2.674077933106496</v>
@@ -3115,7 +3121,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3129,7 +3135,7 @@
         <v>2.64386308474694</v>
       </c>
       <c r="D32" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E32">
         <v>2.844829359063415</v>
@@ -3165,7 +3171,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3179,7 +3185,7 @@
         <v>2.938838994972993</v>
       </c>
       <c r="D33" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E33">
         <v>2.708114289235636</v>
@@ -3215,7 +3221,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3229,7 +3235,7 @@
         <v>2.959611880258242</v>
       </c>
       <c r="D34" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E34">
         <v>2.708114289235636</v>
@@ -3265,7 +3271,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3279,7 +3285,7 @@
         <v>2.63362151616782</v>
       </c>
       <c r="D35" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E35">
         <v>2.706375129633912</v>
@@ -3315,7 +3321,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3329,7 +3335,7 @@
         <v>2.623711665472045</v>
       </c>
       <c r="D36" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E36">
         <v>2.825786465799713</v>
@@ -3365,7 +3371,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3379,7 +3385,7 @@
         <v>2.919479379991807</v>
       </c>
       <c r="D37" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E37">
         <v>2.687923279746057</v>
@@ -3415,7 +3421,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3429,7 +3435,7 @@
         <v>2.939500051198033</v>
       </c>
       <c r="D38" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E38">
         <v>2.687923279746057</v>
@@ -3465,7 +3471,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3479,7 +3485,7 @@
         <v>2.613192965390128</v>
       </c>
       <c r="D39" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E39">
         <v>2.65740457966414</v>
@@ -3515,7 +3521,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3529,7 +3535,7 @@
         <v>2.866121269202039</v>
       </c>
       <c r="D40" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E40">
         <v>2.632273716345684</v>
@@ -3579,7 +3585,7 @@
         <v>2.884068721379623</v>
       </c>
       <c r="D41" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E41">
         <v>2.632273716345684</v>
@@ -3629,7 +3635,7 @@
         <v>2.556888701243869</v>
       </c>
       <c r="D42" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E42">
         <v>2.5709911987269</v>
@@ -3679,7 +3685,7 @@
         <v>2.84066903268222</v>
       </c>
       <c r="D43" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E43">
         <v>2.605728438993726</v>
@@ -3715,7 +3721,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3729,7 +3735,7 @@
         <v>2.857627543154535</v>
       </c>
       <c r="D44" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E44">
         <v>2.605728438993726</v>
@@ -3765,7 +3771,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3779,7 +3785,7 @@
         <v>2.530031126511299</v>
       </c>
       <c r="D45" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E45">
         <v>2.536232918189681</v>
@@ -3815,7 +3821,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3829,7 +3835,7 @@
         <v>2.794653597980052</v>
       </c>
       <c r="D46" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E46">
         <v>2.557736881328888</v>
@@ -3865,7 +3871,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3879,7 +3885,7 @@
         <v>2.809824187676618</v>
       </c>
       <c r="D47" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E47">
         <v>2.557736881328888</v>
@@ -3915,7 +3921,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3965,7 +3971,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3979,7 +3985,7 @@
         <v>2.877968395292299</v>
       </c>
       <c r="D49" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E49">
         <v>2.644629614722029</v>
@@ -4015,7 +4021,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4029,7 +4035,7 @@
         <v>2.896376165252531</v>
       </c>
       <c r="D50" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E50">
         <v>2.644629614722029</v>
@@ -4065,7 +4071,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4079,7 +4085,7 @@
         <v>2.521770137334771</v>
       </c>
       <c r="D51" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E51">
         <v>2.535896862069519</v>
@@ -4115,7 +4121,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4129,7 +4135,7 @@
         <v>2.934431839092635</v>
       </c>
       <c r="D52" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E52">
         <v>2.703517868992319</v>
@@ -4165,7 +4171,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4179,7 +4185,7 @@
         <v>2.955033485192349</v>
       </c>
       <c r="D53" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E53">
         <v>2.703517868992319</v>
@@ -4215,7 +4221,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4265,7 +4271,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4279,7 +4285,7 @@
         <v>2.974730272968942</v>
       </c>
       <c r="D55" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E55">
         <v>2.745546910458406</v>
@@ -4315,7 +4321,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4329,7 +4335,7 @@
         <v>2.996897706887981</v>
       </c>
       <c r="D56" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E56">
         <v>2.745546910458406</v>
@@ -4365,7 +4371,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4379,7 +4385,7 @@
         <v>2.624468326525319</v>
       </c>
       <c r="D57" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E57">
         <v>2.660688149733082</v>
@@ -4415,7 +4421,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4429,7 +4435,7 @@
         <v>3.056805462611843</v>
       </c>
       <c r="D58" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E58">
         <v>2.831146801497014</v>
@@ -4465,7 +4471,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4515,7 +4521,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4529,7 +4535,7 @@
         <v>3.075488420323122</v>
       </c>
       <c r="D60" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E60">
         <v>2.850632094815525</v>
@@ -4579,7 +4585,7 @@
         <v>2.73140795531227</v>
       </c>
       <c r="D61" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E61">
         <v>2.75953055997749</v>
@@ -4629,7 +4635,7 @@
         <v>2.72765316464271</v>
       </c>
       <c r="D62" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E62">
         <v>2.75953055997749</v>
@@ -4679,7 +4685,7 @@
         <v>2.72671446697532</v>
       </c>
       <c r="D63" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E63">
         <v>2.75953055997749</v>
@@ -4729,7 +4735,7 @@
         <v>6.293149296554828</v>
       </c>
       <c r="D64" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E64">
         <v>5.963700498102364</v>
@@ -4765,7 +4771,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4779,7 +4785,7 @@
         <v>6.420239880180696</v>
       </c>
       <c r="D65" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E65">
         <v>6.082402264327184</v>
@@ -4815,7 +4821,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4829,7 +4835,7 @@
         <v>6.609514294497387</v>
       </c>
       <c r="D66" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E66">
         <v>6.259183317962906</v>
@@ -4865,7 +4871,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4879,7 +4885,7 @@
         <v>6.515171551263329</v>
       </c>
       <c r="D67" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E67">
         <v>6.612047937164794</v>
@@ -4915,7 +4921,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4929,7 +4935,7 @@
         <v>6.520829737768901</v>
       </c>
       <c r="D68" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E68">
         <v>6.612047937164794</v>
@@ -4965,7 +4971,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5015,7 +5021,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5065,7 +5071,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5115,7 +5121,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5129,7 +5135,7 @@
         <v>6.781478804637512</v>
       </c>
       <c r="D72" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E72">
         <v>6.821616798629249</v>
@@ -5165,7 +5171,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5179,7 +5185,7 @@
         <v>6.927933775178332</v>
       </c>
       <c r="D73" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E73">
         <v>7.025464228815041</v>
@@ -5215,7 +5221,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5229,7 +5235,7 @@
         <v>7.465293617228137</v>
       </c>
       <c r="D74" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E74">
         <v>7.441132824526438</v>
@@ -5265,7 +5271,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5279,7 +5285,7 @@
         <v>2.399740228983164</v>
       </c>
       <c r="D75" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E75">
         <v>2.284756328614283</v>
@@ -5315,7 +5321,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5329,7 +5335,7 @@
         <v>2.181146111927123</v>
       </c>
       <c r="D76" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E76">
         <v>2.105842395854763</v>
@@ -5365,7 +5371,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5379,7 +5385,7 @@
         <v>2.180858495485883</v>
       </c>
       <c r="D77" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E77">
         <v>2.105842395854763</v>
@@ -5415,7 +5421,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5429,7 +5435,7 @@
         <v>2.355267416838251</v>
       </c>
       <c r="D78" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E78">
         <v>2.241615480893012</v>
@@ -5465,7 +5471,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5479,7 +5485,7 @@
         <v>2.138079262229388</v>
       </c>
       <c r="D79" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E79">
         <v>2.115876072829124</v>
@@ -5515,7 +5521,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5529,7 +5535,7 @@
         <v>2.136977667529256</v>
       </c>
       <c r="D80" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E80">
         <v>2.115876072829124</v>
@@ -5565,7 +5571,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5615,7 +5621,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5665,7 +5671,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5715,7 +5721,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5729,7 +5735,7 @@
         <v>1.925553832103902</v>
       </c>
       <c r="D84" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E84">
         <v>1.985821650998686</v>
@@ -5765,7 +5771,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5815,7 +5821,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5829,7 +5835,7 @@
         <v>1.87975631937778</v>
       </c>
       <c r="D86" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E86">
         <v>2.025900250164519</v>
@@ -5865,7 +5871,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5965,7 +5971,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5979,7 +5985,7 @@
         <v>1.789383875507923</v>
       </c>
       <c r="D89" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E89">
         <v>1.940268655809146</v>
@@ -6015,7 +6021,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6029,7 +6035,7 @@
         <v>1.804905667333501</v>
       </c>
       <c r="D90" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E90">
         <v>1.95497618970289</v>
@@ -6065,7 +6071,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6079,7 +6085,7 @@
         <v>1.809491967335235</v>
       </c>
       <c r="D91" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E91">
         <v>1.959321896917648</v>
@@ -6115,7 +6121,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6129,7 +6135,7 @@
         <v>1.822908408572121</v>
       </c>
       <c r="D92" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E92">
         <v>1.972034524843747</v>
@@ -6165,7 +6171,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6179,7 +6185,7 @@
         <v>2.011491451443282</v>
       </c>
       <c r="D93" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E93">
         <v>1.930405304642352</v>
@@ -6215,7 +6221,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6229,7 +6235,7 @@
         <v>1.820166348365971</v>
       </c>
       <c r="D94" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E94">
         <v>1.969436310418903</v>
@@ -6265,7 +6271,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6279,7 +6285,7 @@
         <v>2.008879751476441</v>
       </c>
       <c r="D95" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E95">
         <v>1.927766633591516</v>
@@ -6315,7 +6321,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6329,7 +6335,7 @@
         <v>1.780154910291897</v>
       </c>
       <c r="D96" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E96">
         <v>1.931523833030682</v>
@@ -6365,7 +6371,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6415,7 +6421,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6429,7 +6435,7 @@
         <v>1.781411528733962</v>
       </c>
       <c r="D98" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E98">
         <v>1.932714530505294</v>
@@ -6465,7 +6471,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6515,7 +6521,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6529,7 +6535,7 @@
         <v>1.786869994736246</v>
       </c>
       <c r="D100" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E100">
         <v>1.937886650750082</v>
@@ -6579,7 +6585,7 @@
         <v>1.77389224303264</v>
       </c>
       <c r="D101" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E101">
         <v>1.925589699135846</v>
@@ -6615,7 +6621,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6629,7 +6635,7 @@
         <v>1.764225388294109</v>
       </c>
       <c r="D102" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E102">
         <v>1.916429958088516</v>
@@ -6829,7 +6835,7 @@
         <v>2.039049007419374</v>
       </c>
       <c r="D106" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E106">
         <v>1.958247448115615</v>
@@ -6865,7 +6871,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6879,7 +6885,7 @@
         <v>1.963804213639886</v>
       </c>
       <c r="D107" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E107">
         <v>2.044635472991321</v>
@@ -6915,7 +6921,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6929,7 +6935,7 @@
         <v>2.084469221121035</v>
       </c>
       <c r="D108" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E108">
         <v>2.00413671738046</v>
@@ -6965,7 +6971,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6979,7 +6985,7 @@
         <v>1.970692549466935</v>
       </c>
       <c r="D109" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E109">
         <v>2.103970465510173</v>
@@ -7015,7 +7021,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7065,7 +7071,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7079,7 +7085,7 @@
         <v>1.989826166099606</v>
       </c>
       <c r="D111" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E111">
         <v>2.069999197311251</v>
@@ -7115,7 +7121,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7129,7 +7135,7 @@
         <v>1.996538974422711</v>
       </c>
       <c r="D112" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E112">
         <v>2.129860772341935</v>
@@ -7165,7 +7171,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7215,7 +7221,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7229,7 +7235,7 @@
         <v>1.976959483296697</v>
       </c>
       <c r="D114" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E114">
         <v>2.110248039295503</v>
@@ -7329,7 +7335,7 @@
         <v>1.920546112528168</v>
       </c>
       <c r="D116" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E116">
         <v>2.053738890308352</v>
@@ -7365,7 +7371,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7415,7 +7421,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7429,7 +7435,7 @@
         <v>2.078859445890371</v>
       </c>
       <c r="D118" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E118">
         <v>2.128859445890371</v>
@@ -7465,7 +7471,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7479,7 +7485,7 @@
         <v>1.864471846503076</v>
       </c>
       <c r="D119" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E119">
         <v>1.997569421794252</v>
@@ -7515,7 +7521,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7565,7 +7571,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7615,7 +7621,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7629,7 +7635,7 @@
         <v>1.863420505387863</v>
       </c>
       <c r="D122" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E122">
         <v>1.996516295719591</v>
@@ -7729,7 +7735,7 @@
         <v>2.029857360363785</v>
       </c>
       <c r="D124" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E124">
         <v>2.011995247378231</v>
@@ -7779,7 +7785,7 @@
         <v>1.892165706973767</v>
       </c>
       <c r="D125" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E125">
         <v>2.025310300703773</v>
@@ -7815,7 +7821,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7865,7 +7871,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7915,7 +7921,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7979,7 +7985,7 @@
         <v>2.183293967129219</v>
       </c>
       <c r="D129" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E129">
         <v>2.097698061214447</v>
@@ -8029,7 +8035,7 @@
         <v>2.10409703769314</v>
       </c>
       <c r="D130" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E130">
         <v>2.097698061214447</v>
@@ -8115,7 +8121,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8165,7 +8171,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8215,7 +8221,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8265,7 +8271,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8315,7 +8321,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8365,7 +8371,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8415,7 +8421,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8465,7 +8471,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8479,7 +8485,7 @@
         <v>2.367284598691813</v>
       </c>
       <c r="D139" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E139">
         <v>2.284677125480481</v>
@@ -8529,7 +8535,7 @@
         <v>2.308705785003503</v>
       </c>
       <c r="D140" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E140">
         <v>2.284677125480481</v>
@@ -8665,7 +8671,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8715,7 +8721,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8765,7 +8771,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8815,7 +8821,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8865,7 +8871,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8929,7 +8935,7 @@
         <v>2.673055621612132</v>
       </c>
       <c r="D148" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E148">
         <v>2.649383477311975</v>
@@ -8979,7 +8985,7 @@
         <v>2.694510447967022</v>
       </c>
       <c r="D149" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E149">
         <v>2.66746656530884</v>
@@ -9029,7 +9035,7 @@
         <v>2.61961842602696</v>
       </c>
       <c r="D150" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E150">
         <v>2.674946565009619</v>
@@ -9315,7 +9321,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9329,7 +9335,7 @@
         <v>2.746485076848839</v>
       </c>
       <c r="D156" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E156">
         <v>2.847982602490786</v>
@@ -9365,7 +9371,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9429,7 +9435,7 @@
         <v>2.750734210259811</v>
       </c>
       <c r="D158" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E158">
         <v>2.800734210259812</v>
@@ -9465,7 +9471,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9529,7 +9535,7 @@
         <v>2.717092536535202</v>
       </c>
       <c r="D160" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E160">
         <v>2.791717770085309</v>
@@ -9615,7 +9621,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9629,7 +9635,7 @@
         <v>2.669840281895235</v>
       </c>
       <c r="D162" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E162">
         <v>2.754805459723328</v>
@@ -9665,7 +9671,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9729,7 +9735,7 @@
         <v>2.704152220032186</v>
       </c>
       <c r="D164" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E164">
         <v>2.721608307945189</v>
@@ -9779,7 +9785,7 @@
         <v>0.7516342779874527</v>
       </c>
       <c r="D165" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E165">
         <v>0.6447312303040151</v>
@@ -9815,7 +9821,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9829,7 +9835,7 @@
         <v>0.6347312303040145</v>
       </c>
       <c r="D166" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E166">
         <v>0.7803954970608276</v>
@@ -9865,7 +9871,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9879,7 +9885,7 @@
         <v>0.7872985447442655</v>
       </c>
       <c r="D167" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E167">
         <v>0.6685373256708909</v>
@@ -9915,7 +9921,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9929,7 +9935,7 @@
         <v>0.6141118398407031</v>
       </c>
       <c r="D168" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E168">
         <v>0.7042015924277036</v>
@@ -9965,7 +9971,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9979,7 +9985,7 @@
         <v>0.7076194190074974</v>
       </c>
       <c r="D169" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E169">
         <v>0.8524403513495589</v>
@@ -10029,7 +10035,7 @@
         <v>0.8587410173081755</v>
       </c>
       <c r="D170" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E170">
         <v>0.7402207509247285</v>
@@ -10079,7 +10085,7 @@
         <v>0.6868795521992208</v>
       </c>
       <c r="D171" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E171">
         <v>0.7750416832667906</v>
@@ -10129,7 +10135,7 @@
         <v>0.794311018129779</v>
       </c>
       <c r="D172" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E172">
         <v>0.9381289071762104</v>
@@ -10165,7 +10171,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10179,7 +10185,7 @@
         <v>0.7478436529603893</v>
       </c>
       <c r="D173" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E173">
         <v>0.9381289071762104</v>
@@ -10215,7 +10221,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10229,7 +10235,7 @@
         <v>0.9437131136379486</v>
       </c>
       <c r="D174" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E174">
         <v>0.8254794310532532</v>
@@ -10265,7 +10271,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10279,7 +10285,7 @@
         <v>0.7734278594221262</v>
       </c>
       <c r="D175" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E175">
         <v>0.8592973200996861</v>
@@ -10315,7 +10321,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10329,7 +10335,7 @@
         <v>0.9016190641047892</v>
       </c>
       <c r="D176" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E176">
         <v>1.04419537245399</v>
@@ -10365,7 +10371,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10379,7 +10385,7 @@
         <v>0.8558611736195321</v>
       </c>
       <c r="D177" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E177">
         <v>1.04419537245399</v>
@@ -10415,7 +10421,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10429,7 +10435,7 @@
         <v>1.048892735560562</v>
       </c>
       <c r="D178" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E178">
         <v>0.9310137903179339</v>
@@ -10465,7 +10471,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10479,7 +10485,7 @@
         <v>0.8805585367261042</v>
       </c>
       <c r="D179" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E179">
         <v>0.963590098667134</v>
@@ -10515,7 +10521,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10529,7 +10535,7 @@
         <v>1.076170489586433</v>
       </c>
       <c r="D180" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E180">
         <v>1.260525374010979</v>
@@ -10579,7 +10585,7 @@
         <v>1.26341395784032</v>
       </c>
       <c r="D181" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E181">
         <v>1.146258524308584</v>
@@ -10629,7 +10635,7 @@
         <v>1.099059073415773</v>
       </c>
       <c r="D182" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E182">
         <v>1.176302541669659</v>
@@ -10679,7 +10685,7 @@
         <v>1.931268098407571</v>
       </c>
       <c r="D183" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E183">
         <v>1.946759727730396</v>
@@ -10715,7 +10721,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10765,7 +10771,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10815,7 +10821,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10829,7 +10835,7 @@
         <v>0.5942088493584849</v>
       </c>
       <c r="D186" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E186">
         <v>0.5982130518354056</v>
@@ -10865,7 +10871,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10915,7 +10921,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10965,7 +10971,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11015,7 +11021,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11029,7 +11035,7 @@
         <v>-0.02499489055226256</v>
       </c>
       <c r="D190" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E190">
         <v>-0.07499489055226238</v>
@@ -11065,7 +11071,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11079,7 +11085,7 @@
         <v>-0.04541693580813089</v>
       </c>
       <c r="D191" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E191">
         <v>-0.1350880582477796</v>
@@ -11115,7 +11121,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11165,7 +11171,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11215,7 +11221,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11365,7 +11371,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11379,7 +11385,7 @@
         <v>-0.5154661476950757</v>
       </c>
       <c r="D197" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E197">
         <v>-0.4838284745942198</v>
@@ -11415,7 +11421,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11429,7 +11435,7 @@
         <v>-0.5144835438345625</v>
       </c>
       <c r="D198" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E198">
         <v>-0.4838284745942198</v>
@@ -11465,7 +11471,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11515,7 +11521,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11529,7 +11535,7 @@
         <v>-0.6795603356321358</v>
       </c>
       <c r="D200" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E200">
         <v>-0.6353746161347429</v>
@@ -11565,7 +11571,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11579,7 +11585,7 @@
         <v>-0.6770489039336995</v>
       </c>
       <c r="D201" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E201">
         <v>-0.6353746161347429</v>
@@ -11615,7 +11621,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11665,7 +11671,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11679,7 +11685,7 @@
         <v>-1.275160705635463</v>
       </c>
       <c r="D203" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E203">
         <v>-0.9575450227817477</v>
@@ -11715,7 +11721,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11729,7 +11735,7 @@
         <v>-1.267100202166811</v>
       </c>
       <c r="D204" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E204">
         <v>-0.9575450227817477</v>
@@ -11765,7 +11771,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11829,7 +11835,7 @@
         <v>-1.30354206111917</v>
       </c>
       <c r="D206" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E206">
         <v>-0.9846924062879019</v>
@@ -11879,7 +11885,7 @@
         <v>-1.295217135083899</v>
       </c>
       <c r="D207" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E207">
         <v>-0.9846924062879019</v>
@@ -11929,7 +11935,7 @@
         <v>-1.315601110783377</v>
       </c>
       <c r="D208" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E208">
         <v>-0.9962271494449686</v>
@@ -11979,7 +11985,7 @@
         <v>-1.307163833353718</v>
       </c>
       <c r="D209" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E209">
         <v>-0.9962271494449686</v>
@@ -12029,7 +12035,7 @@
         <v>-1.303470101275702</v>
       </c>
       <c r="D210" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E210">
         <v>-0.9846235751332797</v>
@@ -12065,7 +12071,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12079,7 +12085,7 @@
         <v>-1.295145845673754</v>
       </c>
       <c r="D211" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E211">
         <v>-0.9846235751332797</v>
@@ -12115,7 +12121,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12129,7 +12135,7 @@
         <v>-1.352240812118975</v>
       </c>
       <c r="D212" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E212">
         <v>-1.031273820287715</v>
@@ -12165,7 +12171,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12179,7 +12185,7 @@
         <v>-1.343462171012276</v>
       </c>
       <c r="D213" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E213">
         <v>-1.031273820287715</v>
@@ -12215,7 +12221,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12265,7 +12271,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12279,7 +12285,7 @@
         <v>-1.277973836666044</v>
       </c>
       <c r="D215" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E215">
         <v>-0.9602358437675207</v>
@@ -12329,7 +12335,7 @@
         <v>-1.269887123902075</v>
       </c>
       <c r="D216" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E216">
         <v>-0.9602358437675207</v>
@@ -12379,7 +12385,7 @@
         <v>-1.030235843767521</v>
       </c>
       <c r="D217" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E217">
         <v>-1.080019061857596</v>
@@ -12429,7 +12435,7 @@
         <v>-1.007888992711643</v>
       </c>
       <c r="D218" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E218">
         <v>-1.080019061857596</v>
@@ -12479,7 +12485,7 @@
         <v>-1.154349245698821</v>
       </c>
       <c r="D219" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E219">
         <v>-0.8419862350162637</v>
@@ -12529,7 +12535,7 @@
         <v>-1.147414314838273</v>
       </c>
       <c r="D220" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E220">
         <v>-0.8419862350162637</v>
@@ -12679,7 +12685,7 @@
         <v>-0.9332125637434627</v>
       </c>
       <c r="D223" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E223">
         <v>-0.6304641914067899</v>
@@ -12715,7 +12721,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12729,7 +12735,7 @@
         <v>-0.9283379125284608</v>
       </c>
       <c r="D224" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E224">
         <v>-0.6304641914067899</v>
@@ -12765,7 +12771,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12779,7 +12785,7 @@
         <v>-1.078298911794628</v>
       </c>
       <c r="D225" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E225">
         <v>-0.7337942740491279</v>
@@ -12829,7 +12835,7 @@
         <v>-1.284045732215318</v>
       </c>
       <c r="D226" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E226">
         <v>-0.9315166474955321</v>
@@ -12879,7 +12885,7 @@
         <v>-1.074552792811861</v>
       </c>
       <c r="D227" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E227">
         <v>-0.7301942595508679</v>
@@ -12915,7 +12921,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12929,7 +12935,7 @@
         <v>0.6306184682796347</v>
       </c>
       <c r="D228" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E228">
         <v>0.8825890610024754</v>
@@ -12965,7 +12971,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12979,7 +12985,7 @@
         <v>2.500083924851446</v>
       </c>
       <c r="D229" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E229">
         <v>2.721828222716436</v>
@@ -13015,7 +13021,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13029,7 +13035,7 @@
         <v>2.484743417251086</v>
       </c>
       <c r="D230" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E230">
         <v>2.721828222716436</v>
@@ -13065,7 +13071,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13079,7 +13085,7 @@
         <v>2.959498476516616</v>
       </c>
       <c r="D231" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E231">
         <v>3.019498476516616</v>
@@ -13115,7 +13121,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13165,7 +13171,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13179,7 +13185,7 @@
         <v>3.973072767193392</v>
       </c>
       <c r="D233" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E233">
         <v>3.630196829293595</v>
@@ -13215,7 +13221,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13265,7 +13271,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13315,7 +13321,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13329,7 +13335,7 @@
         <v>4.556254256131551</v>
       </c>
       <c r="D236" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E236">
         <v>4.211276763316661</v>
@@ -13365,7 +13371,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13415,7 +13421,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13465,7 +13471,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13479,7 +13485,7 @@
         <v>4.667791750685101</v>
       </c>
       <c r="D239" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E239">
         <v>4.322412320952902</v>
@@ -13515,7 +13521,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13529,7 +13535,7 @@
         <v>4.273963746622406</v>
       </c>
       <c r="D240" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E240">
         <v>4.266274031756307</v>
@@ -13565,7 +13571,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13615,7 +13621,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13665,7 +13671,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13679,7 +13685,7 @@
         <v>3.655351043939968</v>
       </c>
       <c r="D243" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E243">
         <v>3.313620049187031</v>
@@ -13715,7 +13721,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13729,7 +13735,7 @@
         <v>2.349652973133038</v>
       </c>
       <c r="D244" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E244">
         <v>2.585321458264525</v>
@@ -13779,7 +13785,7 @@
         <v>2.337296219946928</v>
       </c>
       <c r="D245" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E245">
         <v>2.585321458264525</v>
@@ -13829,7 +13835,7 @@
         <v>2.821499834857581</v>
       </c>
       <c r="D246" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E246">
         <v>2.482773709326562</v>
@@ -13879,7 +13885,7 @@
         <v>1.399171925433256</v>
       </c>
       <c r="D247" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E247">
         <v>1.7228188215915</v>
@@ -13915,7 +13921,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13929,7 +13935,7 @@
         <v>1.94957093986026</v>
       </c>
       <c r="D248" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E248">
         <v>1.61398690043734</v>
@@ -13965,7 +13971,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13979,7 +13985,7 @@
         <v>1.388298565840941</v>
       </c>
       <c r="D249" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E249">
         <v>1.05473712956764</v>
@@ -14029,7 +14035,7 @@
         <v>1.206849236469149</v>
       </c>
       <c r="D250" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E250">
         <v>0.8739416716530437</v>
@@ -14079,7 +14085,7 @@
         <v>1.250249534396463</v>
       </c>
       <c r="D251" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E251">
         <v>0.9171855721103492</v>
@@ -14129,7 +14135,7 @@
         <v>1.265784593473219</v>
       </c>
       <c r="D252" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E252">
         <v>0.9326646489922341</v>
@@ -14165,7 +14171,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14179,7 +14185,7 @@
         <v>1.181086185990114</v>
       </c>
       <c r="D253" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E253">
         <v>0.8482714609955542</v>
@@ -14229,7 +14235,7 @@
         <v>3.393868635799184</v>
       </c>
       <c r="D254" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E254">
         <v>3.232668972857903</v>
@@ -14265,7 +14271,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14279,7 +14285,7 @@
         <v>3.344337857016143</v>
       </c>
       <c r="D255" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E255">
         <v>3.232668972857903</v>
@@ -14315,7 +14321,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14329,7 +14335,7 @@
         <v>3.108144846549583</v>
       </c>
       <c r="D256" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E256">
         <v>3.176241351782863</v>
@@ -14365,7 +14371,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14379,7 +14385,7 @@
         <v>3.110765478091183</v>
       </c>
       <c r="D257" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E257">
         <v>3.176241351782863</v>
@@ -14415,7 +14421,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14429,7 +14435,7 @@
         <v>3.484929217459694</v>
       </c>
       <c r="D258" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E258">
         <v>3.328403460479749</v>
@@ -14465,7 +14471,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14479,7 +14485,7 @@
         <v>3.438944160440425</v>
       </c>
       <c r="D259" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E259">
         <v>3.328403460479749</v>
@@ -14515,7 +14521,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14565,7 +14571,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14615,7 +14621,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14629,7 +14635,7 @@
         <v>3.67612531160249</v>
       </c>
       <c r="D262" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E262">
         <v>3.529413159454653</v>
@@ -14665,7 +14671,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14679,7 +14685,7 @@
         <v>3.637585058248958</v>
       </c>
       <c r="D263" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E263">
         <v>3.529413159454653</v>
@@ -14715,7 +14721,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14729,7 +14735,7 @@
         <v>3.405388602484038</v>
       </c>
       <c r="D264" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E264">
         <v>3.509413159454653</v>
@@ -14765,7 +14771,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14779,7 +14785,7 @@
         <v>3.405511387337113</v>
       </c>
       <c r="D265" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E265">
         <v>3.509413159454653</v>
@@ -14815,7 +14821,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14829,7 +14835,7 @@
         <v>3.451364045513422</v>
       </c>
       <c r="D266" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E266">
         <v>3.509413159454653</v>
@@ -14865,7 +14871,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14879,7 +14885,7 @@
         <v>4.004636932335591</v>
       </c>
       <c r="D267" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E267">
         <v>3.867442887120403</v>
@@ -14929,7 +14935,7 @@
         <v>3.774439165379895</v>
       </c>
       <c r="D268" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E268">
         <v>3.837640654076098</v>
@@ -14979,7 +14985,7 @@
         <v>4.220199786446392</v>
       </c>
       <c r="D269" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E269">
         <v>4.085943565478028</v>
@@ -15015,7 +15021,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15029,7 +15035,7 @@
         <v>3.991103703583256</v>
       </c>
       <c r="D270" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E270">
         <v>4.0441357312043</v>
@@ -15065,7 +15071,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15079,7 +15085,7 @@
         <v>4.24807262091024</v>
       </c>
       <c r="D271" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E271">
         <v>4.172298835483293</v>
@@ -15115,7 +15121,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15129,7 +15135,7 @@
         <v>4.076733299050661</v>
       </c>
       <c r="D272" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E272">
         <v>4.185185728196767</v>
@@ -15165,7 +15171,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15229,7 +15235,7 @@
         <v>3.853669569225198</v>
       </c>
       <c r="D274" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E274">
         <v>3.960609701897911</v>
@@ -15365,7 +15371,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15379,7 +15385,7 @@
         <v>3.457860783201086</v>
       </c>
       <c r="D277" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E277">
         <v>3.562117466477025</v>
@@ -15415,7 +15421,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15429,7 +15435,7 @@
         <v>3.461796612382101</v>
       </c>
       <c r="D278" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E278">
         <v>3.45818163729601</v>
@@ -15465,7 +15471,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15529,7 +15535,7 @@
         <v>1.876063224574707</v>
       </c>
       <c r="D280" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E280">
         <v>1.926860456775207</v>
@@ -15579,7 +15585,7 @@
         <v>1.879462993924748</v>
       </c>
       <c r="D281" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E281">
         <v>1.926860456775207</v>
@@ -15629,7 +15635,7 @@
         <v>1.36286186891499</v>
       </c>
       <c r="D282" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E282">
         <v>1.420876924621103</v>
@@ -15665,7 +15671,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15679,7 +15685,7 @@
         <v>1.365396205962064</v>
       </c>
       <c r="D283" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E283">
         <v>1.420876924621103</v>
@@ -15715,7 +15721,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15729,7 +15735,7 @@
         <v>1.492587172538397</v>
       </c>
       <c r="D284" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E284">
         <v>1.422587172538397</v>
@@ -15765,7 +15771,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15779,7 +15785,7 @@
         <v>1.155028253713973</v>
       </c>
       <c r="D285" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E285">
         <v>1.207786135342488</v>
@@ -15829,7 +15835,7 @@
         <v>1.157212112489207</v>
       </c>
       <c r="D286" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E286">
         <v>1.207786135342488</v>
@@ -15879,7 +15885,7 @@
         <v>1.287557383512098</v>
       </c>
       <c r="D287" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E287">
         <v>1.260086513310223</v>
@@ -15929,7 +15935,7 @@
         <v>-0.2566084186298667</v>
       </c>
       <c r="D288" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E288">
         <v>-0.001048450451905936</v>
@@ -15965,7 +15971,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15979,7 +15985,7 @@
         <v>-0.2875710874180024</v>
       </c>
       <c r="D289" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E289">
         <v>-0.001048450451905936</v>
@@ -16015,7 +16021,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16065,7 +16071,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16115,7 +16121,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16129,7 +16135,7 @@
         <v>-0.3429456734762377</v>
       </c>
       <c r="D292" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E292">
         <v>-0.1559309932859021</v>
@@ -16165,7 +16171,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16179,7 +16185,7 @@
         <v>-0.452945673476238</v>
       </c>
       <c r="D293" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E293">
         <v>-0.1559309932859021</v>
@@ -16215,7 +16221,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16229,7 +16235,7 @@
         <v>-0.07614423041516449</v>
       </c>
       <c r="D294" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E294">
         <v>-0.08649962563060054</v>
@@ -16265,7 +16271,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16279,7 +16285,7 @@
         <v>-0.06685502084603723</v>
       </c>
       <c r="D295" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E295">
         <v>-0.08649962563060054</v>
@@ -16315,7 +16321,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16329,7 +16335,7 @@
         <v>-0.6325763258089658</v>
       </c>
       <c r="D296" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E296">
         <v>-0.7397037652284588</v>
@@ -16365,7 +16371,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16379,7 +16385,7 @@
         <v>-0.6888811406779016</v>
       </c>
       <c r="D297" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E297">
         <v>-0.6347573064746772</v>
@@ -16415,7 +16421,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16429,7 +16435,7 @@
         <v>-0.5922830059527424</v>
       </c>
       <c r="D298" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E298">
         <v>-0.6988811406779014</v>
@@ -16465,7 +16471,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16479,7 +16485,7 @@
         <v>-0.7708727781363214</v>
       </c>
       <c r="D299" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E299">
         <v>-0.7160845060282481</v>
@@ -16515,7 +16521,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16529,7 +16535,7 @@
         <v>-0.6732115427634033</v>
       </c>
       <c r="D300" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E300">
         <v>-0.7808727781363212</v>
@@ -16565,7 +16571,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16579,7 +16585,7 @@
         <v>-0.6051723879795468</v>
       </c>
       <c r="D301" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E301">
         <v>-0.5517269067155315</v>
@@ -16615,7 +16621,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16629,7 +16635,7 @@
         <v>-0.509659617957122</v>
       </c>
       <c r="D302" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E302">
         <v>-0.6151723879795465</v>
@@ -16665,7 +16671,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16679,7 +16685,7 @@
         <v>1.374867998585327</v>
       </c>
       <c r="D303" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E303">
         <v>1.61428021608427</v>
@@ -16715,7 +16721,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16729,7 +16735,7 @@
         <v>1.37455579980999</v>
       </c>
       <c r="D304" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E304">
         <v>1.61428021608427</v>
@@ -16765,7 +16771,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16779,7 +16785,7 @@
         <v>1.659046067002767</v>
       </c>
       <c r="D305" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E305">
         <v>1.701663141543517</v>
@@ -16815,7 +16821,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16829,7 +16835,7 @@
         <v>1.400425101402588</v>
       </c>
       <c r="D306" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E306">
         <v>1.63789275673065</v>
@@ -16865,7 +16871,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16879,7 +16885,7 @@
         <v>1.415426421593279</v>
       </c>
       <c r="D307" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E307">
         <v>1.63789275673065</v>
@@ -16915,7 +16921,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16929,7 +16935,7 @@
         <v>1.672891436539961</v>
       </c>
       <c r="D308" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E308">
         <v>1.702888796158578</v>
@@ -16965,7 +16971,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16979,7 +16985,7 @@
         <v>1.682896717302726</v>
       </c>
       <c r="D309" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E309">
         <v>1.702888796158578</v>
@@ -17015,7 +17021,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17029,7 +17035,7 @@
         <v>1.392287936404873</v>
       </c>
       <c r="D310" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E310">
         <v>1.630374723852328</v>
@@ -17065,7 +17071,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17079,7 +17085,7 @@
         <v>1.392192134372636</v>
       </c>
       <c r="D311" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E311">
         <v>1.630374723852328</v>
@@ -17115,7 +17121,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17129,7 +17135,7 @@
         <v>1.665398674360388</v>
       </c>
       <c r="D312" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E312">
         <v>1.367982501138595</v>
@@ -17165,7 +17171,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17179,7 +17185,7 @@
         <v>1.67530287232815</v>
       </c>
       <c r="D313" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E313">
         <v>1.367982501138595</v>
@@ -17215,7 +17221,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17229,7 +17235,7 @@
         <v>1.683187064752997</v>
       </c>
       <c r="D314" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E314">
         <v>1.385560910531628</v>
@@ -17265,7 +17271,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17279,7 +17285,7 @@
         <v>1.693331241005988</v>
       </c>
       <c r="D315" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E315">
         <v>1.385560910531628</v>
@@ -17315,7 +17321,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17329,7 +17335,7 @@
         <v>1.671335210176903</v>
       </c>
       <c r="D316" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E316">
         <v>1.373848959803819</v>
@@ -17365,7 +17371,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17379,7 +17385,7 @@
         <v>1.68131949631757</v>
       </c>
       <c r="D317" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E317">
         <v>1.373848959803819</v>
@@ -17415,7 +17421,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17429,7 +17435,7 @@
         <v>1.693875753393727</v>
       </c>
       <c r="D318" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E318">
         <v>1.396123425781996</v>
@@ -17465,7 +17471,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17479,7 +17485,7 @@
         <v>1.704164127807133</v>
       </c>
       <c r="D319" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E319">
         <v>1.396123425781996</v>
@@ -17515,7 +17521,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17529,7 +17535,7 @@
         <v>1.366123425781996</v>
       </c>
       <c r="D320" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E320">
         <v>1.403731566187024</v>
@@ -17565,7 +17571,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17579,7 +17585,7 @@
         <v>1.710631890779994</v>
       </c>
       <c r="D321" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E321">
         <v>1.412681767280061</v>
@@ -17615,7 +17621,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17629,7 +17635,7 @@
         <v>1.72114631763706</v>
       </c>
       <c r="D322" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E322">
         <v>1.412681767280061</v>
@@ -17665,7 +17671,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17679,7 +17685,7 @@
         <v>1.382681767280062</v>
       </c>
       <c r="D323" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E323">
         <v>1.420374677351461</v>
@@ -17715,7 +17721,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17729,7 +17735,7 @@
         <v>1.679206240881443</v>
       </c>
       <c r="D324" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E324">
         <v>1.381627077835624</v>
@@ -17779,7 +17785,7 @@
         <v>1.689296712933807</v>
       </c>
       <c r="D325" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E325">
         <v>1.381627077835624</v>
@@ -17829,7 +17835,7 @@
         <v>1.351627077835625</v>
       </c>
       <c r="D326" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E326">
         <v>1.364138386842169</v>
@@ -17879,7 +17885,7 @@
         <v>1.662615013806636</v>
       </c>
       <c r="D327" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E327">
         <v>1.365231699984297</v>
@@ -17915,7 +17921,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17929,7 +17935,7 @@
         <v>1.672481658175022</v>
       </c>
       <c r="D328" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E328">
         <v>1.365231699984297</v>
@@ -17965,7 +17971,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17979,7 +17985,7 @@
         <v>1.335231699984297</v>
       </c>
       <c r="D329" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E329">
         <v>1.330198361076394</v>
@@ -18015,7 +18021,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18029,7 +18035,7 @@
         <v>1.638483426036899</v>
       </c>
       <c r="D330" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E330">
         <v>1.341384970754843</v>
@@ -18079,7 +18085,7 @@
         <v>1.648024517787818</v>
       </c>
       <c r="D331" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E331">
         <v>1.341384970754843</v>
@@ -18179,7 +18185,7 @@
         <v>1.611118158429232</v>
       </c>
       <c r="D333" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E333">
         <v>1.31434273328757</v>
@@ -18229,7 +18235,7 @@
         <v>1.620290072876844</v>
       </c>
       <c r="D334" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E334">
         <v>1.31434273328757</v>
@@ -18279,7 +18285,7 @@
         <v>1.210704115653037</v>
       </c>
       <c r="D335" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E335">
         <v>1.321946243981619</v>
@@ -18329,7 +18335,7 @@
         <v>1.250704115653037</v>
       </c>
       <c r="D336" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E336">
         <v>1.321946243981619</v>
@@ -18379,7 +18385,7 @@
         <v>1.580824889600507</v>
       </c>
       <c r="D337" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E337">
         <v>1.284407057851428</v>
@@ -18415,7 +18421,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18429,7 +18435,7 @@
         <v>1.589588125885168</v>
       </c>
       <c r="D338" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E338">
         <v>1.284407057851428</v>
@@ -18465,7 +18471,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18479,7 +18485,7 @@
         <v>1.180206507742837</v>
       </c>
       <c r="D339" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E339">
         <v>1.27675246238701</v>
@@ -18515,7 +18521,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18529,7 +18535,7 @@
         <v>1.220206507742837</v>
       </c>
       <c r="D340" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E340">
         <v>1.27675246238701</v>
@@ -18565,7 +18571,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18579,7 +18585,7 @@
         <v>1.680056540073359</v>
       </c>
       <c r="D341" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E341">
         <v>1.409353064352823</v>
@@ -18615,7 +18621,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18629,7 +18635,7 @@
         <v>1.717732409003494</v>
       </c>
       <c r="D342" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E342">
         <v>1.409353064352823</v>
@@ -18665,7 +18671,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18679,7 +18685,7 @@
         <v>1.307497917096648</v>
       </c>
       <c r="D343" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E343">
         <v>1.444235818399402</v>
@@ -18715,7 +18721,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18729,7 +18735,7 @@
         <v>1.347497917096648</v>
       </c>
       <c r="D344" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E344">
         <v>1.444235818399402</v>
@@ -18765,7 +18771,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18779,7 +18785,7 @@
         <v>1.842256392262994</v>
       </c>
       <c r="D345" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E345">
         <v>1.530769127897027</v>
@@ -18829,7 +18835,7 @@
         <v>1.431193121765403</v>
       </c>
       <c r="D346" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E346">
         <v>1.572471675023835</v>
@@ -18879,7 +18885,7 @@
         <v>1.471193121765403</v>
       </c>
       <c r="D347" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E347">
         <v>1.572471675023835</v>
@@ -18929,7 +18935,7 @@
         <v>2.306011000659936</v>
       </c>
       <c r="D348" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E348">
         <v>2.348379970519409</v>
@@ -18965,7 +18971,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18979,7 +18985,7 @@
         <v>2.400485390479259</v>
       </c>
       <c r="D349" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E349">
         <v>2.364696230398958</v>
@@ -19015,7 +19021,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19065,7 +19071,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19079,7 +19085,7 @@
         <v>2.315116384839492</v>
       </c>
       <c r="D351" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E351">
         <v>2.323814331699535</v>
@@ -19115,7 +19121,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19129,7 +19135,7 @@
         <v>2.158186337006185</v>
       </c>
       <c r="D352" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E352">
         <v>2.199105803820263</v>
@@ -19165,7 +19171,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19215,7 +19221,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19265,7 +19271,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19279,7 +19285,7 @@
         <v>2.249949180664442</v>
       </c>
       <c r="D355" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E355">
         <v>2.193589002935801</v>
@@ -19315,7 +19321,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19329,7 +19335,7 @@
         <v>3.29910210514231</v>
       </c>
       <c r="D356" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E356">
         <v>3.35230135785332</v>
@@ -19365,7 +19371,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19379,7 +19385,7 @@
         <v>3.804045197377832</v>
       </c>
       <c r="D357" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E357">
         <v>3.415154291605215</v>
@@ -19415,7 +19421,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19429,7 +19435,7 @@
         <v>3.427249571448392</v>
       </c>
       <c r="D358" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E358">
         <v>3.291626526785035</v>
@@ -19465,7 +19471,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19515,7 +19521,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19529,7 +19535,7 @@
         <v>3.442581197445604</v>
       </c>
       <c r="D360" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E360">
         <v>3.306414237004073</v>
@@ -19565,7 +19571,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19579,7 +19585,7 @@
         <v>3.36022431872702</v>
       </c>
       <c r="D361" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E361">
         <v>3.226979110080385</v>
@@ -19615,7 +19621,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19629,7 +19635,7 @@
         <v>3.251003700388559</v>
       </c>
       <c r="D362" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E362">
         <v>3.121633280862579</v>
@@ -19665,7 +19671,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19679,7 +19685,7 @@
         <v>2.99001278638902</v>
       </c>
       <c r="D363" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E363">
         <v>3.032275977245447</v>
@@ -19765,7 +19771,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19779,7 +19785,7 @@
         <v>2.786342722576059</v>
       </c>
       <c r="D365" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E365">
         <v>2.830017022419643</v>
@@ -19815,7 +19821,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19829,7 +19835,7 @@
         <v>2.881784622628198</v>
       </c>
       <c r="D366" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E366">
         <v>2.846342722576059</v>
@@ -19865,7 +19871,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19879,7 +19885,7 @@
         <v>2.713139299753176</v>
       </c>
       <c r="D367" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E367">
         <v>2.672915915531583</v>
@@ -19915,7 +19921,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19929,7 +19935,7 @@
         <v>2.722022378645214</v>
       </c>
       <c r="D368" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E368">
         <v>2.672915915531583</v>
@@ -19965,7 +19971,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19979,7 +19985,7 @@
         <v>2.643362683974768</v>
       </c>
       <c r="D369" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E369">
         <v>2.68802760764238</v>
@@ -20015,7 +20021,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20029,7 +20035,7 @@
         <v>2.738474376085565</v>
       </c>
       <c r="D370" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E370">
         <v>2.678250991863972</v>
@@ -20065,7 +20071,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20079,7 +20085,7 @@
         <v>2.26156876679942</v>
       </c>
       <c r="D371" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E371">
         <v>2.319500204055783</v>
@@ -20115,7 +20121,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20129,7 +20135,7 @@
         <v>2.341086491507057</v>
       </c>
       <c r="D372" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E372">
         <v>2.284741341701965</v>
@@ -20165,7 +20171,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20179,7 +20185,7 @@
         <v>2.25156876679942</v>
       </c>
       <c r="D373" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E373">
         <v>2.298948197976329</v>
@@ -20215,7 +20221,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20229,7 +20235,7 @@
         <v>2.345775623073784</v>
       </c>
       <c r="D374" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E374">
         <v>2.287361910525056</v>
@@ -20265,7 +20271,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20279,7 +20285,7 @@
         <v>1.450725995788351</v>
       </c>
       <c r="D375" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E375">
         <v>1.543612412630503</v>
@@ -20315,7 +20321,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20329,7 +20335,7 @@
         <v>1.378039753255653</v>
       </c>
       <c r="D376" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E376">
         <v>1.473954763536668</v>
@@ -20365,7 +20371,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20379,7 +20385,7 @@
         <v>2.300473418774809</v>
       </c>
       <c r="D377" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E377">
         <v>2.269274816103397</v>
@@ -20429,7 +20435,7 @@
         <v>2.307737312105645</v>
       </c>
       <c r="D378" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E378">
         <v>2.269274816103397</v>
@@ -20479,7 +20485,7 @@
         <v>2.548688372146674</v>
       </c>
       <c r="D379" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E379">
         <v>2.44021981851742</v>
@@ -20515,7 +20521,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20529,7 +20535,7 @@
         <v>4.064626779899114</v>
       </c>
       <c r="D380" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E380">
         <v>3.971827788774664</v>
@@ -20565,7 +20571,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20579,7 +20585,7 @@
         <v>2.704221825320051</v>
       </c>
       <c r="D381" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E381">
         <v>2.757514946748523</v>
@@ -20615,7 +20621,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20629,7 +20635,7 @@
         <v>2.699698304540886</v>
       </c>
       <c r="D382" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E382">
         <v>2.757514946748523</v>
@@ -20665,7 +20671,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20679,7 +20685,7 @@
         <v>2.597723564836138</v>
       </c>
       <c r="D383" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E383">
         <v>2.648687698460786</v>
@@ -20715,7 +20721,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20729,7 +20735,7 @@
         <v>2.594470401040876</v>
       </c>
       <c r="D384" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E384">
         <v>2.648687698460786</v>
@@ -20765,7 +20771,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20779,7 +20785,7 @@
         <v>2.5327482758737</v>
       </c>
       <c r="D385" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E385">
         <v>2.582291478725809</v>
@@ -20815,7 +20821,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20829,7 +20835,7 @@
         <v>2.530270165227095</v>
       </c>
       <c r="D386" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E386">
         <v>2.582291478725809</v>
@@ -20865,7 +20871,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20879,7 +20885,7 @@
         <v>2.615226386520305</v>
       </c>
       <c r="D387" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E387">
         <v>2.605226386520305</v>
@@ -20915,7 +20921,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20929,7 +20935,7 @@
         <v>2.519210324106</v>
       </c>
       <c r="D388" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E388">
         <v>2.474919909368535</v>
@@ -20965,7 +20971,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20979,7 +20985,7 @@
         <v>2.443973795685154</v>
       </c>
       <c r="D389" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E389">
         <v>2.491575608314453</v>
@@ -21015,7 +21021,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21029,7 +21035,7 @@
         <v>2.442554625160083</v>
       </c>
       <c r="D390" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E390">
         <v>2.491575608314453</v>
@@ -21065,7 +21071,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21115,7 +21121,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21129,7 +21135,7 @@
         <v>2.457705873063223</v>
       </c>
       <c r="D392" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E392">
         <v>2.413049360402885</v>
@@ -21165,7 +21171,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21179,7 +21185,7 @@
         <v>2.382591377283335</v>
       </c>
       <c r="D393" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E393">
         <v>2.428850830862097</v>
@@ -21215,7 +21221,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21229,7 +21235,7 @@
         <v>2.381904402604011</v>
       </c>
       <c r="D394" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E394">
         <v>2.428850830862097</v>
@@ -21265,7 +21271,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21279,7 +21285,7 @@
         <v>2.46327835196266</v>
       </c>
       <c r="D395" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E395">
         <v>2.453507343522435</v>
@@ -21315,7 +21321,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21329,7 +21335,7 @@
         <v>2.467705873063223</v>
       </c>
       <c r="D396" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E396">
         <v>2.453507343522435</v>
@@ -21365,7 +21371,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21379,7 +21385,7 @@
         <v>2.447999298642713</v>
       </c>
       <c r="D397" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E397">
         <v>2.403285008753682</v>
@@ -21415,7 +21421,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21429,7 +21435,7 @@
         <v>2.372904061939057</v>
       </c>
       <c r="D398" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E398">
         <v>2.418951665679276</v>
@@ -21465,7 +21471,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21479,7 +21485,7 @@
         <v>2.37233264171712</v>
       </c>
       <c r="D399" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E399">
         <v>2.418951665679276</v>
@@ -21515,7 +21521,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21565,7 +21571,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21615,7 +21621,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21629,7 +21635,7 @@
         <v>2.414261420787727</v>
       </c>
       <c r="D402" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E402">
         <v>2.369346310197177</v>
@@ -21665,7 +21671,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21715,7 +21721,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21765,7 +21771,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21779,7 +21785,7 @@
         <v>2.424261420787727</v>
       </c>
       <c r="D405" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E405">
         <v>2.394544385485897</v>
@@ -21815,7 +21821,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21829,7 +21835,7 @@
         <v>2.414374606666995</v>
       </c>
       <c r="D406" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E406">
         <v>2.394544385485897</v>
@@ -21865,7 +21871,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21879,7 +21885,7 @@
         <v>2.397600622679596</v>
       </c>
       <c r="D407" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E407">
         <v>2.352586340671736</v>
@@ -21915,7 +21921,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21929,7 +21935,7 @@
         <v>2.322605383348882</v>
       </c>
       <c r="D408" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E408">
         <v>2.367553015986731</v>
@@ -21965,7 +21971,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21979,7 +21985,7 @@
         <v>2.322633947364601</v>
       </c>
       <c r="D409" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E409">
         <v>2.367553015986731</v>
@@ -22015,7 +22021,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22029,7 +22035,7 @@
         <v>2.402576819333163</v>
       </c>
       <c r="D410" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E410">
         <v>2.35256729799459</v>
@@ -22065,7 +22071,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22079,7 +22085,7 @@
         <v>2.407600622679595</v>
       </c>
       <c r="D411" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E411">
         <v>2.35256729799459</v>
@@ -22115,7 +22121,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22129,7 +22135,7 @@
         <v>2.39758158000245</v>
       </c>
       <c r="D412" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E412">
         <v>2.35256729799459</v>
@@ -22165,7 +22171,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22179,7 +22185,7 @@
         <v>2.378737718650321</v>
       </c>
       <c r="D413" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E413">
         <v>2.33361115745181</v>
@@ -22215,7 +22221,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22229,7 +22235,7 @@
         <v>2.30377990571649</v>
       </c>
       <c r="D414" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E414">
         <v>2.348315847988621</v>
@@ -22265,7 +22271,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22279,7 +22285,7 @@
         <v>2.304033028113511</v>
       </c>
       <c r="D415" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E415">
         <v>2.348315847988621</v>
@@ -22315,7 +22321,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22329,7 +22335,7 @@
         <v>2.383526783319471</v>
       </c>
       <c r="D416" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E416">
         <v>2.333442409187131</v>
@@ -22365,7 +22371,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22379,7 +22385,7 @@
         <v>2.38873771865032</v>
       </c>
       <c r="D417" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E417">
         <v>2.333442409187131</v>
@@ -22415,7 +22421,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22429,7 +22435,7 @@
         <v>2.378568970385641</v>
       </c>
       <c r="D418" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E418">
         <v>2.333442409187131</v>
@@ -22465,7 +22471,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22479,7 +22485,7 @@
         <v>2.29477967980894</v>
       </c>
       <c r="D419" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E419">
         <v>2.33911879805526</v>
@@ -22529,7 +22535,7 @@
         <v>2.295140160765494</v>
       </c>
       <c r="D420" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E420">
         <v>2.33911879805526</v>
@@ -22579,7 +22585,7 @@
         <v>2.374419198852388</v>
       </c>
       <c r="D421" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E421">
         <v>2.324299038533536</v>
@@ -22629,7 +22635,7 @@
         <v>2.379719599649515</v>
       </c>
       <c r="D422" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E422">
         <v>2.324299038533536</v>
@@ -22679,7 +22685,7 @@
         <v>2.369479279011813</v>
       </c>
       <c r="D423" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E423">
         <v>2.324299038533536</v>
@@ -22729,7 +22735,7 @@
         <v>2.280590400920047</v>
       </c>
       <c r="D424" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E424">
         <v>2.324619216844741</v>
@@ -22765,7 +22771,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22779,7 +22785,7 @@
         <v>2.281120137688396</v>
       </c>
       <c r="D425" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E425">
         <v>2.324619216844741</v>
@@ -22815,7 +22821,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22829,7 +22835,7 @@
         <v>2.360060664151698</v>
       </c>
       <c r="D426" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E426">
         <v>2.309884085228915</v>
@@ -22865,7 +22871,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22915,7 +22921,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22929,7 +22935,7 @@
         <v>2.281700069738552</v>
       </c>
       <c r="D428" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E428">
         <v>2.325753152774585</v>
@@ -22965,7 +22971,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -22979,7 +22985,7 @@
         <v>2.282216569900716</v>
       </c>
       <c r="D429" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E429">
         <v>2.325753152774585</v>
@@ -23015,7 +23021,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23029,7 +23035,7 @@
         <v>2.361183569576388</v>
       </c>
       <c r="D430" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E430">
         <v>2.311011402855666</v>
@@ -23065,7 +23071,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23079,7 +23085,7 @@
         <v>2.255753152774584</v>
       </c>
       <c r="D431" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E431">
         <v>2.30032273597278</v>
@@ -23115,7 +23121,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23129,7 +23135,7 @@
         <v>2.248769782041177</v>
       </c>
       <c r="D432" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E432">
         <v>2.297801715354081</v>
@@ -23165,7 +23171,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23179,7 +23185,7 @@
         <v>2.343406757033516</v>
       </c>
       <c r="D433" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E433">
         <v>2.293164740361742</v>
@@ -23215,7 +23221,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23229,7 +23235,7 @@
         <v>2.237801715354081</v>
       </c>
       <c r="D434" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E434">
         <v>2.26243869034642</v>
@@ -23265,7 +23271,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23279,7 +23285,7 @@
         <v>2.228095614122554</v>
       </c>
       <c r="D435" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E435">
         <v>2.276800683120539</v>
@@ -23315,7 +23321,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23329,7 +23335,7 @@
         <v>2.322610014996799</v>
       </c>
       <c r="D436" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E436">
         <v>2.263257480497806</v>
@@ -23365,7 +23371,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23415,7 +23421,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23429,7 +23435,7 @@
         <v>2.224983216186275</v>
       </c>
       <c r="D438" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E438">
         <v>2.273639077311749</v>
@@ -23479,7 +23485,7 @@
         <v>2.319479164108328</v>
       </c>
       <c r="D439" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E439">
         <v>2.26015123354559</v>
@@ -23629,7 +23635,7 @@
         <v>2.3116287572162</v>
       </c>
       <c r="D442" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E442">
         <v>2.252362519438469</v>
@@ -23665,7 +23671,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23715,7 +23721,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23765,7 +23771,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23829,7 +23835,7 @@
         <v>2.185149484739352</v>
       </c>
       <c r="D446" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E446">
         <v>2.165149484739352</v>
@@ -23929,7 +23935,7 @@
         <v>2.20020073233055</v>
       </c>
       <c r="D448" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E448">
         <v>2.205687152603988</v>
@@ -24015,7 +24021,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24065,7 +24071,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24115,7 +24121,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24165,7 +24171,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24215,7 +24221,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24329,7 +24335,7 @@
         <v>2.142114930387524</v>
       </c>
       <c r="D456" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E456">
         <v>2.162114930387524</v>
@@ -24365,7 +24371,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24379,7 +24385,7 @@
         <v>2.115413806995409</v>
       </c>
       <c r="D457" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E457">
         <v>2.141244762127619</v>
@@ -24465,7 +24471,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24479,7 +24485,7 @@
         <v>2.073994682974101</v>
       </c>
       <c r="D459" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E459">
         <v>2.082201671198685</v>
@@ -24529,7 +24535,7 @@
         <v>2.083994682974101</v>
       </c>
       <c r="D460" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E460">
         <v>2.082201671198685</v>
@@ -24615,7 +24621,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24629,7 +24635,7 @@
         <v>2.057461365020192</v>
       </c>
       <c r="D462" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E462">
         <v>2.066125824243982</v>
@@ -24665,7 +24671,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24715,7 +24721,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24765,7 +24771,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24815,7 +24821,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24865,7 +24871,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24879,7 +24885,7 @@
         <v>2.057577737614682</v>
       </c>
       <c r="D467" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E467">
         <v>2.099815205781953</v>
@@ -24915,7 +24921,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24979,7 +24985,7 @@
         <v>2.075267052489131</v>
       </c>
       <c r="D469" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E469">
         <v>2.105974841560053</v>
@@ -25029,7 +25035,7 @@
         <v>2.0673904197019</v>
       </c>
       <c r="D470" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E470">
         <v>2.109513786914668</v>
@@ -25079,7 +25085,7 @@
         <v>2.101281730695467</v>
       </c>
       <c r="D471" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E471">
         <v>2.131889846669813</v>
@@ -25129,7 +25135,7 @@
         <v>2.093106078618507</v>
       </c>
       <c r="D472" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E472">
         <v>2.134930426541548</v>
@@ -25179,7 +25185,7 @@
         <v>2.114232378900782</v>
       </c>
       <c r="D473" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E473">
         <v>2.144790875533345</v>
@@ -25215,7 +25221,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25229,7 +25235,7 @@
         <v>2.164790875533345</v>
       </c>
       <c r="D474" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E474">
         <v>2.134232378900781</v>
@@ -25265,7 +25271,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25279,7 +25285,7 @@
         <v>2.105907868798473</v>
       </c>
       <c r="D475" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E475">
         <v>2.147583358696166</v>
@@ -25315,7 +25321,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25329,7 +25335,7 @@
         <v>2.178667208693582</v>
       </c>
       <c r="D476" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E476">
         <v>2.148162082573172</v>
@@ -25365,7 +25371,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25379,7 +25385,7 @@
         <v>2.119677460934401</v>
       </c>
       <c r="D477" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E477">
         <v>2.161192839295628</v>
@@ -25415,7 +25421,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25429,7 +25435,7 @@
         <v>2.191253934723685</v>
       </c>
       <c r="D478" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E478">
         <v>2.160797219088007</v>
@@ -25479,7 +25485,7 @@
         <v>2.132167365995042</v>
       </c>
       <c r="D479" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E479">
         <v>2.173537512902076</v>
@@ -25579,7 +25585,7 @@
         <v>2.161339958759847</v>
       </c>
       <c r="D481" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E481">
         <v>2.202370889471942</v>
@@ -25629,7 +25635,7 @@
         <v>2.215480849833102</v>
       </c>
       <c r="D482" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E482">
         <v>2.179965384477054</v>
@@ -25679,7 +25685,7 @@
         <v>1.276065947508897</v>
       </c>
       <c r="D483" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E483">
         <v>1.317566169928825</v>
@@ -25715,7 +25721,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25729,7 +25735,7 @@
         <v>1.37689891014235</v>
       </c>
       <c r="D484" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E484">
         <v>1.288399132562277</v>
@@ -25765,7 +25771,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25779,7 +25785,7 @@
         <v>1.265250934212467</v>
       </c>
       <c r="D485" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E485">
         <v>1.306889515011455</v>
@@ -25815,7 +25821,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25829,7 +25835,7 @@
         <v>1.365853299547489</v>
       </c>
       <c r="D486" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E486">
         <v>1.277491880346475</v>
@@ -25865,7 +25871,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25879,7 +25885,7 @@
         <v>1.365250934212467</v>
       </c>
       <c r="D487" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E487">
         <v>1.29891353608099</v>
@@ -25915,7 +25921,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25929,7 +25935,7 @@
         <v>1.335853299547488</v>
       </c>
       <c r="D488" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E488">
         <v>1.29891353608099</v>
@@ -25965,7 +25971,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25979,7 +25985,7 @@
         <v>1.257848770795328</v>
       </c>
       <c r="D489" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E489">
         <v>1.29958204878089</v>
@@ -26015,7 +26021,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26029,7 +26035,7 @@
         <v>1.358293307486061</v>
       </c>
       <c r="D490" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E490">
         <v>1.270026585471621</v>
@@ -26065,7 +26071,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26079,7 +26085,7 @@
         <v>1.328293307486061</v>
       </c>
       <c r="D491" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E491">
         <v>1.291337761155134</v>
@@ -26115,7 +26121,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26129,7 +26135,7 @@
         <v>1.336383675279734</v>
       </c>
       <c r="D492" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E492">
         <v>1.248391395422367</v>
@@ -26179,7 +26185,7 @@
         <v>1.306383675279734</v>
       </c>
       <c r="D493" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E493">
         <v>1.269382388589295</v>
@@ -26229,7 +26235,7 @@
         <v>1.279467032224208</v>
       </c>
       <c r="D494" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E494">
         <v>1.192187695703653</v>
@@ -26265,7 +26271,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26279,7 +26285,7 @@
         <v>1.280668138023285</v>
       </c>
       <c r="D495" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E495">
         <v>1.2123469216443</v>
@@ -26315,7 +26321,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26329,7 +26335,7 @@
         <v>1.249467032224208</v>
       </c>
       <c r="D496" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E496">
         <v>1.2123469216443</v>
@@ -26365,7 +26371,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26379,7 +26385,7 @@
         <v>1.175386037005039</v>
       </c>
       <c r="D497" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E497">
         <v>1.183866479324669</v>
@@ -26415,7 +26421,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26429,7 +26435,7 @@
         <v>1.24514956586386</v>
       </c>
       <c r="D498" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E498">
         <v>1.158300093222558</v>
@@ -26465,7 +26471,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26479,7 +26485,7 @@
         <v>1.247067111461691</v>
       </c>
       <c r="D499" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E499">
         <v>1.177957811304076</v>
@@ -26515,7 +26521,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26529,7 +26535,7 @@
         <v>1.21514956586386</v>
       </c>
       <c r="D500" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E500">
         <v>1.177957811304076</v>
@@ -26565,7 +26571,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26579,7 +26585,7 @@
         <v>1.140423774825811</v>
       </c>
       <c r="D501" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E501">
         <v>1.202341320423642</v>
@@ -26615,7 +26621,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26629,7 +26635,7 @@
         <v>1.226637749198502</v>
       </c>
       <c r="D502" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E502">
         <v>1.140020157350503</v>
@@ -26665,7 +26671,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26679,7 +26685,7 @@
         <v>1.196637749198502</v>
       </c>
       <c r="D503" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E503">
         <v>1.159407347839835</v>
@@ -26715,7 +26721,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26729,7 +26735,7 @@
         <v>1.121564136970499</v>
       </c>
       <c r="D504" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E504">
         <v>1.183868150557168</v>
@@ -26765,7 +26771,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26779,7 +26785,7 @@
         <v>1.183891513054156</v>
       </c>
       <c r="D505" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E505">
         <v>1.097809364665167</v>
@@ -26815,7 +26821,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26829,7 +26835,7 @@
         <v>1.153891513054155</v>
       </c>
       <c r="D506" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E506">
         <v>1.116571871118987</v>
@@ -26865,7 +26871,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26879,7 +26885,7 @@
         <v>1.078014735637637</v>
       </c>
       <c r="D507" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E507">
         <v>1.141211154989324</v>
@@ -26915,7 +26921,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26923,43 +26929,43 @@
         <v>0</v>
       </c>
       <c r="B508" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C508">
-        <v>1.120386130880944</v>
+        <v>1.043879816012319</v>
       </c>
       <c r="D508" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E508">
-        <v>1.082996540339985</v>
+        <v>1.107775721421902</v>
       </c>
       <c r="F508">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G508">
-        <v>0.008199613869119058</v>
+        <v>0.008256120183987683</v>
       </c>
       <c r="H508">
-        <v>0.008177003459660014</v>
+        <v>0.008172224278578097</v>
       </c>
       <c r="I508">
-        <v>0.03738959054095847</v>
+        <v>0.0638959054095829</v>
       </c>
       <c r="J508">
         <v>0.7389590540958364</v>
       </c>
       <c r="K508">
-        <v>4.79</v>
+        <v>4.88</v>
       </c>
       <c r="L508">
-        <v>4.66</v>
+        <v>4.65</v>
       </c>
       <c r="M508">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="N508">
-        <v>4.63</v>
+        <v>4.64</v>
       </c>
       <c r="O508">
         <v>1</v>
@@ -26970,34 +26976,34 @@
     </row>
     <row r="509" spans="1:16">
       <c r="A509" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B509" t="s">
         <v>150</v>
       </c>
       <c r="C509">
-        <v>1.043879816012319</v>
+        <v>0.9836705709653022</v>
       </c>
       <c r="D509" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E509">
-        <v>1.107775721421902</v>
+        <v>1.048800272379947</v>
       </c>
       <c r="F509">
         <v>1</v>
       </c>
       <c r="G509">
-        <v>0.008256120183987683</v>
+        <v>0.008316329429034699</v>
       </c>
       <c r="H509">
-        <v>0.008172224278578097</v>
+        <v>0.008231199727620053</v>
       </c>
       <c r="I509">
-        <v>0.0638959054095829</v>
+        <v>0.06512970141464436</v>
       </c>
       <c r="J509">
-        <v>0.7389590540958364</v>
+        <v>0.7512970141464546</v>
       </c>
       <c r="K509">
         <v>4.88</v>
@@ -27015,157 +27021,157 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>147</v>
+        <v>275</v>
       </c>
     </row>
     <row r="510" spans="1:16">
       <c r="A510" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B510" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C510">
-        <v>1.096417003653128</v>
+        <v>1.073929973794593</v>
       </c>
       <c r="D510" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E510">
-        <v>1.023774332097018</v>
+        <v>1.086468884218986</v>
       </c>
       <c r="F510">
         <v>-1</v>
       </c>
       <c r="G510">
-        <v>0.008143582996346873</v>
+        <v>0.008106070026205408</v>
       </c>
       <c r="H510">
-        <v>0.008236225667902983</v>
+        <v>0.008073531115781015</v>
       </c>
       <c r="I510">
-        <v>0.07264267155610948</v>
+        <v>-0.01253891042439337</v>
       </c>
       <c r="J510">
         <v>0.7512970141464546</v>
       </c>
       <c r="K510">
-        <v>4.69</v>
+        <v>4.68</v>
       </c>
       <c r="L510">
-        <v>4.62</v>
+        <v>4.59</v>
       </c>
       <c r="M510">
-        <v>4.8</v>
+        <v>4.65</v>
       </c>
       <c r="N510">
-        <v>4.63</v>
+        <v>4.58</v>
       </c>
       <c r="O510">
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="511" spans="1:16">
       <c r="A511" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B511" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C511">
-        <v>1.061287302238483</v>
+        <v>0.8606424187706248</v>
       </c>
       <c r="D511" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E511">
-        <v>1.023774332097018</v>
+        <v>0.9282931888777832</v>
       </c>
       <c r="F511">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G511">
-        <v>0.008258712697761517</v>
+        <v>0.008439357581229377</v>
       </c>
       <c r="H511">
-        <v>0.008236225667902983</v>
+        <v>0.008351706811122217</v>
       </c>
       <c r="I511">
-        <v>0.03751297014146449</v>
+        <v>0.06765077010715848</v>
       </c>
       <c r="J511">
-        <v>0.7512970141464546</v>
+        <v>0.7765077010715934</v>
       </c>
       <c r="K511">
-        <v>4.79</v>
+        <v>4.88</v>
       </c>
       <c r="L511">
-        <v>4.66</v>
+        <v>4.65</v>
       </c>
       <c r="M511">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="N511">
-        <v>4.63</v>
+        <v>4.64</v>
       </c>
       <c r="O511">
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>273</v>
+        <v>398</v>
       </c>
     </row>
     <row r="512" spans="1:16">
       <c r="A512" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B512" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C512">
-        <v>0.9836705709653022</v>
+        <v>0.955943958984943</v>
       </c>
       <c r="D512" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E512">
-        <v>1.048800272379947</v>
+        <v>0.9692391900170905</v>
       </c>
       <c r="F512">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G512">
-        <v>0.008316329429034699</v>
+        <v>0.008224056041015058</v>
       </c>
       <c r="H512">
-        <v>0.008231199727620053</v>
+        <v>0.008190760809982911</v>
       </c>
       <c r="I512">
-        <v>0.06512970141464436</v>
+        <v>-0.01329523103214747</v>
       </c>
       <c r="J512">
-        <v>0.7512970141464546</v>
+        <v>0.7765077010715934</v>
       </c>
       <c r="K512">
-        <v>4.88</v>
+        <v>4.68</v>
       </c>
       <c r="L512">
+        <v>4.59</v>
+      </c>
+      <c r="M512">
         <v>4.65</v>
       </c>
-      <c r="M512">
-        <v>4.78</v>
-      </c>
       <c r="N512">
-        <v>4.64</v>
+        <v>4.58</v>
       </c>
       <c r="O512">
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>273</v>
+        <v>398</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27173,49 +27179,49 @@
         <v>0</v>
       </c>
       <c r="B513" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C513">
-        <v>0.9781788819742268</v>
+        <v>0.746167021374426</v>
       </c>
       <c r="D513" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E513">
-        <v>0.9027630348563518</v>
+        <v>0.7925110025092272</v>
       </c>
       <c r="F513">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G513">
-        <v>0.008261821118025774</v>
+        <v>0.008553832978625575</v>
       </c>
       <c r="H513">
-        <v>0.00835723696514365</v>
+        <v>0.008487488997490772</v>
       </c>
       <c r="I513">
-        <v>0.07541584711787497</v>
+        <v>0.0463439811348012</v>
       </c>
       <c r="J513">
-        <v>0.7765077010715934</v>
+        <v>0.8049140162114586</v>
       </c>
       <c r="K513">
-        <v>4.69</v>
+        <v>4.85</v>
       </c>
       <c r="L513">
-        <v>4.62</v>
+        <v>4.65</v>
       </c>
       <c r="M513">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="N513">
-        <v>4.63</v>
+        <v>4.64</v>
       </c>
       <c r="O513">
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27223,49 +27229,49 @@
         <v>1</v>
       </c>
       <c r="B514" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C514">
-        <v>0.9405281118670676</v>
+        <v>0.7220196008880824</v>
       </c>
       <c r="D514" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E514">
-        <v>0.9027630348563518</v>
+        <v>0.7925110025092272</v>
       </c>
       <c r="F514">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G514">
-        <v>0.008379471888132933</v>
+        <v>0.00857798039911192</v>
       </c>
       <c r="H514">
-        <v>0.00835723696514365</v>
+        <v>0.008487488997490772</v>
       </c>
       <c r="I514">
-        <v>0.03776507701071585</v>
+        <v>0.07049140162114487</v>
       </c>
       <c r="J514">
-        <v>0.7765077010715934</v>
+        <v>0.8049140162114586</v>
       </c>
       <c r="K514">
-        <v>4.79</v>
+        <v>4.88</v>
       </c>
       <c r="L514">
-        <v>4.66</v>
+        <v>4.65</v>
       </c>
       <c r="M514">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="N514">
-        <v>4.63</v>
+        <v>4.64</v>
       </c>
       <c r="O514">
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27273,49 +27279,49 @@
         <v>2</v>
       </c>
       <c r="B515" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C515">
-        <v>0.8606424187706248</v>
+        <v>0.8230024041303738</v>
       </c>
       <c r="D515" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E515">
-        <v>0.9282931888777832</v>
+        <v>0.8371498246167173</v>
       </c>
       <c r="F515">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G515">
-        <v>0.008439357581229377</v>
+        <v>0.008356997595869626</v>
       </c>
       <c r="H515">
-        <v>0.008351706811122217</v>
+        <v>0.008322850175383284</v>
       </c>
       <c r="I515">
-        <v>0.06765077010715848</v>
+        <v>-0.01414742048634343</v>
       </c>
       <c r="J515">
-        <v>0.7765077010715934</v>
+        <v>0.8049140162114586</v>
       </c>
       <c r="K515">
-        <v>4.88</v>
+        <v>4.68</v>
       </c>
       <c r="L515">
+        <v>4.59</v>
+      </c>
+      <c r="M515">
         <v>4.65</v>
       </c>
-      <c r="M515">
-        <v>4.78</v>
-      </c>
       <c r="N515">
-        <v>4.64</v>
+        <v>4.58</v>
       </c>
       <c r="O515">
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -27323,49 +27329,49 @@
         <v>0</v>
       </c>
       <c r="B516" t="s">
+        <v>152</v>
+      </c>
+      <c r="C516">
+        <v>0.5224815208071796</v>
+      </c>
+      <c r="D516" t="s">
+        <v>278</v>
+      </c>
+      <c r="E516">
+        <v>0.5720539524656312</v>
+      </c>
+      <c r="F516">
+        <v>1</v>
+      </c>
+      <c r="G516">
+        <v>0.008777518479192821</v>
+      </c>
+      <c r="H516">
+        <v>0.008707946047534368</v>
+      </c>
+      <c r="I516">
+        <v>0.0495724316584516</v>
+      </c>
+      <c r="J516">
+        <v>0.8510347379779013</v>
+      </c>
+      <c r="K516">
+        <v>4.85</v>
+      </c>
+      <c r="L516">
+        <v>4.65</v>
+      </c>
+      <c r="M516">
+        <v>4.78</v>
+      </c>
+      <c r="N516">
+        <v>4.64</v>
+      </c>
+      <c r="O516">
+        <v>1</v>
+      </c>
+      <c r="P516" t="s">
         <v>148</v>
-      </c>
-      <c r="C516">
-        <v>0.8449532639682586</v>
-      </c>
-      <c r="D516" t="s">
-        <v>277</v>
-      </c>
-      <c r="E516">
-        <v>0.7744618623471129</v>
-      </c>
-      <c r="F516">
-        <v>-1</v>
-      </c>
-      <c r="G516">
-        <v>0.008395046736031741</v>
-      </c>
-      <c r="H516">
-        <v>0.008485538137652886</v>
-      </c>
-      <c r="I516">
-        <v>0.07049140162114576</v>
-      </c>
-      <c r="J516">
-        <v>0.8049140162114586</v>
-      </c>
-      <c r="K516">
-        <v>4.69</v>
-      </c>
-      <c r="L516">
-        <v>4.62</v>
-      </c>
-      <c r="M516">
-        <v>4.79</v>
-      </c>
-      <c r="N516">
-        <v>4.63</v>
-      </c>
-      <c r="O516">
-        <v>1</v>
-      </c>
-      <c r="P516" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -27373,49 +27379,49 @@
         <v>1</v>
       </c>
       <c r="B517" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C517">
-        <v>0.8044618623471131</v>
+        <v>0.4969504786678423</v>
       </c>
       <c r="D517" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E517">
-        <v>0.7664127221849988</v>
+        <v>0.5720539524656312</v>
       </c>
       <c r="F517">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G517">
-        <v>0.008515538137652887</v>
+        <v>0.00880304952133216</v>
       </c>
       <c r="H517">
-        <v>0.008493587277815001</v>
+        <v>0.008707946047534368</v>
       </c>
       <c r="I517">
-        <v>0.03804914016211436</v>
+        <v>0.07510347379778892</v>
       </c>
       <c r="J517">
-        <v>0.8049140162114586</v>
+        <v>0.8510347379779013</v>
       </c>
       <c r="K517">
-        <v>4.79</v>
+        <v>4.88</v>
       </c>
       <c r="L517">
-        <v>4.66</v>
+        <v>4.65</v>
       </c>
       <c r="M517">
-        <v>4.8</v>
+        <v>4.78</v>
       </c>
       <c r="N517">
-        <v>4.63</v>
+        <v>4.64</v>
       </c>
       <c r="O517">
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>397</v>
+        <v>148</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -27423,49 +27429,49 @@
         <v>2</v>
       </c>
       <c r="B518" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C518">
-        <v>0.7220196008880824</v>
+        <v>0.6071574262634218</v>
       </c>
       <c r="D518" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E518">
-        <v>0.7925110025092272</v>
+        <v>0.6226884684027589</v>
       </c>
       <c r="F518">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G518">
-        <v>0.00857798039911192</v>
+        <v>0.008572842573736578</v>
       </c>
       <c r="H518">
-        <v>0.008487488997490772</v>
+        <v>0.008537311531597242</v>
       </c>
       <c r="I518">
-        <v>0.07049140162114487</v>
+        <v>-0.01553104213933709</v>
       </c>
       <c r="J518">
-        <v>0.8049140162114586</v>
+        <v>0.8510347379779013</v>
       </c>
       <c r="K518">
-        <v>4.88</v>
+        <v>4.68</v>
       </c>
       <c r="L518">
+        <v>4.59</v>
+      </c>
+      <c r="M518">
         <v>4.65</v>
       </c>
-      <c r="M518">
-        <v>4.78</v>
-      </c>
       <c r="N518">
-        <v>4.64</v>
+        <v>4.58</v>
       </c>
       <c r="O518">
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>397</v>
+        <v>148</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27476,28 +27482,28 @@
         <v>150</v>
       </c>
       <c r="C519">
-        <v>0.4969504786678423</v>
+        <v>0.9942742592090008</v>
       </c>
       <c r="D519" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E519">
-        <v>0.5720539524656312</v>
+        <v>1.059186671930127</v>
       </c>
       <c r="F519">
         <v>1</v>
       </c>
       <c r="G519">
-        <v>0.00880304952133216</v>
+        <v>0.008305725740791001</v>
       </c>
       <c r="H519">
-        <v>0.008707946047534368</v>
+        <v>0.008220813328069874</v>
       </c>
       <c r="I519">
-        <v>0.07510347379778892</v>
+        <v>0.06491241272112624</v>
       </c>
       <c r="J519">
-        <v>0.8510347379779013</v>
+        <v>0.7491241272112704</v>
       </c>
       <c r="K519">
         <v>4.88</v>
@@ -27515,57 +27521,57 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>148</v>
+        <v>276</v>
       </c>
     </row>
     <row r="520" spans="1:16">
       <c r="A520" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B520" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C520">
-        <v>0.9942742592090008</v>
+        <v>1.084099084651255</v>
       </c>
       <c r="D520" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E520">
-        <v>1.059186671930127</v>
+        <v>1.096572808467593</v>
       </c>
       <c r="F520">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G520">
-        <v>0.008305725740791001</v>
+        <v>0.008095900915348744</v>
       </c>
       <c r="H520">
-        <v>0.008220813328069874</v>
+        <v>0.008063427191532409</v>
       </c>
       <c r="I520">
-        <v>0.06491241272112624</v>
+        <v>-0.01247372381633793</v>
       </c>
       <c r="J520">
         <v>0.7491241272112704</v>
       </c>
       <c r="K520">
-        <v>4.88</v>
+        <v>4.68</v>
       </c>
       <c r="L520">
+        <v>4.59</v>
+      </c>
+      <c r="M520">
         <v>4.65</v>
       </c>
-      <c r="M520">
-        <v>4.78</v>
-      </c>
       <c r="N520">
-        <v>4.64</v>
+        <v>4.58</v>
       </c>
       <c r="O520">
         <v>1</v>
       </c>
       <c r="P520" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -27579,7 +27585,7 @@
         <v>1.041561394347275</v>
       </c>
       <c r="D521" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E521">
         <v>1.105504808397535</v>
@@ -27615,7 +27621,57 @@
         <v>1</v>
       </c>
       <c r="P521" t="s">
-        <v>398</v>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="522" spans="1:16">
+      <c r="A522" s="1">
+        <v>1</v>
+      </c>
+      <c r="B522" t="s">
+        <v>151</v>
+      </c>
+      <c r="C522">
+        <v>1.129448222447797</v>
+      </c>
+      <c r="D522" t="s">
+        <v>279</v>
+      </c>
+      <c r="E522">
+        <v>1.141631246662874</v>
+      </c>
+      <c r="F522">
+        <v>-1</v>
+      </c>
+      <c r="G522">
+        <v>0.008050551777552203</v>
+      </c>
+      <c r="H522">
+        <v>0.008018368753337125</v>
+      </c>
+      <c r="I522">
+        <v>-0.01218302421507778</v>
+      </c>
+      <c r="J522">
+        <v>0.7394341405026076</v>
+      </c>
+      <c r="K522">
+        <v>4.68</v>
+      </c>
+      <c r="L522">
+        <v>4.59</v>
+      </c>
+      <c r="M522">
+        <v>4.65</v>
+      </c>
+      <c r="N522">
+        <v>4.58</v>
+      </c>
+      <c r="O522">
+        <v>1</v>
+      </c>
+      <c r="P522" t="s">
+        <v>400</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-03328-601328.xlsx
+++ b/s60_signal/position-03328-601328.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1569" uniqueCount="401">
   <si>
     <t>trade_time</t>
   </si>
@@ -472,7 +472,7 @@
     <t>2021-11-26</t>
   </si>
   <si>
-    <t>2021-11-16</t>
+    <t>2021-11-29</t>
   </si>
   <si>
     <t>2016-05-31</t>
@@ -853,7 +853,7 @@
     <t>2021-11-23</t>
   </si>
   <si>
-    <t>2021-11-29</t>
+    <t>2021-11-30</t>
   </si>
   <si>
     <t>2016-05-24</t>
@@ -1574,7 +1574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P522"/>
+  <dimension ref="A1:P519"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -27035,7 +27035,7 @@
         <v>1.073929973794593</v>
       </c>
       <c r="D510" t="s">
-        <v>279</v>
+        <v>152</v>
       </c>
       <c r="E510">
         <v>1.086468884218986</v>
@@ -27129,43 +27129,43 @@
         <v>1</v>
       </c>
       <c r="B512" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C512">
-        <v>0.955943958984943</v>
+        <v>0.9692391900170905</v>
       </c>
       <c r="D512" t="s">
         <v>279</v>
       </c>
       <c r="E512">
-        <v>0.9692391900170905</v>
+        <v>1.044655037134966</v>
       </c>
       <c r="F512">
         <v>-1</v>
       </c>
       <c r="G512">
-        <v>0.008224056041015058</v>
+        <v>0.008190760809982911</v>
       </c>
       <c r="H512">
-        <v>0.008190760809982911</v>
+        <v>0.008095344962865035</v>
       </c>
       <c r="I512">
-        <v>-0.01329523103214747</v>
+        <v>-0.07541584711787586</v>
       </c>
       <c r="J512">
         <v>0.7765077010715934</v>
       </c>
       <c r="K512">
-        <v>4.68</v>
+        <v>4.65</v>
       </c>
       <c r="L512">
-        <v>4.59</v>
+        <v>4.58</v>
       </c>
       <c r="M512">
-        <v>4.65</v>
+        <v>4.54</v>
       </c>
       <c r="N512">
-        <v>4.58</v>
+        <v>4.57</v>
       </c>
       <c r="O512">
         <v>1</v>
@@ -27179,10 +27179,10 @@
         <v>0</v>
       </c>
       <c r="B513" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C513">
-        <v>0.746167021374426</v>
+        <v>0.7220196008880824</v>
       </c>
       <c r="D513" t="s">
         <v>278</v>
@@ -27194,19 +27194,19 @@
         <v>1</v>
       </c>
       <c r="G513">
-        <v>0.008553832978625575</v>
+        <v>0.00857798039911192</v>
       </c>
       <c r="H513">
         <v>0.008487488997490772</v>
       </c>
       <c r="I513">
-        <v>0.0463439811348012</v>
+        <v>0.07049140162114487</v>
       </c>
       <c r="J513">
         <v>0.8049140162114586</v>
       </c>
       <c r="K513">
-        <v>4.85</v>
+        <v>4.88</v>
       </c>
       <c r="L513">
         <v>4.65</v>
@@ -27229,43 +27229,43 @@
         <v>1</v>
       </c>
       <c r="B514" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C514">
-        <v>0.7220196008880824</v>
+        <v>0.8371498246167173</v>
       </c>
       <c r="D514" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E514">
-        <v>0.7925110025092272</v>
+        <v>0.915690366399978</v>
       </c>
       <c r="F514">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G514">
-        <v>0.00857798039911192</v>
+        <v>0.008322850175383284</v>
       </c>
       <c r="H514">
-        <v>0.008487488997490772</v>
+        <v>0.008224309633600022</v>
       </c>
       <c r="I514">
-        <v>0.07049140162114487</v>
+        <v>-0.07854054178326075</v>
       </c>
       <c r="J514">
         <v>0.8049140162114586</v>
       </c>
       <c r="K514">
-        <v>4.88</v>
+        <v>4.65</v>
       </c>
       <c r="L514">
-        <v>4.65</v>
+        <v>4.58</v>
       </c>
       <c r="M514">
-        <v>4.78</v>
+        <v>4.54</v>
       </c>
       <c r="N514">
-        <v>4.64</v>
+        <v>4.57</v>
       </c>
       <c r="O514">
         <v>1</v>
@@ -27276,96 +27276,96 @@
     </row>
     <row r="515" spans="1:16">
       <c r="A515" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B515" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C515">
-        <v>0.8230024041303738</v>
+        <v>0.4969504786678423</v>
       </c>
       <c r="D515" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E515">
-        <v>0.8371498246167173</v>
+        <v>0.5720539524656312</v>
       </c>
       <c r="F515">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G515">
-        <v>0.008356997595869626</v>
+        <v>0.00880304952133216</v>
       </c>
       <c r="H515">
-        <v>0.008322850175383284</v>
+        <v>0.008707946047534368</v>
       </c>
       <c r="I515">
-        <v>-0.01414742048634343</v>
+        <v>0.07510347379778892</v>
       </c>
       <c r="J515">
-        <v>0.8049140162114586</v>
+        <v>0.8510347379779013</v>
       </c>
       <c r="K515">
-        <v>4.68</v>
+        <v>4.88</v>
       </c>
       <c r="L515">
-        <v>4.59</v>
+        <v>4.65</v>
       </c>
       <c r="M515">
-        <v>4.65</v>
+        <v>4.78</v>
       </c>
       <c r="N515">
-        <v>4.58</v>
+        <v>4.64</v>
       </c>
       <c r="O515">
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>399</v>
+        <v>148</v>
       </c>
     </row>
     <row r="516" spans="1:16">
       <c r="A516" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B516" t="s">
         <v>152</v>
       </c>
       <c r="C516">
-        <v>0.5224815208071796</v>
+        <v>0.6226884684027589</v>
       </c>
       <c r="D516" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E516">
-        <v>0.5720539524656312</v>
+        <v>0.7063022895803281</v>
       </c>
       <c r="F516">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G516">
-        <v>0.008777518479192821</v>
+        <v>0.008537311531597242</v>
       </c>
       <c r="H516">
-        <v>0.008707946047534368</v>
+        <v>0.008433697710419671</v>
       </c>
       <c r="I516">
-        <v>0.0495724316584516</v>
+        <v>-0.08361382117756921</v>
       </c>
       <c r="J516">
         <v>0.8510347379779013</v>
       </c>
       <c r="K516">
-        <v>4.85</v>
+        <v>4.65</v>
       </c>
       <c r="L516">
-        <v>4.65</v>
+        <v>4.58</v>
       </c>
       <c r="M516">
-        <v>4.78</v>
+        <v>4.54</v>
       </c>
       <c r="N516">
-        <v>4.64</v>
+        <v>4.57</v>
       </c>
       <c r="O516">
         <v>1</v>
@@ -27376,34 +27376,34 @@
     </row>
     <row r="517" spans="1:16">
       <c r="A517" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B517" t="s">
         <v>150</v>
       </c>
       <c r="C517">
-        <v>0.4969504786678423</v>
+        <v>0.9942742592090008</v>
       </c>
       <c r="D517" t="s">
         <v>278</v>
       </c>
       <c r="E517">
-        <v>0.5720539524656312</v>
+        <v>1.059186671930127</v>
       </c>
       <c r="F517">
         <v>1</v>
       </c>
       <c r="G517">
-        <v>0.00880304952133216</v>
+        <v>0.008305725740791001</v>
       </c>
       <c r="H517">
-        <v>0.008707946047534368</v>
+        <v>0.008220813328069874</v>
       </c>
       <c r="I517">
-        <v>0.07510347379778892</v>
+        <v>0.06491241272112624</v>
       </c>
       <c r="J517">
-        <v>0.8510347379779013</v>
+        <v>0.7491241272112704</v>
       </c>
       <c r="K517">
         <v>4.88</v>
@@ -27421,57 +27421,57 @@
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>148</v>
+        <v>276</v>
       </c>
     </row>
     <row r="518" spans="1:16">
       <c r="A518" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B518" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C518">
-        <v>0.6071574262634218</v>
+        <v>1.096572808467593</v>
       </c>
       <c r="D518" t="s">
         <v>279</v>
       </c>
       <c r="E518">
-        <v>0.6226884684027589</v>
+        <v>1.168976462460833</v>
       </c>
       <c r="F518">
         <v>-1</v>
       </c>
       <c r="G518">
-        <v>0.008572842573736578</v>
+        <v>0.008063427191532409</v>
       </c>
       <c r="H518">
-        <v>0.008537311531597242</v>
+        <v>0.007971023537539168</v>
       </c>
       <c r="I518">
-        <v>-0.01553104213933709</v>
+        <v>-0.07240365399324</v>
       </c>
       <c r="J518">
-        <v>0.8510347379779013</v>
+        <v>0.7491241272112704</v>
       </c>
       <c r="K518">
-        <v>4.68</v>
+        <v>4.65</v>
       </c>
       <c r="L518">
-        <v>4.59</v>
+        <v>4.58</v>
       </c>
       <c r="M518">
-        <v>4.65</v>
+        <v>4.54</v>
       </c>
       <c r="N518">
-        <v>4.58</v>
+        <v>4.57</v>
       </c>
       <c r="O518">
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>148</v>
+        <v>276</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -27482,28 +27482,28 @@
         <v>150</v>
       </c>
       <c r="C519">
-        <v>0.9942742592090008</v>
+        <v>1.041561394347275</v>
       </c>
       <c r="D519" t="s">
         <v>278</v>
       </c>
       <c r="E519">
-        <v>1.059186671930127</v>
+        <v>1.105504808397535</v>
       </c>
       <c r="F519">
         <v>1</v>
       </c>
       <c r="G519">
-        <v>0.008305725740791001</v>
+        <v>0.008258438605652724</v>
       </c>
       <c r="H519">
-        <v>0.008220813328069874</v>
+        <v>0.008174495191602463</v>
       </c>
       <c r="I519">
-        <v>0.06491241272112624</v>
+        <v>0.06394341405025994</v>
       </c>
       <c r="J519">
-        <v>0.7491241272112704</v>
+        <v>0.7394341405026076</v>
       </c>
       <c r="K519">
         <v>4.88</v>
@@ -27521,156 +27521,6 @@
         <v>1</v>
       </c>
       <c r="P519" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="520" spans="1:16">
-      <c r="A520" s="1">
-        <v>1</v>
-      </c>
-      <c r="B520" t="s">
-        <v>151</v>
-      </c>
-      <c r="C520">
-        <v>1.084099084651255</v>
-      </c>
-      <c r="D520" t="s">
-        <v>279</v>
-      </c>
-      <c r="E520">
-        <v>1.096572808467593</v>
-      </c>
-      <c r="F520">
-        <v>-1</v>
-      </c>
-      <c r="G520">
-        <v>0.008095900915348744</v>
-      </c>
-      <c r="H520">
-        <v>0.008063427191532409</v>
-      </c>
-      <c r="I520">
-        <v>-0.01247372381633793</v>
-      </c>
-      <c r="J520">
-        <v>0.7491241272112704</v>
-      </c>
-      <c r="K520">
-        <v>4.68</v>
-      </c>
-      <c r="L520">
-        <v>4.59</v>
-      </c>
-      <c r="M520">
-        <v>4.65</v>
-      </c>
-      <c r="N520">
-        <v>4.58</v>
-      </c>
-      <c r="O520">
-        <v>1</v>
-      </c>
-      <c r="P520" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="521" spans="1:16">
-      <c r="A521" s="1">
-        <v>0</v>
-      </c>
-      <c r="B521" t="s">
-        <v>150</v>
-      </c>
-      <c r="C521">
-        <v>1.041561394347275</v>
-      </c>
-      <c r="D521" t="s">
-        <v>278</v>
-      </c>
-      <c r="E521">
-        <v>1.105504808397535</v>
-      </c>
-      <c r="F521">
-        <v>1</v>
-      </c>
-      <c r="G521">
-        <v>0.008258438605652724</v>
-      </c>
-      <c r="H521">
-        <v>0.008174495191602463</v>
-      </c>
-      <c r="I521">
-        <v>0.06394341405025994</v>
-      </c>
-      <c r="J521">
-        <v>0.7394341405026076</v>
-      </c>
-      <c r="K521">
-        <v>4.88</v>
-      </c>
-      <c r="L521">
-        <v>4.65</v>
-      </c>
-      <c r="M521">
-        <v>4.78</v>
-      </c>
-      <c r="N521">
-        <v>4.64</v>
-      </c>
-      <c r="O521">
-        <v>1</v>
-      </c>
-      <c r="P521" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="522" spans="1:16">
-      <c r="A522" s="1">
-        <v>1</v>
-      </c>
-      <c r="B522" t="s">
-        <v>151</v>
-      </c>
-      <c r="C522">
-        <v>1.129448222447797</v>
-      </c>
-      <c r="D522" t="s">
-        <v>279</v>
-      </c>
-      <c r="E522">
-        <v>1.141631246662874</v>
-      </c>
-      <c r="F522">
-        <v>-1</v>
-      </c>
-      <c r="G522">
-        <v>0.008050551777552203</v>
-      </c>
-      <c r="H522">
-        <v>0.008018368753337125</v>
-      </c>
-      <c r="I522">
-        <v>-0.01218302421507778</v>
-      </c>
-      <c r="J522">
-        <v>0.7394341405026076</v>
-      </c>
-      <c r="K522">
-        <v>4.68</v>
-      </c>
-      <c r="L522">
-        <v>4.59</v>
-      </c>
-      <c r="M522">
-        <v>4.65</v>
-      </c>
-      <c r="N522">
-        <v>4.58</v>
-      </c>
-      <c r="O522">
-        <v>1</v>
-      </c>
-      <c r="P522" t="s">
         <v>400</v>
       </c>
     </row>

--- a/s60_signal/position-03328-601328.xlsx
+++ b/s60_signal/position-03328-601328.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1569" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="403">
   <si>
     <t>trade_time</t>
   </si>
@@ -475,6 +475,12 @@
     <t>2021-11-29</t>
   </si>
   <si>
+    <t>2021-11-16</t>
+  </si>
+  <si>
+    <t>2021-11-30</t>
+  </si>
+  <si>
     <t>2016-05-31</t>
   </si>
   <si>
@@ -853,7 +859,7 @@
     <t>2021-11-23</t>
   </si>
   <si>
-    <t>2021-11-30</t>
+    <t>2021-12-01</t>
   </si>
   <si>
     <t>2016-05-24</t>
@@ -1574,7 +1580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P519"/>
+  <dimension ref="A1:P521"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1635,7 +1641,7 @@
         <v>2.636521639996683</v>
       </c>
       <c r="D2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E2">
         <v>2.833647241107702</v>
@@ -1671,7 +1677,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1685,7 +1691,7 @@
         <v>2.808801457176021</v>
       </c>
       <c r="D3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E3">
         <v>2.7135041663212</v>
@@ -1721,7 +1727,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1735,7 +1741,7 @@
         <v>2.746397091058633</v>
       </c>
       <c r="D4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E4">
         <v>2.648930323263125</v>
@@ -1785,7 +1791,7 @@
         <v>2.683209227271539</v>
       </c>
       <c r="D5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E5">
         <v>2.583545744375049</v>
@@ -1821,7 +1827,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1835,7 +1841,7 @@
         <v>2.555958070922727</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E6">
         <v>2.632522016358742</v>
@@ -1871,7 +1877,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1885,7 +1891,7 @@
         <v>2.641252819939413</v>
       </c>
       <c r="D7" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E7">
         <v>2.540130729835057</v>
@@ -1921,7 +1927,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1935,7 +1941,7 @@
         <v>2.512285655110759</v>
       </c>
       <c r="D8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E8">
         <v>2.590994611146576</v>
@@ -1971,7 +1977,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1985,7 +1991,7 @@
         <v>2.615441102246784</v>
       </c>
       <c r="D9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E9">
         <v>2.513421672263544</v>
@@ -2021,7 +2027,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2035,7 +2041,7 @@
         <v>2.515418243442972</v>
       </c>
       <c r="D10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E10">
         <v>2.545423958143926</v>
@@ -2071,7 +2077,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2085,7 +2091,7 @@
         <v>2.487273994427867</v>
       </c>
       <c r="D11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E11">
         <v>2.567211421027677</v>
@@ -2121,7 +2127,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2135,7 +2141,7 @@
         <v>2.487984580081365</v>
       </c>
       <c r="D12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E12">
         <v>2.579898802553291</v>
@@ -2171,7 +2177,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2185,7 +2191,7 @@
         <v>2.500805561667341</v>
       </c>
       <c r="D13" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E13">
         <v>2.59216563562278</v>
@@ -2221,7 +2227,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2235,7 +2241,7 @@
         <v>2.499441989042522</v>
       </c>
       <c r="D14" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E14">
         <v>2.736702547602069</v>
@@ -2285,7 +2291,7 @@
         <v>2.512520850741042</v>
       </c>
       <c r="D15" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E15">
         <v>2.749061943431123</v>
@@ -2321,7 +2327,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2335,7 +2341,7 @@
         <v>2.77984350091858</v>
       </c>
       <c r="D16" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E16">
         <v>2.889061943431122</v>
@@ -2371,7 +2377,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2385,7 +2391,7 @@
         <v>2.517224153471577</v>
       </c>
       <c r="D17" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E17">
         <v>2.753506518310076</v>
@@ -2421,7 +2427,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2435,7 +2441,7 @@
         <v>2.784426680003737</v>
       </c>
       <c r="D18" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E18">
         <v>2.924119959439183</v>
@@ -2471,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2485,7 +2491,7 @@
         <v>2.884280694854824</v>
       </c>
       <c r="D19" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E19">
         <v>2.961861794886389</v>
@@ -2535,7 +2541,7 @@
         <v>2.920719956495094</v>
       </c>
       <c r="D20" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E20">
         <v>2.907075620138133</v>
@@ -2571,7 +2577,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2585,7 +2591,7 @@
         <v>2.648180125005333</v>
       </c>
       <c r="D21" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E21">
         <v>2.848908919700521</v>
@@ -2621,7 +2627,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2671,7 +2677,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2685,7 +2691,7 @@
         <v>2.691620213913162</v>
       </c>
       <c r="D23" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E23">
         <v>2.889959376998489</v>
@@ -2721,7 +2727,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2735,7 +2741,7 @@
         <v>2.984719616116966</v>
       </c>
       <c r="D24" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E24">
         <v>2.755965243802971</v>
@@ -2771,7 +2777,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2785,7 +2791,7 @@
         <v>3.007275184023352</v>
       </c>
       <c r="D25" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E25">
         <v>2.755965243802971</v>
@@ -2821,7 +2827,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2835,7 +2841,7 @@
         <v>2.683495528297218</v>
       </c>
       <c r="D26" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E26">
         <v>2.882281628901694</v>
@@ -2871,7 +2877,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2885,7 +2891,7 @@
         <v>2.976914171586129</v>
       </c>
       <c r="D27" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E27">
         <v>2.747824596132772</v>
@@ -2921,7 +2927,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2935,7 +2941,7 @@
         <v>2.647048085674867</v>
       </c>
       <c r="D28" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E28">
         <v>2.84783915365346</v>
@@ -2971,7 +2977,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2985,7 +2991,7 @@
         <v>2.941898848516719</v>
       </c>
       <c r="D29" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E29">
         <v>2.711305547532774</v>
@@ -3021,7 +3027,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3035,7 +3041,7 @@
         <v>2.962790623816959</v>
       </c>
       <c r="D30" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E30">
         <v>2.711305547532774</v>
@@ -3071,7 +3077,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3085,7 +3091,7 @@
         <v>2.636850318680218</v>
       </c>
       <c r="D31" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E31">
         <v>2.674077933106496</v>
@@ -3121,7 +3127,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3135,7 +3141,7 @@
         <v>2.64386308474694</v>
       </c>
       <c r="D32" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E32">
         <v>2.844829359063415</v>
@@ -3171,7 +3177,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3185,7 +3191,7 @@
         <v>2.938838994972993</v>
       </c>
       <c r="D33" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E33">
         <v>2.708114289235636</v>
@@ -3221,7 +3227,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3235,7 +3241,7 @@
         <v>2.959611880258242</v>
       </c>
       <c r="D34" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E34">
         <v>2.708114289235636</v>
@@ -3271,7 +3277,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3285,7 +3291,7 @@
         <v>2.63362151616782</v>
       </c>
       <c r="D35" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E35">
         <v>2.706375129633912</v>
@@ -3321,7 +3327,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3335,7 +3341,7 @@
         <v>2.623711665472045</v>
       </c>
       <c r="D36" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E36">
         <v>2.825786465799713</v>
@@ -3371,7 +3377,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3385,7 +3391,7 @@
         <v>2.919479379991807</v>
       </c>
       <c r="D37" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E37">
         <v>2.687923279746057</v>
@@ -3421,7 +3427,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3435,7 +3441,7 @@
         <v>2.939500051198033</v>
       </c>
       <c r="D38" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E38">
         <v>2.687923279746057</v>
@@ -3471,7 +3477,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3485,7 +3491,7 @@
         <v>2.613192965390128</v>
       </c>
       <c r="D39" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E39">
         <v>2.65740457966414</v>
@@ -3521,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3535,7 +3541,7 @@
         <v>2.866121269202039</v>
       </c>
       <c r="D40" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E40">
         <v>2.632273716345684</v>
@@ -3585,7 +3591,7 @@
         <v>2.884068721379623</v>
       </c>
       <c r="D41" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E41">
         <v>2.632273716345684</v>
@@ -3635,7 +3641,7 @@
         <v>2.556888701243869</v>
       </c>
       <c r="D42" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E42">
         <v>2.5709911987269</v>
@@ -3685,7 +3691,7 @@
         <v>2.84066903268222</v>
       </c>
       <c r="D43" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E43">
         <v>2.605728438993726</v>
@@ -3721,7 +3727,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3735,7 +3741,7 @@
         <v>2.857627543154535</v>
       </c>
       <c r="D44" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E44">
         <v>2.605728438993726</v>
@@ -3771,7 +3777,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3785,7 +3791,7 @@
         <v>2.530031126511299</v>
       </c>
       <c r="D45" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E45">
         <v>2.536232918189681</v>
@@ -3821,7 +3827,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3835,7 +3841,7 @@
         <v>2.794653597980052</v>
       </c>
       <c r="D46" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E46">
         <v>2.557736881328888</v>
@@ -3871,7 +3877,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3885,7 +3891,7 @@
         <v>2.809824187676618</v>
       </c>
       <c r="D47" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E47">
         <v>2.557736881328888</v>
@@ -3921,7 +3927,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3971,7 +3977,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3985,7 +3991,7 @@
         <v>2.877968395292299</v>
       </c>
       <c r="D49" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E49">
         <v>2.644629614722029</v>
@@ -4021,7 +4027,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4035,7 +4041,7 @@
         <v>2.896376165252531</v>
       </c>
       <c r="D50" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E50">
         <v>2.644629614722029</v>
@@ -4071,7 +4077,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4085,7 +4091,7 @@
         <v>2.521770137334771</v>
       </c>
       <c r="D51" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E51">
         <v>2.535896862069519</v>
@@ -4121,7 +4127,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4135,7 +4141,7 @@
         <v>2.934431839092635</v>
       </c>
       <c r="D52" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E52">
         <v>2.703517868992319</v>
@@ -4171,7 +4177,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4185,7 +4191,7 @@
         <v>2.955033485192349</v>
       </c>
       <c r="D53" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E53">
         <v>2.703517868992319</v>
@@ -4221,7 +4227,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4271,7 +4277,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4285,7 +4291,7 @@
         <v>2.974730272968942</v>
       </c>
       <c r="D55" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E55">
         <v>2.745546910458406</v>
@@ -4321,7 +4327,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4335,7 +4341,7 @@
         <v>2.996897706887981</v>
       </c>
       <c r="D56" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E56">
         <v>2.745546910458406</v>
@@ -4371,7 +4377,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4385,7 +4391,7 @@
         <v>2.624468326525319</v>
       </c>
       <c r="D57" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E57">
         <v>2.660688149733082</v>
@@ -4421,7 +4427,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4435,7 +4441,7 @@
         <v>3.056805462611843</v>
       </c>
       <c r="D58" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E58">
         <v>2.831146801497014</v>
@@ -4471,7 +4477,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4521,7 +4527,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4535,7 +4541,7 @@
         <v>3.075488420323122</v>
       </c>
       <c r="D60" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E60">
         <v>2.850632094815525</v>
@@ -4585,7 +4591,7 @@
         <v>2.73140795531227</v>
       </c>
       <c r="D61" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E61">
         <v>2.75953055997749</v>
@@ -4635,7 +4641,7 @@
         <v>2.72765316464271</v>
       </c>
       <c r="D62" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E62">
         <v>2.75953055997749</v>
@@ -4685,7 +4691,7 @@
         <v>2.72671446697532</v>
       </c>
       <c r="D63" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E63">
         <v>2.75953055997749</v>
@@ -4735,7 +4741,7 @@
         <v>6.293149296554828</v>
       </c>
       <c r="D64" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E64">
         <v>5.963700498102364</v>
@@ -4771,7 +4777,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4785,7 +4791,7 @@
         <v>6.420239880180696</v>
       </c>
       <c r="D65" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E65">
         <v>6.082402264327184</v>
@@ -4821,7 +4827,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4835,7 +4841,7 @@
         <v>6.609514294497387</v>
       </c>
       <c r="D66" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E66">
         <v>6.259183317962906</v>
@@ -4871,7 +4877,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4885,7 +4891,7 @@
         <v>6.515171551263329</v>
       </c>
       <c r="D67" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E67">
         <v>6.612047937164794</v>
@@ -4921,7 +4927,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4935,7 +4941,7 @@
         <v>6.520829737768901</v>
       </c>
       <c r="D68" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E68">
         <v>6.612047937164794</v>
@@ -4971,7 +4977,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5021,7 +5027,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5071,7 +5077,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5121,7 +5127,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5135,7 +5141,7 @@
         <v>6.781478804637512</v>
       </c>
       <c r="D72" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E72">
         <v>6.821616798629249</v>
@@ -5171,7 +5177,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5185,7 +5191,7 @@
         <v>6.927933775178332</v>
       </c>
       <c r="D73" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E73">
         <v>7.025464228815041</v>
@@ -5221,7 +5227,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5235,7 +5241,7 @@
         <v>7.465293617228137</v>
       </c>
       <c r="D74" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E74">
         <v>7.441132824526438</v>
@@ -5271,7 +5277,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5285,7 +5291,7 @@
         <v>2.399740228983164</v>
       </c>
       <c r="D75" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E75">
         <v>2.284756328614283</v>
@@ -5321,7 +5327,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5335,7 +5341,7 @@
         <v>2.181146111927123</v>
       </c>
       <c r="D76" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E76">
         <v>2.105842395854763</v>
@@ -5371,7 +5377,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5385,7 +5391,7 @@
         <v>2.180858495485883</v>
       </c>
       <c r="D77" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E77">
         <v>2.105842395854763</v>
@@ -5421,7 +5427,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5435,7 +5441,7 @@
         <v>2.355267416838251</v>
       </c>
       <c r="D78" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E78">
         <v>2.241615480893012</v>
@@ -5471,7 +5477,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5485,7 +5491,7 @@
         <v>2.138079262229388</v>
       </c>
       <c r="D79" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E79">
         <v>2.115876072829124</v>
@@ -5521,7 +5527,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5535,7 +5541,7 @@
         <v>2.136977667529256</v>
       </c>
       <c r="D80" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E80">
         <v>2.115876072829124</v>
@@ -5571,7 +5577,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5621,7 +5627,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5671,7 +5677,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5721,7 +5727,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5735,7 +5741,7 @@
         <v>1.925553832103902</v>
       </c>
       <c r="D84" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E84">
         <v>1.985821650998686</v>
@@ -5771,7 +5777,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5821,7 +5827,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5835,7 +5841,7 @@
         <v>1.87975631937778</v>
       </c>
       <c r="D86" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E86">
         <v>2.025900250164519</v>
@@ -5871,7 +5877,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5971,7 +5977,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5985,7 +5991,7 @@
         <v>1.789383875507923</v>
       </c>
       <c r="D89" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E89">
         <v>1.940268655809146</v>
@@ -6021,7 +6027,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6035,7 +6041,7 @@
         <v>1.804905667333501</v>
       </c>
       <c r="D90" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E90">
         <v>1.95497618970289</v>
@@ -6071,7 +6077,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6085,7 +6091,7 @@
         <v>1.809491967335235</v>
       </c>
       <c r="D91" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E91">
         <v>1.959321896917648</v>
@@ -6121,7 +6127,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6135,7 +6141,7 @@
         <v>1.822908408572121</v>
       </c>
       <c r="D92" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E92">
         <v>1.972034524843747</v>
@@ -6171,7 +6177,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6185,7 +6191,7 @@
         <v>2.011491451443282</v>
       </c>
       <c r="D93" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E93">
         <v>1.930405304642352</v>
@@ -6221,7 +6227,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6235,7 +6241,7 @@
         <v>1.820166348365971</v>
       </c>
       <c r="D94" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E94">
         <v>1.969436310418903</v>
@@ -6271,7 +6277,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6285,7 +6291,7 @@
         <v>2.008879751476441</v>
       </c>
       <c r="D95" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E95">
         <v>1.927766633591516</v>
@@ -6321,7 +6327,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6335,7 +6341,7 @@
         <v>1.780154910291897</v>
       </c>
       <c r="D96" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E96">
         <v>1.931523833030682</v>
@@ -6371,7 +6377,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6421,7 +6427,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6435,7 +6441,7 @@
         <v>1.781411528733962</v>
       </c>
       <c r="D98" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E98">
         <v>1.932714530505294</v>
@@ -6471,7 +6477,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6521,7 +6527,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6535,7 +6541,7 @@
         <v>1.786869994736246</v>
       </c>
       <c r="D100" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E100">
         <v>1.937886650750082</v>
@@ -6585,7 +6591,7 @@
         <v>1.77389224303264</v>
       </c>
       <c r="D101" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E101">
         <v>1.925589699135846</v>
@@ -6621,7 +6627,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6635,7 +6641,7 @@
         <v>1.764225388294109</v>
       </c>
       <c r="D102" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E102">
         <v>1.916429958088516</v>
@@ -6835,7 +6841,7 @@
         <v>2.039049007419374</v>
       </c>
       <c r="D106" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E106">
         <v>1.958247448115615</v>
@@ -6871,7 +6877,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6885,7 +6891,7 @@
         <v>1.963804213639886</v>
       </c>
       <c r="D107" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E107">
         <v>2.044635472991321</v>
@@ -6921,7 +6927,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6935,7 +6941,7 @@
         <v>2.084469221121035</v>
       </c>
       <c r="D108" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E108">
         <v>2.00413671738046</v>
@@ -6971,7 +6977,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6985,7 +6991,7 @@
         <v>1.970692549466935</v>
       </c>
       <c r="D109" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E109">
         <v>2.103970465510173</v>
@@ -7021,7 +7027,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7071,7 +7077,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7085,7 +7091,7 @@
         <v>1.989826166099606</v>
       </c>
       <c r="D111" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E111">
         <v>2.069999197311251</v>
@@ -7121,7 +7127,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7135,7 +7141,7 @@
         <v>1.996538974422711</v>
       </c>
       <c r="D112" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E112">
         <v>2.129860772341935</v>
@@ -7171,7 +7177,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7221,7 +7227,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7235,7 +7241,7 @@
         <v>1.976959483296697</v>
       </c>
       <c r="D114" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E114">
         <v>2.110248039295503</v>
@@ -7335,7 +7341,7 @@
         <v>1.920546112528168</v>
       </c>
       <c r="D116" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E116">
         <v>2.053738890308352</v>
@@ -7371,7 +7377,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7421,7 +7427,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7435,7 +7441,7 @@
         <v>2.078859445890371</v>
       </c>
       <c r="D118" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E118">
         <v>2.128859445890371</v>
@@ -7471,7 +7477,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7485,7 +7491,7 @@
         <v>1.864471846503076</v>
       </c>
       <c r="D119" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E119">
         <v>1.997569421794252</v>
@@ -7521,7 +7527,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7571,7 +7577,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7621,7 +7627,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7635,7 +7641,7 @@
         <v>1.863420505387863</v>
       </c>
       <c r="D122" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E122">
         <v>1.996516295719591</v>
@@ -7735,7 +7741,7 @@
         <v>2.029857360363785</v>
       </c>
       <c r="D124" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E124">
         <v>2.011995247378231</v>
@@ -7785,7 +7791,7 @@
         <v>1.892165706973767</v>
       </c>
       <c r="D125" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E125">
         <v>2.025310300703773</v>
@@ -7821,7 +7827,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7871,7 +7877,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7921,7 +7927,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7985,7 +7991,7 @@
         <v>2.183293967129219</v>
       </c>
       <c r="D129" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E129">
         <v>2.097698061214447</v>
@@ -8035,7 +8041,7 @@
         <v>2.10409703769314</v>
       </c>
       <c r="D130" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E130">
         <v>2.097698061214447</v>
@@ -8121,7 +8127,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8171,7 +8177,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8221,7 +8227,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8271,7 +8277,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8321,7 +8327,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8371,7 +8377,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8421,7 +8427,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8471,7 +8477,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8485,7 +8491,7 @@
         <v>2.367284598691813</v>
       </c>
       <c r="D139" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E139">
         <v>2.284677125480481</v>
@@ -8535,7 +8541,7 @@
         <v>2.308705785003503</v>
       </c>
       <c r="D140" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E140">
         <v>2.284677125480481</v>
@@ -8671,7 +8677,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8721,7 +8727,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8771,7 +8777,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8821,7 +8827,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8871,7 +8877,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8935,7 +8941,7 @@
         <v>2.673055621612132</v>
       </c>
       <c r="D148" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E148">
         <v>2.649383477311975</v>
@@ -8985,7 +8991,7 @@
         <v>2.694510447967022</v>
       </c>
       <c r="D149" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E149">
         <v>2.66746656530884</v>
@@ -9035,7 +9041,7 @@
         <v>2.61961842602696</v>
       </c>
       <c r="D150" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E150">
         <v>2.674946565009619</v>
@@ -9321,7 +9327,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9335,7 +9341,7 @@
         <v>2.746485076848839</v>
       </c>
       <c r="D156" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E156">
         <v>2.847982602490786</v>
@@ -9371,7 +9377,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9435,7 +9441,7 @@
         <v>2.750734210259811</v>
       </c>
       <c r="D158" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E158">
         <v>2.800734210259812</v>
@@ -9471,7 +9477,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9535,7 +9541,7 @@
         <v>2.717092536535202</v>
       </c>
       <c r="D160" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E160">
         <v>2.791717770085309</v>
@@ -9621,7 +9627,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9635,7 +9641,7 @@
         <v>2.669840281895235</v>
       </c>
       <c r="D162" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E162">
         <v>2.754805459723328</v>
@@ -9671,7 +9677,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9735,7 +9741,7 @@
         <v>2.704152220032186</v>
       </c>
       <c r="D164" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E164">
         <v>2.721608307945189</v>
@@ -9785,7 +9791,7 @@
         <v>0.7516342779874527</v>
       </c>
       <c r="D165" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E165">
         <v>0.6447312303040151</v>
@@ -9821,7 +9827,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9835,7 +9841,7 @@
         <v>0.6347312303040145</v>
       </c>
       <c r="D166" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E166">
         <v>0.7803954970608276</v>
@@ -9871,7 +9877,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9885,7 +9891,7 @@
         <v>0.7872985447442655</v>
       </c>
       <c r="D167" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E167">
         <v>0.6685373256708909</v>
@@ -9921,7 +9927,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9935,7 +9941,7 @@
         <v>0.6141118398407031</v>
       </c>
       <c r="D168" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E168">
         <v>0.7042015924277036</v>
@@ -9971,7 +9977,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9985,7 +9991,7 @@
         <v>0.7076194190074974</v>
       </c>
       <c r="D169" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E169">
         <v>0.8524403513495589</v>
@@ -10035,7 +10041,7 @@
         <v>0.8587410173081755</v>
       </c>
       <c r="D170" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E170">
         <v>0.7402207509247285</v>
@@ -10085,7 +10091,7 @@
         <v>0.6868795521992208</v>
       </c>
       <c r="D171" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E171">
         <v>0.7750416832667906</v>
@@ -10135,7 +10141,7 @@
         <v>0.794311018129779</v>
       </c>
       <c r="D172" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E172">
         <v>0.9381289071762104</v>
@@ -10171,7 +10177,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10185,7 +10191,7 @@
         <v>0.7478436529603893</v>
       </c>
       <c r="D173" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E173">
         <v>0.9381289071762104</v>
@@ -10221,7 +10227,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10235,7 +10241,7 @@
         <v>0.9437131136379486</v>
       </c>
       <c r="D174" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E174">
         <v>0.8254794310532532</v>
@@ -10271,7 +10277,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10285,7 +10291,7 @@
         <v>0.7734278594221262</v>
       </c>
       <c r="D175" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E175">
         <v>0.8592973200996861</v>
@@ -10321,7 +10327,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10335,7 +10341,7 @@
         <v>0.9016190641047892</v>
       </c>
       <c r="D176" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E176">
         <v>1.04419537245399</v>
@@ -10371,7 +10377,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10385,7 +10391,7 @@
         <v>0.8558611736195321</v>
       </c>
       <c r="D177" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E177">
         <v>1.04419537245399</v>
@@ -10421,7 +10427,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10435,7 +10441,7 @@
         <v>1.048892735560562</v>
       </c>
       <c r="D178" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E178">
         <v>0.9310137903179339</v>
@@ -10471,7 +10477,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10485,7 +10491,7 @@
         <v>0.8805585367261042</v>
       </c>
       <c r="D179" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E179">
         <v>0.963590098667134</v>
@@ -10521,7 +10527,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10535,7 +10541,7 @@
         <v>1.076170489586433</v>
       </c>
       <c r="D180" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E180">
         <v>1.260525374010979</v>
@@ -10585,7 +10591,7 @@
         <v>1.26341395784032</v>
       </c>
       <c r="D181" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E181">
         <v>1.146258524308584</v>
@@ -10635,7 +10641,7 @@
         <v>1.099059073415773</v>
       </c>
       <c r="D182" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E182">
         <v>1.176302541669659</v>
@@ -10685,7 +10691,7 @@
         <v>1.931268098407571</v>
       </c>
       <c r="D183" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E183">
         <v>1.946759727730396</v>
@@ -10721,7 +10727,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10771,7 +10777,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10821,7 +10827,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10835,7 +10841,7 @@
         <v>0.5942088493584849</v>
       </c>
       <c r="D186" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E186">
         <v>0.5982130518354056</v>
@@ -10871,7 +10877,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10921,7 +10927,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10971,7 +10977,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11021,7 +11027,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11035,7 +11041,7 @@
         <v>-0.02499489055226256</v>
       </c>
       <c r="D190" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E190">
         <v>-0.07499489055226238</v>
@@ -11071,7 +11077,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11085,7 +11091,7 @@
         <v>-0.04541693580813089</v>
       </c>
       <c r="D191" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E191">
         <v>-0.1350880582477796</v>
@@ -11121,7 +11127,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11171,7 +11177,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11221,7 +11227,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11371,7 +11377,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11385,7 +11391,7 @@
         <v>-0.5154661476950757</v>
       </c>
       <c r="D197" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E197">
         <v>-0.4838284745942198</v>
@@ -11421,7 +11427,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11435,7 +11441,7 @@
         <v>-0.5144835438345625</v>
       </c>
       <c r="D198" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E198">
         <v>-0.4838284745942198</v>
@@ -11471,7 +11477,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11521,7 +11527,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11535,7 +11541,7 @@
         <v>-0.6795603356321358</v>
       </c>
       <c r="D200" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E200">
         <v>-0.6353746161347429</v>
@@ -11571,7 +11577,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11585,7 +11591,7 @@
         <v>-0.6770489039336995</v>
       </c>
       <c r="D201" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E201">
         <v>-0.6353746161347429</v>
@@ -11621,7 +11627,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11671,7 +11677,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11685,7 +11691,7 @@
         <v>-1.275160705635463</v>
       </c>
       <c r="D203" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E203">
         <v>-0.9575450227817477</v>
@@ -11721,7 +11727,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11735,7 +11741,7 @@
         <v>-1.267100202166811</v>
       </c>
       <c r="D204" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E204">
         <v>-0.9575450227817477</v>
@@ -11771,7 +11777,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11835,7 +11841,7 @@
         <v>-1.30354206111917</v>
       </c>
       <c r="D206" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E206">
         <v>-0.9846924062879019</v>
@@ -11885,7 +11891,7 @@
         <v>-1.295217135083899</v>
       </c>
       <c r="D207" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E207">
         <v>-0.9846924062879019</v>
@@ -11935,7 +11941,7 @@
         <v>-1.315601110783377</v>
       </c>
       <c r="D208" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E208">
         <v>-0.9962271494449686</v>
@@ -11985,7 +11991,7 @@
         <v>-1.307163833353718</v>
       </c>
       <c r="D209" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E209">
         <v>-0.9962271494449686</v>
@@ -12035,7 +12041,7 @@
         <v>-1.303470101275702</v>
       </c>
       <c r="D210" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E210">
         <v>-0.9846235751332797</v>
@@ -12071,7 +12077,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12085,7 +12091,7 @@
         <v>-1.295145845673754</v>
       </c>
       <c r="D211" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E211">
         <v>-0.9846235751332797</v>
@@ -12121,7 +12127,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12135,7 +12141,7 @@
         <v>-1.352240812118975</v>
       </c>
       <c r="D212" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E212">
         <v>-1.031273820287715</v>
@@ -12171,7 +12177,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12185,7 +12191,7 @@
         <v>-1.343462171012276</v>
       </c>
       <c r="D213" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E213">
         <v>-1.031273820287715</v>
@@ -12221,7 +12227,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12271,7 +12277,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12285,7 +12291,7 @@
         <v>-1.277973836666044</v>
       </c>
       <c r="D215" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E215">
         <v>-0.9602358437675207</v>
@@ -12335,7 +12341,7 @@
         <v>-1.269887123902075</v>
       </c>
       <c r="D216" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E216">
         <v>-0.9602358437675207</v>
@@ -12385,7 +12391,7 @@
         <v>-1.030235843767521</v>
       </c>
       <c r="D217" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E217">
         <v>-1.080019061857596</v>
@@ -12435,7 +12441,7 @@
         <v>-1.007888992711643</v>
       </c>
       <c r="D218" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E218">
         <v>-1.080019061857596</v>
@@ -12485,7 +12491,7 @@
         <v>-1.154349245698821</v>
       </c>
       <c r="D219" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E219">
         <v>-0.8419862350162637</v>
@@ -12535,7 +12541,7 @@
         <v>-1.147414314838273</v>
       </c>
       <c r="D220" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E220">
         <v>-0.8419862350162637</v>
@@ -12685,7 +12691,7 @@
         <v>-0.9332125637434627</v>
       </c>
       <c r="D223" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E223">
         <v>-0.6304641914067899</v>
@@ -12721,7 +12727,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12735,7 +12741,7 @@
         <v>-0.9283379125284608</v>
       </c>
       <c r="D224" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E224">
         <v>-0.6304641914067899</v>
@@ -12771,7 +12777,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12785,7 +12791,7 @@
         <v>-1.078298911794628</v>
       </c>
       <c r="D225" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E225">
         <v>-0.7337942740491279</v>
@@ -12835,7 +12841,7 @@
         <v>-1.284045732215318</v>
       </c>
       <c r="D226" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E226">
         <v>-0.9315166474955321</v>
@@ -12885,7 +12891,7 @@
         <v>-1.074552792811861</v>
       </c>
       <c r="D227" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E227">
         <v>-0.7301942595508679</v>
@@ -12921,7 +12927,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12935,7 +12941,7 @@
         <v>0.6306184682796347</v>
       </c>
       <c r="D228" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E228">
         <v>0.8825890610024754</v>
@@ -12971,7 +12977,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12985,7 +12991,7 @@
         <v>2.500083924851446</v>
       </c>
       <c r="D229" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E229">
         <v>2.721828222716436</v>
@@ -13021,7 +13027,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13035,7 +13041,7 @@
         <v>2.484743417251086</v>
       </c>
       <c r="D230" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E230">
         <v>2.721828222716436</v>
@@ -13071,7 +13077,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13085,7 +13091,7 @@
         <v>2.959498476516616</v>
       </c>
       <c r="D231" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E231">
         <v>3.019498476516616</v>
@@ -13121,7 +13127,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13171,7 +13177,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13185,7 +13191,7 @@
         <v>3.973072767193392</v>
       </c>
       <c r="D233" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E233">
         <v>3.630196829293595</v>
@@ -13221,7 +13227,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13271,7 +13277,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13321,7 +13327,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13335,7 +13341,7 @@
         <v>4.556254256131551</v>
       </c>
       <c r="D236" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E236">
         <v>4.211276763316661</v>
@@ -13371,7 +13377,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13421,7 +13427,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13471,7 +13477,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13485,7 +13491,7 @@
         <v>4.667791750685101</v>
       </c>
       <c r="D239" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E239">
         <v>4.322412320952902</v>
@@ -13521,7 +13527,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13535,7 +13541,7 @@
         <v>4.273963746622406</v>
       </c>
       <c r="D240" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E240">
         <v>4.266274031756307</v>
@@ -13571,7 +13577,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13621,7 +13627,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13671,7 +13677,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13685,7 +13691,7 @@
         <v>3.655351043939968</v>
       </c>
       <c r="D243" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E243">
         <v>3.313620049187031</v>
@@ -13721,7 +13727,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13735,7 +13741,7 @@
         <v>2.349652973133038</v>
       </c>
       <c r="D244" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E244">
         <v>2.585321458264525</v>
@@ -13785,7 +13791,7 @@
         <v>2.337296219946928</v>
       </c>
       <c r="D245" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E245">
         <v>2.585321458264525</v>
@@ -13835,7 +13841,7 @@
         <v>2.821499834857581</v>
       </c>
       <c r="D246" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E246">
         <v>2.482773709326562</v>
@@ -13885,7 +13891,7 @@
         <v>1.399171925433256</v>
       </c>
       <c r="D247" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E247">
         <v>1.7228188215915</v>
@@ -13921,7 +13927,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13935,7 +13941,7 @@
         <v>1.94957093986026</v>
       </c>
       <c r="D248" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E248">
         <v>1.61398690043734</v>
@@ -13971,7 +13977,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13985,7 +13991,7 @@
         <v>1.388298565840941</v>
       </c>
       <c r="D249" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E249">
         <v>1.05473712956764</v>
@@ -14035,7 +14041,7 @@
         <v>1.206849236469149</v>
       </c>
       <c r="D250" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E250">
         <v>0.8739416716530437</v>
@@ -14085,7 +14091,7 @@
         <v>1.250249534396463</v>
       </c>
       <c r="D251" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E251">
         <v>0.9171855721103492</v>
@@ -14135,7 +14141,7 @@
         <v>1.265784593473219</v>
       </c>
       <c r="D252" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E252">
         <v>0.9326646489922341</v>
@@ -14171,7 +14177,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14185,7 +14191,7 @@
         <v>1.181086185990114</v>
       </c>
       <c r="D253" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E253">
         <v>0.8482714609955542</v>
@@ -14235,7 +14241,7 @@
         <v>3.393868635799184</v>
       </c>
       <c r="D254" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E254">
         <v>3.232668972857903</v>
@@ -14271,7 +14277,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14285,7 +14291,7 @@
         <v>3.344337857016143</v>
       </c>
       <c r="D255" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E255">
         <v>3.232668972857903</v>
@@ -14321,7 +14327,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14335,7 +14341,7 @@
         <v>3.108144846549583</v>
       </c>
       <c r="D256" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E256">
         <v>3.176241351782863</v>
@@ -14371,7 +14377,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14385,7 +14391,7 @@
         <v>3.110765478091183</v>
       </c>
       <c r="D257" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E257">
         <v>3.176241351782863</v>
@@ -14421,7 +14427,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14435,7 +14441,7 @@
         <v>3.484929217459694</v>
       </c>
       <c r="D258" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E258">
         <v>3.328403460479749</v>
@@ -14471,7 +14477,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14485,7 +14491,7 @@
         <v>3.438944160440425</v>
       </c>
       <c r="D259" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E259">
         <v>3.328403460479749</v>
@@ -14521,7 +14527,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14571,7 +14577,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14621,7 +14627,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14635,7 +14641,7 @@
         <v>3.67612531160249</v>
       </c>
       <c r="D262" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E262">
         <v>3.529413159454653</v>
@@ -14671,7 +14677,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14685,7 +14691,7 @@
         <v>3.637585058248958</v>
       </c>
       <c r="D263" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E263">
         <v>3.529413159454653</v>
@@ -14721,7 +14727,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14735,7 +14741,7 @@
         <v>3.405388602484038</v>
       </c>
       <c r="D264" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E264">
         <v>3.509413159454653</v>
@@ -14771,7 +14777,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14785,7 +14791,7 @@
         <v>3.405511387337113</v>
       </c>
       <c r="D265" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E265">
         <v>3.509413159454653</v>
@@ -14821,7 +14827,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14835,7 +14841,7 @@
         <v>3.451364045513422</v>
       </c>
       <c r="D266" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E266">
         <v>3.509413159454653</v>
@@ -14871,7 +14877,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14885,7 +14891,7 @@
         <v>4.004636932335591</v>
       </c>
       <c r="D267" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E267">
         <v>3.867442887120403</v>
@@ -14935,7 +14941,7 @@
         <v>3.774439165379895</v>
       </c>
       <c r="D268" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E268">
         <v>3.837640654076098</v>
@@ -14985,7 +14991,7 @@
         <v>4.220199786446392</v>
       </c>
       <c r="D269" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E269">
         <v>4.085943565478028</v>
@@ -15021,7 +15027,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15035,7 +15041,7 @@
         <v>3.991103703583256</v>
       </c>
       <c r="D270" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E270">
         <v>4.0441357312043</v>
@@ -15071,7 +15077,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15085,7 +15091,7 @@
         <v>4.24807262091024</v>
       </c>
       <c r="D271" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E271">
         <v>4.172298835483293</v>
@@ -15121,7 +15127,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15135,7 +15141,7 @@
         <v>4.076733299050661</v>
       </c>
       <c r="D272" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E272">
         <v>4.185185728196767</v>
@@ -15171,7 +15177,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15235,7 +15241,7 @@
         <v>3.853669569225198</v>
       </c>
       <c r="D274" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E274">
         <v>3.960609701897911</v>
@@ -15371,7 +15377,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15385,7 +15391,7 @@
         <v>3.457860783201086</v>
       </c>
       <c r="D277" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E277">
         <v>3.562117466477025</v>
@@ -15421,7 +15427,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15435,7 +15441,7 @@
         <v>3.461796612382101</v>
       </c>
       <c r="D278" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E278">
         <v>3.45818163729601</v>
@@ -15471,7 +15477,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15535,7 +15541,7 @@
         <v>1.876063224574707</v>
       </c>
       <c r="D280" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E280">
         <v>1.926860456775207</v>
@@ -15585,7 +15591,7 @@
         <v>1.879462993924748</v>
       </c>
       <c r="D281" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E281">
         <v>1.926860456775207</v>
@@ -15635,7 +15641,7 @@
         <v>1.36286186891499</v>
       </c>
       <c r="D282" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E282">
         <v>1.420876924621103</v>
@@ -15671,7 +15677,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15685,7 +15691,7 @@
         <v>1.365396205962064</v>
       </c>
       <c r="D283" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E283">
         <v>1.420876924621103</v>
@@ -15721,7 +15727,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15735,7 +15741,7 @@
         <v>1.492587172538397</v>
       </c>
       <c r="D284" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E284">
         <v>1.422587172538397</v>
@@ -15771,7 +15777,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15785,7 +15791,7 @@
         <v>1.155028253713973</v>
       </c>
       <c r="D285" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E285">
         <v>1.207786135342488</v>
@@ -15835,7 +15841,7 @@
         <v>1.157212112489207</v>
       </c>
       <c r="D286" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E286">
         <v>1.207786135342488</v>
@@ -15885,7 +15891,7 @@
         <v>1.287557383512098</v>
       </c>
       <c r="D287" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E287">
         <v>1.260086513310223</v>
@@ -15935,7 +15941,7 @@
         <v>-0.2566084186298667</v>
       </c>
       <c r="D288" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E288">
         <v>-0.001048450451905936</v>
@@ -15971,7 +15977,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15985,7 +15991,7 @@
         <v>-0.2875710874180024</v>
       </c>
       <c r="D289" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E289">
         <v>-0.001048450451905936</v>
@@ -16021,7 +16027,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16071,7 +16077,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16121,7 +16127,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16135,7 +16141,7 @@
         <v>-0.3429456734762377</v>
       </c>
       <c r="D292" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E292">
         <v>-0.1559309932859021</v>
@@ -16171,7 +16177,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16185,7 +16191,7 @@
         <v>-0.452945673476238</v>
       </c>
       <c r="D293" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E293">
         <v>-0.1559309932859021</v>
@@ -16221,7 +16227,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16235,7 +16241,7 @@
         <v>-0.07614423041516449</v>
       </c>
       <c r="D294" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E294">
         <v>-0.08649962563060054</v>
@@ -16271,7 +16277,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16285,7 +16291,7 @@
         <v>-0.06685502084603723</v>
       </c>
       <c r="D295" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E295">
         <v>-0.08649962563060054</v>
@@ -16321,7 +16327,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16335,7 +16341,7 @@
         <v>-0.6325763258089658</v>
       </c>
       <c r="D296" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E296">
         <v>-0.7397037652284588</v>
@@ -16371,7 +16377,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16385,7 +16391,7 @@
         <v>-0.6888811406779016</v>
       </c>
       <c r="D297" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E297">
         <v>-0.6347573064746772</v>
@@ -16421,7 +16427,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16435,7 +16441,7 @@
         <v>-0.5922830059527424</v>
       </c>
       <c r="D298" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E298">
         <v>-0.6988811406779014</v>
@@ -16471,7 +16477,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16485,7 +16491,7 @@
         <v>-0.7708727781363214</v>
       </c>
       <c r="D299" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E299">
         <v>-0.7160845060282481</v>
@@ -16521,7 +16527,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16535,7 +16541,7 @@
         <v>-0.6732115427634033</v>
       </c>
       <c r="D300" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E300">
         <v>-0.7808727781363212</v>
@@ -16571,7 +16577,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16585,7 +16591,7 @@
         <v>-0.6051723879795468</v>
       </c>
       <c r="D301" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E301">
         <v>-0.5517269067155315</v>
@@ -16621,7 +16627,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16635,7 +16641,7 @@
         <v>-0.509659617957122</v>
       </c>
       <c r="D302" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E302">
         <v>-0.6151723879795465</v>
@@ -16671,7 +16677,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16685,7 +16691,7 @@
         <v>1.374867998585327</v>
       </c>
       <c r="D303" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E303">
         <v>1.61428021608427</v>
@@ -16721,7 +16727,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16735,7 +16741,7 @@
         <v>1.37455579980999</v>
       </c>
       <c r="D304" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E304">
         <v>1.61428021608427</v>
@@ -16771,7 +16777,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16785,7 +16791,7 @@
         <v>1.659046067002767</v>
       </c>
       <c r="D305" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E305">
         <v>1.701663141543517</v>
@@ -16821,7 +16827,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16835,7 +16841,7 @@
         <v>1.400425101402588</v>
       </c>
       <c r="D306" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E306">
         <v>1.63789275673065</v>
@@ -16871,7 +16877,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16885,7 +16891,7 @@
         <v>1.415426421593279</v>
       </c>
       <c r="D307" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E307">
         <v>1.63789275673065</v>
@@ -16921,7 +16927,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16935,7 +16941,7 @@
         <v>1.672891436539961</v>
       </c>
       <c r="D308" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E308">
         <v>1.702888796158578</v>
@@ -16971,7 +16977,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16985,7 +16991,7 @@
         <v>1.682896717302726</v>
       </c>
       <c r="D309" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E309">
         <v>1.702888796158578</v>
@@ -17021,7 +17027,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17035,7 +17041,7 @@
         <v>1.392287936404873</v>
       </c>
       <c r="D310" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E310">
         <v>1.630374723852328</v>
@@ -17071,7 +17077,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17085,7 +17091,7 @@
         <v>1.392192134372636</v>
       </c>
       <c r="D311" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E311">
         <v>1.630374723852328</v>
@@ -17121,7 +17127,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17135,7 +17141,7 @@
         <v>1.665398674360388</v>
       </c>
       <c r="D312" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E312">
         <v>1.367982501138595</v>
@@ -17171,7 +17177,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17185,7 +17191,7 @@
         <v>1.67530287232815</v>
       </c>
       <c r="D313" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E313">
         <v>1.367982501138595</v>
@@ -17221,7 +17227,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17235,7 +17241,7 @@
         <v>1.683187064752997</v>
       </c>
       <c r="D314" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E314">
         <v>1.385560910531628</v>
@@ -17271,7 +17277,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17285,7 +17291,7 @@
         <v>1.693331241005988</v>
       </c>
       <c r="D315" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E315">
         <v>1.385560910531628</v>
@@ -17321,7 +17327,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17335,7 +17341,7 @@
         <v>1.671335210176903</v>
       </c>
       <c r="D316" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E316">
         <v>1.373848959803819</v>
@@ -17371,7 +17377,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17385,7 +17391,7 @@
         <v>1.68131949631757</v>
       </c>
       <c r="D317" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E317">
         <v>1.373848959803819</v>
@@ -17421,7 +17427,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17435,7 +17441,7 @@
         <v>1.693875753393727</v>
       </c>
       <c r="D318" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E318">
         <v>1.396123425781996</v>
@@ -17471,7 +17477,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17485,7 +17491,7 @@
         <v>1.704164127807133</v>
       </c>
       <c r="D319" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E319">
         <v>1.396123425781996</v>
@@ -17521,7 +17527,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17535,7 +17541,7 @@
         <v>1.366123425781996</v>
       </c>
       <c r="D320" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E320">
         <v>1.403731566187024</v>
@@ -17571,7 +17577,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17585,7 +17591,7 @@
         <v>1.710631890779994</v>
       </c>
       <c r="D321" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E321">
         <v>1.412681767280061</v>
@@ -17621,7 +17627,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17635,7 +17641,7 @@
         <v>1.72114631763706</v>
       </c>
       <c r="D322" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E322">
         <v>1.412681767280061</v>
@@ -17671,7 +17677,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17685,7 +17691,7 @@
         <v>1.382681767280062</v>
       </c>
       <c r="D323" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E323">
         <v>1.420374677351461</v>
@@ -17721,7 +17727,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17735,7 +17741,7 @@
         <v>1.679206240881443</v>
       </c>
       <c r="D324" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E324">
         <v>1.381627077835624</v>
@@ -17785,7 +17791,7 @@
         <v>1.689296712933807</v>
       </c>
       <c r="D325" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E325">
         <v>1.381627077835624</v>
@@ -17835,7 +17841,7 @@
         <v>1.351627077835625</v>
       </c>
       <c r="D326" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E326">
         <v>1.364138386842169</v>
@@ -17885,7 +17891,7 @@
         <v>1.662615013806636</v>
       </c>
       <c r="D327" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E327">
         <v>1.365231699984297</v>
@@ -17921,7 +17927,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17935,7 +17941,7 @@
         <v>1.672481658175022</v>
       </c>
       <c r="D328" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E328">
         <v>1.365231699984297</v>
@@ -17971,7 +17977,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17985,7 +17991,7 @@
         <v>1.335231699984297</v>
       </c>
       <c r="D329" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E329">
         <v>1.330198361076394</v>
@@ -18021,7 +18027,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18035,7 +18041,7 @@
         <v>1.638483426036899</v>
       </c>
       <c r="D330" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E330">
         <v>1.341384970754843</v>
@@ -18085,7 +18091,7 @@
         <v>1.648024517787818</v>
       </c>
       <c r="D331" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E331">
         <v>1.341384970754843</v>
@@ -18185,7 +18191,7 @@
         <v>1.611118158429232</v>
       </c>
       <c r="D333" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E333">
         <v>1.31434273328757</v>
@@ -18235,7 +18241,7 @@
         <v>1.620290072876844</v>
       </c>
       <c r="D334" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E334">
         <v>1.31434273328757</v>
@@ -18285,7 +18291,7 @@
         <v>1.210704115653037</v>
       </c>
       <c r="D335" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E335">
         <v>1.321946243981619</v>
@@ -18335,7 +18341,7 @@
         <v>1.250704115653037</v>
       </c>
       <c r="D336" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E336">
         <v>1.321946243981619</v>
@@ -18385,7 +18391,7 @@
         <v>1.580824889600507</v>
       </c>
       <c r="D337" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E337">
         <v>1.284407057851428</v>
@@ -18421,7 +18427,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18435,7 +18441,7 @@
         <v>1.589588125885168</v>
       </c>
       <c r="D338" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E338">
         <v>1.284407057851428</v>
@@ -18471,7 +18477,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18485,7 +18491,7 @@
         <v>1.180206507742837</v>
       </c>
       <c r="D339" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E339">
         <v>1.27675246238701</v>
@@ -18521,7 +18527,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18535,7 +18541,7 @@
         <v>1.220206507742837</v>
       </c>
       <c r="D340" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E340">
         <v>1.27675246238701</v>
@@ -18571,7 +18577,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18585,7 +18591,7 @@
         <v>1.680056540073359</v>
       </c>
       <c r="D341" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E341">
         <v>1.409353064352823</v>
@@ -18621,7 +18627,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18635,7 +18641,7 @@
         <v>1.717732409003494</v>
       </c>
       <c r="D342" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E342">
         <v>1.409353064352823</v>
@@ -18671,7 +18677,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18685,7 +18691,7 @@
         <v>1.307497917096648</v>
       </c>
       <c r="D343" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E343">
         <v>1.444235818399402</v>
@@ -18721,7 +18727,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18735,7 +18741,7 @@
         <v>1.347497917096648</v>
       </c>
       <c r="D344" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E344">
         <v>1.444235818399402</v>
@@ -18771,7 +18777,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18785,7 +18791,7 @@
         <v>1.842256392262994</v>
       </c>
       <c r="D345" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E345">
         <v>1.530769127897027</v>
@@ -18835,7 +18841,7 @@
         <v>1.431193121765403</v>
       </c>
       <c r="D346" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E346">
         <v>1.572471675023835</v>
@@ -18885,7 +18891,7 @@
         <v>1.471193121765403</v>
       </c>
       <c r="D347" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E347">
         <v>1.572471675023835</v>
@@ -18935,7 +18941,7 @@
         <v>2.306011000659936</v>
       </c>
       <c r="D348" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E348">
         <v>2.348379970519409</v>
@@ -18971,7 +18977,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18985,7 +18991,7 @@
         <v>2.400485390479259</v>
       </c>
       <c r="D349" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E349">
         <v>2.364696230398958</v>
@@ -19021,7 +19027,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19071,7 +19077,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19085,7 +19091,7 @@
         <v>2.315116384839492</v>
       </c>
       <c r="D351" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E351">
         <v>2.323814331699535</v>
@@ -19121,7 +19127,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19135,7 +19141,7 @@
         <v>2.158186337006185</v>
       </c>
       <c r="D352" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E352">
         <v>2.199105803820263</v>
@@ -19171,7 +19177,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19221,7 +19227,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19271,7 +19277,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19285,7 +19291,7 @@
         <v>2.249949180664442</v>
       </c>
       <c r="D355" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E355">
         <v>2.193589002935801</v>
@@ -19321,7 +19327,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19335,7 +19341,7 @@
         <v>3.29910210514231</v>
       </c>
       <c r="D356" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E356">
         <v>3.35230135785332</v>
@@ -19371,7 +19377,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19385,7 +19391,7 @@
         <v>3.804045197377832</v>
       </c>
       <c r="D357" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E357">
         <v>3.415154291605215</v>
@@ -19421,7 +19427,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19435,7 +19441,7 @@
         <v>3.427249571448392</v>
       </c>
       <c r="D358" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E358">
         <v>3.291626526785035</v>
@@ -19471,7 +19477,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19521,7 +19527,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19535,7 +19541,7 @@
         <v>3.442581197445604</v>
       </c>
       <c r="D360" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E360">
         <v>3.306414237004073</v>
@@ -19571,7 +19577,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19585,7 +19591,7 @@
         <v>3.36022431872702</v>
       </c>
       <c r="D361" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E361">
         <v>3.226979110080385</v>
@@ -19621,7 +19627,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19635,7 +19641,7 @@
         <v>3.251003700388559</v>
       </c>
       <c r="D362" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E362">
         <v>3.121633280862579</v>
@@ -19671,7 +19677,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19685,7 +19691,7 @@
         <v>2.99001278638902</v>
       </c>
       <c r="D363" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E363">
         <v>3.032275977245447</v>
@@ -19771,7 +19777,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19785,7 +19791,7 @@
         <v>2.786342722576059</v>
       </c>
       <c r="D365" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E365">
         <v>2.830017022419643</v>
@@ -19821,7 +19827,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19835,7 +19841,7 @@
         <v>2.881784622628198</v>
       </c>
       <c r="D366" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E366">
         <v>2.846342722576059</v>
@@ -19871,7 +19877,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19885,7 +19891,7 @@
         <v>2.713139299753176</v>
       </c>
       <c r="D367" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E367">
         <v>2.672915915531583</v>
@@ -19921,7 +19927,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19935,7 +19941,7 @@
         <v>2.722022378645214</v>
       </c>
       <c r="D368" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E368">
         <v>2.672915915531583</v>
@@ -19971,7 +19977,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19985,7 +19991,7 @@
         <v>2.643362683974768</v>
       </c>
       <c r="D369" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E369">
         <v>2.68802760764238</v>
@@ -20021,7 +20027,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20035,7 +20041,7 @@
         <v>2.738474376085565</v>
       </c>
       <c r="D370" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E370">
         <v>2.678250991863972</v>
@@ -20071,7 +20077,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20085,7 +20091,7 @@
         <v>2.26156876679942</v>
       </c>
       <c r="D371" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E371">
         <v>2.319500204055783</v>
@@ -20121,7 +20127,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20135,7 +20141,7 @@
         <v>2.341086491507057</v>
       </c>
       <c r="D372" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E372">
         <v>2.284741341701965</v>
@@ -20171,7 +20177,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20185,7 +20191,7 @@
         <v>2.25156876679942</v>
       </c>
       <c r="D373" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E373">
         <v>2.298948197976329</v>
@@ -20221,7 +20227,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20235,7 +20241,7 @@
         <v>2.345775623073784</v>
       </c>
       <c r="D374" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E374">
         <v>2.287361910525056</v>
@@ -20271,7 +20277,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20285,7 +20291,7 @@
         <v>1.450725995788351</v>
       </c>
       <c r="D375" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E375">
         <v>1.543612412630503</v>
@@ -20321,7 +20327,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20335,7 +20341,7 @@
         <v>1.378039753255653</v>
       </c>
       <c r="D376" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E376">
         <v>1.473954763536668</v>
@@ -20371,7 +20377,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20385,7 +20391,7 @@
         <v>2.300473418774809</v>
       </c>
       <c r="D377" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E377">
         <v>2.269274816103397</v>
@@ -20435,7 +20441,7 @@
         <v>2.307737312105645</v>
       </c>
       <c r="D378" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E378">
         <v>2.269274816103397</v>
@@ -20485,7 +20491,7 @@
         <v>2.548688372146674</v>
       </c>
       <c r="D379" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E379">
         <v>2.44021981851742</v>
@@ -20521,7 +20527,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20535,7 +20541,7 @@
         <v>4.064626779899114</v>
       </c>
       <c r="D380" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E380">
         <v>3.971827788774664</v>
@@ -20571,7 +20577,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20585,7 +20591,7 @@
         <v>2.704221825320051</v>
       </c>
       <c r="D381" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E381">
         <v>2.757514946748523</v>
@@ -20621,7 +20627,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20635,7 +20641,7 @@
         <v>2.699698304540886</v>
       </c>
       <c r="D382" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E382">
         <v>2.757514946748523</v>
@@ -20671,7 +20677,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20685,7 +20691,7 @@
         <v>2.597723564836138</v>
       </c>
       <c r="D383" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E383">
         <v>2.648687698460786</v>
@@ -20721,7 +20727,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20735,7 +20741,7 @@
         <v>2.594470401040876</v>
       </c>
       <c r="D384" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E384">
         <v>2.648687698460786</v>
@@ -20771,7 +20777,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20785,7 +20791,7 @@
         <v>2.5327482758737</v>
       </c>
       <c r="D385" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E385">
         <v>2.582291478725809</v>
@@ -20821,7 +20827,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20835,7 +20841,7 @@
         <v>2.530270165227095</v>
       </c>
       <c r="D386" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E386">
         <v>2.582291478725809</v>
@@ -20871,7 +20877,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20885,7 +20891,7 @@
         <v>2.615226386520305</v>
       </c>
       <c r="D387" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E387">
         <v>2.605226386520305</v>
@@ -20921,7 +20927,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20935,7 +20941,7 @@
         <v>2.519210324106</v>
       </c>
       <c r="D388" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E388">
         <v>2.474919909368535</v>
@@ -20971,7 +20977,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20985,7 +20991,7 @@
         <v>2.443973795685154</v>
       </c>
       <c r="D389" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E389">
         <v>2.491575608314453</v>
@@ -21021,7 +21027,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21035,7 +21041,7 @@
         <v>2.442554625160083</v>
       </c>
       <c r="D390" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E390">
         <v>2.491575608314453</v>
@@ -21071,7 +21077,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21121,7 +21127,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21135,7 +21141,7 @@
         <v>2.457705873063223</v>
       </c>
       <c r="D392" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E392">
         <v>2.413049360402885</v>
@@ -21171,7 +21177,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21185,7 +21191,7 @@
         <v>2.382591377283335</v>
       </c>
       <c r="D393" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E393">
         <v>2.428850830862097</v>
@@ -21221,7 +21227,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21235,7 +21241,7 @@
         <v>2.381904402604011</v>
       </c>
       <c r="D394" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E394">
         <v>2.428850830862097</v>
@@ -21271,7 +21277,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21285,7 +21291,7 @@
         <v>2.46327835196266</v>
       </c>
       <c r="D395" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E395">
         <v>2.453507343522435</v>
@@ -21321,7 +21327,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21335,7 +21341,7 @@
         <v>2.467705873063223</v>
       </c>
       <c r="D396" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E396">
         <v>2.453507343522435</v>
@@ -21371,7 +21377,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21385,7 +21391,7 @@
         <v>2.447999298642713</v>
       </c>
       <c r="D397" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E397">
         <v>2.403285008753682</v>
@@ -21421,7 +21427,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21435,7 +21441,7 @@
         <v>2.372904061939057</v>
       </c>
       <c r="D398" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E398">
         <v>2.418951665679276</v>
@@ -21471,7 +21477,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21485,7 +21491,7 @@
         <v>2.37233264171712</v>
       </c>
       <c r="D399" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E399">
         <v>2.418951665679276</v>
@@ -21521,7 +21527,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21571,7 +21577,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21621,7 +21627,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21635,7 +21641,7 @@
         <v>2.414261420787727</v>
       </c>
       <c r="D402" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E402">
         <v>2.369346310197177</v>
@@ -21671,7 +21677,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21721,7 +21727,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21771,7 +21777,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21785,7 +21791,7 @@
         <v>2.424261420787727</v>
       </c>
       <c r="D405" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E405">
         <v>2.394544385485897</v>
@@ -21821,7 +21827,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21835,7 +21841,7 @@
         <v>2.414374606666995</v>
       </c>
       <c r="D406" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E406">
         <v>2.394544385485897</v>
@@ -21871,7 +21877,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21885,7 +21891,7 @@
         <v>2.397600622679596</v>
       </c>
       <c r="D407" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E407">
         <v>2.352586340671736</v>
@@ -21921,7 +21927,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21935,7 +21941,7 @@
         <v>2.322605383348882</v>
       </c>
       <c r="D408" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E408">
         <v>2.367553015986731</v>
@@ -21971,7 +21977,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21985,7 +21991,7 @@
         <v>2.322633947364601</v>
       </c>
       <c r="D409" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E409">
         <v>2.367553015986731</v>
@@ -22021,7 +22027,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22035,7 +22041,7 @@
         <v>2.402576819333163</v>
       </c>
       <c r="D410" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E410">
         <v>2.35256729799459</v>
@@ -22071,7 +22077,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22085,7 +22091,7 @@
         <v>2.407600622679595</v>
       </c>
       <c r="D411" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E411">
         <v>2.35256729799459</v>
@@ -22121,7 +22127,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22135,7 +22141,7 @@
         <v>2.39758158000245</v>
       </c>
       <c r="D412" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E412">
         <v>2.35256729799459</v>
@@ -22171,7 +22177,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22185,7 +22191,7 @@
         <v>2.378737718650321</v>
       </c>
       <c r="D413" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E413">
         <v>2.33361115745181</v>
@@ -22221,7 +22227,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22235,7 +22241,7 @@
         <v>2.30377990571649</v>
       </c>
       <c r="D414" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E414">
         <v>2.348315847988621</v>
@@ -22271,7 +22277,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22285,7 +22291,7 @@
         <v>2.304033028113511</v>
       </c>
       <c r="D415" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E415">
         <v>2.348315847988621</v>
@@ -22321,7 +22327,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22335,7 +22341,7 @@
         <v>2.383526783319471</v>
       </c>
       <c r="D416" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E416">
         <v>2.333442409187131</v>
@@ -22371,7 +22377,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22385,7 +22391,7 @@
         <v>2.38873771865032</v>
       </c>
       <c r="D417" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E417">
         <v>2.333442409187131</v>
@@ -22421,7 +22427,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22435,7 +22441,7 @@
         <v>2.378568970385641</v>
       </c>
       <c r="D418" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E418">
         <v>2.333442409187131</v>
@@ -22471,7 +22477,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22485,7 +22491,7 @@
         <v>2.29477967980894</v>
       </c>
       <c r="D419" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E419">
         <v>2.33911879805526</v>
@@ -22535,7 +22541,7 @@
         <v>2.295140160765494</v>
       </c>
       <c r="D420" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E420">
         <v>2.33911879805526</v>
@@ -22585,7 +22591,7 @@
         <v>2.374419198852388</v>
       </c>
       <c r="D421" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E421">
         <v>2.324299038533536</v>
@@ -22635,7 +22641,7 @@
         <v>2.379719599649515</v>
       </c>
       <c r="D422" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E422">
         <v>2.324299038533536</v>
@@ -22685,7 +22691,7 @@
         <v>2.369479279011813</v>
       </c>
       <c r="D423" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E423">
         <v>2.324299038533536</v>
@@ -22735,7 +22741,7 @@
         <v>2.280590400920047</v>
       </c>
       <c r="D424" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E424">
         <v>2.324619216844741</v>
@@ -22771,7 +22777,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22785,7 +22791,7 @@
         <v>2.281120137688396</v>
       </c>
       <c r="D425" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E425">
         <v>2.324619216844741</v>
@@ -22821,7 +22827,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22835,7 +22841,7 @@
         <v>2.360060664151698</v>
       </c>
       <c r="D426" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E426">
         <v>2.309884085228915</v>
@@ -22871,7 +22877,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22921,7 +22927,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22935,7 +22941,7 @@
         <v>2.281700069738552</v>
       </c>
       <c r="D428" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E428">
         <v>2.325753152774585</v>
@@ -22971,7 +22977,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -22985,7 +22991,7 @@
         <v>2.282216569900716</v>
       </c>
       <c r="D429" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E429">
         <v>2.325753152774585</v>
@@ -23021,7 +23027,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23035,7 +23041,7 @@
         <v>2.361183569576388</v>
       </c>
       <c r="D430" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E430">
         <v>2.311011402855666</v>
@@ -23071,7 +23077,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23085,7 +23091,7 @@
         <v>2.255753152774584</v>
       </c>
       <c r="D431" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E431">
         <v>2.30032273597278</v>
@@ -23121,7 +23127,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23135,7 +23141,7 @@
         <v>2.248769782041177</v>
       </c>
       <c r="D432" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E432">
         <v>2.297801715354081</v>
@@ -23171,7 +23177,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23185,7 +23191,7 @@
         <v>2.343406757033516</v>
       </c>
       <c r="D433" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E433">
         <v>2.293164740361742</v>
@@ -23221,7 +23227,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23235,7 +23241,7 @@
         <v>2.237801715354081</v>
       </c>
       <c r="D434" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E434">
         <v>2.26243869034642</v>
@@ -23271,7 +23277,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23285,7 +23291,7 @@
         <v>2.228095614122554</v>
       </c>
       <c r="D435" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E435">
         <v>2.276800683120539</v>
@@ -23321,7 +23327,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23335,7 +23341,7 @@
         <v>2.322610014996799</v>
       </c>
       <c r="D436" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E436">
         <v>2.263257480497806</v>
@@ -23371,7 +23377,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23421,7 +23427,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23435,7 +23441,7 @@
         <v>2.224983216186275</v>
       </c>
       <c r="D438" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E438">
         <v>2.273639077311749</v>
@@ -23485,7 +23491,7 @@
         <v>2.319479164108328</v>
       </c>
       <c r="D439" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E439">
         <v>2.26015123354559</v>
@@ -23635,7 +23641,7 @@
         <v>2.3116287572162</v>
       </c>
       <c r="D442" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E442">
         <v>2.252362519438469</v>
@@ -23671,7 +23677,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23721,7 +23727,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23771,7 +23777,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23835,7 +23841,7 @@
         <v>2.185149484739352</v>
       </c>
       <c r="D446" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E446">
         <v>2.165149484739352</v>
@@ -23935,7 +23941,7 @@
         <v>2.20020073233055</v>
       </c>
       <c r="D448" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E448">
         <v>2.205687152603988</v>
@@ -24021,7 +24027,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24071,7 +24077,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24121,7 +24127,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24171,7 +24177,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24221,7 +24227,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24335,7 +24341,7 @@
         <v>2.142114930387524</v>
       </c>
       <c r="D456" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E456">
         <v>2.162114930387524</v>
@@ -24371,7 +24377,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24385,7 +24391,7 @@
         <v>2.115413806995409</v>
       </c>
       <c r="D457" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E457">
         <v>2.141244762127619</v>
@@ -24471,7 +24477,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24485,7 +24491,7 @@
         <v>2.073994682974101</v>
       </c>
       <c r="D459" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E459">
         <v>2.082201671198685</v>
@@ -24535,7 +24541,7 @@
         <v>2.083994682974101</v>
       </c>
       <c r="D460" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E460">
         <v>2.082201671198685</v>
@@ -24621,7 +24627,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24635,7 +24641,7 @@
         <v>2.057461365020192</v>
       </c>
       <c r="D462" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E462">
         <v>2.066125824243982</v>
@@ -24671,7 +24677,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24721,7 +24727,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24771,7 +24777,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24821,7 +24827,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24871,7 +24877,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24885,7 +24891,7 @@
         <v>2.057577737614682</v>
       </c>
       <c r="D467" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E467">
         <v>2.099815205781953</v>
@@ -24921,7 +24927,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24985,7 +24991,7 @@
         <v>2.075267052489131</v>
       </c>
       <c r="D469" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E469">
         <v>2.105974841560053</v>
@@ -25035,7 +25041,7 @@
         <v>2.0673904197019</v>
       </c>
       <c r="D470" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E470">
         <v>2.109513786914668</v>
@@ -25085,7 +25091,7 @@
         <v>2.101281730695467</v>
       </c>
       <c r="D471" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E471">
         <v>2.131889846669813</v>
@@ -25135,7 +25141,7 @@
         <v>2.093106078618507</v>
       </c>
       <c r="D472" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E472">
         <v>2.134930426541548</v>
@@ -25185,7 +25191,7 @@
         <v>2.114232378900782</v>
       </c>
       <c r="D473" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E473">
         <v>2.144790875533345</v>
@@ -25221,7 +25227,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25235,7 +25241,7 @@
         <v>2.164790875533345</v>
       </c>
       <c r="D474" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E474">
         <v>2.134232378900781</v>
@@ -25271,7 +25277,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25285,7 +25291,7 @@
         <v>2.105907868798473</v>
       </c>
       <c r="D475" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E475">
         <v>2.147583358696166</v>
@@ -25321,7 +25327,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25335,7 +25341,7 @@
         <v>2.178667208693582</v>
       </c>
       <c r="D476" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E476">
         <v>2.148162082573172</v>
@@ -25371,7 +25377,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25385,7 +25391,7 @@
         <v>2.119677460934401</v>
       </c>
       <c r="D477" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E477">
         <v>2.161192839295628</v>
@@ -25421,7 +25427,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25435,7 +25441,7 @@
         <v>2.191253934723685</v>
       </c>
       <c r="D478" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E478">
         <v>2.160797219088007</v>
@@ -25485,7 +25491,7 @@
         <v>2.132167365995042</v>
       </c>
       <c r="D479" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E479">
         <v>2.173537512902076</v>
@@ -25585,7 +25591,7 @@
         <v>2.161339958759847</v>
       </c>
       <c r="D481" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E481">
         <v>2.202370889471942</v>
@@ -25635,7 +25641,7 @@
         <v>2.215480849833102</v>
       </c>
       <c r="D482" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E482">
         <v>2.179965384477054</v>
@@ -25685,7 +25691,7 @@
         <v>1.276065947508897</v>
       </c>
       <c r="D483" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E483">
         <v>1.317566169928825</v>
@@ -25721,7 +25727,7 @@
         <v>1</v>
       </c>
       <c r="P483" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="484" spans="1:16">
@@ -25735,7 +25741,7 @@
         <v>1.37689891014235</v>
       </c>
       <c r="D484" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E484">
         <v>1.288399132562277</v>
@@ -25771,7 +25777,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -25785,7 +25791,7 @@
         <v>1.265250934212467</v>
       </c>
       <c r="D485" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E485">
         <v>1.306889515011455</v>
@@ -25821,7 +25827,7 @@
         <v>1</v>
       </c>
       <c r="P485" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -25835,7 +25841,7 @@
         <v>1.365853299547489</v>
       </c>
       <c r="D486" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E486">
         <v>1.277491880346475</v>
@@ -25871,7 +25877,7 @@
         <v>1</v>
       </c>
       <c r="P486" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -25885,7 +25891,7 @@
         <v>1.365250934212467</v>
       </c>
       <c r="D487" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E487">
         <v>1.29891353608099</v>
@@ -25921,7 +25927,7 @@
         <v>1</v>
       </c>
       <c r="P487" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -25935,7 +25941,7 @@
         <v>1.335853299547488</v>
       </c>
       <c r="D488" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E488">
         <v>1.29891353608099</v>
@@ -25971,7 +25977,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -25985,7 +25991,7 @@
         <v>1.257848770795328</v>
       </c>
       <c r="D489" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E489">
         <v>1.29958204878089</v>
@@ -26021,7 +26027,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26035,7 +26041,7 @@
         <v>1.358293307486061</v>
       </c>
       <c r="D490" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E490">
         <v>1.270026585471621</v>
@@ -26071,7 +26077,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26085,7 +26091,7 @@
         <v>1.328293307486061</v>
       </c>
       <c r="D491" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E491">
         <v>1.291337761155134</v>
@@ -26121,7 +26127,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -26135,7 +26141,7 @@
         <v>1.336383675279734</v>
       </c>
       <c r="D492" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E492">
         <v>1.248391395422367</v>
@@ -26185,7 +26191,7 @@
         <v>1.306383675279734</v>
       </c>
       <c r="D493" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E493">
         <v>1.269382388589295</v>
@@ -26235,7 +26241,7 @@
         <v>1.279467032224208</v>
       </c>
       <c r="D494" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E494">
         <v>1.192187695703653</v>
@@ -26271,7 +26277,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -26285,7 +26291,7 @@
         <v>1.280668138023285</v>
       </c>
       <c r="D495" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E495">
         <v>1.2123469216443</v>
@@ -26321,7 +26327,7 @@
         <v>1</v>
       </c>
       <c r="P495" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -26335,7 +26341,7 @@
         <v>1.249467032224208</v>
       </c>
       <c r="D496" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E496">
         <v>1.2123469216443</v>
@@ -26371,7 +26377,7 @@
         <v>1</v>
       </c>
       <c r="P496" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="497" spans="1:16">
@@ -26385,7 +26391,7 @@
         <v>1.175386037005039</v>
       </c>
       <c r="D497" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E497">
         <v>1.183866479324669</v>
@@ -26421,7 +26427,7 @@
         <v>1</v>
       </c>
       <c r="P497" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="498" spans="1:16">
@@ -26435,7 +26441,7 @@
         <v>1.24514956586386</v>
       </c>
       <c r="D498" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E498">
         <v>1.158300093222558</v>
@@ -26471,7 +26477,7 @@
         <v>1</v>
       </c>
       <c r="P498" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="499" spans="1:16">
@@ -26485,7 +26491,7 @@
         <v>1.247067111461691</v>
       </c>
       <c r="D499" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E499">
         <v>1.177957811304076</v>
@@ -26521,7 +26527,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -26535,7 +26541,7 @@
         <v>1.21514956586386</v>
       </c>
       <c r="D500" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E500">
         <v>1.177957811304076</v>
@@ -26571,7 +26577,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -26585,7 +26591,7 @@
         <v>1.140423774825811</v>
       </c>
       <c r="D501" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E501">
         <v>1.202341320423642</v>
@@ -26621,7 +26627,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -26635,7 +26641,7 @@
         <v>1.226637749198502</v>
       </c>
       <c r="D502" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E502">
         <v>1.140020157350503</v>
@@ -26671,7 +26677,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -26685,7 +26691,7 @@
         <v>1.196637749198502</v>
       </c>
       <c r="D503" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E503">
         <v>1.159407347839835</v>
@@ -26721,7 +26727,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -26735,7 +26741,7 @@
         <v>1.121564136970499</v>
       </c>
       <c r="D504" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E504">
         <v>1.183868150557168</v>
@@ -26771,7 +26777,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -26785,7 +26791,7 @@
         <v>1.183891513054156</v>
       </c>
       <c r="D505" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E505">
         <v>1.097809364665167</v>
@@ -26821,7 +26827,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -26835,7 +26841,7 @@
         <v>1.153891513054155</v>
       </c>
       <c r="D506" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E506">
         <v>1.116571871118987</v>
@@ -26871,7 +26877,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -26885,7 +26891,7 @@
         <v>1.078014735637637</v>
       </c>
       <c r="D507" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E507">
         <v>1.141211154989324</v>
@@ -26921,7 +26927,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -26935,7 +26941,7 @@
         <v>1.043879816012319</v>
       </c>
       <c r="D508" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E508">
         <v>1.107775721421902</v>
@@ -26985,7 +26991,7 @@
         <v>0.9836705709653022</v>
       </c>
       <c r="D509" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E509">
         <v>1.048800272379947</v>
@@ -27021,7 +27027,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27071,7 +27077,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27085,7 +27091,7 @@
         <v>0.8606424187706248</v>
       </c>
       <c r="D511" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E511">
         <v>0.9282931888777832</v>
@@ -27121,7 +27127,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -27135,7 +27141,7 @@
         <v>0.9692391900170905</v>
       </c>
       <c r="D512" t="s">
-        <v>279</v>
+        <v>154</v>
       </c>
       <c r="E512">
         <v>1.044655037134966</v>
@@ -27171,7 +27177,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -27185,7 +27191,7 @@
         <v>0.7220196008880824</v>
       </c>
       <c r="D513" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E513">
         <v>0.7925110025092272</v>
@@ -27221,7 +27227,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -27235,10 +27241,10 @@
         <v>0.8371498246167173</v>
       </c>
       <c r="D514" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E514">
-        <v>0.915690366399978</v>
+        <v>0.8088549836440295</v>
       </c>
       <c r="F514">
         <v>-1</v>
@@ -27247,10 +27253,10 @@
         <v>0.008322850175383284</v>
       </c>
       <c r="H514">
-        <v>0.008224309633600022</v>
+        <v>0.008391145016355971</v>
       </c>
       <c r="I514">
-        <v>-0.07854054178326075</v>
+        <v>0.02829484097268775</v>
       </c>
       <c r="J514">
         <v>0.8049140162114586</v>
@@ -27262,16 +27268,16 @@
         <v>4.58</v>
       </c>
       <c r="M514">
-        <v>4.54</v>
+        <v>4.71</v>
       </c>
       <c r="N514">
-        <v>4.57</v>
+        <v>4.6</v>
       </c>
       <c r="O514">
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -27279,13 +27285,13 @@
         <v>0</v>
       </c>
       <c r="B515" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C515">
-        <v>0.4969504786678423</v>
+        <v>0.5224815208071796</v>
       </c>
       <c r="D515" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E515">
         <v>0.5720539524656312</v>
@@ -27294,19 +27300,19 @@
         <v>1</v>
       </c>
       <c r="G515">
-        <v>0.00880304952133216</v>
+        <v>0.008777518479192821</v>
       </c>
       <c r="H515">
         <v>0.008707946047534368</v>
       </c>
       <c r="I515">
-        <v>0.07510347379778892</v>
+        <v>0.0495724316584516</v>
       </c>
       <c r="J515">
         <v>0.8510347379779013</v>
       </c>
       <c r="K515">
-        <v>4.88</v>
+        <v>4.85</v>
       </c>
       <c r="L515">
         <v>4.65</v>
@@ -27329,43 +27335,43 @@
         <v>1</v>
       </c>
       <c r="B516" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C516">
-        <v>0.6226884684027589</v>
+        <v>0.4969504786678423</v>
       </c>
       <c r="D516" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E516">
-        <v>0.7063022895803281</v>
+        <v>0.5720539524656312</v>
       </c>
       <c r="F516">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G516">
-        <v>0.008537311531597242</v>
+        <v>0.00880304952133216</v>
       </c>
       <c r="H516">
-        <v>0.008433697710419671</v>
+        <v>0.008707946047534368</v>
       </c>
       <c r="I516">
-        <v>-0.08361382117756921</v>
+        <v>0.07510347379778892</v>
       </c>
       <c r="J516">
         <v>0.8510347379779013</v>
       </c>
       <c r="K516">
+        <v>4.88</v>
+      </c>
+      <c r="L516">
         <v>4.65</v>
       </c>
-      <c r="L516">
-        <v>4.58</v>
-      </c>
       <c r="M516">
-        <v>4.54</v>
+        <v>4.78</v>
       </c>
       <c r="N516">
-        <v>4.57</v>
+        <v>4.64</v>
       </c>
       <c r="O516">
         <v>1</v>
@@ -27376,152 +27382,252 @@
     </row>
     <row r="517" spans="1:16">
       <c r="A517" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B517" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C517">
-        <v>0.9942742592090008</v>
+        <v>0.6226884684027589</v>
       </c>
       <c r="D517" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E517">
-        <v>1.059186671930127</v>
+        <v>0.5916263841240843</v>
       </c>
       <c r="F517">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G517">
-        <v>0.008305725740791001</v>
+        <v>0.008537311531597242</v>
       </c>
       <c r="H517">
-        <v>0.008220813328069874</v>
+        <v>0.008608373615875915</v>
       </c>
       <c r="I517">
-        <v>0.06491241272112624</v>
+        <v>0.03106208427867463</v>
       </c>
       <c r="J517">
-        <v>0.7491241272112704</v>
+        <v>0.8510347379779013</v>
       </c>
       <c r="K517">
-        <v>4.88</v>
+        <v>4.65</v>
       </c>
       <c r="L517">
-        <v>4.65</v>
+        <v>4.58</v>
       </c>
       <c r="M517">
-        <v>4.78</v>
+        <v>4.71</v>
       </c>
       <c r="N517">
-        <v>4.64</v>
+        <v>4.6</v>
       </c>
       <c r="O517">
         <v>1</v>
       </c>
       <c r="P517" t="s">
-        <v>276</v>
+        <v>148</v>
       </c>
     </row>
     <row r="518" spans="1:16">
       <c r="A518" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B518" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C518">
-        <v>1.096572808467593</v>
+        <v>0.9942742592090008</v>
       </c>
       <c r="D518" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E518">
-        <v>1.168976462460833</v>
+        <v>1.059186671930127</v>
       </c>
       <c r="F518">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G518">
-        <v>0.008063427191532409</v>
+        <v>0.008305725740791001</v>
       </c>
       <c r="H518">
-        <v>0.007971023537539168</v>
+        <v>0.008220813328069874</v>
       </c>
       <c r="I518">
-        <v>-0.07240365399324</v>
+        <v>0.06491241272112624</v>
       </c>
       <c r="J518">
         <v>0.7491241272112704</v>
       </c>
       <c r="K518">
+        <v>4.88</v>
+      </c>
+      <c r="L518">
         <v>4.65</v>
       </c>
-      <c r="L518">
-        <v>4.58</v>
-      </c>
       <c r="M518">
-        <v>4.54</v>
+        <v>4.78</v>
       </c>
       <c r="N518">
-        <v>4.57</v>
+        <v>4.64</v>
       </c>
       <c r="O518">
         <v>1</v>
       </c>
       <c r="P518" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="519" spans="1:16">
       <c r="A519" s="1">
+        <v>1</v>
+      </c>
+      <c r="B519" t="s">
+        <v>152</v>
+      </c>
+      <c r="C519">
+        <v>1.096572808467593</v>
+      </c>
+      <c r="D519" t="s">
+        <v>281</v>
+      </c>
+      <c r="E519">
+        <v>1.071625360834916</v>
+      </c>
+      <c r="F519">
+        <v>-1</v>
+      </c>
+      <c r="G519">
+        <v>0.008063427191532409</v>
+      </c>
+      <c r="H519">
+        <v>0.008128374639165083</v>
+      </c>
+      <c r="I519">
+        <v>0.02494744763267631</v>
+      </c>
+      <c r="J519">
+        <v>0.7491241272112704</v>
+      </c>
+      <c r="K519">
+        <v>4.65</v>
+      </c>
+      <c r="L519">
+        <v>4.58</v>
+      </c>
+      <c r="M519">
+        <v>4.71</v>
+      </c>
+      <c r="N519">
+        <v>4.6</v>
+      </c>
+      <c r="O519">
+        <v>1</v>
+      </c>
+      <c r="P519" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="520" spans="1:16">
+      <c r="A520" s="1">
         <v>0</v>
       </c>
-      <c r="B519" t="s">
+      <c r="B520" t="s">
         <v>150</v>
       </c>
-      <c r="C519">
+      <c r="C520">
         <v>1.041561394347275</v>
       </c>
-      <c r="D519" t="s">
-        <v>278</v>
-      </c>
-      <c r="E519">
+      <c r="D520" t="s">
+        <v>280</v>
+      </c>
+      <c r="E520">
         <v>1.105504808397535</v>
       </c>
-      <c r="F519">
-        <v>1</v>
-      </c>
-      <c r="G519">
+      <c r="F520">
+        <v>1</v>
+      </c>
+      <c r="G520">
         <v>0.008258438605652724</v>
       </c>
-      <c r="H519">
+      <c r="H520">
         <v>0.008174495191602463</v>
       </c>
-      <c r="I519">
+      <c r="I520">
         <v>0.06394341405025994</v>
       </c>
-      <c r="J519">
+      <c r="J520">
         <v>0.7394341405026076</v>
       </c>
-      <c r="K519">
+      <c r="K520">
         <v>4.88</v>
       </c>
-      <c r="L519">
+      <c r="L520">
         <v>4.65</v>
       </c>
-      <c r="M519">
+      <c r="M520">
         <v>4.78</v>
       </c>
-      <c r="N519">
+      <c r="N520">
         <v>4.64</v>
       </c>
-      <c r="O519">
-        <v>1</v>
-      </c>
-      <c r="P519" t="s">
-        <v>400</v>
+      <c r="O520">
+        <v>1</v>
+      </c>
+      <c r="P520" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="521" spans="1:16">
+      <c r="A521" s="1">
+        <v>1</v>
+      </c>
+      <c r="B521" t="s">
+        <v>154</v>
+      </c>
+      <c r="C521">
+        <v>1.212969002118162</v>
+      </c>
+      <c r="D521" t="s">
+        <v>281</v>
+      </c>
+      <c r="E521">
+        <v>1.117265198232718</v>
+      </c>
+      <c r="F521">
+        <v>-1</v>
+      </c>
+      <c r="G521">
+        <v>0.007927030997881839</v>
+      </c>
+      <c r="H521">
+        <v>0.00808273480176728</v>
+      </c>
+      <c r="I521">
+        <v>0.09570380388544386</v>
+      </c>
+      <c r="J521">
+        <v>0.7394341405026076</v>
+      </c>
+      <c r="K521">
+        <v>4.54</v>
+      </c>
+      <c r="L521">
+        <v>4.57</v>
+      </c>
+      <c r="M521">
+        <v>4.71</v>
+      </c>
+      <c r="N521">
+        <v>4.6</v>
+      </c>
+      <c r="O521">
+        <v>1</v>
+      </c>
+      <c r="P521" t="s">
+        <v>402</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-03328-601328.xlsx
+++ b/s60_signal/position-03328-601328.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="404">
   <si>
     <t>trade_time</t>
   </si>
@@ -478,388 +478,391 @@
     <t>2021-11-16</t>
   </si>
   <si>
+    <t>2016-05-31</t>
+  </si>
+  <si>
+    <t>2016-06-07</t>
+  </si>
+  <si>
+    <t>2016-06-13</t>
+  </si>
+  <si>
+    <t>2016-06-28</t>
+  </si>
+  <si>
+    <t>2016-06-14</t>
+  </si>
+  <si>
+    <t>2016-06-29</t>
+  </si>
+  <si>
+    <t>2016-07-06</t>
+  </si>
+  <si>
+    <t>2016-07-07</t>
+  </si>
+  <si>
+    <t>2016-07-08</t>
+  </si>
+  <si>
+    <t>2016-07-11</t>
+  </si>
+  <si>
+    <t>2016-07-13</t>
+  </si>
+  <si>
+    <t>2016-07-15</t>
+  </si>
+  <si>
+    <t>2016-07-18</t>
+  </si>
+  <si>
+    <t>2016-07-19</t>
+  </si>
+  <si>
+    <t>2016-07-20</t>
+  </si>
+  <si>
+    <t>2016-07-21</t>
+  </si>
+  <si>
+    <t>2016-07-25</t>
+  </si>
+  <si>
+    <t>2016-07-27</t>
+  </si>
+  <si>
+    <t>2016-07-29</t>
+  </si>
+  <si>
+    <t>2016-12-15</t>
+  </si>
+  <si>
+    <t>2017-01-03</t>
+  </si>
+  <si>
+    <t>2017-02-14</t>
+  </si>
+  <si>
+    <t>2017-02-15</t>
+  </si>
+  <si>
+    <t>2017-03-02</t>
+  </si>
+  <si>
+    <t>2017-04-18</t>
+  </si>
+  <si>
+    <t>2017-04-26</t>
+  </si>
+  <si>
+    <t>2017-04-27</t>
+  </si>
+  <si>
+    <t>2017-05-04</t>
+  </si>
+  <si>
+    <t>2017-05-05</t>
+  </si>
+  <si>
+    <t>2017-05-09</t>
+  </si>
+  <si>
+    <t>2017-05-12</t>
+  </si>
+  <si>
+    <t>2017-06-02</t>
+  </si>
+  <si>
+    <t>2017-06-06</t>
+  </si>
+  <si>
+    <t>2017-06-08</t>
+  </si>
+  <si>
+    <t>2017-06-14</t>
+  </si>
+  <si>
+    <t>2017-06-22</t>
+  </si>
+  <si>
+    <t>2017-06-23</t>
+  </si>
+  <si>
+    <t>2017-06-20</t>
+  </si>
+  <si>
+    <t>2017-06-29</t>
+  </si>
+  <si>
+    <t>2017-07-03</t>
+  </si>
+  <si>
+    <t>2017-07-04</t>
+  </si>
+  <si>
+    <t>2017-07-05</t>
+  </si>
+  <si>
+    <t>2017-07-06</t>
+  </si>
+  <si>
+    <t>2017-10-12</t>
+  </si>
+  <si>
+    <t>2017-10-19</t>
+  </si>
+  <si>
+    <t>2017-10-26</t>
+  </si>
+  <si>
+    <t>2017-10-31</t>
+  </si>
+  <si>
+    <t>2018-03-15</t>
+  </si>
+  <si>
+    <t>2018-06-05</t>
+  </si>
+  <si>
+    <t>2018-06-08</t>
+  </si>
+  <si>
+    <t>2018-05-16</t>
+  </si>
+  <si>
+    <t>2018-06-13</t>
+  </si>
+  <si>
+    <t>2018-06-14</t>
+  </si>
+  <si>
+    <t>2018-06-19</t>
+  </si>
+  <si>
+    <t>2018-06-29</t>
+  </si>
+  <si>
+    <t>2018-07-12</t>
+  </si>
+  <si>
+    <t>2018-07-04</t>
+  </si>
+  <si>
+    <t>2018-07-13</t>
+  </si>
+  <si>
+    <t>2018-07-16</t>
+  </si>
+  <si>
+    <t>2018-07-18</t>
+  </si>
+  <si>
+    <t>2018-11-05</t>
+  </si>
+  <si>
+    <t>2018-11-15</t>
+  </si>
+  <si>
+    <t>2018-11-19</t>
+  </si>
+  <si>
+    <t>2018-11-07</t>
+  </si>
+  <si>
+    <t>2018-11-21</t>
+  </si>
+  <si>
+    <t>2018-11-22</t>
+  </si>
+  <si>
+    <t>2018-11-27</t>
+  </si>
+  <si>
+    <t>2018-12-03</t>
+  </si>
+  <si>
+    <t>2018-12-04</t>
+  </si>
+  <si>
+    <t>2018-12-10</t>
+  </si>
+  <si>
+    <t>2018-12-11</t>
+  </si>
+  <si>
+    <t>2019-05-09</t>
+  </si>
+  <si>
+    <t>2019-05-27</t>
+  </si>
+  <si>
+    <t>2019-05-30</t>
+  </si>
+  <si>
+    <t>2019-06-25</t>
+  </si>
+  <si>
+    <t>2019-07-04</t>
+  </si>
+  <si>
+    <t>2019-07-08</t>
+  </si>
+  <si>
+    <t>2019-07-09</t>
+  </si>
+  <si>
+    <t>2019-07-15</t>
+  </si>
+  <si>
+    <t>2019-07-16</t>
+  </si>
+  <si>
+    <t>2019-07-17</t>
+  </si>
+  <si>
+    <t>2019-07-18</t>
+  </si>
+  <si>
+    <t>2019-07-22</t>
+  </si>
+  <si>
+    <t>2019-07-23</t>
+  </si>
+  <si>
+    <t>2019-07-24</t>
+  </si>
+  <si>
+    <t>2019-07-25</t>
+  </si>
+  <si>
+    <t>2019-09-19</t>
+  </si>
+  <si>
+    <t>2019-09-23</t>
+  </si>
+  <si>
+    <t>2019-09-27</t>
+  </si>
+  <si>
+    <t>2019-09-06</t>
+  </si>
+  <si>
+    <t>2019-09-30</t>
+  </si>
+  <si>
+    <t>2019-11-25</t>
+  </si>
+  <si>
+    <t>2020-07-14</t>
+  </si>
+  <si>
+    <t>2020-07-24</t>
+  </si>
+  <si>
+    <t>2020-08-14</t>
+  </si>
+  <si>
+    <t>2020-08-18</t>
+  </si>
+  <si>
+    <t>2020-08-12</t>
+  </si>
+  <si>
+    <t>2020-08-19</t>
+  </si>
+  <si>
+    <t>2020-08-03</t>
+  </si>
+  <si>
+    <t>2020-11-20</t>
+  </si>
+  <si>
+    <t>2020-12-08</t>
+  </si>
+  <si>
+    <t>2020-12-09</t>
+  </si>
+  <si>
+    <t>2021-03-19</t>
+  </si>
+  <si>
+    <t>2021-05-10</t>
+  </si>
+  <si>
+    <t>2021-05-12</t>
+  </si>
+  <si>
+    <t>2021-04-22</t>
+  </si>
+  <si>
+    <t>2021-05-14</t>
+  </si>
+  <si>
+    <t>2021-05-18</t>
+  </si>
+  <si>
+    <t>2021-05-20</t>
+  </si>
+  <si>
+    <t>2021-05-26</t>
+  </si>
+  <si>
+    <t>2021-05-07</t>
+  </si>
+  <si>
+    <t>2021-05-27</t>
+  </si>
+  <si>
+    <t>2021-05-21</t>
+  </si>
+  <si>
+    <t>2021-06-02</t>
+  </si>
+  <si>
+    <t>2021-06-03</t>
+  </si>
+  <si>
+    <t>2021-06-09</t>
+  </si>
+  <si>
+    <t>2021-06-10</t>
+  </si>
+  <si>
+    <t>2021-06-15</t>
+  </si>
+  <si>
+    <t>2021-06-16</t>
+  </si>
+  <si>
+    <t>2021-06-18</t>
+  </si>
+  <si>
+    <t>2021-06-28</t>
+  </si>
+  <si>
+    <t>2021-10-29</t>
+  </si>
+  <si>
+    <t>2021-11-02</t>
+  </si>
+  <si>
+    <t>2021-11-12</t>
+  </si>
+  <si>
+    <t>2021-11-22</t>
+  </si>
+  <si>
+    <t>2021-11-23</t>
+  </si>
+  <si>
     <t>2021-11-30</t>
   </si>
   <si>
-    <t>2016-05-31</t>
-  </si>
-  <si>
-    <t>2016-06-07</t>
-  </si>
-  <si>
-    <t>2016-06-13</t>
-  </si>
-  <si>
-    <t>2016-06-28</t>
-  </si>
-  <si>
-    <t>2016-06-14</t>
-  </si>
-  <si>
-    <t>2016-06-29</t>
-  </si>
-  <si>
-    <t>2016-07-06</t>
-  </si>
-  <si>
-    <t>2016-07-07</t>
-  </si>
-  <si>
-    <t>2016-07-08</t>
-  </si>
-  <si>
-    <t>2016-07-11</t>
-  </si>
-  <si>
-    <t>2016-07-13</t>
-  </si>
-  <si>
-    <t>2016-07-15</t>
-  </si>
-  <si>
-    <t>2016-07-18</t>
-  </si>
-  <si>
-    <t>2016-07-19</t>
-  </si>
-  <si>
-    <t>2016-07-20</t>
-  </si>
-  <si>
-    <t>2016-07-21</t>
-  </si>
-  <si>
-    <t>2016-07-25</t>
-  </si>
-  <si>
-    <t>2016-07-27</t>
-  </si>
-  <si>
-    <t>2016-07-29</t>
-  </si>
-  <si>
-    <t>2016-12-15</t>
-  </si>
-  <si>
-    <t>2017-01-03</t>
-  </si>
-  <si>
-    <t>2017-02-14</t>
-  </si>
-  <si>
-    <t>2017-02-15</t>
-  </si>
-  <si>
-    <t>2017-03-02</t>
-  </si>
-  <si>
-    <t>2017-04-18</t>
-  </si>
-  <si>
-    <t>2017-04-26</t>
-  </si>
-  <si>
-    <t>2017-04-27</t>
-  </si>
-  <si>
-    <t>2017-05-04</t>
-  </si>
-  <si>
-    <t>2017-05-05</t>
-  </si>
-  <si>
-    <t>2017-05-09</t>
-  </si>
-  <si>
-    <t>2017-05-12</t>
-  </si>
-  <si>
-    <t>2017-06-02</t>
-  </si>
-  <si>
-    <t>2017-06-06</t>
-  </si>
-  <si>
-    <t>2017-06-08</t>
-  </si>
-  <si>
-    <t>2017-06-14</t>
-  </si>
-  <si>
-    <t>2017-06-22</t>
-  </si>
-  <si>
-    <t>2017-06-23</t>
-  </si>
-  <si>
-    <t>2017-06-20</t>
-  </si>
-  <si>
-    <t>2017-06-29</t>
-  </si>
-  <si>
-    <t>2017-07-03</t>
-  </si>
-  <si>
-    <t>2017-07-04</t>
-  </si>
-  <si>
-    <t>2017-07-05</t>
-  </si>
-  <si>
-    <t>2017-07-06</t>
-  </si>
-  <si>
-    <t>2017-10-12</t>
-  </si>
-  <si>
-    <t>2017-10-19</t>
-  </si>
-  <si>
-    <t>2017-10-26</t>
-  </si>
-  <si>
-    <t>2017-10-31</t>
-  </si>
-  <si>
-    <t>2018-03-15</t>
-  </si>
-  <si>
-    <t>2018-06-05</t>
-  </si>
-  <si>
-    <t>2018-06-08</t>
-  </si>
-  <si>
-    <t>2018-05-16</t>
-  </si>
-  <si>
-    <t>2018-06-13</t>
-  </si>
-  <si>
-    <t>2018-06-14</t>
-  </si>
-  <si>
-    <t>2018-06-19</t>
-  </si>
-  <si>
-    <t>2018-06-29</t>
-  </si>
-  <si>
-    <t>2018-07-12</t>
-  </si>
-  <si>
-    <t>2018-07-04</t>
-  </si>
-  <si>
-    <t>2018-07-13</t>
-  </si>
-  <si>
-    <t>2018-07-16</t>
-  </si>
-  <si>
-    <t>2018-07-18</t>
-  </si>
-  <si>
-    <t>2018-11-05</t>
-  </si>
-  <si>
-    <t>2018-11-15</t>
-  </si>
-  <si>
-    <t>2018-11-19</t>
-  </si>
-  <si>
-    <t>2018-11-07</t>
-  </si>
-  <si>
-    <t>2018-11-21</t>
-  </si>
-  <si>
-    <t>2018-11-22</t>
-  </si>
-  <si>
-    <t>2018-11-27</t>
-  </si>
-  <si>
-    <t>2018-12-03</t>
-  </si>
-  <si>
-    <t>2018-12-04</t>
-  </si>
-  <si>
-    <t>2018-12-10</t>
-  </si>
-  <si>
-    <t>2018-12-11</t>
-  </si>
-  <si>
-    <t>2019-05-09</t>
-  </si>
-  <si>
-    <t>2019-05-27</t>
-  </si>
-  <si>
-    <t>2019-05-30</t>
-  </si>
-  <si>
-    <t>2019-06-25</t>
-  </si>
-  <si>
-    <t>2019-07-04</t>
-  </si>
-  <si>
-    <t>2019-07-08</t>
-  </si>
-  <si>
-    <t>2019-07-09</t>
-  </si>
-  <si>
-    <t>2019-07-15</t>
-  </si>
-  <si>
-    <t>2019-07-16</t>
-  </si>
-  <si>
-    <t>2019-07-17</t>
-  </si>
-  <si>
-    <t>2019-07-18</t>
-  </si>
-  <si>
-    <t>2019-07-22</t>
-  </si>
-  <si>
-    <t>2019-07-23</t>
-  </si>
-  <si>
-    <t>2019-07-24</t>
-  </si>
-  <si>
-    <t>2019-07-25</t>
-  </si>
-  <si>
-    <t>2019-09-19</t>
-  </si>
-  <si>
-    <t>2019-09-23</t>
-  </si>
-  <si>
-    <t>2019-09-27</t>
-  </si>
-  <si>
-    <t>2019-09-06</t>
-  </si>
-  <si>
-    <t>2019-09-30</t>
-  </si>
-  <si>
-    <t>2019-11-25</t>
-  </si>
-  <si>
-    <t>2020-07-14</t>
-  </si>
-  <si>
-    <t>2020-07-24</t>
-  </si>
-  <si>
-    <t>2020-08-14</t>
-  </si>
-  <si>
-    <t>2020-08-18</t>
-  </si>
-  <si>
-    <t>2020-08-12</t>
-  </si>
-  <si>
-    <t>2020-08-19</t>
-  </si>
-  <si>
-    <t>2020-08-03</t>
-  </si>
-  <si>
-    <t>2020-11-20</t>
-  </si>
-  <si>
-    <t>2020-12-08</t>
-  </si>
-  <si>
-    <t>2020-12-09</t>
-  </si>
-  <si>
-    <t>2021-03-19</t>
-  </si>
-  <si>
-    <t>2021-05-10</t>
-  </si>
-  <si>
-    <t>2021-05-12</t>
-  </si>
-  <si>
-    <t>2021-04-22</t>
-  </si>
-  <si>
-    <t>2021-05-14</t>
-  </si>
-  <si>
-    <t>2021-05-18</t>
-  </si>
-  <si>
-    <t>2021-05-20</t>
-  </si>
-  <si>
-    <t>2021-05-26</t>
-  </si>
-  <si>
-    <t>2021-05-07</t>
-  </si>
-  <si>
-    <t>2021-05-27</t>
-  </si>
-  <si>
-    <t>2021-05-21</t>
-  </si>
-  <si>
-    <t>2021-06-02</t>
-  </si>
-  <si>
-    <t>2021-06-03</t>
-  </si>
-  <si>
-    <t>2021-06-09</t>
-  </si>
-  <si>
-    <t>2021-06-10</t>
-  </si>
-  <si>
-    <t>2021-06-15</t>
-  </si>
-  <si>
-    <t>2021-06-16</t>
-  </si>
-  <si>
-    <t>2021-06-18</t>
-  </si>
-  <si>
-    <t>2021-06-28</t>
-  </si>
-  <si>
-    <t>2021-10-29</t>
-  </si>
-  <si>
-    <t>2021-11-02</t>
-  </si>
-  <si>
-    <t>2021-11-12</t>
-  </si>
-  <si>
-    <t>2021-11-22</t>
-  </si>
-  <si>
-    <t>2021-11-23</t>
-  </si>
-  <si>
     <t>2021-12-01</t>
+  </si>
+  <si>
+    <t>2021-12-02</t>
   </si>
   <si>
     <t>2016-05-24</t>
@@ -1641,7 +1644,7 @@
         <v>2.636521639996683</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E2">
         <v>2.833647241107702</v>
@@ -1677,7 +1680,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1691,7 +1694,7 @@
         <v>2.808801457176021</v>
       </c>
       <c r="D3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E3">
         <v>2.7135041663212</v>
@@ -1727,7 +1730,7 @@
         <v>1</v>
       </c>
       <c r="P3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1741,7 +1744,7 @@
         <v>2.746397091058633</v>
       </c>
       <c r="D4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E4">
         <v>2.648930323263125</v>
@@ -1791,7 +1794,7 @@
         <v>2.683209227271539</v>
       </c>
       <c r="D5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E5">
         <v>2.583545744375049</v>
@@ -1827,7 +1830,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -1841,7 +1844,7 @@
         <v>2.555958070922727</v>
       </c>
       <c r="D6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E6">
         <v>2.632522016358742</v>
@@ -1877,7 +1880,7 @@
         <v>1</v>
       </c>
       <c r="P6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -1891,7 +1894,7 @@
         <v>2.641252819939413</v>
       </c>
       <c r="D7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E7">
         <v>2.540130729835057</v>
@@ -1927,7 +1930,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -1941,7 +1944,7 @@
         <v>2.512285655110759</v>
       </c>
       <c r="D8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E8">
         <v>2.590994611146576</v>
@@ -1977,7 +1980,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -1991,7 +1994,7 @@
         <v>2.615441102246784</v>
       </c>
       <c r="D9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E9">
         <v>2.513421672263544</v>
@@ -2027,7 +2030,7 @@
         <v>1</v>
       </c>
       <c r="P9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -2041,7 +2044,7 @@
         <v>2.515418243442972</v>
       </c>
       <c r="D10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E10">
         <v>2.545423958143926</v>
@@ -2077,7 +2080,7 @@
         <v>1</v>
       </c>
       <c r="P10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -2091,7 +2094,7 @@
         <v>2.487273994427867</v>
       </c>
       <c r="D11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E11">
         <v>2.567211421027677</v>
@@ -2127,7 +2130,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -2141,7 +2144,7 @@
         <v>2.487984580081365</v>
       </c>
       <c r="D12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E12">
         <v>2.579898802553291</v>
@@ -2177,7 +2180,7 @@
         <v>1</v>
       </c>
       <c r="P12" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -2191,7 +2194,7 @@
         <v>2.500805561667341</v>
       </c>
       <c r="D13" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E13">
         <v>2.59216563562278</v>
@@ -2227,7 +2230,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -2241,7 +2244,7 @@
         <v>2.499441989042522</v>
       </c>
       <c r="D14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E14">
         <v>2.736702547602069</v>
@@ -2291,7 +2294,7 @@
         <v>2.512520850741042</v>
       </c>
       <c r="D15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E15">
         <v>2.749061943431123</v>
@@ -2327,7 +2330,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -2341,7 +2344,7 @@
         <v>2.77984350091858</v>
       </c>
       <c r="D16" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E16">
         <v>2.889061943431122</v>
@@ -2377,7 +2380,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -2391,7 +2394,7 @@
         <v>2.517224153471577</v>
       </c>
       <c r="D17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E17">
         <v>2.753506518310076</v>
@@ -2427,7 +2430,7 @@
         <v>1</v>
       </c>
       <c r="P17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -2441,7 +2444,7 @@
         <v>2.784426680003737</v>
       </c>
       <c r="D18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E18">
         <v>2.924119959439183</v>
@@ -2477,7 +2480,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -2491,7 +2494,7 @@
         <v>2.884280694854824</v>
       </c>
       <c r="D19" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E19">
         <v>2.961861794886389</v>
@@ -2541,7 +2544,7 @@
         <v>2.920719956495094</v>
       </c>
       <c r="D20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E20">
         <v>2.907075620138133</v>
@@ -2577,7 +2580,7 @@
         <v>1</v>
       </c>
       <c r="P20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -2591,7 +2594,7 @@
         <v>2.648180125005333</v>
       </c>
       <c r="D21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E21">
         <v>2.848908919700521</v>
@@ -2627,7 +2630,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -2677,7 +2680,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -2691,7 +2694,7 @@
         <v>2.691620213913162</v>
       </c>
       <c r="D23" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E23">
         <v>2.889959376998489</v>
@@ -2727,7 +2730,7 @@
         <v>1</v>
       </c>
       <c r="P23" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -2741,7 +2744,7 @@
         <v>2.984719616116966</v>
       </c>
       <c r="D24" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E24">
         <v>2.755965243802971</v>
@@ -2777,7 +2780,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -2791,7 +2794,7 @@
         <v>3.007275184023352</v>
       </c>
       <c r="D25" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E25">
         <v>2.755965243802971</v>
@@ -2827,7 +2830,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -2841,7 +2844,7 @@
         <v>2.683495528297218</v>
       </c>
       <c r="D26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E26">
         <v>2.882281628901694</v>
@@ -2877,7 +2880,7 @@
         <v>1</v>
       </c>
       <c r="P26" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -2891,7 +2894,7 @@
         <v>2.976914171586129</v>
       </c>
       <c r="D27" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E27">
         <v>2.747824596132772</v>
@@ -2927,7 +2930,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -2941,7 +2944,7 @@
         <v>2.647048085674867</v>
       </c>
       <c r="D28" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E28">
         <v>2.84783915365346</v>
@@ -2977,7 +2980,7 @@
         <v>1</v>
       </c>
       <c r="P28" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -2991,7 +2994,7 @@
         <v>2.941898848516719</v>
       </c>
       <c r="D29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E29">
         <v>2.711305547532774</v>
@@ -3027,7 +3030,7 @@
         <v>1</v>
       </c>
       <c r="P29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -3041,7 +3044,7 @@
         <v>2.962790623816959</v>
       </c>
       <c r="D30" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E30">
         <v>2.711305547532774</v>
@@ -3077,7 +3080,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -3091,7 +3094,7 @@
         <v>2.636850318680218</v>
       </c>
       <c r="D31" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E31">
         <v>2.674077933106496</v>
@@ -3127,7 +3130,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -3141,7 +3144,7 @@
         <v>2.64386308474694</v>
       </c>
       <c r="D32" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E32">
         <v>2.844829359063415</v>
@@ -3177,7 +3180,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -3191,7 +3194,7 @@
         <v>2.938838994972993</v>
       </c>
       <c r="D33" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E33">
         <v>2.708114289235636</v>
@@ -3227,7 +3230,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -3241,7 +3244,7 @@
         <v>2.959611880258242</v>
       </c>
       <c r="D34" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E34">
         <v>2.708114289235636</v>
@@ -3277,7 +3280,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -3291,7 +3294,7 @@
         <v>2.63362151616782</v>
       </c>
       <c r="D35" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E35">
         <v>2.706375129633912</v>
@@ -3327,7 +3330,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -3341,7 +3344,7 @@
         <v>2.623711665472045</v>
       </c>
       <c r="D36" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E36">
         <v>2.825786465799713</v>
@@ -3377,7 +3380,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -3391,7 +3394,7 @@
         <v>2.919479379991807</v>
       </c>
       <c r="D37" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E37">
         <v>2.687923279746057</v>
@@ -3427,7 +3430,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -3441,7 +3444,7 @@
         <v>2.939500051198033</v>
       </c>
       <c r="D38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E38">
         <v>2.687923279746057</v>
@@ -3477,7 +3480,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39" spans="1:16">
@@ -3491,7 +3494,7 @@
         <v>2.613192965390128</v>
       </c>
       <c r="D39" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E39">
         <v>2.65740457966414</v>
@@ -3527,7 +3530,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -3541,7 +3544,7 @@
         <v>2.866121269202039</v>
       </c>
       <c r="D40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E40">
         <v>2.632273716345684</v>
@@ -3591,7 +3594,7 @@
         <v>2.884068721379623</v>
       </c>
       <c r="D41" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E41">
         <v>2.632273716345684</v>
@@ -3641,7 +3644,7 @@
         <v>2.556888701243869</v>
       </c>
       <c r="D42" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E42">
         <v>2.5709911987269</v>
@@ -3691,7 +3694,7 @@
         <v>2.84066903268222</v>
       </c>
       <c r="D43" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E43">
         <v>2.605728438993726</v>
@@ -3727,7 +3730,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -3741,7 +3744,7 @@
         <v>2.857627543154535</v>
       </c>
       <c r="D44" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E44">
         <v>2.605728438993726</v>
@@ -3777,7 +3780,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -3791,7 +3794,7 @@
         <v>2.530031126511299</v>
       </c>
       <c r="D45" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E45">
         <v>2.536232918189681</v>
@@ -3827,7 +3830,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -3841,7 +3844,7 @@
         <v>2.794653597980052</v>
       </c>
       <c r="D46" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E46">
         <v>2.557736881328888</v>
@@ -3877,7 +3880,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -3891,7 +3894,7 @@
         <v>2.809824187676618</v>
       </c>
       <c r="D47" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E47">
         <v>2.557736881328888</v>
@@ -3927,7 +3930,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -3977,7 +3980,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -3991,7 +3994,7 @@
         <v>2.877968395292299</v>
       </c>
       <c r="D49" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E49">
         <v>2.644629614722029</v>
@@ -4027,7 +4030,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -4041,7 +4044,7 @@
         <v>2.896376165252531</v>
       </c>
       <c r="D50" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E50">
         <v>2.644629614722029</v>
@@ -4077,7 +4080,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -4091,7 +4094,7 @@
         <v>2.521770137334771</v>
       </c>
       <c r="D51" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E51">
         <v>2.535896862069519</v>
@@ -4127,7 +4130,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -4141,7 +4144,7 @@
         <v>2.934431839092635</v>
       </c>
       <c r="D52" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E52">
         <v>2.703517868992319</v>
@@ -4177,7 +4180,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -4191,7 +4194,7 @@
         <v>2.955033485192349</v>
       </c>
       <c r="D53" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E53">
         <v>2.703517868992319</v>
@@ -4227,7 +4230,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -4277,7 +4280,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -4291,7 +4294,7 @@
         <v>2.974730272968942</v>
       </c>
       <c r="D55" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E55">
         <v>2.745546910458406</v>
@@ -4327,7 +4330,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -4341,7 +4344,7 @@
         <v>2.996897706887981</v>
       </c>
       <c r="D56" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E56">
         <v>2.745546910458406</v>
@@ -4377,7 +4380,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -4391,7 +4394,7 @@
         <v>2.624468326525319</v>
       </c>
       <c r="D57" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E57">
         <v>2.660688149733082</v>
@@ -4427,7 +4430,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -4441,7 +4444,7 @@
         <v>3.056805462611843</v>
       </c>
       <c r="D58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E58">
         <v>2.831146801497014</v>
@@ -4477,7 +4480,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -4527,7 +4530,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -4541,7 +4544,7 @@
         <v>3.075488420323122</v>
       </c>
       <c r="D60" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E60">
         <v>2.850632094815525</v>
@@ -4591,7 +4594,7 @@
         <v>2.73140795531227</v>
       </c>
       <c r="D61" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E61">
         <v>2.75953055997749</v>
@@ -4641,7 +4644,7 @@
         <v>2.72765316464271</v>
       </c>
       <c r="D62" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E62">
         <v>2.75953055997749</v>
@@ -4691,7 +4694,7 @@
         <v>2.72671446697532</v>
       </c>
       <c r="D63" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E63">
         <v>2.75953055997749</v>
@@ -4741,7 +4744,7 @@
         <v>6.293149296554828</v>
       </c>
       <c r="D64" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E64">
         <v>5.963700498102364</v>
@@ -4777,7 +4780,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -4791,7 +4794,7 @@
         <v>6.420239880180696</v>
       </c>
       <c r="D65" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E65">
         <v>6.082402264327184</v>
@@ -4827,7 +4830,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -4841,7 +4844,7 @@
         <v>6.609514294497387</v>
       </c>
       <c r="D66" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E66">
         <v>6.259183317962906</v>
@@ -4877,7 +4880,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -4891,7 +4894,7 @@
         <v>6.515171551263329</v>
       </c>
       <c r="D67" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E67">
         <v>6.612047937164794</v>
@@ -4927,7 +4930,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -4941,7 +4944,7 @@
         <v>6.520829737768901</v>
       </c>
       <c r="D68" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E68">
         <v>6.612047937164794</v>
@@ -4977,7 +4980,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -5027,7 +5030,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -5077,7 +5080,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -5127,7 +5130,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -5141,7 +5144,7 @@
         <v>6.781478804637512</v>
       </c>
       <c r="D72" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E72">
         <v>6.821616798629249</v>
@@ -5177,7 +5180,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -5191,7 +5194,7 @@
         <v>6.927933775178332</v>
       </c>
       <c r="D73" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E73">
         <v>7.025464228815041</v>
@@ -5227,7 +5230,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -5241,7 +5244,7 @@
         <v>7.465293617228137</v>
       </c>
       <c r="D74" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E74">
         <v>7.441132824526438</v>
@@ -5277,7 +5280,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -5291,7 +5294,7 @@
         <v>2.399740228983164</v>
       </c>
       <c r="D75" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E75">
         <v>2.284756328614283</v>
@@ -5327,7 +5330,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -5341,7 +5344,7 @@
         <v>2.181146111927123</v>
       </c>
       <c r="D76" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E76">
         <v>2.105842395854763</v>
@@ -5377,7 +5380,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -5391,7 +5394,7 @@
         <v>2.180858495485883</v>
       </c>
       <c r="D77" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E77">
         <v>2.105842395854763</v>
@@ -5427,7 +5430,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -5441,7 +5444,7 @@
         <v>2.355267416838251</v>
       </c>
       <c r="D78" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E78">
         <v>2.241615480893012</v>
@@ -5477,7 +5480,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -5491,7 +5494,7 @@
         <v>2.138079262229388</v>
       </c>
       <c r="D79" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E79">
         <v>2.115876072829124</v>
@@ -5527,7 +5530,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -5541,7 +5544,7 @@
         <v>2.136977667529256</v>
       </c>
       <c r="D80" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E80">
         <v>2.115876072829124</v>
@@ -5577,7 +5580,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -5627,7 +5630,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -5677,7 +5680,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -5727,7 +5730,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -5741,7 +5744,7 @@
         <v>1.925553832103902</v>
       </c>
       <c r="D84" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E84">
         <v>1.985821650998686</v>
@@ -5777,7 +5780,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -5827,7 +5830,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -5841,7 +5844,7 @@
         <v>1.87975631937778</v>
       </c>
       <c r="D86" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E86">
         <v>2.025900250164519</v>
@@ -5877,7 +5880,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -5977,7 +5980,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -5991,7 +5994,7 @@
         <v>1.789383875507923</v>
       </c>
       <c r="D89" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E89">
         <v>1.940268655809146</v>
@@ -6027,7 +6030,7 @@
         <v>1</v>
       </c>
       <c r="P89" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="90" spans="1:16">
@@ -6041,7 +6044,7 @@
         <v>1.804905667333501</v>
       </c>
       <c r="D90" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E90">
         <v>1.95497618970289</v>
@@ -6077,7 +6080,7 @@
         <v>1</v>
       </c>
       <c r="P90" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="91" spans="1:16">
@@ -6091,7 +6094,7 @@
         <v>1.809491967335235</v>
       </c>
       <c r="D91" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E91">
         <v>1.959321896917648</v>
@@ -6127,7 +6130,7 @@
         <v>1</v>
       </c>
       <c r="P91" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="92" spans="1:16">
@@ -6141,7 +6144,7 @@
         <v>1.822908408572121</v>
       </c>
       <c r="D92" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E92">
         <v>1.972034524843747</v>
@@ -6177,7 +6180,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -6191,7 +6194,7 @@
         <v>2.011491451443282</v>
       </c>
       <c r="D93" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E93">
         <v>1.930405304642352</v>
@@ -6227,7 +6230,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -6241,7 +6244,7 @@
         <v>1.820166348365971</v>
       </c>
       <c r="D94" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E94">
         <v>1.969436310418903</v>
@@ -6277,7 +6280,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -6291,7 +6294,7 @@
         <v>2.008879751476441</v>
       </c>
       <c r="D95" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E95">
         <v>1.927766633591516</v>
@@ -6327,7 +6330,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -6341,7 +6344,7 @@
         <v>1.780154910291897</v>
       </c>
       <c r="D96" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E96">
         <v>1.931523833030682</v>
@@ -6377,7 +6380,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -6427,7 +6430,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -6441,7 +6444,7 @@
         <v>1.781411528733962</v>
       </c>
       <c r="D98" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E98">
         <v>1.932714530505294</v>
@@ -6477,7 +6480,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -6527,7 +6530,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -6541,7 +6544,7 @@
         <v>1.786869994736246</v>
       </c>
       <c r="D100" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E100">
         <v>1.937886650750082</v>
@@ -6591,7 +6594,7 @@
         <v>1.77389224303264</v>
       </c>
       <c r="D101" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E101">
         <v>1.925589699135846</v>
@@ -6627,7 +6630,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -6641,7 +6644,7 @@
         <v>1.764225388294109</v>
       </c>
       <c r="D102" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E102">
         <v>1.916429958088516</v>
@@ -6841,7 +6844,7 @@
         <v>2.039049007419374</v>
       </c>
       <c r="D106" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E106">
         <v>1.958247448115615</v>
@@ -6877,7 +6880,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -6891,7 +6894,7 @@
         <v>1.963804213639886</v>
       </c>
       <c r="D107" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E107">
         <v>2.044635472991321</v>
@@ -6927,7 +6930,7 @@
         <v>1</v>
       </c>
       <c r="P107" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -6941,7 +6944,7 @@
         <v>2.084469221121035</v>
       </c>
       <c r="D108" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E108">
         <v>2.00413671738046</v>
@@ -6977,7 +6980,7 @@
         <v>1</v>
       </c>
       <c r="P108" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -6991,7 +6994,7 @@
         <v>1.970692549466935</v>
       </c>
       <c r="D109" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E109">
         <v>2.103970465510173</v>
@@ -7027,7 +7030,7 @@
         <v>1</v>
       </c>
       <c r="P109" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -7077,7 +7080,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -7091,7 +7094,7 @@
         <v>1.989826166099606</v>
       </c>
       <c r="D111" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E111">
         <v>2.069999197311251</v>
@@ -7127,7 +7130,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -7141,7 +7144,7 @@
         <v>1.996538974422711</v>
       </c>
       <c r="D112" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E112">
         <v>2.129860772341935</v>
@@ -7177,7 +7180,7 @@
         <v>1</v>
       </c>
       <c r="P112" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -7227,7 +7230,7 @@
         <v>1</v>
       </c>
       <c r="P113" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -7241,7 +7244,7 @@
         <v>1.976959483296697</v>
       </c>
       <c r="D114" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E114">
         <v>2.110248039295503</v>
@@ -7341,7 +7344,7 @@
         <v>1.920546112528168</v>
       </c>
       <c r="D116" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E116">
         <v>2.053738890308352</v>
@@ -7377,7 +7380,7 @@
         <v>1</v>
       </c>
       <c r="P116" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -7427,7 +7430,7 @@
         <v>1</v>
       </c>
       <c r="P117" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -7441,7 +7444,7 @@
         <v>2.078859445890371</v>
       </c>
       <c r="D118" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E118">
         <v>2.128859445890371</v>
@@ -7477,7 +7480,7 @@
         <v>1</v>
       </c>
       <c r="P118" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -7491,7 +7494,7 @@
         <v>1.864471846503076</v>
       </c>
       <c r="D119" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E119">
         <v>1.997569421794252</v>
@@ -7527,7 +7530,7 @@
         <v>1</v>
       </c>
       <c r="P119" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -7577,7 +7580,7 @@
         <v>1</v>
       </c>
       <c r="P120" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -7627,7 +7630,7 @@
         <v>1</v>
       </c>
       <c r="P121" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -7641,7 +7644,7 @@
         <v>1.863420505387863</v>
       </c>
       <c r="D122" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E122">
         <v>1.996516295719591</v>
@@ -7741,7 +7744,7 @@
         <v>2.029857360363785</v>
       </c>
       <c r="D124" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E124">
         <v>2.011995247378231</v>
@@ -7791,7 +7794,7 @@
         <v>1.892165706973767</v>
       </c>
       <c r="D125" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E125">
         <v>2.025310300703773</v>
@@ -7827,7 +7830,7 @@
         <v>1</v>
       </c>
       <c r="P125" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -7877,7 +7880,7 @@
         <v>1</v>
       </c>
       <c r="P126" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -7927,7 +7930,7 @@
         <v>1</v>
       </c>
       <c r="P127" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -7991,7 +7994,7 @@
         <v>2.183293967129219</v>
       </c>
       <c r="D129" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E129">
         <v>2.097698061214447</v>
@@ -8041,7 +8044,7 @@
         <v>2.10409703769314</v>
       </c>
       <c r="D130" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E130">
         <v>2.097698061214447</v>
@@ -8127,7 +8130,7 @@
         <v>1</v>
       </c>
       <c r="P131" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -8177,7 +8180,7 @@
         <v>1</v>
       </c>
       <c r="P132" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -8227,7 +8230,7 @@
         <v>1</v>
       </c>
       <c r="P133" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -8277,7 +8280,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -8327,7 +8330,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -8377,7 +8380,7 @@
         <v>1</v>
       </c>
       <c r="P136" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -8427,7 +8430,7 @@
         <v>1</v>
       </c>
       <c r="P137" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -8477,7 +8480,7 @@
         <v>1</v>
       </c>
       <c r="P138" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -8491,7 +8494,7 @@
         <v>2.367284598691813</v>
       </c>
       <c r="D139" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E139">
         <v>2.284677125480481</v>
@@ -8541,7 +8544,7 @@
         <v>2.308705785003503</v>
       </c>
       <c r="D140" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E140">
         <v>2.284677125480481</v>
@@ -8677,7 +8680,7 @@
         <v>1</v>
       </c>
       <c r="P142" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -8727,7 +8730,7 @@
         <v>1</v>
       </c>
       <c r="P143" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -8777,7 +8780,7 @@
         <v>1</v>
       </c>
       <c r="P144" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -8827,7 +8830,7 @@
         <v>1</v>
       </c>
       <c r="P145" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -8877,7 +8880,7 @@
         <v>1</v>
       </c>
       <c r="P146" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -8941,7 +8944,7 @@
         <v>2.673055621612132</v>
       </c>
       <c r="D148" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E148">
         <v>2.649383477311975</v>
@@ -8991,7 +8994,7 @@
         <v>2.694510447967022</v>
       </c>
       <c r="D149" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E149">
         <v>2.66746656530884</v>
@@ -9041,7 +9044,7 @@
         <v>2.61961842602696</v>
       </c>
       <c r="D150" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E150">
         <v>2.674946565009619</v>
@@ -9327,7 +9330,7 @@
         <v>1</v>
       </c>
       <c r="P155" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -9341,7 +9344,7 @@
         <v>2.746485076848839</v>
       </c>
       <c r="D156" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E156">
         <v>2.847982602490786</v>
@@ -9377,7 +9380,7 @@
         <v>1</v>
       </c>
       <c r="P156" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -9441,7 +9444,7 @@
         <v>2.750734210259811</v>
       </c>
       <c r="D158" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E158">
         <v>2.800734210259812</v>
@@ -9477,7 +9480,7 @@
         <v>1</v>
       </c>
       <c r="P158" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -9541,7 +9544,7 @@
         <v>2.717092536535202</v>
       </c>
       <c r="D160" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E160">
         <v>2.791717770085309</v>
@@ -9627,7 +9630,7 @@
         <v>1</v>
       </c>
       <c r="P161" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -9641,7 +9644,7 @@
         <v>2.669840281895235</v>
       </c>
       <c r="D162" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E162">
         <v>2.754805459723328</v>
@@ -9677,7 +9680,7 @@
         <v>1</v>
       </c>
       <c r="P162" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -9741,7 +9744,7 @@
         <v>2.704152220032186</v>
       </c>
       <c r="D164" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E164">
         <v>2.721608307945189</v>
@@ -9791,7 +9794,7 @@
         <v>0.7516342779874527</v>
       </c>
       <c r="D165" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E165">
         <v>0.6447312303040151</v>
@@ -9827,7 +9830,7 @@
         <v>1</v>
       </c>
       <c r="P165" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -9841,7 +9844,7 @@
         <v>0.6347312303040145</v>
       </c>
       <c r="D166" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E166">
         <v>0.7803954970608276</v>
@@ -9877,7 +9880,7 @@
         <v>1</v>
       </c>
       <c r="P166" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -9891,7 +9894,7 @@
         <v>0.7872985447442655</v>
       </c>
       <c r="D167" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E167">
         <v>0.6685373256708909</v>
@@ -9927,7 +9930,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -9941,7 +9944,7 @@
         <v>0.6141118398407031</v>
       </c>
       <c r="D168" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E168">
         <v>0.7042015924277036</v>
@@ -9977,7 +9980,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -9991,7 +9994,7 @@
         <v>0.7076194190074974</v>
       </c>
       <c r="D169" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E169">
         <v>0.8524403513495589</v>
@@ -10041,7 +10044,7 @@
         <v>0.8587410173081755</v>
       </c>
       <c r="D170" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E170">
         <v>0.7402207509247285</v>
@@ -10091,7 +10094,7 @@
         <v>0.6868795521992208</v>
       </c>
       <c r="D171" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E171">
         <v>0.7750416832667906</v>
@@ -10141,7 +10144,7 @@
         <v>0.794311018129779</v>
       </c>
       <c r="D172" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E172">
         <v>0.9381289071762104</v>
@@ -10177,7 +10180,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -10191,7 +10194,7 @@
         <v>0.7478436529603893</v>
       </c>
       <c r="D173" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E173">
         <v>0.9381289071762104</v>
@@ -10227,7 +10230,7 @@
         <v>1</v>
       </c>
       <c r="P173" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -10241,7 +10244,7 @@
         <v>0.9437131136379486</v>
       </c>
       <c r="D174" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E174">
         <v>0.8254794310532532</v>
@@ -10277,7 +10280,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -10291,7 +10294,7 @@
         <v>0.7734278594221262</v>
       </c>
       <c r="D175" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E175">
         <v>0.8592973200996861</v>
@@ -10327,7 +10330,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -10341,7 +10344,7 @@
         <v>0.9016190641047892</v>
       </c>
       <c r="D176" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E176">
         <v>1.04419537245399</v>
@@ -10377,7 +10380,7 @@
         <v>1</v>
       </c>
       <c r="P176" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -10391,7 +10394,7 @@
         <v>0.8558611736195321</v>
       </c>
       <c r="D177" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E177">
         <v>1.04419537245399</v>
@@ -10427,7 +10430,7 @@
         <v>1</v>
       </c>
       <c r="P177" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -10441,7 +10444,7 @@
         <v>1.048892735560562</v>
       </c>
       <c r="D178" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E178">
         <v>0.9310137903179339</v>
@@ -10477,7 +10480,7 @@
         <v>1</v>
       </c>
       <c r="P178" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -10491,7 +10494,7 @@
         <v>0.8805585367261042</v>
       </c>
       <c r="D179" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E179">
         <v>0.963590098667134</v>
@@ -10527,7 +10530,7 @@
         <v>1</v>
       </c>
       <c r="P179" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -10541,7 +10544,7 @@
         <v>1.076170489586433</v>
       </c>
       <c r="D180" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E180">
         <v>1.260525374010979</v>
@@ -10591,7 +10594,7 @@
         <v>1.26341395784032</v>
       </c>
       <c r="D181" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E181">
         <v>1.146258524308584</v>
@@ -10641,7 +10644,7 @@
         <v>1.099059073415773</v>
       </c>
       <c r="D182" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E182">
         <v>1.176302541669659</v>
@@ -10691,7 +10694,7 @@
         <v>1.931268098407571</v>
       </c>
       <c r="D183" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E183">
         <v>1.946759727730396</v>
@@ -10727,7 +10730,7 @@
         <v>1</v>
       </c>
       <c r="P183" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -10777,7 +10780,7 @@
         <v>1</v>
       </c>
       <c r="P184" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -10827,7 +10830,7 @@
         <v>1</v>
       </c>
       <c r="P185" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -10841,7 +10844,7 @@
         <v>0.5942088493584849</v>
       </c>
       <c r="D186" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E186">
         <v>0.5982130518354056</v>
@@ -10877,7 +10880,7 @@
         <v>1</v>
       </c>
       <c r="P186" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -10927,7 +10930,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -10977,7 +10980,7 @@
         <v>1</v>
       </c>
       <c r="P188" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -11027,7 +11030,7 @@
         <v>1</v>
       </c>
       <c r="P189" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -11041,7 +11044,7 @@
         <v>-0.02499489055226256</v>
       </c>
       <c r="D190" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E190">
         <v>-0.07499489055226238</v>
@@ -11077,7 +11080,7 @@
         <v>1</v>
       </c>
       <c r="P190" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -11091,7 +11094,7 @@
         <v>-0.04541693580813089</v>
       </c>
       <c r="D191" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E191">
         <v>-0.1350880582477796</v>
@@ -11127,7 +11130,7 @@
         <v>1</v>
       </c>
       <c r="P191" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -11177,7 +11180,7 @@
         <v>1</v>
       </c>
       <c r="P192" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -11227,7 +11230,7 @@
         <v>1</v>
       </c>
       <c r="P193" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -11377,7 +11380,7 @@
         <v>1</v>
       </c>
       <c r="P196" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="197" spans="1:16">
@@ -11391,7 +11394,7 @@
         <v>-0.5154661476950757</v>
       </c>
       <c r="D197" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E197">
         <v>-0.4838284745942198</v>
@@ -11427,7 +11430,7 @@
         <v>1</v>
       </c>
       <c r="P197" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -11441,7 +11444,7 @@
         <v>-0.5144835438345625</v>
       </c>
       <c r="D198" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E198">
         <v>-0.4838284745942198</v>
@@ -11477,7 +11480,7 @@
         <v>1</v>
       </c>
       <c r="P198" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -11527,7 +11530,7 @@
         <v>1</v>
       </c>
       <c r="P199" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -11541,7 +11544,7 @@
         <v>-0.6795603356321358</v>
       </c>
       <c r="D200" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E200">
         <v>-0.6353746161347429</v>
@@ -11577,7 +11580,7 @@
         <v>1</v>
       </c>
       <c r="P200" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -11591,7 +11594,7 @@
         <v>-0.6770489039336995</v>
       </c>
       <c r="D201" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E201">
         <v>-0.6353746161347429</v>
@@ -11627,7 +11630,7 @@
         <v>1</v>
       </c>
       <c r="P201" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -11677,7 +11680,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -11691,7 +11694,7 @@
         <v>-1.275160705635463</v>
       </c>
       <c r="D203" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E203">
         <v>-0.9575450227817477</v>
@@ -11727,7 +11730,7 @@
         <v>1</v>
       </c>
       <c r="P203" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -11741,7 +11744,7 @@
         <v>-1.267100202166811</v>
       </c>
       <c r="D204" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E204">
         <v>-0.9575450227817477</v>
@@ -11777,7 +11780,7 @@
         <v>1</v>
       </c>
       <c r="P204" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -11841,7 +11844,7 @@
         <v>-1.30354206111917</v>
       </c>
       <c r="D206" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E206">
         <v>-0.9846924062879019</v>
@@ -11891,7 +11894,7 @@
         <v>-1.295217135083899</v>
       </c>
       <c r="D207" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E207">
         <v>-0.9846924062879019</v>
@@ -11941,7 +11944,7 @@
         <v>-1.315601110783377</v>
       </c>
       <c r="D208" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E208">
         <v>-0.9962271494449686</v>
@@ -11991,7 +11994,7 @@
         <v>-1.307163833353718</v>
       </c>
       <c r="D209" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E209">
         <v>-0.9962271494449686</v>
@@ -12041,7 +12044,7 @@
         <v>-1.303470101275702</v>
       </c>
       <c r="D210" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E210">
         <v>-0.9846235751332797</v>
@@ -12077,7 +12080,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="211" spans="1:16">
@@ -12091,7 +12094,7 @@
         <v>-1.295145845673754</v>
       </c>
       <c r="D211" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E211">
         <v>-0.9846235751332797</v>
@@ -12127,7 +12130,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="212" spans="1:16">
@@ -12141,7 +12144,7 @@
         <v>-1.352240812118975</v>
       </c>
       <c r="D212" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E212">
         <v>-1.031273820287715</v>
@@ -12177,7 +12180,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="213" spans="1:16">
@@ -12191,7 +12194,7 @@
         <v>-1.343462171012276</v>
       </c>
       <c r="D213" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E213">
         <v>-1.031273820287715</v>
@@ -12227,7 +12230,7 @@
         <v>1</v>
       </c>
       <c r="P213" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="214" spans="1:16">
@@ -12277,7 +12280,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="215" spans="1:16">
@@ -12291,7 +12294,7 @@
         <v>-1.277973836666044</v>
       </c>
       <c r="D215" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E215">
         <v>-0.9602358437675207</v>
@@ -12341,7 +12344,7 @@
         <v>-1.269887123902075</v>
       </c>
       <c r="D216" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E216">
         <v>-0.9602358437675207</v>
@@ -12391,7 +12394,7 @@
         <v>-1.030235843767521</v>
       </c>
       <c r="D217" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E217">
         <v>-1.080019061857596</v>
@@ -12441,7 +12444,7 @@
         <v>-1.007888992711643</v>
       </c>
       <c r="D218" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E218">
         <v>-1.080019061857596</v>
@@ -12491,7 +12494,7 @@
         <v>-1.154349245698821</v>
       </c>
       <c r="D219" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E219">
         <v>-0.8419862350162637</v>
@@ -12541,7 +12544,7 @@
         <v>-1.147414314838273</v>
       </c>
       <c r="D220" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E220">
         <v>-0.8419862350162637</v>
@@ -12691,7 +12694,7 @@
         <v>-0.9332125637434627</v>
       </c>
       <c r="D223" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E223">
         <v>-0.6304641914067899</v>
@@ -12727,7 +12730,7 @@
         <v>1</v>
       </c>
       <c r="P223" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="224" spans="1:16">
@@ -12741,7 +12744,7 @@
         <v>-0.9283379125284608</v>
       </c>
       <c r="D224" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E224">
         <v>-0.6304641914067899</v>
@@ -12777,7 +12780,7 @@
         <v>1</v>
       </c>
       <c r="P224" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="225" spans="1:16">
@@ -12791,7 +12794,7 @@
         <v>-1.078298911794628</v>
       </c>
       <c r="D225" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E225">
         <v>-0.7337942740491279</v>
@@ -12841,7 +12844,7 @@
         <v>-1.284045732215318</v>
       </c>
       <c r="D226" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E226">
         <v>-0.9315166474955321</v>
@@ -12891,7 +12894,7 @@
         <v>-1.074552792811861</v>
       </c>
       <c r="D227" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E227">
         <v>-0.7301942595508679</v>
@@ -12927,7 +12930,7 @@
         <v>1</v>
       </c>
       <c r="P227" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="228" spans="1:16">
@@ -12941,7 +12944,7 @@
         <v>0.6306184682796347</v>
       </c>
       <c r="D228" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E228">
         <v>0.8825890610024754</v>
@@ -12977,7 +12980,7 @@
         <v>1</v>
       </c>
       <c r="P228" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="229" spans="1:16">
@@ -12991,7 +12994,7 @@
         <v>2.500083924851446</v>
       </c>
       <c r="D229" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E229">
         <v>2.721828222716436</v>
@@ -13027,7 +13030,7 @@
         <v>1</v>
       </c>
       <c r="P229" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="230" spans="1:16">
@@ -13041,7 +13044,7 @@
         <v>2.484743417251086</v>
       </c>
       <c r="D230" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E230">
         <v>2.721828222716436</v>
@@ -13077,7 +13080,7 @@
         <v>1</v>
       </c>
       <c r="P230" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -13091,7 +13094,7 @@
         <v>2.959498476516616</v>
       </c>
       <c r="D231" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E231">
         <v>3.019498476516616</v>
@@ -13127,7 +13130,7 @@
         <v>1</v>
       </c>
       <c r="P231" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -13177,7 +13180,7 @@
         <v>1</v>
       </c>
       <c r="P232" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -13191,7 +13194,7 @@
         <v>3.973072767193392</v>
       </c>
       <c r="D233" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E233">
         <v>3.630196829293595</v>
@@ -13227,7 +13230,7 @@
         <v>1</v>
       </c>
       <c r="P233" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -13277,7 +13280,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -13327,7 +13330,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -13341,7 +13344,7 @@
         <v>4.556254256131551</v>
       </c>
       <c r="D236" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E236">
         <v>4.211276763316661</v>
@@ -13377,7 +13380,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -13427,7 +13430,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -13477,7 +13480,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -13491,7 +13494,7 @@
         <v>4.667791750685101</v>
       </c>
       <c r="D239" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E239">
         <v>4.322412320952902</v>
@@ -13527,7 +13530,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -13541,7 +13544,7 @@
         <v>4.273963746622406</v>
       </c>
       <c r="D240" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E240">
         <v>4.266274031756307</v>
@@ -13577,7 +13580,7 @@
         <v>1</v>
       </c>
       <c r="P240" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -13627,7 +13630,7 @@
         <v>1</v>
       </c>
       <c r="P241" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -13677,7 +13680,7 @@
         <v>1</v>
       </c>
       <c r="P242" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -13691,7 +13694,7 @@
         <v>3.655351043939968</v>
       </c>
       <c r="D243" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E243">
         <v>3.313620049187031</v>
@@ -13727,7 +13730,7 @@
         <v>1</v>
       </c>
       <c r="P243" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -13741,7 +13744,7 @@
         <v>2.349652973133038</v>
       </c>
       <c r="D244" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E244">
         <v>2.585321458264525</v>
@@ -13791,7 +13794,7 @@
         <v>2.337296219946928</v>
       </c>
       <c r="D245" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E245">
         <v>2.585321458264525</v>
@@ -13841,7 +13844,7 @@
         <v>2.821499834857581</v>
       </c>
       <c r="D246" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E246">
         <v>2.482773709326562</v>
@@ -13891,7 +13894,7 @@
         <v>1.399171925433256</v>
       </c>
       <c r="D247" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E247">
         <v>1.7228188215915</v>
@@ -13927,7 +13930,7 @@
         <v>1</v>
       </c>
       <c r="P247" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -13941,7 +13944,7 @@
         <v>1.94957093986026</v>
       </c>
       <c r="D248" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E248">
         <v>1.61398690043734</v>
@@ -13977,7 +13980,7 @@
         <v>1</v>
       </c>
       <c r="P248" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -13991,7 +13994,7 @@
         <v>1.388298565840941</v>
       </c>
       <c r="D249" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E249">
         <v>1.05473712956764</v>
@@ -14041,7 +14044,7 @@
         <v>1.206849236469149</v>
       </c>
       <c r="D250" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E250">
         <v>0.8739416716530437</v>
@@ -14091,7 +14094,7 @@
         <v>1.250249534396463</v>
       </c>
       <c r="D251" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E251">
         <v>0.9171855721103492</v>
@@ -14141,7 +14144,7 @@
         <v>1.265784593473219</v>
       </c>
       <c r="D252" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E252">
         <v>0.9326646489922341</v>
@@ -14177,7 +14180,7 @@
         <v>1</v>
       </c>
       <c r="P252" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -14191,7 +14194,7 @@
         <v>1.181086185990114</v>
       </c>
       <c r="D253" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E253">
         <v>0.8482714609955542</v>
@@ -14241,7 +14244,7 @@
         <v>3.393868635799184</v>
       </c>
       <c r="D254" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E254">
         <v>3.232668972857903</v>
@@ -14277,7 +14280,7 @@
         <v>1</v>
       </c>
       <c r="P254" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -14291,7 +14294,7 @@
         <v>3.344337857016143</v>
       </c>
       <c r="D255" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E255">
         <v>3.232668972857903</v>
@@ -14327,7 +14330,7 @@
         <v>1</v>
       </c>
       <c r="P255" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -14341,7 +14344,7 @@
         <v>3.108144846549583</v>
       </c>
       <c r="D256" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E256">
         <v>3.176241351782863</v>
@@ -14377,7 +14380,7 @@
         <v>1</v>
       </c>
       <c r="P256" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -14391,7 +14394,7 @@
         <v>3.110765478091183</v>
       </c>
       <c r="D257" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E257">
         <v>3.176241351782863</v>
@@ -14427,7 +14430,7 @@
         <v>1</v>
       </c>
       <c r="P257" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -14441,7 +14444,7 @@
         <v>3.484929217459694</v>
       </c>
       <c r="D258" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E258">
         <v>3.328403460479749</v>
@@ -14477,7 +14480,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -14491,7 +14494,7 @@
         <v>3.438944160440425</v>
       </c>
       <c r="D259" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E259">
         <v>3.328403460479749</v>
@@ -14527,7 +14530,7 @@
         <v>1</v>
       </c>
       <c r="P259" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -14577,7 +14580,7 @@
         <v>1</v>
       </c>
       <c r="P260" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -14627,7 +14630,7 @@
         <v>1</v>
       </c>
       <c r="P261" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -14641,7 +14644,7 @@
         <v>3.67612531160249</v>
       </c>
       <c r="D262" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E262">
         <v>3.529413159454653</v>
@@ -14677,7 +14680,7 @@
         <v>1</v>
       </c>
       <c r="P262" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -14691,7 +14694,7 @@
         <v>3.637585058248958</v>
       </c>
       <c r="D263" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E263">
         <v>3.529413159454653</v>
@@ -14727,7 +14730,7 @@
         <v>1</v>
       </c>
       <c r="P263" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -14741,7 +14744,7 @@
         <v>3.405388602484038</v>
       </c>
       <c r="D264" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E264">
         <v>3.509413159454653</v>
@@ -14777,7 +14780,7 @@
         <v>1</v>
       </c>
       <c r="P264" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -14791,7 +14794,7 @@
         <v>3.405511387337113</v>
       </c>
       <c r="D265" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E265">
         <v>3.509413159454653</v>
@@ -14827,7 +14830,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -14841,7 +14844,7 @@
         <v>3.451364045513422</v>
       </c>
       <c r="D266" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E266">
         <v>3.509413159454653</v>
@@ -14877,7 +14880,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -14891,7 +14894,7 @@
         <v>4.004636932335591</v>
       </c>
       <c r="D267" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E267">
         <v>3.867442887120403</v>
@@ -14941,7 +14944,7 @@
         <v>3.774439165379895</v>
       </c>
       <c r="D268" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E268">
         <v>3.837640654076098</v>
@@ -14991,7 +14994,7 @@
         <v>4.220199786446392</v>
       </c>
       <c r="D269" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E269">
         <v>4.085943565478028</v>
@@ -15027,7 +15030,7 @@
         <v>1</v>
       </c>
       <c r="P269" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -15041,7 +15044,7 @@
         <v>3.991103703583256</v>
       </c>
       <c r="D270" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E270">
         <v>4.0441357312043</v>
@@ -15077,7 +15080,7 @@
         <v>1</v>
       </c>
       <c r="P270" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -15091,7 +15094,7 @@
         <v>4.24807262091024</v>
       </c>
       <c r="D271" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E271">
         <v>4.172298835483293</v>
@@ -15127,7 +15130,7 @@
         <v>1</v>
       </c>
       <c r="P271" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -15141,7 +15144,7 @@
         <v>4.076733299050661</v>
       </c>
       <c r="D272" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E272">
         <v>4.185185728196767</v>
@@ -15177,7 +15180,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -15241,7 +15244,7 @@
         <v>3.853669569225198</v>
       </c>
       <c r="D274" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E274">
         <v>3.960609701897911</v>
@@ -15377,7 +15380,7 @@
         <v>1</v>
       </c>
       <c r="P276" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -15391,7 +15394,7 @@
         <v>3.457860783201086</v>
       </c>
       <c r="D277" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E277">
         <v>3.562117466477025</v>
@@ -15427,7 +15430,7 @@
         <v>1</v>
       </c>
       <c r="P277" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="278" spans="1:16">
@@ -15441,7 +15444,7 @@
         <v>3.461796612382101</v>
       </c>
       <c r="D278" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E278">
         <v>3.45818163729601</v>
@@ -15477,7 +15480,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="279" spans="1:16">
@@ -15541,7 +15544,7 @@
         <v>1.876063224574707</v>
       </c>
       <c r="D280" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E280">
         <v>1.926860456775207</v>
@@ -15591,7 +15594,7 @@
         <v>1.879462993924748</v>
       </c>
       <c r="D281" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E281">
         <v>1.926860456775207</v>
@@ -15641,7 +15644,7 @@
         <v>1.36286186891499</v>
       </c>
       <c r="D282" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E282">
         <v>1.420876924621103</v>
@@ -15677,7 +15680,7 @@
         <v>1</v>
       </c>
       <c r="P282" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -15691,7 +15694,7 @@
         <v>1.365396205962064</v>
       </c>
       <c r="D283" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E283">
         <v>1.420876924621103</v>
@@ -15727,7 +15730,7 @@
         <v>1</v>
       </c>
       <c r="P283" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="284" spans="1:16">
@@ -15741,7 +15744,7 @@
         <v>1.492587172538397</v>
       </c>
       <c r="D284" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E284">
         <v>1.422587172538397</v>
@@ -15777,7 +15780,7 @@
         <v>1</v>
       </c>
       <c r="P284" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="285" spans="1:16">
@@ -15791,7 +15794,7 @@
         <v>1.155028253713973</v>
       </c>
       <c r="D285" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E285">
         <v>1.207786135342488</v>
@@ -15841,7 +15844,7 @@
         <v>1.157212112489207</v>
       </c>
       <c r="D286" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E286">
         <v>1.207786135342488</v>
@@ -15891,7 +15894,7 @@
         <v>1.287557383512098</v>
       </c>
       <c r="D287" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E287">
         <v>1.260086513310223</v>
@@ -15941,7 +15944,7 @@
         <v>-0.2566084186298667</v>
       </c>
       <c r="D288" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E288">
         <v>-0.001048450451905936</v>
@@ -15977,7 +15980,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -15991,7 +15994,7 @@
         <v>-0.2875710874180024</v>
       </c>
       <c r="D289" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E289">
         <v>-0.001048450451905936</v>
@@ -16027,7 +16030,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16077,7 +16080,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -16127,7 +16130,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -16141,7 +16144,7 @@
         <v>-0.3429456734762377</v>
       </c>
       <c r="D292" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E292">
         <v>-0.1559309932859021</v>
@@ -16177,7 +16180,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -16191,7 +16194,7 @@
         <v>-0.452945673476238</v>
       </c>
       <c r="D293" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E293">
         <v>-0.1559309932859021</v>
@@ -16227,7 +16230,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -16241,7 +16244,7 @@
         <v>-0.07614423041516449</v>
       </c>
       <c r="D294" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E294">
         <v>-0.08649962563060054</v>
@@ -16277,7 +16280,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -16291,7 +16294,7 @@
         <v>-0.06685502084603723</v>
       </c>
       <c r="D295" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E295">
         <v>-0.08649962563060054</v>
@@ -16327,7 +16330,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -16341,7 +16344,7 @@
         <v>-0.6325763258089658</v>
       </c>
       <c r="D296" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E296">
         <v>-0.7397037652284588</v>
@@ -16377,7 +16380,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -16391,7 +16394,7 @@
         <v>-0.6888811406779016</v>
       </c>
       <c r="D297" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E297">
         <v>-0.6347573064746772</v>
@@ -16427,7 +16430,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -16441,7 +16444,7 @@
         <v>-0.5922830059527424</v>
       </c>
       <c r="D298" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E298">
         <v>-0.6988811406779014</v>
@@ -16477,7 +16480,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -16491,7 +16494,7 @@
         <v>-0.7708727781363214</v>
       </c>
       <c r="D299" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E299">
         <v>-0.7160845060282481</v>
@@ -16527,7 +16530,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -16541,7 +16544,7 @@
         <v>-0.6732115427634033</v>
       </c>
       <c r="D300" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E300">
         <v>-0.7808727781363212</v>
@@ -16577,7 +16580,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -16591,7 +16594,7 @@
         <v>-0.6051723879795468</v>
       </c>
       <c r="D301" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E301">
         <v>-0.5517269067155315</v>
@@ -16627,7 +16630,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -16641,7 +16644,7 @@
         <v>-0.509659617957122</v>
       </c>
       <c r="D302" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E302">
         <v>-0.6151723879795465</v>
@@ -16677,7 +16680,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -16691,7 +16694,7 @@
         <v>1.374867998585327</v>
       </c>
       <c r="D303" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E303">
         <v>1.61428021608427</v>
@@ -16727,7 +16730,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -16741,7 +16744,7 @@
         <v>1.37455579980999</v>
       </c>
       <c r="D304" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E304">
         <v>1.61428021608427</v>
@@ -16777,7 +16780,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -16791,7 +16794,7 @@
         <v>1.659046067002767</v>
       </c>
       <c r="D305" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E305">
         <v>1.701663141543517</v>
@@ -16827,7 +16830,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -16841,7 +16844,7 @@
         <v>1.400425101402588</v>
       </c>
       <c r="D306" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E306">
         <v>1.63789275673065</v>
@@ -16877,7 +16880,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -16891,7 +16894,7 @@
         <v>1.415426421593279</v>
       </c>
       <c r="D307" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E307">
         <v>1.63789275673065</v>
@@ -16927,7 +16930,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -16941,7 +16944,7 @@
         <v>1.672891436539961</v>
       </c>
       <c r="D308" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E308">
         <v>1.702888796158578</v>
@@ -16977,7 +16980,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -16991,7 +16994,7 @@
         <v>1.682896717302726</v>
       </c>
       <c r="D309" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E309">
         <v>1.702888796158578</v>
@@ -17027,7 +17030,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17041,7 +17044,7 @@
         <v>1.392287936404873</v>
       </c>
       <c r="D310" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E310">
         <v>1.630374723852328</v>
@@ -17077,7 +17080,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -17091,7 +17094,7 @@
         <v>1.392192134372636</v>
       </c>
       <c r="D311" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E311">
         <v>1.630374723852328</v>
@@ -17127,7 +17130,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -17141,7 +17144,7 @@
         <v>1.665398674360388</v>
       </c>
       <c r="D312" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E312">
         <v>1.367982501138595</v>
@@ -17177,7 +17180,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -17191,7 +17194,7 @@
         <v>1.67530287232815</v>
       </c>
       <c r="D313" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E313">
         <v>1.367982501138595</v>
@@ -17227,7 +17230,7 @@
         <v>1</v>
       </c>
       <c r="P313" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -17241,7 +17244,7 @@
         <v>1.683187064752997</v>
       </c>
       <c r="D314" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E314">
         <v>1.385560910531628</v>
@@ -17277,7 +17280,7 @@
         <v>1</v>
       </c>
       <c r="P314" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -17291,7 +17294,7 @@
         <v>1.693331241005988</v>
       </c>
       <c r="D315" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E315">
         <v>1.385560910531628</v>
@@ -17327,7 +17330,7 @@
         <v>1</v>
       </c>
       <c r="P315" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -17341,7 +17344,7 @@
         <v>1.671335210176903</v>
       </c>
       <c r="D316" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E316">
         <v>1.373848959803819</v>
@@ -17377,7 +17380,7 @@
         <v>1</v>
       </c>
       <c r="P316" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -17391,7 +17394,7 @@
         <v>1.68131949631757</v>
       </c>
       <c r="D317" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E317">
         <v>1.373848959803819</v>
@@ -17427,7 +17430,7 @@
         <v>1</v>
       </c>
       <c r="P317" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -17441,7 +17444,7 @@
         <v>1.693875753393727</v>
       </c>
       <c r="D318" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E318">
         <v>1.396123425781996</v>
@@ -17477,7 +17480,7 @@
         <v>1</v>
       </c>
       <c r="P318" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -17491,7 +17494,7 @@
         <v>1.704164127807133</v>
       </c>
       <c r="D319" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E319">
         <v>1.396123425781996</v>
@@ -17527,7 +17530,7 @@
         <v>1</v>
       </c>
       <c r="P319" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -17541,7 +17544,7 @@
         <v>1.366123425781996</v>
       </c>
       <c r="D320" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E320">
         <v>1.403731566187024</v>
@@ -17577,7 +17580,7 @@
         <v>1</v>
       </c>
       <c r="P320" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -17591,7 +17594,7 @@
         <v>1.710631890779994</v>
       </c>
       <c r="D321" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E321">
         <v>1.412681767280061</v>
@@ -17627,7 +17630,7 @@
         <v>1</v>
       </c>
       <c r="P321" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -17641,7 +17644,7 @@
         <v>1.72114631763706</v>
       </c>
       <c r="D322" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E322">
         <v>1.412681767280061</v>
@@ -17677,7 +17680,7 @@
         <v>1</v>
       </c>
       <c r="P322" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -17691,7 +17694,7 @@
         <v>1.382681767280062</v>
       </c>
       <c r="D323" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E323">
         <v>1.420374677351461</v>
@@ -17727,7 +17730,7 @@
         <v>1</v>
       </c>
       <c r="P323" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="324" spans="1:16">
@@ -17741,7 +17744,7 @@
         <v>1.679206240881443</v>
       </c>
       <c r="D324" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E324">
         <v>1.381627077835624</v>
@@ -17791,7 +17794,7 @@
         <v>1.689296712933807</v>
       </c>
       <c r="D325" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E325">
         <v>1.381627077835624</v>
@@ -17841,7 +17844,7 @@
         <v>1.351627077835625</v>
       </c>
       <c r="D326" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E326">
         <v>1.364138386842169</v>
@@ -17891,7 +17894,7 @@
         <v>1.662615013806636</v>
       </c>
       <c r="D327" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E327">
         <v>1.365231699984297</v>
@@ -17927,7 +17930,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -17941,7 +17944,7 @@
         <v>1.672481658175022</v>
       </c>
       <c r="D328" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E328">
         <v>1.365231699984297</v>
@@ -17977,7 +17980,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -17991,7 +17994,7 @@
         <v>1.335231699984297</v>
       </c>
       <c r="D329" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E329">
         <v>1.330198361076394</v>
@@ -18027,7 +18030,7 @@
         <v>1</v>
       </c>
       <c r="P329" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="330" spans="1:16">
@@ -18041,7 +18044,7 @@
         <v>1.638483426036899</v>
       </c>
       <c r="D330" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E330">
         <v>1.341384970754843</v>
@@ -18091,7 +18094,7 @@
         <v>1.648024517787818</v>
       </c>
       <c r="D331" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E331">
         <v>1.341384970754843</v>
@@ -18191,7 +18194,7 @@
         <v>1.611118158429232</v>
       </c>
       <c r="D333" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E333">
         <v>1.31434273328757</v>
@@ -18241,7 +18244,7 @@
         <v>1.620290072876844</v>
       </c>
       <c r="D334" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E334">
         <v>1.31434273328757</v>
@@ -18291,7 +18294,7 @@
         <v>1.210704115653037</v>
       </c>
       <c r="D335" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E335">
         <v>1.321946243981619</v>
@@ -18341,7 +18344,7 @@
         <v>1.250704115653037</v>
       </c>
       <c r="D336" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E336">
         <v>1.321946243981619</v>
@@ -18391,7 +18394,7 @@
         <v>1.580824889600507</v>
       </c>
       <c r="D337" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E337">
         <v>1.284407057851428</v>
@@ -18427,7 +18430,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -18441,7 +18444,7 @@
         <v>1.589588125885168</v>
       </c>
       <c r="D338" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E338">
         <v>1.284407057851428</v>
@@ -18477,7 +18480,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -18491,7 +18494,7 @@
         <v>1.180206507742837</v>
       </c>
       <c r="D339" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E339">
         <v>1.27675246238701</v>
@@ -18527,7 +18530,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -18541,7 +18544,7 @@
         <v>1.220206507742837</v>
       </c>
       <c r="D340" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E340">
         <v>1.27675246238701</v>
@@ -18577,7 +18580,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -18591,7 +18594,7 @@
         <v>1.680056540073359</v>
       </c>
       <c r="D341" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E341">
         <v>1.409353064352823</v>
@@ -18627,7 +18630,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -18641,7 +18644,7 @@
         <v>1.717732409003494</v>
       </c>
       <c r="D342" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E342">
         <v>1.409353064352823</v>
@@ -18677,7 +18680,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -18691,7 +18694,7 @@
         <v>1.307497917096648</v>
       </c>
       <c r="D343" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E343">
         <v>1.444235818399402</v>
@@ -18727,7 +18730,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -18741,7 +18744,7 @@
         <v>1.347497917096648</v>
       </c>
       <c r="D344" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E344">
         <v>1.444235818399402</v>
@@ -18777,7 +18780,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -18791,7 +18794,7 @@
         <v>1.842256392262994</v>
       </c>
       <c r="D345" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E345">
         <v>1.530769127897027</v>
@@ -18841,7 +18844,7 @@
         <v>1.431193121765403</v>
       </c>
       <c r="D346" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E346">
         <v>1.572471675023835</v>
@@ -18891,7 +18894,7 @@
         <v>1.471193121765403</v>
       </c>
       <c r="D347" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E347">
         <v>1.572471675023835</v>
@@ -18941,7 +18944,7 @@
         <v>2.306011000659936</v>
       </c>
       <c r="D348" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E348">
         <v>2.348379970519409</v>
@@ -18977,7 +18980,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -18991,7 +18994,7 @@
         <v>2.400485390479259</v>
       </c>
       <c r="D349" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E349">
         <v>2.364696230398958</v>
@@ -19027,7 +19030,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19077,7 +19080,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -19091,7 +19094,7 @@
         <v>2.315116384839492</v>
       </c>
       <c r="D351" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E351">
         <v>2.323814331699535</v>
@@ -19127,7 +19130,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -19141,7 +19144,7 @@
         <v>2.158186337006185</v>
       </c>
       <c r="D352" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E352">
         <v>2.199105803820263</v>
@@ -19177,7 +19180,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -19227,7 +19230,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -19277,7 +19280,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -19291,7 +19294,7 @@
         <v>2.249949180664442</v>
       </c>
       <c r="D355" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E355">
         <v>2.193589002935801</v>
@@ -19327,7 +19330,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -19341,7 +19344,7 @@
         <v>3.29910210514231</v>
       </c>
       <c r="D356" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E356">
         <v>3.35230135785332</v>
@@ -19377,7 +19380,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -19391,7 +19394,7 @@
         <v>3.804045197377832</v>
       </c>
       <c r="D357" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E357">
         <v>3.415154291605215</v>
@@ -19427,7 +19430,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -19441,7 +19444,7 @@
         <v>3.427249571448392</v>
       </c>
       <c r="D358" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E358">
         <v>3.291626526785035</v>
@@ -19477,7 +19480,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -19527,7 +19530,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -19541,7 +19544,7 @@
         <v>3.442581197445604</v>
       </c>
       <c r="D360" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E360">
         <v>3.306414237004073</v>
@@ -19577,7 +19580,7 @@
         <v>1</v>
       </c>
       <c r="P360" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="361" spans="1:16">
@@ -19591,7 +19594,7 @@
         <v>3.36022431872702</v>
       </c>
       <c r="D361" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E361">
         <v>3.226979110080385</v>
@@ -19627,7 +19630,7 @@
         <v>1</v>
       </c>
       <c r="P361" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="362" spans="1:16">
@@ -19641,7 +19644,7 @@
         <v>3.251003700388559</v>
       </c>
       <c r="D362" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E362">
         <v>3.121633280862579</v>
@@ -19677,7 +19680,7 @@
         <v>1</v>
       </c>
       <c r="P362" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -19691,7 +19694,7 @@
         <v>2.99001278638902</v>
       </c>
       <c r="D363" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E363">
         <v>3.032275977245447</v>
@@ -19777,7 +19780,7 @@
         <v>1</v>
       </c>
       <c r="P364" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -19791,7 +19794,7 @@
         <v>2.786342722576059</v>
       </c>
       <c r="D365" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E365">
         <v>2.830017022419643</v>
@@ -19827,7 +19830,7 @@
         <v>1</v>
       </c>
       <c r="P365" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -19841,7 +19844,7 @@
         <v>2.881784622628198</v>
       </c>
       <c r="D366" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E366">
         <v>2.846342722576059</v>
@@ -19877,7 +19880,7 @@
         <v>1</v>
       </c>
       <c r="P366" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -19891,7 +19894,7 @@
         <v>2.713139299753176</v>
       </c>
       <c r="D367" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E367">
         <v>2.672915915531583</v>
@@ -19927,7 +19930,7 @@
         <v>1</v>
       </c>
       <c r="P367" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -19941,7 +19944,7 @@
         <v>2.722022378645214</v>
       </c>
       <c r="D368" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E368">
         <v>2.672915915531583</v>
@@ -19977,7 +19980,7 @@
         <v>1</v>
       </c>
       <c r="P368" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -19991,7 +19994,7 @@
         <v>2.643362683974768</v>
       </c>
       <c r="D369" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E369">
         <v>2.68802760764238</v>
@@ -20027,7 +20030,7 @@
         <v>1</v>
       </c>
       <c r="P369" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20041,7 +20044,7 @@
         <v>2.738474376085565</v>
       </c>
       <c r="D370" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E370">
         <v>2.678250991863972</v>
@@ -20077,7 +20080,7 @@
         <v>1</v>
       </c>
       <c r="P370" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -20091,7 +20094,7 @@
         <v>2.26156876679942</v>
       </c>
       <c r="D371" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E371">
         <v>2.319500204055783</v>
@@ -20127,7 +20130,7 @@
         <v>1</v>
       </c>
       <c r="P371" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -20141,7 +20144,7 @@
         <v>2.341086491507057</v>
       </c>
       <c r="D372" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E372">
         <v>2.284741341701965</v>
@@ -20177,7 +20180,7 @@
         <v>1</v>
       </c>
       <c r="P372" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="373" spans="1:16">
@@ -20191,7 +20194,7 @@
         <v>2.25156876679942</v>
       </c>
       <c r="D373" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E373">
         <v>2.298948197976329</v>
@@ -20227,7 +20230,7 @@
         <v>1</v>
       </c>
       <c r="P373" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="374" spans="1:16">
@@ -20241,7 +20244,7 @@
         <v>2.345775623073784</v>
       </c>
       <c r="D374" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E374">
         <v>2.287361910525056</v>
@@ -20277,7 +20280,7 @@
         <v>1</v>
       </c>
       <c r="P374" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="375" spans="1:16">
@@ -20291,7 +20294,7 @@
         <v>1.450725995788351</v>
       </c>
       <c r="D375" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E375">
         <v>1.543612412630503</v>
@@ -20327,7 +20330,7 @@
         <v>1</v>
       </c>
       <c r="P375" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="376" spans="1:16">
@@ -20341,7 +20344,7 @@
         <v>1.378039753255653</v>
       </c>
       <c r="D376" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E376">
         <v>1.473954763536668</v>
@@ -20377,7 +20380,7 @@
         <v>1</v>
       </c>
       <c r="P376" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="377" spans="1:16">
@@ -20391,7 +20394,7 @@
         <v>2.300473418774809</v>
       </c>
       <c r="D377" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E377">
         <v>2.269274816103397</v>
@@ -20441,7 +20444,7 @@
         <v>2.307737312105645</v>
       </c>
       <c r="D378" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E378">
         <v>2.269274816103397</v>
@@ -20491,7 +20494,7 @@
         <v>2.548688372146674</v>
       </c>
       <c r="D379" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E379">
         <v>2.44021981851742</v>
@@ -20527,7 +20530,7 @@
         <v>1</v>
       </c>
       <c r="P379" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="380" spans="1:16">
@@ -20541,7 +20544,7 @@
         <v>4.064626779899114</v>
       </c>
       <c r="D380" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E380">
         <v>3.971827788774664</v>
@@ -20577,7 +20580,7 @@
         <v>1</v>
       </c>
       <c r="P380" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -20591,7 +20594,7 @@
         <v>2.704221825320051</v>
       </c>
       <c r="D381" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E381">
         <v>2.757514946748523</v>
@@ -20627,7 +20630,7 @@
         <v>1</v>
       </c>
       <c r="P381" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -20641,7 +20644,7 @@
         <v>2.699698304540886</v>
       </c>
       <c r="D382" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E382">
         <v>2.757514946748523</v>
@@ -20677,7 +20680,7 @@
         <v>1</v>
       </c>
       <c r="P382" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -20691,7 +20694,7 @@
         <v>2.597723564836138</v>
       </c>
       <c r="D383" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E383">
         <v>2.648687698460786</v>
@@ -20727,7 +20730,7 @@
         <v>1</v>
       </c>
       <c r="P383" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -20741,7 +20744,7 @@
         <v>2.594470401040876</v>
       </c>
       <c r="D384" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E384">
         <v>2.648687698460786</v>
@@ -20777,7 +20780,7 @@
         <v>1</v>
       </c>
       <c r="P384" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -20791,7 +20794,7 @@
         <v>2.5327482758737</v>
       </c>
       <c r="D385" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E385">
         <v>2.582291478725809</v>
@@ -20827,7 +20830,7 @@
         <v>1</v>
       </c>
       <c r="P385" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -20841,7 +20844,7 @@
         <v>2.530270165227095</v>
       </c>
       <c r="D386" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E386">
         <v>2.582291478725809</v>
@@ -20877,7 +20880,7 @@
         <v>1</v>
       </c>
       <c r="P386" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -20891,7 +20894,7 @@
         <v>2.615226386520305</v>
       </c>
       <c r="D387" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E387">
         <v>2.605226386520305</v>
@@ -20927,7 +20930,7 @@
         <v>1</v>
       </c>
       <c r="P387" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -20941,7 +20944,7 @@
         <v>2.519210324106</v>
       </c>
       <c r="D388" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E388">
         <v>2.474919909368535</v>
@@ -20977,7 +20980,7 @@
         <v>1</v>
       </c>
       <c r="P388" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -20991,7 +20994,7 @@
         <v>2.443973795685154</v>
       </c>
       <c r="D389" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E389">
         <v>2.491575608314453</v>
@@ -21027,7 +21030,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21041,7 +21044,7 @@
         <v>2.442554625160083</v>
       </c>
       <c r="D390" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E390">
         <v>2.491575608314453</v>
@@ -21077,7 +21080,7 @@
         <v>1</v>
       </c>
       <c r="P390" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -21127,7 +21130,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -21141,7 +21144,7 @@
         <v>2.457705873063223</v>
       </c>
       <c r="D392" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E392">
         <v>2.413049360402885</v>
@@ -21177,7 +21180,7 @@
         <v>1</v>
       </c>
       <c r="P392" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -21191,7 +21194,7 @@
         <v>2.382591377283335</v>
       </c>
       <c r="D393" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E393">
         <v>2.428850830862097</v>
@@ -21227,7 +21230,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -21241,7 +21244,7 @@
         <v>2.381904402604011</v>
       </c>
       <c r="D394" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E394">
         <v>2.428850830862097</v>
@@ -21277,7 +21280,7 @@
         <v>1</v>
       </c>
       <c r="P394" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -21291,7 +21294,7 @@
         <v>2.46327835196266</v>
       </c>
       <c r="D395" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E395">
         <v>2.453507343522435</v>
@@ -21327,7 +21330,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -21341,7 +21344,7 @@
         <v>2.467705873063223</v>
       </c>
       <c r="D396" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E396">
         <v>2.453507343522435</v>
@@ -21377,7 +21380,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -21391,7 +21394,7 @@
         <v>2.447999298642713</v>
       </c>
       <c r="D397" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E397">
         <v>2.403285008753682</v>
@@ -21427,7 +21430,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -21441,7 +21444,7 @@
         <v>2.372904061939057</v>
       </c>
       <c r="D398" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E398">
         <v>2.418951665679276</v>
@@ -21477,7 +21480,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -21491,7 +21494,7 @@
         <v>2.37233264171712</v>
       </c>
       <c r="D399" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E399">
         <v>2.418951665679276</v>
@@ -21527,7 +21530,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -21577,7 +21580,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -21627,7 +21630,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -21641,7 +21644,7 @@
         <v>2.414261420787727</v>
       </c>
       <c r="D402" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E402">
         <v>2.369346310197177</v>
@@ -21677,7 +21680,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -21727,7 +21730,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -21777,7 +21780,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -21791,7 +21794,7 @@
         <v>2.424261420787727</v>
       </c>
       <c r="D405" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E405">
         <v>2.394544385485897</v>
@@ -21827,7 +21830,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -21841,7 +21844,7 @@
         <v>2.414374606666995</v>
       </c>
       <c r="D406" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E406">
         <v>2.394544385485897</v>
@@ -21877,7 +21880,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -21891,7 +21894,7 @@
         <v>2.397600622679596</v>
       </c>
       <c r="D407" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E407">
         <v>2.352586340671736</v>
@@ -21927,7 +21930,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -21941,7 +21944,7 @@
         <v>2.322605383348882</v>
       </c>
       <c r="D408" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E408">
         <v>2.367553015986731</v>
@@ -21977,7 +21980,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -21991,7 +21994,7 @@
         <v>2.322633947364601</v>
       </c>
       <c r="D409" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E409">
         <v>2.367553015986731</v>
@@ -22027,7 +22030,7 @@
         <v>1</v>
       </c>
       <c r="P409" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="410" spans="1:16">
@@ -22041,7 +22044,7 @@
         <v>2.402576819333163</v>
       </c>
       <c r="D410" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E410">
         <v>2.35256729799459</v>
@@ -22077,7 +22080,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -22091,7 +22094,7 @@
         <v>2.407600622679595</v>
       </c>
       <c r="D411" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E411">
         <v>2.35256729799459</v>
@@ -22127,7 +22130,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -22141,7 +22144,7 @@
         <v>2.39758158000245</v>
       </c>
       <c r="D412" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E412">
         <v>2.35256729799459</v>
@@ -22177,7 +22180,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -22191,7 +22194,7 @@
         <v>2.378737718650321</v>
       </c>
       <c r="D413" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E413">
         <v>2.33361115745181</v>
@@ -22227,7 +22230,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -22241,7 +22244,7 @@
         <v>2.30377990571649</v>
       </c>
       <c r="D414" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E414">
         <v>2.348315847988621</v>
@@ -22277,7 +22280,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -22291,7 +22294,7 @@
         <v>2.304033028113511</v>
       </c>
       <c r="D415" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E415">
         <v>2.348315847988621</v>
@@ -22327,7 +22330,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -22341,7 +22344,7 @@
         <v>2.383526783319471</v>
       </c>
       <c r="D416" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E416">
         <v>2.333442409187131</v>
@@ -22377,7 +22380,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -22391,7 +22394,7 @@
         <v>2.38873771865032</v>
       </c>
       <c r="D417" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E417">
         <v>2.333442409187131</v>
@@ -22427,7 +22430,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -22441,7 +22444,7 @@
         <v>2.378568970385641</v>
       </c>
       <c r="D418" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E418">
         <v>2.333442409187131</v>
@@ -22477,7 +22480,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -22491,7 +22494,7 @@
         <v>2.29477967980894</v>
       </c>
       <c r="D419" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E419">
         <v>2.33911879805526</v>
@@ -22541,7 +22544,7 @@
         <v>2.295140160765494</v>
       </c>
       <c r="D420" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E420">
         <v>2.33911879805526</v>
@@ -22591,7 +22594,7 @@
         <v>2.374419198852388</v>
       </c>
       <c r="D421" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E421">
         <v>2.324299038533536</v>
@@ -22641,7 +22644,7 @@
         <v>2.379719599649515</v>
       </c>
       <c r="D422" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E422">
         <v>2.324299038533536</v>
@@ -22691,7 +22694,7 @@
         <v>2.369479279011813</v>
       </c>
       <c r="D423" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E423">
         <v>2.324299038533536</v>
@@ -22741,7 +22744,7 @@
         <v>2.280590400920047</v>
       </c>
       <c r="D424" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E424">
         <v>2.324619216844741</v>
@@ -22777,7 +22780,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -22791,7 +22794,7 @@
         <v>2.281120137688396</v>
       </c>
       <c r="D425" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E425">
         <v>2.324619216844741</v>
@@ -22827,7 +22830,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -22841,7 +22844,7 @@
         <v>2.360060664151698</v>
       </c>
       <c r="D426" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E426">
         <v>2.309884085228915</v>
@@ -22877,7 +22880,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -22927,7 +22930,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -22941,7 +22944,7 @@
         <v>2.281700069738552</v>
       </c>
       <c r="D428" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E428">
         <v>2.325753152774585</v>
@@ -22977,7 +22980,7 @@
         <v>1</v>
       </c>
       <c r="P428" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -22991,7 +22994,7 @@
         <v>2.282216569900716</v>
       </c>
       <c r="D429" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E429">
         <v>2.325753152774585</v>
@@ -23027,7 +23030,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23041,7 +23044,7 @@
         <v>2.361183569576388</v>
       </c>
       <c r="D430" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E430">
         <v>2.311011402855666</v>
@@ -23077,7 +23080,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23091,7 +23094,7 @@
         <v>2.255753152774584</v>
       </c>
       <c r="D431" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E431">
         <v>2.30032273597278</v>
@@ -23127,7 +23130,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -23141,7 +23144,7 @@
         <v>2.248769782041177</v>
       </c>
       <c r="D432" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E432">
         <v>2.297801715354081</v>
@@ -23177,7 +23180,7 @@
         <v>1</v>
       </c>
       <c r="P432" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -23191,7 +23194,7 @@
         <v>2.343406757033516</v>
       </c>
       <c r="D433" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E433">
         <v>2.293164740361742</v>
@@ -23227,7 +23230,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -23241,7 +23244,7 @@
         <v>2.237801715354081</v>
       </c>
       <c r="D434" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E434">
         <v>2.26243869034642</v>
@@ -23277,7 +23280,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -23291,7 +23294,7 @@
         <v>2.228095614122554</v>
       </c>
       <c r="D435" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E435">
         <v>2.276800683120539</v>
@@ -23327,7 +23330,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -23341,7 +23344,7 @@
         <v>2.322610014996799</v>
       </c>
       <c r="D436" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E436">
         <v>2.263257480497806</v>
@@ -23377,7 +23380,7 @@
         <v>1</v>
       </c>
       <c r="P436" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -23427,7 +23430,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -23441,7 +23444,7 @@
         <v>2.224983216186275</v>
       </c>
       <c r="D438" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E438">
         <v>2.273639077311749</v>
@@ -23491,7 +23494,7 @@
         <v>2.319479164108328</v>
       </c>
       <c r="D439" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E439">
         <v>2.26015123354559</v>
@@ -23641,7 +23644,7 @@
         <v>2.3116287572162</v>
       </c>
       <c r="D442" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E442">
         <v>2.252362519438469</v>
@@ -23677,7 +23680,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -23727,7 +23730,7 @@
         <v>1</v>
       </c>
       <c r="P443" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -23777,7 +23780,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -23841,7 +23844,7 @@
         <v>2.185149484739352</v>
       </c>
       <c r="D446" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E446">
         <v>2.165149484739352</v>
@@ -23941,7 +23944,7 @@
         <v>2.20020073233055</v>
       </c>
       <c r="D448" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E448">
         <v>2.205687152603988</v>
@@ -24027,7 +24030,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24077,7 +24080,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24127,7 +24130,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -24177,7 +24180,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -24227,7 +24230,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -24341,7 +24344,7 @@
         <v>2.142114930387524</v>
       </c>
       <c r="D456" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E456">
         <v>2.162114930387524</v>
@@ -24377,7 +24380,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -24391,7 +24394,7 @@
         <v>2.115413806995409</v>
       </c>
       <c r="D457" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E457">
         <v>2.141244762127619</v>
@@ -24477,7 +24480,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -24491,7 +24494,7 @@
         <v>2.073994682974101</v>
       </c>
       <c r="D459" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E459">
         <v>2.082201671198685</v>
@@ -24541,7 +24544,7 @@
         <v>2.083994682974101</v>
       </c>
       <c r="D460" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E460">
         <v>2.082201671198685</v>
@@ -24627,7 +24630,7 @@
         <v>1</v>
       </c>
       <c r="P461" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -24641,7 +24644,7 @@
         <v>2.057461365020192</v>
       </c>
       <c r="D462" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E462">
         <v>2.066125824243982</v>
@@ -24677,7 +24680,7 @@
         <v>1</v>
       </c>
       <c r="P462" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -24727,7 +24730,7 @@
         <v>1</v>
       </c>
       <c r="P463" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -24777,7 +24780,7 @@
         <v>1</v>
       </c>
       <c r="P464" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -24827,7 +24830,7 @@
         <v>1</v>
       </c>
       <c r="P465" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="466" spans="1:16">
@@ -24877,7 +24880,7 @@
         <v>1</v>
       </c>
       <c r="P466" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="467" spans="1:16">
@@ -24891,7 +24894,7 @@
         <v>2.057577737614682</v>
       </c>
       <c r="D467" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E467">
         <v>2.099815205781953</v>
@@ -24927,7 +24930,7 @@
         <v>1</v>
       </c>
       <c r="P467" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="468" spans="1:16">
@@ -24991,7 +24994,7 @@
         <v>2.075267052489131</v>
       </c>
       <c r="D469" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E469">
         <v>2.105974841560053</v>
@@ -25041,7 +25044,7 @@
         <v>2.0673904197019</v>
       </c>
       <c r="D470" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E470">
         <v>2.109513786914668</v>
@@ -25091,7 +25094,7 @@
         <v>2.101281730695467</v>
       </c>
       <c r="D471" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E471">
         <v>2.131889846669813</v>
@@ -25141,7 +25144,7 @@
         <v>2.093106078618507</v>
       </c>
       <c r="D472" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E472">
         <v>2.134930426541548</v>
@@ -25191,7 +25194,7 @@
         <v>2.114232378900782</v>
       </c>
       <c r="D473" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E473">
         <v>2.144790875533345</v>
@@ -25227,7 +25230,7 @@
         <v>1</v>
       </c>
       <c r="P473" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -25241,7 +25244,7 @@
         <v>2.164790875533345</v>
       </c>
       <c r="D474" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E474">
         <v>2.134232378900781</v>
@@ -25277,7 +25280,7 @@
         <v>1</v>
       </c>
       <c r="P474" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -25291,7 +25294,7 @@
         <v>2.105907868798473</v>
       </c>
       <c r="D475" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E475">
         <v>2.147583358696166</v>
@@ -25327,7 +25330,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -25341,7 +25344,7 @@
         <v>2.178667208693582</v>
       </c>
       <c r="D476" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E476">
         <v>2.148162082573172</v>
@@ -25377,7 +25380,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -25391,7 +25394,7 @@
         <v>2.119677460934401</v>
       </c>
       <c r="D477" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E477">
         <v>2.161192839295628</v>
@@ -25427,7 +25430,7 @@
         <v>1</v>
       </c>
       <c r="P477" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -25441,7 +25444,7 @@
         <v>2.191253934723685</v>
       </c>
       <c r="D478" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E478">
         <v>2.160797219088007</v>
@@ -25491,7 +25494,7 @@
         <v>2.132167365995042</v>
       </c>
       <c r="D479" t="s"